--- a/Figure_Plot/figure_plot_4_c/input/dsfunction_May2025_exact_V5_k20_classified.xlsx
+++ b/Figure_Plot/figure_plot_4_c/input/dsfunction_May2025_exact_V5_k20_classified.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[[0.060170960951030736,33.55936901291673,-1860.0,1.0,1.0,4.0,-1.0],[33.55936901291673,34.67600894798226,-1187.2576,0.0,1.0,5.0,-1.0],[34.67600894798226,38.58424872071159,0.0,0.0,0.0,6.0,-1.0],[38.58424872071159,55.333847746694445,788.5,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[0.060170960951030736,33.55936901291673,-1860.0,1.0,1.0,4.0,-1.0],[33.55936901291673,34.67600894798226,-1187.2576,0.0,1.0,5.0,-1.0],[34.67600894798226,38.58424872071159,0.0,0.0,0.0,6.0,-1.0],[38.58424872071159,55.333847746694445,788.5001,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -494,7 +494,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[[0.06465534703439174,33.23411054699684,-1860.0,1.0,1.0,1.0,-1.0],[33.23411054699684,37.30755241365889,0.0,0.0,0.0,3.0,-1.0],[37.30755241365889,57.67476174696917,788.5,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[0.06465534703439174,33.23411054699684,-1860.0,1.0,1.0,1.0,-1.0],[33.23411054699684,37.30755241365889,0.0,0.0,0.0,3.0,-1.0],[37.30755241365889,40.79907401365494,788.5,0.0,0.0,0.0,-1.0],[40.79907401365494,57.67476174696917,788.5001,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[[0.06616840205486296,32.800398540187444,-1860.0,1.0,1.0,2.0,-1.0],[32.800398540187444,33.395566360880764,-1187.2576,0.0,1.0,1.0,-1.0],[33.395566360880764,36.96657328504068,0.0,0.0,0.0,2.0,-1.0],[36.96657328504068,58.987782650693504,788.5,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[0.06616840205486296,32.800398540187444,-1860.0,1.0,1.0,2.0,-1.0],[32.800398540187444,33.395566360880764,-1187.2576,0.0,1.0,1.0,-1.0],[33.395566360880764,36.96657328504068,0.0,0.0,0.0,2.0,-1.0],[36.96657328504068,37.561741105734,788.5,0.0,0.0,0.0,-1.0],[37.561741105734,58.987782650693504,788.5001,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -540,7 +540,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[[0.0670736637155955,33.99047647618151,-1860.0,1.0,1.0,1.0,-1.0],[33.99047647618151,38.08468026389292,0.0,0.0,0.0,1.0,-1.0],[38.08468026389292,57.9708129470626,788.5,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[0.0670736637155955,33.99047647618151,-1860.0,1.0,1.0,1.0,-1.0],[33.99047647618151,38.08468026389292,0.0,0.0,0.0,1.0,-1.0],[38.08468026389292,42.17888405160432,788.5,0.0,0.0,0.0,-1.0],[42.17888405160432,57.9708129470626,788.5001,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[[0.06497865084935292,33.03424703297528,-1860.0,1.0,1.0,0.0,-1.0],[33.03424703297528,36.817605699776614,0.0,0.0,0.0,2.0,-1.0],[36.817605699776614,53.57247979561111,788.5,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[0.06497865084935292,33.03424703297528,-1860.0,1.0,1.0,0.0,-1.0],[33.03424703297528,36.817605699776614,0.0,0.0,0.0,2.0,-1.0],[36.817605699776614,40.600964366577955,788.5,0.0,0.0,0.0,-1.0],[40.600964366577955,53.57247979561111,788.5001,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -678,7 +678,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[[0.06779395822912662,19.75227599612784,-1860.0,8.0,0.0,0.0,1.0],[19.75227599612784,30.489266198618044,-733.6842,8.0,0.0,0.0,1.0],[30.489266198618044,34.068262932781444,0.0,8.0,8.0,1.0,-1.0],[34.068262932781444,36.454260755557044,227.85,8.0,8.0,0.0,-1.0],[36.454260755557044,59.12124007192525,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[0.06779395822912662,19.75227599612784,-1860.0,8.0,0.0,0.0,1.0],[19.75227599612784,30.489266198618044,-733.6842,8.0,0.0,0.0,1.0],[30.489266198618044,34.068262932781444,0.0,8.0,8.0,1.0,-1.0],[34.068262932781444,36.454260755557044,227.85,8.0,8.0,0.0,-1.0],[36.454260755557044,59.12124007192525,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -724,7 +724,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[0.06653263779102629,20.630675151460323,-1860.0,6.0,0.0,0.0,1.0],[20.630675151460323,31.190640226047257,-733.6842,6.0,0.0,0.0,1.0],[31.190640226047257,34.52536603907471,0.0,6.0,8.0,1.0,-1.0],[34.52536603907471,36.192728945588435,227.85,6.0,8.0,0.0,-1.0],[36.192728945588435,55.08950855274401,1860.0,6.0,8.0,0.0,-1.0]]</t>
+          <t>[[0.06653263779102629,20.630675151460323,-1860.0,5.0,0.0,0.0,1.0],[20.630675151460323,31.190640226047257,-733.6842,5.0,0.0,0.0,1.0],[31.190640226047257,34.52536603907471,0.0,5.0,8.0,1.0,-1.0],[34.52536603907471,36.192728945588435,227.85,5.0,8.0,0.0,-1.0],[36.192728945588435,55.08950855274401,1860.0,6.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -747,7 +747,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[[0.06338621875704924,20.490649315513156,-1860.0,5.0,0.0,0.0,1.0],[20.490649315513156,32.16337108508807,-733.6842,5.0,0.0,0.0,1.0],[32.16337108508807,35.66518761596055,0.0,5.0,8.0,1.0,-1.0],[35.66518761596055,36.83245979291804,227.85,5.0,8.0,0.0,-1.0],[36.83245979291804,57.84335897815289,1860.0,5.0,8.0,0.0,-1.0]]</t>
+          <t>[[0.06338621875704924,20.490649315513156,-1860.0,4.0,0.0,0.0,1.0],[20.490649315513156,32.16337108508807,-733.6842,4.0,0.0,0.0,1.0],[32.16337108508807,35.66518761596055,0.0,4.0,8.0,1.0,-1.0],[35.66518761596055,36.83245979291804,227.85,4.0,8.0,0.0,-1.0],[36.83245979291804,57.84335897815289,1860.0,5.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -770,7 +770,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[[0.06528634851762935,20.146638897019525,-1860.0,4.0,0.0,0.0,1.0],[20.146638897019525,30.47419163624907,-733.6842,4.0,0.0,0.0,1.0],[30.47419163624907,33.916709215992256,0.0,4.0,8.0,3.0,-1.0],[33.916709215992256,36.21172093582105,227.85,4.0,8.0,0.0,-1.0],[36.21172093582105,56.86682641428014,1860.0,4.0,8.0,0.0,-1.0]]</t>
+          <t>[[0.06528634851762935,20.146638897019525,-1860.0,3.0,0.0,0.0,1.0],[20.146638897019525,30.47419163624907,-733.6842,3.0,0.0,0.0,1.0],[30.47419163624907,33.916709215992256,0.0,3.0,8.0,3.0,-1.0],[33.916709215992256,36.21172093582105,227.85,3.0,8.0,0.0,-1.0],[36.21172093582105,56.86682641428014,1860.0,3.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -793,7 +793,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[[1.8166138653001007,30.920474953362262,-1860.0,4.0,8.0,0.0,-1.0],[30.920474953362262,32.01873386234574,-1607.5346,3.0,8.0,0.0,-1.0],[32.01873386234574,35.86264004378791,0.0,3.0,7.0,1.0,-1.0],[35.86264004378791,36.41176949827965,409.2,3.0,7.0,0.0,-1.0],[36.41176949827965,56.18042985998225,1860.0,3.0,7.0,0.0,-1.0]]</t>
+          <t>[[1.8166138653001007,30.920474953362262,-1860.0,3.0,8.0,0.0,-1.0],[30.920474953362262,32.01873386234574,-1607.5346,2.0,8.0,0.0,-1.0],[32.01873386234574,35.86264004378791,0.0,2.0,7.0,1.0,-1.0],[35.86264004378791,36.41176949827965,409.2,2.0,7.0,0.0,-1.0],[36.41176949827965,56.18042985998225,1860.0,2.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[[1.7155904815176586,31.762469445016727,-1860.0,3.0,8.0,0.0,-1.0],[31.762469445016727,33.4632361787997,-1607.5346,2.0,8.0,0.0,-1.0],[33.4632361787997,36.86476964636562,0.0,2.0,7.0,1.0,-1.0],[36.86476964636562,37.43169189095995,409.2,2.0,7.0,1.0,-1.0],[37.43169189095995,57.840892696355546,1860.0,2.0,7.0,1.0,-1.0]]</t>
+          <t>[[1.7155904815176586,31.762469445016727,-1860.0,3.0,8.0,0.0,-1.0],[31.762469445016727,33.4632361787997,-1607.5346,2.0,8.0,0.0,-1.0],[33.4632361787997,36.86476964636562,0.0,1.0,7.0,1.0,-1.0],[36.86476964636562,37.43169189095995,409.2,2.0,7.0,1.0,-1.0],[37.43169189095995,57.840892696355546,1860.0,1.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -839,7 +839,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[[1.9317174431021071,32.937582659746525,-1860.0,2.0,8.0,0.0,-1.0],[32.937582659746525,36.32004068338047,0.0,1.0,7.0,1.0,-1.0],[36.32004068338047,36.88378368731946,409.2,1.0,7.0,1.0,-1.0],[36.88378368731946,57.74227483306207,1860.0,1.0,7.0,1.0,-1.0]]</t>
+          <t>[[1.9317174431021071,32.937582659746525,-1860.0,1.0,8.0,0.0,-1.0],[32.937582659746525,36.32004068338047,0.0,1.0,7.0,1.0,-1.0],[36.32004068338047,36.88378368731946,409.2,1.0,7.0,1.0,-1.0],[36.88378368731946,57.74227483306207,1860.0,1.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -885,7 +885,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[[-1.9424211562153533,28.423180474808113,-733.6842,0.0,0.0,0.0,1.0],[28.423180474808113,31.400200242555513,0.0,0.0,8.0,3.0,-1.0],[31.400200242555513,35.56802791740187,227.85,0.0,8.0,0.0,-1.0],[35.56802791740187,57.00257024518314,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-1.9424211562153533,28.423180474808113,-733.6843,0.0,0.0,0.0,1.0],[28.423180474808113,31.400200242555513,0.0,0.0,8.0,3.0,-1.0],[31.400200242555513,35.56802791740187,227.85,0.0,8.0,0.0,-1.0],[35.56802791740187,57.00257024518314,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -908,7 +908,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[[-2.012018185287039,28.64544107970071,-733.6842,0.0,0.0,0.0,1.0],[28.64544107970071,31.94701361593016,0.0,0.0,8.0,2.0,-1.0],[31.94701361593016,32.41866683539151,227.85,0.0,8.0,1.0,-1.0],[32.41866683539151,44.68165054138661,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[-2.012018185287039,28.64544107970071,-733.6843,0.0,0.0,0.0,1.0],[28.64544107970071,31.94701361593016,0.0,0.0,8.0,2.0,-1.0],[31.94701361593016,32.41866683539151,227.85,0.0,8.0,1.0,-1.0],[32.41866683539151,44.68165054138661,1860.0,0.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[[-1.8995333109743828,27.960678930205635,-1860.0,1.0,2.0,0.0,-1.0],[27.960678930205635,28.38725339079392,-1808.4765,0.0,2.0,1.0,-1.0],[28.38725339079392,31.37327461491192,0.0,0.0,1.0,2.0,-1.0],[31.37327461491192,32.2264235360885,227.85,0.0,1.0,1.0,-1.0],[32.2264235360885,40.33133828726593,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[-1.8995333109743828,27.960678930205635,-1860.0,0.0,2.0,0.0,-1.0],[27.960678930205635,28.38725339079392,-1808.4765,0.0,2.0,1.0,-1.0],[28.38725339079392,31.37327461491192,0.0,0.0,1.0,2.0,-1.0],[31.37327461491192,32.2264235360885,227.85,0.0,1.0,1.0,-1.0],[32.2264235360885,40.33133828726593,1860.0,0.0,1.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[[-1.908971127352784,25.94695106833728,-1860.0,1.0,1.0,0.0,-1.0],[25.94695106833728,27.936659796600857,-1808.4765,0.0,1.0,0.0,-1.0],[27.936659796600857,31.120193761822577,0.0,0.0,0.0,1.0,-1.0],[31.120193761822577,37.487261692266024,227.85,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-1.908971127352784,25.94695106833728,-1860.0,1.0,1.0,0.0,-1.0],[25.94695106833728,27.936659796600857,-1808.4765,0.0,1.0,0.0,-1.0],[27.936659796600857,31.120193761822577,0.0,0.0,0.0,1.0,-1.0],[31.120193761822577,34.70166947269701,227.85,0.0,0.0,0.0,-1.0],[34.70166947269701,37.487261692266024,227.8501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[[-1.988261951986372,10.563100188026741,-1860.0,8.0,0.0,0.0,1.0],[10.563100188026741,28.377936773851808,-733.6842,8.0,0.0,0.0,1.0],[28.377936773851808,31.616997971274543,0.0,8.0,8.0,4.0,-1.0],[31.616997971274543,38.09512036612002,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-1.988261951986372,10.563100188026741,-1860.0,6.0,0.0,0.0,1.0],[10.563100188026741,28.377936773851808,-733.6842,7.0,0.0,0.0,1.0],[28.377936773851808,31.616997971274543,0.0,6.0,8.0,4.0,-1.0],[31.616997971274543,38.09512036612002,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[[-2.1054115346025535,28.216056015357637,-1860.0,8.0,0.0,0.0,1.0],[28.216056015357637,31.163976471603767,0.0,7.0,7.0,3.0,-1.0],[31.163976471603767,31.585107965353217,1071.35,7.0,7.0,0.0,-1.0],[31.585107965353217,39.58660634659271,1860.0,7.0,7.0,0.0,-1.0]]</t>
+          <t>[[-2.1054115346025535,28.216056015357637,-1860.0,7.0,0.0,0.0,1.0],[28.216056015357637,31.163976471603767,0.0,6.0,7.0,3.0,-1.0],[31.163976471603767,31.585107965353217,1071.35,7.0,7.0,0.0,-1.0],[31.585107965353217,39.58660634659271,1860.0,7.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[[-2.0111242358530035,28.172706093507696,-1860.0,7.0,0.0,0.0,1.0],[28.172706093507696,31.34995139133514,0.0,6.0,7.0,4.0,-1.0],[31.34995139133514,37.30728632476159,1860.0,6.0,7.0,1.0,-1.0]]</t>
+          <t>[[-2.0111242358530035,28.172706093507696,-1860.0,6.0,0.0,0.0,1.0],[28.172706093507696,31.34995139133514,0.0,5.0,7.0,4.0,-1.0],[31.34995139133514,37.30728632476159,1860.0,6.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[[-2.018065211083488,27.27166340726742,-1860.0,6.0,0.0,0.0,1.0],[27.27166340726742,28.45908483774111,-873.8504,5.0,8.0,3.0,-1.0],[28.45908483774111,31.625541985670935,0.0,5.0,7.0,4.0,-1.0],[31.625541985670935,32.41715627265339,1071.35,5.0,7.0,4.0,-1.0],[32.41715627265339,37.166841994548136,1860.0,5.0,8.0,3.0,-1.0]]</t>
+          <t>[[-2.018065211083488,27.27166340726742,-1860.0,5.0,0.0,0.0,1.0],[27.27166340726742,28.45908483774111,-873.8504,4.0,8.0,3.0,-1.0],[28.45908483774111,31.625541985670935,0.0,4.0,7.0,4.0,-1.0],[31.625541985670935,32.41715627265339,1071.35,5.0,7.0,4.0,-1.0],[32.41715627265339,37.166841994548136,1860.0,4.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[[-2.0098448650053102,28.070507245416543,-1860.0,5.0,0.0,0.0,1.0],[28.070507245416543,28.906072581817153,-873.8504,4.0,8.0,3.0,-1.0],[28.906072581817153,31.830551259219273,0.0,4.0,7.0,4.0,-1.0],[31.830551259219273,32.24833392741957,1071.35,4.0,7.0,4.0,-1.0],[32.24833392741957,39.35063928682474,1860.0,4.0,7.0,4.0,-1.0]]</t>
+          <t>[[-2.0098448650053102,28.070507245416543,-1860.0,4.0,0.0,0.0,1.0],[28.070507245416543,28.906072581817153,-873.8504,3.0,8.0,3.0,-1.0],[28.906072581817153,31.830551259219273,0.0,3.0,7.0,4.0,-1.0],[31.830551259219273,32.24833392741957,1071.35,3.0,7.0,4.0,-1.0],[32.24833392741957,39.35063928682474,1860.0,2.0,7.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[[-1.9825007850115588,27.619586495747388,-1860.0,4.0,0.0,0.0,1.0],[27.619586495747388,28.430602585631195,-873.8504,3.0,8.0,4.0,-1.0],[28.430602585631195,31.269158900224518,0.0,3.0,7.0,5.0,-1.0],[31.269158900224518,38.162795664236874,1860.0,3.0,7.0,2.0,-1.0]]</t>
+          <t>[[-1.9825007850115588,27.619586495747388,-1860.0,3.0,0.0,0.0,1.0],[27.619586495747388,28.430602585631195,-873.8504,2.0,8.0,4.0,-1.0],[28.430602585631195,31.269158900224518,0.0,2.0,7.0,5.0,-1.0],[31.269158900224518,38.162795664236874,1860.0,2.0,7.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[[-2.012203340280024,27.527594329197264,-1860.0,2.0,0.0,0.0,1.0],[27.527594329197264,28.348144264460522,-873.8504,1.0,8.0,3.0,-1.0],[28.348144264460522,31.630344005513557,0.0,1.0,7.0,4.0,-1.0],[31.630344005513557,38.60501845525125,1860.0,1.0,7.0,4.0,-1.0]]</t>
+          <t>[[-2.012203340280024,27.527594329197264,-1860.0,1.0,0.0,0.0,1.0],[27.527594329197264,28.348144264460522,-873.8504,1.0,8.0,3.0,-1.0],[28.348144264460522,31.630344005513557,0.0,1.0,7.0,4.0,-1.0],[31.630344005513557,38.60501845525125,1860.0,1.0,7.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[[8.810626718004732,30.5894160099191,-0.0,0.0,0.0,1.0,1.0],[30.5894160099191,31.460567581595676,890.0,0.0,8.0,3.0,-1.0],[31.460567581595676,37.558628583331696,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[8.810626718004732,30.5894160099191,0.0,0.0,0.0,1.0,1.0],[30.5894160099191,31.460567581595676,890.0,0.0,8.0,3.0,-1.0],[31.460567581595676,37.558628583331696,1860.0,0.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[[9.00210244527421,27.343315870579815,-1860.0,1.0,8.0,1.0,-1.0],[27.343315870579815,27.93496791655742,-1074.7923,0.0,8.0,2.0,-1.0],[27.93496791655742,30.893228146445416,0.0,0.0,7.0,3.0,-1.0],[30.893228146445416,31.189054169434222,890.0,0.0,7.0,3.0,-1.0],[31.189054169434222,38.288878721165425,1860.0,0.0,7.0,3.0,-1.0]]</t>
+          <t>[[9.00210244527421,27.343315870579815,-1860.0,0.0,8.0,1.0,-1.0],[27.343315870579815,27.93496791655742,-1074.7923,0.0,8.0,2.0,-1.0],[27.93496791655742,30.893228146445416,0.0,0.0,7.0,3.0,-1.0],[30.893228146445416,31.189054169434222,890.0,0.0,7.0,3.0,-1.0],[31.189054169434222,38.288878721165425,1860.0,0.0,7.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[[9.000932317558064,27.535632913147765,-1860.0,1.0,6.0,1.0,-1.0],[27.535632913147765,30.855280781014578,-0.0,0.0,5.0,3.0,-1.0],[30.855280781014578,36.38802722745927,1860.0,0.0,5.0,2.0,-1.0]]</t>
+          <t>[[9.000932317558064,27.535632913147765,-1860.0,1.0,6.0,1.0,-1.0],[27.535632913147765,30.855280781014578,0.0,0.0,5.0,3.0,-1.0],[30.855280781014578,36.38802722745927,1860.0,0.0,5.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[[9.123094998532288,27.032695158751824,-1860.0,1.0,5.0,1.0,-1.0],[27.032695158751824,30.719965779973496,-0.0,0.0,4.0,3.0,-1.0],[30.719965779973496,35.19736582002838,1860.0,0.0,4.0,3.0,-1.0]]</t>
+          <t>[[9.123094998532288,27.032695158751824,-1860.0,1.0,5.0,1.0,-1.0],[27.032695158751824,30.719965779973496,0.0,0.0,4.0,3.0,-1.0],[30.719965779973496,35.19736582002838,1860.0,0.0,4.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[[8.912042912743143,27.59932076443066,-1860.0,1.0,4.0,1.0,-1.0],[27.59932076443066,30.757733922462357,-0.0,0.0,3.0,3.0,-1.0],[30.757733922462357,34.96895146650461,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[8.912042912743143,27.59932076443066,-1860.0,0.0,4.0,1.0,-1.0],[27.59932076443066,30.757733922462357,0.0,0.0,3.0,3.0,-1.0],[30.757733922462357,34.96895146650461,1860.0,0.0,3.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[[9.097615965395647,27.415981424534454,-1860.0,1.0,3.0,1.0,-1.0],[27.415981424534454,31.48672930434308,-0.0,0.0,2.0,3.0,-1.0],[31.48672930434308,34.28536847171151,1860.0,0.0,3.0,3.0,-1.0]]</t>
+          <t>[[9.097615965395647,27.415981424534454,-1860.0,1.0,3.0,1.0,-1.0],[27.415981424534454,31.48672930434308,0.0,0.0,2.0,3.0,-1.0],[31.48672930434308,34.28536847171151,1860.0,0.0,3.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>[[8.817587694406777,27.848276135806955,-1860.0,1.0,2.0,0.0,-1.0],[27.848276135806955,31.497997206760417,-0.0,0.0,1.0,2.0,-1.0],[31.497997206760417,34.62632955329195,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[8.817587694406777,27.848276135806955,-1860.0,0.0,2.0,0.0,-1.0],[27.848276135806955,31.497997206760417,0.0,0.0,1.0,2.0,-1.0],[31.497997206760417,34.62632955329195,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>[[8.74419367151912,26.17242353912569,-1860.0,1.0,2.0,0.0,-1.0],[26.17242353912569,30.70853816220137,-0.0,0.0,1.0,1.0,-1.0],[30.70853816220137,32.37973828649241,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[8.74419367151912,26.17242353912569,-1860.0,0.0,2.0,0.0,-1.0],[26.17242353912569,30.70853816220137,0.0,0.0,1.0,1.0,-1.0],[30.70853816220137,32.37973828649241,1860.0,0.0,1.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>[[9.066043689600008,22.674963057544133,-1860.0,9.0,2.0,2.0,1.0],[22.674963057544133,23.567351212819155,-733.6842,9.0,2.0,2.0,1.0],[23.567351212819155,29.367874222106813,0.0,0.0,2.0,1.0,-1.0],[29.367874222106813,31.152650532656864,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[9.066043689600008,22.674963057544133,-1860.0,8.0,2.0,2.0,1.0],[22.674963057544133,23.567351212819155,-733.6842,9.0,2.0,2.0,1.0],[23.567351212819155,29.367874222106813,0.0,0.0,2.0,1.0,-1.0],[29.367874222106813,31.152650532656864,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>[[9.171067817334693,23.91575175274224,-1860.0,10.0,1.0,1.0,1.0],[23.91575175274224,24.585964658897126,-733.6842,9.0,1.0,2.0,1.0],[24.585964658897126,27.266816283516683,0.0,0.0,1.0,1.0,-1.0],[27.266816283516683,28.830646397878084,0.0,0.0,0.0,1.0,-1.0],[28.830646397878084,31.28809372044601,1860.0,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[9.171067817334693,23.91575175274224,-1860.0,10.0,1.0,1.0,1.0],[23.91575175274224,24.585964658897126,-733.6842,9.0,1.0,2.0,1.0],[24.585964658897126,27.49022058556831,0.0,0.0,1.0,1.0,-1.0],[27.49022058556831,28.830646397878084,0.0,0.0,0.0,1.0,-1.0],[28.830646397878084,31.28809372044601,1860.0,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>[[9.041946005126093,20.28750270023145,-1860.0,9.0,0.0,0.0,1.0],[20.28750270023145,22.756039535742385,-733.6842,8.0,0.0,1.0,1.0],[22.756039535742385,25.224576371253317,0.0,8.0,0.0,1.0,1.0],[25.224576371253317,27.69311320676425,1016.5,9.0,0.0,0.0,1.0],[27.69311320676425,36.19585119574635,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[9.041946005126093,20.28750270023145,-1860.0,9.0,0.0,0.0,1.0],[20.28750270023145,22.756039535742385,-733.6842,8.0,0.0,1.0,1.0],[22.756039535742385,25.224576371253317,0.0,8.0,0.0,1.0,1.0],[25.224576371253317,27.69311320676425,1016.5,8.0,0.0,0.0,1.0],[27.69311320676425,36.19585119574635,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>[[8.856569223926636,26.629476736272274,-1860.0,9.0,0.0,0.0,1.0],[26.629476736272274,26.894744012575934,-1275.7341,10.0,10.0,2.0,-1.0],[26.894744012575934,29.812684051916264,0.0,10.0,10.0,2.0,-1.0],[29.812684051916264,30.077951328219932,527.3,11.0,10.0,1.0,-1.0],[30.077951328219932,35.11802957798959,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[8.856569223926636,26.629476736272274,-1860.0,8.0,0.0,0.0,1.0],[26.629476736272274,26.894744012575934,-1275.7341,10.0,10.0,2.0,-1.0],[26.894744012575934,29.812684051916264,0.0,10.0,10.0,2.0,-1.0],[29.812684051916264,30.077951328219932,527.3,10.0,10.0,1.0,-1.0],[30.077951328219932,35.11802957798959,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[[8.883721641699175,26.023060795421237,-1860.0,8.0,0.0,0.0,1.0],[26.023060795421237,26.308716447983272,-1074.7923,8.0,9.0,5.0,-1.0],[26.308716447983272,28.879617321041582,0.0,8.0,9.0,5.0,-1.0],[28.879617321041582,37.16363124534058,1860.0,9.0,9.0,4.0,-1.0]]</t>
+          <t>[[8.883721641699175,26.023060795421237,-1860.0,8.0,0.0,0.0,1.0],[26.023060795421237,26.308716447983272,-1074.7923,8.0,9.0,5.0,-1.0],[26.308716447983272,28.879617321041582,0.0,8.0,9.0,5.0,-1.0],[28.879617321041582,37.16363124534058,1860.0,8.0,9.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>[[-5.818061373212677,25.915850407123074,-1860.0,7.0,0.0,0.0,1.0],[25.915850407123074,28.917706926884563,0.0,7.0,9.0,5.0,-1.0],[28.917706926884563,29.346543572564777,708.65,8.0,9.0,4.0,-1.0],[29.346543572564777,36.636766549128396,1860.0,8.0,9.0,4.0,-1.0]]</t>
+          <t>[[-5.818061373212677,25.915850407123074,-1860.0,6.0,0.0,0.0,1.0],[25.915850407123074,28.917706926884563,0.0,6.0,9.0,5.0,-1.0],[28.917706926884563,29.346543572564777,708.65,8.0,9.0,4.0,-1.0],[29.346543572564777,36.636766549128396,1860.0,8.0,9.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>[[-6.662870971355539,26.731532219809445,-1860.0,6.0,0.0,0.0,1.0],[26.731532219809445,29.439186532606605,0.0,6.0,8.0,6.0,-1.0],[29.439186532606605,29.890462251406134,890.0,6.0,8.0,5.0,-1.0],[29.890462251406134,38.013425189797616,1860.0,6.0,9.0,4.0,-1.0]]</t>
+          <t>[[-6.662870971355539,26.731532219809445,-1860.0,4.0,0.0,0.0,1.0],[26.731532219809445,29.439186532606605,0.0,5.0,8.0,6.0,-1.0],[29.439186532606605,29.890462251406134,890.0,5.0,8.0,5.0,-1.0],[29.890462251406134,38.013425189797616,1860.0,5.0,9.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>[[-6.50381465897646,26.412303512129107,-1860.0,5.0,0.0,0.0,1.0],[26.412303512129107,29.444051238415142,0.0,5.0,8.0,5.0,-1.0],[29.444051238415142,36.37376032706895,1860.0,5.0,8.0,5.0,-1.0]]</t>
+          <t>[[-6.50381465897646,26.412303512129107,-1860.0,4.0,0.0,0.0,1.0],[26.412303512129107,29.444051238415142,0.0,4.0,8.0,5.0,-1.0],[29.444051238415142,36.37376032706895,1860.0,4.0,8.0,5.0,-1.0]]</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>[[-7.334748459522696,25.94414888309117,-1860.0,4.0,0.0,0.0,1.0],[25.94414888309117,26.382029111283455,-1074.7923,4.0,9.0,5.0,-1.0],[26.382029111283455,29.009310480437183,0.0,4.0,8.0,6.0,-1.0],[29.009310480437183,30.32295116501405,890.0,4.0,8.0,6.0,-1.0],[30.32295116501405,36.015394131513794,1860.0,4.0,9.0,5.0,-1.0]]</t>
+          <t>[[-7.334748459522696,25.94414888309117,-1860.0,4.0,0.0,0.0,1.0],[25.94414888309117,26.382029111283455,-1074.7923,4.0,9.0,5.0,-1.0],[26.382029111283455,29.009310480437183,0.0,3.0,8.0,6.0,-1.0],[29.009310480437183,30.32295116501405,890.0,4.0,8.0,6.0,-1.0],[30.32295116501405,36.015394131513794,1860.0,3.0,9.0,5.0,-1.0]]</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>[[-7.005196674078064,25.867468543704604,-1860.0,3.0,0.0,0.0,1.0],[25.867468543704604,28.60685731185316,0.0,3.0,9.0,4.0,-1.0],[28.60685731185316,29.51998690123601,708.65,4.0,9.0,3.0,-1.0],[29.51998690123601,38.19471800037311,1860.0,4.0,9.0,3.0,-1.0]]</t>
+          <t>[[-7.005196674078064,25.867468543704604,-1860.0,2.0,0.0,0.0,1.0],[25.867468543704604,28.60685731185316,0.0,3.0,9.0,4.0,-1.0],[28.60685731185316,29.51998690123601,708.65,4.0,9.0,3.0,-1.0],[29.51998690123601,38.19471800037311,1860.0,4.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>[[-7.267607775967381,27.574744159808855,-0.0,0.0,0.0,1.0,1.0],[27.574744159808855,29.36153143856661,708.65,1.0,9.0,4.0,-1.0],[29.36153143856661,36.95537737328708,1860.0,1.0,10.0,3.0,-1.0]]</t>
+          <t>[[-7.267607775967381,27.574744159808855,0.0,0.0,0.0,1.0,1.0],[27.574744159808855,29.36153143856661,708.65,1.0,9.0,4.0,-1.0],[29.36153143856661,36.95537737328708,1860.0,1.0,10.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>[[-7.3821907424165625,25.733054553881573,-1860.0,2.0,9.0,2.0,-1.0],[25.733054553881573,26.18668805109114,-1275.7341,1.0,9.0,2.0,-1.0],[26.18668805109114,28.908489034348513,0.0,1.0,9.0,2.0,-1.0],[28.908489034348513,37.52752548133022,1860.0,2.0,9.0,1.0,-1.0]]</t>
+          <t>[[-7.3821907424165625,25.733054553881573,-1860.0,1.0,9.0,2.0,-1.0],[25.733054553881573,26.18668805109114,-1275.7341,1.0,9.0,2.0,-1.0],[26.18668805109114,28.908489034348513,0.0,1.0,9.0,2.0,-1.0],[28.908489034348513,37.52752548133022,1860.0,2.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>[[-6.608616881100971,26.200571197575094,-1860.0,2.0,7.0,1.0,-1.0],[26.200571197575094,26.713214761304407,-1476.6759,2.0,7.0,1.0,-1.0],[26.713214761304407,29.276432579950978,0.0,2.0,6.0,2.0,-1.0],[29.276432579950978,44.14309592810107,1860.0,2.0,6.0,2.0,-1.0]]</t>
+          <t>[[-6.608616881100971,26.200571197575094,-1860.0,2.0,7.0,1.0,-1.0],[26.200571197575094,26.713214761304407,-1476.6759,2.0,7.0,1.0,-1.0],[26.713214761304407,29.276432579950978,0.0,1.0,6.0,2.0,-1.0],[29.276432579950978,44.14309592810107,1860.0,2.0,6.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>[[-6.98926725343526,25.153675226563507,-1860.0,2.0,6.0,1.0,-1.0],[25.153675226563507,25.65590870281349,-1275.7341,1.0,6.0,2.0,-1.0],[25.65590870281349,28.669309560313373,0.0,1.0,5.0,3.0,-1.0],[28.669309560313373,29.17154303656335,708.65,1.0,5.0,3.0,-1.0],[29.17154303656335,42.73184689531283,1860.0,1.0,5.0,3.0,-1.0]]</t>
+          <t>[[-6.98926725343526,25.153675226563507,-1860.0,2.0,6.0,1.0,-1.0],[25.153675226563507,25.65590870281349,-1275.7341,1.0,6.0,2.0,-1.0],[25.65590870281349,28.669309560313373,0.0,1.0,5.0,3.0,-1.0],[28.669309560313373,29.17154303656335,708.65,0.0,5.0,3.0,-1.0],[29.17154303656335,42.73184689531283,1860.0,0.0,5.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>[[-7.282536128271969,25.780529853585662,-1860.0,2.0,5.0,1.0,-1.0],[25.780529853585662,28.880192289384816,0.0,1.0,4.0,3.0,-1.0],[28.880192289384816,29.39680269535134,708.65,1.0,4.0,2.0,-1.0],[29.39680269535134,43.86189406241405,1860.0,1.0,5.0,1.0,-1.0]]</t>
+          <t>[[-7.282536128271969,25.780529853585662,-1860.0,1.0,5.0,1.0,-1.0],[25.780529853585662,28.880192289384816,0.0,0.0,4.0,3.0,-1.0],[28.880192289384816,29.39680269535134,708.65,0.0,4.0,2.0,-1.0],[29.39680269535134,43.86189406241405,1860.0,1.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>[[-6.931448681315284,26.766024967401567,-1860.0,9.0,12.0,2.0,0.0],[26.766024967401567,27.787160532514203,-1275.7341,1.0,5.0,1.0,-1.0],[27.787160532514203,30.8505672278521,0.0,1.0,4.0,2.0,-1.0],[30.8505672278521,43.614761791759996,1860.0,1.0,4.0,2.0,-1.0]]</t>
+          <t>[[-6.931448681315284,26.766024967401567,-1860.0,8.0,12.0,2.0,0.0],[26.766024967401567,27.787160532514203,-1275.7341,0.0,5.0,1.0,-1.0],[27.787160532514203,30.8505672278521,0.0,0.0,4.0,2.0,-1.0],[30.8505672278521,43.614761791759996,1860.0,1.0,4.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>[[-7.031478070497841,25.3124637578032,-1860.0,8.0,1.0,1.0,1.0],[25.3124637578032,26.877493201108088,-1808.4765,8.0,1.0,1.0,1.0],[26.877493201108088,27.399169682209717,-1023.2687,9.0,10.0,4.0,0.0],[27.399169682209717,30.529228568819498,0.0,9.0,9.0,5.0,0.0],[30.529228568819498,44.6144935585635,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-7.031478070497841,25.3124637578032,-1860.0,7.0,1.0,1.0,1.0],[25.3124637578032,26.877493201108088,-1808.4765,8.0,1.0,1.0,1.0],[26.877493201108088,27.399169682209717,-1023.2687,9.0,10.0,4.0,0.0],[27.399169682209717,30.529228568819498,0.0,8.0,9.0,5.0,0.0],[30.529228568819498,44.6144935585635,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>[[-6.95385357622328,27.934473498843133,-1860.0,8.0,0.0,1.0,1.0],[27.934473498843133,28.45519479847099,-1808.4765,8.0,0.0,1.0,1.0],[28.45519479847099,31.579522596238135,0.0,8.0,0.0,1.0,1.0],[31.579522596238135,32.100243895865994,46.5,9.0,0.0,0.0,1.0],[32.100243895865994,44.59755508693456,708.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-6.95385357622328,27.934473498843133,-1860.0,8.0,0.0,1.0,1.0],[27.934473498843133,28.45519479847099,-1808.4765,8.0,0.0,1.0,1.0],[28.45519479847099,31.579522596238135,0.0,8.0,0.0,1.0,1.0],[31.579522596238135,32.100243895865994,46.5,9.0,0.0,0.0,1.0],[32.100243895865994,44.59755508693456,708.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>[[-6.973173071348222,28.30589884125289,-1860.0,8.0,0.0,0.0,1.0],[28.30589884125289,29.35900546550964,-1023.2687,9.0,9.0,4.0,-1.0],[29.35900546550964,32.51832533827989,0.0,9.0,9.0,4.0,-1.0],[32.51832533827989,45.155604829360875,708.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-6.973173071348222,28.30589884125289,-1860.0,8.0,0.0,0.0,1.0],[28.30589884125289,29.35900546550964,-1023.2687,9.0,9.0,4.0,-1.0],[29.35900546550964,32.51832533827989,0.0,9.0,9.0,4.0,-1.0],[32.51832533827989,45.155604829360875,708.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>[[-7.080457594970696,27.59013405290203,-1860.0,7.0,0.0,0.0,1.0],[27.59013405290203,29.600023423793203,-1808.4765,7.0,0.0,0.0,1.0],[29.600023423793203,30.102495766516,-1023.2687,8.0,9.0,4.0,-1.0],[30.102495766516,33.11732982285276,0.0,8.0,9.0,4.0,-1.0],[33.11732982285276,34.624746851021136,755.15,9.0,9.0,3.0,-1.0],[34.624746851021136,42.66430433458583,1860.0,9.0,9.0,3.0,-1.0]]</t>
+          <t>[[-7.080457594970696,27.59013405290203,-1860.0,6.0,0.0,0.0,1.0],[27.59013405290203,29.600023423793203,-1808.4765,7.0,0.0,0.0,1.0],[29.600023423793203,30.102495766516,-1023.2687,8.0,9.0,4.0,-1.0],[30.102495766516,33.11732982285276,0.0,8.0,9.0,4.0,-1.0],[33.11732982285276,34.624746851021136,755.15,9.0,9.0,3.0,-1.0],[34.624746851021136,42.66430433458583,1860.0,9.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>[[-7.080243864962062,27.00854689121286,-1860.0,6.0,0.0,0.0,1.0],[27.00854689121286,28.4694950664775,-1808.4765,6.0,0.0,0.0,1.0],[28.4694950664775,31.39139141700678,0.0,8.0,9.0,3.0,-1.0],[31.39139141700678,32.36535686718321,755.15,8.0,9.0,3.0,-1.0],[32.36535686718321,41.13104591877104,1860.0,8.0,9.0,3.0,-1.0]]</t>
+          <t>[[-7.080243864962062,27.00854689121286,-1860.0,6.0,0.0,0.0,1.0],[27.00854689121286,28.4694950664775,-1808.4765,5.0,0.0,0.0,1.0],[28.4694950664775,31.39139141700678,0.0,7.0,9.0,3.0,-1.0],[31.39139141700678,32.36535686718321,755.15,8.0,9.0,3.0,-1.0],[32.36535686718321,41.13104591877104,1860.0,7.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>[[-2.266535582554761,27.53854110422391,-1860.0,5.0,0.0,0.0,1.0],[27.53854110422391,29.372699669564135,-1808.4765,5.0,0.0,0.0,1.0],[29.372699669564135,29.831239310899193,-1023.2687,6.0,9.0,4.0,-1.0],[29.831239310899193,33.041016800244584,0.0,6.0,8.0,5.0,-1.0],[33.041016800244584,43.128888909615824,1860.0,6.0,9.0,4.0,-1.0]]</t>
+          <t>[[-2.266535582554761,27.53854110422391,-1860.0,4.0,0.0,0.0,1.0],[27.53854110422391,29.372699669564135,-1808.4765,4.0,0.0,0.0,1.0],[29.372699669564135,29.831239310899193,-1023.2687,5.0,9.0,4.0,-1.0],[29.831239310899193,33.041016800244584,0.0,5.0,8.0,5.0,-1.0],[33.041016800244584,43.128888909615824,1860.0,5.0,9.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>[[3.36619092463286,29.340287645617497,-1860.0,7.0,9.0,2.0,-1.0],[29.340287645617497,29.72796073100533,-1023.2687,6.0,9.0,3.0,-1.0],[29.72796073100533,32.82934541410797,0.0,6.0,9.0,3.0,-1.0],[32.82934541410797,33.99236467027146,755.15,7.0,9.0,2.0,-1.0],[33.99236467027146,41.74582637802807,1860.0,4.0,6.0,1.0,-1.0]]</t>
+          <t>[[3.36619092463286,29.340287645617497,-1860.0,6.0,9.0,2.0,-1.0],[29.340287645617497,29.72796073100533,-1023.2687,5.0,9.0,3.0,-1.0],[29.72796073100533,32.82934541410797,0.0,5.0,9.0,3.0,-1.0],[32.82934541410797,33.99236467027146,755.15,6.0,9.0,2.0,-1.0],[33.99236467027146,41.74582637802807,1860.0,3.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>[[6.098201703062192,29.545879098244402,-1860.0,5.0,9.0,3.0,-1.0],[29.545879098244402,30.30225578841157,-1023.2687,5.0,9.0,3.0,-1.0],[30.30225578841157,33.70595089416383,0.0,5.0,9.0,3.0,-1.0],[33.70595089416383,34.08413923924741,755.15,6.0,9.0,2.0,-1.0],[34.08413923924741,34.84051592941458,1299.2,3.0,6.0,1.0,-1.0],[34.84051592941458,43.538847866337015,1860.0,3.0,6.0,1.0,-1.0]]</t>
+          <t>[[6.098201703062192,29.545879098244402,-1860.0,4.0,9.0,3.0,-1.0],[29.545879098244402,30.30225578841157,-1023.2687,4.0,9.0,3.0,-1.0],[30.30225578841157,33.70595089416383,0.0,4.0,9.0,3.0,-1.0],[33.70595089416383,34.08413923924741,755.15,5.0,9.0,2.0,-1.0],[34.08413923924741,34.84051592941458,1299.2,2.0,6.0,1.0,-1.0],[34.84051592941458,43.538847866337015,1860.0,2.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>[[6.385288520844072,29.8579772501956,-1860.0,5.0,10.0,2.0,-1.0],[29.8579772501956,30.230559610978958,-1224.2105,5.0,10.0,2.0,-1.0],[30.230559610978958,33.58380085802918,0.0,5.0,10.0,2.0,-1.0],[33.58380085802918,34.70154794037925,1299.2,2.0,6.0,1.0,-1.0],[34.70154794037925,43.27094223839647,1860.0,2.0,6.0,1.0,-1.0]]</t>
+          <t>[[6.385288520844072,29.8579772501956,-1860.0,5.0,10.0,2.0,-1.0],[29.8579772501956,30.230559610978958,-1224.2105,4.0,10.0,2.0,-1.0],[30.230559610978958,33.58380085802918,0.0,4.0,10.0,2.0,-1.0],[33.58380085802918,34.70154794037925,1299.2,2.0,6.0,1.0,-1.0],[34.70154794037925,43.27094223839647,1860.0,2.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>[[6.398895967454417,29.52315472353404,-1860.0,4.0,9.0,3.0,-1.0],[29.52315472353404,30.574257394264933,-1023.2687,3.0,9.0,3.0,-1.0],[30.574257394264933,33.72756540645761,0.0,3.0,8.0,4.0,-1.0],[33.72756540645761,34.07793296336791,936.5,3.0,8.0,4.0,-1.0],[34.07793296336791,41.08528410157385,1860.0,3.0,9.0,3.0,-1.0]]</t>
+          <t>[[6.398895967454417,29.52315472353404,-1860.0,3.0,9.0,3.0,-1.0],[29.52315472353404,30.574257394264933,-1023.2687,2.0,9.0,3.0,-1.0],[30.574257394264933,33.72756540645761,0.0,3.0,8.0,4.0,-1.0],[33.72756540645761,34.07793296336791,936.5,2.0,8.0,4.0,-1.0],[34.07793296336791,41.08528410157385,1860.0,2.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>[[6.71034681312255,28.479060754392393,-1808.4765,0.0,0.0,0.0,1.0],[28.479060754392393,28.848022007634256,-1023.2687,1.0,9.0,3.0,-1.0],[28.848022007634256,32.168673286811014,0.0,1.0,9.0,3.0,-1.0],[32.168673286811014,34.013479553020325,755.15,2.0,9.0,2.0,-1.0],[34.013479553020325,43.237510884066864,1860.0,2.0,10.0,1.0,-1.0]]</t>
+          <t>[[6.71034681312255,28.479060754392393,-1808.4766,0.0,0.0,0.0,1.0],[28.479060754392393,28.848022007634256,-1023.2687,1.0,9.0,3.0,-1.0],[28.848022007634256,32.168673286811014,0.0,1.0,9.0,3.0,-1.0],[32.168673286811014,34.013479553020325,755.15,2.0,9.0,2.0,-1.0],[34.013479553020325,43.237510884066864,1860.0,2.0,10.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>[[6.187173382665312,28.758009927775554,-1808.4765,0.0,0.0,0.0,1.0],[28.758009927775554,29.48610142923072,-822.3269,0.0,8.0,4.0,-1.0],[29.48610142923072,32.398467435051394,0.0,0.0,8.0,4.0,-1.0],[32.398467435051394,42.22770270469618,1860.0,1.0,9.0,2.0,-1.0]]</t>
+          <t>[[6.187173382665312,28.758009927775554,-1808.4766,0.0,0.0,0.0,1.0],[28.758009927775554,29.48610142923072,-822.3269,0.0,8.0,4.0,-1.0],[29.48610142923072,32.398467435051394,0.0,0.0,8.0,4.0,-1.0],[32.398467435051394,42.22770270469618,1860.0,1.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>[[6.094123538194833,29.680539472691198,-1860.0,9.0,11.0,3.0,0.0],[29.680539472691198,30.134124394508436,-1607.5346,9.0,11.0,3.0,0.0],[30.134124394508436,34.21638869086358,-0.0,1.0,2.0,1.0,-1.0],[34.21638869086358,50.99903079810138,1860.0,1.0,3.0,1.0,-1.0]]</t>
+          <t>[[6.094123538194833,29.680539472691198,-1860.0,9.0,11.0,3.0,0.0],[29.680539472691198,30.134124394508436,-1607.5346,9.0,11.0,3.0,0.0],[30.134124394508436,34.21638869086358,0.0,1.0,2.0,1.0,-1.0],[34.21638869086358,50.99903079810138,1860.0,1.0,3.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>[[6.05963658236621,26.560727622221183,-1860.0,9.0,3.0,0.0,1.0],[26.560727622221183,28.51321248315975,-733.6842,8.0,3.0,1.0,1.0],[28.51321248315975,31.930060989802246,0.0,8.0,2.0,2.0,1.0],[31.930060989802246,32.90630342027153,1197.85,8.0,2.0,2.0,1.0],[32.90630342027153,54.38363689059579,1860.0,8.0,3.0,1.0,1.0]]</t>
+          <t>[[6.05963658236621,26.560727622221183,-1860.0,8.0,3.0,0.0,1.0],[26.560727622221183,28.51321248315975,-733.6842,8.0,3.0,1.0,1.0],[28.51321248315975,31.930060989802246,0.0,8.0,2.0,2.0,1.0],[31.930060989802246,32.90630342027153,1197.85,8.0,2.0,2.0,1.0],[32.90630342027153,54.38363689059579,1860.0,8.0,3.0,1.0,1.0]]</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>[[6.457575473822436,25.83903520552078,-1860.0,9.0,1.0,0.0,1.0],[25.83903520552078,27.879188861489027,-733.6842,8.0,1.0,1.0,1.0],[27.879188861489027,30.9394193454414,0.0,8.0,0.0,2.0,1.0],[30.9394193454414,31.95949617342552,1197.85,8.0,0.0,2.0,1.0],[31.95949617342552,56.951378459036555,1860.0,8.0,1.0,1.0,1.0]]</t>
+          <t>[[6.457575473822436,25.83903520552078,-1860.0,8.0,1.0,0.0,1.0],[25.83903520552078,27.879188861489027,-733.6842,8.0,1.0,1.0,1.0],[27.879188861489027,30.9394193454414,0.0,8.0,0.0,2.0,1.0],[30.9394193454414,31.95949617342552,1197.85,8.0,0.0,2.0,1.0],[31.95949617342552,56.951378459036555,1860.0,7.0,1.0,1.0,1.0]]</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>[[6.31652131096733,26.269679136685227,-1860.0,9.0,0.0,0.0,1.0],[26.269679136685227,28.702991066650824,-733.6842,8.0,0.0,1.0,1.0],[28.702991066650824,32.10962776860266,0.0,8.0,0.0,1.0,1.0],[32.10962776860266,39.40956355849945,1016.5,9.0,0.0,0.0,1.0],[39.40956355849945,54.49609752428615,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[6.31652131096733,26.269679136685227,-1860.0,8.0,0.0,0.0,1.0],[26.269679136685227,28.702991066650824,-733.6842,8.0,0.0,1.0,1.0],[28.702991066650824,32.10962776860266,0.0,7.0,0.0,1.0,1.0],[32.10962776860266,39.40956355849945,1016.5,9.0,0.0,0.0,1.0],[39.40956355849945,54.49609752428615,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>[[6.186252771594396,29.884053141634652,-1860.0,8.0,0.0,0.0,1.0],[29.884053141634652,31.742704151049576,-733.6842,8.0,0.0,0.0,1.0],[31.742704151049576,34.99534341752569,0.0,8.0,0.0,1.0,1.0],[34.99534341752569,40.106633693416725,1016.5,9.0,0.0,0.0,1.0],[40.106633693416725,52.18786525461372,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[6.186252771594396,29.884053141634652,-1860.0,7.0,0.0,0.0,1.0],[29.884053141634652,31.742704151049576,-733.6842,8.0,0.0,0.0,1.0],[31.742704151049576,34.99534341752569,0.0,7.0,0.0,1.0,1.0],[34.99534341752569,40.106633693416725,1016.5,9.0,0.0,0.0,1.0],[40.106633693416725,52.18786525461372,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>[[6.042334770243211,30.736623411644523,-1860.0,7.0,0.0,0.0,1.0],[30.736623411644523,34.53574474109087,-733.6842,7.0,0.0,0.0,1.0],[34.53574474109087,37.85997590435644,0.0,7.0,0.0,1.0,1.0],[37.85997590435644,40.709316901441206,1016.5,8.0,0.0,0.0,1.0],[40.709316901441206,53.056461222141856,1860.0,8.0,9.0,3.0,-1.0]]</t>
+          <t>[[6.042334770243211,30.736623411644523,-1860.0,6.0,0.0,0.0,1.0],[30.736623411644523,34.53574474109087,-733.6842,7.0,0.0,0.0,1.0],[34.53574474109087,37.85997590435644,0.0,6.0,0.0,1.0,1.0],[37.85997590435644,40.709316901441206,1016.5,8.0,0.0,0.0,1.0],[40.709316901441206,53.056461222141856,1860.0,8.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>[[6.200485742445525,29.17403952937586,-1860.0,6.0,0.0,0.0,1.0],[29.17403952937586,31.618034613091854,-733.6842,6.0,0.0,0.0,1.0],[31.618034613091854,35.03962773029424,0.0,6.0,0.0,1.0,1.0],[35.03962773029424,39.92761789772622,1016.5,7.0,0.0,0.0,1.0],[39.92761789772622,41.394014947955824,1725.15,8.0,9.0,2.0,-1.0],[41.394014947955824,54.59158840002218,1860.0,8.0,9.0,2.0,-1.0]]</t>
+          <t>[[6.200485742445525,29.17403952937586,-1860.0,6.0,0.0,0.0,1.0],[29.17403952937586,31.618034613091854,-733.6842,5.0,0.0,0.0,1.0],[31.618034613091854,35.03962773029424,0.0,6.0,0.0,1.0,1.0],[35.03962773029424,39.92761789772622,1016.5,7.0,0.0,0.0,1.0],[39.92761789772622,41.394014947955824,1725.15,8.0,9.0,2.0,-1.0],[41.394014947955824,54.59158840002218,1860.0,8.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>[[6.225850190061506,28.014124484041044,-1860.0,5.0,0.0,0.0,1.0],[28.014124484041044,33.58786907087302,-733.6842,5.0,0.0,0.0,1.0],[33.58786907087302,37.134797444311545,0.0,5.0,0.0,1.0,1.0],[37.134797444311545,39.668317711053355,1016.5,6.0,0.0,0.0,1.0],[39.668317711053355,56.389551471549275,1860.0,6.0,9.0,3.0,-1.0]]</t>
+          <t>[[6.225850190061506,28.014124484041044,-1860.0,4.0,0.0,0.0,1.0],[28.014124484041044,33.58786907087302,-733.6842,4.0,0.0,0.0,1.0],[33.58786907087302,37.134797444311545,0.0,4.0,0.0,1.0,1.0],[37.134797444311545,39.668317711053355,1016.5,4.0,0.0,0.0,1.0],[39.668317711053355,56.389551471549275,1860.0,6.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>[[10.044765917111793,29.85788793471034,-1860.0,4.0,0.0,0.0,1.0],[29.85788793471034,33.0832798910636,-733.6842,4.0,0.0,0.0,1.0],[33.0832798910636,36.76944212689588,0.0,4.0,0.0,1.0,1.0],[36.76944212689588,40.45560436272817,1016.5,5.0,0.0,0.0,1.0],[40.45560436272817,55.661023585536356,1860.0,5.0,9.0,3.0,-1.0]]</t>
+          <t>[[10.044765917111793,29.85788793471034,-1860.0,3.0,0.0,0.0,1.0],[29.85788793471034,33.0832798910636,-733.6842,3.0,0.0,0.0,1.0],[33.0832798910636,36.76944212689588,0.0,3.0,0.0,1.0,1.0],[36.76944212689588,40.45560436272817,1016.5,4.0,0.0,0.0,1.0],[40.45560436272817,55.661023585536356,1860.0,4.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>[[9.222657630748097,29.500499044187904,-1860.0,3.0,0.0,0.0,1.0],[29.500499044187904,31.70461224130092,-733.6842,3.0,0.0,0.0,1.0],[31.70461224130092,35.23119335668176,0.0,3.0,0.0,1.0,1.0],[35.23119335668176,40.08024239033041,1016.5,4.0,0.0,0.0,1.0],[40.08024239033041,52.864098933585936,1860.0,4.0,9.0,3.0,-1.0]]</t>
+          <t>[[9.222657630748097,29.500499044187904,-1860.0,3.0,0.0,0.0,1.0],[29.500499044187904,31.70461224130092,-733.6842,2.0,0.0,0.0,1.0],[31.70461224130092,35.23119335668176,0.0,2.0,0.0,1.0,1.0],[35.23119335668176,40.08024239033041,1016.5,3.0,0.0,0.0,1.0],[40.08024239033041,52.864098933585936,1860.0,3.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>[[9.953973035437304,23.008611728590267,-1860.0,2.0,0.0,0.0,1.0],[23.008611728590267,31.56165087238014,-733.6842,2.0,0.0,0.0,1.0],[31.56165087238014,35.16293051187061,0.0,2.0,0.0,1.0,1.0],[35.16293051187061,38.764210151361084,1016.5,3.0,0.0,0.0,1.0],[38.764210151361084,54.5198085741319,1860.0,3.0,9.0,3.0,-1.0]]</t>
+          <t>[[9.953973035437304,23.008611728590267,-1860.0,2.0,0.0,0.0,1.0],[23.008611728590267,31.56165087238014,-733.6842,2.0,0.0,0.0,1.0],[31.56165087238014,35.16293051187061,0.0,1.0,0.0,1.0,1.0],[35.16293051187061,38.764210151361084,1016.5,2.0,0.0,0.0,1.0],[38.764210151361084,54.5198085741319,1860.0,2.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>[[9.73102477340215,32.031469719122335,-1860.0,2.0,0.0,0.0,1.0],[32.031469719122335,40.45608225417218,-0.0,2.0,0.0,1.0,1.0],[40.45608225417218,58.79200365398655,1860.0,2.0,8.0,4.0,-1.0]]</t>
+          <t>[[9.73102477340215,32.031469719122335,-1860.0,1.0,0.0,0.0,1.0],[32.031469719122335,40.45608225417218,0.0,2.0,0.0,1.0,1.0],[40.45608225417218,58.79200365398655,1860.0,2.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>[[9.503965080018071,31.57908898205053,-1860.0,1.0,0.0,0.0,1.0],[31.57908898205053,40.77705727456405,-0.0,1.0,0.0,1.0,1.0],[40.77705727456405,41.6968541038154,890.0,1.0,8.0,4.0,-1.0],[41.6968541038154,55.03390812796001,1860.0,1.0,8.0,4.0,-1.0]]</t>
+          <t>[[9.503965080018071,31.57908898205053,-1860.0,1.0,0.0,0.0,1.0],[31.57908898205053,40.77705727456405,0.0,1.0,0.0,1.0,1.0],[40.77705727456405,41.6968541038154,890.0,1.0,8.0,4.0,-1.0],[41.6968541038154,55.03390812796001,1860.0,1.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>[[9.515455611933138,40.31012682184718,-0.0,0.0,0.0,1.0,1.0],[40.31012682184718,55.707462426804184,1860.0,1.0,9.0,2.0,-1.0]]</t>
+          <t>[[9.515455611933138,40.31012682184718,0.0,0.0,0.0,1.0,1.0],[40.31012682184718,55.707462426804184,1860.0,1.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>[[9.58124836654681,39.921888996433026,-0.0,0.0,0.0,1.0,1.0],[39.921888996433026,53.75365163652822,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[9.58124836654681,39.921888996433026,0.0,0.0,0.0,1.0,1.0],[39.921888996433026,53.75365163652822,1860.0,0.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>[[9.718753169976825,33.57171765706868,-1860.0,1.0,4.0,1.0,-1.0],[33.57171765706868,34.471829524506106,-1074.7923,0.0,4.0,2.0,-1.0],[34.471829524506106,38.07227699425582,0.0,0.0,3.0,3.0,-1.0],[38.07227699425582,38.972388861693254,890.0,0.0,3.0,3.0,-1.0],[38.972388861693254,54.27429060812954,1860.0,0.0,3.0,3.0,-1.0]]</t>
+          <t>[[9.718753169976825,33.57171765706868,-1860.0,0.0,4.0,1.0,-1.0],[33.57171765706868,34.471829524506106,-1074.7923,0.0,4.0,2.0,-1.0],[34.471829524506106,38.07227699425582,0.0,0.0,3.0,3.0,-1.0],[38.07227699425582,38.972388861693254,890.0,0.0,3.0,3.0,-1.0],[38.972388861693254,54.27429060812954,1860.0,0.0,3.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>[[9.23685406081708,22.48916018283284,-1860.0,9.0,1.0,0.0,1.0],[22.48916018283284,22.930903720233367,-733.6842,9.0,1.0,0.0,1.0],[22.930903720233367,31.765774468243873,0.0,0.0,1.0,1.0,-1.0],[31.765774468243873,52.96946426346909,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[9.23685406081708,22.48916018283284,-1860.0,8.0,1.0,0.0,1.0],[22.48916018283284,22.930903720233367,-733.6842,9.0,1.0,0.0,1.0],[22.930903720233367,31.765774468243873,0.0,0.0,1.0,1.0,-1.0],[31.765774468243873,52.96946426346909,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>[[9.519828571434266,20.530027531303,-1860.0,9.0,0.0,0.0,1.0],[20.530027531303,21.753382971288413,-532.7423,8.0,0.0,1.0,1.0],[21.753382971288413,24.200093851259243,0.0,8.0,0.0,2.0,1.0],[24.200093851259243,25.42344929124466,1197.85,9.0,0.0,1.0,1.0],[25.42344929124466,49.89055809095296,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[9.519828571434266,20.530027531303,-1860.0,8.0,0.0,0.0,1.0],[20.530027531303,21.753382971288413,-532.7423,8.0,0.0,1.0,1.0],[21.753382971288413,24.200093851259243,0.0,8.0,0.0,2.0,1.0],[24.200093851259243,25.42344929124466,1197.85,9.0,0.0,1.0,1.0],[25.42344929124466,49.89055809095296,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>[[9.52167137946254,22.842992102229722,-1860.0,9.0,0.0,0.0,1.0],[22.842992102229722,35.33173027982396,-733.6842,9.0,0.0,0.0,1.0],[35.33173027982396,50.73450736552351,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[9.52167137946254,22.842992102229722,-1860.0,7.0,0.0,0.0,1.0],[22.842992102229722,35.33173027982396,-733.6842,9.0,0.0,0.0,1.0],[35.33173027982396,50.73450736552351,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>[[9.796336877994353,22.046653992895312,-1860.0,8.0,0.0,0.0,1.0],[22.046653992895312,36.21108315699955,-733.6842,8.0,0.0,0.0,1.0],[36.21108315699955,40.039307255406094,0.0,8.0,8.0,3.0,-1.0],[40.039307255406094,47.695755452219196,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[9.796336877994353,22.046653992895312,-1860.0,6.0,0.0,0.0,1.0],[22.046653992895312,36.21108315699955,-733.6842,7.0,0.0,0.0,1.0],[36.21108315699955,40.039307255406094,0.0,6.0,8.0,3.0,-1.0],[40.039307255406094,47.695755452219196,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>[[9.584146004254329,23.43552812007446,-1860.0,7.0,0.0,0.0,1.0],[23.43552812007446,36.09964891168144,-733.6842,7.0,0.0,0.0,1.0],[36.09964891168144,40.057186659058615,0.0,8.0,9.0,1.0,-1.0],[40.057186659058615,40.452940433796336,46.5,8.0,9.0,1.0,-1.0],[40.452940433796336,40.848694208534056,227.85,7.0,8.0,0.0,-1.0],[40.848694208534056,48.76376970328842,1860.0,7.0,8.0,0.0,-1.0]]</t>
+          <t>[[9.584146004254329,23.43552812007446,-1860.0,6.0,0.0,0.0,1.0],[23.43552812007446,36.09964891168144,-733.6842,7.0,0.0,0.0,1.0],[36.09964891168144,40.057186659058615,0.0,7.0,9.0,1.0,-1.0],[40.057186659058615,40.452940433796336,46.5,8.0,9.0,1.0,-1.0],[40.452940433796336,40.848694208534056,227.85,7.0,8.0,0.0,-1.0],[40.848694208534056,48.76376970328842,1860.0,7.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>[[8.64397061757689,23.05043299389458,-1860.0,6.0,0.0,0.0,1.0],[23.05043299389458,36.25635683885246,-733.6842,6.0,0.0,0.0,1.0],[36.25635683885246,40.25815194338516,0.0,6.0,8.0,3.0,-1.0],[40.25815194338516,41.45869047474496,227.85,6.0,8.0,0.0,-1.0],[41.45869047474496,48.26174215245054,1860.0,6.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.64397061757689,23.05043299389458,-1860.0,5.0,0.0,0.0,1.0],[23.05043299389458,36.25635683885246,-733.6842,5.0,0.0,0.0,1.0],[36.25635683885246,40.25815194338516,0.0,5.0,8.0,3.0,-1.0],[40.25815194338516,41.45869047474496,227.85,5.0,8.0,0.0,-1.0],[41.45869047474496,48.26174215245054,1860.0,5.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>[[5.862221143019794,23.2250913812518,-1860.0,5.0,0.0,0.0,1.0],[23.2250913812518,34.95676046113829,-733.6842,5.0,0.0,0.0,1.0],[34.95676046113829,39.18016132989743,0.0,5.0,8.0,4.0,-1.0],[39.18016132989743,41.05722838267927,227.85,5.0,8.0,0.0,-1.0],[41.05722838267927,52.3196306993703,1860.0,5.0,8.0,0.0,-1.0]]</t>
+          <t>[[5.862221143019794,23.2250913812518,-1860.0,3.0,0.0,0.0,1.0],[23.2250913812518,34.95676046113829,-733.6842,4.0,0.0,0.0,1.0],[34.95676046113829,39.18016132989743,0.0,4.0,8.0,4.0,-1.0],[39.18016132989743,41.05722838267927,227.85,4.0,8.0,0.0,-1.0],[41.05722838267927,52.3196306993703,1860.0,5.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>[[5.627116174204419,23.219334010162427,-1860.0,4.0,0.0,0.0,1.0],[23.219334010162427,35.256114634765275,-733.6842,4.0,0.0,0.0,1.0],[35.256114634765275,38.95973944233538,0.0,4.0,8.0,3.0,-1.0],[38.95973944233538,40.34859874517417,227.85,4.0,8.0,3.0,-1.0],[40.34859874517417,51.4594731678845,1860.0,4.0,9.0,2.0,-1.0]]</t>
+          <t>[[5.627116174204419,23.219334010162427,-1860.0,3.0,0.0,0.0,1.0],[23.219334010162427,35.256114634765275,-733.6842,3.0,0.0,0.0,1.0],[35.256114634765275,38.95973944233538,0.0,3.0,8.0,3.0,-1.0],[38.95973944233538,40.34859874517417,227.85,3.0,8.0,3.0,-1.0],[40.34859874517417,51.4594731678845,1860.0,3.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>[[1.9884784494145846,22.881439909653615,-1860.0,3.0,0.0,0.0,1.0],[22.881439909653615,35.815177956468254,-733.6842,3.0,0.0,0.0,1.0],[35.815177956468254,39.79478966318045,0.0,3.0,8.0,1.0,-1.0],[39.79478966318045,41.78459551653655,227.85,3.0,8.0,0.0,-1.0],[41.78459551653655,51.236173319978015,1860.0,3.0,8.0,0.0,-1.0]]</t>
+          <t>[[1.9884784494145846,22.881439909653615,-1860.0,3.0,0.0,0.0,1.0],[22.881439909653615,35.815177956468254,-733.6842,2.0,0.0,0.0,1.0],[35.815177956468254,39.79478966318045,0.0,2.0,8.0,1.0,-1.0],[39.79478966318045,41.78459551653655,227.85,2.0,8.0,0.0,-1.0],[41.78459551653655,51.236173319978015,1860.0,2.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>[[1.8387703061257163,21.71229952226691,-1860.0,2.0,0.0,0.0,1.0],[21.71229952226691,36.73862649056879,-733.6842,2.0,0.0,0.0,1.0],[36.73862649056879,41.101108513624176,0.0,2.0,8.0,3.0,-1.0],[41.101108513624176,49.82607255973494,1860.0,2.0,8.0,0.0,-1.0]]</t>
+          <t>[[1.8387703061257163,21.71229952226691,-1860.0,1.0,0.0,0.0,1.0],[21.71229952226691,36.73862649056879,-733.6842,2.0,0.0,0.0,1.0],[36.73862649056879,41.101108513624176,0.0,2.0,8.0,3.0,-1.0],[41.101108513624176,49.82607255973494,1860.0,2.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -3622,11 +3622,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>[[-4.5925615795403685,36.02884467400938,-733.6842,0.0,0.0,0.0,1.0],[36.02884467400938,39.97814805977116,0.0,0.0,9.0,2.0,-1.0],[39.97814805977116,41.1065204557031,46.5,1.0,9.0,1.0,-1.0],[41.1065204557031,41.670706653669065,227.85,0.0,8.0,0.0,-1.0],[41.670706653669065,51.26187201909054,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-4.5925615795403685,36.02884467400938,-733.6843,0.0,0.0,0.0,1.0],[36.02884467400938,39.97814805977116,0.0,0.0,9.0,2.0,-1.0],[39.97814805977116,41.1065204557031,46.5,1.0,9.0,1.0,-1.0],[41.1065204557031,41.670706653669065,227.85,0.0,8.0,0.0,-1.0],[41.670706653669065,51.26187201909054,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>-733.6842</v>
+        <v>-733.6843</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>[[-4.112252481348731,33.34138079507791,-1860.0,1.0,8.0,1.0,-1.0],[33.34138079507791,35.64621976593494,-1074.7922,0.0,8.0,1.0,-1.0],[35.64621976593494,39.103478222220474,0.0,0.0,7.0,2.0,-1.0],[39.103478222220474,39.67968796493473,890.0,0.0,7.0,2.0,-1.0],[39.67968796493473,52.93251204736262,1860.0,0.0,7.0,2.0,-1.0]]</t>
+          <t>[[-4.112252481348731,33.34138079507791,-1860.0,1.0,8.0,1.0,-1.0],[33.34138079507791,35.64621976593494,-1074.7921,0.0,8.0,1.0,-1.0],[35.64621976593494,39.103478222220474,0.0,0.0,7.0,2.0,-1.0],[39.103478222220474,39.67968796493473,890.0001,0.0,7.0,2.0,-1.0],[39.67968796493473,52.93251204736262,1860.0,0.0,7.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>[[-4.895667298450673,33.63212204143139,-1860.0,1.0,7.0,0.0,-1.0],[33.63212204143139,34.17476696171142,-1074.7922,0.0,7.0,1.0,-1.0],[34.17476696171142,37.97328140367162,0.0,0.0,6.0,2.0,-1.0],[37.97328140367162,40.14386108479174,890.0,0.0,6.0,2.0,-1.0],[40.14386108479174,48.826179809272205,1860.0,0.0,6.0,2.0,-1.0]]</t>
+          <t>[[-4.895667298450673,33.63212204143139,-1860.0,1.0,7.0,0.0,-1.0],[33.63212204143139,34.17476696171142,-1074.7921,0.0,7.0,1.0,-1.0],[34.17476696171142,37.97328140367162,0.0,0.0,6.0,2.0,-1.0],[37.97328140367162,40.14386108479174,890.0001,0.0,6.0,2.0,-1.0],[40.14386108479174,48.826179809272205,1860.0,0.0,6.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>[[-4.4881139493366,33.648967563900946,-1860.0,1.0,6.0,1.0,-1.0],[33.648967563900946,34.75439021645856,-1074.7922,0.0,6.0,1.0,-1.0],[34.75439021645856,38.62336950041019,0.0,0.0,5.0,2.0,-1.0],[38.62336950041019,50.23030735226509,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-4.4881139493366,33.648967563900946,-1860.0,1.0,6.0,1.0,-1.0],[33.648967563900946,34.75439021645856,-1074.7921,0.0,6.0,1.0,-1.0],[34.75439021645856,38.62336950041019,0.0,0.0,5.0,2.0,-1.0],[38.62336950041019,50.23030735226509,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>[[-4.548724307462819,33.33541867154124,-1860.0,1.0,5.0,1.0,-1.0],[33.33541867154124,35.00677792061495,-1074.7922,0.0,5.0,1.0,-1.0],[35.00677792061495,38.90661616845361,0.0,0.0,4.0,2.0,-1.0],[38.90661616845361,40.02085566783608,890.0,0.0,4.0,0.0,-1.0],[40.02085566783608,50.60613091196957,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-4.548724307462819,33.33541867154124,-1860.0,1.0,5.0,1.0,-1.0],[33.33541867154124,35.00677792061495,-1074.7921,0.0,5.0,1.0,-1.0],[35.00677792061495,38.90661616845361,0.0,0.0,4.0,2.0,-1.0],[38.90661616845361,40.02085566783608,890.0001,0.0,4.0,0.0,-1.0],[40.02085566783608,50.60613091196957,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>[[-4.436531506642835,32.42116870133077,-1860.0,1.0,5.0,0.0,-1.0],[32.42116870133077,33.978536315752194,-1074.7922,0.0,5.0,0.0,-1.0],[33.978536315752194,37.612394082735506,0.0,0.0,4.0,1.0,-1.0],[37.612394082735506,38.13151662087598,890.0,0.0,4.0,1.0,-1.0],[38.13151662087598,46.956599769264024,1860.0,0.0,4.0,1.0,-1.0]]</t>
+          <t>[[-4.436531506642835,32.42116870133077,-1860.0,1.0,5.0,0.0,-1.0],[32.42116870133077,33.978536315752194,-1074.7921,0.0,5.0,0.0,-1.0],[33.978536315752194,37.612394082735506,0.0,0.0,4.0,1.0,-1.0],[37.612394082735506,38.13151662087598,890.0001,0.0,4.0,1.0,-1.0],[38.13151662087598,46.956599769264024,1860.0,0.0,4.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>[[-4.513958606228754,32.934685247909954,-1860.0,1.0,4.0,0.0,-1.0],[32.934685247909954,34.93194625346402,-1074.7922,0.0,4.0,1.0,-1.0],[34.93194625346402,38.427153013183634,0.0,0.0,3.0,2.0,-1.0],[38.427153013183634,38.92646826457215,890.0,0.0,3.0,2.0,-1.0],[38.92646826457215,44.91825128123434,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[-4.513958606228754,32.934685247909954,-1860.0,1.0,4.0,0.0,-1.0],[32.934685247909954,34.93194625346402,-1074.7921,0.0,4.0,1.0,-1.0],[34.93194625346402,38.427153013183634,0.0,0.0,3.0,2.0,-1.0],[38.427153013183634,38.92646826457215,890.0001,0.0,3.0,2.0,-1.0],[38.92646826457215,44.91825128123434,1860.0,0.0,3.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>[[-4.810640504202817,32.86100263542682,-1860.0,1.0,3.0,0.0,-1.0],[32.86100263542682,36.581658747982836,0.0,0.0,2.0,1.0,-1.0],[36.581658747982836,37.04674076205234,890.0,0.0,2.0,1.0,-1.0],[37.04674076205234,41.23247888867785,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[-4.810640504202817,32.86100263542682,-1860.0,1.0,3.0,0.0,-1.0],[32.86100263542682,36.581658747982836,0.0,0.0,2.0,1.0,-1.0],[36.581658747982836,37.04674076205234,890.0001,0.0,2.0,1.0,-1.0],[37.04674076205234,41.23247888867785,1860.0,0.0,2.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -3829,11 +3829,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>[[-4.701487278192305,32.52958542222231,-1860.0,1.0,2.0,0.0,-1.0],[32.52958542222231,33.56378188612272,-1074.7922,0.0,2.0,1.0,-1.0],[33.56378188612272,37.18346950977414,0.0,0.0,1.0,2.0,-1.0],[37.18346950977414,39.76896066952516,890.0,0.0,1.0,1.0,-1.0],[39.76896066952516,46.49123768487779,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[-4.701487278192305,32.52958542222231,-1860.0,1.0,2.0,0.0,-1.0],[32.52958542222231,33.56378188612272,-1074.7921,0.0,2.0,1.0,-1.0],[33.56378188612272,37.18346950977414,0.0,0.0,1.0,2.0,-1.0],[37.18346950977414,39.76896066952516,890.0001,0.0,1.0,1.0,-1.0],[39.76896066952516,46.49123768487779,1860.0,0.0,1.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>890</v>
+        <v>890.0001</v>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>[[-4.495298292173052,24.796358250910963,-1860.0,9.0,0.0,0.0,1.0],[24.796358250910963,35.718670860196525,0.0,9.0,0.0,1.0,1.0],[35.718670860196525,44.65510844961199,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-4.495298292173052,24.796358250910963,-1860.0,8.0,0.0,0.0,1.0],[24.796358250910963,35.718670860196525,0.0,7.0,0.0,1.0,1.0],[35.718670860196525,44.65510844961199,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>[[-4.3981422541550295,24.77468043619473,-1860.0,8.0,0.0,0.0,1.0],[24.77468043619473,35.714488945075885,0.0,8.0,0.0,1.0,1.0],[35.714488945075885,40.72856784497975,1860.0,9.0,9.0,2.0,-1.0]]</t>
+          <t>[[-4.3981422541550295,24.77468043619473,-1860.0,7.0,0.0,0.0,1.0],[24.77468043619473,35.714488945075885,0.0,6.0,0.0,1.0,1.0],[35.714488945075885,40.72856784497975,1860.0,8.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>[[-4.571120265029684,25.75084319835525,-1860.0,7.0,0.0,0.0,1.0],[25.75084319835525,33.575866027615874,0.0,7.0,0.0,1.0,1.0],[33.575866027615874,43.84620849102045,1860.0,8.0,9.0,1.0,-1.0]]</t>
+          <t>[[-4.571120265029684,25.75084319835525,-1860.0,6.0,0.0,0.0,1.0],[25.75084319835525,33.575866027615874,0.0,6.0,0.0,1.0,1.0],[33.575866027615874,43.84620849102045,1860.0,8.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>[[-4.659987055350011,24.261434604896554,-1860.0,6.0,0.0,0.0,1.0],[24.261434604896554,34.40930185410588,0.0,6.0,0.0,1.0,1.0],[34.40930185410588,45.57195582823613,1860.0,6.0,8.0,3.0,-1.0]]</t>
+          <t>[[-4.659987055350011,24.261434604896554,-1860.0,5.0,0.0,0.0,1.0],[24.261434604896554,34.40930185410588,0.0,3.0,0.0,1.0,1.0],[34.40930185410588,45.57195582823613,1860.0,6.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>[[-4.453921093408683,24.470777928877318,-1860.0,5.0,0.0,0.0,1.0],[24.470777928877318,33.95428580503667,0.0,5.0,0.0,1.0,1.0],[33.95428580503667,34.42846119884463,890.0,5.0,8.0,4.0,-1.0],[34.42846119884463,42.489442893580076,1860.0,5.0,8.0,4.0,-1.0]]</t>
+          <t>[[-4.453921093408683,24.470777928877318,-1860.0,4.0,0.0,0.0,1.0],[24.470777928877318,33.95428580503667,0.0,3.0,0.0,1.0,1.0],[33.95428580503667,34.42846119884463,890.0,4.0,8.0,4.0,-1.0],[34.42846119884463,42.489442893580076,1860.0,5.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>[[-4.5062635054054745,24.70727374859897,-1860.0,4.0,0.0,0.0,1.0],[24.70727374859897,34.76439313112509,0.0,4.0,0.0,1.0,1.0],[34.76439313112509,35.243303577912044,890.0,4.0,8.0,4.0,-1.0],[35.243303577912044,42.90587072650338,1860.0,4.0,8.0,4.0,-1.0]]</t>
+          <t>[[-4.5062635054054745,24.70727374859897,-1860.0,4.0,0.0,0.0,1.0],[24.70727374859897,34.76439313112509,0.0,3.0,0.0,1.0,1.0],[34.76439313112509,35.243303577912044,890.0,4.0,8.0,4.0,-1.0],[35.243303577912044,42.90587072650338,1860.0,4.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>[[-2.618455385771295,32.04932766359303,-1860.0,2.0,0.0,0.0,1.0],[32.04932766359303,35.6049977199381,0.0,1.0,7.0,5.0,-1.0],[35.6049977199381,41.38296156149882,1860.0,1.0,7.0,5.0,-1.0]]</t>
+          <t>[[-2.618455385771295,32.04932766359303,-1860.0,1.0,0.0,0.0,1.0],[32.04932766359303,35.6049977199381,0.0,1.0,7.0,5.0,-1.0],[35.6049977199381,41.38296156149882,1860.0,1.0,7.0,5.0,-1.0]]</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>[[10.935025213554844,30.159331739625436,-1860.0,1.0,0.0,0.0,1.0],[30.159331739625436,30.490785300419756,-873.8504,0.0,8.0,3.0,-1.0],[30.490785300419756,33.80532090836296,0.0,0.0,7.0,4.0,-1.0],[33.80532090836296,35.462588712334565,1071.35,0.0,7.0,3.0,-1.0],[35.462588712334565,43.74892773219258,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[10.935025213554844,30.159331739625436,-1860.0,0.0,0.0,0.0,1.0],[30.159331739625436,30.490785300419756,-873.8504,0.0,8.0,3.0,-1.0],[30.490785300419756,33.80532090836296,0.0,0.0,7.0,4.0,-1.0],[33.80532090836296,35.462588712334565,1071.35,0.0,7.0,3.0,-1.0],[35.462588712334565,43.74892773219258,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>[[10.59862303866299,30.314017397786472,-1860.0,1.0,7.0,0.0,-1.0],[30.314017397786472,34.91427608158195,0.0,0.0,7.0,1.0,-1.0],[34.91427608158195,75.65942442377049,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[10.59862303866299,30.314017397786472,-1860.0,1.0,7.0,0.0,-1.0],[30.314017397786472,34.91427608158195,0.0,0.0,6.0,1.0,-1.0],[34.91427608158195,75.65942442377049,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>[[10.424821564384656,17.328288023122052,-1860.0,8.0,15.0,0.0,0.0],[17.328288023122052,34.97048008433985,0.0,0.0,7.0,1.0,-1.0],[34.97048008433985,86.36295261049602,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[10.424821564384656,17.328288023122052,-1860.0,8.0,15.0,0.0,0.0],[17.328288023122052,34.97048008433985,0.0,0.0,7.0,1.0,-1.0],[34.97048008433985,86.36295261049602,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>[[10.295243394271406,18.528461346656314,-1860.0,9.0,13.0,1.0,0.0],[18.528461346656314,19.276935705964032,-1607.5346,8.0,13.0,2.0,0.0],[19.276935705964032,35.743371610733846,0.0,0.0,5.0,1.0,-1.0],[35.743371610733846,84.39420496573558,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[10.295243394271406,18.528461346656314,-1860.0,9.0,13.0,1.0,0.0],[18.528461346656314,19.276935705964032,-1607.5346,8.0,13.0,2.0,0.0],[19.276935705964032,35.743371610733846,0.0,0.0,5.0,1.0,-1.0],[35.743371610733846,84.39420496573558,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>[[10.904807859266159,18.341452276730262,-1860.0,9.0,3.0,0.0,1.0],[18.341452276730262,19.994039925055617,-733.6842,9.0,3.0,0.0,1.0],[19.994039925055617,36.51991640830918,0.0,0.0,3.0,1.0,-1.0],[36.51991640830918,92.70789645137128,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[10.904807859266159,18.341452276730262,-1860.0,9.0,3.0,0.0,1.0],[18.341452276730262,19.994039925055617,-733.6842,9.0,3.0,0.0,1.0],[19.994039925055617,36.51991640830918,0.0,0.0,3.0,1.0,-1.0],[36.51991640830918,92.70789645137128,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>[[10.723096815150768,19.48061075300562,-1860.0,9.0,1.0,0.0,1.0],[19.48061075300562,20.2767483837197,-733.6842,9.0,1.0,0.0,1.0],[20.2767483837197,31.422675213716786,0.0,0.0,1.0,1.0,-1.0],[31.422675213716786,34.6072257365731,0.0,0.0,0.0,1.0,-1.0],[34.6072257365731,38.58791389014348,1860.0,0.0,0.0,0.0,-1.0],[38.58791389014348,89.54072225584446,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[10.723096815150768,19.48061075300562,-1860.0,7.0,1.0,0.0,1.0],[19.48061075300562,20.2767483837197,-733.6842,9.0,1.0,0.0,1.0],[20.2767483837197,31.422675213716786,0.0,0.0,1.0,1.0,-1.0],[31.422675213716786,34.6072257365731,0.0,0.0,0.0,1.0,-1.0],[34.6072257365731,38.58791389014348,1860.0,0.0,0.0,0.0,-1.0],[38.58791389014348,89.54072225584446,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>[[10.704894523780043,21.105191622045012,-1860.0,8.0,0.0,0.0,1.0],[21.105191622045012,27.17203159603291,-733.6842,8.0,0.0,0.0,1.0],[27.17203159603291,30.638797295454566,0.0,8.0,0.0,1.0,1.0],[30.638797295454566,43.63916866828577,1016.5,9.0,0.0,0.0,1.0],[43.63916866828577,96.50734558446602,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[10.704894523780043,21.105191622045012,-1860.0,6.0,0.0,0.0,1.0],[21.105191622045012,27.17203159603291,-733.6842,8.0,0.0,0.0,1.0],[27.17203159603291,30.638797295454566,0.0,7.0,0.0,1.0,1.0],[30.638797295454566,43.63916866828577,1016.5,9.0,0.0,0.0,1.0],[43.63916866828577,96.50734558446602,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>[[10.693688779388,22.063281640587462,-1860.0,7.0,0.0,0.0,1.0],[22.063281640587462,26.123850519587265,-733.6842,7.0,0.0,0.0,1.0],[26.123850519587265,29.37230562278711,0.0,7.0,0.0,1.0,1.0],[29.37230562278711,48.05092246618622,1016.5,8.0,0.0,0.0,1.0],[48.05092246618622,91.09295258358418,1860.0,8.0,1.0,0.0,1.0]]</t>
+          <t>[[10.693688779388,22.063281640587462,-1860.0,6.0,0.0,0.0,1.0],[22.063281640587462,26.123850519587265,-733.6842,7.0,0.0,0.0,1.0],[26.123850519587265,29.37230562278711,0.0,6.0,0.0,1.0,1.0],[29.37230562278711,48.05092246618622,1016.5,8.0,0.0,0.0,1.0],[48.05092246618622,91.09295258358418,1860.0,8.0,1.0,0.0,1.0]]</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>[[12.598372861454413,27.390008247241827,-1860.0,7.0,0.0,0.0,1.0],[27.390008247241827,43.73865788416476,-733.6842,7.0,0.0,0.0,1.0],[43.73865788416476,49.18820776313907,0.0,7.0,0.0,1.0,1.0],[49.18820776313907,53.85925051654562,1016.5,8.0,0.0,0.0,1.0],[53.85925051654562,54.63775764211338,1725.15,9.0,9.0,1.0,-1.0],[54.63775764211338,89.67057829266251,1860.0,9.0,9.0,1.0,-1.0]]</t>
+          <t>[[12.598372861454413,27.390008247241827,-1860.0,6.0,0.0,0.0,1.0],[27.390008247241827,43.73865788416476,-733.6842,7.0,0.0,0.0,1.0],[43.73865788416476,49.18820776313907,0.0,6.0,0.0,1.0,1.0],[49.18820776313907,53.85925051654562,1016.5,8.0,0.0,0.0,1.0],[53.85925051654562,54.63775764211338,1725.15,9.0,9.0,1.0,-1.0],[54.63775764211338,89.67057829266251,1860.0,9.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>[[13.37458633449267,26.413039824104207,-1860.0,6.0,0.0,0.0,1.0],[26.413039824104207,42.711106686118626,-733.6842,6.0,0.0,0.0,1.0],[42.711106686118626,46.78562340162223,0.0,6.0,0.0,1.0,1.0],[46.78562340162223,49.23033343092439,1016.5,7.0,0.0,0.0,1.0],[49.23033343092439,53.304850146427995,1725.15,8.0,9.0,1.0,-1.0],[53.304850146427995,94.05001730146405,1860.0,8.0,10.0,0.0,-1.0]]</t>
+          <t>[[13.37458633449267,26.413039824104207,-1860.0,6.0,0.0,0.0,1.0],[26.413039824104207,42.711106686118626,-733.6842,5.0,0.0,0.0,1.0],[42.711106686118626,46.78562340162223,0.0,6.0,0.0,1.0,1.0],[46.78562340162223,49.23033343092439,1016.5,7.0,0.0,0.0,1.0],[49.23033343092439,53.304850146427995,1725.15,8.0,9.0,1.0,-1.0],[53.304850146427995,94.05001730146405,1860.0,8.0,10.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>[[13.639933032358712,28.222331165931784,-1860.0,5.0,0.0,0.0,1.0],[28.222331165931784,41.18446284021896,-733.6842,5.0,0.0,0.0,1.0],[41.18446284021896,45.2351289884337,0.0,5.0,0.0,1.0,1.0],[45.2351289884337,50.095928366291396,1016.5,6.0,0.0,0.0,1.0],[50.095928366291396,93.84312276701061,1860.0,6.0,9.0,2.0,-1.0]]</t>
+          <t>[[13.639933032358712,28.222331165931784,-1860.0,4.0,0.0,0.0,1.0],[28.222331165931784,41.18446284021896,-733.6842,4.0,0.0,0.0,1.0],[41.18446284021896,45.2351289884337,0.0,4.0,0.0,1.0,1.0],[45.2351289884337,50.095928366291396,1016.5,4.0,0.0,0.0,1.0],[50.095928366291396,93.84312276701061,1860.0,6.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>[[13.491941837436226,26.200707349547443,-1860.0,4.0,0.0,0.0,1.0],[26.200707349547443,41.152196187325345,-733.6842,4.0,0.0,0.0,1.0],[41.152196187325345,45.63764283865872,0.0,4.0,0.0,1.0,1.0],[45.63764283865872,52.36581281565877,1016.5,5.0,0.0,0.0,1.0],[52.36581281565877,53.11338725754767,1725.15,6.0,9.0,1.0,-1.0],[53.11338725754767,87.50181158443685,1860.0,6.0,10.0,0.0,-1.0]]</t>
+          <t>[[13.491941837436226,26.200707349547443,-1860.0,3.0,0.0,0.0,1.0],[26.200707349547443,41.152196187325345,-733.6842,3.0,0.0,0.0,1.0],[41.152196187325345,45.63764283865872,0.0,3.0,0.0,1.0,1.0],[45.63764283865872,52.36581281565877,1016.5,4.0,0.0,0.0,1.0],[52.36581281565877,53.11338725754767,1725.15,5.0,9.0,1.0,-1.0],[53.11338725754767,87.50181158443685,1860.0,5.0,10.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>[[16.84510233064838,26.604269294066462,-1860.0,3.0,0.0,0.0,1.0],[26.604269294066462,40.545936384663726,-733.6842,3.0,0.0,0.0,1.0],[40.545936384663726,44.72843651184291,0.0,3.0,0.0,1.0,1.0],[44.72843651184291,52.3963534116714,1016.5,4.0,0.0,0.0,1.0],[52.3963534116714,85.85635442910484,1860.0,4.0,9.0,2.0,-1.0]]</t>
+          <t>[[16.84510233064838,26.604269294066462,-1860.0,2.0,0.0,0.0,1.0],[26.604269294066462,40.545936384663726,-733.6842,2.0,0.0,0.0,1.0],[40.545936384663726,44.72843651184291,0.0,2.0,0.0,1.0,1.0],[44.72843651184291,52.3963534116714,1016.5,3.0,0.0,0.0,1.0],[52.3963534116714,85.85635442910484,1860.0,3.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>[[16.875250434512846,27.82480811334132,-1860.0,2.0,0.0,0.0,1.0],[27.82480811334132,40.33858831771671,-733.6842,2.0,0.0,0.0,1.0],[40.33858831771671,45.031255894357486,0.0,2.0,0.0,1.0,1.0],[45.031255894357486,52.07025725931865,1016.5,3.0,0.0,0.0,1.0],[52.07025725931865,53.634479784865576,1725.15,4.0,9.0,1.0,-1.0],[53.634479784865576,94.30426544908562,1860.0,4.0,10.0,0.0,-1.0]]</t>
+          <t>[[16.875250434512846,27.82480811334132,-1860.0,2.0,0.0,0.0,1.0],[27.82480811334132,40.33858831771671,-733.6842,2.0,0.0,0.0,1.0],[40.33858831771671,45.031255894357486,0.0,1.0,0.0,1.0,1.0],[45.031255894357486,52.07025725931865,1016.5,2.0,0.0,0.0,1.0],[52.07025725931865,53.634479784865576,1725.15,4.0,9.0,1.0,-1.0],[53.634479784865576,94.30426544908562,1860.0,3.0,10.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>[[19.36322207426412,41.50920932146643,-1860.0,2.0,0.0,0.0,1.0],[41.50920932146643,46.091137717439324,-733.6842,2.0,0.0,0.0,1.0],[46.091137717439324,50.67306611341222,0.0,2.0,9.0,2.0,-1.0],[50.67306611341222,53.727685044060806,46.5,3.0,9.0,1.0,-1.0],[53.727685044060806,94.96504060781683,1860.0,4.0,9.0,0.0,-1.0]]</t>
+          <t>[[19.36322207426412,41.50920932146643,-1860.0,2.0,0.0,0.0,1.0],[41.50920932146643,46.091137717439324,-733.6842,2.0,0.0,0.0,1.0],[46.091137717439324,50.67306611341222,0.0,1.0,9.0,2.0,-1.0],[50.67306611341222,53.727685044060806,46.5,2.0,9.0,1.0,-1.0],[53.727685044060806,94.96504060781683,1860.0,3.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>[[19.40057575206109,41.57412990346195,-1860.0,1.0,0.0,0.0,1.0],[41.57412990346195,46.58106148603635,-733.6842,1.0,0.0,0.0,1.0],[46.58106148603635,51.58799306861073,0.0,1.0,9.0,2.0,-1.0],[51.58799306861073,53.01854494934628,46.5,2.0,9.0,1.0,-1.0],[53.01854494934628,90.2128938484703,1860.0,2.0,9.0,1.0,-1.0]]</t>
+          <t>[[19.40057575206109,41.57412990346195,-1860.0,1.0,0.0,0.0,1.0],[41.57412990346195,46.58106148603635,-733.6842,0.0,0.0,0.0,1.0],[46.58106148603635,51.58799306861073,0.0,1.0,9.0,2.0,-1.0],[51.58799306861073,53.01854494934628,46.5,2.0,9.0,1.0,-1.0],[53.01854494934628,90.2128938484703,1860.0,2.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -4749,11 +4749,11 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>[[18.29585114683094,48.156297245432384,-733.6842,0.0,0.0,0.0,1.0],[48.156297245432384,53.38187531268764,0.0,0.0,9.0,2.0,-1.0],[53.38187531268764,54.874897617617705,46.5,1.0,9.0,1.0,-1.0],[54.874897617617705,92.20045524086952,1860.0,2.0,9.0,0.0,-1.0]]</t>
+          <t>[[18.29585114683094,48.156297245432384,-733.6843,0.0,0.0,0.0,1.0],[48.156297245432384,53.38187531268764,0.0,0.0,9.0,2.0,-1.0],[53.38187531268764,54.874897617617705,46.5,1.0,9.0,1.0,-1.0],[54.874897617617705,92.20045524086952,1860.0,2.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>-733.6842</v>
+        <v>-733.6843</v>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>[[18.349246050748278,50.16642770056577,-0.0,0.0,0.0,1.0,1.0],[50.16642770056577,50.88954546533435,890.0,0.0,8.0,2.0,-1.0],[50.88954546533435,89.93790476283763,1860.0,0.0,9.0,1.0,-1.0]]</t>
+          <t>[[18.349246050748278,50.16642770056577,0.0,0.0,0.0,1.0,1.0],[50.16642770056577,50.88954546533435,890.0,0.0,8.0,2.0,-1.0],[50.88954546533435,89.93790476283763,1860.0,0.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>[[19.853463846891557,41.59585373794009,-1860.0,1.0,8.0,0.0,-1.0],[41.59585373794009,43.04534639734332,-1074.7923,0.0,8.0,1.0,-1.0],[43.04534639734332,48.11857070525465,0.0,0.0,7.0,2.0,-1.0],[48.11857070525465,51.01755602406112,890.0,0.0,7.0,2.0,-1.0],[51.01755602406112,91.6033504873517,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[19.853463846891557,41.59585373794009,-1860.0,1.0,8.0,0.0,-1.0],[41.59585373794009,43.04534639734332,-1074.7922,0.0,8.0,1.0,-1.0],[43.04534639734332,48.11857070525465,0.0,0.0,7.0,2.0,-1.0],[48.11857070525465,51.01755602406112,890.0001,0.0,7.0,2.0,-1.0],[51.01755602406112,91.6033504873517,1860.0,0.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>[[19.172314516033506,40.32332084343475,-1860.0,1.0,7.0,0.0,-1.0],[40.32332084343475,44.69939111806949,-1074.7923,0.0,7.0,1.0,-1.0],[44.69939111806949,49.80480643847669,0.0,0.0,7.0,1.0,-1.0],[49.80480643847669,91.37747404750672,1860.0,1.0,7.0,0.0,-1.0]]</t>
+          <t>[[19.172314516033506,40.32332084343475,-1860.0,1.0,7.0,0.0,-1.0],[40.32332084343475,44.69939111806949,-1074.7922,0.0,7.0,1.0,-1.0],[44.69939111806949,49.80480643847669,0.0,0.0,7.0,1.0,-1.0],[49.80480643847669,91.37747404750672,1860.0,1.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>[[18.862835997170503,41.85503298893214,-1860.0,1.0,6.0,0.0,-1.0],[41.85503298893214,44.01055145690979,-1074.7923,0.0,6.0,1.0,-1.0],[44.01055145690979,48.321588392865095,0.0,0.0,5.0,2.0,-1.0],[48.321588392865095,51.91411917282785,890.0,0.0,5.0,2.0,-1.0],[51.91411917282785,89.99494544043306,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[18.862835997170503,41.85503298893214,-1860.0,1.0,6.0,0.0,-1.0],[41.85503298893214,44.01055145690979,-1074.7922,0.0,6.0,1.0,-1.0],[44.01055145690979,48.321588392865095,0.0,0.0,5.0,2.0,-1.0],[48.321588392865095,51.91411917282785,890.0001,0.0,5.0,2.0,-1.0],[51.91411917282785,89.99494544043306,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>[[17.99694564525315,39.653137753570505,-1860.0,1.0,6.0,0.0,-1.0],[39.653137753570505,42.15192915068404,-1074.7923,0.0,6.0,0.0,-1.0],[42.15192915068404,46.31658147920661,0.0,0.0,5.0,1.0,-1.0],[46.31658147920661,48.815372876320154,890.0,0.0,5.0,1.0,-1.0],[48.815372876320154,100.45706175,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[17.99694564525315,39.653137753570505,-1860.0,1.0,6.0,0.0,-1.0],[39.653137753570505,42.15192915068404,-1074.7922,0.0,6.0,0.0,-1.0],[42.15192915068404,46.31658147920661,0.0,0.0,5.0,1.0,-1.0],[46.31658147920661,48.815372876320154,890.0001,0.0,5.0,1.0,-1.0],[48.815372876320154,100.45706175,1860.0,0.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>[[19.300369879741282,39.656269192465615,-1860.0,1.0,5.0,0.0,-1.0],[39.656269192465615,40.41019138923318,-1074.7923,0.0,5.0,0.0,-1.0],[40.41019138923318,44.93372456983859,0.0,0.0,4.0,1.0,-1.0],[44.93372456983859,47.949413356908856,890.0,0.0,4.0,1.0,-1.0],[47.949413356908856,93.93866735973049,1860.0,0.0,4.0,1.0,-1.0]]</t>
+          <t>[[19.300369879741282,39.656269192465615,-1860.0,1.0,5.0,0.0,-1.0],[39.656269192465615,40.41019138923318,-1074.7922,0.0,5.0,0.0,-1.0],[40.41019138923318,44.93372456983859,0.0,0.0,4.0,1.0,-1.0],[44.93372456983859,47.949413356908856,890.0001,0.0,4.0,1.0,-1.0],[47.949413356908856,93.93866735973049,1860.0,0.0,4.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>[[17.737711314380388,38.626436171860085,-1860.0,10.0,4.0,0.0,1.0],[38.626436171860085,41.13308315475765,-1808.4765,9.0,4.0,1.0,1.0],[41.13308315475765,41.96863214905684,-1074.7923,0.0,4.0,0.0,-1.0],[41.96863214905684,46.14637712055278,0.0,0.0,3.0,1.0,-1.0],[46.14637712055278,48.65302410345034,890.0,0.0,3.0,1.0,-1.0],[48.65302410345034,100.45706175,1860.0,0.0,3.0,1.0,-1.0]]</t>
+          <t>[[17.737711314380388,38.626436171860085,-1860.0,10.0,4.0,0.0,1.0],[38.626436171860085,41.13308315475765,-1808.4764,9.0,4.0,1.0,1.0],[41.13308315475765,41.96863214905684,-1074.7922,0.0,4.0,0.0,-1.0],[41.96863214905684,46.14637712055278,0.0,0.0,3.0,1.0,-1.0],[46.14637712055278,48.65302410345034,890.0001,0.0,3.0,1.0,-1.0],[48.65302410345034,100.45706175,1860.0,0.0,3.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -4933,11 +4933,11 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>[[18.924053915325917,41.16032877932794,-1860.0,10.0,3.0,0.0,1.0],[41.16032877932794,41.98389451503172,-1808.4765,9.0,3.0,1.0,1.0],[41.98389451503172,46.10172319355061,0.0,9.0,2.0,2.0,1.0],[46.10172319355061,46.92528892925439,227.85,9.0,2.0,2.0,1.0],[46.92528892925439,51.04311760777328,890.0,0.0,2.0,1.0,-1.0],[51.04311760777328,100.45706175,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[18.924053915325917,41.16032877932794,-1860.0,10.0,3.0,0.0,1.0],[41.16032877932794,41.98389451503172,-1808.4764,9.0,3.0,1.0,1.0],[41.98389451503172,46.10172319355061,0.0,9.0,2.0,2.0,1.0],[46.10172319355061,46.92528892925439,227.8501,9.0,2.0,2.0,1.0],[46.92528892925439,51.04311760777328,890.0001,0.0,2.0,1.0,-1.0],[51.04311760777328,100.45706175,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>890</v>
+        <v>890.0001</v>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>[[19.64682174260916,33.52332760246415,-1860.0,9.0,2.0,0.0,1.0],[33.52332760246415,40.869713057681494,-733.6842,9.0,2.0,0.0,1.0],[40.869713057681494,44.951038310580024,0.0,9.0,1.0,1.0,1.0],[44.951038310580024,49.848628614058256,1197.85,9.0,1.0,1.0,1.0],[49.848628614058256,100.45706175,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[19.64682174260916,33.52332760246415,-1860.0,8.0,2.0,0.0,1.0],[33.52332760246415,40.869713057681494,-733.6842,9.0,2.0,0.0,1.0],[40.869713057681494,44.951038310580024,0.0,9.0,1.0,1.0,1.0],[44.951038310580024,49.848628614058256,1197.85,9.0,1.0,1.0,1.0],[49.848628614058256,100.45706175,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>[[19.184450484062637,32.95838988285303,-1860.0,9.0,1.0,0.0,1.0],[32.95838988285303,39.440243717577914,-733.6842,9.0,1.0,0.0,1.0],[39.440243717577914,43.491402364280965,0.0,9.0,0.0,1.0,1.0],[43.491402364280965,48.35279274032463,1197.85,9.0,0.0,1.0,1.0],[48.35279274032463,99.39739168878312,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[19.184450484062637,32.95838988285303,-1860.0,8.0,1.0,0.0,1.0],[32.95838988285303,39.440243717577914,-733.6842,9.0,1.0,0.0,1.0],[39.440243717577914,43.491402364280965,0.0,9.0,0.0,1.0,1.0],[43.491402364280965,48.35279274032463,1197.85,9.0,0.0,1.0,1.0],[48.35279274032463,99.39739168878312,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>[[19.314279809579716,45.89321687238527,-1860.0,9.0,0.0,0.0,1.0],[45.89321687238527,50.72575088380445,0.0,8.0,8.0,2.0,-1.0],[50.72575088380445,99.05109099799635,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[19.314279809579716,45.89321687238527,-1860.0,8.0,0.0,0.0,1.0],[45.89321687238527,50.72575088380445,0.0,7.0,8.0,2.0,-1.0],[50.72575088380445,99.05109099799635,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>[[17.7712642036819,43.66277656667039,-1860.0,8.0,0.0,0.0,1.0],[43.66277656667039,47.83882694779757,-873.8504,7.0,8.0,2.0,-1.0],[47.83882694779757,52.85008740515018,0.0,7.0,8.0,2.0,-1.0],[52.85008740515018,54.52050755760105,890.0,8.0,8.0,1.0,-1.0],[54.52050755760105,100.45706175,1860.0,8.0,9.0,0.0,-1.0]]</t>
+          <t>[[17.7712642036819,43.66277656667039,-1860.0,8.0,0.0,0.0,1.0],[43.66277656667039,47.83882694779757,-873.8505,7.0,8.0,2.0,-1.0],[47.83882694779757,52.85008740515018,0.0,7.0,8.0,2.0,-1.0],[52.85008740515018,54.52050755760105,890.0,8.0,8.0,1.0,-1.0],[54.52050755760105,100.45706175,1860.0,8.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>[[13.316516355357539,44.9441072206282,-1860.0,7.0,0.0,0.0,1.0],[44.9441072206282,50.07290573932073,0.0,7.0,0.0,1.0,1.0],[50.07290573932073,56.056504011128695,890.0,7.0,8.0,1.0,-1.0],[56.056504011128695,97.94169191378442,1860.0,7.0,9.0,0.0,-1.0]]</t>
+          <t>[[13.316516355357539,44.9441072206282,-1860.0,6.0,0.0,0.0,1.0],[44.9441072206282,50.07290573932073,0.0,7.0,0.0,1.0,1.0],[50.07290573932073,56.056504011128695,890.0,7.0,8.0,1.0,-1.0],[56.056504011128695,97.94169191378442,1860.0,5.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>[[15.387718341693397,47.453515135232266,-1860.0,6.0,0.0,0.0,1.0],[47.453515135232266,52.51653568158051,0.0,5.0,8.0,2.0,-1.0],[52.51653568158051,56.735719470204046,890.0,6.0,8.0,1.0,-1.0],[56.735719470204046,98.9275573564394,1860.0,6.0,8.0,1.0,-1.0]]</t>
+          <t>[[15.387718341693397,47.453515135232266,-1860.0,5.0,0.0,0.0,1.0],[47.453515135232266,52.51653568158051,0.0,5.0,8.0,2.0,-1.0],[52.51653568158051,56.735719470204046,890.0,5.0,8.0,1.0,-1.0],[56.735719470204046,98.9275573564394,1860.0,6.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>[[13.557467447436517,43.40177256144821,-1860.0,5.0,0.0,0.0,1.0],[43.40177256144821,46.912867280743704,-873.8504,4.0,8.0,2.0,-1.0],[46.912867280743704,51.30173567986307,0.0,4.0,8.0,2.0,-1.0],[51.30173567986307,53.935056719334696,890.0,5.0,8.0,1.0,-1.0],[53.935056719334696,100.45706175,1860.0,5.0,9.0,0.0,-1.0]]</t>
+          <t>[[13.557467447436517,43.40177256144821,-1860.0,4.0,0.0,0.0,1.0],[43.40177256144821,46.912867280743704,-873.8505,4.0,8.0,2.0,-1.0],[46.912867280743704,51.30173567986307,0.0,3.0,8.0,2.0,-1.0],[51.30173567986307,53.935056719334696,890.0,4.0,8.0,1.0,-1.0],[53.935056719334696,100.45706175,1860.0,5.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>[[14.205980775788843,43.31364776090793,-1860.0,4.0,0.0,0.0,1.0],[43.31364776090793,45.88197131841844,-873.8504,3.0,8.0,2.0,-1.0],[45.88197131841844,51.01861843343946,0.0,3.0,8.0,2.0,-1.0],[51.01861843343946,53.58694199094996,890.0,4.0,8.0,1.0,-1.0],[53.58694199094996,98.9606581736356,1860.0,4.0,9.0,0.0,-1.0]]</t>
+          <t>[[14.205980775788843,43.31364776090793,-1860.0,3.0,0.0,0.0,1.0],[43.31364776090793,45.88197131841844,-873.8505,2.0,8.0,2.0,-1.0],[45.88197131841844,51.01861843343946,0.0,2.0,8.0,2.0,-1.0],[51.01861843343946,53.58694199094996,890.0,3.0,8.0,1.0,-1.0],[53.58694199094996,98.9606581736356,1860.0,3.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>[[12.882699270253498,44.57615845506954,-1860.0,3.0,0.0,0.0,1.0],[44.57615845506954,47.21728005380421,-873.8504,2.0,8.0,2.0,-1.0],[47.21728005380421,52.49952325127355,0.0,2.0,8.0,2.0,-1.0],[52.49952325127355,55.14064485000822,890.0,3.0,8.0,1.0,-1.0],[55.14064485000822,100.03971202849762,1860.0,3.0,9.0,0.0,-1.0]]</t>
+          <t>[[12.882699270253498,44.57615845506954,-1860.0,2.0,0.0,0.0,1.0],[44.57615845506954,47.21728005380421,-873.8505,2.0,8.0,2.0,-1.0],[47.21728005380421,52.49952325127355,0.0,2.0,8.0,2.0,-1.0],[52.49952325127355,55.14064485000822,890.0,2.0,8.0,1.0,-1.0],[55.14064485000822,100.03971202849762,1860.0,2.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>[[13.562888205077785,43.40533164474804,-1860.0,2.0,0.0,0.0,1.0],[43.40533164474804,45.16076949414041,-873.8504,1.0,8.0,2.0,-1.0],[45.16076949414041,50.42708304231751,0.0,1.0,8.0,2.0,-1.0],[50.42708304231751,53.06023981640606,890.0,2.0,8.0,1.0,-1.0],[53.06023981640606,100.45706175,1860.0,2.0,9.0,0.0,-1.0]]</t>
+          <t>[[13.562888205077785,43.40533164474804,-1860.0,2.0,0.0,0.0,1.0],[43.40533164474804,45.16076949414041,-873.8505,1.0,8.0,2.0,-1.0],[45.16076949414041,50.42708304231751,0.0,1.0,8.0,2.0,-1.0],[50.42708304231751,53.06023981640606,890.0,2.0,8.0,1.0,-1.0],[53.06023981640606,100.45706175,1860.0,2.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>[[14.45151079436823,46.03344240870201,-1860.0,1.0,0.0,0.0,1.0],[46.03344240870201,47.6956493357722,-873.8504,0.0,8.0,2.0,-1.0],[47.6956493357722,52.6822701169828,0.0,0.0,8.0,2.0,-1.0],[52.6822701169828,56.837787434658296,890.0,1.0,8.0,1.0,-1.0],[56.837787434658296,96.73075368434307,1860.0,1.0,9.0,0.0,-1.0]]</t>
+          <t>[[14.45151079436823,46.03344240870201,-1860.0,1.0,0.0,0.0,1.0],[46.03344240870201,47.6956493357722,-873.8505,0.0,8.0,2.0,-1.0],[47.6956493357722,52.6822701169828,0.0,0.0,8.0,2.0,-1.0],[52.6822701169828,56.837787434658296,890.0,0.0,8.0,1.0,-1.0],[56.837787434658296,96.73075368434307,1860.0,1.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>[[13.26656992515346,50.256475547815626,-0.0,0.0,0.0,1.0,1.0],[50.256475547815626,55.54074777962451,890.0,0.0,8.0,1.0,-1.0],[55.54074777962451,100.45706175,1860.0,0.0,9.0,0.0,-1.0]]</t>
+          <t>[[13.26656992515346,50.256475547815626,0.0,0.0,0.0,1.0,1.0],[50.256475547815626,55.54074777962451,890.0,0.0,8.0,1.0,-1.0],[55.54074777962451,100.45706175,1860.0,0.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>[[14.224997611241855,40.648856611974345,-0.0,0.0,0.0,1.0,1.0],[40.648856611974345,63.663185419063936,890.0,0.0,8.0,0.0,-1.0],[63.663185419063936,98.61086990390369,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[14.224997611241855,40.648856611974345,0.0,0.0,0.0,1.0,1.0],[40.648856611974345,63.663185419063936,890.0,0.0,8.0,0.0,-1.0],[63.663185419063936,98.61086990390369,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>[[13.0631040652436,35.13228529876794,-986.1496,0.0,0.0,0.0,1.0],[35.13228529876794,43.959957792177676,-0.0,0.0,8.0,1.0,-1.0],[43.959957792177676,100.45706175,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[13.0631040652436,35.13228529876794,-986.1497,0.0,0.0,0.0,1.0],[35.13228529876794,43.959957792177676,0.0,0.0,8.0,1.0,-1.0],[43.959957792177676,100.45706175,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>[[14.093150567174522,35.902219047686,-1860.0,1.0,7.0,0.0,-1.0],[35.902219047686,42.00875822222922,-0.0,0.0,6.0,1.0,-1.0],[42.00875822222922,100.45706175,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[14.093150567174522,35.902219047686,-1860.0,1.0,7.0,0.0,-1.0],[35.902219047686,42.00875822222922,0.0,0.0,6.0,1.0,-1.0],[42.00875822222922,100.45706175,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>[[14.075358982535585,35.70465964650596,-1860.0,1.0,6.0,0.0,-1.0],[35.70465964650596,42.359829081573764,-0.0,0.0,6.0,1.0,-1.0],[42.359829081573764,96.4330807414997,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[14.075358982535585,35.70465964650596,-1860.0,1.0,6.0,0.0,-1.0],[35.70465964650596,42.359829081573764,0.0,0.0,6.0,1.0,-1.0],[42.359829081573764,96.4330807414997,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>[[13.597342608971536,34.783539008924585,-1860.0,1.0,5.0,1.0,-1.0],[34.783539008924585,41.56312185690956,-0.0,0.0,5.0,1.0,-1.0],[41.56312185690956,97.4946803527856,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[13.597342608971536,34.783539008924585,-1860.0,1.0,5.0,1.0,-1.0],[34.783539008924585,41.56312185690956,0.0,0.0,5.0,1.0,-1.0],[41.56312185690956,97.4946803527856,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>[[13.838907630315594,36.11296720663019,-1860.0,1.0,2.0,0.0,-1.0],[36.11296720663019,42.37754646246867,-0.0,0.0,2.0,1.0,-1.0],[42.37754646246867,82.74927944453887,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[13.838907630315594,36.11296720663019,-1860.0,1.0,2.0,0.0,-1.0],[36.11296720663019,42.37754646246867,0.0,0.0,2.0,1.0,-1.0],[42.37754646246867,82.74927944453887,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>[[13.812296661655028,35.755033195775056,-1860.0,1.0,1.0,0.0,-1.0],[35.755033195775056,39.93460205941696,-0.0,0.0,1.0,1.0,-1.0],[39.93460205941696,42.54683259919316,0.0,0.0,0.0,1.0,-1.0],[42.54683259919316,47.2488475707903,1860.0,0.0,0.0,0.0,-1.0],[47.2488475707903,65.53446134922366,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[13.812296661655028,35.755033195775056,-1860.0,1.0,1.0,0.0,-1.0],[35.755033195775056,40.97949427532744,0.0,0.0,1.0,1.0,-1.0],[40.97949427532744,42.54683259919316,0.0,0.0,0.0,1.0,-1.0],[42.54683259919316,47.2488475707903,1860.0,0.0,0.0,0.0,-1.0],[47.2488475707903,65.53446134922366,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>[[13.690500721491528,35.55788734116837,-1860.0,1.0,0.0,0.0,-1.0],[35.55788734116837,62.89212061576441,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[13.690500721491528,35.55788734116837,-1860.0,1.0,0.0,0.0,-1.0],[35.55788734116837,62.89212061576441,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>[[13.361370108220429,33.697687838089095,-1860.0,1.0,0.0,0.0,-1.0],[33.697687838089095,64.98433049942551,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[13.361370108220429,33.697687838089095,-1860.0,1.0,0.0,0.0,-1.0],[33.697687838089095,64.98433049942551,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>[[14.156169684915382,34.07776706863876,-1860.0,1.0,0.0,0.0,-1.0],[34.07776706863876,64.72637842821318,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[14.156169684915382,34.07776706863876,-1860.0,1.0,0.0,0.0,-1.0],[34.07776706863876,64.72637842821318,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>[[13.359833766607641,29.07844754588593,-1860.0,1.0,0.0,0.0,-1.0],[29.07844754588593,61.989295146249844,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[13.359833766607641,29.07844754588593,-1860.0,1.0,0.0,0.0,-1.0],[29.07844754588593,61.989295146249844,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>[[14.32771698013276,29.117100575966113,-1860.0,8.0,0.0,0.0,1.0],[29.117100575966113,35.79617703860053,-733.6842,8.0,0.0,0.0,1.0],[35.79617703860053,39.61279216010591,0.0,8.0,8.0,3.0,-1.0],[39.61279216010591,40.089869050294084,227.85,8.0,8.0,1.0,-1.0],[40.089869050294084,61.55832910876185,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[14.32771698013276,29.117100575966113,-1860.0,7.0,0.0,0.0,1.0],[29.117100575966113,35.79617703860053,-733.6843,8.0,0.0,0.0,1.0],[35.79617703860053,39.61279216010591,0.0,8.0,8.0,3.0,-1.0],[39.61279216010591,40.089869050294084,227.85,8.0,8.0,1.0,-1.0],[40.089869050294084,61.55832910876185,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>[[12.357863091369897,33.57936852334953,-1860.0,8.0,8.0,2.0,-1.0],[33.57936852334953,36.23205670234698,-1607.5346,7.0,8.0,1.0,-1.0],[36.23205670234698,39.94582015294341,0.0,7.0,8.0,1.0,-1.0],[39.94582015294341,43.12904596774036,227.85,8.0,8.0,0.0,-1.0],[43.12904596774036,64.88108903551948,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[12.357863091369897,33.57936852334953,-1860.0,7.0,8.0,2.0,-1.0],[33.57936852334953,36.23205670234698,-1607.5347,7.0,8.0,1.0,-1.0],[36.23205670234698,39.94582015294341,0.0,7.0,8.0,1.0,-1.0],[39.94582015294341,43.12904596774036,227.85,8.0,8.0,0.0,-1.0],[43.12904596774036,64.88108903551948,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>[[11.21110265021379,35.24802977673849,-1860.0,7.0,8.0,1.0,-1.0],[35.24802977673849,35.77057167079338,-1607.5346,6.0,8.0,1.0,-1.0],[35.77057167079338,39.42836492917757,0.0,6.0,8.0,1.0,-1.0],[39.42836492917757,43.60870008161665,227.85,7.0,8.0,0.0,-1.0],[43.60870008161665,62.94275016164738,1860.0,7.0,8.0,0.0,-1.0]]</t>
+          <t>[[11.21110265021379,35.24802977673849,-1860.0,7.0,8.0,1.0,-1.0],[35.24802977673849,35.77057167079338,-1607.5347,6.0,8.0,1.0,-1.0],[35.77057167079338,39.42836492917757,0.0,6.0,8.0,1.0,-1.0],[39.42836492917757,43.60870008161665,227.85,7.0,8.0,0.0,-1.0],[43.60870008161665,62.94275016164738,1860.0,6.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>[[8.484482162591622,35.29868984702014,-1860.0,6.0,8.0,1.0,-1.0],[35.29868984702014,36.94037603178107,-1607.5346,5.0,8.0,1.0,-1.0],[36.94037603178107,41.31820585781023,0.0,5.0,8.0,1.0,-1.0],[41.31820585781023,45.14880695558573,227.85,6.0,8.0,0.0,-1.0],[45.14880695558573,62.66012625970232,1860.0,6.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.484482162591622,35.29868984702014,-1860.0,6.0,8.0,1.0,-1.0],[35.29868984702014,36.94037603178107,-1607.5347,4.0,8.0,1.0,-1.0],[36.94037603178107,41.31820585781023,0.0,5.0,8.0,1.0,-1.0],[41.31820585781023,45.14880695558573,227.85,5.0,8.0,0.0,-1.0],[45.14880695558573,62.66012625970232,1860.0,5.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>[[8.176251301373576,36.24799841734511,-1860.0,5.0,0.0,0.0,1.0],[36.24799841734511,40.178043013581124,0.0,5.0,8.0,1.0,-1.0],[40.178043013581124,41.86234784053942,227.85,5.0,8.0,0.0,-1.0],[41.86234784053942,63.75831059099721,1860.0,5.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.176251301373576,36.24799841734511,-1860.0,4.0,0.0,0.0,1.0],[36.24799841734511,40.178043013581124,0.0,4.0,8.0,1.0,-1.0],[40.178043013581124,41.86234784053942,227.85,4.0,8.0,0.0,-1.0],[41.86234784053942,63.75831059099721,1860.0,4.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>[[8.200410679129284,36.11397131683742,-1860.0,4.0,8.0,1.0,-1.0],[36.11397131683742,36.68363581964779,-1607.5346,3.0,8.0,1.0,-1.0],[36.68363581964779,40.67128733932038,0.0,3.0,8.0,1.0,-1.0],[40.67128733932038,41.81061634494112,227.85,4.0,8.0,0.0,-1.0],[41.81061634494112,64.59719645735592,1860.0,4.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.200410679129284,36.11397131683742,-1860.0,3.0,8.0,1.0,-1.0],[36.11397131683742,36.68363581964779,-1607.5347,2.0,8.0,1.0,-1.0],[36.68363581964779,40.67128733932038,0.0,2.0,8.0,1.0,-1.0],[40.67128733932038,41.81061634494112,227.85,3.0,8.0,0.0,-1.0],[41.81061634494112,64.59719645735592,1860.0,3.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>[[8.911479795307043,35.554552601145645,-1860.0,3.0,0.0,0.0,1.0],[35.554552601145645,37.72949731998961,-733.6842,3.0,0.0,0.0,1.0],[37.72949731998961,42.07938675767755,0.0,3.0,8.0,1.0,-1.0],[42.07938675767755,42.623122937388544,227.85,3.0,8.0,0.0,-1.0],[42.623122937388544,62.74136158669524,1860.0,3.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.911479795307043,35.554552601145645,-1860.0,2.0,0.0,0.0,1.0],[35.554552601145645,37.72949731998961,-733.6843,2.0,0.0,0.0,1.0],[37.72949731998961,42.07938675767755,0.0,2.0,8.0,1.0,-1.0],[42.07938675767755,42.623122937388544,227.85,2.0,8.0,0.0,-1.0],[42.623122937388544,62.74136158669524,1860.0,2.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>[[8.590642544444625,36.4489796238833,-1860.0,2.0,8.0,3.0,-1.0],[36.4489796238833,37.56331310706084,-1607.5346,1.0,8.0,1.0,-1.0],[37.56331310706084,42.020647039771035,0.0,1.0,8.0,1.0,-1.0],[42.020647039771035,43.692147264537354,227.85,2.0,8.0,0.0,-1.0],[43.692147264537354,63.75014996173319,1860.0,2.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.590642544444625,36.4489796238833,-1860.0,2.0,8.0,3.0,-1.0],[36.4489796238833,37.56331310706084,-1607.5347,1.0,8.0,1.0,-1.0],[37.56331310706084,42.020647039771035,0.0,1.0,8.0,1.0,-1.0],[42.020647039771035,43.692147264537354,227.85,2.0,8.0,0.0,-1.0],[43.692147264537354,63.75014996173319,1860.0,1.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>[[7.726651746095345,35.40296443649466,-1860.0,1.0,0.0,0.0,1.0],[35.40296443649466,37.03098283004757,-733.6842,1.0,0.0,0.0,1.0],[37.03098283004757,41.3723652128553,0.0,1.0,8.0,3.0,-1.0],[41.3723652128553,44.08572920211014,227.85,1.0,8.0,0.0,-1.0],[44.08572920211014,61.451258733341085,1860.0,1.0,8.0,0.0,-1.0]]</t>
+          <t>[[7.726651746095345,35.40296443649466,-1860.0,1.0,0.0,0.0,1.0],[35.40296443649466,37.03098283004757,-733.6843,0.0,0.0,0.0,1.0],[37.03098283004757,41.3723652128553,0.0,1.0,8.0,3.0,-1.0],[41.3723652128553,44.08572920211014,227.85,0.0,8.0,0.0,-1.0],[44.08572920211014,61.451258733341085,1860.0,1.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>[[8.359104983231369,36.184511379983604,-733.6842,0.0,0.0,0.0,1.0],[36.184511379983604,40.08006827552892,0.0,0.0,8.0,1.0,-1.0],[40.08006827552892,43.41911704313919,227.85,0.0,8.0,0.0,-1.0],[43.41911704313919,63.45340964880081,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.359104983231369,36.184511379983604,-733.6844,0.0,0.0,0.0,1.0],[36.184511379983604,40.08006827552892,0.0,0.0,8.0,1.0,-1.0],[40.08006827552892,43.41911704313919,227.85,0.0,8.0,0.0,-1.0],[43.41911704313919,63.45340964880081,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>[[8.39296009039569,35.209335418135765,-733.6842,0.0,0.0,0.0,1.0],[35.209335418135765,39.04024617924149,0.0,0.0,8.0,2.0,-1.0],[39.04024617924149,42.323883974474974,227.85,0.0,8.0,0.0,-1.0],[42.323883974474974,62.572983711748094,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.39296009039569,35.209335418135765,-733.6844,0.0,0.0,0.0,1.0],[35.209335418135765,39.04024617924149,0.0,0.0,8.0,2.0,-1.0],[39.04024617924149,42.323883974474974,227.85,0.0,8.0,0.0,-1.0],[42.323883974474974,62.572983711748094,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>[[8.381231291361221,34.28626217253296,-1860.0,1.0,2.0,0.0,-1.0],[34.28626217253296,36.67749579233343,-1808.4765,0.0,2.0,1.0,-1.0],[36.67749579233343,40.66288515866755,0.0,0.0,1.0,2.0,-1.0],[40.66288515866755,47.83658601806895,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[8.381231291361221,34.28626217253296,-1860.0,0.0,2.0,0.0,-1.0],[34.28626217253296,36.67749579233343,-1808.4765,0.0,2.0,1.0,-1.0],[36.67749579233343,40.66288515866755,0.0,0.0,1.0,2.0,-1.0],[40.66288515866755,47.83658601806895,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>[[8.15703010922491,34.94278558576943,-1860.0,1.0,1.0,1.0,-1.0],[34.94278558576943,36.043570057408246,-1808.4765,0.0,1.0,1.0,-1.0],[36.043570057408246,39.71285162953763,0.0,0.0,0.0,2.0,-1.0],[39.71285162953763,44.482917673305835,227.85,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[8.15703010922491,34.94278558576943,-1860.0,1.0,1.0,1.0,-1.0],[34.94278558576943,36.043570057408246,-1808.4765,0.0,1.0,1.0,-1.0],[36.043570057408246,39.71285162953763,0.0,0.0,0.0,2.0,-1.0],[39.71285162953763,42.2813487300282,227.85,0.0,0.0,0.0,-1.0],[42.2813487300282,44.482917673305835,227.8501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>[[8.214199054710384,35.800383175827015,-1860.0,1.0,0.0,0.0,-1.0],[35.800383175827015,44.148833633533364,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[8.214199054710384,35.800383175827015,-1860.0,1.0,0.0,0.0,-1.0],[35.800383175827015,44.148833633533364,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>[[8.231776226073956,33.37978573773485,-1860.0,1.0,0.0,0.0,-1.0],[33.37978573773485,45.39077535524453,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[8.231776226073956,33.37978573773485,-1860.0,1.0,0.0,0.0,-1.0],[33.37978573773485,45.39077535524453,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>[[8.484932719365416,27.172711165237473,-1860.0,1.0,0.0,0.0,-1.0],[27.172711165237473,46.241872844698754,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[8.484932719365416,27.172711165237473,-1860.0,1.0,0.0,0.0,-1.0],[27.172711165237473,46.241872844698754,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>[[8.444957811119819,24.641902689125708,-1860.0,8.0,0.0,0.0,1.0],[24.641902689125708,30.81216740455652,-733.6842,8.0,0.0,0.0,1.0],[30.81216740455652,33.89729976227193,0.0,8.0,0.0,1.0,1.0],[33.89729976227193,36.21114903055849,1016.5,9.0,0.0,0.0,1.0],[36.21114903055849,46.62347073784799,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[8.444957811119819,24.641902689125708,-1860.0,7.0,0.0,0.0,1.0],[24.641902689125708,30.81216740455652,-733.6843,8.0,0.0,0.0,1.0],[30.81216740455652,33.89729976227193,0.0,7.0,0.0,1.0,1.0],[33.89729976227193,36.21114903055849,1016.5,9.0,0.0,0.0,1.0],[36.21114903055849,46.62347073784799,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>[[8.456687325990359,25.67480672719658,-1860.0,7.0,0.0,0.0,1.0],[25.67480672719658,30.07092231899391,-733.6842,7.0,0.0,0.0,1.0],[30.07092231899391,33.36800901284191,0.0,7.0,0.0,1.0,1.0],[33.36800901284191,35.56606680874057,1016.5,8.0,0.0,0.0,1.0],[35.56606680874057,44.72464095831835,1860.0,8.0,9.0,2.0,-1.0]]</t>
+          <t>[[8.456687325990359,25.67480672719658,-1860.0,6.0,0.0,0.0,1.0],[25.67480672719658,30.07092231899391,-733.6843,6.0,0.0,0.0,1.0],[30.07092231899391,33.36800901284191,0.0,6.0,0.0,1.0,1.0],[33.36800901284191,35.56606680874057,1016.5,7.0,0.0,0.0,1.0],[35.56606680874057,44.72464095831835,1860.0,7.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>[[8.16146712689788,25.243628411246725,-1860.0,6.0,0.0,0.0,1.0],[25.243628411246725,27.471736404857445,-733.6842,6.0,0.0,0.0,1.0],[27.471736404857445,30.442547063005065,0.0,6.0,0.0,1.0,1.0],[30.442547063005065,36.01281704703187,1016.5,7.0,0.0,0.0,1.0],[36.01281704703187,44.92524902147474,1860.0,7.0,9.0,0.0,-1.0]]</t>
+          <t>[[8.16146712689788,25.243628411246725,-1860.0,6.0,0.0,0.0,1.0],[25.243628411246725,27.471736404857445,-733.6843,5.0,0.0,0.0,1.0],[27.471736404857445,30.442547063005065,0.0,6.0,0.0,1.0,1.0],[30.442547063005065,36.01281704703187,1016.5,7.0,0.0,0.0,1.0],[36.01281704703187,44.92524902147474,1860.0,7.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>[[8.595806879666561,24.820478435008496,-1860.0,5.0,0.0,0.0,1.0],[24.820478435008496,27.642160444633184,-733.6842,5.0,0.0,0.0,1.0],[27.642160444633184,30.46384245425787,0.0,5.0,0.0,1.0,1.0],[30.46384245425787,36.459916724710325,1016.5,6.0,0.0,0.0,1.0],[36.459916724710325,43.514121748772034,1860.0,6.0,9.0,3.0,-1.0]]</t>
+          <t>[[8.595806879666561,24.820478435008496,-1860.0,4.0,0.0,0.0,1.0],[24.820478435008496,27.642160444633184,-733.6843,4.0,0.0,0.0,1.0],[27.642160444633184,30.46384245425787,0.0,4.0,0.0,1.0,1.0],[30.46384245425787,36.459916724710325,1016.5,4.0,0.0,0.0,1.0],[36.459916724710325,43.514121748772034,1860.0,5.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>[[12.76980788055936,25.119448349497155,-1860.0,4.0,0.0,0.0,1.0],[25.119448349497155,29.579040741058023,-733.6842,4.0,0.0,0.0,1.0],[29.579040741058023,32.66645085829247,0.0,4.0,0.0,1.0,1.0],[32.66645085829247,36.78299768127174,1016.5,5.0,0.0,0.0,1.0],[36.78299768127174,46.73131917013829,1860.0,5.0,9.0,1.0,-1.0]]</t>
+          <t>[[12.76980788055936,25.119448349497155,-1860.0,3.0,0.0,0.0,1.0],[25.119448349497155,29.579040741058023,-733.6843,3.0,0.0,0.0,1.0],[29.579040741058023,32.66645085829247,0.0,3.0,0.0,1.0,1.0],[32.66645085829247,36.78299768127174,1016.5,4.0,0.0,0.0,1.0],[36.78299768127174,46.73131917013829,1860.0,4.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>[[15.99501225267529,24.866380518087936,-1860.0,3.0,0.0,0.0,1.0],[24.866380518087936,27.925473023402642,-733.6842,3.0,0.0,0.0,1.0],[27.925473023402642,30.984565528717347,0.0,3.0,0.0,1.0,1.0],[30.984565528717347,34.65547653509499,1016.5,4.0,0.0,0.0,1.0],[34.65547653509499,46.28002805529087,1860.0,4.0,9.0,4.0,-1.0]]</t>
+          <t>[[15.99501225267529,24.866380518087936,-1860.0,2.0,0.0,0.0,1.0],[24.866380518087936,27.925473023402642,-733.6843,2.0,0.0,0.0,1.0],[27.925473023402642,30.984565528717347,0.0,2.0,0.0,1.0,1.0],[30.984565528717347,34.65547653509499,1016.5,3.0,0.0,0.0,1.0],[34.65547653509499,46.28002805529087,1860.0,3.0,9.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>[[15.45241967339454,25.600846042245905,-1860.0,2.0,0.0,0.0,1.0],[25.600846042245905,28.500396433346296,-733.6842,2.0,0.0,0.0,1.0],[28.500396433346296,31.399946824446687,0.0,2.0,0.0,1.0,1.0],[31.399946824446687,36.039227450207306,1016.5,3.0,0.0,0.0,1.0],[36.039227450207306,44.1579685452884,1860.0,3.0,9.0,2.0,-1.0]]</t>
+          <t>[[15.45241967339454,25.600846042245905,-1860.0,2.0,0.0,0.0,1.0],[25.600846042245905,28.500396433346296,-733.6843,2.0,0.0,0.0,1.0],[28.500396433346296,31.399946824446687,0.0,1.0,0.0,1.0,1.0],[31.399946824446687,36.039227450207306,1016.5,2.0,0.0,0.0,1.0],[36.039227450207306,44.1579685452884,1860.0,2.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>[[15.99518482713048,25.395510763969092,-1860.0,1.0,0.0,0.0,1.0],[25.395510763969092,28.33311261923116,-733.6842,1.0,0.0,0.0,1.0],[28.33311261923116,31.564474660019435,0.0,1.0,0.0,1.0,1.0],[31.564474660019435,36.26463762843874,1016.5,2.0,0.0,0.0,1.0],[36.26463762843874,45.07744319422494,1860.0,2.0,9.0,2.0,-1.0]]</t>
+          <t>[[15.99518482713048,25.395510763969092,-1860.0,1.0,0.0,0.0,1.0],[25.395510763969092,28.33311261923116,-733.6843,0.0,0.0,0.0,1.0],[28.33311261923116,31.564474660019435,0.0,1.0,0.0,1.0,1.0],[31.564474660019435,36.26463762843874,1016.5,2.0,0.0,0.0,1.0],[36.26463762843874,45.07744319422494,1860.0,2.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -6359,11 +6359,11 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>[[15.336249492833469,28.71106901098448,-733.6842,0.0,0.0,0.0,1.0],[28.71106901098448,31.750800719655167,0.0,0.0,0.0,1.0,1.0],[31.750800719655167,36.00642511179412,1016.5,1.0,0.0,0.0,1.0],[36.00642511179412,45.42959340867324,1860.0,1.0,9.0,2.0,-1.0]]</t>
+          <t>[[15.336249492833469,25.975310473180862,-733.6844,0.0,0.0,0.0,1.0],[25.975310473180862,28.71106901098448,-733.6843,0.0,0.0,0.0,1.0],[28.71106901098448,31.750800719655167,0.0,0.0,0.0,1.0,1.0],[31.750800719655167,36.00642511179412,1016.5,1.0,0.0,0.0,1.0],[36.00642511179412,45.42959340867324,1860.0,0.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>-733.6842</v>
+        <v>-733.6844</v>
       </c>
       <c r="D258" s="4" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>[[16.06438042500798,36.96599093567612,-0.0,0.0,0.0,1.0,1.0],[36.96599093567612,37.25629108165762,890.0,0.0,8.0,3.0,-1.0],[37.25629108165762,44.804094877176674,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[16.06438042500798,36.96599093567612,0.0,0.0,0.0,1.0,1.0],[36.96599093567612,37.25629108165762,890.0,0.0,8.0,3.0,-1.0],[37.25629108165762,44.804094877176674,1860.0,0.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>[[15.719847462416912,35.42905634531299,-0.0,0.0,0.0,1.0,1.0],[35.42905634531299,36.555296852907055,890.0,0.0,8.0,2.0,-1.0],[36.555296852907055,43.59430002536994,1860.0,0.0,9.0,1.0,-1.0]]</t>
+          <t>[[15.719847462416912,35.42905634531299,0.0,0.0,0.0,1.0,1.0],[35.42905634531299,36.555296852907055,890.0,0.0,8.0,2.0,-1.0],[36.555296852907055,43.59430002536994,1860.0,0.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>[[15.467816108780807,31.68783998259861,-1860.0,1.0,8.0,2.0,-1.0],[31.68783998259861,32.27765903255562,-1074.7923,0.0,8.0,1.0,-1.0],[32.27765903255562,35.816573332297686,0.0,0.0,7.0,2.0,-1.0],[35.816573332297686,36.7013019072332,890.0,0.0,7.0,0.0,-1.0],[36.7013019072332,44.66385908165285,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[15.467816108780807,31.68783998259861,-1860.0,1.0,8.0,2.0,-1.0],[31.68783998259861,32.27765903255562,-1074.7921,0.0,8.0,1.0,-1.0],[32.27765903255562,35.816573332297686,0.0,0.0,7.0,2.0,-1.0],[35.816573332297686,36.7013019072332,890.0001,0.0,7.0,0.0,-1.0],[36.7013019072332,44.66385908165285,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>[[15.052156947622725,31.152124706297208,-1860.0,1.0,7.0,1.0,-1.0],[31.152124706297208,34.431747768249416,0.0,0.0,6.0,1.0,-1.0],[34.431747768249416,35.326190421509104,890.0,0.0,6.0,0.0,-1.0],[35.326190421509104,44.568764505192604,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[15.052156947622725,31.152124706297208,-1860.0,1.0,7.0,1.0,-1.0],[31.152124706297208,34.431747768249416,0.0,0.0,6.0,1.0,-1.0],[34.431747768249416,35.326190421509104,890.0001,0.0,6.0,0.0,-1.0],[35.326190421509104,44.568764505192604,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>[[15.640541201465409,30.235122709197704,-1860.0,1.0,7.0,1.0,-1.0],[30.235122709197704,30.515787738192554,-1074.7923,0.0,7.0,0.0,-1.0],[30.515787738192554,33.603103057135925,0.0,0.0,6.0,1.0,-1.0],[33.603103057135925,35.28709323110503,890.0,0.0,6.0,1.0,-1.0],[35.28709323110503,43.426379071955736,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[15.640541201465409,30.235122709197704,-1860.0,1.0,7.0,1.0,-1.0],[30.235122709197704,30.515787738192554,-1074.7921,0.0,7.0,0.0,-1.0],[30.515787738192554,33.603103057135925,0.0,0.0,6.0,1.0,-1.0],[33.603103057135925,35.28709323110503,890.0001,0.0,6.0,1.0,-1.0],[35.28709323110503,43.426379071955736,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>[[14.901878560461185,30.476758797770316,-1860.0,1.0,7.0,0.0,-1.0],[30.476758797770316,30.776275725410876,-1074.7923,0.0,7.0,0.0,-1.0],[30.776275725410876,34.07096192945704,0.0,0.0,6.0,1.0,-1.0],[34.07096192945704,34.370478857097595,890.0,0.0,6.0,0.0,-1.0],[34.370478857097595,44.554054396876644,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[14.901878560461185,30.476758797770316,-1860.0,1.0,7.0,0.0,-1.0],[30.476758797770316,30.776275725410876,-1074.7921,0.0,7.0,0.0,-1.0],[30.776275725410876,34.07096192945704,0.0,0.0,6.0,1.0,-1.0],[34.07096192945704,34.370478857097595,890.0001,0.0,6.0,0.0,-1.0],[34.370478857097595,44.554054396876644,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -6520,7 +6520,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>[[15.912450500068951,30.96146709076174,-1860.0,1.0,6.0,0.0,-1.0],[30.96146709076174,31.2081722807731,-1074.7923,0.0,6.0,1.0,-1.0],[31.2081722807731,34.41533975092074,0.0,0.0,5.0,2.0,-1.0],[34.41533975092074,35.40216051096617,890.0,0.0,5.0,0.0,-1.0],[35.40216051096617,40.33626431119331,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[15.912450500068951,30.96146709076174,-1860.0,1.0,6.0,0.0,-1.0],[30.96146709076174,31.2081722807731,-1074.7921,0.0,6.0,1.0,-1.0],[31.2081722807731,34.41533975092074,0.0,0.0,5.0,2.0,-1.0],[34.41533975092074,35.40216051096617,890.0001,0.0,5.0,0.0,-1.0],[35.40216051096617,40.33626431119331,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>[[16.135123603165802,20.210664734416042,-1860.0,9.0,13.0,1.0,0.0],[20.210664734416042,30.17309861080552,-1074.7923,0.0,6.0,0.0,-1.0],[30.17309861080552,33.56938288684739,0.0,0.0,5.0,1.0,-1.0],[33.56938288684739,34.022220790319636,890.0,0.0,5.0,1.0,-1.0],[34.022220790319636,38.55059982504213,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[16.135123603165802,20.210664734416042,-1860.0,9.0,13.0,1.0,0.0],[20.210664734416042,30.17309861080552,-1074.7921,0.0,6.0,0.0,-1.0],[30.17309861080552,33.56938288684739,0.0,0.0,5.0,1.0,-1.0],[33.56938288684739,34.022220790319636,890.0001,0.0,5.0,1.0,-1.0],[34.022220790319636,38.55059982504213,1860.0,0.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>[[15.675729073966822,20.3956468169795,-1860.0,9.0,5.0,0.0,1.0],[20.3956468169795,21.74419474355455,-1808.4765,9.0,5.0,0.0,1.0],[21.74419474355455,30.284998278529876,-1074.7923,0.0,5.0,0.0,-1.0],[30.284998278529876,33.656368094967505,0.0,0.0,4.0,1.0,-1.0],[33.656368094967505,34.78015803378005,890.0,0.0,4.0,1.0,-1.0],[34.78015803378005,37.92676986245517,1860.0,0.0,4.0,1.0,-1.0]]</t>
+          <t>[[15.675729073966822,20.3956468169795,-1860.0,9.0,5.0,0.0,1.0],[20.3956468169795,21.74419474355455,-1808.4763,9.0,5.0,0.0,1.0],[21.74419474355455,30.284998278529876,-1074.7921,0.0,5.0,0.0,-1.0],[30.284998278529876,33.656368094967505,0.0,0.0,4.0,1.0,-1.0],[33.656368094967505,34.78015803378005,890.0001,0.0,4.0,1.0,-1.0],[34.78015803378005,37.92676986245517,1860.0,0.0,4.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>[[15.870474893686131,21.02302767466669,-1860.0,9.0,4.0,0.0,1.0],[21.02302767466669,21.435231897145133,-1808.4765,9.0,4.0,0.0,1.0],[21.435231897145133,29.26711212423558,-1074.7923,0.0,4.0,0.0,-1.0],[29.26711212423558,32.56474590406314,0.0,0.0,3.0,1.0,-1.0],[32.56474590406314,35.03797123893381,890.0,0.0,3.0,1.0,-1.0],[35.03797123893381,36.27458390636914,1860.0,0.0,3.0,1.0,-1.0]]</t>
+          <t>[[15.870474893686131,21.02302767466669,-1860.0,9.0,4.0,0.0,1.0],[21.02302767466669,21.435231897145133,-1808.4763,9.0,4.0,0.0,1.0],[21.435231897145133,29.26711212423558,-1074.7921,0.0,4.0,0.0,-1.0],[29.26711212423558,32.56474590406314,0.0,0.0,3.0,1.0,-1.0],[32.56474590406314,35.03797123893381,890.0001,0.0,3.0,1.0,-1.0],[35.03797123893381,36.27458390636914,1860.0,0.0,3.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>890</v>
+        <v>890.0001</v>
       </c>
       <c r="D268" s="4" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>[[15.724542238620721,19.698849272077297,-1860.0,9.0,3.0,0.0,1.0],[19.698849272077297,20.535545489647102,-733.6842,9.0,3.0,0.0,1.0],[20.535545489647102,33.922684970763996,0.0,0.0,3.0,1.0,-1.0],[33.922684970763996,36.43277362347341,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[15.724542238620721,19.698849272077297,-1860.0,9.0,3.0,0.0,1.0],[19.698849272077297,20.535545489647102,-733.6842,9.0,3.0,0.0,1.0],[20.535545489647102,33.922684970763996,0.0,0.0,3.0,1.0,-1.0],[33.922684970763996,36.43277362347341,1860.0,0.0,3.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>[[15.360268596773755,20.37500219047014,-1860.0,9.0,2.0,0.0,1.0],[20.37500219047014,20.976770221713707,-733.6842,9.0,2.0,0.0,1.0],[20.976770221713707,32.61095215908933,0.0,0.0,2.0,1.0,-1.0],[32.61095215908933,35.21861362781145,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[15.360268596773755,20.37500219047014,-1860.0,8.0,2.0,0.0,1.0],[20.37500219047014,20.976770221713707,-733.6842,9.0,2.0,0.0,1.0],[20.976770221713707,32.61095215908933,0.0,0.0,2.0,1.0,-1.0],[32.61095215908933,35.21861362781145,1860.0,0.0,2.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>[[15.952667004090516,18.318021832612608,-1860.0,9.0,1.0,0.0,1.0],[18.318021832612608,20.28915085638102,-532.7424,8.0,1.0,1.0,1.0],[20.28915085638102,22.45739278252627,0.0,8.0,1.0,1.0,1.0],[22.45739278252627,24.42852180629468,1197.85,9.0,1.0,0.0,1.0],[24.42852180629468,35.466844339397774,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[15.952667004090516,18.318021832612608,-1860.0,8.0,1.0,0.0,1.0],[18.318021832612608,20.28915085638102,-532.7423,8.0,1.0,1.0,1.0],[20.28915085638102,22.45739278252627,0.0,8.0,1.0,1.0,1.0],[22.45739278252627,24.42852180629468,1197.85,9.0,1.0,0.0,1.0],[24.42852180629468,35.466844339397774,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>[[15.976639529397236,18.698189764717316,-1860.0,8.0,0.0,1.0,1.0],[18.698189764717316,19.670171991617345,-532.7424,8.0,0.0,1.0,1.0],[19.670171991617345,21.80853289079741,0.0,8.0,0.0,1.0,1.0],[21.80853289079741,23.55810089921746,1197.85,9.0,0.0,0.0,1.0],[23.55810089921746,35.22188762201781,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[15.976639529397236,18.698189764717316,-1860.0,8.0,0.0,1.0,1.0],[18.698189764717316,19.670171991617345,-532.7423,8.0,0.0,1.0,1.0],[19.670171991617345,21.80853289079741,0.0,8.0,0.0,1.0,1.0],[21.80853289079741,23.55810089921746,1197.85,9.0,0.0,0.0,1.0],[23.55810089921746,35.22188762201781,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>[[15.832286293910919,21.978467773638812,-1860.0,9.0,8.0,3.0,-1.0],[21.978467773638812,22.13212231063201,-1607.5347,8.0,8.0,4.0,-1.0],[22.13212231063201,31.044085456237454,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[15.832286293910919,21.978467773638812,-1860.0,8.0,8.0,3.0,-1.0],[21.978467773638812,22.13212231063201,-1607.5346,7.0,8.0,4.0,-1.0],[22.13212231063201,31.044085456237454,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>[[12.091956485902598,21.76498431541698,-1860.0,8.0,8.0,3.0,-1.0],[21.76498431541698,21.958444872007266,-1607.5347,7.0,8.0,1.0,-1.0],[21.958444872007266,24.473432107681006,0.0,7.0,7.0,2.0,-1.0],[24.473432107681006,31.244551588341075,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[12.091956485902598,21.76498431541698,-1860.0,7.0,8.0,3.0,-1.0],[21.76498431541698,21.958444872007266,-1607.5346,7.0,8.0,1.0,-1.0],[21.958444872007266,24.473432107681006,0.0,6.0,7.0,2.0,-1.0],[24.473432107681006,31.244551588341075,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>[[10.945183828414104,22.071508761142717,-1860.0,7.0,8.0,3.0,-1.0],[22.071508761142717,22.29403525979729,-1607.5347,6.0,8.0,4.0,-1.0],[22.29403525979729,24.741826744997585,0.0,6.0,7.0,5.0,-1.0],[24.741826744997585,25.18687974230673,409.2,6.0,7.0,4.0,-1.0],[25.18687974230673,32.97530719521676,1860.0,6.0,7.0,4.0,-1.0]]</t>
+          <t>[[10.945183828414104,22.071508761142717,-1860.0,7.0,8.0,3.0,-1.0],[22.071508761142717,22.29403525979729,-1607.5346,6.0,8.0,4.0,-1.0],[22.29403525979729,24.741826744997585,0.0,6.0,7.0,5.0,-1.0],[24.741826744997585,25.18687974230673,409.2,6.0,7.0,4.0,-1.0],[25.18687974230673,32.97530719521676,1860.0,4.0,7.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>[[9.65376696164116,21.75944995118528,-1860.0,6.0,8.0,3.0,-1.0],[21.75944995118528,24.370479615596757,0.0,5.0,7.0,5.0,-1.0],[24.370479615596757,24.845212281853392,409.2,5.0,7.0,4.0,-1.0],[24.845212281853392,33.153033941344454,1860.0,5.0,8.0,3.0,-1.0]]</t>
+          <t>[[9.65376696164116,21.75944995118528,-1860.0,5.0,8.0,3.0,-1.0],[21.75944995118528,24.370479615596757,0.0,5.0,7.0,5.0,-1.0],[24.370479615596757,24.845212281853392,409.2,5.0,7.0,4.0,-1.0],[24.845212281853392,33.153033941344454,1860.0,5.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>[[9.850265458890377,22.098639673055978,-1860.0,5.0,8.0,4.0,-1.0],[22.098639673055978,22.544035099025635,-1607.5347,4.0,8.0,4.0,-1.0],[22.544035099025635,24.993709941858754,0.0,4.0,8.0,4.0,-1.0],[24.993709941858754,25.439105367828414,227.85,5.0,8.0,3.0,-1.0],[25.439105367828414,31.897339044388456,1860.0,5.0,8.0,3.0,-1.0]]</t>
+          <t>[[9.850265458890377,22.098639673055978,-1860.0,5.0,8.0,4.0,-1.0],[22.098639673055978,22.544035099025635,-1607.5346,3.0,8.0,4.0,-1.0],[22.544035099025635,24.993709941858754,0.0,3.0,8.0,4.0,-1.0],[24.993709941858754,25.439105367828414,227.85,4.0,8.0,3.0,-1.0],[25.439105367828414,31.897339044388456,1860.0,5.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>[[7.630236145808632,21.91668362163247,-1860.0,4.0,8.0,3.0,-1.0],[21.91668362163247,22.147110193823174,-1607.5347,3.0,8.0,4.0,-1.0],[22.147110193823174,24.68180248792095,0.0,3.0,7.0,5.0,-1.0],[24.68180248792095,30.442466792688627,1860.0,3.0,8.0,4.0,-1.0]]</t>
+          <t>[[7.630236145808632,21.91668362163247,-1860.0,3.0,8.0,3.0,-1.0],[21.91668362163247,22.147110193823174,-1607.5346,2.0,8.0,4.0,-1.0],[22.147110193823174,24.68180248792095,0.0,3.0,7.0,5.0,-1.0],[24.68180248792095,30.442466792688627,1860.0,2.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>[[-0.6336587098386811,21.454726636478632,-1860.0,3.0,8.0,3.0,-1.0],[21.454726636478632,22.114081422935865,-1607.5347,2.0,8.0,4.0,-1.0],[22.114081422935865,24.421823175536183,0.0,2.0,7.0,5.0,-1.0],[24.421823175536183,25.410855355222033,409.2,2.0,7.0,5.0,-1.0],[25.410855355222033,32.00440321979436,1860.0,2.0,7.0,5.0,-1.0]]</t>
+          <t>[[-0.6336587098386811,21.454726636478632,-1860.0,2.0,8.0,3.0,-1.0],[21.454726636478632,22.114081422935865,-1607.5346,2.0,8.0,4.0,-1.0],[22.114081422935865,24.421823175536183,0.0,2.0,7.0,5.0,-1.0],[24.421823175536183,25.410855355222033,409.2,2.0,7.0,5.0,-1.0],[25.410855355222033,32.00440321979436,1860.0,1.0,7.0,5.0,-1.0]]</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>[[-2.539888137032523,22.05875559180121,-1860.0,2.0,8.0,3.0,-1.0],[22.05875559180121,22.40521536262985,-1607.5347,1.0,8.0,4.0,-1.0],[22.40521536262985,24.83043375843036,0.0,1.0,7.0,5.0,-1.0],[24.83043375843036,31.759629175003248,1860.0,1.0,7.0,5.0,-1.0]]</t>
+          <t>[[-2.539888137032523,22.05875559180121,-1860.0,2.0,8.0,3.0,-1.0],[22.05875559180121,22.40521536262985,-1607.5346,1.0,8.0,4.0,-1.0],[22.40521536262985,24.83043375843036,0.0,1.0,7.0,5.0,-1.0],[24.83043375843036,31.759629175003248,1860.0,0.0,7.0,5.0,-1.0]]</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>[[-8.332828864608409,22.198992470804722,-733.6842,0.0,0.0,0.0,1.0],[22.198992470804722,24.64153817763777,0.0,0.0,8.0,2.0,-1.0],[24.64153817763777,31.969175298136925,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-8.332828864608409,22.198992470804722,-733.6843,0.0,0.0,0.0,1.0],[22.198992470804722,24.64153817763777,0.0,0.0,8.0,2.0,-1.0],[24.64153817763777,31.969175298136925,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>[[-9.702933227245694,20.81253118026722,-733.6842,0.0,0.0,0.0,1.0],[20.81253118026722,23.28675802411962,0.0,0.0,8.0,2.0,-1.0],[23.28675802411962,23.699129164761686,227.85,0.0,8.0,1.0,-1.0],[23.699129164761686,31.121809696318884,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[-9.702933227245694,20.81253118026722,-733.6843,0.0,0.0,0.0,1.0],[20.81253118026722,23.28675802411962,0.0,0.0,8.0,2.0,-1.0],[23.28675802411962,23.699129164761686,227.85,0.0,8.0,1.0,-1.0],[23.699129164761686,31.121809696318884,1860.0,0.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>[[-8.60600868042424,20.667100587490488,-1860.0,1.0,7.0,0.0,-1.0],[20.667100587490488,21.792989405487205,-1808.4765,0.0,7.0,1.0,-1.0],[21.792989405487205,24.044767041480647,0.0,0.0,6.0,2.0,-1.0],[24.044767041480647,24.7953595868118,227.85,0.0,6.0,1.0,-1.0],[24.7953595868118,28.548322313467526,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[-8.60600868042424,20.667100587490488,-1860.0,1.0,7.0,0.0,-1.0],[20.667100587490488,21.792989405487205,-1808.4764,0.0,7.0,1.0,-1.0],[21.792989405487205,24.044767041480647,0.0,0.0,6.0,2.0,-1.0],[24.044767041480647,24.7953595868118,227.85,0.0,6.0,1.0,-1.0],[24.7953595868118,28.548322313467526,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>[[-8.495658764577326,21.080942629242358,-1860.0,1.0,6.0,0.0,-1.0],[21.080942629242358,21.811229083410744,-1808.4765,0.0,6.0,1.0,-1.0],[21.811229083410744,24.3672316730001,0.0,0.0,5.0,2.0,-1.0],[24.3672316730001,25.097518127168485,227.85,0.0,5.0,2.0,-1.0],[25.097518127168485,27.653520716757843,1860.0,0.0,5.0,2.0,-1.0]]</t>
+          <t>[[-8.495658764577326,21.080942629242358,-1860.0,1.0,6.0,0.0,-1.0],[21.080942629242358,21.811229083410744,-1808.4764,0.0,6.0,1.0,-1.0],[21.811229083410744,24.3672316730001,0.0,0.0,5.0,2.0,-1.0],[24.3672316730001,25.097518127168485,227.85,0.0,5.0,2.0,-1.0],[25.097518127168485,27.653520716757843,1860.0,0.0,5.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>[[-8.695105961896813,20.759385942072143,-1860.0,1.0,6.0,0.0,-1.0],[20.759385942072143,21.52443767983757,-1808.4765,0.0,6.0,0.0,-1.0],[21.52443767983757,23.81959289313385,0.0,0.0,5.0,1.0,-1.0],[23.81959289313385,24.202118762016568,227.85,0.0,5.0,1.0,-1.0],[24.202118762016568,29.174955057491847,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[-8.695105961896813,20.759385942072143,-1860.0,1.0,6.0,0.0,-1.0],[20.759385942072143,21.52443767983757,-1808.4764,0.0,6.0,0.0,-1.0],[21.52443767983757,23.81959289313385,0.0,0.0,5.0,1.0,-1.0],[23.81959289313385,24.202118762016568,227.85,0.0,5.0,1.0,-1.0],[24.202118762016568,29.174955057491847,1860.0,0.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>[[-8.786559521560193,20.538598603604882,-1860.0,1.0,4.0,0.0,-1.0],[20.538598603604882,21.35318632930391,-1808.4765,0.0,4.0,0.0,-1.0],[21.35318632930391,23.796949506401,0.0,0.0,3.0,1.0,-1.0],[23.796949506401,31.53553290054178,1860.0,0.0,3.0,1.0,-1.0]]</t>
+          <t>[[-8.786559521560193,20.538598603604882,-1860.0,1.0,4.0,0.0,-1.0],[20.538598603604882,21.35318632930391,-1808.4764,0.0,4.0,0.0,-1.0],[21.35318632930391,23.796949506401,0.0,0.0,3.0,1.0,-1.0],[23.796949506401,31.53553290054178,1860.0,0.0,3.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>[[-8.551771677351692,20.026235174745132,-1860.0,2.0,3.0,1.0,-1.0],[20.026235174745132,21.28702959469058,-1808.4765,0.0,3.0,0.0,-1.0],[21.28702959469058,23.80861843458148,0.0,0.0,2.0,1.0,-1.0],[23.80861843458148,33.054444180848094,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[-8.551771677351692,20.026235174745132,-1860.0,2.0,3.0,1.0,-1.0],[20.026235174745132,21.28702959469058,-1808.4764,0.0,3.0,0.0,-1.0],[21.28702959469058,23.80861843458148,0.0,0.0,2.0,1.0,-1.0],[23.80861843458148,33.054444180848094,1860.0,0.0,2.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>[[-8.500875855240508,19.82590059591878,-1860.0,2.0,2.0,1.0,-1.0],[19.82590059591878,21.174794712640654,-1808.4765,0.0,2.0,0.0,-1.0],[21.174794712640654,23.872582946084393,0.0,0.0,1.0,1.0,-1.0],[23.872582946084393,24.322214318325017,227.85,0.0,1.0,1.0,-1.0],[24.322214318325017,36.01262999658123,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[-8.500875855240508,19.82590059591878,-1860.0,2.0,2.0,1.0,-1.0],[19.82590059591878,21.174794712640654,-1808.4764,0.0,2.0,0.0,-1.0],[21.174794712640654,23.872582946084393,0.0,0.0,1.0,1.0,-1.0],[23.872582946084393,24.322214318325017,227.85,0.0,1.0,1.0,-1.0],[24.322214318325017,36.01262999658123,1860.0,0.0,1.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>[[-9.24631650423712,19.229036167347445,-1860.0,2.0,2.0,0.0,-1.0],[19.229036167347445,20.543283213728273,-1808.4765,0.0,2.0,0.0,-1.0],[20.543283213728273,22.733694957696315,0.0,0.0,1.0,1.0,-1.0],[22.733694957696315,24.924106701664364,227.85,0.0,1.0,0.0,-1.0],[24.924106701664364,34.123836026330146,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-9.24631650423712,19.229036167347445,-1860.0,2.0,2.0,0.0,-1.0],[19.229036167347445,20.543283213728273,-1808.4764,0.0,2.0,0.0,-1.0],[20.543283213728273,22.733694957696315,0.0,0.0,1.0,1.0,-1.0],[22.733694957696315,24.924106701664364,227.85,0.0,1.0,0.0,-1.0],[24.924106701664364,34.123836026330146,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>[[-9.123393332121417,18.442901135502527,-1860.0,1.0,2.0,0.0,-1.0],[18.442901135502527,20.221371746316972,-200.9419,1.0,2.0,0.0,-1.0],[20.221371746316972,22.444460009835034,0.0,1.0,1.0,1.0,-1.0],[22.444460009835034,34.89375428553617,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-9.123393332121417,18.442901135502527,-1860.0,1.0,2.0,0.0,-1.0],[18.442901135502527,20.221371746316972,-200.9418,1.0,2.0,0.0,-1.0],[20.221371746316972,22.444460009835034,0.0,1.0,1.0,1.0,-1.0],[22.444460009835034,34.89375428553617,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>[[-9.027359949009863,19.00989194162133,-1860.0,1.0,0.0,0.0,-1.0],[19.00989194162133,34.34276406931026,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-9.027359949009863,19.00989194162133,-1860.0,1.0,0.0,0.0,-1.0],[19.00989194162133,34.34276406931026,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>[[-8.813884177572477,16.992815391043088,-1860.0,9.0,0.0,0.0,1.0],[16.992815391043088,26.072950424444862,-0.0,9.0,0.0,1.0,1.0],[26.072950424444862,38.49839836488939,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-8.813884177572477,16.992815391043088,-1860.0,9.0,0.0,0.0,1.0],[16.992815391043088,26.072950424444862,0.0,8.0,0.0,1.0,1.0],[26.072950424444862,38.49839836488939,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>[[-8.73173788014999,17.539251582855375,-1860.0,8.0,0.0,0.0,1.0],[17.539251582855375,27.755747485135235,-0.0,8.0,0.0,1.0,1.0],[27.755747485135235,28.242247290005704,890.0,8.0,8.0,4.0,-1.0],[28.242247290005704,39.43174280202651,1860.0,8.0,9.0,3.0,-1.0]]</t>
+          <t>[[-8.73173788014999,17.539251582855375,-1860.0,7.0,0.0,0.0,1.0],[17.539251582855375,27.755747485135235,0.0,7.0,0.0,1.0,1.0],[27.755747485135235,28.242247290005704,890.0,7.0,8.0,4.0,-1.0],[28.242247290005704,39.43174280202651,1860.0,7.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>[[-8.971465657761424,16.835160399350027,-1860.0,7.0,0.0,0.0,1.0],[16.835160399350027,27.753348346589487,-0.0,7.0,0.0,1.0,1.0],[27.753348346589487,28.249629616918558,708.65,8.0,9.0,2.0,-1.0],[28.249629616918558,40.16038010481614,1860.0,8.0,10.0,1.0,-1.0]]</t>
+          <t>[[-8.971465657761424,16.835160399350027,-1860.0,6.0,0.0,0.0,1.0],[16.835160399350027,27.753348346589487,0.0,6.0,0.0,1.0,1.0],[27.753348346589487,28.249629616918558,708.65,8.0,9.0,2.0,-1.0],[28.249629616918558,40.16038010481614,1860.0,8.0,10.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>[[-10.4561744993561,17.453105873594986,-1860.0,6.0,0.0,0.0,1.0],[17.453105873594986,27.735472326787487,-0.0,6.0,0.0,1.0,1.0],[27.735472326787487,38.01783877997999,1860.0,6.0,8.0,4.0,-1.0]]</t>
+          <t>[[-10.4561744993561,17.453105873594986,-1860.0,6.0,0.0,0.0,1.0],[17.453105873594986,27.735472326787487,0.0,6.0,0.0,1.0,1.0],[27.735472326787487,38.01783877997999,1860.0,6.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>[[-9.581443882848344,17.434684435901232,-1860.0,5.0,0.0,0.0,1.0],[17.434684435901232,27.258731097264718,-0.0,5.0,0.0,1.0,1.0],[27.258731097264718,39.04758709090089,1860.0,5.0,9.0,3.0,-1.0]]</t>
+          <t>[[-9.581443882848344,17.434684435901232,-1860.0,5.0,0.0,0.0,1.0],[17.434684435901232,27.258731097264718,0.0,4.0,0.0,1.0,1.0],[27.258731097264718,39.04758709090089,1860.0,5.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>[[-18.963746012354907,17.642961813739145,-1860.0,4.0,0.0,0.0,1.0],[17.642961813739145,28.270715698734197,-0.0,4.0,0.0,1.0,1.0],[28.270715698734197,39.488900355117856,1860.0,5.0,9.0,2.0,-1.0]]</t>
+          <t>[[-18.963746012354907,17.642961813739145,-1860.0,4.0,0.0,0.0,1.0],[17.642961813739145,28.270715698734197,0.0,4.0,0.0,1.0,1.0],[28.270715698734197,39.488900355117856,1860.0,5.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>[[-18.869506492868076,16.90228595607352,-1860.0,3.0,0.0,0.0,1.0],[16.90228595607352,27.209412593904148,-0.0,3.0,0.0,1.0,1.0],[27.209412593904148,27.815714160835363,890.0,3.0,8.0,4.0,-1.0],[27.815714160835363,41.154348633322066,1860.0,3.0,9.0,3.0,-1.0]]</t>
+          <t>[[-18.869506492868076,16.90228595607352,-1860.0,3.0,0.0,0.0,1.0],[16.90228595607352,27.209412593904148,0.0,3.0,0.0,1.0,1.0],[27.209412593904148,27.815714160835363,890.0,3.0,8.0,4.0,-1.0],[27.815714160835363,41.154348633322066,1860.0,3.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>[[-19.730185648214132,17.107605273967906,-1860.0,2.0,0.0,0.0,1.0],[17.107605273967906,27.208289881662985,-0.0,2.0,0.0,1.0,1.0],[27.208289881662985,28.3966057178624,890.0,2.0,8.0,4.0,-1.0],[28.3966057178624,39.09144824365719,1860.0,2.0,8.0,4.0,-1.0]]</t>
+          <t>[[-19.730185648214132,17.107605273967906,-1860.0,2.0,0.0,0.0,1.0],[17.107605273967906,27.208289881662985,0.0,2.0,0.0,1.0,1.0],[27.208289881662985,28.3966057178624,890.0,2.0,8.0,4.0,-1.0],[28.3966057178624,39.09144824365719,1860.0,2.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>[[-18.322836839503953,17.345431669463654,-1860.0,1.0,0.0,0.0,1.0],[17.345431669463654,28.227276299318174,-0.0,1.0,0.0,1.0,1.0],[28.227276299318174,41.52730862469593,1860.0,2.0,9.0,2.0,-1.0]]</t>
+          <t>[[-18.322836839503953,-0.18642912307974768,-1860.0,1.0,0.0,0.0,1.0],[-0.18642912307974768,17.345431669463654,-1860.0,0.0,0.0,0.0,1.0],[17.345431669463654,19.159072441106073,0.0,0.0,0.0,1.0,1.0],[19.159072441106073,22.786353984390917,0.0,1.0,0.0,1.0,1.0],[22.786353984390917,25.20454167991414,0.0,0.0,0.0,1.0,1.0],[25.20454167991414,28.227276299318174,0.0,1.0,0.0,1.0,1.0],[28.227276299318174,41.52730862469593,1860.0,2.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>[[-18.36657183730695,27.688618808674747,-0.0,0.0,0.0,1.0,1.0],[27.688618808674747,28.279069970802716,1678.65,1.0,0.0,0.0,1.0],[28.279069970802716,40.08809321336213,1860.0,1.0,9.0,2.0,-1.0]]</t>
+          <t>[[-18.36657183730695,27.688618808674747,0.0,0.0,0.0,1.0,1.0],[27.688618808674747,28.279069970802716,1678.65,1.0,0.0,0.0,1.0],[28.279069970802716,40.08809321336213,1860.0,1.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>[[-18.547634592004425,28.32207412992179,-0.0,0.0,0.0,1.0,1.0],[28.32207412992179,28.915361582098075,890.0,0.0,8.0,3.0,-1.0],[28.915361582098075,40.18782317344742,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[-18.547634592004425,28.32207412992179,0.0,0.0,0.0,1.0,1.0],[28.32207412992179,28.915361582098075,890.0,0.0,8.0,3.0,-1.0],[28.915361582098075,40.18782317344742,1860.0,0.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>[[-19.59274793037786,26.421433390683582,-0.0,0.0,0.0,1.0,1.0],[26.421433390683582,27.616606931490374,890.0,0.0,8.0,2.0,-1.0],[27.616606931490374,39.568342339558285,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-19.59274793037786,26.421433390683582,0.0,0.0,0.0,1.0,1.0],[26.421433390683582,27.616606931490374,890.0,0.0,8.0,2.0,-1.0],[27.616606931490374,39.568342339558285,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>[[-19.0848640230873,22.318948420012546,-1860.0,1.0,8.0,0.0,-1.0],[22.318948420012546,24.719169431206737,-1074.7923,0.0,8.0,1.0,-1.0],[24.719169431206737,27.719445695199482,0.0,0.0,8.0,1.0,-1.0],[27.719445695199482,28.31950094799803,708.65,1.0,8.0,0.0,-1.0],[28.31950094799803,40.320606003969,1860.0,1.0,8.0,0.0,-1.0]]</t>
+          <t>[[-19.0848640230873,22.318948420012546,-1860.0,1.0,8.0,0.0,-1.0],[22.318948420012546,24.719169431206737,-1074.7922,0.0,8.0,1.0,-1.0],[24.719169431206737,27.719445695199482,0.0,0.0,8.0,1.0,-1.0],[27.719445695199482,28.31950094799803,708.65,1.0,8.0,0.0,-1.0],[28.31950094799803,40.320606003969,1860.0,1.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>[[-18.083173204444062,12.989496696720064,-1860.0,1.0,8.0,0.0,-1.0],[12.989496696720064,23.745420893276876,-1074.7923,0.0,8.0,0.0,-1.0],[23.745420893276876,26.733177614542658,0.0,0.0,7.0,1.0,-1.0],[26.733177614542658,27.330728958795813,890.0,0.0,7.0,1.0,-1.0],[27.330728958795813,41.074409876618404,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[-18.083173204444062,12.989496696720064,-1860.0,1.0,8.0,0.0,-1.0],[12.989496696720064,23.745420893276876,-1074.7922,0.0,8.0,0.0,-1.0],[23.745420893276876,26.733177614542658,0.0,0.0,7.0,1.0,-1.0],[26.733177614542658,27.330728958795813,890.0,0.0,7.0,1.0,-1.0],[27.330728958795813,41.074409876618404,1860.0,0.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>[[-19.997741224992556,12.385340527165038,-1860.0,1.0,7.0,0.0,-1.0],[12.385340527165038,22.58001441210354,-1074.7923,0.0,7.0,0.0,-1.0],[22.58001441210354,25.578447907673688,0.0,0.0,6.0,1.0,-1.0],[25.578447907673688,27.977194704129804,890.0,0.0,6.0,1.0,-1.0],[27.977194704129804,39.37124198729637,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-19.997741224992556,12.385340527165038,-1860.0,1.0,7.0,0.0,-1.0],[12.385340527165038,22.58001441210354,-1074.7922,0.0,7.0,0.0,-1.0],[22.58001441210354,25.578447907673688,0.0,0.0,6.0,1.0,-1.0],[25.578447907673688,27.977194704129804,890.0,0.0,6.0,1.0,-1.0],[27.977194704129804,39.37124198729637,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>[[-18.84860564699721,13.070559642789203,-1860.0,1.0,6.0,0.0,-1.0],[13.070559642789203,22.35613499981798,-1074.7923,0.0,6.0,0.0,-1.0],[22.35613499981798,25.257877298889465,0.0,0.0,5.0,1.0,-1.0],[25.257877298889465,27.579271138146662,890.0,0.0,5.0,1.0,-1.0],[27.579271138146662,38.60589187461833,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[-18.84860564699721,13.070559642789203,-1860.0,1.0,6.0,0.0,-1.0],[13.070559642789203,22.35613499981798,-1074.7922,0.0,6.0,0.0,-1.0],[22.35613499981798,25.257877298889465,0.0,0.0,5.0,1.0,-1.0],[25.257877298889465,27.579271138146662,890.0,0.0,5.0,1.0,-1.0],[27.579271138146662,38.60589187461833,1860.0,0.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>[[-18.72920294444079,12.41922387052568,-1860.0,1.0,5.0,0.0,-1.0],[12.41922387052568,22.410228697967757,-1074.7923,0.0,5.0,0.0,-1.0],[22.410228697967757,24.76105336324824,0.0,0.0,4.0,1.0,-1.0],[24.76105336324824,27.699584194848857,890.0,0.0,4.0,1.0,-1.0],[27.699584194848857,39.4537075212513,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-18.72920294444079,12.41922387052568,-1860.0,1.0,5.0,0.0,-1.0],[12.41922387052568,22.410228697967757,-1074.7922,0.0,5.0,0.0,-1.0],[22.410228697967757,24.76105336324824,0.0,0.0,4.0,1.0,-1.0],[24.76105336324824,27.699584194848857,890.0,0.0,4.0,1.0,-1.0],[27.699584194848857,39.4537075212513,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>[[-18.202335393321956,13.1065339757218,-1860.0,1.0,4.0,0.0,-1.0],[13.1065339757218,21.967534740545506,-1074.7923,0.0,4.0,0.0,-1.0],[21.967534740545506,24.330468277831823,0.0,0.0,3.0,1.0,-1.0],[24.330468277831823,27.284135199439728,890.0,0.0,3.0,1.0,-1.0],[27.284135199439728,40.280269654514484,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-18.202335393321956,13.1065339757218,-1860.0,1.0,4.0,0.0,-1.0],[13.1065339757218,21.967534740545506,-1074.7922,0.0,4.0,0.0,-1.0],[21.967534740545506,24.330468277831823,0.0,0.0,3.0,1.0,-1.0],[24.330468277831823,27.284135199439728,890.0,0.0,3.0,1.0,-1.0],[27.284135199439728,40.280269654514484,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>[[-18.161635208595573,13.240998055117121,-1860.0,1.0,3.0,0.0,-1.0],[13.240998055117121,24.49854582890092,-1074.7923,0.0,3.0,0.0,-1.0],[24.49854582890092,27.461058400949288,0.0,0.0,2.0,1.0,-1.0],[27.461058400949288,30.423570972997656,890.0,0.0,2.0,1.0,-1.0],[30.423570972997656,40.496113717962096,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-18.161635208595573,13.240998055117121,-1860.0,1.0,3.0,0.0,-1.0],[13.240998055117121,24.49854582890092,-1074.7922,0.0,3.0,0.0,-1.0],[24.49854582890092,27.461058400949288,0.0,0.0,2.0,1.0,-1.0],[27.461058400949288,30.423570972997656,890.0,0.0,2.0,1.0,-1.0],[30.423570972997656,40.496113717962096,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>[[-18.717597789029234,5.099322627965442,-1860.0,10.0,3.0,0.0,1.0],[5.099322627965442,5.680223125940923,-1808.4765,9.0,3.0,1.0,1.0],[5.680223125940923,13.231929599622163,-1074.7923,0.0,3.0,0.0,-1.0],[13.231929599622163,14.974631093548602,0.0,0.0,2.0,1.0,-1.0],[14.974631093548602,31.239845036862043,890.0,0.0,2.0,0.0,-1.0],[31.239845036862043,38.79155151054328,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-18.717597789029234,5.099322627965442,-1860.0,10.0,3.0,0.0,1.0],[5.099322627965442,5.680223125940923,-1808.4764,9.0,3.0,1.0,1.0],[5.680223125940923,13.231929599622163,-1074.7922,0.0,3.0,0.0,-1.0],[13.231929599622163,14.974631093548602,0.0,0.0,2.0,1.0,-1.0],[14.974631093548602,31.239845036862043,890.0,0.0,2.0,0.0,-1.0],[31.239845036862043,38.79155151054328,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>[[-18.858695035645415,4.193525130370194,-1860.0,10.0,2.0,0.0,1.0],[4.193525130370194,4.78460769872957,-733.6843,9.0,2.0,1.0,1.0],[4.78460769872957,14.833011360838935,0.0,0.0,2.0,1.0,-1.0],[14.833011360838935,39.658479231932674,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-18.858695035645415,4.193525130370194,-1860.0,10.0,2.0,0.0,1.0],[4.193525130370194,4.78460769872957,-733.6842,9.0,2.0,1.0,1.0],[4.78460769872957,14.833011360838935,0.0,0.0,2.0,1.0,-1.0],[14.833011360838935,39.658479231932674,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>[[-17.846349505466844,5.12504090123748,-1860.0,10.0,1.0,0.0,1.0],[5.12504090123748,5.714050911665797,-733.6843,9.0,1.0,1.0,1.0],[5.714050911665797,13.371181047233907,0.0,0.0,1.0,1.0,-1.0],[13.371181047233907,14.549201068090536,0.0,0.0,0.0,1.0,-1.0],[14.549201068090536,16.31623109937549,1860.0,0.0,0.0,0.0,-1.0],[16.31623109937549,40.46564152693644,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-17.846349505466844,5.12504090123748,-1860.0,10.0,1.0,0.0,1.0],[5.12504090123748,5.714050911665797,-733.6842,9.0,1.0,1.0,1.0],[5.714050911665797,14.549201068090536,0.0,0.0,1.0,1.0,-1.0],[14.549201068090536,40.46564152693644,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>[[-18.44467554567356,4.854090473381191,-1860.0,10.0,0.0,0.0,1.0],[4.854090473381191,5.383607882905164,-733.6843,9.0,0.0,1.0,1.0],[5.383607882905164,33.97754799719963,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-18.44467554567356,4.854090473381191,-1860.0,10.0,0.0,0.0,1.0],[4.854090473381191,5.383607882905164,-733.6842,9.0,0.0,1.0,1.0],[5.383607882905164,33.97754799719963,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -7831,11 +7831,11 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>[[-19.196582680214775,1.30248995448569,-1860.0,9.0,0.0,0.0,1.0],[1.30248995448569,26.233794510202465,-733.6843,9.0,0.0,0.0,1.0],[26.233794510202465,35.652287342362136,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-19.196582680214775,1.30248995448569,-1860.0,9.0,0.0,0.0,1.0],[1.30248995448569,26.233794510202465,-733.6842,9.0,0.0,0.0,1.0],[26.233794510202465,35.652287342362136,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>-733.6843</v>
+        <v>-733.6842</v>
       </c>
       <c r="D322" s="4" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>[[-18.44566975749752,26.326646903304486,-1860.0,9.0,0.0,0.0,1.0],[26.326646903304486,29.09037015397127,0.0,8.0,7.0,1.0,-1.0],[29.09037015397127,36.27605060570493,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-18.44566975749752,26.326646903304486,-1860.0,8.0,0.0,0.0,1.0],[26.326646903304486,29.09037015397127,0.0,8.0,7.0,1.0,-1.0],[29.09037015397127,36.27605060570493,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>[[-18.87824952192215,26.336957040724037,-1860.0,8.0,0.0,0.0,1.0],[26.336957040724037,27.99117191496719,-873.8504,7.0,8.0,0.0,-1.0],[27.99117191496719,30.748196705372443,0.0,7.0,7.0,1.0,-1.0],[30.748196705372443,35.71084132810191,1860.0,7.0,7.0,1.0,-1.0]]</t>
+          <t>[[-18.87824952192215,26.336957040724037,-1860.0,6.0,0.0,0.0,1.0],[26.336957040724037,27.99117191496719,-873.8504,7.0,8.0,0.0,-1.0],[27.99117191496719,30.748196705372443,0.0,7.0,7.0,1.0,-1.0],[30.748196705372443,35.71084132810191,1860.0,7.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>[[-18.795445222113045,25.140693754248474,-1860.0,7.0,0.0,0.0,1.0],[25.140693754248474,26.239097228657513,-1074.7922,7.0,9.0,1.0,-1.0],[26.239097228657513,28.985105914680112,0.0,7.0,8.0,2.0,-1.0],[28.985105914680112,29.53430765188463,890.0,7.0,8.0,1.0,-1.0],[29.53430765188463,35.57552676113434,1860.0,7.0,8.0,1.0,-1.0]]</t>
+          <t>[[-18.795445222113045,25.140693754248474,-1860.0,6.0,0.0,0.0,1.0],[25.140693754248474,26.239097228657513,-1074.7922,7.0,9.0,1.0,-1.0],[26.239097228657513,28.985105914680112,0.0,7.0,8.0,2.0,-1.0],[28.985105914680112,29.53430765188463,890.0,7.0,8.0,1.0,-1.0],[29.53430765188463,35.57552676113434,1860.0,7.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>[[-18.371446659018705,25.32383887525282,-1860.0,6.0,0.0,0.0,1.0],[25.32383887525282,25.87002994443122,-873.8504,5.0,8.0,0.0,-1.0],[25.87002994443122,28.60098529032319,0.0,5.0,7.0,1.0,-1.0],[28.60098529032319,30.239558497858372,1071.35,5.0,7.0,1.0,-1.0],[30.239558497858372,35.70146918964231,1860.0,5.0,7.0,1.0,-1.0]]</t>
+          <t>[[-18.371446659018705,25.32383887525282,-1860.0,5.0,0.0,0.0,1.0],[25.32383887525282,25.87002994443122,-873.8504,5.0,8.0,0.0,-1.0],[25.87002994443122,28.60098529032319,0.0,5.0,7.0,1.0,-1.0],[28.60098529032319,30.239558497858372,1071.35,5.0,7.0,1.0,-1.0],[30.239558497858372,35.70146918964231,1860.0,5.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>[[-18.460136581089603,25.77642098180738,-1860.0,5.0,0.0,0.0,1.0],[25.77642098180738,26.32255132209006,-873.8504,4.0,8.0,2.0,-1.0],[26.32255132209006,29.053203023503453,0.0,4.0,7.0,3.0,-1.0],[29.053203023503453,31.237724384634166,1071.35,4.0,7.0,1.0,-1.0],[31.237724384634166,35.6067671068956,1860.0,4.0,8.0,0.0,-1.0]]</t>
+          <t>[[-18.460136581089603,25.77642098180738,-1860.0,4.0,0.0,0.0,1.0],[25.77642098180738,26.32255132209006,-873.8504,4.0,8.0,2.0,-1.0],[26.32255132209006,29.053203023503453,0.0,4.0,7.0,3.0,-1.0],[29.053203023503453,31.237724384634166,1071.35,4.0,7.0,1.0,-1.0],[31.237724384634166,35.6067671068956,1860.0,4.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>[[-11.457705885176512,26.050139092890394,-1860.0,4.0,7.0,0.0,-1.0],[26.050139092890394,27.474487636361292,-672.9085,3.0,7.0,1.0,-1.0],[27.474487636361292,30.79796757112671,0.0,3.0,6.0,2.0,-1.0],[30.79796757112671,31.27275041895034,1252.7,3.0,6.0,1.0,-1.0],[31.27275041895034,35.545796049363034,1860.0,3.0,6.0,1.0,-1.0]]</t>
+          <t>[[-11.457705885176512,26.050139092890394,-1860.0,4.0,7.0,0.0,-1.0],[26.050139092890394,27.474487636361292,-672.9086,3.0,7.0,1.0,-1.0],[27.474487636361292,30.79796757112671,0.0,3.0,6.0,2.0,-1.0],[30.79796757112671,31.27275041895034,1252.7,3.0,6.0,1.0,-1.0],[31.27275041895034,35.545796049363034,1860.0,3.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -7992,7 +7992,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>[[-8.751260776202853,25.749859251972516,-1860.0,3.0,7.0,2.0,-1.0],[25.749859251972516,26.623305328635183,-672.9085,2.0,7.0,3.0,-1.0],[26.623305328635183,29.68036659695452,0.0,2.0,6.0,4.0,-1.0],[29.68036659695452,30.553812673617188,1252.7,2.0,6.0,4.0,-1.0],[30.553812673617188,34.48432001859919,1860.0,2.0,7.0,3.0,-1.0]]</t>
+          <t>[[-8.751260776202853,25.749859251972516,-1860.0,3.0,7.0,2.0,-1.0],[25.749859251972516,26.623305328635183,-672.9086,2.0,7.0,3.0,-1.0],[26.623305328635183,29.68036659695452,0.0,2.0,6.0,4.0,-1.0],[29.68036659695452,30.553812673617188,1252.7,2.0,6.0,4.0,-1.0],[30.553812673617188,34.48432001859919,1860.0,2.0,7.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>[[-8.720600197365597,27.85785470548778,-1860.0,2.0,6.0,1.0,-1.0],[27.85785470548778,30.906059280725565,0.0,1.0,5.0,3.0,-1.0],[30.906059280725565,31.3415170771881,1434.05,1.0,5.0,3.0,-1.0],[31.3415170771881,34.389721652425884,1860.0,1.0,5.0,3.0,-1.0]]</t>
+          <t>[[-8.720600197365597,27.85785470548778,-1860.0,2.0,6.0,1.0,-1.0],[27.85785470548778,30.906059280725565,0.0,1.0,5.0,3.0,-1.0],[30.906059280725565,31.3415170771881,1434.05,0.0,5.0,3.0,-1.0],[31.3415170771881,34.389721652425884,1860.0,1.0,5.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>[[-9.0369809601662,25.38427064912653,-1860.0,1.0,7.0,2.0,-1.0],[25.38427064912653,28.473357332011776,-672.9085,0.0,7.0,0.0,-1.0],[28.473357332011776,31.121145917341988,0.0,0.0,6.0,1.0,-1.0],[31.121145917341988,31.56244401489702,1252.7,0.0,6.0,1.0,-1.0],[31.56244401489702,34.65153069778226,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[-9.0369809601662,25.38427064912653,-1860.0,1.0,7.0,2.0,-1.0],[25.38427064912653,28.473357332011776,-672.9086,0.0,7.0,0.0,-1.0],[28.473357332011776,31.121145917341988,0.0,0.0,6.0,1.0,-1.0],[31.121145917341988,31.56244401489702,1252.7,0.0,6.0,1.0,-1.0],[31.56244401489702,34.65153069778226,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>[[-8.731740297598687,24.82649491496002,-1860.0,1.0,7.0,0.0,-1.0],[24.82649491496002,25.72138118729492,-672.9085,0.0,7.0,1.0,-1.0],[25.72138118729492,28.406040004299616,0.0,0.0,6.0,2.0,-1.0],[28.406040004299616,30.195812548969418,1252.7,0.0,6.0,0.0,-1.0],[30.195812548969418,35.56513018297881,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[-8.731740297598687,24.82649491496002,-1860.0,1.0,7.0,0.0,-1.0],[24.82649491496002,25.72138118729492,-672.9086,0.0,7.0,1.0,-1.0],[25.72138118729492,28.406040004299616,0.0,0.0,6.0,2.0,-1.0],[28.406040004299616,30.195812548969418,1252.7,0.0,6.0,0.0,-1.0],[30.195812548969418,35.56513018297881,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>[[-8.808865035697247,24.339139950345356,-1860.0,1.0,6.0,1.0,-1.0],[24.339139950345356,26.15546899067646,-672.9085,0.0,6.0,1.0,-1.0],[26.15546899067646,28.879962551173108,0.0,0.0,5.0,2.0,-1.0],[28.879962551173108,31.150373851586984,1252.7,0.0,5.0,0.0,-1.0],[31.150373851586984,36.145278712497515,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-8.808865035697247,24.339139950345356,-1860.0,1.0,6.0,1.0,-1.0],[24.339139950345356,26.15546899067646,-672.9086,0.0,6.0,1.0,-1.0],[26.15546899067646,28.879962551173108,0.0,0.0,5.0,2.0,-1.0],[28.879962551173108,31.150373851586984,1252.7,0.0,5.0,0.0,-1.0],[31.150373851586984,36.145278712497515,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>[[-8.966725062329564,0.5538491698966137,-1860.0,8.0,0.0,0.0,1.0],[0.5538491698966137,23.675243733874474,-733.6842,8.0,0.0,0.0,1.0],[23.675243733874474,26.39540780022481,0.0,8.0,0.0,1.0,1.0],[26.39540780022481,27.755489833399977,1016.5,9.0,0.0,0.0,1.0],[27.755489833399977,35.91598203245099,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-8.966725062329564,0.5538491698966137,-1860.0,8.0,0.0,0.0,1.0],[0.5538491698966137,23.675243733874474,-733.6842,8.0,0.0,0.0,1.0],[23.675243733874474,26.39540780022481,0.0,8.0,0.0,1.0,1.0],[26.39540780022481,27.755489833399977,1016.5,9.0,0.0,0.0,1.0],[27.755489833399977,35.91598203245099,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>[[-8.189371790192736,0.8107482806395137,-1860.0,1.0,0.0,0.0,1.0],[0.8107482806395137,24.382491323295405,-733.6842,1.0,0.0,0.0,1.0],[24.382491323295405,26.953954200676044,0.0,1.0,0.0,1.0,1.0],[26.953954200676044,34.239765686587866,1860.0,2.0,9.0,1.0,-1.0]]</t>
+          <t>[[-8.189371790192736,0.8107482806395137,-1860.0,1.0,0.0,0.0,1.0],[0.8107482806395137,24.382491323295405,-733.6842,0.0,0.0,0.0,1.0],[24.382491323295405,26.953954200676044,0.0,1.0,0.0,1.0,1.0],[26.953954200676044,34.239765686587866,1860.0,2.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>[[-0.8285544780504653,25.031884576340058,-1860.0,1.0,8.0,3.0,-1.0],[25.031884576340058,27.511652704843257,0.0,0.0,8.0,4.0,-1.0],[27.511652704843257,27.865905294629428,227.85,1.0,8.0,3.0,-1.0],[27.865905294629428,34.24245191078052,1860.0,1.0,8.0,3.0,-1.0]]</t>
+          <t>[[-0.8285544780504653,25.031884576340058,-1860.0,1.0,8.0,3.0,-1.0],[25.031884576340058,27.511652704843257,0.0,0.0,8.0,4.0,-1.0],[27.511652704843257,27.865905294629428,227.85,0.0,8.0,3.0,-1.0],[27.865905294629428,34.24245191078052,1860.0,1.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>[[-0.8045334098895883,22.896049447989117,-733.6842,0.0,0.0,0.0,1.0],[22.896049447989117,25.409747629885345,0.0,0.0,8.0,2.0,-1.0],[25.409747629885345,27.205246331239795,227.85,0.0,8.0,2.0,-1.0],[27.205246331239795,34.74634087692848,1860.0,0.0,9.0,1.0,-1.0]]</t>
+          <t>[[-0.8045334098895883,22.896049447989117,-733.6843,0.0,0.0,0.0,1.0],[22.896049447989117,25.409747629885345,0.0,0.0,8.0,2.0,-1.0],[25.409747629885345,27.205246331239795,227.85,0.0,8.0,2.0,-1.0],[27.205246331239795,34.74634087692848,1860.0,0.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>[[-0.8086767806605984,23.28119775225262,-986.1495,0.0,0.0,0.0,1.0],[23.28119775225262,26.42335530002391,0.0,0.0,8.0,2.0,-1.0],[26.42335530002391,33.755056244823585,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-0.8086767806605984,23.28119775225262,-986.1497,0.0,0.0,0.0,1.0],[23.28119775225262,26.42335530002391,0.0,0.0,8.0,2.0,-1.0],[26.42335530002391,33.755056244823585,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C357" t="n">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>[[-0.8226825328544912,22.666785807354938,-986.1495,0.0,0.0,0.0,1.0],[22.666785807354938,26.076547340611146,0.0,0.0,8.0,3.0,-1.0],[26.076547340611146,36.68469433296379,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[-0.8226825328544912,22.666785807354938,-986.1497,0.0,0.0,0.0,1.0],[22.666785807354938,26.076547340611146,0.0,0.0,8.0,3.0,-1.0],[26.076547340611146,36.68469433296379,1860.0,0.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>[[-0.792115077659882,12.814010090091632,-1860.0,9.0,0.0,0.0,1.0],[12.814010090091632,17.91630702799845,-733.6842,9.0,0.0,0.0,1.0],[17.91630702799845,41.30183466007137,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-0.792115077659882,12.814010090091632,-1860.0,8.0,0.0,0.0,1.0],[12.814010090091632,17.91630702799845,-733.6842,9.0,0.0,0.0,1.0],[17.91630702799845,41.30183466007137,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C369" t="n">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>[[-0.7901573278879391,18.16278630648099,-1860.0,9.0,0.0,0.0,1.0],[18.16278630648099,28.93150428055424,0.0,9.0,0.0,1.0,1.0],[28.93150428055424,41.85396584944215,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-0.7901573278879391,18.16278630648099,-1860.0,8.0,0.0,0.0,1.0],[18.16278630648099,28.93150428055424,0.0,9.0,0.0,1.0,1.0],[28.93150428055424,41.85396584944215,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>[[-0.7626232794666812,18.13348796244254,-1860.0,8.0,0.0,0.0,1.0],[18.13348796244254,29.11959914959907,0.0,8.0,0.0,1.0,1.0],[29.11959914959907,29.559043597085328,890.0,8.0,8.0,0.0,-1.0],[29.559043597085328,42.74237702167316,1860.0,8.0,8.0,0.0,-1.0]]</t>
+          <t>[[-0.7626232794666812,18.13348796244254,-1860.0,5.0,0.0,0.0,1.0],[18.13348796244254,29.11959914959907,0.0,7.0,0.0,1.0,1.0],[29.11959914959907,29.559043597085328,890.0,7.0,8.0,0.0,-1.0],[29.559043597085328,42.74237702167316,1860.0,6.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C371" t="n">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>[[-0.7843419030361622,17.71378017751417,-1860.0,7.0,0.0,0.0,1.0],[17.71378017751417,29.759068974151592,0.0,7.0,0.0,1.0,1.0],[29.759068974151592,30.189257859745787,890.0,7.0,8.0,1.0,-1.0],[30.189257859745787,41.80435777078901,1860.0,7.0,8.0,1.0,-1.0]]</t>
+          <t>[[-0.7843419030361622,17.71378017751417,-1860.0,4.0,0.0,0.0,1.0],[17.71378017751417,29.759068974151592,0.0,7.0,0.0,1.0,1.0],[29.759068974151592,30.189257859745787,890.0,7.0,8.0,1.0,-1.0],[30.189257859745787,41.80435777078901,1860.0,5.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>[[-0.7838041493776018,17.488555091540736,-1860.0,6.0,0.0,0.0,1.0],[17.488555091540736,29.23507174641681,0.0,6.0,0.0,1.0,1.0],[29.23507174641681,30.540240263625265,890.0,6.0,8.0,1.0,-1.0],[30.540240263625265,42.28675691850134,1860.0,6.0,8.0,1.0,-1.0]]</t>
+          <t>[[-0.7838041493776018,17.488555091540736,-1860.0,4.0,0.0,0.0,1.0],[17.488555091540736,29.23507174641681,0.0,4.0,0.0,1.0,1.0],[29.23507174641681,30.540240263625265,890.0,4.0,8.0,1.0,-1.0],[30.540240263625265,42.28675691850134,1860.0,5.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C373" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>[[0.4373098028181701,26.72693793185583,-1860.0,6.0,0.0,0.0,1.0],[26.72693793185583,28.06369868417978,-873.8504,5.0,8.0,0.0,-1.0],[28.06369868417978,31.182807106268996,0.0,5.0,7.0,1.0,-1.0],[31.182807106268996,44.55041462950848,1860.0,5.0,7.0,1.0,-1.0]]</t>
+          <t>[[0.4373098028181701,26.72693793185583,-1860.0,3.0,0.0,0.0,1.0],[26.72693793185583,28.06369868417978,-873.8504,4.0,8.0,0.0,-1.0],[28.06369868417978,31.182807106268996,0.0,3.0,7.0,1.0,-1.0],[31.182807106268996,44.55041462950848,1860.0,4.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>[[-0.9883996611836087,25.258160411523082,-1860.0,5.0,0.0,0.0,1.0],[25.258160411523082,27.007931083036862,-873.8504,4.0,8.0,0.0,-1.0],[27.007931083036862,29.63258709030753,0.0,4.0,7.0,1.0,-1.0],[29.63258709030753,31.382357761821307,1071.35,4.0,7.0,1.0,-1.0],[31.382357761821307,42.31842445878244,1860.0,4.0,7.0,1.0,-1.0]]</t>
+          <t>[[-0.9883996611836087,25.258160411523082,-1860.0,3.0,0.0,0.0,1.0],[25.258160411523082,27.007931083036862,-873.8504,3.0,8.0,0.0,-1.0],[27.007931083036862,29.63258709030753,0.0,3.0,7.0,1.0,-1.0],[29.63258709030753,31.382357761821307,1071.35,3.0,7.0,1.0,-1.0],[31.382357761821307,42.31842445878244,1860.0,3.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C375" t="n">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>[[-3.238786972373251,27.35248498107974,-1860.0,4.0,0.0,0.0,1.0],[27.35248498107974,27.80907112963874,-873.8504,3.0,8.0,1.0,-1.0],[27.80907112963874,31.00517416955174,0.0,3.0,7.0,2.0,-1.0],[31.00517416955174,31.918346466669735,1071.35,3.0,7.0,1.0,-1.0],[31.918346466669735,41.96324173496774,1860.0,3.0,7.0,1.0,-1.0]]</t>
+          <t>[[-3.238786972373251,27.35248498107974,-1860.0,2.0,0.0,0.0,1.0],[27.35248498107974,27.80907112963874,-873.8504,2.0,8.0,1.0,-1.0],[27.80907112963874,31.00517416955174,0.0,2.0,7.0,2.0,-1.0],[31.00517416955174,31.918346466669735,1071.35,2.0,7.0,1.0,-1.0],[31.918346466669735,41.96324173496774,1860.0,2.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>[[-2.9947433807787847,25.510747135571663,-1860.0,3.0,0.0,0.0,1.0],[25.510747135571663,26.460930152783344,-873.8504,2.0,8.0,0.0,-1.0],[26.460930152783344,29.31147920441839,0.0,2.0,7.0,1.0,-1.0],[29.31147920441839,30.73675373023591,1071.35,2.0,7.0,1.0,-1.0],[30.73675373023591,44.03931597119946,1860.0,2.0,7.0,1.0,-1.0]]</t>
+          <t>[[-2.9947433807787847,25.510747135571663,-1860.0,2.0,0.0,0.0,1.0],[25.510747135571663,26.460930152783344,-873.8504,2.0,8.0,0.0,-1.0],[26.460930152783344,29.31147920441839,0.0,1.0,7.0,1.0,-1.0],[29.31147920441839,30.73675373023591,1071.35,2.0,7.0,1.0,-1.0],[30.73675373023591,44.03931597119946,1860.0,1.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>[[-2.940369776150578,25.958161273224494,-1860.0,2.0,0.0,0.0,1.0],[25.958161273224494,26.890371952236592,-873.8504,1.0,8.0,1.0,-1.0],[26.890371952236592,29.687003989272892,0.0,1.0,7.0,2.0,-1.0],[29.687003989272892,32.01753068680314,1071.35,1.0,7.0,1.0,-1.0],[32.01753068680314,43.20405883494833,1860.0,1.0,7.0,1.0,-1.0]]</t>
+          <t>[[-2.940369776150578,25.958161273224494,-1860.0,1.0,0.0,0.0,1.0],[25.958161273224494,26.890371952236592,-873.8504,0.0,8.0,1.0,-1.0],[26.890371952236592,29.687003989272892,0.0,1.0,7.0,2.0,-1.0],[29.687003989272892,32.01753068680314,1071.35,0.0,7.0,1.0,-1.0],[32.01753068680314,43.20405883494833,1860.0,1.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>[[-3.317736787693387,26.322060943358295,-1860.0,1.0,0.0,0.0,1.0],[26.322060943358295,26.77805783152832,-873.8504,0.0,8.0,1.0,-1.0],[26.77805783152832,29.514039160548474,0.0,0.0,7.0,2.0,-1.0],[29.514039160548474,30.882029825058556,1071.35,0.0,7.0,1.0,-1.0],[30.882029825058556,41.825955141139175,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[-3.317736787693387,-0.12575857050320582,-1860.0,1.0,0.0,0.0,1.0],[-0.12575857050320582,26.322060943358295,-1860.0,0.0,0.0,0.0,1.0],[26.322060943358295,26.77805783152832,-873.8504,0.0,8.0,1.0,-1.0],[26.77805783152832,29.514039160548474,0.0,0.0,7.0,2.0,-1.0],[29.514039160548474,30.882029825058556,1071.35,0.0,7.0,1.0,-1.0],[30.882029825058556,41.825955141139175,1860.0,0.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C379" t="n">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>[[-3.1675207668873657,23.958319871765298,-1860.0,2.0,7.0,0.0,-1.0],[23.958319871765298,24.41041721574284,-401.8836,2.0,7.0,0.0,-1.0],[24.41041721574284,27.123001279608104,0.0,2.0,6.0,1.0,-1.0],[27.123001279608104,28.931390655518285,1497.3,2.0,6.0,1.0,-1.0],[28.931390655518285,41.590116286889526,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-3.1675207668873657,23.958319871765298,-1860.0,2.0,7.0,0.0,-1.0],[23.958319871765298,24.41041721574284,-401.8837,2.0,7.0,0.0,-1.0],[24.41041721574284,27.123001279608104,0.0,2.0,6.0,1.0,-1.0],[27.123001279608104,28.931390655518285,1497.3,2.0,6.0,1.0,-1.0],[28.931390655518285,41.590116286889526,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C384" t="n">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>[[-3.2429692379502564,22.87532269503339,-1860.0,2.0,5.0,1.0,-1.0],[22.87532269503339,25.207313046192645,-200.9418,1.0,5.0,2.0,-1.0],[25.207313046192645,28.005701467583748,0.0,1.0,5.0,2.0,-1.0],[28.005701467583748,28.4720995378156,1497.3,2.0,5.0,1.0,-1.0],[28.4720995378156,42.930439715002976,1860.0,1.0,4.0,0.0,-1.0]]</t>
+          <t>[[-3.2429692379502564,22.87532269503339,-1860.0,1.0,5.0,1.0,-1.0],[22.87532269503339,25.207313046192645,-200.9418,1.0,5.0,2.0,-1.0],[25.207313046192645,28.005701467583748,0.0,1.0,5.0,2.0,-1.0],[28.005701467583748,28.4720995378156,1497.3,2.0,5.0,1.0,-1.0],[28.4720995378156,42.930439715002976,1860.0,1.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>[[-3.132943569688188,24.27451152586689,-1860.0,2.0,5.0,0.0,-1.0],[24.27451152586689,24.7470538551006,-401.8836,2.0,5.0,0.0,-1.0],[24.7470538551006,27.10976550126914,0.0,2.0,4.0,1.0,-1.0],[27.10976550126914,28.054850159736556,1497.3,2.0,4.0,1.0,-1.0],[28.054850159736556,43.64874702444893,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-3.132943569688188,24.27451152586689,-1860.0,2.0,5.0,0.0,-1.0],[24.27451152586689,24.7470538551006,-401.8837,2.0,5.0,0.0,-1.0],[24.7470538551006,27.10976550126914,0.0,2.0,4.0,1.0,-1.0],[27.10976550126914,28.054850159736556,1497.3,2.0,4.0,1.0,-1.0],[28.054850159736556,43.64874702444893,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>[[-2.949744650801829,23.86187624182115,-1860.0,2.0,2.0,2.0,-1.0],[23.86187624182115,24.650453326898294,-200.9418,1.0,2.0,2.0,-1.0],[24.650453326898294,27.410473124668307,0.0,1.0,2.0,2.0,-1.0],[27.410473124668307,27.80476166720688,1497.3,2.0,2.0,1.0,-1.0],[27.80476166720688,36.08482106051692,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-2.949744650801829,23.86187624182115,-1860.0,1.0,2.0,2.0,-1.0],[23.86187624182115,24.650453326898294,-200.9418,1.0,2.0,2.0,-1.0],[24.650453326898294,27.410473124668307,0.0,1.0,2.0,2.0,-1.0],[27.410473124668307,27.80476166720688,1497.3,2.0,2.0,1.0,-1.0],[27.80476166720688,36.08482106051692,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>[[-3.0940505631117587,22.816301005505593,-1860.0,2.0,2.0,0.0,-1.0],[22.816301005505593,24.749909331521813,-401.8836,1.0,2.0,0.0,-1.0],[24.749909331521813,27.45696098794452,0.0,1.0,1.0,1.0,-1.0],[27.45696098794452,30.164012644367226,1497.3,1.0,1.0,1.0,-1.0],[30.164012644367226,35.1913942920094,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-3.0940505631117587,22.816301005505593,-1860.0,2.0,2.0,0.0,-1.0],[22.816301005505593,24.749909331521813,-401.8837,1.0,2.0,0.0,-1.0],[24.749909331521813,27.45696098794452,0.0,1.0,1.0,1.0,-1.0],[27.45696098794452,30.164012644367226,1497.3,1.0,1.0,1.0,-1.0],[30.164012644367226,35.1913942920094,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C390" t="n">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>[[-3.133647285768385,22.892994648448287,-1860.0,2.0,1.0,0.0,-1.0],[22.892994648448287,36.106520553512134,0.0,1.0,1.0,1.0,-1.0],[36.106520553512134,36.50693042942316,181.35,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-3.133647285768385,7.277009487918283,-1860.0,1.0,1.0,0.0,-1.0],[7.277009487918283,20.0901255170711,-1860.0,2.0,1.0,0.0,-1.0],[20.0901255170711,22.892994648448287,-1860.0,1.0,1.0,0.0,-1.0],[22.892994648448287,36.106520553512134,0.0,1.0,1.0,1.0,-1.0],[36.106520553512134,36.50693042942316,181.3501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>[[-6.519053499862936,10.160326180227317,-1860.0,9.0,0.0,0.0,1.0],[10.160326180227317,11.468512821803023,-532.7423,8.0,0.0,1.0,1.0],[11.468512821803023,12.449652802984803,0.0,8.0,0.0,1.0,1.0],[12.449652802984803,18.663539350469406,1197.85,9.0,0.0,0.0,1.0],[18.663539350469406,25.858565879135792,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-6.519053499862936,10.160326180227317,-1860.0,9.0,0.0,0.0,1.0],[10.160326180227317,11.468512821803023,-532.7424,8.0,0.0,1.0,1.0],[11.468512821803023,12.449652802984803,0.0,8.0,0.0,1.0,1.0],[12.449652802984803,18.663539350469406,1197.85,9.0,0.0,0.0,1.0],[18.663539350469406,25.858565879135792,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>[[-23.157544165598864,16.90843076475364,-1860.0,8.0,9.0,2.0,-1.0],[16.90843076475364,17.403072430560456,-1808.4764,8.0,9.0,2.0,-1.0],[17.403072430560456,18.886997427980923,0.0,8.0,9.0,2.0,-1.0],[18.886997427980923,19.38163909378774,46.5,9.0,9.0,1.0,-1.0],[19.38163909378774,25.811980749276415,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-23.157544165598864,16.90843076475364,-1860.0,8.0,9.0,2.0,-1.0],[16.90843076475364,17.403072430560456,-1808.4764,7.0,9.0,2.0,-1.0],[17.403072430560456,18.886997427980923,0.0,7.0,9.0,2.0,-1.0],[18.886997427980923,19.38163909378774,46.5,8.0,9.0,1.0,-1.0],[19.38163909378774,25.811980749276415,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>[[-23.95174992965749,17.10621284315048,-1860.0,7.0,9.0,3.0,-1.0],[17.10621284315048,19.239094026153488,0.0,7.0,8.0,4.0,-1.0],[19.239094026153488,28.837059349667033,1860.0,7.0,9.0,2.0,-1.0]]</t>
+          <t>[[-23.95174992965749,17.10621284315048,-1860.0,7.0,9.0,3.0,-1.0],[17.10621284315048,19.239094026153488,0.0,7.0,8.0,4.0,-1.0],[19.239094026153488,28.837059349667033,1860.0,6.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C397" t="n">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>[[-27.589920189762932,15.94679725448454,-1860.0,6.0,0.0,0.0,1.0],[15.94679725448454,17.092500345122634,-733.6842,6.0,0.0,0.0,1.0],[17.092500345122634,19.383906526398814,0.0,6.0,8.0,3.0,-1.0],[19.383906526398814,29.1223827968226,1860.0,6.0,9.0,2.0,-1.0]]</t>
+          <t>[[-27.589920189762932,15.94679725448454,-1860.0,6.0,0.0,0.0,1.0],[15.94679725448454,17.092500345122634,-733.6842,5.0,0.0,0.0,1.0],[17.092500345122634,19.383906526398814,0.0,5.0,8.0,3.0,-1.0],[19.383906526398814,29.1223827968226,1860.0,6.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>[[-28.266459330222244,16.8154451342167,-1860.0,5.0,0.0,0.0,1.0],[16.8154451342167,18.506016551633156,0.0,5.0,8.0,3.0,-1.0],[18.506016551633156,19.633064163244132,227.85,5.0,8.0,3.0,-1.0],[19.633064163244132,27.522397444520944,1860.0,5.0,9.0,2.0,-1.0]]</t>
+          <t>[[-28.266459330222244,16.8154451342167,-1860.0,5.0,0.0,0.0,1.0],[16.8154451342167,18.506016551633156,0.0,4.0,8.0,3.0,-1.0],[18.506016551633156,19.633064163244132,227.85,4.0,8.0,3.0,-1.0],[19.633064163244132,27.522397444520944,1860.0,5.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>[[-28.51583558333333,16.458330178919848,-1860.0,4.0,0.0,0.0,1.0],[16.458330178919848,17.582684322976174,-733.6842,4.0,0.0,0.0,1.0],[17.582684322976174,19.26921553906067,0.0,4.0,8.0,4.0,-1.0],[19.26921553906067,19.831392611088834,227.85,4.0,8.0,3.0,-1.0],[19.831392611088834,27.139694547454976,1860.0,4.0,9.0,2.0,-1.0]]</t>
+          <t>[[-28.51583558333333,16.458330178919848,-1860.0,3.0,0.0,0.0,1.0],[16.458330178919848,17.582684322976174,-733.6842,3.0,0.0,0.0,1.0],[17.582684322976174,19.26921553906067,0.0,3.0,8.0,4.0,-1.0],[19.26921553906067,19.831392611088834,227.85,3.0,8.0,3.0,-1.0],[19.831392611088834,27.139694547454976,1860.0,3.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>[[-28.51583558333333,16.659021744360256,-1860.0,3.0,0.0,0.0,1.0],[16.659021744360256,18.39651625696386,0.0,3.0,9.0,2.0,-1.0],[18.39651625696386,28.821483332585455,1860.0,4.0,9.0,1.0,-1.0]]</t>
+          <t>[[-28.51583558333333,16.659021744360256,-1860.0,3.0,0.0,0.0,1.0],[16.659021744360256,18.39651625696386,0.0,2.0,9.0,2.0,-1.0],[18.39651625696386,28.821483332585455,1860.0,3.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>[[-28.51583558333333,16.856873397231563,-1860.0,2.0,8.0,3.0,-1.0],[16.856873397231563,18.558349984002742,0.0,1.0,8.0,4.0,-1.0],[18.558349984002742,19.1255088462598,227.85,2.0,8.0,3.0,-1.0],[19.1255088462598,27.632891780115717,1860.0,2.0,8.0,3.0,-1.0]]</t>
+          <t>[[-28.51583558333333,16.856873397231563,-1860.0,1.0,8.0,3.0,-1.0],[16.856873397231563,18.558349984002742,0.0,1.0,8.0,4.0,-1.0],[18.558349984002742,19.1255088462598,227.85,2.0,8.0,3.0,-1.0],[19.1255088462598,27.632891780115717,1860.0,2.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>[[-28.352162380837775,16.97681646261686,-733.6842,0.0,0.0,0.0,1.0],[16.97681646261686,18.720238725826647,0.0,0.0,9.0,2.0,-1.0],[18.720238725826647,19.30137948022991,46.5,1.0,9.0,1.0,-1.0],[19.30137948022991,29.180772305085412,1860.0,1.0,9.0,1.0,-1.0]]</t>
+          <t>[[-28.352162380837775,16.97681646261686,-733.6843,0.0,0.0,0.0,1.0],[16.97681646261686,18.720238725826647,0.0,0.0,9.0,2.0,-1.0],[18.720238725826647,19.30137948022991,46.5,1.0,9.0,1.0,-1.0],[19.30137948022991,29.180772305085412,1860.0,1.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>[[-28.51583558333333,16.3082887319805,-733.6842,0.0,0.0,0.0,1.0],[16.3082887319805,17.989193393804772,0.0,0.0,8.0,2.0,-1.0],[17.989193393804772,18.549494947746194,227.85,0.0,8.0,2.0,-1.0],[18.549494947746194,26.954018256867542,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-28.51583558333333,16.3082887319805,-733.6843,0.0,0.0,0.0,1.0],[16.3082887319805,17.989193393804772,0.0,0.0,8.0,2.0,-1.0],[17.989193393804772,18.549494947746194,227.85,0.0,8.0,2.0,-1.0],[18.549494947746194,26.954018256867542,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>[[-28.292333007671303,-7.798825774169366,-1860.0,1.0,2.0,0.0,-1.0],[-7.798825774169366,-7.196075561419306,-200.9418,0.0,2.0,0.0,-1.0],[-7.196075561419306,18.119433374083087,0.0,0.0,2.0,1.0,-1.0],[18.119433374083087,31.379938054584343,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-28.292333007671303,-6.59332534866925,-1860.0,1.0,2.0,0.0,-1.0],[-6.59332534866925,18.119433374083087,0.0,0.0,2.0,1.0,-1.0],[18.119433374083087,31.379938054584343,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="E414" s="4" t="inlineStr">
         <is>
-          <t>[0.3434343434,0,0.0101010101,0.4242424242,0,0,0.2222222222,0]</t>
+          <t>[0.3636363636,0,0,0.4141414141,0,0,0.2222222222,0]</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>[[-28.251498498182293,-8.062514982872095,-1860.0,1.0,1.0,0.0,-1.0],[-8.062514982872095,-6.874927717265614,-200.9418,0.0,1.0,0.0,-1.0],[-6.874927717265614,18.064404860470518,0.0,0.0,1.0,1.0,-1.0],[18.064404860470518,30.534071149338583,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-28.251498498182293,-6.281134084462369,-1860.0,1.0,1.0,0.0,-1.0],[-6.281134084462369,18.064404860470518,0.0,0.0,1.0,1.0,-1.0],[18.064404860470518,30.534071149338583,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="E415" s="4" t="inlineStr">
         <is>
-          <t>[0.3434343434,0,0.0202020202,0.4242424242,0,0,0.2121212121,0]</t>
+          <t>[0.3737373737,0,0,0.4141414141,0,0,0.2121212121,0]</t>
         </is>
       </c>
     </row>
@@ -9993,7 +9993,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>[[-28.51583558333333,-8.08576385353344,-1860.0,1.0,0.0,0.0,-1.0],[-8.08576385353344,-7.466670770812229,-200.9418,0.0,0.0,0.0,-1.0],[-7.466670770812229,32.77437960606635,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-28.51583558333333,-6.847577688091018,-1860.0,1.0,0.0,0.0,-1.0],[-6.847577688091018,32.77437960606635,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="E416" s="4" t="inlineStr">
         <is>
-          <t>[0.3333333333,0,0.0101010101,0.6565656566,0,0,0,0]</t>
+          <t>[0.3535353535,0,0,0.6464646465,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -10062,7 +10062,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>[[-28.51583558333333,-8.161336289602811,-1860.0,8.0,0.0,0.0,1.0],[-8.161336289602811,14.587809979860712,-733.6842,8.0,0.0,0.0,1.0],[14.587809979860712,16.38379521166046,0.0,8.0,0.0,1.0,1.0],[16.38379521166046,22.370412650992964,1016.5,9.0,0.0,0.0,1.0],[22.370412650992964,30.751677066058473,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-28.51583558333333,-8.161336289602811,-1860.0,8.0,0.0,0.0,1.0],[-8.161336289602811,14.587809979860712,-733.6842,8.0,0.0,0.0,1.0],[14.587809979860712,16.38379521166046,0.0,8.0,0.0,1.0,1.0],[16.38379521166046,22.370412650992964,1016.5,9.0,0.0,0.0,1.0],[22.370412650992964,30.751677066058473,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>[[-11.908724046901925,20.73534036402382,-1860.0,4.0,9.0,0.0,-1.0],[20.73534036402382,21.176476369576875,-1808.4764,3.0,9.0,1.0,-1.0],[21.176476369576875,23.382156397342122,0.0,3.0,8.0,2.0,-1.0],[23.382156397342122,23.823292402895177,227.85,3.0,8.0,1.0,-1.0],[23.823292402895177,25.146700419554328,590.55,1.0,6.0,0.0,-1.0],[25.146700419554328,31.763740502850084,1860.0,1.0,6.0,0.0,-1.0]]</t>
+          <t>[[-11.908724046901925,20.73534036402382,-1860.0,4.0,9.0,0.0,-1.0],[20.73534036402382,21.176476369576875,-1808.4764,3.0,9.0,1.0,-1.0],[21.176476369576875,23.382156397342122,0.0,1.0,8.0,2.0,-1.0],[23.382156397342122,23.823292402895177,227.85,3.0,8.0,1.0,-1.0],[23.823292402895177,25.146700419554328,590.55,1.0,6.0,0.0,-1.0],[25.146700419554328,31.763740502850084,1860.0,1.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>[[-13.035674578375192,19.366164276537077,-1860.0,1.0,3.0,1.0,-1.0],[19.366164276537077,19.924816670587283,-1808.4764,1.0,3.0,1.0,-1.0],[19.924816670587283,22.15942624678813,0.0,1.0,3.0,1.0,-1.0],[22.15942624678813,22.718078640838343,46.5,2.0,3.0,0.0,-1.0],[22.718078640838343,42.27091243259575,1860.0,2.0,3.0,0.0,-1.0]]</t>
+          <t>[[-13.035674578375192,19.366164276537077,-1860.0,1.0,3.0,1.0,-1.0],[19.366164276537077,19.924816670587283,-1808.4764,1.0,3.0,1.0,-1.0],[19.924816670587283,22.15942624678813,0.0,0.0,3.0,1.0,-1.0],[22.15942624678813,22.718078640838343,46.5,1.0,3.0,0.0,-1.0],[22.718078640838343,42.27091243259575,1860.0,1.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C435" t="n">
@@ -10453,7 +10453,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>[[-12.446742943472662,20.89588487044766,-1860.0,2.0,2.0,0.0,-1.0],[20.89588487044766,21.49128893855338,-1808.4764,1.0,2.0,1.0,-1.0],[21.49128893855338,23.872905210976263,0.0,1.0,1.0,2.0,-1.0],[23.872905210976263,24.468309279081986,227.85,1.0,1.0,2.0,-1.0],[24.468309279081986,46.49825979899363,409.2,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-12.446742943472662,20.89588487044766,-1860.0,2.0,2.0,0.0,-1.0],[20.89588487044766,21.49128893855338,-1808.4764,1.0,2.0,1.0,-1.0],[21.49128893855338,23.872905210976263,0.0,1.0,1.0,2.0,-1.0],[23.872905210976263,24.468309279081986,227.85,1.0,1.0,2.0,-1.0],[24.468309279081986,26.254521483399145,409.2,0.0,0.0,0.0,-1.0],[26.254521483399145,46.49825979899363,409.2001,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>[[-13.362752798384967,18.067167782712055,-1860.0,1.0,2.0,0.0,-1.0],[18.067167782712055,19.8804324316215,-1808.4764,0.0,2.0,1.0,-1.0],[19.8804324316215,22.298118630167423,0.0,0.0,2.0,1.0,-1.0],[22.298118630167423,22.902540179803907,46.5,1.0,2.0,0.0,-1.0],[22.902540179803907,46.47498061562668,1860.0,1.0,2.0,0.0,-1.0]]</t>
+          <t>[[-13.362752798384967,18.067167782712055,-1860.0,0.0,2.0,0.0,-1.0],[18.067167782712055,19.8804324316215,-1808.4764,0.0,2.0,1.0,-1.0],[19.8804324316215,22.298118630167423,0.0,0.0,2.0,1.0,-1.0],[22.298118630167423,22.902540179803907,46.5,1.0,2.0,0.0,-1.0],[22.902540179803907,46.47498061562668,1860.0,1.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C437" t="n">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>[[-12.510026571708218,20.517998799094805,-1860.0,1.0,1.0,0.0,-1.0],[20.517998799094805,21.153153133148713,-1808.4764,0.0,1.0,1.0,-1.0],[21.153153133148713,23.058616135310423,0.0,0.0,0.0,2.0,-1.0],[23.058616135310423,50.37025249962831,227.85,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-12.510026571708218,20.517998799094805,-1860.0,1.0,1.0,0.0,-1.0],[20.517998799094805,21.153153133148713,-1808.4764,0.0,1.0,1.0,-1.0],[21.153153133148713,23.058616135310423,0.0,0.0,0.0,2.0,-1.0],[23.058616135310423,24.96407913747214,227.85,0.0,0.0,0.0,-1.0],[24.96407913747214,50.37025249962831,227.8501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C438" t="n">
@@ -10522,7 +10522,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>[[-13.468146016474295,6.028954467555527,-1860.0,1.0,1.0,0.0,-1.0],[6.028954467555527,21.12348387454636,-0.0,0.0,1.0,1.0,-1.0],[21.12348387454636,23.010300050420213,0.0,0.0,0.0,1.0,-1.0],[23.010300050420213,25.52605495158535,1860.0,0.0,0.0,0.0,-1.0],[25.52605495158535,48.79678778736288,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-13.468146016474295,6.028954467555527,-1860.0,1.0,1.0,0.0,-1.0],[6.028954467555527,21.12348387454636,0.0,0.0,1.0,1.0,-1.0],[21.12348387454636,23.010300050420213,0.0,0.0,0.0,1.0,-1.0],[23.010300050420213,25.52605495158535,1860.0,0.0,0.0,0.0,-1.0],[25.52605495158535,48.79678778736288,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -10545,7 +10545,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>[[-13.037180856471332,6.060877343205567,-1860.0,1.0,0.0,0.0,-1.0],[6.060877343205567,49.98641120246244,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-13.037180856471332,6.060877343205567,-1860.0,1.0,0.0,0.0,-1.0],[6.060877343205567,49.98641120246244,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C440" t="n">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>[[-12.888065504034058,18.190362976117605,-1860.0,9.0,0.0,0.0,1.0],[18.190362976117605,32.143943110063255,-0.0,9.0,0.0,1.0,1.0],[32.143943110063255,49.90304509872135,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-12.888065504034058,18.190362976117605,-1860.0,9.0,0.0,0.0,1.0],[18.190362976117605,32.143943110063255,0.0,9.0,0.0,1.0,1.0],[32.143943110063255,49.90304509872135,662.15,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C443" t="n">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>[[-12.761608216582523,18.15128723523793,-1860.0,8.0,0.0,0.0,1.0],[18.15128723523793,32.31969765065564,-0.0,8.0,0.0,1.0,1.0],[32.31969765065564,33.60773496114816,1678.65,9.0,0.0,2.0,1.0],[33.60773496114816,50.99623865279717,1860.0,9.0,1.0,1.0,1.0]]</t>
+          <t>[[-12.761608216582523,18.15128723523793,-1860.0,7.0,0.0,0.0,1.0],[18.15128723523793,32.31969765065564,0.0,8.0,0.0,1.0,1.0],[32.31969765065564,33.60773496114816,1678.6499,9.0,0.0,2.0,1.0],[33.60773496114816,50.99623865279717,1860.0,9.0,1.0,1.0,1.0]]</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>[[-12.73523555927291,17.54656383104959,-1860.0,7.0,0.0,0.0,1.0],[17.54656383104959,34.298197536334385,-0.0,7.0,0.0,1.0,1.0],[34.298197536334385,51.04983124161917,1860.0,7.0,9.0,2.0,-1.0]]</t>
+          <t>[[-12.73523555927291,17.54656383104959,-1860.0,7.0,0.0,0.0,1.0],[17.54656383104959,34.298197536334385,0.0,7.0,0.0,1.0,1.0],[34.298197536334385,51.04983124161917,1860.0,7.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>[[-12.630442718895095,18.12591559759094,-1860.0,6.0,0.0,0.0,1.0],[18.12591559759094,32.27384042317452,-0.0,6.0,0.0,1.0,1.0],[32.27384042317452,48.267146747747255,1860.0,6.0,9.0,2.0,-1.0]]</t>
+          <t>[[-12.630442718895095,18.12591559759094,-1860.0,6.0,0.0,0.0,1.0],[18.12591559759094,32.27384042317452,0.0,6.0,0.0,1.0,1.0],[32.27384042317452,48.267146747747255,1860.0,6.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>[[-12.931053183247252,17.377753250520712,-1860.0,5.0,0.0,0.0,1.0],[17.377753250520712,32.5321564674047,-0.0,5.0,0.0,1.0,1.0],[32.5321564674047,34.42645686951519,1678.65,6.0,0.0,0.0,1.0],[34.42645686951519,49.58086008639918,1860.0,6.0,1.0,0.0,1.0]]</t>
+          <t>[[-12.931053183247252,17.377753250520712,-1860.0,5.0,0.0,0.0,1.0],[17.377753250520712,32.5321564674047,0.0,5.0,0.0,1.0,1.0],[32.5321564674047,34.42645686951519,1678.6499,6.0,0.0,0.0,1.0],[34.42645686951519,49.58086008639918,1860.0,5.0,1.0,0.0,1.0]]</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -10729,7 +10729,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>[[-12.789751678456406,17.524917111374926,-1860.0,4.0,0.0,0.0,1.0],[17.524917111374926,33.64974093575329,-0.0,4.0,0.0,1.0,1.0],[33.64974093575329,51.064550666081935,1860.0,4.0,9.0,2.0,-1.0]]</t>
+          <t>[[-12.789751678456406,17.524917111374926,-1860.0,4.0,0.0,0.0,1.0],[17.524917111374926,33.64974093575329,0.0,4.0,0.0,1.0,1.0],[33.64974093575329,51.064550666081935,1860.0,4.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C448" t="n">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>[[-12.387430091420587,17.799611991275615,-1860.0,3.0,0.0,0.0,1.0],[17.799611991275615,33.52202974267989,-0.0,3.0,0.0,1.0,1.0],[33.52202974267989,49.87334420414034,1860.0,3.0,9.0,2.0,-1.0]]</t>
+          <t>[[-12.387430091420587,17.799611991275615,-1860.0,3.0,0.0,0.0,1.0],[17.799611991275615,33.52202974267989,0.0,3.0,0.0,1.0,1.0],[33.52202974267989,49.87334420414034,1860.0,3.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>[[-11.166545990068537,28.404275155559752,-1860.0,3.0,0.0,0.0,1.0],[28.404275155559752,30.91670824417107,-873.8504,2.0,8.0,3.0,-1.0],[30.91670824417107,34.05724960493522,0.0,2.0,8.0,3.0,-1.0],[34.05724960493522,51.01617295306163,1860.0,3.0,9.0,1.0,-1.0]]</t>
+          <t>[[-11.166545990068537,28.404275155559752,-1860.0,3.0,0.0,0.0,1.0],[28.404275155559752,30.91670824417107,-873.8505,2.0,8.0,3.0,-1.0],[30.91670824417107,34.05724960493522,0.0,2.0,8.0,3.0,-1.0],[34.05724960493522,51.01617295306163,1860.0,3.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>[[-7.640204688437672,30.186354010912417,-1860.0,2.0,8.0,2.0,-1.0],[30.186354010912417,30.768301067825497,-873.8504,2.0,8.0,2.0,-1.0],[30.768301067825497,34.25998340930396,0.0,2.0,8.0,2.0,-1.0],[34.25998340930396,34.84193046621704,890.0,3.0,8.0,1.0,-1.0],[34.84193046621704,49.97255394595708,1860.0,3.0,9.0,0.0,-1.0]]</t>
+          <t>[[-7.640204688437672,30.186354010912417,-1860.0,2.0,8.0,2.0,-1.0],[30.186354010912417,30.768301067825497,-873.8505,2.0,8.0,2.0,-1.0],[30.768301067825497,34.25998340930396,0.0,1.0,8.0,2.0,-1.0],[34.25998340930396,34.84193046621704,889.9999,2.0,8.0,1.0,-1.0],[34.84193046621704,49.97255394595708,1860.0,3.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C451" t="n">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>[[-7.4856277310705694,30.797224793110733,-1860.0,1.0,8.0,2.0,-1.0],[30.797224793110733,34.22553994452995,0.0,1.0,8.0,2.0,-1.0],[34.22553994452995,35.368311661669686,890.0,2.0,8.0,1.0,-1.0],[35.368311661669686,49.08157226734657,1860.0,2.0,9.0,0.0,-1.0]]</t>
+          <t>[[-7.4856277310705694,30.797224793110733,-1860.0,1.0,8.0,2.0,-1.0],[30.797224793110733,34.22553994452995,0.0,1.0,8.0,2.0,-1.0],[34.22553994452995,35.368311661669686,889.9999,2.0,8.0,1.0,-1.0],[35.368311661669686,49.08157226734657,1860.0,1.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C452" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>[[-7.9743499847910035,30.436236141724955,-1860.0,1.0,0.0,0.0,1.0],[30.436236141724955,31.018214719399438,-873.8504,0.0,8.0,2.0,-1.0],[31.018214719399438,33.928107607771864,0.0,0.0,8.0,2.0,-1.0],[33.928107607771864,34.51008618544635,890.0,1.0,8.0,1.0,-1.0],[34.51008618544635,49.64152920498293,1860.0,1.0,9.0,0.0,-1.0]]</t>
+          <t>[[-7.9743499847910035,30.436236141724955,-1860.0,1.0,0.0,0.0,1.0],[30.436236141724955,31.018214719399438,-873.8505,0.0,8.0,2.0,-1.0],[31.018214719399438,33.928107607771864,0.0,0.0,8.0,2.0,-1.0],[33.928107607771864,34.51008618544635,889.9999,1.0,8.0,1.0,-1.0],[34.51008618544635,49.64152920498293,1860.0,1.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>[[-7.847153200307435,30.646372336029042,-1860.0,1.0,0.0,0.0,1.0],[30.646372336029042,34.66808395922837,-0.0,1.0,0.0,1.0,1.0],[34.66808395922837,37.54073511865647,890.0,1.0,8.0,0.0,-1.0],[37.54073511865647,49.03133975636885,1860.0,1.0,8.0,0.0,-1.0]]</t>
+          <t>[[-7.847153200307435,30.646372336029042,-1860.0,1.0,0.0,0.0,1.0],[30.646372336029042,34.66808395922837,0.0,1.0,0.0,1.0,1.0],[34.66808395922837,37.54073511865647,889.9999,1.0,8.0,0.0,-1.0],[37.54073511865647,49.03133975636885,1860.0,1.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C454" t="n">
@@ -10890,11 +10890,11 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>[[-7.981039677926239,29.75385873808272,-1860.0,1.0,0.0,0.0,1.0],[29.75385873808272,34.89952670390212,-873.8504,0.0,8.0,0.0,-1.0],[34.89952670390212,38.90171289953943,0.0,0.0,7.0,1.0,-1.0],[38.90171289953943,40.61693555481257,1071.35,0.0,7.0,1.0,-1.0],[40.61693555481257,48.6213079460872,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[-7.981039677926239,29.75385873808272,-1860.0,1.0,0.0,0.0,1.0],[29.75385873808272,34.89952670390212,-873.8505,0.0,8.0,0.0,-1.0],[34.89952670390212,38.90171289953943,0.0,0.0,7.0,1.0,-1.0],[38.90171289953943,40.61693555481257,1071.3499,0.0,7.0,1.0,-1.0],[40.61693555481257,48.6213079460872,1860.0,0.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C455" t="n">
-        <v>-873.8504</v>
+        <v>-873.8505</v>
       </c>
       <c r="D455" s="4" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>[[-7.391476067821784,8.815961861520975,-986.1496,0.0,0.0,0.0,1.0],[8.815961861520975,33.40655734052378,-0.0,0.0,8.0,1.0,-1.0],[33.40655734052378,47.93736375993453,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-7.391476067821784,8.815961861520975,-986.1497,0.0,0.0,0.0,1.0],[8.815961861520975,33.40655734052378,0.0,0.0,8.0,1.0,-1.0],[33.40655734052378,47.93736375993453,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C456" t="n">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>[[-7.50252825896867,8.725470877811897,-1860.0,1.0,7.0,0.0,-1.0],[8.725470877811897,33.36798808551572,-0.0,0.0,7.0,1.0,-1.0],[33.36798808551572,52.00013524256007,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-7.50252825896867,8.725470877811897,-1860.0,1.0,7.0,0.0,-1.0],[8.725470877811897,33.36798808551572,0.0,0.0,7.0,1.0,-1.0],[33.36798808551572,52.00013524256007,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>[[-7.88717335140371,9.044753456036549,-1860.0,1.0,6.0,0.0,-1.0],[9.044753456036549,32.874872666508026,-0.0,0.0,6.0,1.0,-1.0],[32.874872666508026,54.19655827587724,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[-7.88717335140371,9.044753456036549,-1860.0,1.0,6.0,0.0,-1.0],[9.044753456036549,32.874872666508026,0.0,0.0,6.0,1.0,-1.0],[32.874872666508026,54.19655827587724,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C458" t="n">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>[[-7.871601879230988,9.1470993319877,-1860.0,1.0,5.0,0.0,-1.0],[9.1470993319877,34.35999001527465,-0.0,0.0,5.0,1.0,-1.0],[34.35999001527465,54.5303025619042,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-7.871601879230988,9.1470993319877,-1860.0,1.0,5.0,0.0,-1.0],[9.1470993319877,34.35999001527465,0.0,0.0,5.0,1.0,-1.0],[34.35999001527465,54.5303025619042,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -11005,7 +11005,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>[[-8.06501593357726,9.678007584631597,-1860.0,1.0,4.0,0.0,-1.0],[9.678007584631597,34.151143471816226,-0.0,0.0,4.0,1.0,-1.0],[34.151143471816226,52.5059953872047,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-8.06501593357726,9.678007584631597,-1860.0,1.0,4.0,0.0,-1.0],[9.678007584631597,34.151143471816226,0.0,0.0,4.0,1.0,-1.0],[34.151143471816226,52.5059953872047,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C460" t="n">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>[[-7.452173238962049,9.01199110040751,-1860.0,1.0,3.0,0.0,-1.0],[9.01199110040751,34.88424934798826,-0.0,0.0,3.0,1.0,-1.0],[34.88424934798826,50.76040781809462,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-7.452173238962049,9.01199110040751,-1860.0,1.0,3.0,0.0,-1.0],[9.01199110040751,34.88424934798826,0.0,0.0,3.0,1.0,-1.0],[34.88424934798826,50.76040781809462,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>[[-8.132259430011528,9.377048097731977,-1860.0,1.0,2.0,0.0,-1.0],[9.377048097731977,33.52781710151612,-0.0,0.0,2.0,1.0,-1.0],[33.52781710151612,51.640893854354225,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-8.132259430011528,9.377048097731977,-1860.0,1.0,2.0,0.0,-1.0],[9.377048097731977,33.52781710151612,0.0,0.0,2.0,1.0,-1.0],[33.52781710151612,51.640893854354225,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C462" t="n">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>[[-7.811071104687318,8.991548733924635,-1860.0,1.0,1.0,0.0,-1.0],[8.991548733924635,30.317950836778262,-0.0,0.0,1.0,1.0,-1.0],[30.317950836778262,33.54922388266518,0.0,0.0,0.0,1.0,-1.0],[33.54922388266518,36.7804969285521,1860.0,0.0,0.0,0.0,-1.0],[36.7804969285521,56.16813520387358,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-7.811071104687318,8.991548733924635,-1860.0,1.0,1.0,0.0,-1.0],[8.991548733924635,33.54922388266518,0.0,0.0,1.0,1.0,-1.0],[33.54922388266518,56.16813520387358,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>[[-7.509250764453817,9.287177164359285,-1860.0,1.0,0.0,0.0,-1.0],[9.287177164359285,54.07765164119422,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-7.509250764453817,9.287177164359285,-1860.0,1.0,0.0,0.0,-1.0],[9.287177164359285,54.07765164119422,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>[[-7.998756354782032,3.2823498029561913,-1860.0,9.0,0.0,0.0,1.0],[3.2823498029561913,9.219774096502626,-733.6843,9.0,0.0,0.0,1.0],[9.219774096502626,50.781744151327665,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-7.998756354782032,3.2823498029561913,-1860.0,9.0,0.0,0.0,1.0],[3.2823498029561913,9.219774096502626,-733.6842,9.0,0.0,0.0,1.0],[9.219774096502626,50.781744151327665,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>[[-7.5259422466292625,8.88714186218196,-1860.0,9.0,0.0,0.0,1.0],[8.88714186218196,29.555469999203503,-733.6843,9.0,0.0,0.0,1.0],[29.555469999203503,52.65536615234522,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-7.5259422466292625,8.88714186218196,-1860.0,9.0,0.0,0.0,1.0],[8.88714186218196,29.555469999203503,-733.6842,9.0,0.0,0.0,1.0],[29.555469999203503,52.65536615234522,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C466" t="n">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>[[-7.83124313551667,9.15363989450027,-1860.0,8.0,0.0,0.0,1.0],[9.15363989450027,29.778140716663696,-733.6843,8.0,0.0,0.0,1.0],[29.778140716663696,32.81115554345243,0.0,8.0,8.0,2.0,-1.0],[32.81115554345243,35.23756740488342,227.85,8.0,8.0,1.0,-1.0],[35.23756740488342,52.22245043490036,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-7.83124313551667,9.15363989450027,-1860.0,8.0,0.0,0.0,1.0],[9.15363989450027,29.778140716663696,-733.6842,8.0,0.0,0.0,1.0],[29.778140716663696,32.81115554345243,0.0,8.0,8.0,2.0,-1.0],[32.81115554345243,35.23756740488342,227.85,8.0,8.0,1.0,-1.0],[35.23756740488342,52.22245043490036,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C467" t="n">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>[[-7.948929564089551,8.896219842097295,-1860.0,7.0,0.0,0.0,1.0],[8.896219842097295,29.22657257370211,-733.6843,7.0,0.0,0.0,1.0],[29.22657257370211,32.13090867821708,0.0,7.0,8.0,1.0,-1.0],[32.13090867821708,35.616112003635045,227.85,7.0,8.0,1.0,-1.0],[35.616112003635045,49.556925305306926,1860.0,7.0,8.0,1.0,-1.0]]</t>
+          <t>[[-7.948929564089551,8.896219842097295,-1860.0,7.0,0.0,0.0,1.0],[8.896219842097295,29.22657257370211,-733.6842,7.0,0.0,0.0,1.0],[29.22657257370211,32.13090867821708,0.0,7.0,8.0,1.0,-1.0],[32.13090867821708,35.616112003635045,227.85,7.0,8.0,1.0,-1.0],[35.616112003635045,49.556925305306926,1860.0,7.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>[[-7.779917561568604,9.173138445962588,-1860.0,6.0,0.0,0.0,1.0],[9.173138445962588,30.364458455376578,-733.6843,6.0,0.0,0.0,1.0],[30.364458455376578,33.39178988529286,0.0,6.0,8.0,2.0,-1.0],[33.39178988529286,34.602722457259375,227.85,6.0,8.0,2.0,-1.0],[34.602722457259375,52.161244750773825,1860.0,6.0,8.0,2.0,-1.0]]</t>
+          <t>[[-7.779917561568604,9.173138445962588,-1860.0,6.0,0.0,0.0,1.0],[9.173138445962588,30.364458455376578,-733.6842,6.0,0.0,0.0,1.0],[30.364458455376578,33.39178988529286,0.0,6.0,8.0,2.0,-1.0],[33.39178988529286,34.602722457259375,227.85,6.0,8.0,2.0,-1.0],[34.602722457259375,52.161244750773825,1860.0,6.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>[[-7.778354666204955,9.193166131691363,-1860.0,5.0,0.0,0.0,1.0],[9.193166131691363,29.80144138627975,-733.6843,5.0,0.0,0.0,1.0],[29.80144138627975,33.438195842971815,0.0,5.0,8.0,3.0,-1.0],[33.438195842971815,34.65044732853584,227.85,5.0,8.0,1.0,-1.0],[34.65044732853584,52.22809386921417,1860.0,5.0,8.0,1.0,-1.0]]</t>
+          <t>[[-7.778354666204955,9.193166131691363,-1860.0,5.0,0.0,0.0,1.0],[9.193166131691363,29.80144138627975,-733.6842,5.0,0.0,0.0,1.0],[29.80144138627975,33.438195842971815,0.0,5.0,8.0,3.0,-1.0],[33.438195842971815,34.65044732853584,227.85,5.0,8.0,1.0,-1.0],[34.65044732853584,52.22809386921417,1860.0,5.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -11258,7 +11258,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>[[-7.795372522931508,8.664729823290738,-1860.0,4.0,0.0,0.0,1.0],[8.664729823290738,32.08872162368394,-733.6843,4.0,0.0,0.0,1.0],[32.08872162368394,35.254125921034365,0.0,4.0,8.0,2.0,-1.0],[35.254125921034365,54.87963256460705,1860.0,4.0,9.0,0.0,-1.0]]</t>
+          <t>[[-7.795372522931508,8.664729823290738,-1860.0,4.0,0.0,0.0,1.0],[8.664729823290738,32.08872162368394,-733.6842,4.0,0.0,0.0,1.0],[32.08872162368394,35.254125921034365,0.0,4.0,8.0,2.0,-1.0],[35.254125921034365,54.87963256460705,1860.0,4.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C471" t="n">
@@ -11281,7 +11281,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>[[-8.127396585498271,8.772950009571108,-1860.0,3.0,0.0,0.0,1.0],[8.772950009571108,31.70913467430812,-733.6843,3.0,0.0,0.0,1.0],[31.70913467430812,35.330637516108695,0.0,3.0,8.0,2.0,-1.0],[35.330637516108695,51.627400304211314,1860.0,3.0,8.0,1.0,-1.0]]</t>
+          <t>[[-8.127396585498271,8.772950009571108,-1860.0,3.0,0.0,0.0,1.0],[8.772950009571108,31.70913467430812,-733.6842,3.0,0.0,0.0,1.0],[31.70913467430812,35.330637516108695,0.0,3.0,8.0,2.0,-1.0],[35.330637516108695,51.627400304211314,1860.0,3.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>[[-2.2953996911123196,9.064560437938052,-1860.0,2.0,0.0,0.0,1.0],[9.064560437938052,30.161629249031595,-733.6843,2.0,0.0,0.0,1.0],[30.161629249031595,33.407332143045984,0.0,2.0,8.0,2.0,-1.0],[33.407332143045984,34.48923310771745,227.85,2.0,8.0,2.0,-1.0],[34.48923310771745,51.25869806012514,1860.0,2.0,8.0,2.0,-1.0]]</t>
+          <t>[[-2.2953996911123196,9.064560437938052,-1860.0,2.0,0.0,0.0,1.0],[9.064560437938052,30.161629249031595,-733.6842,2.0,0.0,0.0,1.0],[30.161629249031595,33.407332143045984,0.0,1.0,8.0,2.0,-1.0],[33.407332143045984,34.48923310771745,227.85,2.0,8.0,2.0,-1.0],[34.48923310771745,51.25869806012514,1860.0,1.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C473" t="n">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>[[1.1803474957605447,30.770960056018414,-1860.0,2.0,8.0,1.0,-1.0],[30.770960056018414,32.77710328044268,-1607.5347,1.0,8.0,1.0,-1.0],[32.77710328044268,36.28785392318514,0.0,1.0,8.0,1.0,-1.0],[36.28785392318514,37.79246134150333,227.85,2.0,8.0,0.0,-1.0],[37.79246134150333,50.83239230026104,1860.0,2.0,8.0,0.0,-1.0]]</t>
+          <t>[[1.1803474957605447,30.770960056018414,-1860.0,2.0,8.0,1.0,-1.0],[30.770960056018414,32.77710328044268,-1607.5346,1.0,8.0,1.0,-1.0],[32.77710328044268,36.28785392318514,0.0,1.0,8.0,1.0,-1.0],[36.28785392318514,37.79246134150333,227.85,2.0,8.0,0.0,-1.0],[37.79246134150333,50.83239230026104,1860.0,1.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>[[8.84718636594401,30.1015725931777,-1860.0,1.0,8.0,0.0,-1.0],[30.1015725931777,30.553793576735863,-1607.5347,0.0,8.0,1.0,-1.0],[30.553793576735863,33.71934046164301,0.0,0.0,7.0,2.0,-1.0],[33.71934046164301,37.337108330108315,409.2,0.0,7.0,1.0,-1.0],[37.337108330108315,53.617063738202205,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.84718636594401,30.1015725931777,-1860.0,1.0,8.0,0.0,-1.0],[30.1015725931777,30.553793576735863,-1607.5346,0.0,8.0,1.0,-1.0],[30.553793576735863,33.71934046164301,0.0,0.0,7.0,2.0,-1.0],[33.71934046164301,37.337108330108315,409.2,0.0,7.0,1.0,-1.0],[37.337108330108315,53.617063738202205,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>[[8.629600166848725,24.505992982956336,-1860.0,1.0,8.0,0.0,-1.0],[24.505992982956336,26.9485149546652,-1808.4765,0.0,8.0,0.0,-1.0],[26.9485149546652,29.79812392165887,0.0,0.0,7.0,1.0,-1.0],[29.79812392165887,33.86899387450698,227.85,0.0,7.0,0.0,-1.0],[33.86899387450698,48.931212700044966,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[8.629600166848725,24.505992982956336,-1860.0,1.0,8.0,0.0,-1.0],[24.505992982956336,26.9485149546652,-1808.4764,0.0,8.0,0.0,-1.0],[26.9485149546652,29.79812392165887,0.0,0.0,7.0,1.0,-1.0],[29.79812392165887,33.86899387450698,227.85,0.0,7.0,0.0,-1.0],[33.86899387450698,48.931212700044966,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -11442,7 +11442,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>[[8.578850941358132,25.691822073148877,-1860.0,1.0,7.0,0.0,-1.0],[25.691822073148877,29.11441629950702,-1808.4765,0.0,7.0,0.0,-1.0],[29.11441629950702,32.53701052586517,0.0,0.0,6.0,1.0,-1.0],[32.53701052586517,33.392659082454706,227.85,0.0,6.0,0.0,-1.0],[33.392659082454706,50.93345449254022,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[8.578850941358132,25.691822073148877,-1860.0,1.0,7.0,0.0,-1.0],[25.691822073148877,29.11441629950702,-1808.4764,0.0,7.0,0.0,-1.0],[29.11441629950702,32.53701052586517,0.0,0.0,6.0,1.0,-1.0],[32.53701052586517,33.392659082454706,227.85,0.0,6.0,0.0,-1.0],[33.392659082454706,50.93345449254022,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>[[8.58402710487467,24.645981237977466,-1860.0,1.0,6.0,1.0,-1.0],[24.645981237977466,27.684729317213126,-1808.4765,0.0,6.0,0.0,-1.0],[27.684729317213126,30.723477396448793,0.0,0.0,5.0,1.0,-1.0],[30.723477396448793,33.328118607222216,227.85,0.0,5.0,0.0,-1.0],[33.328118607222216,51.5606070826362,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[8.58402710487467,24.645981237977466,-1860.0,1.0,6.0,1.0,-1.0],[24.645981237977466,27.684729317213126,-1808.4764,0.0,6.0,0.0,-1.0],[27.684729317213126,30.723477396448793,0.0,0.0,5.0,1.0,-1.0],[30.723477396448793,33.328118607222216,227.85,0.0,5.0,0.0,-1.0],[33.328118607222216,51.5606070826362,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -11488,7 +11488,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>[[8.712982875655083,24.97042591158625,-1860.0,1.0,6.0,0.0,-1.0],[24.97042591158625,25.692978935405414,-1808.4765,0.0,6.0,1.0,-1.0],[25.692978935405414,28.221914518772483,0.0,0.0,5.0,2.0,-1.0],[28.221914518772483,32.19595614977788,227.85,0.0,5.0,0.0,-1.0],[32.19595614977788,44.479357554703654,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[8.712982875655083,24.97042591158625,-1860.0,1.0,6.0,0.0,-1.0],[24.97042591158625,25.692978935405414,-1808.4764,0.0,6.0,1.0,-1.0],[25.692978935405414,28.221914518772483,0.0,0.0,5.0,2.0,-1.0],[28.221914518772483,32.19595614977788,227.85,0.0,5.0,0.0,-1.0],[32.19595614977788,44.479357554703654,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C481" t="n">
@@ -11511,7 +11511,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>[[8.82649513126567,14.423283006946393,-1860.0,8.0,13.0,2.0,0.0],[14.423283006946393,24.497501183171693,-1808.4765,0.0,6.0,0.0,-1.0],[24.497501183171693,27.48245471686808,0.0,0.0,5.0,1.0,-1.0],[27.48245471686808,45.765295110758444,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[8.82649513126567,14.423283006946393,-1860.0,8.0,13.0,2.0,0.0],[14.423283006946393,24.497501183171693,-1808.4764,0.0,6.0,0.0,-1.0],[24.497501183171693,27.48245471686808,0.0,0.0,5.0,1.0,-1.0],[27.48245471686808,45.765295110758444,1860.0,0.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -11534,7 +11534,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>[[8.660443620862267,15.446325744617937,-1860.0,9.0,13.0,1.0,0.0],[15.446325744617937,24.171031332303798,-1808.4765,0.0,5.0,0.0,-1.0],[24.171031332303798,26.756129284210722,0.0,0.0,4.0,1.0,-1.0],[26.756129284210722,28.04867826016418,227.85,0.0,4.0,0.0,-1.0],[28.04867826016418,40.651030775710424,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[8.660443620862267,15.446325744617937,-1860.0,9.0,13.0,1.0,0.0],[15.446325744617937,24.171031332303798,-1808.4764,0.0,5.0,0.0,-1.0],[24.171031332303798,26.756129284210722,0.0,0.0,4.0,1.0,-1.0],[26.756129284210722,28.04867826016418,227.85,0.0,4.0,0.0,-1.0],[28.04867826016418,40.651030775710424,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>[[8.548162273718686,15.656809220158557,-1860.0,10.0,4.0,0.0,1.0],[15.656809220158557,24.310814198433185,-1808.4765,0.0,4.0,0.0,-1.0],[24.310814198433185,27.09245865573574,0.0,0.0,3.0,1.0,-1.0],[27.09245865573574,39.14625130404683,1860.0,0.0,3.0,1.0,-1.0]]</t>
+          <t>[[8.548162273718686,15.656809220158557,-1860.0,10.0,4.0,0.0,1.0],[15.656809220158557,24.310814198433185,-1808.4764,0.0,4.0,0.0,-1.0],[24.310814198433185,27.09245865573574,0.0,0.0,3.0,1.0,-1.0],[27.09245865573574,39.14625130404683,1860.0,0.0,3.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C484" t="n">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>[[8.632676841069298,15.006814361456225,-1860.0,10.0,3.0,0.0,1.0],[15.006814361456225,24.416255462979787,-1808.4765,0.0,3.0,0.0,-1.0],[24.416255462979787,27.148028686002757,0.0,0.0,2.0,1.0,-1.0],[27.148028686002757,28.058619760343745,227.85,0.0,2.0,1.0,-1.0],[28.058619760343745,38.68218229432196,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[8.632676841069298,15.006814361456225,-1860.0,9.0,3.0,0.0,1.0],[15.006814361456225,24.416255462979787,-1808.4764,0.0,3.0,0.0,-1.0],[24.416255462979787,27.148028686002757,0.0,0.0,2.0,1.0,-1.0],[27.148028686002757,28.058619760343745,227.85,0.0,2.0,1.0,-1.0],[28.058619760343745,38.68218229432196,1860.0,0.0,2.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C485" t="n">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>[[8.616079852194712,15.022587019903547,-1860.0,10.0,2.0,0.0,1.0],[15.022587019903547,24.952673129852236,-1808.4765,0.0,2.0,0.0,-1.0],[24.952673129852236,27.51527599693577,0.0,0.0,1.0,1.0,-1.0],[27.51527599693577,40.32829033235344,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[8.616079852194712,15.022587019903547,-1860.0,10.0,2.0,0.0,1.0],[15.022587019903547,24.952673129852236,-1808.4764,0.0,2.0,0.0,-1.0],[24.952673129852236,27.51527599693577,0.0,0.0,1.0,1.0,-1.0],[27.51527599693577,40.32829033235344,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C486" t="n">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>[[8.08920529025552,15.947533603561325,-1860.0,10.0,1.0,0.0,1.0],[15.947533603561325,24.788152956030356,-1808.4765,0.0,1.0,0.0,-1.0],[24.788152956030356,27.407595727132293,0.0,0.0,0.0,1.0,-1.0],[27.407595727132293,40.50480958264197,227.85,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[8.08920529025552,15.947533603561325,-1860.0,10.0,1.0,0.0,1.0],[15.947533603561325,24.788152956030356,-1808.4764,0.0,1.0,0.0,-1.0],[24.788152956030356,27.407595727132293,0.0,0.0,0.0,1.0,-1.0],[27.407595727132293,30.35446884462197,227.85,0.0,0.0,0.0,-1.0],[30.35446884462197,40.50480958264197,227.8501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C487" t="n">
@@ -11649,11 +11649,11 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>[[8.842562569053646,15.41074883013695,-1860.0,9.0,0.0,1.0,1.0],[15.41074883013695,16.306410593011947,-481.2189,9.0,0.0,1.0,1.0],[16.306410593011947,18.097734118761938,0.0,9.0,0.0,1.0,1.0],[18.097734118761938,38.39940074392852,227.85,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[8.842562569053646,15.41074883013695,-1860.0,8.0,0.0,1.0,1.0],[15.41074883013695,16.306410593011947,-481.2188,9.0,0.0,1.0,1.0],[16.306410593011947,18.097734118761938,0.0,8.0,0.0,1.0,1.0],[18.097734118761938,38.39940074392852,227.8501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C488" t="n">
-        <v>227.85</v>
+        <v>227.8501</v>
       </c>
       <c r="D488" s="4" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>[[8.919905311090957,15.155385387502504,-1860.0,9.0,0.0,0.0,1.0],[15.155385387502504,18.273125425708276,-733.6843,9.0,0.0,0.0,1.0],[18.273125425708276,36.97956565494292,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[8.919905311090957,15.155385387502504,-1860.0,9.0,0.0,0.0,1.0],[15.155385387502504,18.273125425708276,-733.6842,9.0,0.0,0.0,1.0],[18.273125425708276,36.97956565494292,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C489" t="n">
@@ -11695,7 +11695,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>[[8.550657227158867,15.978622018906291,-1860.0,8.0,0.0,0.0,1.0],[15.978622018906291,17.464214977255775,-733.6843,8.0,0.0,0.0,1.0],[17.464214977255775,19.544045118945057,0.0,8.0,0.0,1.0,1.0],[19.544045118945057,30.83455160240114,1016.5,9.0,0.0,0.0,1.0],[30.83455160240114,37.96539780247866,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[8.550657227158867,15.978622018906291,-1860.0,7.0,0.0,0.0,1.0],[15.978622018906291,17.464214977255775,-733.6843,8.0,0.0,0.0,1.0],[17.464214977255775,19.544045118945057,0.0,7.0,0.0,1.0,1.0],[19.544045118945057,30.83455160240114,1016.4999,9.0,0.0,0.0,1.0],[30.83455160240114,37.96539780247866,1678.65,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -11718,7 +11718,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>[[6.6348014116466745,15.477132553586404,-1860.0,7.0,0.0,0.0,1.0],[15.477132553586404,18.424576267566312,-733.6843,7.0,0.0,0.0,1.0],[18.424576267566312,20.38953874355292,0.0,7.0,0.0,1.0,1.0],[20.38953874355292,29.23186988549265,1016.5,8.0,0.0,0.0,1.0],[29.23186988549265,39.056682265425685,1860.0,8.0,9.0,2.0,-1.0]]</t>
+          <t>[[6.6348014116466745,15.477132553586404,-1860.0,6.0,0.0,0.0,1.0],[15.477132553586404,18.424576267566312,-733.6843,7.0,0.0,0.0,1.0],[18.424576267566312,20.38953874355292,0.0,6.0,0.0,1.0,1.0],[20.38953874355292,29.23186988549265,1016.4999,8.0,0.0,0.0,1.0],[29.23186988549265,39.056682265425685,1860.0,8.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C491" t="n">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>[[5.014245738012112,15.464234063745074,-1860.0,6.0,0.0,0.0,1.0],[15.464234063745074,17.48681244937081,-733.6843,6.0,0.0,0.0,1.0],[17.48681244937081,19.509390834996545,0.0,6.0,0.0,1.0,1.0],[19.509390834996545,29.285186365520925,1016.5,7.0,0.0,0.0,1.0],[29.285186365520925,38.38678910083674,1860.0,7.0,9.0,2.0,-1.0]]</t>
+          <t>[[5.014245738012112,15.464234063745074,-1860.0,5.0,0.0,0.0,1.0],[15.464234063745074,17.48681244937081,-733.6843,5.0,0.0,0.0,1.0],[17.48681244937081,19.509390834996545,0.0,5.0,0.0,1.0,1.0],[19.509390834996545,29.285186365520925,1016.4999,6.0,0.0,0.0,1.0],[29.285186365520925,38.38678910083674,1860.0,6.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>[[4.80593404755855,15.80707791294227,-1860.0,5.0,0.0,0.0,1.0],[15.80707791294227,17.226580347185333,-733.6843,5.0,0.0,0.0,1.0],[17.226580347185333,19.355833998549926,0.0,5.0,0.0,1.0,1.0],[19.355833998549926,29.292351038251347,1016.5,6.0,0.0,0.0,1.0],[29.292351038251347,39.93861929507431,1860.0,6.0,9.0,2.0,-1.0]]</t>
+          <t>[[4.80593404755855,15.80707791294227,-1860.0,3.0,0.0,0.0,1.0],[15.80707791294227,17.226580347185333,-733.6843,4.0,0.0,0.0,1.0],[17.226580347185333,19.355833998549926,0.0,4.0,0.0,1.0,1.0],[19.355833998549926,29.292351038251347,1016.4999,4.0,0.0,0.0,1.0],[29.292351038251347,39.93861929507431,1860.0,6.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>[[5.136988153927689,15.74779109715457,-1860.0,4.0,0.0,0.0,1.0],[15.74779109715457,18.82834679034947,-733.6843,4.0,0.0,0.0,1.0],[18.82834679034947,20.88205058581274,0.0,4.0,0.0,1.0,1.0],[20.88205058581274,30.123717665397443,1016.5,5.0,0.0,0.0,1.0],[30.123717665397443,39.0231007790716,1860.0,5.0,9.0,1.0,-1.0]]</t>
+          <t>[[5.136988153927689,15.74779109715457,-1860.0,4.0,0.0,0.0,1.0],[15.74779109715457,18.82834679034947,-733.6843,3.0,0.0,0.0,1.0],[18.82834679034947,20.88205058581274,0.0,3.0,0.0,1.0,1.0],[20.88205058581274,30.123717665397443,1016.4999,4.0,0.0,0.0,1.0],[30.123717665397443,39.0231007790716,1860.0,4.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -11810,7 +11810,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>[[5.36313052343956,14.794150075647046,-1860.0,3.0,0.0,0.0,1.0],[14.794150075647046,18.162371344292577,-733.6843,3.0,0.0,0.0,1.0],[18.162371344292577,19.846481978615344,0.0,3.0,0.0,1.0,1.0],[19.846481978615344,30.287967911416487,1016.5,4.0,0.0,0.0,1.0],[30.287967911416487,38.70852108303031,1860.0,4.0,9.0,1.0,-1.0]]</t>
+          <t>[[5.36313052343956,14.794150075647046,-1860.0,3.0,0.0,0.0,1.0],[14.794150075647046,18.162371344292577,-733.6843,2.0,0.0,0.0,1.0],[18.162371344292577,19.846481978615344,0.0,2.0,0.0,1.0,1.0],[19.846481978615344,30.287967911416487,1016.4999,4.0,0.0,0.0,1.0],[30.287967911416487,38.70852108303031,1860.0,3.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C495" t="n">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>[[3.5918526248606204,18.159338784552713,-1860.0,3.0,0.0,0.0,1.0],[18.159338784552713,29.88438862040245,0.0,3.0,0.0,1.0,1.0],[29.88438862040245,30.239693160882744,890.0,3.0,8.0,3.0,-1.0],[30.239693160882744,38.76700213240982,1860.0,3.0,8.0,3.0,-1.0]]</t>
+          <t>[[3.5918526248606204,18.159338784552713,-1860.0,2.0,0.0,0.0,1.0],[18.159338784552713,29.88438862040245,0.0,2.0,0.0,1.0,1.0],[29.88438862040245,30.239693160882744,890.0,2.0,8.0,3.0,-1.0],[30.239693160882744,38.76700213240982,1860.0,2.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C496" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>[[3.3390809357406224,17.87989495737115,-1860.0,2.0,0.0,0.0,1.0],[17.87989495737115,29.938130975308656,0.0,2.0,0.0,1.0,1.0],[29.938130975308656,30.647438976363805,890.0,2.0,8.0,1.0,-1.0],[30.647438976363805,38.44982698797043,1860.0,2.0,8.0,1.0,-1.0]]</t>
+          <t>[[3.3390809357406224,17.87989495737115,-1860.0,1.0,0.0,0.0,1.0],[17.87989495737115,27.100898971088064,0.0,2.0,0.0,1.0,1.0],[27.100898971088064,29.938130975308656,0.0,0.0,0.0,1.0,1.0],[29.938130975308656,30.647438976363805,890.0,2.0,8.0,1.0,-1.0],[30.647438976363805,38.44982698797043,1860.0,2.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>[[3.7020015909171002,17.18838567738531,-1860.0,1.0,0.0,0.0,1.0],[17.18838567738531,18.96290989928902,-1860.0,0.0,0.0,0.0,1.0],[18.96290989928902,21.09233896557347,0.0,0.0,0.0,1.0,1.0],[21.09233896557347,29.61005523071129,0.0,1.0,0.0,1.0,1.0],[29.61005523071129,30.319864919472774,890.0,1.0,8.0,3.0,-1.0],[30.319864919472774,38.83758118461059,1860.0,1.0,8.0,3.0,-1.0]]</t>
+          <t>[[3.7020015909171002,18.96290989928902,-1860.0,0.0,0.0,0.0,1.0],[18.96290989928902,26.77081647566535,0.0,1.0,0.0,1.0,1.0],[26.77081647566535,28.545340697569063,0.0,0.0,0.0,1.0,1.0],[28.545340697569063,29.61005523071129,0.0,1.0,0.0,1.0,1.0],[29.61005523071129,30.319864919472774,890.0,1.0,8.0,3.0,-1.0],[30.319864919472774,38.83758118461059,1860.0,1.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>[[3.5676443893777567,24.40867347535547,-1860.0,1.0,3.0,0.0,-1.0],[24.40867347535547,26.49277638395324,-1074.7922,0.0,3.0,0.0,-1.0],[26.49277638395324,29.271580262083603,0.0,0.0,2.0,1.0,-1.0],[29.271580262083603,37.95534238124098,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[3.5676443893777567,24.40867347535547,-1860.0,0.0,3.0,0.0,-1.0],[24.40867347535547,26.49277638395324,-1074.7922,0.0,3.0,0.0,-1.0],[26.49277638395324,29.271580262083603,0.0,0.0,2.0,1.0,-1.0],[29.271580262083603,37.95534238124098,1860.0,0.0,2.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C507" t="n">
@@ -12247,7 +12247,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>[[3.8386374432748696,18.05559317772364,-1860.0,8.0,0.0,0.0,1.0],[18.05559317772364,19.909978708303917,-733.6842,8.0,0.0,0.0,1.0],[19.909978708303917,22.073428493980902,0.0,8.0,0.0,1.0,1.0],[22.073428493980902,30.418163381592137,1016.5,9.0,0.0,0.0,1.0],[30.418163381592137,34.4359986978494,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[3.8386374432748696,18.05559317772364,-1860.0,8.0,0.0,0.0,1.0],[18.05559317772364,19.909978708303917,-733.6842,8.0,0.0,0.0,1.0],[19.909978708303917,22.073428493980902,0.0,8.0,0.0,1.0,1.0],[22.073428493980902,30.418163381592137,1016.5,9.0,0.0,0.0,1.0],[30.418163381592137,34.4359986978494,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C514" t="n">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>[[3.852624596638034,17.856215668709932,-1860.0,7.0,0.0,0.0,1.0],[17.856215668709932,20.65693388312431,-733.6842,7.0,0.0,0.0,1.0],[20.65693388312431,22.835270272113274,0.0,7.0,0.0,1.0,1.0],[22.835270272113274,29.681470351792864,1016.5,8.0,0.0,0.0,1.0],[29.681470351792864,34.66052495519621,1860.0,8.0,9.0,2.0,-1.0]]</t>
+          <t>[[3.852624596638034,17.856215668709932,-1860.0,6.0,0.0,0.0,1.0],[17.856215668709932,20.65693388312431,-733.6842,6.0,0.0,0.0,1.0],[20.65693388312431,22.835270272113274,0.0,6.0,0.0,1.0,1.0],[22.835270272113274,29.681470351792864,1016.5,7.0,0.0,0.0,1.0],[29.681470351792864,34.66052495519621,1860.0,7.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C515" t="n">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>[[3.7308772600832674,17.193471352098303,-1860.0,6.0,0.0,0.0,1.0],[17.193471352098303,20.63739077098587,-733.6842,6.0,0.0,0.0,1.0],[20.63739077098587,22.8289758557325,0.0,6.0,0.0,1.0,1.0],[22.8289758557325,29.716814693507636,1016.5,7.0,0.0,0.0,1.0],[29.716814693507636,34.72615203007137,1860.0,7.0,9.0,2.0,-1.0]]</t>
+          <t>[[3.7308772600832674,17.193471352098303,-1860.0,5.0,0.0,0.0,1.0],[17.193471352098303,20.63739077098587,-733.6842,5.0,0.0,0.0,1.0],[20.63739077098587,22.8289758557325,0.0,5.0,0.0,1.0,1.0],[22.8289758557325,29.716814693507636,1016.5,7.0,0.0,0.0,1.0],[29.716814693507636,34.72615203007137,1860.0,7.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C516" t="n">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>[[3.7331082354585186,17.71248440328762,-1860.0,5.0,0.0,0.0,1.0],[17.71248440328762,20.197706833123902,-733.6842,5.0,0.0,0.0,1.0],[20.197706833123902,22.37227645923065,0.0,5.0,0.0,1.0,1.0],[22.37227645923065,30.75990215992811,1016.5,6.0,0.0,0.0,1.0],[30.75990215992811,34.487735804682536,1860.0,6.0,9.0,0.0,-1.0]]</t>
+          <t>[[3.7331082354585186,17.71248440328762,-1860.0,4.0,0.0,0.0,1.0],[17.71248440328762,20.197706833123902,-733.6842,4.0,0.0,0.0,1.0],[20.197706833123902,22.37227645923065,0.0,4.0,0.0,1.0,1.0],[22.37227645923065,30.75990215992811,1016.5,5.0,0.0,0.0,1.0],[30.75990215992811,34.487735804682536,1860.0,6.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C517" t="n">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>[[2.7878386935804578,16.8274046597201,-1860.0,4.0,0.0,0.0,1.0],[16.8274046597201,20.337296151255007,-733.6842,4.0,0.0,0.0,1.0],[20.337296151255007,22.443231046175953,0.0,4.0,0.0,1.0,1.0],[22.443231046175953,30.164992327552756,1016.5,5.0,0.0,0.0,1.0],[30.164992327552756,37.53576445977606,1860.0,5.0,9.0,2.0,-1.0]]</t>
+          <t>[[2.7878386935804578,16.8274046597201,-1860.0,3.0,0.0,0.0,1.0],[16.8274046597201,20.337296151255007,-733.6842,3.0,0.0,0.0,1.0],[20.337296151255007,22.443231046175953,0.0,3.0,0.0,1.0,1.0],[22.443231046175953,30.164992327552756,1016.5,4.0,0.0,0.0,1.0],[30.164992327552756,37.53576445977606,1860.0,4.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C518" t="n">
@@ -12362,7 +12362,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>[[3.0552479507692314,18.04728954197882,-1860.0,3.0,0.0,0.0,1.0],[18.04728954197882,20.32868717542376,-733.6842,3.0,0.0,0.0,1.0],[20.32868717542376,22.6100848088687,0.0,3.0,0.0,1.0,1.0],[22.6100848088687,30.10610560447349,1016.5,4.0,0.0,0.0,1.0],[30.10610560447349,30.432019552108486,1725.15,5.0,9.0,1.0,-1.0],[30.432019552108486,35.320728766633344,1860.0,5.0,9.0,1.0,-1.0]]</t>
+          <t>[[3.0552479507692314,18.04728954197882,-1860.0,3.0,0.0,0.0,1.0],[18.04728954197882,20.32868717542376,-733.6842,2.0,0.0,0.0,1.0],[20.32868717542376,22.6100848088687,0.0,2.0,0.0,1.0,1.0],[22.6100848088687,30.10610560447349,1016.5,3.0,0.0,0.0,1.0],[30.10610560447349,30.432019552108486,1725.15,4.0,9.0,1.0,-1.0],[30.432019552108486,35.320728766633344,1860.0,4.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C519" t="n">
@@ -12385,7 +12385,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>[[2.828559302774794,17.378212630666162,-1860.0,2.0,0.0,0.0,1.0],[17.378212630666162,19.96481766673574,-733.6842,2.0,0.0,0.0,1.0],[19.96481766673574,22.228097073296617,0.0,2.0,0.0,1.0,1.0],[22.228097073296617,30.63456344052274,1016.5,3.0,0.0,0.0,1.0],[30.63456344052274,34.837796624135805,1860.0,3.0,9.0,0.0,-1.0]]</t>
+          <t>[[2.828559302774794,17.378212630666162,-1860.0,2.0,0.0,0.0,1.0],[17.378212630666162,19.96481766673574,-733.6842,2.0,0.0,0.0,1.0],[19.96481766673574,22.228097073296617,0.0,2.0,0.0,1.0,1.0],[22.228097073296617,30.63456344052274,1016.5,2.0,0.0,0.0,1.0],[30.63456344052274,34.837796624135805,1860.0,3.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C520" t="n">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>[[2.760839825309646,18.24087360009212,-1860.0,1.0,0.0,0.0,1.0],[18.24087360009212,20.260008440281137,-1860.0,0.0,0.0,0.0,1.0],[20.260008440281137,22.279143280470155,0.0,0.0,0.0,1.0,1.0],[22.279143280470155,30.01916016786139,0.0,1.0,0.0,1.0,1.0],[30.01916016786139,30.355682641226228,890.0,1.0,8.0,1.0,-1.0],[30.355682641226228,36.07656468842845,1860.0,1.0,8.0,1.0,-1.0]]</t>
+          <t>[[2.760839825309646,20.260008440281137,-1860.0,1.0,0.0,0.0,1.0],[20.260008440281137,26.990457907577863,0.0,0.0,0.0,1.0,1.0],[26.990457907577863,30.01916016786139,0.0,1.0,0.0,1.0,1.0],[30.01916016786139,30.355682641226228,890.0,0.0,8.0,1.0,-1.0],[30.355682641226228,36.07656468842845,1860.0,1.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -12500,7 +12500,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>[[2.7173527521838956,25.235552994200457,-1860.0,1.0,8.0,0.0,-1.0],[25.235552994200457,26.229003004877658,-1074.7922,0.0,8.0,1.0,-1.0],[26.229003004877658,29.209353036909263,0.0,0.0,7.0,2.0,-1.0],[29.209353036909263,30.202803047586464,890.0,0.0,7.0,0.0,-1.0],[30.202803047586464,35.501203104531534,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[2.7173527521838956,25.235552994200457,-1860.0,1.0,8.0,0.0,-1.0],[25.235552994200457,26.229003004877658,-1074.7923,0.0,8.0,1.0,-1.0],[26.229003004877658,29.209353036909263,0.0,0.0,7.0,2.0,-1.0],[29.209353036909263,30.202803047586464,890.0,0.0,7.0,0.0,-1.0],[30.202803047586464,35.501203104531534,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C525" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>[[3.033755273987173,25.887433501254144,-1860.0,1.0,7.0,0.0,-1.0],[25.887433501254144,26.590623600554668,-1074.7922,0.0,7.0,0.0,-1.0],[26.590623600554668,29.403383997756755,0.0,0.0,6.0,1.0,-1.0],[29.403383997756755,30.45816914670754,890.0,0.0,6.0,0.0,-1.0],[30.45816914670754,37.84166518936303,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[3.033755273987173,25.887433501254144,-1860.0,1.0,7.0,0.0,-1.0],[25.887433501254144,26.590623600554668,-1074.7923,0.0,7.0,0.0,-1.0],[26.590623600554668,29.403383997756755,0.0,0.0,6.0,1.0,-1.0],[29.403383997756755,30.45816914670754,890.0,0.0,6.0,0.0,-1.0],[30.45816914670754,37.84166518936303,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C526" t="n">
@@ -12546,7 +12546,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>[[2.8988015939037197,25.708916748372157,-1860.0,1.0,6.0,0.0,-1.0],[25.708916748372157,27.070714668041912,-1074.7922,0.0,6.0,1.0,-1.0],[27.070714668041912,30.134759987298867,0.0,0.0,5.0,2.0,-1.0],[30.134759987298867,32.1774568668035,890.0,0.0,5.0,0.0,-1.0],[32.1774568668035,36.60330010573021,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[2.8988015939037197,25.708916748372157,-1860.0,1.0,6.0,0.0,-1.0],[25.708916748372157,27.070714668041912,-1074.7923,0.0,6.0,1.0,-1.0],[27.070714668041912,30.134759987298867,0.0,0.0,5.0,2.0,-1.0],[30.134759987298867,32.1774568668035,890.0,0.0,5.0,0.0,-1.0],[32.1774568668035,36.60330010573021,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -12592,7 +12592,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>[[2.8543732486296145,26.25298389498913,-1860.0,1.0,4.0,0.0,-1.0],[26.25298389498913,29.480378466900785,0.0,0.0,4.0,2.0,-1.0],[29.480378466900785,42.79338107603637,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[2.8543732486296145,26.25298389498913,-1860.0,1.0,4.0,0.0,-1.0],[26.25298389498913,29.480378466900785,0.0,0.0,3.0,2.0,-1.0],[29.480378466900785,42.79338107603637,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C529" t="n">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>[[2.7500164488974335,25.80571477074939,-1860.0,1.0,3.0,1.0,-1.0],[25.80571477074939,29.71346024902938,0.0,0.0,3.0,2.0,-1.0],[29.71346024902938,41.43669668386936,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[2.7500164488974335,25.80571477074939,-1860.0,1.0,3.0,1.0,-1.0],[25.80571477074939,29.71346024902938,0.0,0.0,2.0,2.0,-1.0],[29.71346024902938,41.43669668386936,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C530" t="n">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>[[2.8374702402250533,25.5441163892489,-1860.0,1.0,2.0,1.0,-1.0],[25.5441163892489,29.193398806056305,0.0,0.0,2.0,2.0,-1.0],[29.193398806056305,42.9795768251065,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[2.8374702402250533,25.5441163892489,-1860.0,1.0,2.0,1.0,-1.0],[25.5441163892489,29.193398806056305,0.0,0.0,1.0,2.0,-1.0],[29.193398806056305,42.9795768251065,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C531" t="n">
@@ -12661,7 +12661,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>[[2.9255890984794393,25.650125412853704,-1860.0,1.0,1.0,1.0,-1.0],[25.650125412853704,28.769179416787427,0.0,0.0,1.0,2.0,-1.0],[28.769179416787427,47.037924296970665,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[2.9255890984794393,25.650125412853704,-1860.0,1.0,1.0,1.0,-1.0],[25.650125412853704,26.095704556272807,0.0,0.0,1.0,2.0,-1.0],[26.095704556272807,28.769179416787427,0.0,0.0,0.0,2.0,-1.0],[28.769179416787427,30.55149599046384,1860.0,0.0,0.0,0.0,-1.0],[30.55149599046384,47.037924296970665,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C532" t="n">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>[[2.901672760188005,21.739943251045954,-1860.0,9.0,0.0,0.0,1.0],[21.739943251045954,36.296788630345276,0.0,9.0,0.0,1.0,1.0],[36.296788630345276,45.28778136461839,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[2.901672760188005,21.739943251045954,-1860.0,8.0,0.0,0.0,1.0],[21.739943251045954,36.296788630345276,0.0,9.0,0.0,1.0,1.0],[36.296788630345276,45.28778136461839,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C538" t="n">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>[[-1.4814532064442627,21.341401455558504,-1860.0,8.0,0.0,0.0,1.0],[21.341401455558504,36.081161758101956,0.0,8.0,0.0,1.0,1.0],[36.081161758101956,36.55663789689368,890.0,8.0,8.0,4.0,-1.0],[36.55663789689368,45.59068453393645,1860.0,8.0,8.0,4.0,-1.0]]</t>
+          <t>[[-1.4814532064442627,21.341401455558504,-1860.0,7.0,0.0,0.0,1.0],[21.341401455558504,36.081161758101956,0.0,7.0,0.0,1.0,1.0],[36.081161758101956,36.55663789689368,890.0,7.0,8.0,4.0,-1.0],[36.55663789689368,45.59068453393645,1860.0,8.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C539" t="n">
@@ -12845,7 +12845,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>[[-3.0126129553512984,20.656689076322607,-1860.0,7.0,0.0,0.0,1.0],[20.656689076322607,35.764754202922965,0.0,7.0,0.0,1.0,1.0],[35.764754202922965,36.268356373809645,890.0,7.0,8.0,4.0,-1.0],[36.268356373809645,46.8440019624299,1860.0,7.0,8.0,4.0,-1.0]]</t>
+          <t>[[-3.0126129553512984,20.656689076322607,-1860.0,6.0,0.0,0.0,1.0],[20.656689076322607,35.764754202922965,0.0,7.0,0.0,1.0,1.0],[35.764754202922965,36.268356373809645,890.0,7.0,8.0,4.0,-1.0],[36.268356373809645,46.8440019624299,1860.0,6.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C540" t="n">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>[[-6.945689090104867,20.737775993827807,-1860.0,6.0,0.0,0.0,1.0],[20.737775993827807,36.70900584994281,0.0,6.0,0.0,1.0,1.0],[36.70900584994281,37.24138017847997,890.0,6.0,8.0,4.0,-1.0],[37.24138017847997,45.75936943507464,1860.0,6.0,8.0,4.0,-1.0]]</t>
+          <t>[[-6.945689090104867,20.737775993827807,-1860.0,5.0,0.0,0.0,1.0],[20.737775993827807,36.70900584994281,0.0,4.0,0.0,1.0,1.0],[36.70900584994281,37.24138017847997,890.0,4.0,8.0,4.0,-1.0],[37.24138017847997,45.75936943507464,1860.0,6.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C541" t="n">
@@ -12891,7 +12891,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>[[-11.39848926879086,21.134509917775084,-1860.0,5.0,0.0,0.0,1.0],[21.134509917775084,36.544877953516846,0.0,5.0,0.0,1.0,1.0],[36.544877953516846,45.106193528928934,1860.0,5.0,8.0,3.0,-1.0]]</t>
+          <t>[[-11.39848926879086,21.134509917775084,-1860.0,4.0,0.0,0.0,1.0],[21.134509917775084,36.544877953516846,0.0,4.0,0.0,1.0,1.0],[36.544877953516846,45.106193528928934,1860.0,5.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C542" t="n">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>[[-14.292704665772625,21.431522159172808,-1860.0,4.0,0.0,0.0,1.0],[21.431522159172808,36.31661666956674,0.0,4.0,0.0,1.0,1.0],[36.31661666956674,36.9120204499825,890.0,4.0,8.0,4.0,-1.0],[36.9120204499825,44.65226959538734,1860.0,4.0,8.0,4.0,-1.0]]</t>
+          <t>[[-14.292704665772625,21.431522159172808,-1860.0,3.0,0.0,0.0,1.0],[21.431522159172808,36.31661666956674,0.0,3.0,0.0,1.0,1.0],[36.31661666956674,36.9120204499825,890.0,3.0,8.0,4.0,-1.0],[36.9120204499825,44.65226959538734,1860.0,3.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -12937,7 +12937,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>[[-14.821895666685798,21.07748771183696,-1860.0,3.0,0.0,0.0,1.0],[21.07748771183696,36.633887175863485,0.0,3.0,0.0,1.0,1.0],[36.633887175863485,37.830533288480915,1678.65,4.0,0.0,0.0,1.0],[37.830533288480915,44.412086907876756,1860.0,4.0,9.0,2.0,-1.0]]</t>
+          <t>[[-14.821895666685798,21.07748771183696,-1860.0,3.0,0.0,0.0,1.0],[21.07748771183696,36.633887175863485,0.0,2.0,0.0,1.0,1.0],[36.633887175863485,37.830533288480915,1678.65,3.0,0.0,0.0,1.0],[37.830533288480915,44.412086907876756,1860.0,3.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C544" t="n">
@@ -12960,7 +12960,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>[[-15.800245108512707,22.319923039660644,-1860.0,2.0,0.0,0.0,1.0],[22.319923039660644,36.9326541631271,0.0,2.0,0.0,1.0,1.0],[36.9326541631271,37.567990298929985,890.0,2.0,8.0,4.0,-1.0],[37.567990298929985,47.09803233597332,1860.0,2.0,8.0,4.0,-1.0]]</t>
+          <t>[[-15.800245108512707,22.319923039660644,-1860.0,2.0,0.0,0.0,1.0],[22.319923039660644,36.9326541631271,0.0,2.0,0.0,1.0,1.0],[36.9326541631271,37.567990298929985,890.0,1.0,8.0,4.0,-1.0],[37.567990298929985,47.09803233597332,1860.0,1.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C545" t="n">
@@ -12983,7 +12983,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>[[-14.74384651414167,18.903274861010285,-1860.0,1.0,0.0,0.0,1.0],[18.903274861010285,20.772559381852066,-1860.0,0.0,0.0,0.0,1.0],[20.772559381852066,23.264938742974433,0.0,0.0,0.0,1.0,1.0],[23.264938742974433,36.97302522914745,0.0,1.0,0.0,1.0,1.0],[36.97302522914745,46.94254267363692,1860.0,1.0,8.0,2.0,-1.0]]</t>
+          <t>[[-14.74384651414167,20.772559381852066,-1860.0,1.0,0.0,0.0,1.0],[20.772559381852066,30.742076826341535,0.0,1.0,0.0,1.0,1.0],[30.742076826341535,36.97302522914745,0.0,0.0,0.0,1.0,1.0],[36.97302522914745,46.94254267363692,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>[[-14.12082405334311,28.901135585017197,-1860.0,1.0,8.0,0.0,-1.0],[28.901135585017197,33.08382610541334,-1074.7922,0.0,8.0,0.0,-1.0],[33.08382610541334,36.66898940861003,0.0,0.0,7.0,1.0,-1.0],[36.66898940861003,37.26651662580947,890.0,0.0,7.0,0.0,-1.0],[37.26651662580947,45.0343704494023,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-14.12082405334311,28.901135585017197,-1860.0,1.0,8.0,0.0,-1.0],[28.901135585017197,33.08382610541334,-1074.7923,0.0,8.0,0.0,-1.0],[33.08382610541334,36.66898940861003,0.0,0.0,7.0,1.0,-1.0],[36.66898940861003,37.26651662580947,890.0,0.0,7.0,0.0,-1.0],[37.26651662580947,45.0343704494023,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C551" t="n">
@@ -13121,7 +13121,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>[[-14.23646373709396,26.961725408764313,-1860.0,1.0,7.0,0.0,-1.0],[26.961725408764313,36.51492868896334,0.0,0.0,7.0,1.0,-1.0],[36.51492868896334,44.873981559137476,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[-14.23646373709396,26.961725408764313,-1860.0,1.0,7.0,0.0,-1.0],[26.961725408764313,36.51492868896334,0.0,0.0,7.0,1.0,-1.0],[36.51492868896334,44.873981559137476,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C552" t="n">
@@ -13144,7 +13144,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>[[-14.952068224539028,27.02830181960754,-1860.0,1.0,6.0,0.0,-1.0],[27.02830181960754,35.29716258587884,0.0,0.0,6.0,1.0,-1.0],[35.29716258587884,48.018486841680826,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[-14.952068224539028,27.02830181960754,-1860.0,1.0,6.0,0.0,-1.0],[27.02830181960754,35.29716258587884,0.0,0.0,6.0,1.0,-1.0],[35.29716258587884,48.018486841680826,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C553" t="n">
@@ -13167,7 +13167,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>[[-14.795484139741667,26.930122698168134,-1860.0,1.0,5.0,0.0,-1.0],[26.930122698168134,36.7479125423822,0.0,0.0,5.0,1.0,-1.0],[36.7479125423822,45.9520905213329,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-14.795484139741667,26.930122698168134,-1860.0,1.0,5.0,0.0,-1.0],[26.930122698168134,36.7479125423822,0.0,0.0,5.0,1.0,-1.0],[36.7479125423822,45.9520905213329,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C554" t="n">
@@ -13190,7 +13190,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>[[-14.081071884181647,26.556187147484586,-1860.0,1.0,4.0,0.0,-1.0],[26.556187147484586,36.86713346895214,0.0,0.0,4.0,1.0,-1.0],[36.86713346895214,45.96502728201175,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-14.081071884181647,26.556187147484586,-1860.0,1.0,4.0,0.0,-1.0],[26.556187147484586,36.86713346895214,0.0,0.0,4.0,1.0,-1.0],[36.86713346895214,45.96502728201175,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C555" t="n">
@@ -13213,7 +13213,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>[[-14.299893828677986,26.90369554479748,-1860.0,1.0,3.0,0.0,-1.0],[26.90369554479748,35.57813541289757,0.0,0.0,3.0,1.0,-1.0],[35.57813541289757,39.373202855191366,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-14.299893828677986,26.90369554479748,-1860.0,1.0,3.0,0.0,-1.0],[26.90369554479748,35.57813541289757,0.0,0.0,3.0,1.0,-1.0],[35.57813541289757,39.373202855191366,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C556" t="n">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>[[-14.694086409330586,26.662162776441107,-1860.0,1.0,2.0,0.0,-1.0],[26.662162776441107,37.40404568183636,0.0,0.0,2.0,1.0,-1.0],[37.40404568183636,38.478233972375875,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[-14.694086409330586,26.662162776441107,-1860.0,1.0,2.0,0.0,-1.0],[26.662162776441107,37.40404568183636,0.0,0.0,2.0,1.0,-1.0],[37.40404568183636,38.478233972375875,1860.0,0.0,1.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C557" t="n">
@@ -13259,7 +13259,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>[[-14.880460656356275,26.7239166758429,-1860.0,1.0,1.0,0.0,-1.0],[26.7239166758429,37.53024845044009,0.0,0.0,1.0,1.0,-1.0],[37.53024845044009,38.61088162789981,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-14.880460656356275,26.7239166758429,-1860.0,1.0,1.0,0.0,-1.0],[26.7239166758429,33.748032329331075,0.0,0.0,1.0,1.0,-1.0],[33.748032329331075,37.53024845044009,0.0,0.0,0.0,1.0,-1.0],[37.53024845044009,38.61088162789981,1860.0,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C558" t="n">
@@ -13374,7 +13374,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>[[-14.530285299219964,-0.49534455146290846,-1860.0,8.0,0.0,0.0,1.0],[-0.49534455146290846,24.455661222327414,-733.6842,8.0,0.0,0.0,1.0],[24.455661222327414,27.054724323763907,0.0,9.0,9.0,2.0,-1.0],[27.054724323763907,28.0943495643385,46.5,9.0,9.0,2.0,-1.0],[28.0943495643385,36.93116410922258,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-14.530285299219964,-0.49534455146290846,-1860.0,8.0,0.0,0.0,1.0],[-0.49534455146290846,24.455661222327414,-733.6842,8.0,0.0,0.0,1.0],[24.455661222327414,27.054724323763907,0.0,9.0,9.0,2.0,-1.0],[27.054724323763907,28.0943495643385,46.5,9.0,9.0,2.0,-1.0],[28.0943495643385,36.93116410922258,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C563" t="n">
@@ -13558,11 +13558,11 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>[[-17.621245709939604,24.49811383490921,-733.6842,0.0,0.0,0.0,1.0],[24.49811383490921,27.306071137899128,0.0,0.0,9.0,3.0,-1.0],[27.306071137899128,27.86766259849711,1725.15,2.0,9.0,1.0,-1.0],[27.86766259849711,37.97630888926083,1860.0,2.0,9.0,1.0,-1.0]]</t>
+          <t>[[-17.621245709939604,24.49811383490921,-733.6843,0.0,0.0,0.0,1.0],[24.49811383490921,27.306071137899128,0.0,0.0,9.0,3.0,-1.0],[27.306071137899128,27.86766259849711,1725.15,2.0,9.0,1.0,-1.0],[27.86766259849711,37.97630888926083,1860.0,2.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C571" t="n">
-        <v>-733.6842</v>
+        <v>-733.6843</v>
       </c>
       <c r="D571" s="4" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>[[-19.143167850157166,22.295058623737592,-1860.0,1.0,8.0,1.0,-1.0],[22.295058623737592,23.95258768269338,-1074.7922,0.0,8.0,2.0,-1.0],[23.95258768269338,26.16262642796777,0.0,0.0,7.0,3.0,-1.0],[26.16262642796777,26.715136114286363,890.0,0.0,7.0,3.0,-1.0],[26.715136114286363,35.555291095383915,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-19.143167850157166,22.295058623737592,-1860.0,1.0,8.0,1.0,-1.0],[22.295058623737592,23.95258768269338,-1074.7922,0.0,8.0,2.0,-1.0],[23.95258768269338,26.16262642796777,0.0,0.0,7.0,3.0,-1.0],[26.16262642796777,26.715136114286363,890.0001,0.0,7.0,3.0,-1.0],[26.715136114286363,35.555291095383915,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C573" t="n">
@@ -13650,7 +13650,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>[[-17.62081740897492,22.808883169583492,-1860.0,1.0,6.0,1.0,-1.0],[22.808883169583492,23.355230474699145,-1074.7922,0.0,6.0,2.0,-1.0],[23.355230474699145,26.086967000277422,0.0,0.0,5.0,3.0,-1.0],[26.086967000277422,26.633314305393075,890.0,0.0,5.0,3.0,-1.0],[26.633314305393075,36.46756579747485,1860.0,0.0,6.0,2.0,-1.0]]</t>
+          <t>[[-17.62081740897492,22.808883169583492,-1860.0,1.0,6.0,1.0,-1.0],[22.808883169583492,23.355230474699145,-1074.7922,0.0,6.0,2.0,-1.0],[23.355230474699145,26.086967000277422,0.0,0.0,5.0,3.0,-1.0],[26.086967000277422,26.633314305393075,890.0001,0.0,5.0,3.0,-1.0],[26.633314305393075,36.46756579747485,1860.0,0.0,6.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C575" t="n">
@@ -13696,7 +13696,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>[[-17.212868878855527,22.451366393779875,-1860.0,1.0,4.0,1.0,-1.0],[22.451366393779875,24.08140345977859,-1074.7922,0.0,4.0,2.0,-1.0],[24.08140345977859,26.79813190310978,0.0,0.0,3.0,3.0,-1.0],[26.79813190310978,36.57835429910207,1860.0,0.0,3.0,3.0,-1.0]]</t>
+          <t>[[-17.212868878855527,22.451366393779875,-1860.0,0.0,4.0,1.0,-1.0],[22.451366393779875,24.08140345977859,-1074.7922,0.0,4.0,2.0,-1.0],[24.08140345977859,26.79813190310978,0.0,0.0,3.0,3.0,-1.0],[26.79813190310978,36.57835429910207,1860.0,0.0,3.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C577" t="n">
@@ -13719,7 +13719,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>[[-17.920124183740267,23.327523859970636,-1860.0,1.0,3.0,1.0,-1.0],[23.327523859970636,23.824483474955105,-1074.7922,0.0,3.0,2.0,-1.0],[23.824483474955105,26.30928154987745,0.0,0.0,2.0,3.0,-1.0],[26.30928154987745,28.297120009815327,890.0,0.0,2.0,3.0,-1.0],[28.297120009815327,31.27887769972213,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[-17.920124183740267,23.327523859970636,-1860.0,1.0,3.0,1.0,-1.0],[23.327523859970636,23.824483474955105,-1074.7922,0.0,3.0,2.0,-1.0],[23.824483474955105,26.30928154987745,0.0,0.0,2.0,3.0,-1.0],[26.30928154987745,28.297120009815327,890.0001,0.0,2.0,3.0,-1.0],[28.297120009815327,31.27887769972213,1860.0,0.0,3.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C578" t="n">
@@ -13742,7 +13742,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>[[-18.453038871129028,22.97451571834117,-1860.0,1.0,3.0,0.0,-1.0],[22.97451571834117,23.473642882069722,-1074.7922,0.0,3.0,1.0,-1.0],[23.473642882069722,25.96927870071251,0.0,0.0,2.0,2.0,-1.0],[25.96927870071251,28.464914519355293,890.0,0.0,2.0,2.0,-1.0],[28.464914519355293,30.960550337998075,1860.0,0.0,3.0,1.0,-1.0]]</t>
+          <t>[[-18.453038871129028,22.97451571834117,-1860.0,1.0,3.0,0.0,-1.0],[22.97451571834117,23.473642882069722,-1074.7922,0.0,3.0,1.0,-1.0],[23.473642882069722,25.96927870071251,0.0,0.0,2.0,2.0,-1.0],[25.96927870071251,28.464914519355293,890.0001,0.0,2.0,2.0,-1.0],[28.464914519355293,30.960550337998075,1860.0,0.0,3.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C579" t="n">
@@ -13765,7 +13765,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>[[-18.33661349057718,20.188767897113728,-1860.0,1.0,3.0,0.0,-1.0],[20.188767897113728,23.69107529599472,-1074.7922,0.0,3.0,0.0,-1.0],[23.69107529599472,26.192723438052575,0.0,0.0,2.0,1.0,-1.0],[26.192723438052575,29.194701208521998,890.0,0.0,2.0,1.0,-1.0],[29.194701208521998,31.196019722168277,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-18.33661349057718,20.188767897113728,-1860.0,1.0,3.0,0.0,-1.0],[20.188767897113728,23.69107529599472,-1074.7922,0.0,3.0,0.0,-1.0],[23.69107529599472,26.192723438052575,0.0,0.0,2.0,1.0,-1.0],[26.192723438052575,29.194701208521998,890.0001,0.0,2.0,1.0,-1.0],[29.194701208521998,31.196019722168277,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C580" t="n">
@@ -13788,11 +13788,11 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>[[-17.325188007870292,-4.345116533696082,-1860.0,10.0,3.0,0.0,1.0],[-4.345116533696082,21.13428302671996,-1074.7922,0.0,3.0,0.0,-1.0],[21.13428302671996,23.53799996638185,0.0,0.0,2.0,1.0,-1.0],[23.53799996638185,29.787664009502766,890.0,0.0,2.0,0.0,-1.0],[29.787664009502766,30.268407397435148,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-17.325188007870292,-3.864373145763704,-1860.0,1.0,3.0,0.0,-1.0],[-3.864373145763704,21.13428302671996,-1074.7922,0.0,3.0,0.0,-1.0],[21.13428302671996,23.53799996638185,0.0,0.0,2.0,1.0,-1.0],[23.53799996638185,29.787664009502766,890.0001,0.0,2.0,0.0,-1.0],[29.787664009502766,30.268407397435148,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C581" t="n">
-        <v>890</v>
+        <v>890.0001</v>
       </c>
       <c r="D581" s="4" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
       </c>
       <c r="E581" s="4" t="inlineStr">
         <is>
-          <t>[0.2727272727,0,0.5353535354,0.0505050505,0,0.1313131313,0.0101010101,0]</t>
+          <t>[0.2828282828,0,0.5252525253,0.0505050505,0,0.1313131313,0.0101010101,0]</t>
         </is>
       </c>
     </row>
@@ -13811,7 +13811,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>[[-17.656335934047352,-4.702199129227216,-1860.0,10.0,2.0,0.0,1.0],[-4.702199129227216,-4.203963098272595,-934.626,9.0,2.0,0.0,1.0],[-4.203963098272595,24.19549066614078,0.0,0.0,2.0,1.0,-1.0],[24.19549066614078,31.669031130460088,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-17.656335934047352,-4.203963098272595,-1860.0,1.0,2.0,0.0,-1.0],[-4.203963098272595,24.19549066614078,0.0,0.0,2.0,1.0,-1.0],[24.19549066614078,31.669031130460088,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C582" t="n">
@@ -13824,7 +13824,7 @@
       </c>
       <c r="E582" s="4" t="inlineStr">
         <is>
-          <t>[0.2626262626,0.0101010101,0,0.5757575758,0,0,0.1515151515,0]</t>
+          <t>[0.2727272727,0,0,0.5757575758,0,0,0.1515151515,0]</t>
         </is>
       </c>
     </row>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>[[-18.4914812858837,-4.953106608294783,-1860.0,10.0,1.0,0.0,1.0],[-4.953106608294783,-4.4695932269523215,-934.626,9.0,1.0,0.0,1.0],[-4.4695932269523215,24.057696272252898,0.0,0.0,1.0,1.0,-1.0],[24.057696272252898,29.37634346701997,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-18.4914812858837,-4.4695932269523215,-1860.0,10.0,1.0,0.0,1.0],[-4.4695932269523215,21.640129365540595,0.0,0.0,1.0,1.0,-1.0],[21.640129365540595,24.057696272252898,0.0,0.0,0.0,1.0,-1.0],[24.057696272252898,26.95877656030767,1860.0,0.0,0.0,0.0,-1.0],[26.95877656030767,29.37634346701997,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C583" t="n">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="E583" s="4" t="inlineStr">
         <is>
-          <t>[0.2828282828,0.0101010101,0,0.595959596,0,0,0.1111111111,0]</t>
+          <t>[0.2929292929,0,0,0.595959596,0,0,0.1111111111,0]</t>
         </is>
       </c>
     </row>
@@ -13857,7 +13857,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>[[-17.992717946082532,-10.47895952316101,-1860.0,9.0,1.0,0.0,1.0],[-10.47895952316101,-4.733144258573962,-733.6842,9.0,1.0,0.0,1.0],[-4.733144258573962,-4.291158468990343,181.35,9.0,0.0,0.0,1.0],[-4.291158468990343,-3.849172679406724,1016.5,9.0,0.0,0.0,1.0],[-3.849172679406724,25.763875222695745,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-17.992717946082532,-10.47895952316101,-1860.0,9.0,1.0,0.0,1.0],[-10.47895952316101,-4.291158468990343,-733.6842,9.0,1.0,0.0,1.0],[-4.291158468990343,-0.31328636273777377,1860.0,0.0,0.0,0.0,-1.0],[-0.31328636273777377,25.763875222695745,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C584" t="n">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="E584" s="4" t="inlineStr">
         <is>
-          <t>[0.1717171717,0.1313131313,0,0,0.0202020202,0,0.6767676768,0]</t>
+          <t>[0.1717171717,0.1414141414,0,0,0,0,0.6868686869,0]</t>
         </is>
       </c>
     </row>
@@ -13926,7 +13926,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>[[-17.541201200501405,-3.9120485460436196,-1860.0,8.0,0.0,0.0,1.0],[-3.9120485460436196,15.872205307201554,-733.6842,8.0,0.0,0.0,1.0],[15.872205307201554,17.630805649712237,0.0,8.0,8.0,3.0,-1.0],[17.630805649712237,18.949755906595243,227.85,8.0,8.0,1.0,-1.0],[18.949755906595243,25.984157276637976,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-17.541201200501405,-3.9120485460436196,-1860.0,8.0,0.0,0.0,1.0],[-3.9120485460436196,15.872205307201554,-733.6842,8.0,0.0,0.0,1.0],[15.872205307201554,17.630805649712237,0.0,8.0,8.0,3.0,-1.0],[17.630805649712237,18.949755906595243,227.85,8.0,8.0,1.0,-1.0],[18.949755906595243,25.984157276637976,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C587" t="n">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>[[-14.60846950085199,15.801729690813085,-1860.0,2.0,9.0,0.0,-1.0],[15.801729690813085,16.21267832853829,-1808.4764,1.0,9.0,1.0,-1.0],[16.21267832853829,17.445524241713905,-1607.5346,0.0,8.0,1.0,-1.0],[17.445524241713905,19.500267430339925,0.0,0.0,8.0,1.0,-1.0],[19.500267430339925,19.911216068065123,227.85,1.0,8.0,0.0,-1.0],[19.911216068065123,26.075445633943183,1860.0,1.0,8.0,0.0,-1.0]]</t>
+          <t>[[-14.60846950085199,15.801729690813085,-1860.0,2.0,9.0,0.0,-1.0],[15.801729690813085,16.21267832853829,-1808.4765,1.0,9.0,1.0,-1.0],[16.21267832853829,17.445524241713905,-1607.5347,0.0,8.0,1.0,-1.0],[17.445524241713905,19.500267430339925,0.0,0.0,8.0,1.0,-1.0],[19.500267430339925,19.911216068065123,227.85,1.0,8.0,0.0,-1.0],[19.911216068065123,26.075445633943183,1860.0,1.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C595" t="n">
@@ -14133,7 +14133,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>[[-13.089258523851058,14.852002584084783,-733.6842,0.0,0.0,0.0,1.0],[14.852002584084783,16.44864607596683,0.0,0.0,9.0,1.0,-1.0],[16.44864607596683,18.44445044081939,46.5,1.0,9.0,0.0,-1.0],[18.44445044081939,20.440254805671948,227.85,0.0,8.0,0.0,-1.0],[20.440254805671948,26.42766790022963,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-13.089258523851058,14.852002584084783,-733.6844,0.0,0.0,0.0,1.0],[14.852002584084783,16.44864607596683,0.0,0.0,9.0,1.0,-1.0],[16.44864607596683,18.44445044081939,46.5,1.0,9.0,0.0,-1.0],[18.44445044081939,20.440254805671948,227.85,0.0,8.0,0.0,-1.0],[20.440254805671948,26.42766790022963,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C596" t="n">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>[[-13.582656085878643,13.324792810262409,-785.2077,0.0,0.0,0.0,1.0],[13.324792810262409,14.931207669733517,0.0,0.0,8.0,1.0,-1.0],[14.931207669733517,16.537622529204626,181.35,0.0,8.0,1.0,-1.0],[16.537622529204626,26.17611168603127,1860.0,0.0,9.0,0.0,-1.0]]</t>
+          <t>[[-13.582656085878643,13.324792810262409,-785.2079,0.0,0.0,0.0,1.0],[13.324792810262409,14.931207669733517,0.0,0.0,8.0,1.0,-1.0],[14.931207669733517,16.537622529204626,181.35,0.0,8.0,1.0,-1.0],[16.537622529204626,26.17611168603127,1860.0,1.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C597" t="n">
@@ -14179,7 +14179,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>[[-14.065811190081442,12.98551863422074,-1860.0,1.0,8.0,0.0,-1.0],[12.98551863422074,14.703063384970084,0.0,0.0,7.0,1.0,-1.0],[14.703063384970084,16.420608135719426,181.35,0.0,7.0,1.0,-1.0],[16.420608135719426,28.443421390964843,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-14.065811190081442,12.98551863422074,-1860.0,1.0,7.0,0.0,-1.0],[12.98551863422074,14.703063384970084,0.0,0.0,7.0,1.0,-1.0],[14.703063384970084,16.420608135719426,181.35,0.0,7.0,1.0,-1.0],[16.420608135719426,28.443421390964843,1860.0,1.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C598" t="n">
@@ -14202,7 +14202,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>[[-13.638813213151954,13.116121458189317,-1860.0,1.0,7.0,0.0,-1.0],[13.116121458189317,14.549421529868313,0.0,0.0,6.0,1.0,-1.0],[14.549421529868313,15.98272160154731,181.35,0.0,6.0,1.0,-1.0],[15.98272160154731,33.66008915225493,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-13.638813213151954,13.116121458189317,-1860.0,1.0,7.0,0.0,-1.0],[13.116121458189317,14.549421529868313,0.0,0.0,6.0,1.0,-1.0],[14.549421529868313,15.98272160154731,181.35,0.0,6.0,1.0,-1.0],[15.98272160154731,33.66008915225493,1860.0,1.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C599" t="n">
@@ -14225,7 +14225,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>[[-13.943712320387379,13.713081043081251,-1860.0,1.0,6.0,0.0,-1.0],[13.713081043081251,15.19469497326707,0.0,0.0,5.0,1.0,-1.0],[15.19469497326707,16.67630890345289,181.35,0.0,5.0,1.0,-1.0],[16.67630890345289,34.949547375744665,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[-13.943712320387379,13.713081043081251,-1860.0,1.0,6.0,0.0,-1.0],[13.713081043081251,15.19469497326707,0.0,0.0,5.0,1.0,-1.0],[15.19469497326707,16.67630890345289,181.35,0.0,5.0,1.0,-1.0],[16.67630890345289,34.949547375744665,1860.0,1.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C600" t="n">
@@ -14248,7 +14248,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>[[-13.458419018136013,13.489774983372822,-1860.0,1.0,5.0,0.0,-1.0],[13.489774983372822,14.933428233453654,0.0,0.0,4.0,1.0,-1.0],[14.933428233453654,16.377081483534486,181.35,0.0,4.0,1.0,-1.0],[16.377081483534486,34.18213823453139,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-13.458419018136013,13.489774983372822,-1860.0,1.0,5.0,0.0,-1.0],[13.489774983372822,14.933428233453654,0.0,0.0,4.0,1.0,-1.0],[14.933428233453654,16.377081483534486,181.35,0.0,4.0,1.0,-1.0],[16.377081483534486,34.18213823453139,1860.0,1.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C601" t="n">
@@ -14271,7 +14271,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>[[-13.1795604552901,13.627744745986098,-1860.0,1.0,4.0,0.0,-1.0],[13.627744745986098,15.014329497776243,0.0,0.0,3.0,1.0,-1.0],[15.014329497776243,16.863109166829773,181.35,0.0,3.0,1.0,-1.0],[16.863109166829773,32.577736353784786,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-13.1795604552901,13.627744745986098,-1860.0,1.0,4.0,0.0,-1.0],[13.627744745986098,15.014329497776243,0.0,0.0,3.0,1.0,-1.0],[15.014329497776243,16.863109166829773,181.35,0.0,3.0,1.0,-1.0],[16.863109166829773,32.577736353784786,1860.0,1.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C602" t="n">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>[[-13.491455190456973,13.044121775419748,-1860.0,1.0,3.0,0.0,-1.0],[13.044121775419748,14.93952013012523,0.0,0.0,2.0,1.0,-1.0],[14.93952013012523,16.361068896154343,181.35,0.0,2.0,1.0,-1.0],[16.361068896154343,33.41965408850366,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-13.491455190456973,13.044121775419748,-1860.0,1.0,2.0,0.0,-1.0],[13.044121775419748,14.93952013012523,0.0,0.0,2.0,1.0,-1.0],[14.93952013012523,16.361068896154343,181.35,0.0,2.0,1.0,-1.0],[16.361068896154343,33.41965408850366,1860.0,1.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C603" t="n">
@@ -14317,7 +14317,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>[[-13.798500505043743,13.636940747544651,-1860.0,1.0,2.0,0.0,-1.0],[13.636940747544651,15.080911339786143,0.0,0.0,1.0,1.0,-1.0],[15.080911339786143,17.0062054627748,181.35,0.0,1.0,1.0,-1.0],[17.0062054627748,33.852529038925574,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-13.798500505043743,13.155617216797486,-1860.0,1.0,2.0,0.0,-1.0],[13.155617216797486,13.636940747544651,-1860.0,1.0,1.0,0.0,-1.0],[13.636940747544651,15.080911339786143,0.0,0.0,1.0,1.0,-1.0],[15.080911339786143,17.0062054627748,181.35,0.0,1.0,1.0,-1.0],[17.0062054627748,33.852529038925574,1860.0,1.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C604" t="n">
@@ -14340,7 +14340,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>[[-13.09164031997929,11.850995537604339,-1860.0,1.0,1.0,0.0,-1.0],[11.850995537604339,16.167990205263045,-1860.0,0.0,1.0,0.0,-1.0],[16.167990205263045,18.086654502000243,0.0,0.0,0.0,1.0,-1.0],[18.086654502000243,34.39530102426646,181.35,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-13.09164031997929,16.167990205263045,-1860.0,1.0,0.0,0.0,-1.0],[16.167990205263045,18.086654502000243,0.0,0.0,0.0,1.0,-1.0],[18.086654502000243,34.39530102426646,181.35,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C605" t="n">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>[[-13.674291219793194,12.104456180844352,-1860.0,1.0,1.0,0.0,-1.0],[12.104456180844352,14.491377236458941,0.0,0.0,1.0,1.0,-1.0],[14.491377236458941,33.58674568137564,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-13.674291219793194,12.104456180844352,-1860.0,1.0,1.0,0.0,-1.0],[12.104456180844352,13.059224603090186,0.0,0.0,1.0,1.0,-1.0],[13.059224603090186,14.491377236458941,0.0,0.0,0.0,1.0,-1.0],[14.491377236458941,33.58674568137564,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C606" t="n">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>[[-13.252081670763886,-3.6843685574201412,-1860.0,10.0,0.0,0.0,1.0],[-3.6843685574201412,34.108098240287646,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-13.252081670763886,-3.2059829017529538,-1860.0,10.0,0.0,0.0,1.0],[-3.2059829017529538,34.108098240287646,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C608" t="n">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="E608" s="4" t="inlineStr">
         <is>
-          <t>[0.202020202,0,0,0.797979798,0,0,0,0]</t>
+          <t>[0.2121212121,0,0,0.7878787879,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -14455,7 +14455,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>[[-13.04004209056855,7.333007074773429,-1860.0,8.0,0.0,0.0,1.0],[7.333007074773429,24.227730772861896,0.0,9.0,0.0,1.0,1.0],[24.227730772861896,36.15341808915964,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-13.04004209056855,7.333007074773429,-1860.0,9.0,0.0,0.0,1.0],[7.333007074773429,24.227730772861896,0.0,9.0,0.0,1.0,1.0],[24.227730772861896,36.15341808915964,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C610" t="n">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>[[-13.79743690539747,6.295463740289181,-1860.0,7.0,0.0,0.0,1.0],[6.295463740289181,25.43155959332409,0.0,8.0,0.0,1.0,1.0],[25.43155959332409,30.693985952908683,1678.65,9.0,0.0,0.0,1.0],[30.693985952908683,33.56440033086392,1860.0,9.0,9.0,1.0,-1.0]]</t>
+          <t>[[-13.79743690539747,6.295463740289181,-1860.0,8.0,0.0,0.0,1.0],[6.295463740289181,25.43155959332409,0.0,8.0,0.0,1.0,1.0],[25.43155959332409,30.693985952908683,1678.65,9.0,0.0,0.0,1.0],[30.693985952908683,33.56440033086392,1860.0,9.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C611" t="n">
@@ -14501,7 +14501,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>[[-13.477651010691503,6.5141244327980665,-1860.0,6.0,0.0,0.0,1.0],[6.5141244327980665,25.5539105694548,0.0,7.0,0.0,1.0,1.0],[25.5539105694548,29.36186779678615,1678.65,8.0,0.0,0.0,1.0],[29.36186779678615,33.645819677533915,1860.0,8.0,9.0,1.0,-1.0]]</t>
+          <t>[[-13.477651010691503,6.5141244327980665,-1860.0,7.0,0.0,0.0,1.0],[6.5141244327980665,25.5539105694548,0.0,7.0,0.0,1.0,1.0],[25.5539105694548,29.36186779678615,1678.65,8.0,0.0,0.0,1.0],[29.36186779678615,33.645819677533915,1860.0,8.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C612" t="n">
@@ -14524,7 +14524,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>[[-13.63629985442631,6.973972321648217,-1860.0,5.0,0.0,0.0,1.0],[6.973972321648217,23.270466600404824,0.0,6.0,0.0,1.0,1.0],[23.270466600404824,29.98078777401048,1678.65,7.0,0.0,0.0,1.0],[29.98078777401048,33.81525701607086,1860.0,7.0,9.0,1.0,-1.0]]</t>
+          <t>[[-13.63629985442631,6.973972321648217,-1860.0,6.0,0.0,0.0,1.0],[6.973972321648217,23.270466600404824,0.0,6.0,0.0,1.0,1.0],[23.270466600404824,29.98078777401048,1678.65,7.0,0.0,0.0,1.0],[29.98078777401048,33.81525701607086,1860.0,7.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C613" t="n">
@@ -14547,7 +14547,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>[[-12.677717925832917,6.72792425719083,-1860.0,4.0,0.0,0.0,1.0],[6.72792425719083,24.28541004183137,0.0,5.0,0.0,1.0,1.0],[24.28541004183137,29.829879236981007,1678.65,6.0,0.0,0.0,1.0],[29.829879236981007,33.064152934151636,1860.0,6.0,9.0,1.0,-1.0]]</t>
+          <t>[[-12.677717925832917,6.72792425719083,-1860.0,5.0,0.0,0.0,1.0],[6.72792425719083,24.28541004183137,0.0,5.0,0.0,1.0,1.0],[24.28541004183137,29.829879236981007,1678.65,6.0,0.0,0.0,1.0],[29.829879236981007,33.064152934151636,1860.0,6.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C614" t="n">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>[[-4.872993494586886,6.501520124567865,-1860.0,2.0,0.0,0.0,1.0],[6.501520124567865,23.75940285707852,0.0,2.0,0.0,1.0,1.0],[23.75940285707852,30.819445793105608,1678.65,3.0,0.0,0.0,1.0],[30.819445793105608,33.95724265356209,1860.0,3.0,9.0,1.0,-1.0]]</t>
+          <t>[[-4.872993494586886,6.501520124567865,-1860.0,2.0,0.0,0.0,1.0],[6.501520124567865,23.75940285707852,0.0,2.0,0.0,1.0,1.0],[23.75940285707852,30.819445793105608,1678.65,3.0,0.0,0.0,1.0],[30.819445793105608,33.95724265356209,1860.0,2.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C617" t="n">
@@ -14639,7 +14639,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>[[-4.881552307742827,6.067825225044898,-1860.0,1.0,0.0,0.0,1.0],[6.067825225044898,6.849923620244021,-1860.0,0.0,0.0,0.0,1.0],[6.849923620244021,7.632022015443144,0.0,0.0,0.0,1.0,1.0],[7.632022015443144,24.05608831462473,0.0,1.0,0.0,1.0,1.0],[24.05608831462473,29.921826278618152,1678.65,2.0,0.0,0.0,1.0],[29.921826278618152,33.83231825461377,1860.0,2.0,9.0,1.0,-1.0]]</t>
+          <t>[[-4.881552307742827,6.849923620244021,-1860.0,1.0,0.0,0.0,1.0],[6.849923620244021,19.36349794342999,0.0,1.0,0.0,1.0,1.0],[19.36349794342999,24.05608831462473,0.0,0.0,0.0,1.0,1.0],[24.05608831462473,29.921826278618152,1678.65,1.0,0.0,0.0,1.0],[29.921826278618152,33.83231825461377,1860.0,0.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C618" t="n">
@@ -14662,7 +14662,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>[[4.830693769807795,23.767145310053905,0.0,0.0,0.0,1.0,1.0],[23.767145310053905,29.778717227592352,1678.65,1.0,0.0,0.0,1.0],[29.778717227592352,34.58797476162311,1860.0,1.0,9.0,1.0,-1.0]]</t>
+          <t>[[4.830693769807795,23.767145310053905,0.0,0.0,0.0,1.0,1.0],[23.767145310053905,29.778717227592352,1678.65,0.0,0.0,0.0,1.0],[29.778717227592352,34.58797476162311,1860.0,0.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C619" t="n">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>[[4.967796904095384,24.25360834401886,-1860.0,1.0,8.0,1.0,-1.0],[24.25360834401886,27.760119514914038,-1074.7922,0.0,8.0,0.0,-1.0],[27.760119514914038,30.828316789447317,0.0,0.0,7.0,1.0,-1.0],[30.828316789447317,31.266630685809215,890.0,0.0,7.0,1.0,-1.0],[31.266630685809215,48.36087264392321,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[4.967796904095384,24.25360834401886,-1860.0,1.0,8.0,1.0,-1.0],[24.25360834401886,27.760119514914038,-1074.7923,0.0,8.0,0.0,-1.0],[27.760119514914038,30.828316789447317,0.0,0.0,7.0,1.0,-1.0],[30.828316789447317,31.266630685809215,890.0,0.0,7.0,1.0,-1.0],[31.266630685809215,48.36087264392321,1860.0,0.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C622" t="n">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>[[4.591093059070173,24.979428511129314,-1860.0,1.0,8.0,0.0,-1.0],[24.979428511129314,26.921174744658757,-1074.7922,0.0,8.0,0.0,-1.0],[26.921174744658757,29.83379409495292,0.0,0.0,7.0,1.0,-1.0],[29.83379409495292,52.64931233892387,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[4.591093059070173,24.979428511129314,-1860.0,1.0,8.0,0.0,-1.0],[24.979428511129314,26.921174744658757,-1074.7923,0.0,8.0,0.0,-1.0],[26.921174744658757,29.83379409495292,0.0,0.0,7.0,1.0,-1.0],[29.83379409495292,52.64931233892387,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C623" t="n">
@@ -14777,7 +14777,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>[[4.863091593793426,24.239072919225187,-1860.0,1.0,7.0,0.0,-1.0],[24.239072919225187,24.74896716463129,-1074.7922,0.0,7.0,1.0,-1.0],[24.74896716463129,27.808332637067878,0.0,0.0,6.0,2.0,-1.0],[27.808332637067878,30.357803864098372,890.0,0.0,6.0,0.0,-1.0],[30.357803864098372,55.34262188899722,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[4.863091593793426,24.239072919225187,-1860.0,1.0,7.0,0.0,-1.0],[24.239072919225187,24.74896716463129,-1074.7923,0.0,7.0,1.0,-1.0],[24.74896716463129,27.808332637067878,0.0,0.0,6.0,2.0,-1.0],[27.808332637067878,30.357803864098372,890.0,0.0,6.0,0.0,-1.0],[30.357803864098372,55.34262188899722,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C624" t="n">
@@ -14800,7 +14800,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>[[5.0936561679229095,24.37261782561748,-1860.0,1.0,6.0,0.0,-1.0],[24.37261782561748,24.893670843393007,-1074.7922,0.0,6.0,1.0,-1.0],[24.893670843393007,27.49893593227065,0.0,0.0,5.0,2.0,-1.0],[27.49893593227065,31.146307056699357,890.0,0.0,5.0,0.0,-1.0],[31.146307056699357,56.67790492770027,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[5.0936561679229095,24.37261782561748,-1860.0,1.0,6.0,0.0,-1.0],[24.37261782561748,24.893670843393007,-1074.7923,0.0,6.0,1.0,-1.0],[24.893670843393007,27.49893593227065,0.0,0.0,5.0,2.0,-1.0],[27.49893593227065,31.146307056699357,890.0,0.0,5.0,0.0,-1.0],[31.146307056699357,56.67790492770027,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C625" t="n">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>[[5.037254937043609,24.0029293191894,-1860.0,1.0,5.0,0.0,-1.0],[24.0029293191894,24.52975360758234,-1074.7922,0.0,5.0,0.0,-1.0],[24.52975360758234,27.16387504954703,0.0,0.0,4.0,1.0,-1.0],[27.16387504954703,30.324820779904663,890.0,0.0,4.0,0.0,-1.0],[30.324820779904663,57.192859487944524,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[5.037254937043609,24.0029293191894,-1860.0,1.0,5.0,0.0,-1.0],[24.0029293191894,24.52975360758234,-1074.7923,0.0,5.0,0.0,-1.0],[24.52975360758234,27.16387504954703,0.0,0.0,4.0,1.0,-1.0],[27.16387504954703,30.324820779904663,890.0,0.0,4.0,0.0,-1.0],[30.324820779904663,57.192859487944524,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C626" t="n">
@@ -14869,7 +14869,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>[[5.0102696048923185,24.62393903975309,-1860.0,1.0,3.0,0.0,-1.0],[24.62393903975309,27.720834213678472,0.0,0.0,3.0,1.0,-1.0],[27.720834213678472,56.10903997466116,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[5.0102696048923185,24.62393903975309,-1860.0,0.0,3.0,0.0,-1.0],[24.62393903975309,27.720834213678472,0.0,0.0,2.0,1.0,-1.0],[27.720834213678472,56.10903997466116,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C628" t="n">
@@ -14892,7 +14892,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>[[4.857921714079791,24.36676019334334,-1860.0,1.0,2.0,0.0,-1.0],[24.36676019334334,27.960493597418203,0.0,0.0,2.0,2.0,-1.0],[27.960493597418203,55.6835798574243,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[4.857921714079791,24.36676019334334,-1860.0,1.0,2.0,0.0,-1.0],[24.36676019334334,27.960493597418203,0.0,0.0,1.0,2.0,-1.0],[27.960493597418203,55.6835798574243,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C629" t="n">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>[[5.008691202990625,25.15708760715045,-1860.0,1.0,1.0,0.0,-1.0],[25.15708760715045,28.179347067774426,0.0,0.0,1.0,1.0,-1.0],[28.179347067774426,54.8759723032862,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[5.008691202990625,25.15708760715045,-1860.0,1.0,1.0,0.0,-1.0],[25.15708760715045,25.660797517254448,0.0,0.0,1.0,1.0,-1.0],[25.660797517254448,28.179347067774426,0.0,0.0,0.0,1.0,-1.0],[28.179347067774426,30.697896618294404,1860.0,0.0,0.0,0.0,-1.0],[30.697896618294404,54.8759723032862,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C630" t="n">
@@ -15007,7 +15007,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>[[5.100775592433641,16.0172212623511,-1860.0,8.0,0.0,0.0,1.0],[16.0172212623511,21.97164617321517,-733.6842,8.0,0.0,0.0,1.0],[21.97164617321517,24.452656552741864,0.0,8.0,0.0,1.0,1.0],[24.452656552741864,33.384293919037965,1016.5,9.0,0.0,0.0,1.0],[33.384293919037965,54.224781107062206,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[5.100775592433641,16.0172212623511,-1860.0,7.0,0.0,0.0,1.0],[16.0172212623511,21.97164617321517,-733.6843,8.0,0.0,0.0,1.0],[21.97164617321517,24.452656552741864,0.0,7.0,0.0,1.0,1.0],[24.452656552741864,33.384293919037965,1016.5,9.0,0.0,0.0,1.0],[33.384293919037965,54.224781107062206,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C634" t="n">
@@ -15030,7 +15030,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>[[4.992893814078394,16.03823118937139,-1860.0,7.0,0.0,0.0,1.0],[16.03823118937139,22.349852546681674,-733.6842,7.0,0.0,0.0,1.0],[22.349852546681674,24.979694778894295,0.0,7.0,0.0,1.0,1.0],[24.979694778894295,34.44712681485972,1016.5,8.0,0.0,0.0,1.0],[34.44712681485972,57.06377001188824,1860.0,8.0,1.0,0.0,1.0]]</t>
+          <t>[[4.992893814078394,16.03823118937139,-1860.0,6.0,0.0,0.0,1.0],[16.03823118937139,22.349852546681674,-733.6843,6.0,0.0,0.0,1.0],[22.349852546681674,24.979694778894295,0.0,6.0,0.0,1.0,1.0],[24.979694778894295,34.44712681485972,1016.5,7.0,0.0,0.0,1.0],[34.44712681485972,57.06377001188824,1860.0,8.0,1.0,0.0,1.0]]</t>
         </is>
       </c>
       <c r="C635" t="n">
@@ -15053,7 +15053,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>[[5.024863077657301,15.319835764701056,-1860.0,6.0,0.0,0.0,1.0],[15.319835764701056,20.98207074257512,-733.6842,6.0,0.0,0.0,1.0],[20.98207074257512,23.55581391433606,0.0,6.0,0.0,1.0,1.0],[23.55581391433606,33.850786601379816,1016.5,7.0,0.0,0.0,1.0],[33.850786601379816,55.984977878523885,1860.0,7.0,1.0,0.0,1.0]]</t>
+          <t>[[5.024863077657301,15.319835764701056,-1860.0,5.0,0.0,0.0,1.0],[15.319835764701056,20.98207074257512,-733.6843,5.0,0.0,0.0,1.0],[20.98207074257512,23.55581391433606,0.0,5.0,0.0,1.0,1.0],[23.55581391433606,33.850786601379816,1016.5,6.0,0.0,0.0,1.0],[33.850786601379816,55.984977878523885,1860.0,6.0,1.0,0.0,1.0]]</t>
         </is>
       </c>
       <c r="C636" t="n">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>[[5.075011052085991,15.038088377698118,-1860.0,5.0,0.0,0.0,1.0],[15.038088377698118,21.8549307583801,-733.6842,5.0,0.0,0.0,1.0],[21.8549307583801,24.476793212488555,0.0,5.0,0.0,1.0,1.0],[24.476793212488555,32.342380574813916,1016.5,6.0,0.0,0.0,1.0],[32.342380574813916,56.98788764343339,1860.0,6.0,1.0,0.0,1.0]]</t>
+          <t>[[5.075011052085991,15.038088377698118,-1860.0,3.0,0.0,0.0,1.0],[15.038088377698118,21.8549307583801,-733.6843,4.0,0.0,0.0,1.0],[21.8549307583801,24.476793212488555,0.0,4.0,0.0,1.0,1.0],[24.476793212488555,32.342380574813916,1016.5,4.0,0.0,0.0,1.0],[32.342380574813916,56.98788764343339,1860.0,6.0,1.0,0.0,1.0]]</t>
         </is>
       </c>
       <c r="C637" t="n">
@@ -15099,7 +15099,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>[[5.049031821720391,16.308173777922356,-1860.0,4.0,0.0,0.0,1.0],[16.308173777922356,21.425965576195974,-733.6842,4.0,0.0,0.0,1.0],[21.425965576195974,23.47308229550542,0.0,4.0,0.0,1.0,1.0],[23.47308229550542,33.1968867122253,1016.5,5.0,0.0,0.0,1.0],[33.1968867122253,55.71517062462923,1860.0,5.0,1.0,0.0,1.0]]</t>
+          <t>[[5.049031821720391,16.308173777922356,-1860.0,3.0,0.0,0.0,1.0],[16.308173777922356,21.425965576195974,-733.6843,3.0,0.0,0.0,1.0],[21.425965576195974,23.47308229550542,0.0,3.0,0.0,1.0,1.0],[23.47308229550542,33.1968867122253,1016.5,4.0,0.0,0.0,1.0],[33.1968867122253,55.71517062462923,1860.0,4.0,1.0,0.0,1.0]]</t>
         </is>
       </c>
       <c r="C638" t="n">
@@ -15122,7 +15122,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>[[5.062513955862454,15.982296530286714,-1860.0,3.0,0.0,0.0,1.0],[15.982296530286714,21.442187817498844,-733.6842,3.0,0.0,0.0,1.0],[21.442187817498844,23.92395658441345,0.0,3.0,0.0,1.0,1.0],[23.92395658441345,32.85832414530603,1016.5,4.0,0.0,0.0,1.0],[32.85832414530603,54.20153554077163,1860.0,4.0,1.0,0.0,1.0]]</t>
+          <t>[[5.062513955862454,15.982296530286714,-1860.0,3.0,0.0,0.0,1.0],[15.982296530286714,21.442187817498844,-733.6843,2.0,0.0,0.0,1.0],[21.442187817498844,23.92395658441345,0.0,2.0,0.0,1.0,1.0],[23.92395658441345,32.85832414530603,1016.5,3.0,0.0,0.0,1.0],[32.85832414530603,54.20153554077163,1860.0,3.0,1.0,0.0,1.0]]</t>
         </is>
       </c>
       <c r="C639" t="n">
@@ -15145,7 +15145,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>[[5.149124104043402,15.561247222066516,-1860.0,2.0,0.0,0.0,1.0],[15.561247222066516,20.76730878107807,-733.6842,2.0,0.0,0.0,1.0],[20.76730878107807,22.849733404682695,0.0,2.0,0.0,1.0,1.0],[22.849733404682695,34.82367499040927,1016.5,3.0,0.0,0.0,1.0],[34.82367499040927,56.68913353825781,1860.0,3.0,1.0,0.0,1.0]]</t>
+          <t>[[5.149124104043402,15.561247222066516,-1860.0,1.0,0.0,0.0,1.0],[15.561247222066516,20.76730878107807,-733.6843,2.0,0.0,0.0,1.0],[20.76730878107807,22.849733404682695,0.0,2.0,0.0,1.0,1.0],[22.849733404682695,34.82367499040927,1016.5,2.0,0.0,0.0,1.0],[34.82367499040927,56.68913353825781,1860.0,3.0,1.0,0.0,1.0]]</t>
         </is>
       </c>
       <c r="C640" t="n">
@@ -15168,7 +15168,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>[[12.453519927190623,21.744944337543433,-1860.0,2.0,0.0,0.0,1.0],[21.744944337543433,30.1514711850055,-733.6842,2.0,0.0,0.0,1.0],[30.1514711850055,33.248612655123104,0.0,2.0,0.0,1.0,1.0],[33.248612655123104,38.557998032467566,1016.5,3.0,0.0,0.0,1.0],[38.557998032467566,56.25594929028244,1860.0,3.0,9.0,1.0,-1.0]]</t>
+          <t>[[12.453519927190623,21.744944337543433,-1860.0,1.0,0.0,0.0,1.0],[21.744944337543433,30.1514711850055,-733.6843,2.0,0.0,0.0,1.0],[30.1514711850055,33.248612655123104,0.0,2.0,0.0,1.0,1.0],[33.248612655123104,38.557998032467566,1016.5,2.0,0.0,0.0,1.0],[38.557998032467566,56.25594929028244,1860.0,3.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C641" t="n">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>[[14.359218967168415,21.612356946148715,-1860.0,1.0,0.0,0.0,1.0],[21.612356946148715,29.718805275597287,-733.6842,1.0,0.0,0.0,1.0],[29.718805275597287,33.13204667747037,0.0,1.0,0.0,1.0,1.0],[33.13204667747037,38.25190878027999,1016.5,2.0,0.0,0.0,1.0],[38.25190878027999,56.59808131534781,1860.0,2.0,9.0,1.0,-1.0]]</t>
+          <t>[[14.359218967168415,21.612356946148715,-1860.0,1.0,0.0,0.0,1.0],[21.612356946148715,29.718805275597287,-733.6843,1.0,0.0,0.0,1.0],[29.718805275597287,33.13204667747037,0.0,1.0,0.0,1.0,1.0],[33.13204667747037,38.25190878027999,1016.5,2.0,0.0,0.0,1.0],[38.25190878027999,56.59808131534781,1860.0,2.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C642" t="n">
@@ -15214,11 +15214,11 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>[[15.468694675348974,30.718274688690588,-733.6842,0.0,0.0,0.0,1.0],[30.718274688690588,34.33001732342939,0.0,0.0,0.0,1.0,1.0],[34.33001732342939,39.94828364413419,1016.5,1.0,0.0,0.0,1.0],[39.94828364413419,55.19786365747581,1860.0,1.0,9.0,1.0,-1.0]]</t>
+          <t>[[15.468694675348974,27.909141528338186,-733.6844,0.0,0.0,0.0,1.0],[27.909141528338186,30.718274688690588,-733.6843,0.0,0.0,0.0,1.0],[30.718274688690588,34.33001732342939,0.0,0.0,0.0,1.0,1.0],[34.33001732342939,39.94828364413419,1016.5,0.0,0.0,0.0,1.0],[39.94828364413419,55.19786365747581,1860.0,1.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C643" t="n">
-        <v>-733.6842</v>
+        <v>-733.6844</v>
       </c>
       <c r="D643" s="4" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>[[15.433312970188537,39.84677261349068,-0.0,0.0,0.0,1.0,1.0],[39.84677261349068,40.26056006507207,890.0,0.0,8.0,2.0,-1.0],[40.26056006507207,56.398270676746364,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[15.433312970188537,39.84677261349068,0.0,0.0,0.0,1.0,1.0],[39.84677261349068,40.26056006507207,890.0,0.0,8.0,2.0,-1.0],[40.26056006507207,56.398270676746364,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C644" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>[[15.37756823849231,39.594717827547726,-0.0,0.0,0.0,1.0,1.0],[39.594717827547726,40.00517799007409,890.0,0.0,8.0,1.0,-1.0],[40.00517799007409,56.01312432860224,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[15.37756823849231,39.594717827547726,0.0,0.0,0.0,1.0,1.0],[39.594717827547726,40.00517799007409,890.0,0.0,8.0,1.0,-1.0],[40.00517799007409,56.01312432860224,1860.0,0.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C645" t="n">
@@ -15283,7 +15283,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>[[15.010904772646576,34.85850389486829,-1860.0,1.0,8.0,0.0,-1.0],[34.85850389486829,35.70308258092028,-1074.7922,0.0,8.0,0.0,-1.0],[35.70308258092028,39.50368666815423,0.0,0.0,7.0,1.0,-1.0],[39.50368666815423,40.34826535420621,890.0,0.0,7.0,1.0,-1.0],[40.34826535420621,56.81754973221998,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[15.010904772646576,34.85850389486829,-1860.0,1.0,8.0,0.0,-1.0],[34.85850389486829,35.70308258092028,-1074.7921,0.0,8.0,0.0,-1.0],[35.70308258092028,39.50368666815423,0.0,0.0,7.0,1.0,-1.0],[39.50368666815423,40.34826535420621,890.0001,0.0,7.0,1.0,-1.0],[40.34826535420621,56.81754973221998,1860.0,0.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C646" t="n">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>[[15.740607208219268,33.310480943479895,-1860.0,1.0,7.0,0.0,-1.0],[33.310480943479895,34.87224749772528,-1074.7922,0.0,7.0,0.0,-1.0],[34.87224749772528,38.776663883338756,0.0,0.0,6.0,1.0,-1.0],[38.776663883338756,54.39432942579264,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[15.740607208219268,33.310480943479895,-1860.0,1.0,7.0,0.0,-1.0],[33.310480943479895,34.87224749772528,-1074.7921,0.0,7.0,0.0,-1.0],[34.87224749772528,38.776663883338756,0.0,0.0,6.0,1.0,-1.0],[38.776663883338756,54.39432942579264,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C647" t="n">
@@ -15329,7 +15329,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>[[15.001412810804764,34.90126157782096,-1860.0,1.0,6.0,0.0,-1.0],[34.90126157782096,35.31584176046713,-1074.7922,0.0,6.0,0.0,-1.0],[35.31584176046713,39.461643586928844,0.0,0.0,5.0,1.0,-1.0],[39.461643586928844,56.04485089277568,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[15.001412810804764,34.90126157782096,-1860.0,1.0,6.0,0.0,-1.0],[34.90126157782096,35.31584176046713,-1074.7921,0.0,6.0,0.0,-1.0],[35.31584176046713,39.461643586928844,0.0,0.0,5.0,1.0,-1.0],[39.461643586928844,56.04485089277568,1860.0,0.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C648" t="n">
@@ -15352,7 +15352,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>[[15.093806695932079,32.88485232806318,-1860.0,1.0,5.0,0.0,-1.0],[32.88485232806318,35.31090400517196,-1074.7922,0.0,5.0,0.0,-1.0],[35.31090400517196,38.949981520835145,0.0,0.0,4.0,1.0,-1.0],[38.949981520835145,39.75866541320474,890.0,0.0,4.0,0.0,-1.0],[39.75866541320474,55.12365936822706,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[15.093806695932079,32.88485232806318,-1860.0,1.0,5.0,0.0,-1.0],[32.88485232806318,35.31090400517196,-1074.7921,0.0,5.0,0.0,-1.0],[35.31090400517196,38.949981520835145,0.0,0.0,4.0,1.0,-1.0],[38.949981520835145,39.75866541320474,890.0001,0.0,4.0,0.0,-1.0],[39.75866541320474,55.12365936822706,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C649" t="n">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>[[15.081344426556138,27.67290722465218,-1860.0,1.0,5.0,0.0,-1.0],[27.67290722465218,34.14856809224443,-1074.7922,0.0,5.0,0.0,-1.0],[34.14856809224443,38.105916400217474,0.0,0.0,4.0,1.0,-1.0],[38.105916400217474,39.54495214857131,890.0,0.0,4.0,0.0,-1.0],[39.54495214857131,50.697479198313516,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[15.081344426556138,27.67290722465218,-1860.0,1.0,5.0,0.0,-1.0],[27.67290722465218,34.14856809224443,-1074.7921,0.0,5.0,0.0,-1.0],[34.14856809224443,38.105916400217474,0.0,0.0,4.0,1.0,-1.0],[38.105916400217474,39.54495214857131,890.0001,0.0,4.0,0.0,-1.0],[39.54495214857131,50.697479198313516,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C650" t="n">
@@ -15398,7 +15398,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>[[14.77468045156605,30.73523133969364,-1860.0,1.0,4.0,0.0,-1.0],[30.73523133969364,33.39532315438157,-1074.7922,0.0,4.0,0.0,-1.0],[33.39532315438157,36.72043792274149,0.0,0.0,3.0,1.0,-1.0],[36.72043792274149,39.38052973742942,890.0,0.0,3.0,0.0,-1.0],[39.38052973742942,47.6933166583292,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[14.77468045156605,30.73523133969364,-1860.0,1.0,4.0,0.0,-1.0],[30.73523133969364,33.39532315438157,-1074.7921,0.0,4.0,0.0,-1.0],[33.39532315438157,36.72043792274149,0.0,0.0,3.0,1.0,-1.0],[36.72043792274149,39.38052973742942,890.0001,0.0,3.0,0.0,-1.0],[39.38052973742942,47.6933166583292,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C651" t="n">
@@ -15421,11 +15421,11 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>[[15.751388302345143,29.827492769927723,-1860.0,1.0,3.0,0.0,-1.0],[29.827492769927723,34.519527592455255,-1074.7922,0.0,3.0,0.0,-1.0],[34.519527592455255,38.20612638158402,0.0,0.0,2.0,1.0,-1.0],[38.20612638158402,39.88185310391528,890.0,0.0,2.0,0.0,-1.0],[39.88185310391528,48.930777404504084,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[15.751388302345143,29.827492769927723,-1860.0,1.0,3.0,0.0,-1.0],[29.827492769927723,34.519527592455255,-1074.7921,0.0,3.0,0.0,-1.0],[34.519527592455255,38.20612638158402,0.0,0.0,2.0,1.0,-1.0],[38.20612638158402,39.88185310391528,890.0001,0.0,2.0,0.0,-1.0],[39.88185310391528,48.930777404504084,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C652" t="n">
-        <v>890</v>
+        <v>890.0001</v>
       </c>
       <c r="D652" s="4" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>[[15.878218514382214,30.989303834002033,-1860.0,1.0,2.0,0.0,-1.0],[30.989303834002033,36.77652799896281,-0.0,0.0,1.0,1.0,-1.0],[36.77652799896281,47.707951421666515,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[15.878218514382214,30.989303834002033,-1860.0,1.0,2.0,0.0,-1.0],[30.989303834002033,36.77652799896281,0.0,0.0,2.0,1.0,-1.0],[36.77652799896281,47.707951421666515,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C653" t="n">
@@ -15467,7 +15467,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>[[15.177786281558943,30.55278578257377,-1860.0,1.0,1.0,0.0,-1.0],[30.55278578257377,33.49693462319364,-0.0,0.0,1.0,1.0,-1.0],[33.49693462319364,37.09533876172902,0.0,0.0,0.0,1.0,-1.0],[37.09533876172902,37.42246641068678,1860.0,0.0,0.0,0.0,-1.0],[37.42246641068678,47.56342352837742,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[15.177786281558943,30.55278578257377,-1860.0,1.0,1.0,0.0,-1.0],[30.55278578257377,37.09533876172902,0.0,0.0,1.0,1.0,-1.0],[37.09533876172902,47.56342352837742,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C654" t="n">
@@ -15490,7 +15490,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>[[15.774416554386047,29.372975476177313,-1860.0,1.0,0.0,0.0,-1.0],[29.372975476177313,46.3711741284164,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[15.774416554386047,29.372975476177313,-1860.0,1.0,0.0,0.0,-1.0],[29.372975476177313,46.3711741284164,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C655" t="n">
@@ -15513,7 +15513,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>[[15.134100086077074,23.042745215831857,-1860.0,9.0,0.0,1.0,1.0],[23.042745215831857,23.651102533505302,-733.6842,9.0,0.0,1.0,1.0],[23.651102533505302,45.2477873109126,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[15.134100086077074,23.042745215831857,-1860.0,7.0,0.0,1.0,1.0],[23.042745215831857,23.651102533505302,-733.6842,9.0,0.0,1.0,1.0],[23.651102533505302,45.2477873109126,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C656" t="n">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>[[15.59322238749069,24.223458261848442,-1860.0,8.0,0.0,0.0,1.0],[24.223458261848442,28.230353489228833,-733.6842,8.0,0.0,0.0,1.0],[28.230353489228833,31.312580587213745,0.0,8.0,0.0,1.0,1.0],[31.312580587213745,35.011253104795635,1016.5,9.0,0.0,0.0,1.0],[35.011253104795635,46.10727065754133,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[15.59322238749069,24.223458261848442,-1860.0,7.0,0.0,0.0,1.0],[24.223458261848442,28.230353489228833,-733.6842,8.0,0.0,0.0,1.0],[28.230353489228833,31.312580587213745,0.0,7.0,0.0,1.0,1.0],[31.312580587213745,35.011253104795635,1016.5,9.0,0.0,0.0,1.0],[35.011253104795635,46.10727065754133,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C658" t="n">
@@ -15582,7 +15582,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>[[15.757141210793566,23.390326556607754,-1860.0,7.0,0.0,0.0,1.0],[23.390326556607754,29.191547419426534,-733.6842,7.0,0.0,0.0,1.0],[29.191547419426534,32.550148971584775,0.0,7.0,0.0,1.0,1.0],[32.550148971584775,34.68744086841275,1016.5,8.0,0.0,0.0,1.0],[34.68744086841275,35.29809569607788,1725.15,9.0,9.0,2.0,-1.0],[35.29809569607788,45.98455518021775,1860.0,9.0,9.0,2.0,-1.0]]</t>
+          <t>[[15.757141210793566,23.390326556607754,-1860.0,6.0,0.0,0.0,1.0],[23.390326556607754,29.191547419426534,-733.6842,7.0,0.0,0.0,1.0],[29.191547419426534,32.550148971584775,0.0,6.0,0.0,1.0,1.0],[32.550148971584775,34.68744086841275,1016.5,8.0,0.0,0.0,1.0],[34.68744086841275,35.29809569607788,1725.15,8.0,9.0,2.0,-1.0],[35.29809569607788,45.98455518021775,1860.0,9.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C659" t="n">
@@ -15605,7 +15605,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>[[15.412417416526957,23.307904819403745,-1860.0,6.0,0.0,0.0,1.0],[23.307904819403745,28.9005417297748,-733.6842,6.0,0.0,0.0,1.0],[28.9005417297748,32.19032814764013,0.0,6.0,0.0,1.0,1.0],[32.19032814764013,34.49317864014586,1016.5,7.0,0.0,0.0,1.0],[34.49317864014586,34.82215728193239,1725.15,8.0,9.0,2.0,-1.0],[34.82215728193239,47.9813029533937,1860.0,8.0,9.0,2.0,-1.0]]</t>
+          <t>[[15.412417416526957,23.307904819403745,-1860.0,6.0,0.0,0.0,1.0],[23.307904819403745,28.9005417297748,-733.6842,5.0,0.0,0.0,1.0],[28.9005417297748,32.19032814764013,0.0,5.0,0.0,1.0,1.0],[32.19032814764013,34.49317864014586,1016.5,7.0,0.0,0.0,1.0],[34.49317864014586,34.82215728193239,1725.15,8.0,9.0,2.0,-1.0],[34.82215728193239,47.9813029533937,1860.0,8.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C660" t="n">
@@ -15628,7 +15628,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>[[15.480965077534327,22.737637267054176,-1860.0,5.0,0.0,0.0,1.0],[22.737637267054176,28.612086182379766,-733.6842,5.0,0.0,0.0,1.0],[28.612086182379766,31.722088549316844,0.0,5.0,0.0,1.0,1.0],[31.722088549316844,34.140979279156795,1016.5,6.0,0.0,0.0,1.0],[34.140979279156795,34.832090916253925,1725.15,7.0,9.0,2.0,-1.0],[34.832090916253925,49.69099111384219,1860.0,7.0,9.0,2.0,-1.0]]</t>
+          <t>[[15.480965077534327,22.737637267054176,-1860.0,5.0,0.0,0.0,1.0],[22.737637267054176,28.612086182379766,-733.6842,4.0,0.0,0.0,1.0],[28.612086182379766,31.722088549316844,0.0,4.0,0.0,1.0,1.0],[31.722088549316844,34.140979279156795,1016.5,4.0,0.0,0.0,1.0],[34.140979279156795,34.832090916253925,1725.15,7.0,9.0,2.0,-1.0],[34.832090916253925,49.69099111384219,1860.0,7.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C661" t="n">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>[[15.301263784589397,19.08752914840641,-1860.0,4.0,0.0,0.0,1.0],[19.08752914840641,28.381089586866356,-733.6842,4.0,0.0,0.0,1.0],[28.381089586866356,31.478943066353004,0.0,4.0,0.0,1.0,1.0],[31.478943066353004,34.23259060367447,1016.5,5.0,0.0,0.0,1.0],[34.23259060367447,34.57679654583965,1725.15,6.0,9.0,2.0,-1.0],[34.57679654583965,49.37765205894252,1860.0,6.0,9.0,2.0,-1.0]]</t>
+          <t>[[15.301263784589397,19.08752914840641,-1860.0,3.0,0.0,0.0,1.0],[19.08752914840641,28.381089586866356,-733.6842,3.0,0.0,0.0,1.0],[28.381089586866356,31.478943066353004,0.0,3.0,0.0,1.0,1.0],[31.478943066353004,34.23259060367447,1016.5,4.0,0.0,0.0,1.0],[34.23259060367447,34.57679654583965,1725.15,5.0,9.0,2.0,-1.0],[34.57679654583965,49.37765205894252,1860.0,5.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C662" t="n">
@@ -15674,7 +15674,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>[[15.319409572035747,27.97448690278405,-1860.0,4.0,0.0,0.0,1.0],[27.97448690278405,35.07367662491115,-0.0,4.0,0.0,1.0,1.0],[35.07367662491115,45.87679141945238,1860.0,5.0,9.0,2.0,-1.0]]</t>
+          <t>[[15.319409572035747,27.97448690278405,-1860.0,3.0,0.0,0.0,1.0],[27.97448690278405,35.07367662491115,0.0,3.0,0.0,1.0,1.0],[35.07367662491115,45.87679141945238,1860.0,4.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C663" t="n">
@@ -15697,7 +15697,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>[[15.875033184735637,27.98434482472492,-1860.0,3.0,0.0,0.0,1.0],[27.98434482472492,34.644466226719025,-0.0,3.0,0.0,1.0,1.0],[34.644466226719025,35.249931808718486,890.0,3.0,8.0,4.0,-1.0],[35.249931808718486,45.84557949370911,1860.0,3.0,8.0,4.0,-1.0]]</t>
+          <t>[[15.875033184735637,27.98434482472492,-1860.0,1.0,0.0,0.0,1.0],[27.98434482472492,34.644466226719025,0.0,2.0,0.0,1.0,1.0],[34.644466226719025,35.249931808718486,890.0,2.0,8.0,4.0,-1.0],[35.249931808718486,45.84557949370911,1860.0,2.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C664" t="n">
@@ -15720,7 +15720,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>[[7.40668292284102,32.0729403673296,-1860.0,3.0,0.0,0.0,1.0],[32.0729403673296,32.458350639899734,-1074.7923,3.0,9.0,2.0,-1.0],[32.458350639899734,35.92704309303094,0.0,2.0,7.0,1.0,-1.0],[35.92704309303094,36.31245336560107,1071.35,2.0,7.0,1.0,-1.0],[36.31245336560107,45.56229990728429,1860.0,2.0,7.0,1.0,-1.0]]</t>
+          <t>[[7.40668292284102,32.0729403673296,-1860.0,1.0,0.0,0.0,1.0],[32.0729403673296,32.458350639899734,-1074.7922,2.0,9.0,2.0,-1.0],[32.458350639899734,35.92704309303094,0.0,2.0,7.0,1.0,-1.0],[35.92704309303094,36.31245336560107,1071.35,2.0,7.0,1.0,-1.0],[36.31245336560107,45.56229990728429,1860.0,1.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C665" t="n">
@@ -15743,7 +15743,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>[[7.342765194682687,31.577713215216676,-1860.0,2.0,0.0,0.0,1.0],[31.577713215216676,35.09568954077806,0.0,2.0,8.0,3.0,-1.0],[35.09568954077806,35.87746205756948,890.0,2.0,8.0,3.0,-1.0],[35.87746205756948,46.040504775857926,1860.0,2.0,8.0,3.0,-1.0]]</t>
+          <t>[[7.342765194682687,31.577713215216676,-1860.0,1.0,0.0,0.0,1.0],[31.577713215216676,35.09568954077806,0.0,2.0,8.0,3.0,-1.0],[35.09568954077806,35.87746205756948,890.0,2.0,8.0,3.0,-1.0],[35.87746205756948,46.040504775857926,1860.0,1.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C666" t="n">
@@ -15766,7 +15766,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>[[6.9510885856512665,31.628901835611902,-1860.0,1.0,0.0,0.0,1.0],[31.628901835611902,32.412324478467795,-1074.7923,1.0,9.0,2.0,-1.0],[32.412324478467795,35.937726371319314,0.0,1.0,8.0,3.0,-1.0],[35.937726371319314,36.32943769274726,890.0,1.0,8.0,3.0,-1.0],[36.32943769274726,45.73050940701798,1860.0,1.0,9.0,2.0,-1.0]]</t>
+          <t>[[6.9510885856512665,31.628901835611902,-1860.0,0.0,0.0,0.0,1.0],[31.628901835611902,32.412324478467795,-1074.7922,1.0,9.0,2.0,-1.0],[32.412324478467795,35.937726371319314,0.0,1.0,8.0,3.0,-1.0],[35.937726371319314,36.32943769274726,890.0,1.0,8.0,3.0,-1.0],[36.32943769274726,45.73050940701798,1860.0,1.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C667" t="n">
@@ -15789,7 +15789,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>[[7.168922608885759,34.13795349870542,-0.0,0.0,0.0,1.0,1.0],[34.13795349870542,35.382678001312485,890.0,0.0,8.0,3.0,-1.0],[35.382678001312485,48.24483119491879,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[7.168922608885759,34.13795349870542,0.0,0.0,0.0,1.0,1.0],[34.13795349870542,35.382678001312485,890.0,0.0,8.0,3.0,-1.0],[35.382678001312485,48.24483119491879,1860.0,0.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C668" t="n">
@@ -15812,7 +15812,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>[[6.937129663466531,29.632533295052465,-1860.0,1.0,8.0,2.0,-1.0],[29.632533295052465,30.037808359902215,-1074.7923,0.0,8.0,2.0,-1.0],[30.037808359902215,33.2800088787002,0.0,0.0,7.0,3.0,-1.0],[33.2800088787002,34.901109138099194,890.0,0.0,7.0,3.0,-1.0],[34.901109138099194,47.05936108359166,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[6.937129663466531,29.632533295052465,-1860.0,1.0,8.0,2.0,-1.0],[29.632533295052465,30.037808359902215,-1074.7922,0.0,8.0,2.0,-1.0],[30.037808359902215,33.2800088787002,0.0,0.0,7.0,3.0,-1.0],[33.2800088787002,34.901109138099194,890.0,0.0,7.0,3.0,-1.0],[34.901109138099194,47.05936108359166,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C669" t="n">
@@ -15835,7 +15835,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>[[7.417254319787326,28.14665665296946,-1860.0,1.0,8.0,0.0,-1.0],[28.14665665296946,29.166135456240713,-1074.7923,0.0,8.0,1.0,-1.0],[29.166135456240713,32.56439813381156,0.0,0.0,7.0,2.0,-1.0],[32.56439813381156,34.26352947259698,890.0,0.0,7.0,2.0,-1.0],[34.26352947259698,41.06005482773866,1860.0,0.0,7.0,2.0,-1.0]]</t>
+          <t>[[7.417254319787326,28.14665665296946,-1860.0,1.0,8.0,0.0,-1.0],[28.14665665296946,29.166135456240713,-1074.7922,0.0,8.0,1.0,-1.0],[29.166135456240713,32.56439813381156,0.0,0.0,7.0,2.0,-1.0],[32.56439813381156,34.26352947259698,890.0,0.0,7.0,2.0,-1.0],[34.26352947259698,41.06005482773866,1860.0,0.0,7.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C670" t="n">
@@ -15858,7 +15858,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>[[7.22917318841805,27.595961505092752,-1860.0,1.0,8.0,0.0,-1.0],[27.595961505092752,28.868885774884923,-1074.7923,0.0,8.0,1.0,-1.0],[28.868885774884923,32.05119644936534,0.0,0.0,7.0,2.0,-1.0],[32.05119644936534,32.68765858426143,890.0,0.0,7.0,1.0,-1.0],[32.68765858426143,38.734048865774234,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[7.22917318841805,27.595961505092752,-1860.0,1.0,8.0,0.0,-1.0],[27.595961505092752,28.868885774884923,-1074.7922,0.0,8.0,1.0,-1.0],[28.868885774884923,32.05119644936534,0.0,0.0,7.0,2.0,-1.0],[32.05119644936534,32.68765858426143,890.0,0.0,7.0,1.0,-1.0],[32.68765858426143,38.734048865774234,1860.0,0.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C671" t="n">
@@ -15881,7 +15881,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>[[7.07979083730359,27.449390922018026,-1860.0,1.0,7.0,0.0,-1.0],[27.449390922018026,28.139885840143936,-1074.7923,0.0,7.0,0.0,-1.0],[28.139885840143936,30.90186551264759,0.0,0.0,6.0,1.0,-1.0],[30.90186551264759,32.28285534889942,890.0,0.0,6.0,1.0,-1.0],[32.28285534889942,41.25928928453629,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[7.07979083730359,27.449390922018026,-1860.0,1.0,7.0,0.0,-1.0],[27.449390922018026,28.139885840143936,-1074.7922,0.0,7.0,0.0,-1.0],[28.139885840143936,30.90186551264759,0.0,0.0,6.0,1.0,-1.0],[30.90186551264759,32.28285534889942,890.0,0.0,6.0,1.0,-1.0],[32.28285534889942,41.25928928453629,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C672" t="n">
@@ -15927,7 +15927,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>[[6.855898764790677,27.84861379160557,-1860.0,1.0,5.0,0.0,-1.0],[27.84861379160557,28.23029951936584,-1074.7923,0.0,5.0,0.0,-1.0],[28.23029951936584,31.665471069208277,0.0,0.0,4.0,1.0,-1.0],[31.665471069208277,44.642785813057486,1860.0,0.0,4.0,1.0,-1.0]]</t>
+          <t>[[6.855898764790677,27.84861379160557,-1860.0,1.0,5.0,0.0,-1.0],[27.84861379160557,28.23029951936584,-1074.7922,0.0,5.0,0.0,-1.0],[28.23029951936584,31.665471069208277,0.0,0.0,4.0,1.0,-1.0],[31.665471069208277,44.642785813057486,1860.0,0.0,4.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C674" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>[[6.422290305579039,28.485493283549324,-1860.0,1.0,4.0,0.0,-1.0],[28.485493283549324,29.233398469243234,-1074.7923,0.0,4.0,1.0,-1.0],[29.233398469243234,32.225019212018864,0.0,0.0,3.0,2.0,-1.0],[32.225019212018864,32.59897180486582,890.0,0.0,3.0,2.0,-1.0],[32.59897180486582,43.443596997427484,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[6.422290305579039,28.485493283549324,-1860.0,1.0,4.0,0.0,-1.0],[28.485493283549324,29.233398469243234,-1074.7922,0.0,4.0,1.0,-1.0],[29.233398469243234,32.225019212018864,0.0,0.0,3.0,2.0,-1.0],[32.225019212018864,32.59897180486582,890.0,0.0,3.0,2.0,-1.0],[32.59897180486582,43.443596997427484,1860.0,0.0,3.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C675" t="n">
@@ -15973,7 +15973,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>[[7.070425708983416,28.78504312001573,-1860.0,1.0,3.0,0.0,-1.0],[28.78504312001573,29.49699778922991,-1074.7923,0.0,3.0,0.0,-1.0],[29.49699778922991,32.70079380069369,0.0,0.0,2.0,1.0,-1.0],[32.70079380069369,35.548612477550385,890.0,0.0,2.0,1.0,-1.0],[35.548612477550385,42.31218183508504,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[7.070425708983416,28.78504312001573,-1860.0,1.0,3.0,0.0,-1.0],[28.78504312001573,29.49699778922991,-1074.7922,0.0,3.0,0.0,-1.0],[29.49699778922991,32.70079380069369,0.0,0.0,2.0,1.0,-1.0],[32.70079380069369,35.548612477550385,890.0,0.0,2.0,1.0,-1.0],[35.548612477550385,42.31218183508504,1860.0,0.0,2.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C676" t="n">
@@ -15996,7 +15996,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>[[7.116012772742423,24.391889204313728,-1860.0,9.0,3.0,2.0,1.0],[24.391889204313728,25.494604721222537,-1808.4765,9.0,3.0,2.0,1.0],[25.494604721222537,29.537894949888162,-1074.7923,0.0,3.0,0.0,-1.0],[29.537894949888162,32.47846966164498,0.0,0.0,2.0,1.0,-1.0],[32.47846966164498,33.94875701752339,890.0,0.0,2.0,1.0,-1.0],[33.94875701752339,43.50562483073305,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[7.116012772742423,24.391889204313728,-1860.0,9.0,3.0,2.0,1.0],[24.391889204313728,25.494604721222537,-1808.4764,9.0,3.0,2.0,1.0],[25.494604721222537,29.537894949888162,-1074.7922,0.0,3.0,0.0,-1.0],[29.537894949888162,32.47846966164498,0.0,0.0,2.0,1.0,-1.0],[32.47846966164498,33.94875701752339,890.0,0.0,2.0,1.0,-1.0],[33.94875701752339,43.50562483073305,1860.0,0.0,2.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C677" t="n">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>[[6.815609251831358,24.449312384869366,-1860.0,10.0,2.0,0.0,1.0],[24.449312384869366,29.847384772534063,-1074.7923,0.0,2.0,0.0,-1.0],[29.847384772534063,33.08622820513288,0.0,0.0,1.0,1.0,-1.0],[33.08622820513288,37.764557607775615,890.0,0.0,1.0,0.0,-1.0],[37.764557607775615,42.44288701041835,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[6.815609251831358,24.449312384869366,-1860.0,10.0,2.0,0.0,1.0],[24.449312384869366,29.847384772534063,-1074.7922,0.0,2.0,0.0,-1.0],[29.847384772534063,33.08622820513288,0.0,0.0,1.0,1.0,-1.0],[33.08622820513288,37.764557607775615,890.0,0.0,1.0,0.0,-1.0],[37.764557607775615,42.44288701041835,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C678" t="n">
@@ -16065,11 +16065,11 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>[[6.826923434851289,23.88813063111298,-1860.0,9.0,1.0,1.0,1.0],[23.88813063111298,24.27588534011893,-1808.4765,9.0,1.0,1.0,1.0],[24.27588534011893,26.990168303160562,0.0,9.0,1.0,1.0,1.0],[26.990168303160562,27.37792301216651,46.5,10.0,1.0,0.0,1.0],[27.37792301216651,45.214639626440096,890.0,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[6.826923434851289,23.88813063111298,-1860.0,9.0,1.0,1.0,1.0],[23.88813063111298,24.27588534011893,-1808.4764,9.0,1.0,1.0,1.0],[24.27588534011893,26.990168303160562,0.0,9.0,1.0,1.0,1.0],[26.990168303160562,27.37792301216651,46.5,10.0,1.0,0.0,1.0],[27.37792301216651,45.214639626440096,890.0001,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C680" t="n">
-        <v>890</v>
+        <v>890.0001</v>
       </c>
       <c r="D680" s="4" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>[[7.224868158370898,26.004920315026013,-1860.0,9.0,0.0,1.0,1.0],[26.004920315026013,36.68377350214362,-0.0,9.0,0.0,1.0,1.0],[36.68377350214362,43.680263521289646,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[7.224868158370898,26.004920315026013,-1860.0,9.0,0.0,1.0,1.0],[26.004920315026013,36.68377350214362,0.0,9.0,0.0,1.0,1.0],[36.68377350214362,43.680263521289646,662.15,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C682" t="n">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>[[7.185375415205917,26.35311924123216,-1860.0,8.0,0.0,1.0,1.0],[26.35311924123216,35.03285229452706,-0.0,8.0,0.0,1.0,1.0],[35.03285229452706,35.75616338230164,890.0,8.0,8.0,4.0,-1.0],[35.75616338230164,42.98927426004739,1860.0,8.0,9.0,3.0,-1.0]]</t>
+          <t>[[7.185375415205917,26.35311924123216,-1860.0,8.0,0.0,1.0,1.0],[26.35311924123216,35.03285229452706,0.0,8.0,0.0,1.0,1.0],[35.03285229452706,35.75616338230164,889.9999,8.0,8.0,4.0,-1.0],[35.75616338230164,42.98927426004739,1860.0,8.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C683" t="n">
@@ -16157,7 +16157,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>[[7.121039743720916,26.710328764446032,-1860.0,7.0,0.0,1.0,1.0],[26.710328764446032,36.5049732748086,-0.0,7.0,0.0,1.0,1.0],[36.5049732748086,36.8677378863035,890.0,7.0,8.0,3.0,-1.0],[36.8677378863035,43.03473628171697,1860.0,7.0,9.0,2.0,-1.0]]</t>
+          <t>[[7.121039743720916,26.710328764446032,-1860.0,7.0,0.0,1.0,1.0],[26.710328764446032,36.5049732748086,0.0,7.0,0.0,1.0,1.0],[36.5049732748086,36.8677378863035,889.9999,7.0,8.0,3.0,-1.0],[36.8677378863035,43.03473628171697,1860.0,7.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C684" t="n">
@@ -16180,7 +16180,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>[[7.019629382299565,26.105943105379367,-1860.0,6.0,0.0,1.0,1.0],[26.105943105379367,36.412552515842464,-0.0,6.0,0.0,1.0,1.0],[36.412552515842464,37.55773133922725,890.0,6.0,8.0,4.0,-1.0],[37.55773133922725,44.81053055399757,1860.0,6.0,8.0,4.0,-1.0]]</t>
+          <t>[[7.019629382299565,26.105943105379367,-1860.0,5.0,0.0,1.0,1.0],[26.105943105379367,36.412552515842464,0.0,4.0,0.0,1.0,1.0],[36.412552515842464,37.55773133922725,889.9999,4.0,8.0,4.0,-1.0],[37.55773133922725,44.81053055399757,1860.0,5.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C685" t="n">
@@ -16203,7 +16203,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>[[5.855215861552942,24.168189152101355,-1860.0,5.0,0.0,0.0,1.0],[24.168189152101355,36.25475152386331,-0.0,5.0,0.0,1.0,1.0],[36.25475152386331,36.621010989674275,890.0,5.0,8.0,4.0,-1.0],[36.621010989674275,42.114902976838806,1860.0,5.0,9.0,3.0,-1.0]]</t>
+          <t>[[5.855215861552942,24.168189152101355,-1860.0,4.0,0.0,0.0,1.0],[24.168189152101355,36.25475152386331,0.0,4.0,0.0,1.0,1.0],[36.25475152386331,36.621010989674275,889.9999,4.0,8.0,4.0,-1.0],[36.621010989674275,42.114902976838806,1860.0,3.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C686" t="n">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>[[5.797994855764833,32.81892929969216,-1860.0,5.0,0.0,0.0,1.0],[32.81892929969216,37.4510894900797,-0.0,5.0,0.0,1.0,1.0],[37.4510894900797,44.013316426462055,1860.0,5.0,8.0,3.0,-1.0]]</t>
+          <t>[[5.797994855764833,32.81892929969216,-1860.0,4.0,0.0,0.0,1.0],[32.81892929969216,37.4510894900797,0.0,4.0,0.0,1.0,1.0],[37.4510894900797,44.013316426462055,1860.0,3.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C687" t="n">
@@ -16249,7 +16249,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>[[5.420225279167751,33.84564490494072,-1860.0,4.0,0.0,0.0,1.0],[33.84564490494072,34.235034214882816,-873.8504,3.0,8.0,3.0,-1.0],[34.235034214882816,37.73953800436168,0.0,3.0,7.0,4.0,-1.0],[37.73953800436168,43.969766963435205,1860.0,3.0,8.0,3.0,-1.0]]</t>
+          <t>[[5.420225279167751,33.84564490494072,-1860.0,3.0,0.0,0.0,1.0],[33.84564490494072,34.235034214882816,-873.8505,2.0,8.0,3.0,-1.0],[34.235034214882816,37.73953800436168,0.0,2.0,7.0,4.0,-1.0],[37.73953800436168,43.969766963435205,1860.0,2.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C688" t="n">
@@ -16272,7 +16272,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>[[5.7508207852407525,33.001741461744125,-1860.0,3.0,0.0,0.0,1.0],[33.001741461744125,36.78659155570293,0.0,2.0,7.0,4.0,-1.0],[36.78659155570293,37.92204658389057,1071.35,2.0,7.0,4.0,-1.0],[37.92204658389057,43.220836715432895,1860.0,2.0,7.0,4.0,-1.0]]</t>
+          <t>[[5.7508207852407525,33.001741461744125,-1860.0,2.0,0.0,0.0,1.0],[33.001741461744125,36.78659155570293,0.0,2.0,7.0,4.0,-1.0],[36.78659155570293,37.92204658389057,1071.3499,2.0,7.0,4.0,-1.0],[37.92204658389057,43.220836715432895,1860.0,2.0,7.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C689" t="n">
@@ -16295,7 +16295,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>[[5.964350820839753,32.520769149082675,-1860.0,2.0,0.0,0.0,1.0],[32.520769149082675,36.03558922193835,0.0,1.0,7.0,4.0,-1.0],[36.03558922193835,37.98826704019151,1071.35,1.0,7.0,1.0,-1.0],[37.98826704019151,44.62737162225224,1860.0,1.0,8.0,0.0,-1.0]]</t>
+          <t>[[5.964350820839753,32.520769149082675,-1860.0,2.0,0.0,0.0,1.0],[32.520769149082675,36.03558922193835,0.0,1.0,7.0,4.0,-1.0],[36.03558922193835,37.98826704019151,1071.3499,1.0,7.0,1.0,-1.0],[37.98826704019151,44.62737162225224,1860.0,1.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C690" t="n">
@@ -16318,7 +16318,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>[[5.752687575372794,32.6346037524853,-1860.0,1.0,0.0,0.0,1.0],[32.6346037524853,36.14094064515214,0.0,0.0,7.0,5.0,-1.0],[36.14094064515214,37.309719609374426,1071.35,0.0,7.0,5.0,-1.0],[37.309719609374426,44.32239339470812,1860.0,0.0,7.0,5.0,-1.0]]</t>
+          <t>[[5.752687575372794,32.6346037524853,-1860.0,1.0,0.0,0.0,1.0],[32.6346037524853,36.14094064515214,0.0,0.0,7.0,5.0,-1.0],[36.14094064515214,37.309719609374426,1071.3499,0.0,7.0,5.0,-1.0],[37.309719609374426,44.32239339470812,1860.0,0.0,7.0,5.0,-1.0]]</t>
         </is>
       </c>
       <c r="C691" t="n">
@@ -16341,7 +16341,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>[[6.19610098460995,37.06424312311912,-0.0,0.0,0.0,1.0,1.0],[37.06424312311912,37.43172100572042,890.0,0.0,8.0,2.0,-1.0],[37.43172100572042,42.576411362138614,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[6.19610098460995,37.06424312311912,0.0,0.0,0.0,1.0,1.0],[37.06424312311912,37.43172100572042,889.9999,0.0,8.0,2.0,-1.0],[37.43172100572042,42.576411362138614,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C692" t="n">
@@ -16364,7 +16364,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>[[5.777144260757365,35.54331894192165,-0.0,0.0,0.0,1.0,1.0],[35.54331894192165,36.023418533553325,890.0,0.0,8.0,0.0,-1.0],[36.023418533553325,53.30700383229388,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[5.777144260757365,35.54331894192165,0.0,0.0,0.0,1.0,1.0],[35.54331894192165,36.023418533553325,889.9999,0.0,8.0,0.0,-1.0],[36.023418533553325,53.30700383229388,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C693" t="n">
@@ -16410,7 +16410,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>[[5.942806062990978,31.221650593240938,-1860.0,1.0,7.0,0.0,-1.0],[31.221650593240938,31.853621706497186,-1074.7923,0.0,7.0,1.0,-1.0],[31.853621706497186,35.01347727277843,0.0,0.0,6.0,2.0,-1.0],[35.01347727277843,36.27741949929093,890.0,0.0,6.0,2.0,-1.0],[36.27741949929093,68.50794627535963,1860.0,0.0,6.0,2.0,-1.0]]</t>
+          <t>[[5.942806062990978,31.221650593240938,-1860.0,1.0,7.0,0.0,-1.0],[31.221650593240938,31.853621706497186,-1074.7923,0.0,7.0,1.0,-1.0],[31.853621706497186,35.01347727277843,0.0,0.0,6.0,2.0,-1.0],[35.01347727277843,36.27741949929093,889.9999,0.0,6.0,2.0,-1.0],[36.27741949929093,68.50794627535963,1860.0,0.0,6.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C695" t="n">
@@ -16433,7 +16433,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>[[5.644910302815902,30.8937013071726,-1860.0,1.0,6.0,0.0,-1.0],[30.8937013071726,32.04137362555245,-1074.7923,0.0,6.0,1.0,-1.0],[32.04137362555245,35.48439058069199,0.0,0.0,5.0,2.0,-1.0],[35.48439058069199,37.20589905826177,890.0,0.0,5.0,2.0,-1.0],[37.20589905826177,62.45469006261847,1860.0,0.0,5.0,2.0,-1.0]]</t>
+          <t>[[5.644910302815902,30.8937013071726,-1860.0,1.0,6.0,0.0,-1.0],[30.8937013071726,32.04137362555245,-1074.7923,0.0,6.0,1.0,-1.0],[32.04137362555245,35.48439058069199,0.0,0.0,5.0,2.0,-1.0],[35.48439058069199,37.20589905826177,889.9999,0.0,5.0,2.0,-1.0],[37.20589905826177,62.45469006261847,1860.0,0.0,5.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C696" t="n">
@@ -16479,7 +16479,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>[[5.656569383363265,31.483819955773455,-1860.0,1.0,4.0,0.0,-1.0],[31.483819955773455,32.71368903065013,-1074.7923,0.0,4.0,1.0,-1.0],[32.71368903065013,36.403296255280154,0.0,0.0,3.0,2.0,-1.0],[36.403296255280154,37.01823079271849,890.0,0.0,3.0,2.0,-1.0],[37.01823079271849,66.5350885897587,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[5.656569383363265,31.483819955773455,-1860.0,1.0,4.0,0.0,-1.0],[31.483819955773455,32.71368903065013,-1074.7923,0.0,4.0,1.0,-1.0],[32.71368903065013,36.403296255280154,0.0,0.0,3.0,2.0,-1.0],[36.403296255280154,37.01823079271849,889.9999,0.0,3.0,2.0,-1.0],[37.01823079271849,66.5350885897587,1860.0,0.0,3.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C698" t="n">
@@ -16502,7 +16502,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>[[5.949061243550825,31.691487132188282,-1860.0,10.0,11.0,2.0,0.0],[31.691487132188282,34.75606164274036,0.0,9.0,11.0,3.0,0.0],[34.75606164274036,35.368976544850774,890.0,0.0,2.0,1.0,-1.0],[35.368976544850774,66.62763655248197,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[5.949061243550825,31.691487132188282,-1860.0,10.0,11.0,2.0,0.0],[31.691487132188282,34.75606164274036,0.0,9.0,11.0,3.0,0.0],[34.75606164274036,35.368976544850774,889.9999,0.0,2.0,1.0,-1.0],[35.368976544850774,66.62763655248197,1860.0,0.0,2.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C699" t="n">
@@ -16525,7 +16525,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>[[5.9211837771289675,31.90178804470698,-1860.0,9.0,1.0,2.0,1.0],[31.90178804470698,32.50598814395298,-1607.5347,8.0,1.0,3.0,1.0],[32.50598814395298,33.110188243198984,-822.3269,9.0,10.0,4.0,0.0],[33.110188243198984,36.73538883867498,0.0,9.0,10.0,4.0,0.0],[36.73538883867498,37.94378903716698,890.0,0.0,1.0,1.0,-1.0],[37.94378903716698,65.736993602483,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[5.9211837771289675,31.90178804470698,-1860.0,9.0,1.0,2.0,1.0],[31.90178804470698,32.50598814395298,-1607.5347,8.0,1.0,3.0,1.0],[32.50598814395298,33.110188243198984,-822.327,9.0,10.0,4.0,0.0],[33.110188243198984,36.73538883867498,0.0,9.0,10.0,4.0,0.0],[36.73538883867498,37.94378903716698,889.9999,0.0,1.0,1.0,-1.0],[37.94378903716698,65.736993602483,1860.0,0.0,1.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C700" t="n">
@@ -16548,11 +16548,11 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>[[5.5820891349112465,32.32630314018349,-1860.0,9.0,2.0,0.0,1.0],[32.32630314018349,35.89219834088645,0.0,9.0,1.0,1.0,1.0],[35.89219834088645,36.48651420767028,227.85,9.0,1.0,1.0,1.0],[36.48651420767028,37.67514594123794,890.0,0.0,1.0,0.0,-1.0],[37.67514594123794,64.41935994651018,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[5.5820891349112465,32.32630314018349,-1860.0,9.0,2.0,0.0,1.0],[32.32630314018349,35.89219834088645,0.0,9.0,1.0,1.0,1.0],[35.89219834088645,36.48651420767028,227.8499,9.0,1.0,1.0,1.0],[36.48651420767028,37.67514594123794,889.9999,0.0,1.0,0.0,-1.0],[37.67514594123794,64.41935994651018,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C701" t="n">
-        <v>227.85</v>
+        <v>227.8499</v>
       </c>
       <c r="D701" s="4" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>[[5.8823909272670205,32.29880920212269,-1860.0,9.0,1.0,1.0,1.0],[32.29880920212269,36.31869893960072,0.0,9.0,0.0,1.0,1.0],[36.31869893960072,62.73511721445639,1860.0,9.0,1.0,1.0,1.0]]</t>
+          <t>[[5.8823909272670205,32.29880920212269,-1860.0,8.0,1.0,1.0,1.0],[32.29880920212269,36.31869893960072,0.0,8.0,1.0,1.0,1.0],[36.31869893960072,62.73511721445639,1860.0,9.0,1.0,1.0,1.0]]</t>
         </is>
       </c>
       <c r="C702" t="n">
@@ -16594,7 +16594,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>[[5.980859745441576,32.362751141045614,-1860.0,9.0,0.0,1.0,1.0],[32.362751141045614,38.811657926637714,-0.0,9.0,0.0,1.0,1.0],[38.811657926637714,64.02102081577047,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[5.980859745441576,32.362751141045614,-1860.0,9.0,0.0,1.0,1.0],[32.362751141045614,38.811657926637714,0.0,8.0,0.0,1.0,1.0],[38.811657926637714,64.02102081577047,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C703" t="n">
@@ -16617,7 +16617,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>[[5.551586064375953,34.682302039284565,-1860.0,9.0,0.0,0.0,1.0],[34.682302039284565,38.93053145229207,-0.0,9.0,0.0,3.0,1.0],[38.93053145229207,65.63368776262496,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[5.551586064375953,34.682302039284565,-1860.0,8.0,0.0,0.0,1.0],[34.682302039284565,38.93053145229207,0.0,8.0,0.0,3.0,1.0],[38.93053145229207,65.63368776262496,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C704" t="n">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>[[5.519737223169096,33.328697471364436,-1860.0,8.0,0.0,0.0,1.0],[33.328697471364436,39.8371775294527,-0.0,8.0,0.0,3.0,1.0],[39.8371775294527,41.0205375400142,890.0,8.0,8.0,2.0,-1.0],[41.0205375400142,64.09605774596352,1860.0,8.0,9.0,1.0,-1.0]]</t>
+          <t>[[5.519737223169096,33.328697471364436,-1860.0,6.0,0.0,0.0,1.0],[33.328697471364436,39.8371775294527,0.0,8.0,0.0,3.0,1.0],[39.8371775294527,41.0205375400142,890.0,8.0,8.0,2.0,-1.0],[41.0205375400142,64.09605774596352,1860.0,8.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C705" t="n">
@@ -16663,7 +16663,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>[[5.8738382526313515,34.02257256186337,-1860.0,7.0,0.0,0.0,1.0],[34.02257256186337,38.71402828006871,-0.0,7.0,0.0,3.0,1.0],[38.71402828006871,63.930602765422385,1860.0,7.0,8.0,2.0,-1.0]]</t>
+          <t>[[5.8738382526313515,34.02257256186337,-1860.0,5.0,0.0,0.0,1.0],[34.02257256186337,38.71402828006871,0.0,7.0,0.0,3.0,1.0],[38.71402828006871,63.930602765422385,1860.0,5.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C706" t="n">
@@ -16686,7 +16686,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>[[5.790447701973391,33.61829338027952,-1860.0,6.0,0.0,0.0,1.0],[33.61829338027952,39.53911160970635,-0.0,6.0,0.0,3.0,1.0],[39.53911160970635,40.131193432649034,890.0,6.0,8.0,3.0,-1.0],[40.131193432649034,64.40654817329906,1860.0,6.0,8.0,3.0,-1.0]]</t>
+          <t>[[5.790447701973391,33.61829338027952,-1860.0,4.0,0.0,0.0,1.0],[33.61829338027952,39.53911160970635,0.0,4.0,0.0,3.0,1.0],[39.53911160970635,40.131193432649034,890.0,5.0,8.0,3.0,-1.0],[40.131193432649034,64.40654817329906,1860.0,6.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C707" t="n">
@@ -16709,7 +16709,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>[[5.717840236276732,34.20607486027302,-1860.0,5.0,0.0,0.0,1.0],[34.20607486027302,34.82538430862077,-1074.7923,5.0,9.0,3.0,-1.0],[34.82538430862077,38.54124099870724,0.0,5.0,8.0,4.0,-1.0],[38.54124099870724,39.77985989540272,890.0,5.0,8.0,4.0,-1.0],[39.77985989540272,67.02947562270352,1860.0,5.0,8.0,4.0,-1.0]]</t>
+          <t>[[5.717840236276732,34.20607486027302,-1860.0,3.0,0.0,0.0,1.0],[34.20607486027302,34.82538430862077,-1074.7922,4.0,9.0,3.0,-1.0],[34.82538430862077,38.54124099870724,0.0,4.0,8.0,4.0,-1.0],[38.54124099870724,39.77985989540272,890.0,4.0,8.0,4.0,-1.0],[39.77985989540272,67.02947562270352,1860.0,5.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C708" t="n">
@@ -16732,7 +16732,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>[[5.59923945864782,33.54709545904373,-1860.0,4.0,0.0,0.0,1.0],[33.54709545904373,34.154657546008856,-1074.7923,4.0,9.0,3.0,-1.0],[34.154657546008856,37.80003006779963,0.0,4.0,8.0,4.0,-1.0],[37.80003006779963,38.407592154764764,890.0,4.0,8.0,1.0,-1.0],[38.407592154764764,65.74788606819554,1860.0,4.0,8.0,1.0,-1.0]]</t>
+          <t>[[5.59923945864782,33.54709545904373,-1860.0,3.0,0.0,0.0,1.0],[33.54709545904373,34.154657546008856,-1074.7922,3.0,9.0,3.0,-1.0],[34.154657546008856,37.80003006779963,0.0,3.0,8.0,4.0,-1.0],[37.80003006779963,38.407592154764764,890.0,3.0,8.0,1.0,-1.0],[38.407592154764764,65.74788606819554,1860.0,3.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C709" t="n">
@@ -16755,7 +16755,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>[[10.505498645660388,34.93527156472982,-1860.0,3.0,0.0,0.0,1.0],[34.93527156472982,39.278342305897716,0.0,3.0,0.0,3.0,1.0],[39.278342305897716,64.25099906761314,1860.0,3.0,8.0,4.0,-1.0]]</t>
+          <t>[[10.505498645660388,34.93527156472982,-1860.0,2.0,0.0,0.0,1.0],[34.93527156472982,39.278342305897716,0.0,1.0,0.0,3.0,1.0],[39.278342305897716,64.25099906761314,1860.0,2.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C710" t="n">
@@ -16778,7 +16778,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>[[17.0354249272596,34.30955869369576,-1860.0,2.0,0.0,0.0,1.0],[34.30955869369576,39.107929184372466,-0.0,2.0,0.0,3.0,1.0],[39.107929184372466,40.06760328250781,890.0,2.0,8.0,2.0,-1.0],[40.06760328250781,64.53929278495903,1860.0,2.0,8.0,2.0,-1.0]]</t>
+          <t>[[17.0354249272596,34.30955869369576,-1860.0,1.0,0.0,0.0,1.0],[34.30955869369576,39.107929184372466,0.0,1.0,0.0,3.0,1.0],[39.107929184372466,40.06760328250781,890.0,2.0,8.0,2.0,-1.0],[40.06760328250781,64.53929278495903,1860.0,2.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C711" t="n">
@@ -16801,7 +16801,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>[[16.245864004337356,34.34927316690133,-1860.0,1.0,0.0,0.0,1.0],[34.34927316690133,38.99117295217414,-0.0,1.0,0.0,3.0,1.0],[38.99117295217414,40.383742887755986,890.0,1.0,8.0,3.0,-1.0],[40.383742887755986,62.20067187853821,1860.0,1.0,8.0,3.0,-1.0]]</t>
+          <t>[[16.245864004337356,34.34927316690133,-1860.0,0.0,0.0,0.0,1.0],[34.34927316690133,35.277653123955886,0.0,1.0,0.0,3.0,1.0],[35.277653123955886,38.99117295217414,0.0,0.0,0.0,3.0,1.0],[38.99117295217414,40.383742887755986,890.0,1.0,8.0,3.0,-1.0],[40.383742887755986,62.20067187853821,1860.0,1.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C712" t="n">
@@ -16824,7 +16824,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>[[13.377518634125957,38.178981092299246,-0.0,0.0,0.0,1.0,1.0],[38.178981092299246,40.163098088953106,1678.65,1.0,0.0,1.0,1.0],[40.163098088953106,62.484414301309066,1860.0,1.0,9.0,2.0,-1.0]]</t>
+          <t>[[13.377518634125957,38.178981092299246,0.0,0.0,0.0,1.0,1.0],[38.178981092299246,40.163098088953106,1678.65,1.0,0.0,1.0,1.0],[40.163098088953106,62.484414301309066,1860.0,1.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C713" t="n">
@@ -16847,7 +16847,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>[[10.100087511346796,29.88787855184674,-1860.0,1.0,0.0,0.0,1.0],[29.88787855184674,39.2321132098606,-0.0,1.0,0.0,1.0,1.0],[39.2321132098606,64.51651287272165,1860.0,1.0,8.0,0.0,-1.0]]</t>
+          <t>[[10.100087511346796,29.88787855184674,-1860.0,0.0,0.0,0.0,1.0],[29.88787855184674,35.384487174207834,0.0,1.0,0.0,1.0,1.0],[35.384487174207834,38.13279148538838,0.0,0.0,0.0,1.0,1.0],[38.13279148538838,39.2321132098606,0.0,1.0,0.0,1.0,1.0],[39.2321132098606,64.51651287272165,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C714" t="n">
@@ -16870,7 +16870,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>[[6.038010189969462,35.23858817463015,-1860.0,1.0,0.0,0.0,1.0],[35.23858817463015,36.40661129401657,-873.8504,0.0,8.0,0.0,-1.0],[36.40661129401657,40.49469221186907,0.0,0.0,7.0,1.0,-1.0],[40.49469221186907,41.6627153312555,1071.35,0.0,7.0,0.0,-1.0],[41.6627153312555,63.855154599597626,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[6.038010189969462,35.23858817463015,-1860.0,0.0,0.0,0.0,1.0],[35.23858817463015,36.40661129401657,-873.8504,0.0,8.0,0.0,-1.0],[36.40661129401657,40.49469221186907,0.0,0.0,7.0,1.0,-1.0],[40.49469221186907,41.6627153312555,1071.35,0.0,7.0,0.0,-1.0],[41.6627153312555,63.855154599597626,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C715" t="n">
@@ -16893,7 +16893,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>[[5.9133631656834655,37.28989980832542,-0.0,0.0,0.0,1.0,1.0],[37.28989980832542,39.61408770778038,890.0,0.0,8.0,1.0,-1.0],[39.61408770778038,63.43701367719371,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[5.9133631656834655,37.28989980832542,0.0,0.0,0.0,1.0,1.0],[37.28989980832542,39.61408770778038,890.0,0.0,8.0,1.0,-1.0],[39.61408770778038,63.43701367719371,1860.0,0.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C716" t="n">
@@ -16916,7 +16916,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>[[5.8700633407018366,32.30276536943349,-1860.0,1.0,8.0,2.0,-1.0],[32.30276536943349,33.504251825284925,-1074.7923,0.0,8.0,0.0,-1.0],[33.504251825284925,37.10871119283924,0.0,0.0,7.0,1.0,-1.0],[37.10871119283924,39.51168410454211,890.0,0.0,7.0,1.0,-1.0],[39.51168410454211,65.34364290534803,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[5.8700633407018366,32.30276536943349,-1860.0,1.0,8.0,2.0,-1.0],[32.30276536943349,33.504251825284925,-1074.7922,0.0,8.0,0.0,-1.0],[33.504251825284925,37.10871119283924,0.0,0.0,7.0,1.0,-1.0],[37.10871119283924,39.51168410454211,890.0,0.0,7.0,1.0,-1.0],[39.51168410454211,65.34364290534803,1860.0,0.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C717" t="n">
@@ -16939,7 +16939,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>[[5.629739286392475,31.895303771490912,-1860.0,1.0,7.0,0.0,-1.0],[31.895303771490912,35.065285692106244,-1074.7923,0.0,7.0,0.0,-1.0],[35.065285692106244,38.68812217280947,0.0,0.0,6.0,1.0,-1.0],[38.68812217280947,39.593831292985286,890.0,0.0,6.0,1.0,-1.0],[39.593831292985286,50.46234073509498,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[5.629739286392475,31.895303771490912,-1860.0,1.0,7.0,0.0,-1.0],[31.895303771490912,35.065285692106244,-1074.7922,0.0,7.0,0.0,-1.0],[35.065285692106244,38.68812217280947,0.0,0.0,6.0,1.0,-1.0],[38.68812217280947,39.593831292985286,890.0,0.0,6.0,1.0,-1.0],[39.593831292985286,50.46234073509498,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C718" t="n">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>[[6.003789211278378,32.55206763164108,-1860.0,1.0,6.0,0.0,-1.0],[32.55206763164108,35.411112999987836,-1074.7923,0.0,6.0,0.0,-1.0],[35.411112999987836,39.08702847357652,0.0,0.0,5.0,1.0,-1.0],[39.08702847357652,41.12920373668134,890.0,0.0,5.0,1.0,-1.0],[41.12920373668134,46.43885942075388,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[6.003789211278378,32.55206763164108,-1860.0,1.0,6.0,0.0,-1.0],[32.55206763164108,35.411112999987836,-1074.7922,0.0,6.0,0.0,-1.0],[35.411112999987836,39.08702847357652,0.0,0.0,5.0,1.0,-1.0],[39.08702847357652,41.12920373668134,890.0,0.0,5.0,1.0,-1.0],[41.12920373668134,46.43885942075388,1860.0,0.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C719" t="n">
@@ -16985,7 +16985,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>[[5.538603565668832,31.641517815382105,-1860.0,1.0,6.0,1.0,-1.0],[31.641517815382105,33.19990075566349,-1074.7923,0.0,6.0,1.0,-1.0],[33.19990075566349,36.70626237129662,0.0,0.0,5.0,2.0,-1.0],[36.70626237129662,37.09585810636697,890.0,0.0,5.0,0.0,-1.0],[37.09585810636697,44.10858133763322,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[5.538603565668832,31.641517815382105,-1860.0,1.0,6.0,1.0,-1.0],[31.641517815382105,33.19990075566349,-1074.7922,0.0,6.0,1.0,-1.0],[33.19990075566349,36.70626237129662,0.0,0.0,5.0,2.0,-1.0],[36.70626237129662,37.09585810636697,890.0,0.0,5.0,0.0,-1.0],[37.09585810636697,44.10858133763322,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C720" t="n">
@@ -17008,7 +17008,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>[[6.075732337210046,31.84029389353122,-1860.0,1.0,5.0,1.0,-1.0],[31.84029389353122,32.58709277922169,-1074.7923,0.0,5.0,0.0,-1.0],[32.58709277922169,35.94768776482881,0.0,0.0,4.0,1.0,-1.0],[35.94768776482881,38.56148386474545,890.0,0.0,4.0,0.0,-1.0],[38.56148386474545,43.04227717888826,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[6.075732337210046,31.84029389353122,-1860.0,1.0,5.0,1.0,-1.0],[31.84029389353122,32.58709277922169,-1074.7922,0.0,5.0,0.0,-1.0],[32.58709277922169,35.94768776482881,0.0,0.0,4.0,1.0,-1.0],[35.94768776482881,38.56148386474545,890.0,0.0,4.0,0.0,-1.0],[38.56148386474545,43.04227717888826,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C721" t="n">
@@ -17031,7 +17031,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>[[6.323637585308626,31.845397912843964,-1860.0,1.0,4.0,0.0,-1.0],[31.845397912843964,32.19986680628195,-1074.7923,0.0,4.0,0.0,-1.0],[32.19986680628195,35.744555740661866,0.0,0.0,3.0,1.0,-1.0],[35.744555740661866,37.87136910128981,890.0,0.0,3.0,0.0,-1.0],[37.87136910128981,41.416058035669714,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[6.323637585308626,31.845397912843964,-1860.0,1.0,4.0,0.0,-1.0],[31.845397912843964,32.19986680628195,-1074.7922,0.0,4.0,0.0,-1.0],[32.19986680628195,35.744555740661866,0.0,0.0,3.0,1.0,-1.0],[35.744555740661866,37.87136910128981,890.0,0.0,3.0,0.0,-1.0],[37.87136910128981,41.416058035669714,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C722" t="n">
@@ -17054,7 +17054,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>[[5.532599802694209,32.41959273462963,-1860.0,1.0,3.0,0.0,-1.0],[32.41959273462963,32.82089113659882,-1074.7923,0.0,3.0,1.0,-1.0],[32.82089113659882,36.43257675432149,0.0,0.0,2.0,2.0,-1.0],[36.43257675432149,38.840367166136595,890.0,0.0,2.0,0.0,-1.0],[38.840367166136595,45.261141597643565,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[5.532599802694209,32.41959273462963,-1860.0,1.0,3.0,0.0,-1.0],[32.41959273462963,32.82089113659882,-1074.7922,0.0,3.0,1.0,-1.0],[32.82089113659882,36.43257675432149,0.0,0.0,2.0,2.0,-1.0],[36.43257675432149,38.840367166136595,890.0,0.0,2.0,0.0,-1.0],[38.840367166136595,45.261141597643565,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C723" t="n">
@@ -17077,7 +17077,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>[[5.807691584223856,31.43842393144155,-1860.0,1.0,2.0,1.0,-1.0],[31.43842393144155,31.809883820531663,-1074.7923,0.0,2.0,0.0,-1.0],[31.809883820531663,35.15302282234266,0.0,0.0,1.0,1.0,-1.0],[35.15302282234266,40.724921158694336,890.0,0.0,1.0,0.0,-1.0],[40.724921158694336,42.582220604144894,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[5.807691584223856,31.43842393144155,-1860.0,1.0,2.0,1.0,-1.0],[31.43842393144155,31.809883820531663,-1074.7922,0.0,2.0,0.0,-1.0],[31.809883820531663,35.15302282234266,0.0,0.0,1.0,1.0,-1.0],[35.15302282234266,40.724921158694336,890.0,0.0,1.0,0.0,-1.0],[40.724921158694336,42.582220604144894,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C724" t="n">
@@ -17100,7 +17100,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>[[5.863834486850254,31.473342677814987,-1860.0,1.0,1.0,0.0,-1.0],[31.473342677814987,33.025434083328,-0.0,0.0,1.0,2.0,-1.0],[33.025434083328,36.51763974573228,0.0,0.0,0.0,2.0,-1.0],[36.51763974573228,37.29368544848879,1860.0,0.0,0.0,0.0,-1.0],[37.29368544848879,44.27809677329735,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[5.863834486850254,31.473342677814987,-1860.0,1.0,1.0,0.0,-1.0],[31.473342677814987,36.51763974573228,0.0,0.0,1.0,2.0,-1.0],[36.51763974573228,44.27809677329735,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C725" t="n">
@@ -17123,7 +17123,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>[[6.274995285997301,31.837474971500754,-1860.0,1.0,0.0,1.0,-1.0],[31.837474971500754,41.918452875642956,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[6.274995285997301,31.837474971500754,-1860.0,1.0,0.0,1.0,-1.0],[31.837474971500754,41.918452875642956,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C726" t="n">
@@ -17146,7 +17146,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>[[5.722181504183003,31.073599830421916,-1860.0,1.0,0.0,0.0,-1.0],[31.073599830421916,41.576330279863754,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[5.722181504183003,31.073599830421916,-1860.0,1.0,0.0,0.0,-1.0],[31.073599830421916,41.576330279863754,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C727" t="n">
@@ -17215,7 +17215,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>[[6.08874873479854,28.614641867900705,-1860.0,9.0,0.0,0.0,1.0],[28.614641867900705,28.990073420119074,-1074.7923,9.0,9.0,2.0,-1.0],[28.990073420119074,32.368957390084404,0.0,9.0,8.0,3.0,-1.0],[32.368957390084404,43.25647240441712,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[6.08874873479854,28.614641867900705,-1860.0,8.0,0.0,0.0,1.0],[28.614641867900705,28.990073420119074,-1074.7922,8.0,9.0,2.0,-1.0],[28.990073420119074,32.368957390084404,0.0,8.0,8.0,3.0,-1.0],[32.368957390084404,43.25647240441712,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C730" t="n">
@@ -17238,7 +17238,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>[[6.093610436480207,29.864418878405466,-1860.0,8.0,0.0,0.0,1.0],[29.864418878405466,30.25410426269932,-873.8505,7.0,8.0,1.0,-1.0],[30.25410426269932,33.761272721344035,0.0,7.0,8.0,1.0,-1.0],[33.761272721344035,44.672463481572024,1860.0,8.0,8.0,0.0,-1.0]]</t>
+          <t>[[6.093610436480207,29.864418878405466,-1860.0,7.0,0.0,0.0,1.0],[29.864418878405466,30.25410426269932,-873.8504,7.0,8.0,1.0,-1.0],[30.25410426269932,33.761272721344035,0.0,6.0,8.0,1.0,-1.0],[33.761272721344035,44.672463481572024,1860.0,8.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C731" t="n">
@@ -17261,7 +17261,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>[[5.940295990748728,29.46027690807245,-1860.0,7.0,0.0,0.0,1.0],[29.46027690807245,30.218985969921604,-873.8505,6.0,8.0,4.0,-1.0],[30.218985969921604,33.25382221731821,0.0,6.0,7.0,5.0,-1.0],[33.25382221731821,33.63317674824279,1071.35,6.0,7.0,5.0,-1.0],[33.63317674824279,43.49639455228177,1860.0,6.0,7.0,5.0,-1.0]]</t>
+          <t>[[5.940295990748728,29.46027690807245,-1860.0,7.0,0.0,0.0,1.0],[29.46027690807245,30.218985969921604,-873.8504,5.0,8.0,4.0,-1.0],[30.218985969921604,33.25382221731821,0.0,6.0,7.0,5.0,-1.0],[33.25382221731821,33.63317674824279,1071.35,6.0,7.0,5.0,-1.0],[33.63317674824279,43.49639455228177,1860.0,5.0,7.0,5.0,-1.0]]</t>
         </is>
       </c>
       <c r="C732" t="n">
@@ -17284,7 +17284,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>[[5.792876763597392,29.695944878509668,-1860.0,6.0,0.0,0.0,1.0],[29.695944878509668,30.07535865811145,-1074.7923,6.0,9.0,2.0,-1.0],[30.07535865811145,33.11066889492571,0.0,6.0,8.0,3.0,-1.0],[33.11066889492571,33.49008267452749,890.0,6.0,8.0,3.0,-1.0],[33.49008267452749,43.35484094417383,1860.0,6.0,8.0,3.0,-1.0]]</t>
+          <t>[[5.792876763597392,29.695944878509668,-1860.0,5.0,0.0,0.0,1.0],[29.695944878509668,30.07535865811145,-1074.7922,5.0,9.0,2.0,-1.0],[30.07535865811145,33.11066889492571,0.0,6.0,8.0,3.0,-1.0],[33.11066889492571,33.49008267452749,890.0,4.0,8.0,3.0,-1.0],[33.49008267452749,43.35484094417383,1860.0,5.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C733" t="n">
@@ -17307,7 +17307,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>[[5.920771901706709,29.45730616428769,-1860.0,5.0,0.0,0.0,1.0],[29.45730616428769,32.54406475610159,0.0,4.0,7.0,4.0,-1.0],[32.54406475610159,32.92990958007833,1071.35,4.0,7.0,4.0,-1.0],[32.92990958007833,44.119409475403714,1860.0,4.0,8.0,3.0,-1.0]]</t>
+          <t>[[5.920771901706709,29.45730616428769,-1860.0,4.0,0.0,0.0,1.0],[29.45730616428769,32.54406475610159,0.0,3.0,7.0,4.0,-1.0],[32.54406475610159,32.92990958007833,1071.35,3.0,7.0,4.0,-1.0],[32.92990958007833,44.119409475403714,1860.0,3.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C734" t="n">
@@ -17330,7 +17330,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>[[5.729929070450166,28.72834939554622,-1860.0,4.0,0.0,0.0,1.0],[28.72834939554622,29.09929165885422,-1074.7923,4.0,9.0,2.0,-1.0],[29.09929165885422,32.437772028626235,0.0,4.0,8.0,3.0,-1.0],[32.437772028626235,42.45321313794226,1860.0,4.0,9.0,2.0,-1.0]]</t>
+          <t>[[5.729929070450166,28.72834939554622,-1860.0,4.0,0.0,0.0,1.0],[28.72834939554622,29.09929165885422,-1074.7922,3.0,9.0,2.0,-1.0],[29.09929165885422,32.437772028626235,0.0,3.0,8.0,3.0,-1.0],[32.437772028626235,42.45321313794226,1860.0,3.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C735" t="n">
@@ -17353,7 +17353,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>[[6.028534461864241,29.182923856584985,-1860.0,3.0,0.0,0.0,1.0],[29.182923856584985,29.55638175004822,-873.8505,2.0,8.0,3.0,-1.0],[29.55638175004822,32.917502791217366,0.0,2.0,7.0,4.0,-1.0],[32.917502791217366,43.000865914724784,1860.0,2.0,8.0,1.0,-1.0]]</t>
+          <t>[[6.028534461864241,29.182923856584985,-1860.0,2.0,0.0,0.0,1.0],[29.182923856584985,29.55638175004822,-873.8504,2.0,8.0,3.0,-1.0],[29.55638175004822,32.917502791217366,0.0,2.0,7.0,4.0,-1.0],[32.917502791217366,43.000865914724784,1860.0,2.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C736" t="n">
@@ -17376,7 +17376,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>[[5.904617264301909,28.885789318489433,-1860.0,2.0,0.0,0.0,1.0],[28.885789318489433,30.4438348814852,-873.8505,1.0,8.0,3.0,-1.0],[30.4438348814852,33.559926007476726,0.0,1.0,7.0,4.0,-1.0],[33.559926007476726,44.46624494844708,1860.0,1.0,7.0,4.0,-1.0]]</t>
+          <t>[[5.904617264301909,28.885789318489433,-1860.0,2.0,0.0,0.0,1.0],[28.885789318489433,30.4438348814852,-873.8504,1.0,8.0,3.0,-1.0],[30.4438348814852,33.559926007476726,0.0,1.0,7.0,4.0,-1.0],[33.559926007476726,44.46624494844708,1860.0,1.0,7.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C737" t="n">
@@ -17399,7 +17399,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>[[5.834823644290232,29.464308432555832,-1860.0,1.0,0.0,0.0,1.0],[29.464308432555832,29.851677035642155,-873.8505,0.0,8.0,4.0,-1.0],[29.851677035642155,32.95062586033272,0.0,0.0,7.0,5.0,-1.0],[32.95062586033272,33.337994463419044,1071.35,0.0,7.0,2.0,-1.0],[33.337994463419044,44.18431534983604,1860.0,0.0,7.0,2.0,-1.0]]</t>
+          <t>[[5.834823644290232,29.464308432555832,-1860.0,1.0,0.0,0.0,1.0],[29.464308432555832,29.851677035642155,-873.8504,0.0,8.0,4.0,-1.0],[29.851677035642155,32.95062586033272,0.0,0.0,7.0,5.0,-1.0],[32.95062586033272,33.337994463419044,1071.35,0.0,7.0,2.0,-1.0],[33.337994463419044,44.18431534983604,1860.0,0.0,7.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C738" t="n">
@@ -17422,7 +17422,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>[[14.603709426006594,31.69296770568061,-0.0,0.0,0.0,1.0,1.0],[31.69296770568061,31.973119480757227,890.0,0.0,8.0,2.0,-1.0],[31.973119480757227,42.338735158592286,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[14.603709426006594,31.69296770568061,0.0,0.0,0.0,1.0,1.0],[31.69296770568061,31.973119480757227,890.0,0.0,8.0,2.0,-1.0],[31.973119480757227,42.338735158592286,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C739" t="n">
@@ -17445,7 +17445,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>[[14.245771520889912,26.922191625735785,-1860.0,1.0,8.0,3.0,-1.0],[26.922191625735785,28.733108783570913,-1074.7923,0.0,8.0,2.0,-1.0],[28.733108783570913,31.75130404662945,0.0,0.0,8.0,2.0,-1.0],[31.75130404662945,32.35494309924116,708.65,1.0,8.0,1.0,-1.0],[32.35494309924116,44.12590462516947,1860.0,1.0,8.0,1.0,-1.0]]</t>
+          <t>[[14.245771520889912,26.922191625735785,-1860.0,1.0,8.0,3.0,-1.0],[26.922191625735785,28.733108783570913,-1074.7922,0.0,8.0,2.0,-1.0],[28.733108783570913,31.75130404662945,0.0,0.0,8.0,2.0,-1.0],[31.75130404662945,32.35494309924116,708.65,1.0,8.0,1.0,-1.0],[32.35494309924116,44.12590462516947,1860.0,1.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C740" t="n">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>[[13.63758398867611,28.437049312171897,-1860.0,1.0,6.0,3.0,-1.0],[28.437049312171897,28.739079216733035,-1074.7923,0.0,6.0,2.0,-1.0],[28.739079216733035,32.061408166905565,0.0,0.0,5.0,3.0,-1.0],[32.061408166905565,43.53854454022883,1860.0,0.0,5.0,2.0,-1.0]]</t>
+          <t>[[13.63758398867611,28.437049312171897,-1860.0,1.0,6.0,3.0,-1.0],[28.437049312171897,28.739079216733035,-1074.7922,0.0,6.0,2.0,-1.0],[28.739079216733035,32.061408166905565,0.0,0.0,5.0,3.0,-1.0],[32.061408166905565,43.53854454022883,1860.0,0.0,5.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C742" t="n">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>[[15.114865484076022,27.020927533341908,-1860.0,1.0,5.0,1.0,-1.0],[27.020927533341908,28.34382331659367,-1074.7923,0.0,5.0,2.0,-1.0],[28.34382331659367,31.51877319639791,0.0,0.0,5.0,2.0,-1.0],[31.51877319639791,31.783352353048265,708.65,1.0,5.0,1.0,-1.0],[31.783352353048265,41.30820199246097,1860.0,1.0,5.0,1.0,-1.0]]</t>
+          <t>[[15.114865484076022,27.020927533341908,-1860.0,1.0,5.0,1.0,-1.0],[27.020927533341908,28.34382331659367,-1074.7922,0.0,5.0,2.0,-1.0],[28.34382331659367,31.51877319639791,0.0,0.0,5.0,2.0,-1.0],[31.51877319639791,31.783352353048265,708.65,1.0,5.0,1.0,-1.0],[31.783352353048265,41.30820199246097,1860.0,1.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C743" t="n">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>[[14.10266160291317,27.256677252821802,-1860.0,1.0,4.0,2.0,-1.0],[27.256677252821802,29.449013194473242,-1074.7923,0.0,4.0,2.0,-1.0],[29.449013194473242,32.46347511424397,0.0,0.0,4.0,2.0,-1.0],[32.46347511424397,33.285601092363265,708.65,1.0,4.0,1.0,-1.0],[33.285601092363265,41.23281888084973,1860.0,1.0,5.0,0.0,-1.0]]</t>
+          <t>[[14.10266160291317,27.256677252821802,-1860.0,1.0,4.0,2.0,-1.0],[27.256677252821802,29.449013194473242,-1074.7922,0.0,4.0,2.0,-1.0],[29.449013194473242,32.46347511424397,0.0,0.0,4.0,2.0,-1.0],[32.46347511424397,33.285601092363265,708.65,1.0,4.0,1.0,-1.0],[33.285601092363265,41.23281888084973,1860.0,1.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C744" t="n">
@@ -17560,7 +17560,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>[[14.814695644686502,29.37746717540806,-1860.0,1.0,3.0,1.0,-1.0],[29.37746717540806,29.674666594402378,-1074.7923,0.0,3.0,2.0,-1.0],[29.674666594402378,32.94386020333987,0.0,0.0,2.0,3.0,-1.0],[32.94386020333987,44.23743812512394,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[14.814695644686502,29.37746717540806,-1860.0,0.0,3.0,1.0,-1.0],[29.37746717540806,29.674666594402378,-1074.7922,0.0,3.0,2.0,-1.0],[29.674666594402378,32.94386020333987,0.0,0.0,2.0,3.0,-1.0],[32.94386020333987,44.23743812512394,1860.0,0.0,3.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C745" t="n">

--- a/Figure_Plot/figure_plot_4_c/input/dsfunction_May2025_exact_V5_k20_classified.xlsx
+++ b/Figure_Plot/figure_plot_4_c/input/dsfunction_May2025_exact_V5_k20_classified.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[[-55.21350582479238,33.52015590482914,-1860.0,1.0,1.0,4.0,-1.0],[33.52015590482914,34.62932667644941,-1187.2576,0.0,1.0,5.0,-1.0],[34.62932667644941,38.51142437712035,0.0,0.0,0.0,6.0,-1.0],[38.51142437712035,39.06600976293049,788.5,0.0,0.0,0.0,-1.0],[39.06600976293049,110.60752453243785,788.5001,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-55.21350582479238,33.52015590482914,-1860.0,1.0,1.0,4.0,-1.0,0.1564457831325301],[33.52015590482914,34.62932667644941,-1187.2576,0.0,1.0,5.0,-1.0,0.11794546506024095],[34.62932667644941,38.51142437712035,0.0,0.0,0.0,6.0,-1.0,0.05],[38.51142437712035,39.06600976293049,788.5,0.0,0.0,0.0,-1.0,0.0],[39.06600976293049,110.60752453243785,788.5001,0.0,0.0,0.0,-1.0,-6.341154087929901e-09]]</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -502,7 +502,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[[-57.54545105290039,33.20491722258214,-1860.0,1.0,1.0,1.0,-1.0],[33.20491722258214,37.25111198645716,0.0,0.0,0.0,3.0,-1.0],[37.25111198645716,40.71927892692146,788.5,0.0,0.0,0.0,-1.0],[40.71927892692146,115.28486814690395,788.5001,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-57.54545105290039,33.20491722258214,-1860.0,1.0,1.0,1.0,-1.0,0.1564457831325301],[33.20491722258214,37.25111198645716,0.0,0.0,0.0,3.0,-1.0,0.05],[37.25111198645716,40.71927892692146,788.5,0.0,0.0,0.0,-1.0,0.0],[40.71927892692146,115.28486814690395,788.5001,0.0,0.0,0.0,-1.0,-6.341154087929901e-09]]</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -528,7 +528,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[[-58.85544584658378,32.77850273407499,-1860.0,1.0,1.0,2.0,-1.0],[32.77850273407499,33.36968949911149,-1187.2576,0.0,1.0,1.0,-1.0],[33.36968949911149,36.91681008933054,0.0,0.0,0.0,2.0,-1.0],[36.91681008933054,37.50799685436705,788.5,0.0,0.0,0.0,-1.0],[37.50799685436705,117.90939689933214,788.5001,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-58.85544584658378,32.77850273407499,-1860.0,1.0,1.0,2.0,-1.0,0.1564457831325301],[32.77850273407499,33.36968949911149,-1187.2576,0.0,1.0,1.0,-1.0,0.11794546506024095],[33.36968949911149,36.91681008933054,0.0,0.0,0.0,2.0,-1.0,0.05],[36.91681008933054,37.50799685436705,788.5,0.0,0.0,0.0,-1.0,0.0],[37.50799685436705,117.90939689933214,788.5001,0.0,0.0,0.0,-1.0,-6.341154087929901e-09]]</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -554,7 +554,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[[-57.836665619631404,34.538196046443915,-1860.0,1.0,0.0,0.0,-1.0],[34.538196046443915,115.87455223040959,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-57.836665619631404,34.538196046443915,-1860.0,1.0,0.0,0.0,-1.0,0.10644578313253011],[34.538196046443915,115.87455223040959,0.0,0.0,0.0,1.0,-1.0,0.0]]</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -580,7 +580,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[[-53.4425224939124,32.99267166301042,-1860.0,1.0,0.0,1.0,-1.0],[32.99267166301042,107.07998094037286,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-53.4425224939124,32.99267166301042,-1860.0,1.0,0.0,1.0,-1.0,0.10644578313253011],[32.99267166301042,107.07998094037286,0.0,0.0,0.0,1.0,-1.0,0.0]]</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -606,7 +606,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[[-58.07825482224207,32.344276789518176,-1860.0,1.0,0.0,0.0,-1.0],[32.344276789518176,116.34972551270192,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-58.07825482224207,32.344276789518176,-1860.0,1.0,0.0,0.0,-1.0,0.10644578313253011],[32.344276789518176,116.34972551270192,0.0,0.0,0.0,1.0,-1.0,0.0]]</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -632,7 +632,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[[-60.60348112022488,18.529094506997787,-1860.0,10.0,0.0,0.0,1.0],[18.529094506997787,19.746518747416594,-733.6842,9.0,0.0,1.0,1.0],[19.746518747416594,121.40144282238725,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-60.60348112022488,18.529094506997787,-1860.0,10.0,0.0,0.0,1.0,0.10644578313253011],[18.529094506997787,19.746518747416594,-733.6842,9.0,0.0,1.0,1.0,0.041987951204819275],[19.746518747416594,121.40144282238725,0.0,0.0,0.0,1.0,-1.0,0.0]]</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -658,7 +658,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[[-62.01479091969236,16.466958505843593,-1860.0,9.0,0.0,0.0,1.0],[16.466958505843593,19.58131364177757,-733.6842,9.0,0.0,0.0,1.0],[19.58131364177757,124.22364620915887,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-62.01479091969236,16.466958505843593,-1860.0,9.0,0.0,0.0,1.0,0.10644578313253011],[16.466958505843593,19.58131364177757,-733.6842,9.0,0.0,0.0,1.0,0.041987951204819275],[19.58131364177757,124.22364620915887,0.0,0.0,0.0,1.0,-1.0,0.0]]</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -684,7 +684,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[[-59.04456049791762,20.426447632301794,-1860.0,9.0,0.0,0.0,1.0],[20.426447632301794,32.28779212934948,-733.6842,9.0,0.0,0.0,1.0],[32.28779212934948,118.28253973294511,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-59.04456049791762,20.426447632301794,-1860.0,9.0,0.0,0.0,1.0,0.10644578313253011],[20.426447632301794,32.28779212934948,-733.6842,9.0,0.0,0.0,1.0,0.041987951204819275],[32.28779212934948,118.28253973294511,0.0,0.0,0.0,1.0,-1.0,0.0]]</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -710,7 +710,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[[-58.985652155467,19.818110384214442,-1860.0,8.0,0.0,0.0,1.0],[19.818110384214442,30.483281254246528,-733.6842,8.0,0.0,0.0,1.0],[30.483281254246528,34.03833821092389,0.0,8.0,8.0,1.0,-1.0],[34.03833821092389,36.408376182042126,227.85,8.0,8.0,0.0,-1.0],[36.408376182042126,118.17468618562137,1678.6501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-58.985652155467,19.818110384214442,-1860.0,8.0,0.0,0.0,1.0,0.21289156626506023],[19.818110384214442,30.483281254246528,-733.6842,8.0,0.0,0.0,1.0,0.14843373433734938],[30.483281254246528,34.03833821092389,0.0,8.0,8.0,1.0,-1.0,0.1064457831325301],[34.03833821092389,36.408376182042126,227.85,8.0,8.0,0.0,-1.0,0.09199746353836397],[36.408376182042126,118.17468618562137,1678.6501,0.0,0.0,0.0,-1.0,-6.341154115685477e-09]]</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -736,7 +736,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[[-60.01341871595816,19.55599192733849,-1860.0,7.0,0.0,0.0,1.0],[19.55599192733849,32.21476180240841,-733.6842,7.0,0.0,0.0,1.0],[32.21476180240841,35.83155319528553,0.0,7.0,8.0,1.0,-1.0],[35.83155319528553,36.43435176076505,227.85,7.0,8.0,1.0,-1.0],[36.43435176076505,120.22335236241835,1860.0,7.0,8.0,1.0,-1.0]]</t>
+          <t>[[-60.01341871595816,19.55599192733849,-1860.0,7.0,0.0,0.0,1.0,0.3193373493975903],[19.55599192733849,32.21476180240841,-733.6842,7.0,0.0,0.0,1.0,0.25487951746987947],[32.21476180240841,35.83155319528553,0.0,7.0,8.0,1.0,-1.0,0.2128915662650602],[35.83155319528553,36.43435176076505,227.85,7.0,8.0,1.0,-1.0,0.19844324667089405],[36.43435176076505,120.22335236241835,1860.0,7.0,8.0,1.0,-1.0,0.09494610019023457]]</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[-54.95644327716195,20.677145689545995,-1860.0,5.0,0.0,0.0,1.0],[20.677145689545995,31.166475546242722,-733.6842,5.0,0.0,0.0,1.0],[31.166475546242722,34.478895500989054,0.0,5.0,8.0,1.0,-1.0],[34.478895500989054,36.13510547836222,227.85,5.0,8.0,0.0,-1.0],[36.13510547836222,110.11248446769699,1860.0,6.0,8.0,0.0,-1.0]]</t>
+          <t>[[-54.95644327716195,20.677145689545995,-1860.0,5.0,0.0,0.0,1.0,0.4257831325301204],[20.677145689545995,31.166475546242722,-733.6842,5.0,0.0,0.0,1.0,0.3613253006024096],[31.166475546242722,34.478895500989054,0.0,5.0,8.0,1.0,-1.0,0.3193373493975903],[34.478895500989054,36.13510547836222,227.85,5.0,8.0,0.0,-1.0,0.30488902980342414],[36.13510547836222,110.11248446769699,1860.0,6.0,8.0,0.0,-1.0,0.20139188332276464]]</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -788,7 +788,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[[-57.7165865406388,20.5472561602151,-1860.0,4.0,0.0,0.0,1.0],[20.5472561602151,32.14189952330457,-733.6842,4.0,0.0,0.0,1.0],[32.14189952330457,35.62029253223142,0.0,4.0,8.0,1.0,-1.0],[35.62029253223142,36.77975686854036,227.85,4.0,8.0,0.0,-1.0],[36.77975686854036,115.62333173754874,1860.0,5.0,8.0,0.0,-1.0]]</t>
+          <t>[[-57.7165865406388,20.5472561602151,-1860.0,4.0,0.0,0.0,1.0,0.5322289156626506],[20.5472561602151,32.14189952330457,-733.6842,4.0,0.0,0.0,1.0,0.4677710837349398],[32.14189952330457,35.62029253223142,0.0,4.0,8.0,1.0,-1.0,0.4257831325301205],[35.62029253223142,36.77975686854036,227.85,4.0,8.0,0.0,-1.0,0.41133481293595436],[36.77975686854036,115.62333173754874,1860.0,5.0,8.0,0.0,-1.0,0.30783766645529487]]</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[[-56.73625371724488,20.20228717450702,-1860.0,3.0,0.0,0.0,1.0],[20.20228717450702,30.460759293407264,-733.6842,3.0,0.0,0.0,1.0],[30.460759293407264,33.880249999707345,0.0,3.0,8.0,3.0,-1.0],[33.880249999707345,36.159910470574076,227.85,3.0,8.0,0.0,-1.0],[36.159910470574076,113.66836648004265,1860.0,3.0,8.0,0.0,-1.0]]</t>
+          <t>[[-56.73625371724488,20.20228717450702,-1860.0,3.0,0.0,0.0,1.0,0.6386746987951806],[20.20228717450702,30.460759293407264,-733.6842,3.0,0.0,0.0,1.0,0.5742168668674698],[30.460759293407264,33.880249999707345,0.0,3.0,8.0,3.0,-1.0,0.5322289156626505],[33.880249999707345,36.159910470574076,227.85,3.0,8.0,0.0,-1.0,0.5177805960684844],[36.159910470574076,113.66836648004265,1860.0,3.0,8.0,0.0,-1.0,0.41428344958782487]]</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[[-52.54720212938205,19.998492124391127,-1860.0,3.0,0.0,0.0,1.0],[19.998492124391127,30.907619079845738,-733.6842,2.0,0.0,0.0,1.0],[30.907619079845738,34.18035716648213,0.0,2.0,8.0,1.0,-1.0],[34.18035716648213,35.816726209800315,227.85,2.0,8.0,0.0,-1.0],[35.816726209800315,110.5442458546644,1860.0,2.0,8.0,0.0,-1.0]]</t>
+          <t>[[-52.54720212938205,19.998492124391127,-1860.0,3.0,0.0,0.0,1.0,0.7451204819277106],[19.998492124391127,30.907619079845738,-733.6842,2.0,0.0,0.0,1.0,0.6806626499999998],[30.907619079845738,34.18035716648213,0.0,2.0,8.0,1.0,-1.0,0.6386746987951806],[34.18035716648213,35.816726209800315,227.85,2.0,8.0,0.0,-1.0,0.6242263792010144],[35.816726209800315,110.5442458546644,1860.0,2.0,8.0,0.0,-1.0,0.520729232720355]]</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -866,7 +866,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[[-54.40971173332023,19.92346444419082,-1860.0,1.0,0.0,0.0,1.0],[19.92346444419082,31.749197017885756,-733.6842,2.0,0.0,0.0,1.0],[31.749197017885756,35.69110787578406,0.0,2.0,8.0,1.0,-1.0],[35.69110787578406,36.817368120897875,227.85,2.0,8.0,0.0,-1.0],[36.817368120897875,113.96619491119344,1860.0,2.0,8.0,0.0,-1.0]]</t>
+          <t>[[-54.40971173332023,19.92346444419082,-1860.0,1.0,0.0,0.0,1.0,0.8515662650602407],[19.92346444419082,31.749197017885756,-733.6842,2.0,0.0,0.0,1.0,0.7871084331325299],[31.749197017885756,35.69110787578406,0.0,2.0,8.0,1.0,-1.0,0.7451204819277106],[35.69110787578406,36.817368120897875,227.85,2.0,8.0,0.0,-1.0,0.7306721623335445],[36.817368120897875,113.96619491119344,1860.0,2.0,8.0,0.0,-1.0,0.627175015852885]]</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -892,7 +892,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[[-53.87883994685785,20.037483552888446,-1860.0,1.0,0.0,0.0,1.0],[20.037483552888446,32.91684295057152,-733.6842,1.0,0.0,0.0,1.0],[32.91684295057152,36.276675836923616,0.0,1.0,8.0,1.0,-1.0],[36.276675836923616,113.55283222302202,1860.0,1.0,8.0,0.0,-1.0]]</t>
+          <t>[[-53.87883994685785,20.037483552888446,-1860.0,1.0,0.0,0.0,1.0,0.9580120481927707],[20.037483552888446,32.91684295057152,-733.6842,1.0,0.0,0.0,1.0,0.8935542162650599],[32.91684295057152,36.276675836923616,0.0,1.0,8.0,1.0,-1.0,0.8515662650602407],[36.276675836923616,113.55283222302202,1860.0,1.0,8.0,0.0,-1.0,0.7336207989854151]]</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -918,7 +918,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[[-61.55544104828966,31.35588228437262,-733.6843,0.0,0.0,0.0,1.0],[31.35588228437262,34.95244963918535,0.0,0.0,8.0,1.0,-1.0],[34.95244963918535,35.55187753165415,227.85,0.0,8.0,0.0,-1.0],[35.55187753165415,117.67349879987822,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-61.55544104828966,31.35588228437262,-733.6843,0.0,0.0,0.0,1.0,1.0000000051204816],[31.35588228437262,34.95244963918535,0.0,0.0,8.0,1.0,-1.0,0.9580120481927707],[34.95244963918535,35.55187753165415,227.85,0.0,8.0,0.0,-1.0,0.9435637285986046],[35.55187753165415,117.67349879987822,1860.0,0.0,8.0,0.0,-1.0,0.8400665821179452]]</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -944,7 +944,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[[-60.88741255761385,31.374313114140328,0.0,0.0,0.0,1.0,1.0],[31.374313114140328,35.514262343001086,890.0,0.0,8.0,0.0,-1.0],[35.514262343001086,115.94756164658165,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-60.88741255761385,31.374313114140328,0.0,0.0,0.0,1.0,1.0,1.000000005120482],[31.374313114140328,35.514262343001086,890.0,0.0,8.0,0.0,-1.0,0.943563733719087],[35.514262343001086,115.94756164658165,1860.0,0.0,8.0,0.0,-1.0,0.8820545390456564]]</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -970,7 +970,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[[-48.70568691196069,28.596540578686323,-1860.0,1.0,8.0,1.0,-1.0],[28.596540578686323,29.53353727554265,-1074.7922,0.0,8.0,1.0,-1.0],[29.53353727554265,32.8130257145398,0.0,0.0,7.0,2.0,-1.0],[32.8130257145398,35.15551745668062,890.0001,0.0,7.0,0.0,-1.0],[35.15551745668062,91.37531926806025,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-48.70568691196069,28.596540578686323,-1860.0,1.0,8.0,1.0,-1.0,0.9885003221781861],[28.596540578686323,29.53353727554265,-1074.7922,0.0,8.0,1.0,-1.0,0.9435637312143307],[29.53353727554265,32.8130257145398,0.0,0.0,7.0,2.0,-1.0,0.882054539045656],[32.8130257145398,35.15551745668062,890.0001,0.0,7.0,0.0,-1.0,0.8256182613031069],[35.15551745668062,91.37531926806025,1860.0,0.0,7.0,0.0,-1.0,0.7641090729708304]]</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -996,7 +996,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[[-48.44422230141655,28.810661363275607,-1860.0,1.0,7.0,1.0,-1.0],[28.810661363275607,30.206833959625463,-1074.7922,0.0,7.0,1.0,-1.0],[30.206833959625463,33.464570017775124,0.0,0.0,7.0,1.0,-1.0],[33.464570017775124,34.39535174867503,708.6501,1.0,7.0,0.0,-1.0],[34.39535174867503,90.70764646811932,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[-48.44422230141655,28.810661363275607,-1860.0,1.0,7.0,1.0,-1.0,0.8705548561033605],[28.810661363275607,30.206833959625463,-1074.7922,0.0,7.0,1.0,-1.0,0.8256182651395051],[30.206833959625463,33.464570017775124,0.0,0.0,7.0,1.0,-1.0,0.7641090729708304],[33.464570017775124,34.39535174867503,708.6501,1.0,7.0,0.0,-1.0,0.7191724781705767],[34.39535174867503,90.70764646811932,1860.0,0.0,6.0,0.0,-1.0,0.6461636068960048]]</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[[-49.53928549786991,28.15841464406519,-1860.0,1.0,6.0,0.0,-1.0],[28.15841464406519,29.588433665082405,-1074.7922,0.0,6.0,1.0,-1.0],[29.588433665082405,32.92514471412257,0.0,0.0,5.0,2.0,-1.0],[32.92514471412257,34.35516373513977,890.0001,0.0,5.0,0.0,-1.0],[34.35516373513977,92.9859435968454,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-49.53928549786991,28.15841464406519,-1860.0,1.0,6.0,0.0,-1.0,0.7526093900285349],[28.15841464406519,29.588433665082405,-1074.7922,0.0,6.0,1.0,-1.0,0.7076727990646795],[29.588433665082405,32.92514471412257,0.0,0.0,5.0,2.0,-1.0,0.6461636068960048],[32.92514471412257,34.35516373513977,890.0001,0.0,5.0,0.0,-1.0,0.5897273291534557],[34.35516373513977,92.9859435968454,1860.0,0.0,5.0,0.0,-1.0,0.5282181408211792]]</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[[-50.246694718015384,28.12521634883303,-1860.0,1.0,5.0,1.0,-1.0],[28.12521634883303,29.092770806448435,-1074.7922,0.0,5.0,1.0,-1.0],[29.092770806448435,32.47921140810238,0.0,0.0,4.0,2.0,-1.0],[32.47921140810238,34.89809755214092,890.0001,0.0,4.0,0.0,-1.0],[34.89809755214092,94.40269669548877,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-50.246694718015384,28.12521634883303,-1860.0,1.0,5.0,1.0,-1.0,0.6346639239537093],[28.12521634883303,29.092770806448435,-1074.7922,0.0,5.0,1.0,-1.0,0.5897273329898539],[29.092770806448435,32.47921140810238,0.0,0.0,4.0,2.0,-1.0,0.5282181408211792],[32.47921140810238,34.89809755214092,890.0001,0.0,4.0,0.0,-1.0,0.47178186307863007],[34.89809755214092,94.40269669548877,1860.0,0.0,4.0,0.0,-1.0,0.4102726747463536]]</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[[-43.54321822063645,28.63491190893164,-1860.0,1.0,4.0,1.0,-1.0],[28.63491190893164,29.46934115898445,-1074.7922,0.0,4.0,1.0,-1.0],[29.46934115898445,32.38984353416929,0.0,0.0,3.0,2.0,-1.0],[32.38984353416929,34.89313128432771,890.0001,0.0,3.0,0.0,-1.0],[34.89313128432771,81.20395466225868,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-43.54321822063645,28.63491190893164,-1860.0,1.0,4.0,1.0,-1.0,0.5167184578788837],[28.63491190893164,29.46934115898445,-1074.7922,0.0,4.0,1.0,-1.0,0.47178186691502827],[29.46934115898445,32.38984353416929,0.0,0.0,3.0,2.0,-1.0,0.4102726747463536],[32.38984353416929,34.89313128432771,890.0001,0.0,3.0,0.0,-1.0,0.3538363970038044],[34.89313128432771,81.20395466225868,1860.0,0.0,3.0,0.0,-1.0,0.29232720867152795]]</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[[-42.355864177779836,28.871056320702635,-1860.0,1.0,3.0,0.0,-1.0],[28.871056320702635,29.68045314454902,-1074.7922,0.0,3.0,1.0,-1.0],[29.68045314454902,32.918040439934586,0.0,0.0,2.0,2.0,-1.0],[32.918040439934586,33.727437263780985,890.0001,0.0,2.0,0.0,-1.0],[33.727437263780985,78.64896098725572,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-42.355864177779836,28.871056320702635,-1860.0,1.0,3.0,0.0,-1.0,0.398772991804058],[28.871056320702635,29.68045314454902,-1074.7922,0.0,3.0,1.0,-1.0,0.35383640084020257],[29.68045314454902,32.918040439934586,0.0,0.0,2.0,2.0,-1.0,0.2923272086715279],[32.918040439934586,33.727437263780985,890.0001,0.0,2.0,0.0,-1.0,0.23589093092897875],[33.727437263780985,78.64896098725572,1860.0,0.0,2.0,0.0,-1.0,0.17438174259670225]]</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[[-42.671200102660976,28.74907840612734,-1860.0,1.0,2.0,0.0,-1.0],[28.74907840612734,30.381541914899643,-1074.7922,0.0,2.0,1.0,-1.0],[30.381541914899643,34.05458480963732,0.0,0.0,1.0,2.0,-1.0],[34.05458480963732,34.4627006868304,890.0001,0.0,1.0,0.0,-1.0],[34.4627006868304,79.35544717806877,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-42.671200102660976,28.74907840612734,-1860.0,1.0,2.0,0.0,-1.0,0.2808275257292324],[28.74907840612734,30.381541914899643,-1074.7922,0.0,2.0,1.0,-1.0,0.235890934765377],[30.381541914899643,34.05458480963732,0.0,0.0,1.0,2.0,-1.0,0.1743817425967023],[34.05458480963732,34.4627006868304,890.0001,0.0,1.0,0.0,-1.0,0.11794546485415316],[34.4627006868304,79.35544717806877,1860.0,0.0,1.0,0.0,-1.0,0.056436276521876674]]</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[[-44.1304049092147,28.325906562013664,-1860.0,1.0,1.0,1.0,-1.0],[28.325906562013664,29.173348801443233,-1074.7922,0.0,1.0,1.0,-1.0],[29.173348801443233,32.13939663944674,0.0,0.0,0.0,2.0,-1.0],[32.13939663944674,34.25800223802066,890.0001,0.0,0.0,0.0,-1.0],[34.25800223802066,82.56220988550623,890.0002,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-44.1304049092147,28.325906562013664,-1860.0,1.0,1.0,1.0,-1.0,0.16288205965440677],[28.325906562013664,29.173348801443233,-1074.7922,0.0,1.0,1.0,-1.0,0.11794546869055136],[29.173348801443233,32.13939663944674,0.0,0.0,0.0,2.0,-1.0,0.05643627652187667],[32.13939663944674,34.25800223802066,890.0001,0.0,0.0,0.0,-1.0,-1.2206724797625412e-09],[34.25800223802066,82.56220988550623,890.0002,0.0,0.0,0.0,-1.0,-7.561826567692442e-09]]</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[[-40.91240871510341,30.234851608140303,-1860.0,1.0,0.0,0.0,-1.0],[30.234851608140303,75.97237610165412,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-40.91240871510341,30.234851608140303,-1860.0,1.0,0.0,0.0,-1.0,0.10644577557070356],[30.234851608140303,75.97237610165412,0.0,0.0,0.0,1.0,-1.0,-7.561826560753548e-09]]</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[[-41.305203946971595,28.264063373291727,-1860.0,1.0,0.0,0.0,-1.0],[28.264063373291727,76.88349451188483,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-41.305203946971595,28.264063373291727,-1860.0,1.0,0.0,0.0,-1.0,0.10644577557070356],[28.264063373291727,76.88349451188483,0.0,0.0,0.0,1.0,-1.0,-7.561826560753548e-09]]</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[[-42.44759081518525,25.97681227222151,-1860.0,1.0,0.0,0.0,-1.0],[25.97681227222151,78.61096849330363,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-42.44759081518525,25.97681227222151,-1860.0,1.0,0.0,0.0,-1.0,0.10644577557070356],[25.97681227222151,78.61096849330363,0.0,0.0,0.0,1.0,-1.0,-7.561826560753548e-09]]</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[[-40.92379864450677,14.144662110142754,-1860.0,1.0,0.0,0.0,-1.0],[14.144662110142754,75.85258267209045,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-40.92379864450677,14.144662110142754,-1860.0,1.0,0.0,0.0,-1.0,0.10644577557070356],[14.144662110142754,75.85258267209045,0.0,0.0,0.0,1.0,-1.0,-7.561826560753548e-09]]</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[[-42.679970495774675,10.726759078278647,-1860.0,9.0,0.0,1.0,1.0],[10.726759078278647,79.21783211981267,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-42.679970495774675,10.726759078278647,-1860.0,9.0,0.0,1.0,1.0,0.10644577557070356],[10.726759078278647,79.21783211981267,0.0,0.0,0.0,1.0,-1.0,-7.561826560753548e-09]]</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[[-42.60889387584584,11.245352920700064,-1860.0,9.0,0.0,0.0,1.0],[11.245352920700064,27.56482164692609,-733.6842,9.0,0.0,0.0,1.0],[27.56482164692609,79.37913485269374,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-42.60889387584584,11.245352920700064,-1860.0,9.0,0.0,0.0,1.0,0.10644577557070356],[11.245352920700064,27.56482164692609,-733.6842,9.0,0.0,0.0,1.0,0.041987943642992714],[27.56482164692609,79.37913485269374,0.0,0.0,0.0,1.0,-1.0,-7.561826560753548e-09]]</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[[-42.07164427009277,10.613202723271158,-1860.0,6.0,0.0,0.0,1.0],[10.613202723271158,28.30887652256896,-733.6843,8.0,0.0,0.0,1.0],[28.30887652256896,31.52627175880493,0.0,6.0,8.0,4.0,-1.0],[31.52627175880493,78.17850268422642,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-42.07164427009277,10.613202723271158,-1860.0,6.0,0.0,0.0,1.0,0.21289155870323373],[10.613202723271158,28.30887652256896,-733.6843,8.0,0.0,0.0,1.0,0.14843373249841446],[28.30887652256896,31.52627175880493,0.0,6.0,8.0,4.0,-1.0,0.1064457755707036],[31.52627175880493,78.17850268422642,1678.65,0.0,0.0,0.0,-1.0,-7.561826526059079e-09]]</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[[-43.797429415797815,28.152675021315083,-1860.0,8.0,0.0,0.0,1.0],[28.152675021315083,31.499191506762195,0.0,7.0,7.0,3.0,-1.0],[31.499191506762195,81.27862422778797,1860.0,6.0,7.0,0.0,-1.0]]</t>
+          <t>[[-43.797429415797815,28.152675021315083,-1860.0,8.0,0.0,0.0,1.0,0.2548795156309445],[28.152675021315083,31.499191506762195,0.0,7.0,7.0,3.0,-1.0,0.1484337324984144],[31.499191506762195,81.27862422778797,1860.0,6.0,7.0,0.0,-1.0,0.030488266423588775]]</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[[-41.3295347964676,28.102307263748145,-1860.0,6.0,0.0,0.0,1.0],[28.102307263748145,31.25830008466704,0.0,6.0,7.0,4.0,-1.0],[31.25830008466704,31.6527991872819,1071.35,6.0,7.0,1.0,-1.0],[31.6527991872819,76.62569688537619,1860.0,5.0,7.0,1.0,-1.0]]</t>
+          <t>[[-41.3295347964676,28.102307263748145,-1860.0,6.0,0.0,0.0,1.0,0.36132529876347463],[28.102307263748145,31.25830008466704,0.0,6.0,7.0,4.0,-1.0,0.2548795156309445],[31.25830008466704,31.6527991872819,1071.35,6.0,7.0,1.0,-1.0,0.18694356128725398],[31.6527991872819,76.62569688537619,1860.0,5.0,7.0,1.0,-1.0,0.13693404955611888]]</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[[-41.20297241671511,27.206798691444448,-1860.0,5.0,0.0,0.0,1.0],[27.206798691444448,28.3862775036541,-873.8505,4.0,8.0,3.0,-1.0],[28.3862775036541,31.531554336213162,0.0,4.0,7.0,4.0,-1.0],[31.531554336213162,32.31787354435292,1071.35,5.0,7.0,4.0,-1.0],[32.31787354435292,76.35174920017977,1860.0,5.0,8.0,3.0,-1.0]]</t>
+          <t>[[-41.20297241671511,27.206798691444448,-1860.0,5.0,0.0,0.0,1.0,0.4677710818960047],[27.206798691444448,28.3862775036541,-873.8505,4.0,8.0,3.0,-1.0,0.41133481532973964],[28.3862775036541,31.531554336213162,0.0,4.0,7.0,4.0,-1.0,0.3613252987634746],[31.531554336213162,32.31787354435292,1071.35,5.0,7.0,4.0,-1.0,0.29338934441978404],[32.31787354435292,76.35174920017977,1860.0,5.0,8.0,3.0,-1.0,0.24337983268864893]]</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[[-43.37032901683536,28.007630255219176,-1860.0,5.0,0.0,0.0,1.0],[28.007630255219176,28.837606525824462,-873.8505,4.0,8.0,3.0,-1.0],[28.837606525824462,32.157511608245606,0.0,3.0,7.0,4.0,-1.0],[32.157511608245606,80.7111234386548,1860.0,4.0,7.0,4.0,-1.0]]</t>
+          <t>[[-43.37032901683536,28.007630255219176,-1860.0,5.0,0.0,0.0,1.0,0.5742168650285349],[28.007630255219176,28.837606525824462,-873.8505,4.0,8.0,3.0,-1.0,0.5177805984622698],[28.837606525824462,32.157511608245606,0.0,3.0,7.0,4.0,-1.0,0.4677710818960047],[32.157511608245606,80.7111234386548,1860.0,4.0,7.0,4.0,-1.0,0.34982561582117905]]</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[[-42.127797234259994,27.55584442848228,-1860.0,3.0,0.0,0.0,1.0],[27.55584442848228,28.361435661577566,-873.8505,2.0,8.0,4.0,-1.0],[28.361435661577566,31.18100497741107,0.0,2.0,7.0,5.0,-1.0],[31.18100497741107,31.583800593958706,1071.35,2.0,7.0,2.0,-1.0],[31.583800593958706,78.30809211348532,1860.0,2.0,7.0,2.0,-1.0]]</t>
+          <t>[[-42.127797234259994,27.55584442848228,-1860.0,3.0,0.0,0.0,1.0,0.6806626481610649],[27.55584442848228,28.361435661577566,-873.8505,2.0,8.0,4.0,-1.0,0.6242263815947999],[28.361435661577566,31.18100497741107,0.0,2.0,7.0,5.0,-1.0,0.5742168650285349],[31.18100497741107,31.583800593958706,1071.35,2.0,7.0,2.0,-1.0,0.5062809106848443],[31.583800593958706,78.30809211348532,1860.0,2.0,7.0,2.0,-1.0,0.4562713989537092]]</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[[-40.85082649940425,28.1163202337562,-1860.0,3.0,0.0,0.0,1.0],[28.1163202337562,31.233479408136333,0.0,2.0,7.0,3.0,-1.0],[31.233479408136333,32.01276920173136,1071.35,2.0,7.0,3.0,-1.0],[32.01276920173136,75.65299764305323,1860.0,2.0,8.0,2.0,-1.0]]</t>
+          <t>[[-40.85082649940425,28.1163202337562,-1860.0,3.0,0.0,0.0,1.0,0.787108431293595],[28.1163202337562,31.233479408136333,0.0,2.0,7.0,3.0,-1.0,0.6806626481610649],[31.233479408136333,32.01276920173136,1071.35,2.0,7.0,3.0,-1.0,0.6127266938173743],[32.01276920173136,75.65299764305323,1860.0,2.0,8.0,2.0,-1.0,0.5627171820862393]]</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[[-42.629425135811296,27.465847260490158,-1860.0,1.0,0.0,0.0,1.0],[27.465847260490158,28.688439220890764,-873.8505,1.0,8.0,3.0,-1.0],[28.688439220890764,31.541153795158856,0.0,1.0,7.0,4.0,-1.0],[31.541153795158856,79.22224025078252,1860.0,1.0,7.0,4.0,-1.0]]</t>
+          <t>[[-42.629425135811296,27.465847260490158,-1860.0,1.0,0.0,0.0,1.0,0.893554214426125],[27.465847260490158,28.688439220890764,-873.8505,1.0,8.0,3.0,-1.0,0.83711794785986],[28.688439220890764,31.541153795158856,0.0,1.0,7.0,4.0,-1.0,0.787108431293595],[31.541153795158856,79.22224025078252,1860.0,1.0,7.0,4.0,-1.0,0.6691629652187694]]</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[[-20.941593046846556,27.970114577054098,-1860.0,1.0,0.0,0.0,1.0],[27.970114577054098,28.27203869818929,-873.8505,0.0,8.0,4.0,-1.0],[28.27203869818929,31.29127990954118,0.0,0.0,7.0,5.0,-1.0],[31.29127990954118,31.895128151811562,1071.35,0.0,7.0,5.0,-1.0],[31.895128151811562,69.33371917257503,1860.0,0.0,7.0,5.0,-1.0]]</t>
+          <t>[[-20.941593046846556,27.970114577054098,-1860.0,1.0,0.0,0.0,1.0,0.9999999975586551],[27.970114577054098,28.27203869818929,-873.8505,0.0,8.0,4.0,-1.0,0.9435637309923901],[28.27203869818929,31.29127990954118,0.0,0.0,7.0,5.0,-1.0,0.893554214426125],[31.29127990954118,31.895128151811562,1071.35,0.0,7.0,5.0,-1.0,0.8256182600824344],[31.895128151811562,69.33371917257503,1860.0,0.0,7.0,5.0,-1.0,0.7756087483512994]]</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[[-19.93737514732223,30.539885653001036,0.0,0.0,0.0,1.0,1.0],[30.539885653001036,31.405210123863718,890.0,0.0,8.0,3.0,-1.0],[31.405210123863718,66.30663044865867,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[-19.93737514732223,30.539885653001036,0.0,0.0,0.0,1.0,1.0,0.9999999975586551],[30.539885653001036,31.405210123863718,890.0,0.0,8.0,3.0,-1.0,0.94356372615726],[31.405210123863718,66.30663044865867,1860.0,0.0,8.0,3.0,-1.0,0.8820545314838295]]</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[[-20.284673830617002,27.318581253273067,-1860.0,1.0,8.0,1.0,-1.0],[27.318581253273067,27.906275760481584,-1074.7923,0.0,8.0,2.0,-1.0],[27.906275760481584,30.84474829652418,0.0,0.0,7.0,3.0,-1.0],[30.84474829652418,31.138595550128443,890.0,0.0,7.0,3.0,-1.0],[31.138595550128443,67.57565499705663,1860.0,0.0,7.0,3.0,-1.0]]</t>
+          <t>[[-20.284673830617002,27.318581253273067,-1860.0,1.0,8.0,1.0,-1.0,0.9885003146163596],[27.318581253273067,27.906275760481584,-1074.7923,0.0,8.0,2.0,-1.0,0.9435637293753958],[27.906275760481584,30.84474829652418,0.0,0.0,7.0,3.0,-1.0,0.8820545314838295],[30.84474829652418,31.138595550128443,890.0,0.0,7.0,3.0,-1.0,0.8256182600824344],[31.138595550128443,67.57565499705663,1860.0,0.0,7.0,3.0,-1.0,0.7641090654090039]]</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[[-18.667721105697424,27.148896502837687,-1860.0,1.0,7.0,1.0,-1.0],[27.148896502837687,27.691104995246384,-1074.7923,0.0,7.0,1.0,-1.0],[27.691104995246384,30.67325170349423,0.0,0.0,6.0,2.0,-1.0],[30.67325170349423,30.944355949698583,890.0,0.0,6.0,1.0,-1.0],[30.944355949698583,62.39244850940315,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[-18.667721105697424,27.148896502837687,-1860.0,1.0,7.0,1.0,-1.0,0.870554848541534],[27.148896502837687,27.691104995246384,-1074.7923,0.0,7.0,1.0,-1.0,0.8256182633005702],[27.691104995246384,30.67325170349423,0.0,0.0,6.0,2.0,-1.0,0.7641090654090039],[30.67325170349423,30.944355949698583,890.0,0.0,6.0,1.0,-1.0,0.7076727940076089],[30.944355949698583,62.39244850940315,1860.0,0.0,6.0,1.0,-1.0,0.6461635993341783]]</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[[-18.38616259234314,27.50325061789266,-1860.0,1.0,6.0,1.0,-1.0],[27.50325061789266,30.800693483298822,0.0,0.0,5.0,3.0,-1.0],[30.800693483298822,63.77512213736047,1860.0,0.0,5.0,2.0,-1.0]]</t>
+          <t>[[-18.38616259234314,27.50325061789266,-1860.0,1.0,6.0,1.0,-1.0,0.8141185771401389],[27.50325061789266,30.800693483298822,0.0,0.0,5.0,3.0,-1.0,0.7076727940076089],[30.800693483298822,63.77512213736047,1860.0,0.0,5.0,2.0,-1.0,0.5897273279327833]]</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[[-16.951175822963805,27.000103421297162,-1860.0,1.0,5.0,1.0,-1.0],[27.000103421297162,30.66271002498558,0.0,0.0,4.0,3.0,-1.0],[30.66271002498558,61.27163664152447,1860.0,0.0,4.0,3.0,-1.0]]</t>
+          <t>[[-16.951175822963805,27.000103421297162,-1860.0,1.0,5.0,1.0,-1.0,0.6961731110653133],[27.000103421297162,30.66271002498558,0.0,0.0,4.0,3.0,-1.0,0.5897273279327833],[30.66271002498558,61.27163664152447,1860.0,0.0,4.0,3.0,-1.0,0.4717818618579576]]</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[[-17.144865641018328,27.561469101722928,-1860.0,1.0,4.0,1.0,-1.0],[27.561469101722928,30.698755750336346,0.0,0.0,3.0,3.0,-1.0],[30.698755750336346,61.02586002026608,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[-17.144865641018328,27.561469101722928,-1860.0,1.0,4.0,1.0,-1.0,0.5782276449904877],[27.561469101722928,30.698755750336346,0.0,0.0,3.0,3.0,-1.0,0.4717818618579576],[30.698755750336346,61.02586002026608,1860.0,0.0,3.0,2.0,-1.0,0.353836395783132]]</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[[-16.090136540920213,27.37769052683558,-1860.0,1.0,3.0,1.0,-1.0],[27.37769052683558,31.421209323836123,0.0,0.0,2.0,3.0,-1.0],[31.421209323836123,59.47312097802737,1860.0,0.0,3.0,3.0,-1.0]]</t>
+          <t>[[-16.090136540920213,27.37769052683558,-1860.0,1.0,3.0,1.0,-1.0,0.4602821789156621],[27.37769052683558,31.421209323836123,0.0,0.0,2.0,3.0,-1.0,0.353836395783132],[31.421209323836123,59.47312097802737,1860.0,0.0,3.0,3.0,-1.0,0.23589092970830633]]</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[[-14.945932570785384,27.381705201270325,-1860.0,0.0,2.0,1.0,-1.0],[27.381705201270325,31.144161892119723,0.0,0.0,1.0,3.0,-1.0],[31.144161892119723,55.36497683946271,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[-14.945932570785384,27.381705201270325,-1860.0,0.0,2.0,1.0,-1.0,0.34233671284083644],[27.381705201270325,31.144161892119723,0.0,0.0,1.0,3.0,-1.0,0.2358909297083063],[31.144161892119723,55.36497683946271,1860.0,0.0,1.0,1.0,-1.0,0.11794546363348067]]</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>[[-16.991154164478402,27.80729742335238,-1860.0,0.0,2.0,0.0,-1.0],[27.80729742335238,31.43260564433291,0.0,0.0,1.0,2.0,-1.0],[31.43260564433291,60.43507141217713,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-16.991154164478402,27.80729742335238,-1860.0,0.0,2.0,0.0,-1.0,0.34233671284083644],[27.80729742335238,31.43260564433291,0.0,0.0,1.0,2.0,-1.0,0.2358909297083063],[31.43260564433291,60.43507141217713,1860.0,0.0,1.0,0.0,-1.0,0.11794546363348067]]</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>[[-14.89135094345417,26.134895394910835,-1860.0,0.0,2.0,0.0,-1.0],[26.134895394910835,30.877814046744945,0.0,0.0,1.0,1.0,-1.0],[30.877814046744945,56.0152829014657,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[-14.89135094345417,26.134895394910835,-1860.0,0.0,2.0,0.0,-1.0,0.34233671284083644],[26.134895394910835,30.877814046744945,0.0,0.0,1.0,1.0,-1.0,0.2358909297083063],[30.877814046744945,56.0152829014657,1860.0,0.0,1.0,1.0,-1.0,0.11794546363348067]]</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>[[-13.020563153456848,26.425082512738335,-1860.0,1.0,1.0,0.0,-1.0],[26.425082512738335,27.08989676553938,0.0,0.0,1.0,1.0,-1.0],[27.08989676553938,29.970758527677233,0.0,0.0,0.0,1.0,-1.0],[29.970758527677233,32.408410787947716,1860.0,0.0,0.0,0.0,-1.0],[32.408410787947716,53.23925737571372,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-13.020563153456848,26.425082512738335,-1860.0,1.0,1.0,0.0,-1.0,0.2243912467660108],[26.425082512738335,27.08989676553938,0.0,0.0,1.0,1.0,-1.0,0.1179454636334807],[27.08989676553938,29.970758527677233,0.0,0.0,0.0,1.0,-1.0,0.1179454636334807],[29.970758527677233,32.408410787947716,1860.0,0.0,0.0,0.0,-1.0,-2.441344931769507e-09],[32.408410787947716,53.23925737571372,1860.0,0.0,1.0,0.0,-1.0,-2.441344931769507e-09]]</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>[0,0,0.6648142528,0,0]</t>
+          <t>[0,0,3.5456760149,0,0]</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>[[-12.945958085776626,26.110194679583827,-1860.0,1.0,0.0,0.0,-1.0],[26.110194679583827,53.405119623557326,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-12.945958085776626,26.110194679583827,-1860.0,1.0,0.0,0.0,-1.0,0.10644578069118518],[26.110194679583827,53.405119623557326,0.0,0.0,0.0,1.0,-1.0,-2.441344931769507e-09]]</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>[[-15.038784743655128,23.654884315957652,-1860.0,10.0,1.0,0.0,1.0],[23.654884315957652,23.895217664154004,-934.626,10.0,1.0,0.0,1.0],[23.895217664154004,56.820886367054314,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-15.038784743655128,23.654884315957652,-1860.0,10.0,1.0,0.0,1.0,0.10644578069118518],[23.654884315957652,23.895217664154004,-934.626,10.0,1.0,0.0,1.0,0.053487630088775544],[23.895217664154004,56.820886367054314,0.0,0.0,0.0,1.0,-1.0,-2.441344931769507e-09]]</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>[[-19.968942004288422,24.014195415559293,-1860.0,10.0,0.0,0.0,1.0],[24.014195415559293,24.596753527080452,-733.6842,9.0,0.0,1.0,1.0],[24.596753527080452,67.12349566812526,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-19.968942004288422,24.014195415559293,-1860.0,10.0,0.0,0.0,1.0,0.10644578069118518],[24.014195415559293,24.596753527080452,-733.6842,9.0,0.0,1.0,1.0,0.04198794876347434],[24.596753527080452,67.12349566812526,0.0,0.0,0.0,1.0,-1.0,-2.441344931769507e-09]]</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>[[-18.111959185494165,20.3030973216375,-1860.0,9.0,0.0,0.0,1.0],[20.3030973216375,22.755122205071437,-733.6843,8.0,0.0,1.0,1.0],[22.755122205071437,25.207147088505373,0.0,8.0,0.0,1.0,1.0],[25.207147088505373,27.659171971939315,1016.5,8.0,0.0,0.0,1.0],[27.659171971939315,63.34975638636661,1678.6501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-18.111959185494165,20.3030973216375,-1860.0,9.0,0.0,0.0,1.0,0.21289156382371532],[20.3030973216375,22.755122205071437,-733.6843,8.0,0.0,1.0,1.0,0.14843373761889606],[22.755122205071437,25.207147088505373,0.0,8.0,0.0,1.0,1.0,0.1064457806911852],[25.207147088505373,27.659171971939315,1016.5,8.0,0.0,0.0,1.0,0.041987949365883986],[27.659171971939315,63.34975638636661,1678.6501,0.0,0.0,0.0,-1.0,-8.782499019699408e-09]]</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>[[-17.40489113013632,26.598425382858792,-1860.0,7.0,0.0,0.0,1.0],[26.598425382858792,26.86191829611026,-1275.7341,9.0,10.0,2.0,-1.0],[26.86191829611026,29.7603403418764,0.0,8.0,10.0,2.0,-1.0],[29.7603403418764,30.02383325512787,527.3,10.0,10.0,1.0,-1.0],[30.02383325512787,61.37948993205254,662.1501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-17.40489113013632,26.598425382858792,-1860.0,7.0,0.0,0.0,1.0,0.14843373249841407],[26.598425382858792,26.86191829611026,-1275.7341,9.0,10.0,2.0,-1.0,0.11499682858275144],[26.86191829611026,29.7603403418764,0.0,8.0,10.0,2.0,-1.0,0.04198794936588397],[29.7603403418764,30.02383325512787,527.3,10.0,10.0,1.0,-1.0,0.008551043849079912],[30.02383325512787,61.37948993205254,662.1501,0.0,0.0,0.0,-1.0,-8.782499026638302e-09]]</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[[-19.396187961942232,26.002998023836618,-1860.0,7.0,0.0,0.0,1.0],[26.002998023836618,26.28674293624774,-1074.7923,8.0,9.0,5.0,-1.0],[26.28674293624774,29.124192060358915,0.0,7.0,9.0,5.0,-1.0],[29.124192060358915,65.443540848982,1860.0,9.0,9.0,4.0,-1.0]]</t>
+          <t>[[-19.396187961942232,26.002998023836618,-1860.0,7.0,0.0,0.0,1.0,0.25487951563094424],[26.002998023836618,26.28674293624774,-1074.7923,8.0,9.0,5.0,-1.0,0.20994293038998035],[26.28674293624774,29.124192060358915,0.0,7.0,9.0,5.0,-1.0,0.1484337324984141],[29.124192060358915,65.443540848982,1860.0,9.0,9.0,4.0,-1.0,0.03048826642358847]]</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>[[-48.27288929555375,26.271541002871203,-1860.0,6.0,0.0,0.0,1.0],[26.271541002871203,28.82735004167435,0.0,6.0,9.0,5.0,-1.0],[28.82735004167435,29.253318214808203,708.65,8.0,9.0,4.0,-1.0],[29.253318214808203,79.09159447146948,1860.0,8.0,9.0,4.0,-1.0]]</t>
+          <t>[[-48.27288929555375,26.271541002871203,-1860.0,6.0,0.0,0.0,1.0,0.3613252987634743],[26.271541002871203,28.82735004167435,0.0,6.0,9.0,5.0,-1.0,0.2548795156309442],[28.82735004167435,29.253318214808203,708.65,8.0,9.0,4.0,-1.0,0.20994292717184462],[29.253318214808203,79.09159447146948,1860.0,8.0,9.0,4.0,-1.0,0.13693404955611854]]</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>[[-51.33916713250869,26.65757733612658,-1860.0,4.0,0.0,0.0,1.0],[26.65757733612658,29.79537740095674,0.0,4.0,8.0,6.0,-1.0],[29.79537740095674,82.68972135095078,1860.0,5.0,9.0,4.0,-1.0]]</t>
+          <t>[[-51.33916713250869,26.65757733612658,-1860.0,4.0,0.0,0.0,1.0,0.4677710818960044],[26.65757733612658,29.79537740095674,0.0,4.0,8.0,6.0,-1.0,0.3613252987634743],[29.79537740095674,82.68972135095078,1860.0,5.0,9.0,4.0,-1.0,0.24337983268864866]]</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>[[-49.38138964502187,26.335532069466353,-1860.0,4.0,0.0,0.0,1.0],[26.335532069466353,29.34700054674714,0.0,4.0,8.0,5.0,-1.0],[29.34700054674714,79.25133531311437,1860.0,5.0,8.0,5.0,-1.0]]</t>
+          <t>[[-49.38138964502187,26.335532069466353,-1860.0,4.0,0.0,0.0,1.0,0.5742168650285345],[26.335532069466353,29.34700054674714,0.0,4.0,8.0,5.0,-1.0,0.4677710818960044],[29.34700054674714,79.25133531311437,1860.0,5.0,8.0,5.0,-1.0,0.34982561582117877]]</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>[[-50.68489105055918,26.30148258101398,-1860.0,3.0,0.0,0.0,1.0],[26.30148258101398,29.34614142520048,0.0,3.0,8.0,6.0,-1.0],[29.34614142520048,30.216043952110915,890.0,3.0,8.0,6.0,-1.0],[30.216043952110915,79.36553672255027,1860.0,3.0,9.0,5.0,-1.0]]</t>
+          <t>[[-50.68489105055918,26.30148258101398,-1860.0,3.0,0.0,0.0,1.0,0.6806626481610647],[26.30148258101398,29.34614142520048,0.0,3.0,8.0,6.0,-1.0,0.5742168650285345],[29.34614142520048,30.216043952110915,890.0,3.0,8.0,6.0,-1.0,0.5177805936271395],[30.216043952110915,79.36553672255027,1860.0,3.0,9.0,5.0,-1.0,0.4562713989537089]]</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>[[-52.205111348529236,25.79875477861726,-1860.0,2.0,0.0,0.0,1.0],[25.79875477861726,28.973330725652296,0.0,2.0,9.0,4.0,-1.0],[28.973330725652296,29.42684157522873,708.65,4.0,9.0,3.0,-1.0],[29.42684157522873,83.39463267482428,1860.0,4.0,9.0,3.0,-1.0]]</t>
+          <t>[[-52.205111348529236,25.79875477861726,-1860.0,2.0,0.0,0.0,1.0,0.7871084312935948],[25.79875477861726,28.973330725652296,0.0,2.0,9.0,4.0,-1.0,0.6806626481610647],[28.973330725652296,29.42684157522873,708.65,4.0,9.0,3.0,-1.0,0.6357260597019652],[29.42684157522873,83.39463267482428,1860.0,4.0,9.0,3.0,-1.0,0.5627171820862391]]</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>[[-50.14377603427248,26.016945536669397,-1860.0,1.0,0.0,0.0,1.0],[26.016945536669397,28.613333772042424,0.0,3.0,9.0,4.0,-1.0],[28.613333772042424,79.24290436181627,1860.0,3.0,9.0,3.0,-1.0]]</t>
+          <t>[[-50.14377603427248,26.016945536669397,-1860.0,1.0,0.0,0.0,1.0,0.8935542144261248],[26.016945536669397,28.613333772042424,0.0,3.0,9.0,4.0,-1.0,0.7871084312935948],[28.613333772042424,79.24290436181627,1860.0,3.0,9.0,3.0,-1.0,0.6691629652187692]]</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>[[-48.120554601851914,26.229353571560658,-1860.0,1.0,0.0,0.0,1.0],[26.229353571560658,29.136891880018133,0.0,1.0,8.0,6.0,-1.0],[29.136891880018133,76.07286743083165,1860.0,1.0,9.0,5.0,-1.0]]</t>
+          <t>[[-48.120554601851914,26.229353571560658,-1860.0,1.0,0.0,0.0,1.0,0.9999999975586549],[26.229353571560658,29.136891880018133,0.0,1.0,8.0,6.0,-1.0,0.8935542144261248],[29.136891880018133,76.07286743083165,1860.0,1.0,9.0,5.0,-1.0,0.7756087483512992]]</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>[[-51.49059292522183,27.489587909901516,0.0,0.0,0.0,1.0,1.0],[27.489587909901516,29.264423434286314,708.65,1.0,9.0,4.0,-1.0],[29.264423434286314,81.17836252254153,1860.0,1.0,10.0,3.0,-1.0]]</t>
+          <t>[[-51.49059292522183,27.489587909901516,0.0,0.0,0.0,1.0,1.0,0.9999999975586549],[27.489587909901516,29.264423434286314,708.65,1.0,9.0,4.0,-1.0,0.9550634090995553],[29.264423434286314,81.17836252254153,1860.0,1.0,10.0,3.0,-1.0,0.8820545314838293]]</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>[[-52.291906966163346,25.661747616193118,-1860.0,2.0,9.0,2.0,-1.0],[25.661747616193118,26.1123467756287,-1275.7341,1.0,9.0,2.0,-1.0],[26.1123467756287,28.815941732242216,0.0,1.0,9.0,2.0,-1.0],[28.815941732242216,82.43724170507701,1860.0,2.0,9.0,1.0,-1.0]]</t>
+          <t>[[-52.291906966163346,25.661747616193118,-1860.0,2.0,9.0,2.0,-1.0,0.9885003146163593],[25.661747616193118,26.1123467756287,-1275.7341,1.0,9.0,2.0,-1.0,0.9550634107006968],[26.1123467756287,28.815941732242216,0.0,1.0,9.0,2.0,-1.0,0.8820545314838293],[28.815941732242216,82.43724170507701,1860.0,2.0,9.0,1.0,-1.0,0.7641090654090037]]</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>[[-50.45962200133792,25.143479829883148,-1860.0,2.0,8.0,2.0,-1.0],[25.143479829883148,25.577980415120052,-1275.7341,1.0,8.0,3.0,-1.0],[25.577980415120052,28.184983926541463,0.0,1.0,7.0,4.0,-1.0],[28.184983926541463,28.619484511778367,708.65,1.0,7.0,4.0,-1.0],[28.619484511778367,79.45605298449598,1860.0,1.0,7.0,4.0,-1.0]]</t>
+          <t>[[-50.45962200133792,25.143479829883148,-1860.0,2.0,8.0,2.0,-1.0,0.8705548485415338],[25.143479829883148,25.577980415120052,-1275.7341,1.0,8.0,3.0,-1.0,0.8371179446258712],[25.577980415120052,28.184983926541463,0.0,1.0,7.0,4.0,-1.0,0.7641090654090037],[28.184983926541463,28.619484511778367,708.65,1.0,7.0,4.0,-1.0,0.7191724769499042],[28.619484511778367,79.45605298449598,1860.0,1.0,7.0,4.0,-1.0,0.6461635993341781]]</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>[[-53.87025548498356,25.37175829635096,-1860.0,1.0,7.0,3.0,-1.0],[25.37175829635096,28.201830217112914,0.0,1.0,6.0,4.0,-1.0],[28.201830217112914,29.14518752403356,708.65,1.0,6.0,4.0,-1.0],[29.14518752403356,87.16166189965348,1860.0,1.0,6.0,4.0,-1.0]]</t>
+          <t>[[-53.87025548498356,25.37175829635096,-1860.0,1.0,7.0,3.0,-1.0,0.7526093824667082],[25.37175829635096,28.201830217112914,0.0,1.0,6.0,4.0,-1.0,0.6461635993341781],[28.201830217112914,29.14518752403356,708.65,1.0,6.0,4.0,-1.0,0.6012270108750786],[29.14518752403356,87.16166189965348,1860.0,1.0,6.0,4.0,-1.0,0.5282181332593525]]</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>[[-57.36032969030301,26.150849915474247,-1860.0,2.0,7.0,1.0,-1.0],[26.150849915474247,26.66006442526558,-1476.6759,2.0,7.0,1.0,-1.0],[26.66006442526558,29.206136974222197,0.0,2.0,6.0,2.0,-1.0],[29.206136974222197,94.89480873730311,1860.0,2.0,6.0,2.0,-1.0]]</t>
+          <t>[[-57.36032969030301,26.150849915474247,-1860.0,2.0,7.0,1.0,-1.0,0.6346639163918826],[26.150849915474247,26.66006442526558,-1476.6759,2.0,7.0,1.0,-1.0,0.6127266938015212],[26.66006442526558,29.206136974222197,0.0,2.0,6.0,2.0,-1.0,0.5282181332593525],[29.206136974222197,94.89480873730311,1860.0,2.0,6.0,2.0,-1.0,0.4102726671845269]]</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>[[-56.710381402183344,25.104963618499127,-1860.0,2.0,6.0,1.0,-1.0],[25.104963618499127,25.60383767350328,-1275.7341,1.0,6.0,2.0,-1.0],[25.60383767350328,28.597082003528257,0.0,1.0,5.0,3.0,-1.0],[28.597082003528257,29.09595605853241,708.65,0.0,5.0,3.0,-1.0],[29.09595605853241,92.45296104406091,1860.0,1.0,5.0,3.0,-1.0]]</t>
+          <t>[[-56.710381402183344,25.104963618499127,-1860.0,2.0,6.0,1.0,-1.0,0.6346639163918826],[25.104963618499127,25.60383767350328,-1275.7341,1.0,6.0,2.0,-1.0,0.60122701247622],[25.60383767350328,28.597082003528257,0.0,1.0,5.0,3.0,-1.0,0.5282181332593525],[28.597082003528257,29.09595605853241,708.65,0.0,5.0,3.0,-1.0,0.483281544800253],[29.09595605853241,92.45296104406091,1860.0,1.0,5.0,3.0,-1.0,0.4102726671845269]]</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>[[-58.426966318957994,25.730423827588908,-1860.0,2.0,5.0,1.0,-1.0],[25.730423827588908,26.243578645555658,-1275.7341,1.0,5.0,2.0,-1.0],[26.243578645555658,28.80935273538941,0.0,1.0,4.0,3.0,-1.0],[28.80935273538941,29.32250755335616,708.65,1.0,4.0,2.0,-1.0],[29.32250755335616,95.00632425310008,1860.0,1.0,5.0,1.0,-1.0]]</t>
+          <t>[[-58.426966318957994,25.730423827588908,-1860.0,2.0,5.0,1.0,-1.0,0.516718450317057],[25.730423827588908,26.243578645555658,-1275.7341,1.0,5.0,2.0,-1.0,0.4832815464013943],[26.243578645555658,28.80935273538941,0.0,1.0,4.0,3.0,-1.0,0.4102726671845269],[28.80935273538941,29.32250755335616,708.65,1.0,4.0,2.0,-1.0,0.36533607872542734],[29.32250755335616,95.00632425310008,1860.0,1.0,5.0,1.0,-1.0,0.29232720110970123]]</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>[[-57.47765915439056,26.709674677019102,-1860.0,9.0,12.0,2.0,0.0],[26.709674677019102,27.723979903903547,-1275.7341,0.0,5.0,1.0,-1.0],[27.723979903903547,30.766895584556913,0.0,1.0,4.0,2.0,-1.0],[30.766895584556913,94.16097226483527,1860.0,1.0,4.0,2.0,-1.0]]</t>
+          <t>[[-57.47765915439056,26.709674677019102,-1860.0,9.0,12.0,2.0,0.0,0.516718450317057],[26.709674677019102,27.723979903903547,-1275.7341,0.0,5.0,1.0,-1.0,0.4832815464013943],[27.723979903903547,30.766895584556913,0.0,1.0,4.0,2.0,-1.0,0.4102726671845269],[30.766895584556913,94.16097226483527,1860.0,1.0,4.0,2.0,-1.0,0.29232720110970123]]</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>[[-54.48868702728052,25.713558982146253,-1860.0,9.0,12.0,2.0,0.0],[25.713558982146253,26.674064922378918,-822.3269,8.0,12.0,3.0,0.0],[26.674064922378918,29.555582743076883,0.0,8.0,11.0,4.0,0.0],[29.555582743076883,89.10695103750153,1860.0,8.0,12.0,3.0,0.0]]</t>
+          <t>[[-54.48868702728052,25.713558982146253,-1860.0,9.0,12.0,2.0,0.0,0.623164233449587],[25.713558982146253,26.674064922378918,-822.3269,8.0,12.0,3.0,0.0,0.5637793271242859],[26.674064922378918,29.555582743076883,0.0,8.0,11.0,4.0,0.0,0.516718450317057],[29.555582743076883,89.10695103750153,1860.0,8.0,12.0,3.0,0.0,0.39877298424223134]]</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>[[-55.013845694876345,26.577236033412298,-1860.0,8.0,12.0,2.0,-1.0],[26.577236033412298,29.976864438757666,0.0,8.0,11.0,3.0,-1.0],[29.976864438757666,30.46252563952128,1117.85,8.0,11.0,3.0,-1.0],[30.46252563952128,90.19885333344689,1860.0,8.0,11.0,3.0,-1.0]]</t>
+          <t>[[-55.013845694876345,26.577236033412298,-1860.0,8.0,12.0,2.0,-1.0,0.623164233449587],[26.577236033412298,29.976864438757666,0.0,8.0,11.0,3.0,-1.0,0.516718450317057],[29.976864438757666,30.46252563952128,1117.85,8.0,11.0,3.0,-1.0,0.4458338593214958],[30.46252563952128,90.19885333344689,1860.0,8.0,11.0,3.0,-1.0,0.39877298424223134]]</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>[[-54.73432406704254,26.275421672518284,-1860.0,8.0,4.0,0.0,1.0],[26.275421672518284,26.754769280444684,-1808.4765,8.0,4.0,0.0,1.0],[26.754769280444684,29.630854928003053,0.0,8.0,4.0,1.0,1.0],[29.630854928003053,88.5906107029497,1860.0,9.0,4.0,0.0,1.0]]</t>
+          <t>[[-54.73432406704254,26.275421672518284,-1860.0,8.0,4.0,0.0,1.0,0.623164233449587],[26.275421672518284,26.754769280444684,-1808.4765,8.0,4.0,0.0,1.0,0.6202155994134425],[26.754769280444684,29.630854928003053,0.0,8.0,4.0,1.0,1.0,0.516718450317057],[29.630854928003053,88.5906107029497,1860.0,9.0,4.0,0.0,1.0,0.39877298424223134]]</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>[[-58.302466788037684,26.471255001882646,-1860.0,8.0,12.0,2.0,0.0],[26.471255001882646,27.498815266002886,-1023.2687,9.0,12.0,2.0,0.0],[27.498815266002886,30.0677159263035,0.0,9.0,11.0,3.0,0.0],[30.0677159263035,31.095276190423753,708.65,0.0,3.0,0.0,-1.0],[31.095276190423753,95.31779269793915,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-58.302466788037684,26.471255001882646,-1860.0,8.0,12.0,2.0,0.0,0.5052187673747615],[26.471255001882646,27.498815266002886,-1023.2687,9.0,12.0,2.0,0.0,0.4573335423747614],[27.498815266002886,30.0677159263035,0.0,9.0,11.0,3.0,0.0,0.3987729842422313],[30.0677159263035,31.095276190423753,708.65,0.0,3.0,0.0,-1.0,0.35383639578313175],[31.095276190423753,95.31779269793915,1860.0,0.0,3.0,0.0,-1.0,0.28082751816740564]]</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>[[-56.5172364587329,26.156779012077486,-1860.0,7.0,2.0,1.0,1.0],[26.156779012077486,26.65481524985345,-1808.4765,8.0,2.0,1.0,1.0],[26.65481524985345,29.14499643873328,0.0,8.0,2.0,1.0,1.0],[29.14499643873328,30.639105152061184,46.5,9.0,2.0,0.0,1.0],[30.639105152061184,92.395598636281,1860.0,9.0,2.0,0.0,1.0]]</t>
+          <t>[[-56.5172364587329,26.156779012077486,-1860.0,7.0,2.0,1.0,1.0,0.3872733012999358],[26.156779012077486,26.65481524985345,-1808.4765,8.0,2.0,1.0,1.0,0.3843246672637912],[26.65481524985345,29.14499643873328,0.0,8.0,2.0,1.0,1.0,0.2808275181674057],[29.14499643873328,30.639105152061184,46.5,9.0,2.0,0.0,1.0,0.2778788815155351],[30.639105152061184,92.395598636281,1860.0,9.0,2.0,0.0,1.0,0.16288205209258005]]</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>[[-58.67744969955918,25.268845322928478,-1860.0,7.0,1.0,1.0,1.0],[25.268845322928478,26.82340634186344,-1808.4765,8.0,1.0,1.0,1.0],[26.82340634186344,27.34159334817509,-1023.2687,9.0,10.0,4.0,0.0],[27.34159334817509,30.45071538604501,0.0,7.0,9.0,5.0,0.0],[30.45071538604501,30.96890239235666,708.65,0.0,1.0,0.0,-1.0],[30.96890239235666,96.26046518762485,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-58.67744969955918,25.268845322928478,-1860.0,7.0,1.0,1.0,1.0,0.2693278352251102],[25.268845322928478,26.82340634186344,-1808.4765,8.0,1.0,1.0,1.0,0.26637920118896563],[26.82340634186344,27.34159334817509,-1023.2687,9.0,10.0,4.0,0.0,0.22144261022511022],[27.34159334817509,30.45071538604501,0.0,7.0,9.0,5.0,0.0,0.1628820520925801],[30.45071538604501,30.96890239235666,708.65,0.0,1.0,0.0,-1.0,0.11794546363348055],[30.96890239235666,96.26046518762485,1860.0,0.0,1.0,0.0,-1.0,0.04493658601775448]]</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>[[-58.505262239381125,27.873519500558942,-1860.0,8.0,0.0,1.0,1.0],[27.873519500558942,28.390757714570555,-1808.4765,8.0,0.0,1.0,1.0],[28.390757714570555,31.49418699864026,0.0,7.0,0.0,1.0,1.0],[31.49418699864026,32.011425212651886,46.5,9.0,0.0,0.0,1.0],[32.011425212651886,96.1489637500924,708.6501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-58.505262239381125,27.873519500558942,-1860.0,8.0,0.0,1.0,1.0,0.15138236915028452],[27.873519500558942,28.390757714570555,-1808.4765,8.0,0.0,1.0,1.0,0.14843373511413996],[28.390757714570555,31.49418699864026,0.0,7.0,0.0,1.0,1.0,0.04493658601775442],[31.49418699864026,32.011425212651886,46.5,9.0,0.0,0.0,1.0,0.04198794936588378],[32.011425212651886,96.1489637500924,708.6501,0.0,0.0,0.0,-1.0,-8.782499227866225e-09]]</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>[[-59.10195097205732,28.244262165920127,-1860.0,7.0,0.0,0.0,1.0],[28.244262165920127,29.290324598710278,-1023.2687,9.0,9.0,4.0,-1.0],[29.290324598710278,32.42851189708073,0.0,8.0,9.0,4.0,-1.0],[32.42851189708073,97.28438273006998,708.6501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-59.10195097205732,28.244262165920127,-1860.0,7.0,0.0,0.0,1.0,0.15138236915028452],[28.244262165920127,29.290324598710278,-1023.2687,9.0,9.0,4.0,-1.0,0.10349714415028453],[29.290324598710278,32.42851189708073,0.0,8.0,9.0,4.0,-1.0,0.04493658601775442],[32.42851189708073,97.28438273006998,708.6501,0.0,0.0,0.0,-1.0,-8.782499227866225e-09]]</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>[[-56.82521952452722,27.524594182112118,-1860.0,6.0,0.0,0.0,1.0],[27.524594182112118,29.52103947694382,-1808.4765,7.0,0.0,0.0,1.0],[29.52103947694382,30.02015080065174,-1023.2687,8.0,9.0,4.0,-1.0],[30.02015080065174,33.51393006660721,0.0,8.0,9.0,4.0,-1.0],[33.51393006660721,34.51215271402307,755.15,9.0,9.0,3.0,-1.0],[34.51215271402307,92.40906626414235,1860.0,9.0,9.0,3.0,-1.0]]</t>
+          <t>[[-56.82521952452722,27.524594182112118,-1860.0,6.0,0.0,0.0,1.0,0.25782815228281464],[27.524594182112118,29.52103947694382,-1808.4765,7.0,0.0,0.0,1.0,0.25487951824667004],[29.52103947694382,30.02015080065174,-1023.2687,8.0,9.0,4.0,-1.0,0.2099429272828146],[30.02015080065174,33.51393006660721,0.0,8.0,9.0,4.0,-1.0,0.1513823691502845],[33.51393006660721,34.51215271402307,755.15,9.0,9.0,3.0,-1.0,0.10349714403931429],[34.51215271402307,92.40906626414235,1860.0,9.0,9.0,3.0,-1.0,0.033436903075458865]]</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>[[-55.29153364869517,26.94176999579944,-1860.0,6.0,0.0,0.0,1.0],[26.94176999579944,28.392945942466987,-1808.4765,5.0,0.0,0.0,1.0],[28.392945942466987,31.77902315135794,0.0,8.0,9.0,3.0,-1.0],[31.77902315135794,32.74647378246964,755.15,8.0,9.0,3.0,-1.0],[32.74647378246964,89.34233570250416,1860.0,7.0,9.0,3.0,-1.0]]</t>
+          <t>[[-55.29153364869517,26.94176999579944,-1860.0,6.0,0.0,0.0,1.0,0.3642739354153447],[26.94176999579944,28.392945942466987,-1808.4765,5.0,0.0,0.0,1.0,0.3613253013792001],[28.392945942466987,31.77902315135794,0.0,8.0,9.0,3.0,-1.0,0.2578281522828146],[31.77902315135794,32.74647378246964,755.15,8.0,9.0,3.0,-1.0,0.20994292717184437],[32.74647378246964,89.34233570250416,1860.0,7.0,9.0,3.0,-1.0,0.13988268620798894]]</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>[[-47.66196007472534,27.491000204955057,-1860.0,5.0,0.0,0.0,1.0],[27.491000204955057,29.312890151129125,-1808.4765,4.0,0.0,0.0,1.0],[29.312890151129125,29.768362637672638,-1023.2687,5.0,9.0,4.0,-1.0],[29.768362637672638,32.956670043477274,0.0,5.0,8.0,5.0,-1.0],[32.956670043477274,88.5243134017864,1860.0,6.0,9.0,4.0,-1.0]]</t>
+          <t>[[-47.66196007472534,27.491000204955057,-1860.0,5.0,0.0,0.0,1.0,0.4707197185478749],[27.491000204955057,29.312890151129125,-1808.4765,4.0,0.0,0.0,1.0,0.46777108451173033],[29.312890151129125,29.768362637672638,-1023.2687,5.0,9.0,4.0,-1.0,0.42283449354787495],[29.768362637672638,32.956670043477274,0.0,5.0,8.0,5.0,-1.0,0.3642739354153448],[32.956670043477274,88.5243134017864,1860.0,6.0,9.0,4.0,-1.0,0.24632846934051916]]</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>[[-35.01344452876235,27.754588035486,-1860.0,3.0,0.0,0.0,1.0],[27.754588035486,28.909827898631683,-1808.4765,3.0,0.0,0.0,1.0],[28.909827898631683,29.29490785301357,-1224.2106,5.0,10.0,2.0,-1.0],[29.29490785301357,32.375547488068705,0.0,6.0,9.0,3.0,-1.0],[32.375547488068705,32.7606274424506,755.15,5.0,9.0,3.0,-1.0],[32.7606274424506,80.12546183142328,1860.0,5.0,10.0,2.0,-1.0]]</t>
+          <t>[[-35.01344452876235,27.754588035486,-1860.0,3.0,0.0,0.0,1.0,0.577165501680405],[27.754588035486,28.909827898631683,-1808.4765,3.0,0.0,0.0,1.0,0.5742168676442605],[28.909827898631683,29.29490785301357,-1224.2106,5.0,10.0,2.0,-1.0,0.5407799637285978],[29.29490785301357,32.375547488068705,0.0,6.0,9.0,3.0,-1.0,0.4707197185478749],[32.375547488068705,32.7606274424506,755.15,5.0,9.0,3.0,-1.0,0.4228344934369047],[32.7606274424506,80.12546183142328,1860.0,5.0,10.0,2.0,-1.0,0.3527742524730493]]</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>[[-31.34244446021263,26.50898874190432,-1860.0,2.0,0.0,0.0,1.0],[26.50898874190432,29.51425799915715,-1808.4765,2.0,0.0,0.0,1.0],[29.51425799915715,29.889916656313755,-1023.2687,4.0,9.0,4.0,-1.0],[29.889916656313755,32.89518591356658,0.0,3.0,9.0,4.0,-1.0],[32.89518591356658,33.64650322787979,755.15,4.0,9.0,3.0,-1.0],[33.64650322787979,80.97949402961183,1860.0,4.0,10.0,2.0,-1.0]]</t>
+          <t>[[-31.34244446021263,26.50898874190432,-1860.0,2.0,0.0,0.0,1.0,0.683611284812935],[26.50898874190432,29.51425799915715,-1808.4765,2.0,0.0,0.0,1.0,0.6806626507767904],[29.51425799915715,29.889916656313755,-1023.2687,4.0,9.0,4.0,-1.0,0.6357260598129351],[29.889916656313755,32.89518591356658,0.0,3.0,9.0,4.0,-1.0,0.5771655016804049],[32.89518591356658,33.64650322787979,755.15,4.0,9.0,3.0,-1.0,0.5292802765694348],[33.64650322787979,80.97949402961183,1860.0,4.0,10.0,2.0,-1.0,0.4592200356055793]]</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>[[-30.50036519670833,28.343972004871922,-1860.0,2.0,0.0,0.0,1.0],[28.343972004871922,29.824332689188402,-1808.4765,2.0,0.0,0.0,1.0],[29.824332689188402,33.1551442289005,0.0,3.0,10.0,3.0,-1.0],[33.1551442289005,33.52523439997961,573.8,4.0,10.0,2.0,-1.0],[33.52523439997961,80.15659595594887,1860.0,5.0,11.0,1.0,-1.0]]</t>
+          <t>[[-30.50036519670833,28.343972004871922,-1860.0,2.0,0.0,0.0,1.0,0.790057067945465],[28.343972004871922,29.824332689188402,-1808.4765,2.0,0.0,0.0,1.0,0.7871084339093205],[29.824332689188402,33.1551442289005,0.0,3.0,10.0,3.0,-1.0,0.683611284812935],[33.1551442289005,33.52523439997961,573.8,4.0,10.0,2.0,-1.0,0.6472257426442602],[33.52523439997961,80.15659595594887,1860.0,5.0,11.0,1.0,-1.0,0.5656658187381094]]</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>[[-28.287492166665018,26.004245782391486,-1860.0,1.0,0.0,0.0,1.0],[26.004245782391486,29.136461433298592,-1808.4765,0.0,0.0,0.0,1.0],[29.136461433298592,29.484485394510493,-1224.2106,2.0,10.0,3.0,-1.0],[29.484485394510493,32.6167010454176,0.0,3.0,9.0,4.0,-1.0],[32.6167010454176,33.6607729290533,755.15,2.0,9.0,3.0,-1.0],[33.6607729290533,75.77167223569327,1860.0,2.0,9.0,3.0,-1.0]]</t>
+          <t>[[-28.287492166665018,26.004245782391486,-1860.0,1.0,0.0,0.0,1.0,0.8965028510779951],[26.004245782391486,29.136461433298592,-1808.4765,0.0,0.0,0.0,1.0,0.8935542170418506],[29.136461433298592,29.484485394510493,-1224.2106,2.0,10.0,3.0,-1.0,0.8601173131261879],[29.484485394510493,32.6167010454176,0.0,3.0,9.0,4.0,-1.0,0.790057067945465],[32.6167010454176,33.6607729290533,755.15,2.0,9.0,3.0,-1.0,0.7421718428344949],[33.6607729290533,75.77167223569327,1860.0,2.0,9.0,3.0,-1.0,0.6721116018706395]]</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>[0,0.3480239612,3.1322156509,0,1.0440718836]</t>
+          <t>[3.1322156509,0.3480239612,3.1322156509,0,1.0440718836]</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>[[-30.136449600046355,-0.3384854497553178,-1860.0,1.0,0.0,0.0,1.0],[-0.3384854497553178,29.822868507246582,-1860.0,0.0,0.0,0.0,1.0],[29.822868507246582,33.09337676764438,0.0,2.0,9.0,4.0,-1.0],[33.09337676764438,33.82015638106611,708.65,2.0,9.0,4.0,-1.0],[33.82015638106611,78.51710260650268,1860.0,2.0,9.0,4.0,-1.0]]</t>
+          <t>[[-30.136449600046355,-0.3384854497553178,-1860.0,1.0,0.0,0.0,1.0,1.0000000001743807],[-0.3384854497553178,29.822868507246582,-1860.0,0.0,0.0,0.0,1.0,1.0000000001743807],[29.822868507246582,33.09337676764438,0.0,2.0,9.0,4.0,-1.0,0.8935542170418506],[33.09337676764438,33.82015638106611,708.65,2.0,9.0,4.0,-1.0,0.848617628582751],[33.82015638106611,78.51710260650268,1860.0,2.0,9.0,4.0,-1.0,0.775608750967025]]</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>[[-29.816817257821768,31.387561335967867,0.0,0.0,0.0,1.0,1.0],[31.387561335967867,32.12054790595337,708.65,1.0,9.0,3.0,-1.0],[32.12054790595337,79.76467495501117,1860.0,1.0,10.0,2.0,-1.0]]</t>
+          <t>[[-29.816817257821768,31.387561335967867,0.0,0.0,0.0,1.0,1.0,1.000000000174381],[31.387561335967867,32.12054790595337,708.65,1.0,9.0,3.0,-1.0,0.9550634117152814],[32.12054790595337,79.76467495501117,1860.0,1.0,10.0,2.0,-1.0,0.8820545340995554]]</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>[[-29.85335593936555,28.727571319855187,-785.2079,0.0,0.0,0.0,1.0],[28.727571319855187,31.982067278700782,0.0,0.0,8.0,5.0,-1.0],[31.982067278700782,32.70528860288869,181.35,0.0,8.0,4.0,-1.0],[32.70528860288869,78.26823202672705,1860.0,0.0,9.0,3.0,-1.0]]</t>
+          <t>[[-29.85335593936555,28.727571319855187,-785.2079,0.0,0.0,0.0,1.0,1.0000000084020282],[28.727571319855187,31.982067278700782,0.0,0.0,8.0,5.0,-1.0,0.9550634117152812],[31.982067278700782,32.70528860288869,181.35,0.0,8.0,4.0,-1.0,0.9435637287729857],[32.70528860288869,78.26823202672705,1860.0,0.0,9.0,3.0,-1.0,0.8371179456404556]]</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>[[-30.076888106035895,28.339306156413507,-1860.0,2.0,8.0,2.0,-1.0],[28.339306156413507,31.6048076990349,0.0,1.0,8.0,4.0,-1.0],[31.6048076990349,78.41032980994157,1860.0,1.0,8.0,3.0,-1.0]]</t>
+          <t>[[-30.076888106035895,28.339306156413507,-1860.0,2.0,8.0,2.0,-1.0,0.9435637287729857],[28.339306156413507,31.6048076990349,0.0,1.0,8.0,4.0,-1.0,0.8371179456404556],[31.6048076990349,78.41032980994157,1860.0,1.0,8.0,3.0,-1.0,0.71917247956563]]</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>[[-41.06631671354253,28.265628904419394,-1860.0,2.0,7.0,1.0,-1.0],[28.265628904419394,31.567150124322346,0.0,1.0,7.0,3.0,-1.0],[31.567150124322346,99.95580396516915,1860.0,2.0,7.0,1.0,-1.0]]</t>
+          <t>[[-41.06631671354253,28.265628904419394,-1860.0,2.0,7.0,1.0,-1.0,0.8256182626981601],[28.265628904419394,31.567150124322346,0.0,1.0,7.0,3.0,-1.0,0.71917247956563],[31.567150124322346,99.95580396516915,1860.0,2.0,7.0,1.0,-1.0,0.6012270134908044]]</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>[[-40.982529982121534,28.287940321289057,-1860.0,2.0,6.0,1.0,-1.0],[28.287940321289057,31.60912725364436,0.0,1.0,6.0,3.0,-1.0],[31.60912725364436,100.87959755705492,1860.0,1.0,6.0,3.0,-1.0]]</t>
+          <t>[[-40.982529982121534,28.287940321289057,-1860.0,2.0,6.0,1.0,-1.0,0.7076727966233345],[28.287940321289057,31.60912725364436,0.0,1.0,6.0,3.0,-1.0,0.6012270134908044],[31.60912725364436,100.87959755705492,1860.0,1.0,6.0,3.0,-1.0,0.4832815474159788]]</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>[[-38.206210027271354,28.422677289257663,-1860.0,2.0,6.0,1.0,-1.0],[28.422677289257663,29.31106245347806,-200.9418,2.0,6.0,1.0,-1.0],[29.31106245347806,32.420410528249406,0.0,2.0,5.0,2.0,-1.0],[32.420410528249406,33.3087956924698,1678.65,2.0,5.0,2.0,-1.0],[33.3087956924698,94.60737202367648,1860.0,2.0,5.0,2.0,-1.0]]</t>
+          <t>[[-38.206210027271354,28.422677289257663,-1860.0,2.0,6.0,1.0,-1.0,0.5897273305485089],[28.422677289257663,29.31106245347806,-200.9418,2.0,6.0,1.0,-1.0,0.49478122874128],[29.31106245347806,32.420410528249406,0.0,2.0,5.0,2.0,-1.0,0.4832815474159788],[32.420410528249406,33.3087956924698,1678.65,2.0,5.0,2.0,-1.0,0.37683576428344867],[33.3087956924698,94.60737202367648,1860.0,2.0,5.0,2.0,-1.0,0.36533608134115314]]</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>[[-39.767064622806856,28.786438361405942,-1860.0,2.0,4.0,2.0,-1.0],[28.786438361405942,32.49203311730933,0.0,1.0,4.0,3.0,-1.0],[32.49203311730933,33.8816311507731,1678.65,1.0,4.0,1.0,-1.0],[33.8816311507731,98.7295393790825,1860.0,1.0,4.0,1.0,-1.0]]</t>
+          <t>[[-39.767064622806856,28.786438361405942,-1860.0,2.0,4.0,2.0,-1.0,0.4717818644736832],[28.786438361405942,32.49203311730933,0.0,1.0,4.0,3.0,-1.0,0.3653360813411531],[32.49203311730933,33.8816311507731,1678.65,1.0,4.0,1.0,-1.0,0.25889029820862297],[33.8816311507731,98.7295393790825,1860.0,1.0,4.0,1.0,-1.0,0.24739061526632744]]</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>[[-40.37314484830769,29.108863642580218,-1860.0,2.0,3.0,2.0,-1.0],[29.108863642580218,32.83944127967487,0.0,1.0,3.0,3.0,-1.0],[32.83944127967487,33.30576348431171,1678.65,2.0,3.0,1.0,-1.0],[33.30576348431171,99.05719433810496,1860.0,2.0,3.0,1.0,-1.0]]</t>
+          <t>[[-40.37314484830769,29.108863642580218,-1860.0,2.0,3.0,2.0,-1.0,0.3538363983988576],[29.108863642580218,32.83944127967487,0.0,1.0,3.0,3.0,-1.0,0.2473906152663275],[32.83944127967487,33.30576348431171,1678.65,2.0,3.0,1.0,-1.0,0.14094483213379738],[33.30576348431171,99.05719433810496,1860.0,2.0,3.0,1.0,-1.0,0.12944514919150185]]</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>[[-39.9312137528976,28.195043834873594,-1860.0,2.0,3.0,0.0,-1.0],[28.195043834873594,34.63941955263574,0.0,1.0,3.0,2.0,-1.0],[34.63941955263574,35.099732103904465,1678.65,2.0,3.0,0.0,-1.0],[35.099732103904465,97.70223907645095,1860.0,2.0,3.0,0.0,-1.0]]</t>
+          <t>[[-39.9312137528976,28.195043834873594,-1860.0,2.0,3.0,0.0,-1.0,0.3538363983988576],[28.195043834873594,34.63941955263574,0.0,1.0,3.0,2.0,-1.0,0.2473906152663275],[34.63941955263574,35.099732103904465,1678.65,2.0,3.0,0.0,-1.0,0.14094483213379738],[35.099732103904465,97.70223907645095,1860.0,2.0,3.0,0.0,-1.0,0.12944514919150185]]</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>[[-38.81078372171171,29.672954440553802,-1860.0,9.0,11.0,3.0,0.0],[29.672954440553802,30.123505349516073,-1607.5346,9.0,11.0,3.0,0.0],[30.123505349516073,34.17846353017652,0.0,1.0,3.0,1.0,-1.0],[34.17846353017652,95.90393805800792,1860.0,1.0,3.0,1.0,-1.0]]</t>
+          <t>[[-38.81078372171171,29.672954440553802,-1860.0,9.0,11.0,3.0,0.0,0.3538363983988576],[29.672954440553802,30.123505349516073,-1607.5346,9.0,11.0,3.0,0.0,0.33938807731452025],[30.123505349516073,34.17846353017652,0.0,1.0,3.0,1.0,-1.0,0.2473906152663275],[34.17846353017652,95.90393805800792,1860.0,1.0,3.0,1.0,-1.0,0.12944514919150185]]</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>[[-40.42276711654497,30.94431522854996,-1860.0,9.0,3.0,1.0,1.0],[30.94431522854996,31.41383550713612,-733.6842,9.0,3.0,1.0,1.0],[31.41383550713612,34.70047745723917,0.0,9.0,2.0,2.0,1.0],[34.70047745723917,35.169997735825326,1197.85,9.0,2.0,2.0,1.0],[35.169997735825326,99.96379618071413,1860.0,9.0,2.0,2.0,1.0]]</t>
+          <t>[[-40.42276711654497,30.94431522854996,-1860.0,9.0,3.0,1.0,1.0,0.4602821815313877],[30.94431522854996,31.41383550713612,-733.6842,9.0,3.0,1.0,1.0,0.3958243496036769],[31.41383550713612,34.70047745723917,0.0,9.0,2.0,2.0,1.0,0.3538363983988576],[34.70047745723917,35.169997735825326,1197.85,9.0,2.0,2.0,1.0,0.27787888413126094],[35.169997735825326,99.96379618071413,1860.0,9.0,2.0,2.0,1.0,0.23589093232403197]]</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>[[-42.26436372586337,26.585215308604184,-1860.0,9.0,3.0,0.0,1.0],[26.585215308604184,28.52464007013848,-733.6842,8.0,3.0,1.0,1.0],[28.52464007013848,31.91863340282351,0.0,8.0,2.0,2.0,1.0],[31.91863340282351,32.88834578359066,1197.85,8.0,2.0,2.0,1.0],[32.88834578359066,102.70763719882537,1860.0,8.0,3.0,1.0,1.0]]</t>
+          <t>[[-42.26436372586337,26.585215308604184,-1860.0,9.0,3.0,0.0,1.0,0.5667279646639178],[26.585215308604184,28.52464007013848,-733.6842,8.0,3.0,1.0,1.0,0.502270132736207],[28.52464007013848,31.91863340282351,0.0,8.0,2.0,2.0,1.0,0.4602821815313877],[31.91863340282351,32.88834578359066,1197.85,8.0,2.0,2.0,1.0,0.384324667263791],[32.88834578359066,102.70763719882537,1860.0,8.0,3.0,1.0,1.0,0.3423367154565621]]</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>[[-40.304693299273865,26.62272168760319,-1860.0,9.0,2.0,0.0,1.0],[26.62272168760319,28.026793330684526,-733.6842,8.0,2.0,1.0,1.0],[28.026793330684526,31.30296049787431,0.0,8.0,1.0,2.0,1.0],[31.30296049787431,32.70703214095565,1197.85,8.0,1.0,2.0,1.0],[32.70703214095565,99.63444712783269,1860.0,8.0,2.0,1.0,1.0]]</t>
+          <t>[[-40.304693299273865,26.62272168760319,-1860.0,9.0,2.0,0.0,1.0,0.4487824985890922],[26.62272168760319,28.026793330684526,-733.6842,8.0,2.0,1.0,1.0,0.3843246666613814],[28.026793330684526,31.30296049787431,0.0,8.0,1.0,2.0,1.0,0.3423367154565621],[31.30296049787431,32.70703214095565,1197.85,8.0,1.0,2.0,1.0,0.2663792011889654],[32.70703214095565,99.63444712783269,1860.0,8.0,2.0,1.0,1.0,0.22439124938173644]]</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>[[-44.03622751139168,25.878268929674014,-1860.0,9.0,1.0,0.0,1.0],[25.878268929674014,27.90477607289332,-733.6842,8.0,1.0,1.0,1.0],[27.90477607289332,30.944536787722264,0.0,8.0,0.0,2.0,1.0],[30.944536787722264,31.957790359331902,1197.85,8.0,0.0,2.0,1.0],[31.957790359331902,107.44518144425066,1860.0,8.0,1.0,1.0,1.0]]</t>
+          <t>[[-44.03622751139168,25.878268929674014,-1860.0,9.0,1.0,0.0,1.0,0.33083703251426655],[25.878268929674014,27.90477607289332,-733.6842,8.0,1.0,1.0,1.0,0.2663792005865557],[27.90477607289332,30.944536787722264,0.0,8.0,0.0,2.0,1.0,0.2243912493817364],[30.944536787722264,31.957790359331902,1197.85,8.0,0.0,2.0,1.0,0.1484337351141397],[31.957790359331902,107.44518144425066,1860.0,8.0,1.0,1.0,1.0,0.10644578330691078]]</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>[[-41.863054902351486,26.297348904450722,-1860.0,9.0,0.0,0.0,1.0],[26.297348904450722,28.714384500436616,-733.6842,8.0,0.0,1.0,1.0],[28.714384500436616,32.09823433481687,0.0,8.0,0.0,1.0,1.0],[32.09823433481687,39.349341122774554,1016.5,9.0,0.0,0.0,1.0],[39.349341122774554,102.67567373760497,1678.6501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-41.863054902351486,26.297348904450722,-1860.0,9.0,0.0,0.0,1.0,0.2128915664394409],[26.297348904450722,28.714384500436616,-733.6842,8.0,0.0,1.0,1.0,0.1484337345117301],[28.714384500436616,32.09823433481687,0.0,8.0,0.0,1.0,1.0,0.1064457833069108],[32.09823433481687,39.349341122774554,1016.5,9.0,0.0,0.0,1.0,0.041987951981609595],[39.349341122774554,102.67567373760497,1678.6501,0.0,0.0,0.0,-1.0,-6.166773411364623e-09]]</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>[[-39.815359711424925,29.879390973550834,-1860.0,8.0,0.0,0.0,1.0],[29.879390973550834,31.72560953474224,-733.6842,8.0,0.0,0.0,1.0],[31.72560953474224,34.95649201682722,0.0,8.0,0.0,1.0,1.0],[34.95649201682722,40.03359306010359,1016.5,9.0,0.0,0.0,1.0],[40.03359306010359,98.18947773763304,1678.6501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-39.815359711424925,29.879390973550834,-1860.0,8.0,0.0,0.0,1.0,0.2128915664394409],[29.879390973550834,31.72560953474224,-733.6842,8.0,0.0,0.0,1.0,0.1484337345117301],[31.72560953474224,34.95649201682722,0.0,8.0,0.0,1.0,1.0,0.1064457833069108],[34.95649201682722,40.03359306010359,1016.5,9.0,0.0,0.0,1.0,0.041987951981609595],[40.03359306010359,98.18947773763304,1678.6501,0.0,0.0,0.0,-1.0,-6.166773411364623e-09]]</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>[[-40.97179168165544,30.728682104517752,-1860.0,6.0,0.0,0.0,1.0],[30.728682104517752,34.502391251158436,-733.6842,7.0,0.0,0.0,1.0],[34.502391251158436,38.276100397799134,0.0,6.0,0.0,1.0,1.0],[38.276100397799134,40.63466861444957,1016.5,8.0,0.0,0.0,1.0],[40.63466861444957,100.0705876740405,1860.0,8.0,9.0,3.0,-1.0]]</t>
+          <t>[[-40.97179168165544,30.728682104517752,-1860.0,6.0,0.0,0.0,1.0,0.319337349571971],[30.728682104517752,34.502391251158436,-733.6842,7.0,0.0,0.0,1.0,0.2548795176442602],[34.502391251158436,38.276100397799134,0.0,6.0,0.0,1.0,1.0,0.2128915664394409],[38.276100397799134,40.63466861444957,1016.5,8.0,0.0,0.0,1.0,0.1484337351141397],[40.63466861444957,100.0705876740405,1860.0,8.0,9.0,3.0,-1.0,0.09494610036461527]]</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>[[-42.19061691513114,29.18221342597692,-1860.0,5.0,0.0,0.0,1.0],[29.18221342597692,31.609860716490793,-733.6842,5.0,0.0,0.0,1.0],[31.609860716490793,35.00856692321023,0.0,5.0,0.0,1.0,1.0],[35.00856692321023,39.86386150423798,1016.5,6.0,0.0,0.0,1.0],[39.86386150423798,41.320449878546306,1725.15,7.0,9.0,2.0,-1.0],[41.320449878546306,102.98269105759884,1860.0,7.0,9.0,2.0,-1.0]]</t>
+          <t>[[-42.19061691513114,29.18221342597692,-1860.0,5.0,0.0,0.0,1.0,0.42578313270450113],[29.18221342597692,31.609860716490793,-733.6842,5.0,0.0,0.0,1.0,0.3613253007767903],[31.609860716490793,35.00856692321023,0.0,5.0,0.0,1.0,1.0,0.319337349571971],[35.00856692321023,39.86386150423798,1016.5,6.0,0.0,0.0,1.0,0.2548795182466698],[39.86386150423798,41.320449878546306,1725.15,7.0,9.0,2.0,-1.0,0.20994292978757026],[41.320449878546306,102.98269105759884,1860.0,7.0,9.0,2.0,-1.0,0.20139188349714537]]</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>[[-43.93785109142626,28.036155095056195,-1860.0,5.0,0.0,0.0,1.0],[28.036155095056195,33.572617109401,-733.6842,4.0,0.0,0.0,1.0],[33.572617109401,37.09582020943861,0.0,4.0,0.0,1.0,1.0],[37.09582020943861,39.612393852322604,1016.5,4.0,0.0,0.0,1.0],[39.612393852322604,106.55325275303704,1860.0,6.0,9.0,3.0,-1.0]]</t>
+          <t>[[-43.93785109142626,28.036155095056195,-1860.0,5.0,0.0,0.0,1.0,0.5322289158370312],[28.036155095056195,33.572617109401,-733.6842,4.0,0.0,0.0,1.0,0.4677710839093204],[33.572617109401,37.09582020943861,0.0,4.0,0.0,1.0,1.0,0.4257831327045011],[37.09582020943861,39.612393852322604,1016.5,4.0,0.0,0.0,1.0,0.3613253013791999],[39.612393852322604,106.55325275303704,1860.0,6.0,9.0,3.0,-1.0,0.30783766662967543]]</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>[[-35.57149175131278,29.877921425122466,-1860.0,3.0,0.0,0.0,1.0],[29.877921425122466,33.08173885333959,-733.6842,3.0,0.0,0.0,1.0],[33.08173885333959,36.74324448558771,0.0,3.0,0.0,1.0,1.0],[36.74324448558771,40.40475011783583,1016.5,4.0,0.0,0.0,1.0],[40.40475011783583,101.27728125396092,1860.0,4.0,9.0,3.0,-1.0]]</t>
+          <t>[[-35.57149175131278,29.877921425122466,-1860.0,3.0,0.0,0.0,1.0,0.6386746989695613],[29.877921425122466,33.08173885333959,-733.6842,3.0,0.0,0.0,1.0,0.5742168670418505],[33.08173885333959,36.74324448558771,0.0,3.0,0.0,1.0,1.0,0.5322289158370312],[36.74324448558771,40.40475011783583,1016.5,4.0,0.0,0.0,1.0,0.46777108451173005],[40.40475011783583,101.27728125396092,1860.0,4.0,9.0,3.0,-1.0,0.4142834497622056]]</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>[[-34.418783672089745,29.072945313644233,-1860.0,3.0,0.0,0.0,1.0],[29.072945313644233,31.700189271674603,-733.6842,2.0,0.0,0.0,1.0],[31.700189271674603,35.203181215715105,0.0,2.0,0.0,1.0,1.0],[35.203181215715105,40.019795138770775,1016.5,3.0,0.0,0.0,1.0],[40.019795138770775,96.50554023642377,1860.0,3.0,9.0,3.0,-1.0]]</t>
+          <t>[[-34.418783672089745,29.072945313644233,-1860.0,3.0,0.0,0.0,1.0,0.7451204821020914],[29.072945313644233,31.700189271674603,-733.6842,2.0,0.0,0.0,1.0,0.6806626501743805],[31.700189271674603,35.203181215715105,0.0,2.0,0.0,1.0,1.0,0.6386746989695613],[35.203181215715105,40.019795138770775,1016.5,3.0,0.0,0.0,1.0,0.57421686764426],[40.019795138770775,96.50554023642377,1860.0,3.0,9.0,3.0,-1.0,0.5207292328947357]]</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>[[-34.6118625032573,23.070339347829012,-1860.0,1.0,0.0,0.0,1.0],[23.070339347829012,31.56616752744638,-733.6842,2.0,0.0,0.0,1.0],[31.56616752744638,35.143358339916844,0.0,2.0,0.0,1.0,1.0],[35.143358339916844,38.72054915238732,1016.5,2.0,0.0,0.0,1.0],[38.72054915238732,99.0856441128265,1860.0,3.0,9.0,3.0,-1.0]]</t>
+          <t>[[-34.6118625032573,23.070339347829012,-1860.0,1.0,0.0,0.0,1.0,0.8515662652346214],[23.070339347829012,31.56616752744638,-733.6842,2.0,0.0,0.0,1.0,0.7871084333069106],[31.56616752744638,35.143358339916844,0.0,2.0,0.0,1.0,1.0,0.7451204821020914],[35.143358339916844,38.72054915238732,1016.5,2.0,0.0,0.0,1.0,0.6806626507767901],[38.72054915238732,99.0856441128265,1860.0,3.0,9.0,3.0,-1.0,0.6271750160272658]]</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>[[-39.329954107182246,32.04638640470476,-1860.0,1.0,0.0,0.0,1.0],[32.04638640470476,40.41464701644324,0.0,2.0,0.0,1.0,1.0],[40.41464701644324,107.85298253457094,1860.0,1.0,8.0,4.0,-1.0]]</t>
+          <t>[[-39.329954107182246,32.04638640470476,-1860.0,1.0,0.0,0.0,1.0,0.8935542164394408],[32.04638640470476,40.41464701644324,0.0,2.0,0.0,1.0,1.0,0.7871084333069106],[40.41464701644324,107.85298253457094,1860.0,1.0,8.0,4.0,-1.0,0.669162967232085]]</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>[[-36.02597796792387,31.583703347414662,-1860.0,1.0,0.0,0.0,1.0],[31.583703347414662,41.17696893945594,0.0,0.0,0.0,1.0,1.0],[41.17696893945594,41.63379111050552,890.0,0.0,8.0,4.0,-1.0],[41.63379111050552,100.56385117590196,1860.0,0.0,8.0,4.0,-1.0]]</t>
+          <t>[[-36.02597796792387,31.583703347414662,-1860.0,1.0,0.0,0.0,1.0,0.9999999995719708],[31.583703347414662,41.17696893945594,0.0,0.0,0.0,1.0,1.0,0.8935542164394408],[41.17696893945594,41.63379111050552,890.0,0.0,8.0,4.0,-1.0,0.8371179450380457],[41.63379111050552,100.56385117590196,1860.0,0.0,8.0,4.0,-1.0,0.7756087503646152]]</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>[0,0,0,0,0.456822171]</t>
+          <t>[0,0,9.593265592,0,0.456822171]</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>[[-36.676551202937915,40.25863071614498,0.0,0.0,0.0,1.0,1.0],[40.25863071614498,101.89946924167523,1860.0,1.0,9.0,2.0,-1.0]]</t>
+          <t>[[-36.676551202937915,40.25863071614498,0.0,0.0,0.0,1.0,1.0,0.9999999995719708],[40.25863071614498,101.89946924167523,1860.0,1.0,9.0,2.0,-1.0,0.8820545334971452]]</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>[[-34.5911549034346,39.8666753576712,0.0,0.0,0.0,1.0,1.0],[39.8666753576712,97.92605490650962,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[-34.5911549034346,39.8666753576712,0.0,0.0,0.0,1.0,1.0,0.9999999995719708],[39.8666753576712,97.92605490650962,1860.0,0.0,8.0,3.0,-1.0,0.8820545334971452]]</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>[[-35.85648095898932,35.684936037634245,-1860.0,1.0,9.0,0.0,-1.0],[35.684936037634245,39.33035855975518,0.0,1.0,8.0,1.0,-1.0],[39.33035855975518,39.7860363750203,708.65,1.0,8.0,1.0,-1.0],[39.7860363750203,100.39118580528103,1860.0,1.0,8.0,1.0,-1.0]]</t>
+          <t>[[-35.85648095898932,35.684936037634245,-1860.0,1.0,9.0,0.0,-1.0,0.9885003166296753],[35.684936037634245,39.33035855975518,0.0,1.0,8.0,1.0,-1.0,0.8820545334971452],[39.33035855975518,39.7860363750203,708.65,1.0,8.0,1.0,-1.0,0.8371179450380457],[39.7860363750203,100.39118580528103,1860.0,1.0,8.0,1.0,-1.0,0.7641090674223197]]</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>[[-36.83546633851479,35.517555688794545,-1860.0,1.0,7.0,1.0,-1.0],[35.517555688794545,36.9089599585505,-1074.7923,0.0,7.0,2.0,-1.0],[36.9089599585505,40.61937134456636,0.0,0.0,6.0,3.0,-1.0],[40.61937134456636,41.08317276781834,890.0,0.0,6.0,3.0,-1.0],[41.08317276781834,101.84115921382809,1860.0,0.0,7.0,2.0,-1.0]]</t>
+          <t>[[-36.83546633851479,35.517555688794545,-1860.0,1.0,7.0,1.0,-1.0,0.8705548505548497],[35.517555688794545,36.9089599585505,-1074.7923,0.0,7.0,2.0,-1.0,0.8256182653138859],[36.9089599585505,40.61937134456636,0.0,0.0,6.0,3.0,-1.0,0.7641090674223197],[40.61937134456636,41.08317276781834,890.0,0.0,6.0,3.0,-1.0,0.7076727960209246],[41.08317276781834,101.84115921382809,1860.0,0.0,7.0,2.0,-1.0,0.6461636013474941]]</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>[[-36.126573921264566,35.56762793289505,-1860.0,1.0,6.0,1.0,-1.0],[35.56762793289505,36.486784366922734,-1074.7923,0.0,6.0,2.0,-1.0],[36.486784366922734,40.163410103033485,0.0,0.0,6.0,2.0,-1.0],[40.163410103033485,41.54214475407501,708.65,1.0,6.0,1.0,-1.0],[41.54214475407501,101.28731296587469,1860.0,1.0,6.0,1.0,-1.0]]</t>
+          <t>[[-36.126573921264566,35.56762793289505,-1860.0,1.0,6.0,1.0,-1.0,0.7526093844800241],[35.56762793289505,36.486784366922734,-1074.7923,0.0,6.0,2.0,-1.0,0.7076727992390603],[36.486784366922734,40.163410103033485,0.0,0.0,6.0,2.0,-1.0,0.6461636013474941],[40.163410103033485,41.54214475407501,708.65,1.0,6.0,1.0,-1.0,0.6012270128883945],[41.54214475407501,101.28731296587469,1860.0,1.0,6.0,1.0,-1.0,0.5282181352726685]]</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>[[-37.21605931685209,35.29872780370737,-1860.0,1.0,6.0,0.0,-1.0],[35.29872780370737,35.76656513996905,-1275.7341,1.0,6.0,0.0,-1.0],[35.76656513996905,39.509263830062444,0.0,1.0,5.0,1.0,-1.0],[39.509263830062444,39.97710116632411,708.65,1.0,5.0,1.0,-1.0],[39.97710116632411,102.66730422538842,1860.0,1.0,5.0,1.0,-1.0]]</t>
+          <t>[[-37.21605931685209,35.29872780370737,-1860.0,1.0,6.0,0.0,-1.0,0.6346639184051985],[35.29872780370737,35.76656513996905,-1275.7341,1.0,6.0,0.0,-1.0,0.601227014489536],[35.76656513996905,39.509263830062444,0.0,1.0,5.0,1.0,-1.0,0.5282181352726685],[39.509263830062444,39.97710116632411,708.65,1.0,5.0,1.0,-1.0,0.48328154681356894],[39.97710116632411,102.66730422538842,1860.0,1.0,5.0,1.0,-1.0,0.41027266919784283]]</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>[[-34.83678426817589,33.561181230526756,-1860.0,1.0,4.0,1.0,-1.0],[33.561181230526756,34.45527228279738,-1074.7923,0.0,4.0,2.0,-1.0],[34.45527228279738,38.03163649187988,0.0,0.0,3.0,3.0,-1.0],[38.03163649187988,38.925727544150504,890.0,0.0,3.0,3.0,-1.0],[38.925727544150504,98.82982804628224,1860.0,0.0,3.0,3.0,-1.0]]</t>
+          <t>[[-34.83678426817589,33.561181230526756,-1860.0,1.0,4.0,1.0,-1.0,0.516718452330373],[33.561181230526756,34.45527228279738,-1074.7923,0.0,4.0,2.0,-1.0,0.47178186708940906],[34.45527228279738,38.03163649187988,0.0,0.0,3.0,3.0,-1.0,0.4102726691978428],[38.03163649187988,38.925727544150504,890.0,0.0,3.0,3.0,-1.0,0.3538363977964477],[38.925727544150504,98.82982804628224,1860.0,0.0,3.0,3.0,-1.0,0.29232720312301713]]</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>[[-36.97572041064796,34.96934615794786,-1860.0,1.0,3.0,1.0,-1.0],[34.96934615794786,35.909804544465466,-1074.7923,0.0,3.0,2.0,-1.0],[35.909804544465466,40.14186728379463,0.0,0.0,3.0,2.0,-1.0],[40.14186728379463,103.62280837373211,1860.0,1.0,3.0,1.0,-1.0]]</t>
+          <t>[[-36.97572041064796,34.96934615794786,-1860.0,1.0,3.0,1.0,-1.0,0.3987729862555473],[34.96934615794786,35.909804544465466,-1074.7923,0.0,3.0,2.0,-1.0,0.35383640101458347],[35.909804544465466,40.14186728379463,0.0,0.0,3.0,2.0,-1.0,0.2923272031230172],[40.14186728379463,103.62280837373211,1860.0,1.0,3.0,1.0,-1.0,0.17438173704819154]]</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>[[-35.07272470213099,32.73671986986556,-1860.0,1.0,3.0,0.0,-1.0],[32.73671986986556,36.30563800523381,-1074.7923,0.0,3.0,1.0,-1.0],[36.30563800523381,39.874556140602046,0.0,0.0,3.0,1.0,-1.0],[39.874556140602046,40.7667856744441,708.65,1.0,3.0,0.0,-1.0],[40.7667856744441,98.31559060725696,1860.0,1.0,3.0,0.0,-1.0]]</t>
+          <t>[[-35.07272470213099,32.73671986986556,-1860.0,1.0,3.0,0.0,-1.0,0.3987729862555473],[32.73671986986556,36.30563800523381,-1074.7923,0.0,3.0,1.0,-1.0,0.35383640101458347],[36.30563800523381,39.874556140602046,0.0,0.0,3.0,1.0,-1.0,0.2923272031230172],[39.874556140602046,40.7667856744441,708.65,1.0,3.0,0.0,-1.0,0.24739061466391762],[40.7667856744441,98.31559060725696,1860.0,1.0,3.0,0.0,-1.0,0.17438173704819154]]</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>[[-38.46136814755726,29.712931202196977,-1860.0,1.0,3.0,0.0,-1.0],[29.712931202196977,32.11343470042775,-1074.7923,0.0,3.0,0.0,-1.0],[32.11343470042775,35.95424029759702,0.0,0.0,2.0,1.0,-1.0],[35.95424029759702,39.79504589476627,890.0,0.0,2.0,1.0,-1.0],[39.79504589476627,105.08874104664356,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-38.46136814755726,29.712931202196977,-1860.0,1.0,3.0,0.0,-1.0,0.3987729862555473],[29.712931202196977,32.11343470042775,-1074.7923,0.0,3.0,0.0,-1.0,0.35383640101458347],[32.11343470042775,35.95424029759702,0.0,0.0,2.0,1.0,-1.0,0.2923272031230172],[35.95424029759702,39.79504589476627,890.0,0.0,2.0,1.0,-1.0,0.23589093172162212],[39.79504589476627,105.08874104664356,1860.0,0.0,3.0,0.0,-1.0,0.17438173704819154]]</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>[[-36.84879219161092,29.07002365390351,-1860.0,1.0,2.0,0.0,-1.0],[29.07002365390351,32.31954274487958,-1074.7923,0.0,2.0,0.0,-1.0],[32.31954274487958,36.03327884885223,0.0,0.0,1.0,1.0,-1.0],[36.03327884885223,39.74701495282486,890.0,0.0,1.0,1.0,-1.0],[39.74701495282486,101.95209469436665,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-36.84879219161092,29.07002365390351,-1860.0,1.0,2.0,0.0,-1.0,0.2808275201807216],[29.07002365390351,32.31954274487958,-1074.7923,0.0,2.0,0.0,-1.0,0.23589093493975777],[32.31954274487958,36.03327884885223,0.0,0.0,1.0,1.0,-1.0,0.1743817370481915],[36.03327884885223,39.74701495282486,890.0,0.0,1.0,1.0,-1.0,0.11794546564679644],[39.74701495282486,101.95209469436665,1860.0,0.0,2.0,0.0,-1.0,0.05643627097336586]]</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>[[-35.32370002647493,28.77999163578331,-1860.0,1.0,1.0,0.0,-1.0],[28.77999163578331,48.50420445493969,-1074.7923,0.0,1.0,0.0,-1.0],[48.50420445493969,53.883535223800514,0.0,0.0,0.0,1.0,-1.0],[53.883535223800514,59.711143556733084,890.0,0.0,0.0,0.0,-1.0],[59.711143556733084,98.7112916309741,890.0001,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-35.32370002647493,28.77999163578331,-1860.0,1.0,1.0,0.0,-1.0,0.162882054105896],[28.77999163578331,48.50420445493969,-1074.7923,0.0,1.0,0.0,-1.0,0.11794546886493218],[48.50420445493969,53.883535223800514,0.0,0.0,0.0,1.0,-1.0,0.05643627097336591],[53.883535223800514,59.711143556733084,890.0,0.0,0.0,0.0,-1.0,-4.2802913990946934e-10],[59.711143556733084,98.7112916309741,890.0001,0.0,0.0,0.0,-1.0,-6.769183234778264e-09]]</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>[0,19.7242128192,0,0,0]</t>
+          <t>[0,19.7242128192,5.3793307689,0,0]</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>[[-34.49575614183493,22.546778905102478,-1860.0,9.0,1.0,0.0,1.0],[22.546778905102478,22.985567636232766,-733.6842,9.0,1.0,0.0,1.0],[22.985567636232766,31.761342258838525,0.0,0.0,1.0,1.0,-1.0],[31.761342258838525,96.7020744661211,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-34.49575614183493,22.546778905102478,-1860.0,9.0,1.0,0.0,1.0,0.2243912519974623],[22.546778905102478,22.985567636232766,-733.6842,9.0,1.0,0.0,1.0,0.15993342006975148],[22.985567636232766,31.761342258838525,0.0,0.0,1.0,1.0,-1.0,0.1179454688649322],[31.761342258838525,96.7020744661211,1860.0,0.0,1.0,0.0,-1.0,2.7901065624558186e-09]]</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>[[-30.850900948084423,21.8065723382443,-1860.0,9.0,0.0,1.0,1.0],[21.8065723382443,23.021744798698037,-733.6842,9.0,0.0,1.0,1.0],[23.021744798698037,90.26128761047164,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-30.850900948084423,21.8065723382443,-1860.0,9.0,0.0,1.0,1.0,0.10644578592263666],[21.8065723382443,23.021744798698037,-733.6842,9.0,0.0,1.0,1.0,0.041987953994925824],[23.021744798698037,90.26128761047164,0.0,0.0,0.0,1.0,-1.0,2.790106548578031e-09]]</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>[[-31.691164606598434,22.8917218498569,-1860.0,8.0,0.0,0.0,1.0],[22.8917218498569,35.710430032812326,-733.6842,9.0,0.0,0.0,1.0],[35.710430032812326,91.9473433515845,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-31.691164606598434,22.8917218498569,-1860.0,8.0,0.0,0.0,1.0,0.10644578592263666],[22.8917218498569,35.710430032812326,-733.6842,9.0,0.0,0.0,1.0,0.041987953994925824],[35.710430032812326,91.9473433515845,0.0,0.0,0.0,1.0,-1.0,2.790106548578031e-09]]</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>[[-28.103081696230486,22.0914659806693,-1860.0,7.0,0.0,0.0,1.0],[22.0914659806693,36.161149799194234,-733.6842,8.0,0.0,0.0,1.0],[36.161149799194234,39.96376704744422,0.0,8.0,8.0,3.0,-1.0],[39.96376704744422,85.59517402644403,1678.6501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-28.103081696230486,22.0914659806693,-1860.0,7.0,0.0,0.0,1.0,0.21289156905516682],[22.0914659806693,36.161149799194234,-733.6842,8.0,0.0,0.0,1.0,0.14843373712745597],[36.161149799194234,39.96376704744422,0.0,8.0,8.0,3.0,-1.0,0.1064457859226367],[39.96376704744422,85.59517402644403,1678.6501,0.0,0.0,0.0,-1.0,-3.5510475115962947e-09]]</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>[[-29.59547769477976,23.47391226545036,-1860.0,7.0,0.0,0.0,1.0],[23.47391226545036,36.05332321898639,-733.6842,7.0,0.0,0.0,1.0],[36.05332321898639,39.98438914196639,0.0,8.0,9.0,1.0,-1.0],[39.98438914196639,40.3774957342644,46.5,8.0,9.0,1.0,-1.0],[40.3774957342644,41.163708918860394,227.85,7.0,8.0,0.0,-1.0],[41.163708918860394,87.9433934023225,1860.0,7.0,8.0,0.0,-1.0]]</t>
+          <t>[[-29.59547769477976,23.47391226545036,-1860.0,7.0,0.0,0.0,1.0,0.3193373521876969],[23.47391226545036,36.05332321898639,-733.6842,7.0,0.0,0.0,1.0,0.25487952025998606],[36.05332321898639,39.98438914196639,0.0,8.0,9.0,1.0,-1.0,0.2128915690551668],[39.98438914196639,40.3774957342644,46.5,8.0,9.0,1.0,-1.0,0.20994293240329615],[40.3774957342644,41.163708918860394,227.85,7.0,8.0,0.0,-1.0,0.19844324946100064],[41.163708918860394,87.9433934023225,1860.0,7.0,8.0,0.0,-1.0,0.09494610298034116]]</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>[[-30.973800917296757,23.086569605206414,-1860.0,6.0,0.0,0.0,1.0],[23.086569605206414,36.20415951140204,-733.6842,5.0,0.0,0.0,1.0],[36.20415951140204,40.17918675570374,0.0,6.0,8.0,3.0,-1.0],[40.17918675570374,41.371694928994245,227.85,5.0,8.0,0.0,-1.0],[41.371694928994245,87.87951368732419,1860.0,6.0,8.0,0.0,-1.0]]</t>
+          <t>[[-30.973800917296757,23.086569605206414,-1860.0,6.0,0.0,0.0,1.0,0.425783135320227],[23.086569605206414,36.20415951140204,-733.6842,5.0,0.0,0.0,1.0,0.3613253033925162],[36.20415951140204,40.17918675570374,0.0,6.0,8.0,3.0,-1.0,0.3193373521876969],[40.17918675570374,41.371694928994245,227.85,5.0,8.0,0.0,-1.0,0.30488903259353073],[41.371694928994245,87.87951368732419,1860.0,6.0,8.0,0.0,-1.0,0.20139188611287123]]</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>[[-40.59518841333071,23.26432773268955,-1860.0,4.0,0.0,0.0,1.0],[23.26432773268955,35.38365196478099,-733.6842,4.0,0.0,0.0,1.0],[35.38365196478099,39.11267480542451,0.0,4.0,8.0,4.0,-1.0],[39.11267480542451,40.97718622574626,227.85,4.0,8.0,0.0,-1.0],[40.97718622574626,98.7770402557208,1860.0,4.0,8.0,0.0,-1.0]]</t>
+          <t>[[-40.59518841333071,23.26432773268955,-1860.0,4.0,0.0,0.0,1.0,0.5322289184527571],[23.26432773268955,35.38365196478099,-733.6842,4.0,0.0,0.0,1.0,0.4677710865250463],[35.38365196478099,39.11267480542451,0.0,4.0,8.0,4.0,-1.0,0.425783135320227],[39.11267480542451,40.97718622574626,227.85,4.0,8.0,0.0,-1.0,0.41133481572606084],[40.97718622574626,98.7770402557208,1860.0,4.0,8.0,0.0,-1.0,0.30783766924540135]]</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>[[-40.20524081947566,23.25494578715829,-1860.0,3.0,0.0,0.0,1.0],[23.25494578715829,35.21121282898787,-733.6842,3.0,0.0,0.0,1.0],[35.21121282898787,39.34992065115965,0.0,3.0,8.0,3.0,-1.0],[39.34992065115965,40.26963350053116,227.85,4.0,8.0,3.0,-1.0],[40.26963350053116,97.29183016156458,1860.0,3.0,9.0,2.0,-1.0]]</t>
+          <t>[[-40.20524081947566,23.25494578715829,-1860.0,3.0,0.0,0.0,1.0,0.6386747015852872],[23.25494578715829,35.21121282898787,-733.6842,3.0,0.0,0.0,1.0,0.5742168696575763],[35.21121282898787,39.34992065115965,0.0,3.0,8.0,3.0,-1.0,0.5322289184527571],[39.34992065115965,40.26963350053116,227.85,4.0,8.0,3.0,-1.0,0.517780598858591],[40.26963350053116,97.29183016156458,1860.0,3.0,9.0,2.0,-1.0,0.41428345237793146]]</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>[[-47.25921642114884,22.906395668684006,-1860.0,2.0,0.0,0.0,1.0],[22.906395668684006,35.75362041752664,-733.6842,2.0,0.0,0.0,1.0],[35.75362041752664,39.70661264793976,0.0,3.0,8.0,1.0,-1.0],[39.70661264793976,41.683108763146315,227.85,2.0,8.0,0.0,-1.0],[41.683108763146315,100.48386819054144,1860.0,2.0,8.0,0.0,-1.0]]</t>
+          <t>[[-47.25921642114884,22.906395668684006,-1860.0,2.0,0.0,0.0,1.0,0.7451204847178172],[22.906395668684006,35.75362041752664,-733.6842,2.0,0.0,0.0,1.0,0.6806626527901064],[35.75362041752664,39.70661264793976,0.0,3.0,8.0,1.0,-1.0,0.6386747015852872],[39.70661264793976,41.683108763146315,227.85,2.0,8.0,0.0,-1.0,0.624226381991121],[41.683108763146315,100.48386819054144,1860.0,2.0,8.0,0.0,-1.0,0.5207292355104616]]</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>[[-46.148531947483505,21.73985886615094,-1860.0,2.0,0.0,0.0,1.0],[21.73985886615094,36.66567528616987,-733.6842,2.0,0.0,0.0,1.0],[36.66567528616987,40.99897682746568,0.0,2.0,8.0,3.0,-1.0],[40.99897682746568,97.81337481334415,1860.0,1.0,8.0,0.0,-1.0]]</t>
+          <t>[[-46.148531947483505,21.73985886615094,-1860.0,2.0,0.0,0.0,1.0,0.8515662678503473],[21.73985886615094,36.66567528616987,-733.6842,2.0,0.0,0.0,1.0,0.7871084359226365],[36.66567528616987,40.99897682746568,0.0,2.0,8.0,3.0,-1.0,0.7451204847178172],[40.99897682746568,97.81337481334415,1860.0,1.0,8.0,0.0,-1.0,0.6271750186429916]]</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>[[-52.78923497376588,23.417120440370375,-1860.0,1.0,0.0,0.0,1.0],[23.417120440370375,36.89579554763258,-733.6842,0.0,0.0,0.0,1.0],[36.89579554763258,41.043080196020945,0.0,1.0,8.0,3.0,-1.0],[41.043080196020945,102.21552875974938,1860.0,1.0,8.0,0.0,-1.0]]</t>
+          <t>[[-52.78923497376588,23.417120440370375,-1860.0,1.0,0.0,0.0,1.0,0.9580120509828773],[23.417120440370375,36.89579554763258,-733.6842,0.0,0.0,0.0,1.0,0.8935542190551665],[36.89579554763258,41.043080196020945,0.0,1.0,8.0,3.0,-1.0,0.8515662678503473],[41.043080196020945,102.21552875974938,1860.0,1.0,8.0,0.0,-1.0,0.7336208017755217]]</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>[0,0,4.1472846484,0,0]</t>
+          <t>[13.4786751073,0,4.1472846484,0,0]</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>[[-60.44699517817127,35.94393370776033,-733.6843,0.0,0.0,0.0,1.0],[35.94393370776033,39.86682034846684,0.0,0.0,9.0,2.0,-1.0],[39.86682034846684,40.987645102954424,46.5,1.0,9.0,1.0,-1.0],[40.987645102954424,41.5480574801982,227.85,0.0,8.0,0.0,-1.0],[41.5480574801982,107.11630561772145,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-60.44699517817127,35.94393370776033,-733.6843,0.0,0.0,0.0,1.0,1.0000000079105882],[35.94393370776033,39.86682034846684,0.0,0.0,9.0,2.0,-1.0,0.9580120509828773],[39.86682034846684,40.987645102954424,46.5,1.0,9.0,1.0,-1.0,0.9550634143310067],[40.987645102954424,41.5480574801982,227.85,0.0,8.0,0.0,-1.0,0.9435637313887112],[41.5480574801982,107.11630561772145,1860.0,0.0,8.0,0.0,-1.0,0.8400665849080517]]</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>[[-60.307202730584066,37.76460267711313,0.0,0.0,0.0,1.0,1.0],[37.76460267711313,38.8790550112915,890.0,0.0,8.0,0.0,-1.0],[38.8790550112915,106.30342122908331,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-60.307202730584066,37.76460267711313,0.0,0.0,0.0,1.0,1.0,1.000000007910588],[37.76460267711313,38.8790550112915,890.0,0.0,8.0,0.0,-1.0,0.9435637365091929],[38.8790550112915,106.30342122908331,1860.0,0.0,8.0,0.0,-1.0,0.8820545418357624]]</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>[[-61.15701701006009,33.28163998563261,-1860.0,1.0,8.0,1.0,-1.0],[33.28163998563261,35.571061973406984,-1074.7921,0.0,8.0,1.0,-1.0],[35.571061973406984,39.00519495506853,0.0,0.0,7.0,2.0,-1.0],[39.00519495506853,40.14990594895572,890.0001,0.0,7.0,2.0,-1.0],[40.14990594895572,109.97727657607398,1860.0,0.0,7.0,2.0,-1.0]]</t>
+          <t>[[-61.15701701006009,33.28163998563261,-1860.0,1.0,8.0,1.0,-1.0,0.9885003249682927],[33.28163998563261,35.571061973406984,-1074.7921,0.0,8.0,1.0,-1.0,0.9435637282815457],[35.571061973406984,39.00519495506853,0.0,0.0,7.0,2.0,-1.0,0.8820545418357626],[39.00519495506853,40.14990594895572,890.0001,0.0,7.0,2.0,-1.0,0.8256182640932135],[40.14990594895572,109.97727657607398,1860.0,0.0,7.0,2.0,-1.0,0.764109075760937]]</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>[[-58.617514406173555,33.554082805404505,-1860.0,1.0,7.0,0.0,-1.0],[33.554082805404505,34.09309799377631,-1074.7921,0.0,7.0,1.0,-1.0],[34.09309799377631,37.86620431237891,0.0,0.0,6.0,2.0,-1.0],[37.86620431237891,40.02226506586612,890.0001,0.0,6.0,2.0,-1.0],[40.02226506586612,102.54802691699508,1860.0,0.0,6.0,2.0,-1.0]]</t>
+          <t>[[-58.617514406173555,33.554082805404505,-1860.0,1.0,7.0,0.0,-1.0,0.8705548588934671],[33.554082805404505,34.09309799377631,-1074.7921,0.0,7.0,1.0,-1.0,0.8256182622067201],[34.09309799377631,37.86620431237891,0.0,0.0,6.0,2.0,-1.0,0.764109075760937],[37.86620431237891,40.02226506586612,890.0001,0.0,6.0,2.0,-1.0,0.7076727980183879],[40.02226506586612,102.54802691699508,1860.0,0.0,6.0,2.0,-1.0,0.6461636096861114]]</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>[[-59.206535250938295,33.57687478221239,-1860.0,1.0,6.0,1.0,-1.0],[33.57687478221239,34.67490330331477,-1074.7921,0.0,6.0,1.0,-1.0],[34.67490330331477,38.51800312717308,0.0,0.0,5.0,2.0,-1.0],[38.51800312717308,104.9487286538668,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-59.206535250938295,33.57687478221239,-1860.0,1.0,6.0,1.0,-1.0,0.7526093928186415],[33.57687478221239,34.67490330331477,-1074.7921,0.0,6.0,1.0,-1.0,0.7076727961318945],[34.67490330331477,38.51800312717308,0.0,0.0,5.0,2.0,-1.0,0.6461636096861114],[38.51800312717308,104.9487286538668,1860.0,0.0,5.0,0.0,-1.0,0.5282181436112858]]</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>[[-59.70357952689521,33.2664774316129,-1860.0,1.0,5.0,1.0,-1.0],[33.2664774316129,34.92665702015769,-1074.7921,0.0,5.0,1.0,-1.0],[34.92665702015769,38.80040939342885,0.0,0.0,4.0,2.0,-1.0],[38.80040939342885,39.90719578579204,890.0001,0.0,4.0,0.0,-1.0],[39.90719578579204,105.76098613140196,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-59.70357952689521,33.2664774316129,-1860.0,1.0,5.0,1.0,-1.0,0.6346639267438159],[33.2664774316129,34.92665702015769,-1074.7921,0.0,5.0,1.0,-1.0,0.5897273300570689],[34.92665702015769,38.80040939342885,0.0,0.0,4.0,2.0,-1.0,0.5282181436112858],[38.80040939342885,39.90719578579204,890.0001,0.0,4.0,0.0,-1.0,0.47178186586873666],[39.90719578579204,105.76098613140196,1860.0,0.0,4.0,0.0,-1.0,0.4102726775364602]]</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>[[-55.8296627825497,33.893462722545216,-1860.0,1.0,4.0,0.0,-1.0],[33.893462722545216,34.409112869126226,-1074.7921,0.0,4.0,1.0,-1.0],[34.409112869126226,38.018663895193264,0.0,0.0,3.0,2.0,-1.0],[38.018663895193264,39.56561433493628,890.0001,0.0,3.0,0.0,-1.0],[39.56561433493628,98.34973104517088,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-55.8296627825497,33.893462722545216,-1860.0,1.0,4.0,0.0,-1.0,0.5167184606689903],[33.893462722545216,34.409112869126226,-1074.7921,0.0,4.0,1.0,-1.0,0.4717818639822433],[34.409112869126226,38.018663895193264,0.0,0.0,3.0,2.0,-1.0,0.4102726775364602],[38.018663895193264,39.56561433493628,890.0001,0.0,3.0,0.0,-1.0,0.353836399793911],[39.56561433493628,98.34973104517088,1860.0,0.0,3.0,0.0,-1.0,0.29232721146163454]]</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>[[-53.94616849369185,34.83341916372515,-1860.0,1.0,3.0,1.0,-1.0],[34.83341916372515,35.32939451376658,-1074.7921,0.0,3.0,2.0,-1.0],[35.32939451376658,38.80122196405663,0.0,0.0,2.0,3.0,-1.0],[38.80122196405663,39.7931726641395,890.0001,0.0,2.0,2.0,-1.0],[39.7931726641395,94.35046116869744,1860.0,0.0,2.0,2.0,-1.0]]</t>
+          <t>[[-53.94616849369185,34.83341916372515,-1860.0,1.0,3.0,1.0,-1.0,0.3987729945941646],[34.83341916372515,35.32939451376658,-1074.7921,0.0,3.0,2.0,-1.0,0.3538363979074176],[35.32939451376658,38.80122196405663,0.0,0.0,2.0,3.0,-1.0,0.2923272114616345],[38.80122196405663,39.7931726641395,890.0001,0.0,2.0,2.0,-1.0,0.23589093371908534],[39.7931726641395,94.35046116869744,1860.0,0.0,2.0,2.0,-1.0,0.17438174538680884]]</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>[[-50.853759897083485,32.76300876624162,-1860.0,1.0,2.0,0.0,-1.0],[32.76300876624162,33.22497986382904,-1074.7921,0.0,2.0,1.0,-1.0],[33.22497986382904,36.920748644528494,0.0,0.0,1.0,2.0,-1.0],[36.920748644528494,39.23060413246565,890.0001,0.0,1.0,2.0,-1.0],[39.23060413246565,87.27559828155853,1860.0,0.0,1.0,2.0,-1.0]]</t>
+          <t>[[-50.853759897083485,32.76300876624162,-1860.0,1.0,2.0,0.0,-1.0,0.280827528519339],[32.76300876624162,33.22497986382904,-1074.7921,0.0,2.0,1.0,-1.0,0.23589093183259202],[33.22497986382904,36.920748644528494,0.0,0.0,1.0,2.0,-1.0,0.1743817453868089],[36.920748644528494,39.23060413246565,890.0001,0.0,1.0,2.0,-1.0,0.11794546764425975],[39.23060413246565,87.27559828155853,1860.0,0.0,1.0,2.0,-1.0,0.056436279311983265]]</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>[[-55.894212241262395,33.479040035401795,-1860.0,1.0,1.0,1.0,-1.0],[33.479040035401795,36.04723693990363,-1074.7921,0.0,1.0,1.0,-1.0],[36.04723693990363,39.64271260620622,0.0,0.0,0.0,2.0,-1.0],[39.64271260620622,40.15635198710659,890.0001,0.0,0.0,0.0,-1.0],[40.15635198710659,97.68396264794788,890.0002,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-55.894212241262395,33.479040035401795,-1860.0,1.0,1.0,1.0,-1.0,0.16288206244451336],[33.479040035401795,36.04723693990363,-1074.7921,0.0,1.0,1.0,-1.0,0.11794546575776638],[36.04723693990363,39.64271260620622,0.0,0.0,0.0,2.0,-1.0,0.05643627931198326],[39.64271260620622,40.15635198710659,890.0001,0.0,0.0,0.0,-1.0,1.569434110448853e-09],[40.15635198710659,97.68396264794788,890.0002,0.0,0.0,0.0,-1.0,-4.771719977481048e-09]]</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>[[-51.18425824727567,34.59366101837799,-1860.0,1.0,1.0,0.0,-1.0],[34.59366101837799,35.059845362213075,-1074.7921,0.0,1.0,0.0,-1.0],[35.059845362213075,38.78932011289367,0.0,0.0,0.0,1.0,-1.0],[38.78932011289367,42.98497920740933,890.0001,0.0,0.0,0.0,-1.0],[42.98497920740933,88.20486055941153,890.0002,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-51.18425824727567,34.59366101837799,-1860.0,1.0,1.0,0.0,-1.0,0.16288206244451336],[34.59366101837799,35.059845362213075,-1074.7921,0.0,1.0,0.0,-1.0,0.11794546575776638],[35.059845362213075,38.78932011289367,0.0,0.0,0.0,1.0,-1.0,0.05643627931198326],[38.78932011289367,42.98497920740933,890.0001,0.0,0.0,0.0,-1.0,1.569434110448853e-09],[42.98497920740933,88.20486055941153,890.0002,0.0,0.0,0.0,-1.0,-4.771719977481048e-09]]</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>[0,0.4661843438,0,0,0]</t>
+          <t>[0,0.4661843438,3.7294747507,0,0]</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>[[-52.321817547854735,29.95888569369305,-1860.0,1.0,1.0,0.0,-1.0],[29.95888569369305,35.221023691699,-1074.7921,0.0,1.0,0.0,-1.0],[35.221023691699,39.04803314479426,0.0,0.0,0.0,1.0,-1.0],[39.04803314479426,43.35341877952641,890.0001,0.0,0.0,0.0,-1.0],[43.35341877952641,90.71266076158008,890.0002,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-52.321817547854735,29.95888569369305,-1860.0,1.0,1.0,0.0,-1.0,0.16288206244451336],[29.95888569369305,35.221023691699,-1074.7921,0.0,1.0,0.0,-1.0,0.11794546575776638],[35.221023691699,39.04803314479426,0.0,0.0,0.0,1.0,-1.0,0.05643627931198326],[39.04803314479426,43.35341877952641,890.0001,0.0,0.0,0.0,-1.0,1.569434110448853e-09],[43.35341877952641,90.71266076158008,890.0002,0.0,0.0,0.0,-1.0,-4.771719977481048e-09]]</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>[0,5.262137998,0,0,0]</t>
+          <t>[0,5.262137998,3.8270094531,0,0]</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>[[-51.73590358302149,30.46858612554768,-1860.0,1.0,0.0,0.0,-1.0],[30.46858612554768,90.34006417918768,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-51.73590358302149,30.46858612554768,-1860.0,1.0,0.0,0.0,-1.0,0.10644578470196424],[30.46858612554768,90.34006417918768,0.0,0.0,0.0,1.0,-1.0,1.569434117387747e-09]]</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>[[-53.20465434026467,19.104343138595752,-1860.0,1.0,0.0,0.0,-1.0],[19.104343138595752,92.87906353932499,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-53.20465434026467,19.104343138595752,-1860.0,1.0,0.0,0.0,-1.0,0.10644578470196424],[19.104343138595752,92.87906353932499,0.0,0.0,0.0,1.0,-1.0,1.569434117387747e-09]]</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>[[-50.29413927919539,12.970906995060083,-1860.0,10.0,0.0,0.0,1.0],[12.970906995060083,14.80467645228488,-733.6842,9.0,0.0,1.0,1.0],[14.80467645228488,86.78012764835816,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-50.29413927919539,12.970906995060083,-1860.0,10.0,0.0,0.0,1.0,0.10644578470196424],[12.970906995060083,14.80467645228488,-733.6842,9.0,0.0,1.0,1.0,0.04198795277425339],[14.80467645228488,86.78012764835816,0.0,0.0,0.0,1.0,-1.0,1.569434117387747e-09]]</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>[[-51.921250863501825,11.827160069401629,-1860.0,9.0,0.0,0.0,1.0],[11.827160069401629,25.147723547918773,-733.6842,9.0,0.0,0.0,1.0],[25.147723547918773,90.32333771066334,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-51.921250863501825,11.827160069401629,-1860.0,9.0,0.0,0.0,1.0,0.10644578470196424],[11.827160069401629,25.147723547918773,-733.6842,9.0,0.0,0.0,1.0,0.04198795277425339],[25.147723547918773,90.32333771066334,0.0,0.0,0.0,1.0,-1.0,1.569434117387747e-09]]</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>[[-53.645705033958095,24.764810069157193,-1860.0,8.0,0.0,0.0,1.0],[24.764810069157193,35.61406373122345,0.0,7.0,0.0,1.0,1.0],[35.61406373122345,93.80551519139703,662.1501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-53.645705033958095,24.764810069157193,-1860.0,8.0,0.0,0.0,1.0,0.1484337359067835],[24.764810069157193,35.61406373122345,0.0,7.0,0.0,1.0,1.0,0.04198795277425339],[35.61406373122345,93.80551519139703,662.1501,0.0,0.0,0.0,-1.0,-5.37412960660566e-09]]</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>[[-49.524852353289816,24.730469950303203,-1860.0,8.0,0.0,0.0,1.0],[24.730469950303203,35.59710248253633,0.0,7.0,0.0,1.0,1.0],[35.59710248253633,85.85527794411453,1860.0,9.0,9.0,2.0,-1.0]]</t>
+          <t>[[-49.524852353289816,24.730469950303203,-1860.0,8.0,0.0,0.0,1.0,0.2548795190393136],[24.730469950303203,35.59710248253633,0.0,7.0,0.0,1.0,1.0,0.1484337359067835],[35.59710248253633,85.85527794411453,1860.0,9.0,9.0,2.0,-1.0,0.030488269831957862]]</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>[[-52.988449021079816,25.709951565677258,-1860.0,7.0,0.0,0.0,1.0],[25.709951565677258,33.482633105110054,0.0,6.0,0.0,1.0,1.0],[33.482633105110054,33.968425701324605,708.65,8.0,9.0,1.0,-1.0],[33.968425701324605,92.26353724707059,1860.0,8.0,9.0,1.0,-1.0]]</t>
+          <t>[[-52.988449021079816,25.709951565677258,-1860.0,7.0,0.0,0.0,1.0,0.3613253021718437],[25.709951565677258,33.482633105110054,0.0,6.0,0.0,1.0,1.0,0.2548795190393136],[33.482633105110054,33.968425701324605,708.65,8.0,9.0,1.0,-1.0,0.20994293058021404],[33.968425701324605,92.26353724707059,1860.0,8.0,9.0,1.0,-1.0,0.13693405296448796]]</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>[[-54.891929938936144,24.235980088385162,-1860.0,5.0,0.0,0.0,1.0],[24.235980088385162,34.31596862689743,0.0,5.0,0.0,1.0,1.0],[34.31596862689743,34.81996805382305,890.0,5.0,8.0,3.0,-1.0],[34.81996805382305,95.80389871182226,1860.0,6.0,8.0,3.0,-1.0]]</t>
+          <t>[[-54.891929938936144,24.235980088385162,-1860.0,5.0,0.0,0.0,1.0,0.46777108530437383],[24.235980088385162,34.31596862689743,0.0,5.0,0.0,1.0,1.0,0.3613253021718437],[34.31596862689743,34.81996805382305,890.0,5.0,8.0,3.0,-1.0,0.30488903077044865],[34.81996805382305,95.80389871182226,1860.0,6.0,8.0,3.0,-1.0,0.24337983609701808]]</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>[[-51.39728508039744,24.434302898584406,-1860.0,4.0,0.0,0.0,1.0],[24.434302898584406,33.85437593945173,0.0,3.0,0.0,1.0,1.0],[33.85437593945173,34.79638324353846,890.0,4.0,8.0,4.0,-1.0],[34.79638324353846,89.43280688056883,1860.0,5.0,8.0,4.0,-1.0]]</t>
+          <t>[[-51.39728508039744,24.434302898584406,-1860.0,4.0,0.0,0.0,1.0,0.5742168684369039],[24.434302898584406,33.85437593945173,0.0,3.0,0.0,1.0,1.0,0.4677710853043738],[33.85437593945173,34.79638324353846,890.0,4.0,8.0,4.0,-1.0,0.4113348139029787],[34.79638324353846,89.43280688056883,1860.0,5.0,8.0,4.0,-1.0,0.34982561922954813]]</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>[[-51.91839773731432,24.67043448346152,-1860.0,4.0,0.0,0.0,1.0],[24.67043448346152,34.660282164432274,0.0,3.0,0.0,1.0,1.0],[34.660282164432274,35.135989196859455,890.0,4.0,8.0,4.0,-1.0],[35.135989196859455,90.31800495841223,1860.0,4.0,8.0,4.0,-1.0]]</t>
+          <t>[[-51.91839773731432,24.67043448346152,-1860.0,4.0,0.0,0.0,1.0,0.6806626515694341],[24.67043448346152,34.660282164432274,0.0,3.0,0.0,1.0,1.0,0.574216868436904],[34.660282164432274,35.135989196859455,890.0,4.0,8.0,4.0,-1.0,0.5177805970355089],[35.135989196859455,90.31800495841223,1860.0,4.0,8.0,4.0,-1.0,0.45627140236207836]]</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>[[-51.52745064853717,23.97811434779703,-1860.0,3.0,0.0,0.0,1.0],[23.97811434779703,34.83203931602007,0.0,3.0,0.0,1.0,1.0],[34.83203931602007,35.30394909724717,890.0,3.0,8.0,3.0,-1.0],[35.30394909724717,89.57357393836239,1860.0,3.0,8.0,3.0,-1.0]]</t>
+          <t>[[-51.52745064853717,23.97811434779703,-1860.0,3.0,0.0,0.0,1.0,0.7871084347019641],[23.97811434779703,34.83203931602007,0.0,3.0,0.0,1.0,1.0,0.6806626515694341],[34.83203931602007,35.30394909724717,890.0,3.0,8.0,3.0,-1.0,0.624226380168039],[35.30394909724717,89.57357393836239,1860.0,3.0,8.0,3.0,-1.0,0.5627171854946085]]</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>[[-49.86942882250132,25.32306251500549,-1860.0,2.0,0.0,0.0,1.0],[25.32306251500549,34.43730388924874,0.0,1.0,0.0,1.0,1.0],[34.43730388924874,34.8930159579609,890.0,2.0,8.0,4.0,-1.0],[34.8930159579609,86.38847972243528,1860.0,2.0,8.0,4.0,-1.0]]</t>
+          <t>[[-49.86942882250132,25.32306251500549,-1860.0,2.0,0.0,0.0,1.0,0.8935542178344942],[25.32306251500549,34.43730388924874,0.0,1.0,0.0,1.0,1.0,0.7871084347019641],[34.43730388924874,34.8930159579609,890.0,2.0,8.0,4.0,-1.0,0.730672163300569],[34.8930159579609,86.38847972243528,1860.0,2.0,8.0,4.0,-1.0,0.6691629686271385]]</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>[[-46.619872333041414,-0.2638645123387846,-1860.0,1.0,0.0,0.0,1.0],[-0.2638645123387846,24.459339658702618,-1860.0,0.0,0.0,0.0,1.0],[24.459339658702618,27.10825439131419,0.0,0.0,0.0,1.0,1.0],[27.10825439131419,31.964598067768762,0.0,1.0,0.0,1.0,1.0],[31.964598067768762,32.84756964530595,0.0,0.0,0.0,1.0,1.0],[32.84756964530595,33.730541222843144,0.0,1.0,0.0,1.0,1.0],[33.730541222843144,35.496484377917525,0.0,0.0,0.0,1.0,1.0],[35.496484377917525,85.38437850876893,1860.0,1.0,8.0,4.0,-1.0]]</t>
+          <t>[[-46.619872333041414,-0.2638645123387846,-1860.0,1.0,0.0,0.0,1.0,1.0000000009670242],[-0.2638645123387846,24.459339658702618,-1860.0,0.0,0.0,0.0,1.0,1.0000000009670242],[24.459339658702618,27.10825439131419,0.0,0.0,0.0,1.0,1.0,0.8935542178344942],[27.10825439131419,31.964598067768762,0.0,1.0,0.0,1.0,1.0,0.8935542178344942],[31.964598067768762,32.84756964530595,0.0,0.0,0.0,1.0,1.0,0.8935542178344942],[32.84756964530595,33.730541222843144,0.0,1.0,0.0,1.0,1.0,0.8935542178344942],[33.730541222843144,35.496484377917525,0.0,0.0,0.0,1.0,1.0,0.8935542178344942],[35.496484377917525,85.38437850876893,1860.0,1.0,8.0,4.0,-1.0,0.7756087517596686]]</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>[0,0,5.739315254,0,0]</t>
+          <t>[0,0,11.0371447192,0,0]</t>
         </is>
       </c>
     </row>
@@ -4688,7 +4688,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>[[-23.36956512978107,34.9693520383119,0.0,0.0,0.0,1.0,1.0],[34.9693520383119,35.30657121269394,890.0,0.0,8.0,3.0,-1.0],[35.30657121269394,77.45896801044898,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[-23.36956512978107,34.9693520383119,0.0,0.0,0.0,1.0,1.0,1.000000000967024],[34.9693520383119,35.30657121269394,890.0,0.0,8.0,3.0,-1.0,0.943563729565629],[35.30657121269394,77.45896801044898,1860.0,0.0,8.0,3.0,-1.0,0.8820545348921984]]</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>[[-21.878877305082888,33.43285135509576,0.0,0.0,0.0,1.0,1.0],[33.43285135509576,33.762087835215866,890.0,0.0,8.0,3.0,-1.0],[33.762087835215866,76.5628302508303,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[-21.878877305082888,33.43285135509576,0.0,0.0,0.0,1.0,1.0,1.000000000967024],[33.43285135509576,33.762087835215866,890.0,0.0,8.0,3.0,-1.0,0.943563729565629],[33.762087835215866,76.5628302508303,1860.0,0.0,8.0,3.0,-1.0,0.8820545348921984]]</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>[[-38.30599945116664,29.74850845376514,-1860.0,1.0,8.0,1.0,-1.0],[29.74850845376514,32.17902659322698,-1074.7922,0.0,8.0,2.0,-1.0],[32.17902659322698,35.58175198847357,0.0,0.0,8.0,2.0,-1.0],[35.58175198847357,36.06785561636595,708.65,0.0,8.0,1.0,-1.0],[36.06785561636595,107.03898528865193,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[-38.30599945116664,29.74850845376514,-1860.0,1.0,8.0,1.0,-1.0,0.9885003180247287],[29.74850845376514,32.17902659322698,-1074.7922,0.0,8.0,2.0,-1.0,0.9435637270608733],[32.17902659322698,35.58175198847357,0.0,0.0,8.0,2.0,-1.0,0.8820545348921986],[35.58175198847357,36.06785561636595,708.65,0.0,8.0,1.0,-1.0,0.8371179464330991],[36.06785561636595,107.03898528865193,1860.0,0.0,8.0,1.0,-1.0,0.7641090688173731]]</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>[[-44.405548663775164,31.35124101529985,-1860.0,1.0,8.0,0.0,-1.0],[31.35124101529985,33.01014881849126,-1074.7922,0.0,8.0,1.0,-1.0],[33.01014881849126,36.880933692604586,0.0,0.0,7.0,2.0,-1.0],[36.880933692604586,120.93226238763671,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[-44.405548663775164,31.35124101529985,-1860.0,1.0,8.0,0.0,-1.0,0.9885003180247287],[31.35124101529985,33.01014881849126,-1074.7922,0.0,8.0,1.0,-1.0,0.9435637270608733],[33.01014881849126,36.880933692604586,0.0,0.0,7.0,2.0,-1.0,0.8820545348921986],[36.880933692604586,120.93226238763671,1860.0,0.0,7.0,1.0,-1.0,0.7641090688173731]]</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>[[-54.4621783464445,16.691273335596136,-1860.0,8.0,14.0,1.0,0.0],[16.691273335596136,30.399736503695706,-1074.7922,0.0,8.0,0.0,-1.0],[30.399736503695706,33.66365630562419,0.0,0.0,7.0,1.0,-1.0],[33.66365630562419,34.96922422639557,890.0,0.0,7.0,0.0,-1.0],[34.96922422639557,140.72022580887798,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-54.4621783464445,16.691273335596136,-1860.0,8.0,14.0,1.0,0.0,0.9885003180247287],[16.691273335596136,30.399736503695706,-1074.7922,0.0,8.0,0.0,-1.0,0.9435637270608733],[30.399736503695706,33.66365630562419,0.0,0.0,7.0,1.0,-1.0,0.8820545348921986],[33.66365630562419,34.96922422639557,890.0,0.0,7.0,0.0,-1.0,0.8256182634908036],[34.96922422639557,140.72022580887798,1860.0,0.0,7.0,0.0,-1.0,0.7641090688173731]]</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>[[-65.51330948172671,17.536084672381705,-1860.0,8.0,15.0,0.0,0.0],[17.536084672381705,19.8218478142379,0.0,8.0,14.0,1.0,0.0],[19.8218478142379,35.060268759945856,890.0,0.0,7.0,0.0,-1.0],[35.060268759945856,162.30108365660737,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-65.51330948172671,17.536084672381705,-1860.0,8.0,15.0,0.0,0.0,0.9885003180247287],[17.536084672381705,19.8218478142379,0.0,8.0,14.0,1.0,0.0,0.8820545348921986],[19.8218478142379,35.060268759945856,890.0,0.0,7.0,0.0,-1.0,0.8256182634908036],[35.060268759945856,162.30108365660737,1860.0,0.0,7.0,0.0,-1.0,0.7641090688173731]]</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>[[-66.3758326675593,18.05393442937404,-1860.0,8.0,14.0,1.0,0.0],[18.05393442937404,18.828519448611956,-621.385,8.0,14.0,1.0,0.0],[18.828519448611956,21.15227450632571,0.0,8.0,13.0,2.0,0.0],[21.15227450632571,35.09480485260829,890.0,0.0,6.0,0.0,-1.0],[35.09480485260829,165.22508808457894,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[-66.3758326675593,18.05393442937404,-1860.0,8.0,14.0,1.0,0.0,0.8705548519499031],[18.05393442937404,18.828519448611956,-621.385,8.0,14.0,1.0,0.0,0.7996702585764092],[18.828519448611956,21.15227450632571,0.0,8.0,13.0,2.0,0.0,0.7641090688173731],[21.15227450632571,35.09480485260829,890.0,0.0,6.0,0.0,-1.0,0.707672797415978],[35.09480485260829,165.22508808457894,1860.0,0.0,6.0,0.0,-1.0,0.6461636027425475]]</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>[[-63.80371817719276,17.977744426764346,-1860.0,9.0,5.0,0.0,1.0],[17.977744426764346,18.7212122686185,-1607.5346,8.0,5.0,1.0,1.0],[18.7212122686185,19.46468011047267,-621.385,8.0,13.0,2.0,0.0],[19.46468011047267,21.695083636035136,0.0,8.0,13.0,2.0,0.0],[21.695083636035136,35.820972631264084,890.0,0.0,5.0,0.0,-1.0],[35.820972631264084,158.49316653719976,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-63.80371817719276,17.977744426764346,-1860.0,9.0,5.0,0.0,1.0,0.7526093858750775],[17.977744426764346,18.7212122686185,-1607.5346,8.0,5.0,1.0,1.0,0.7381610647907402],[18.7212122686185,19.46468011047267,-621.385,8.0,13.0,2.0,0.0,0.6817247925015836],[19.46468011047267,21.695083636035136,0.0,8.0,13.0,2.0,0.0,0.6461636027425475],[21.695083636035136,35.820972631264084,890.0,0.0,5.0,0.0,-1.0,0.5897273313411524],[35.820972631264084,158.49316653719976,1860.0,0.0,5.0,0.0,-1.0,0.5282181366677219]]</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>[[-65.22050293571763,17.713478058820172,-1860.0,8.0,4.0,1.0,1.0],[17.713478058820172,19.235202480738295,-1607.5346,8.0,4.0,1.0,1.0],[19.235202480738295,20.756926902656417,0.0,8.0,4.0,1.0,1.0],[20.756926902656417,24.561237957451723,227.85,9.0,4.0,0.0,1.0],[24.561237957451723,35.213308910878595,890.0,0.0,4.0,0.0,-1.0],[35.213308910878595,162.27729814104202,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-65.22050293571763,17.713478058820172,-1860.0,8.0,4.0,1.0,1.0,0.6346639198002519],[17.713478058820172,19.235202480738295,-1607.5346,8.0,4.0,1.0,1.0,0.6202155987159146],[19.235202480738295,20.756926902656417,0.0,8.0,4.0,1.0,1.0,0.5282181366677219],[20.756926902656417,24.561237957451723,227.85,9.0,4.0,0.0,1.0,0.5137698170735557],[24.561237957451723,35.213308910878595,890.0,0.0,4.0,0.0,-1.0,0.4717818652663268],[35.213308910878595,162.27729814104202,1860.0,0.0,4.0,0.0,-1.0,0.41027267059289624]]</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>[[-70.89828073283897,16.923764210524723,-1860.0,8.0,3.0,1.0,1.0],[16.923764210524723,18.565297760867978,-1607.5346,8.0,3.0,1.0,1.0],[18.565297760867978,21.027598086382838,0.0,8.0,3.0,1.0,1.0],[21.027598086382838,21.848364861554472,227.85,9.0,3.0,0.0,1.0],[21.848364861554472,36.62216681464369,890.0,0.0,3.0,0.0,-1.0],[36.62216681464369,174.5109850434764,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-70.89828073283897,16.923764210524723,-1860.0,8.0,3.0,1.0,1.0,0.5167184537254264],[16.923764210524723,18.565297760867978,-1607.5346,8.0,3.0,1.0,1.0,0.502270132641089],[18.565297760867978,21.027598086382838,0.0,8.0,3.0,1.0,1.0,0.4102726705928962],[21.027598086382838,21.848364861554472,227.85,9.0,3.0,0.0,1.0,0.39582435099873003],[21.848364861554472,36.62216681464369,890.0,0.0,3.0,0.0,-1.0,0.3538363991915011],[36.62216681464369,174.5109850434764,1860.0,0.0,3.0,0.0,-1.0,0.29232720451807054]]</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>[[-71.46854877345271,17.815167650359953,-1860.0,9.0,2.0,0.0,1.0],[17.815167650359953,19.468569806356484,-1607.5346,8.0,2.0,1.0,1.0],[19.468569806356484,21.94867304035128,0.0,8.0,2.0,1.0,1.0],[21.94867304035128,24.428776274346077,227.85,9.0,2.0,0.0,1.0],[24.428776274346077,35.17589028832353,890.0,0.0,2.0,0.0,-1.0],[35.17589028832353,175.71507354802864,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-71.46854877345271,17.815167650359953,-1860.0,9.0,2.0,0.0,1.0,0.3987729876506007],[17.815167650359953,19.468569806356484,-1607.5346,8.0,2.0,1.0,1.0,0.38432466656626335],[19.468569806356484,21.94867304035128,0.0,8.0,2.0,1.0,1.0,0.2923272045180706],[21.94867304035128,24.428776274346077,227.85,9.0,2.0,0.0,1.0,0.27787888492390445],[24.428776274346077,35.17589028832353,890.0,0.0,2.0,0.0,-1.0,0.23589093311667553],[35.17589028832353,175.71507354802864,1860.0,0.0,2.0,0.0,-1.0,0.17438173844324495]]</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>[[-68.09452862554292,18.104011572138802,-1860.0,8.0,1.0,1.0,1.0],[18.104011572138802,18.894823867530377,-1607.5346,8.0,1.0,1.0,1.0],[18.894823867530377,21.267260753705116,0.0,6.0,1.0,1.0,1.0],[21.267260753705116,22.05807304909669,227.85,9.0,1.0,0.0,1.0],[22.05807304909669,34.71106977536189,890.0,0.0,1.0,0.0,-1.0],[34.71106977536189,168.35834769653815,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-68.09452862554292,18.104011572138802,-1860.0,8.0,1.0,1.0,1.0,0.280827521575775],[18.104011572138802,18.894823867530377,-1607.5346,8.0,1.0,1.0,1.0,0.26637920049143765],[18.894823867530377,21.267260753705116,0.0,6.0,1.0,1.0,1.0,0.1743817384432449],[21.267260753705116,22.05807304909669,227.85,9.0,1.0,0.0,1.0,0.15993341884907875],[22.05807304909669,34.71106977536189,890.0,0.0,1.0,0.0,-1.0,0.11794546704184984],[34.71106977536189,168.35834769653815,1860.0,0.0,1.0,0.0,-1.0,0.05643627236841926]]</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>[[-75.20299798124202,17.67205711178549,-1860.0,8.0,0.0,1.0,1.0],[17.67205711178549,18.532011325609815,-1607.5346,8.0,0.0,1.0,1.0],[18.532011325609815,21.1118739670828,0.0,7.0,0.0,1.0,1.0],[21.1118739670828,25.411645036204447,227.85,9.0,0.0,0.0,1.0],[25.411645036204447,181.9233119522323,890.0001,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-75.20299798124202,17.67205711178549,-1860.0,8.0,0.0,1.0,1.0,0.16288205550094942],[17.67205711178549,18.532011325609815,-1607.5346,8.0,0.0,1.0,1.0,0.14843373441661206],[18.532011325609815,21.1118739670828,0.0,7.0,0.0,1.0,1.0,0.05643627236841932],[21.1118739670828,25.411645036204447,227.85,9.0,0.0,0.0,1.0,0.041987952774253184],[25.411645036204447,181.9233119522323,890.0001,0.0,0.0,0.0,-1.0,-5.374129828650265e-09]]</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>[[-73.0410672154109,20.680180431772186,-1860.0,9.0,0.0,0.0,1.0],[20.680180431772186,26.537758409721135,-733.6842,9.0,0.0,0.0,1.0],[26.537758409721135,177.16119212840826,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-73.0410672154109,20.680180431772186,-1860.0,9.0,0.0,0.0,1.0,0.10644577775840028],[20.680180431772186,26.537758409721135,-733.6842,9.0,0.0,0.0,1.0,0.041987945830689447],[26.537758409721135,177.16119212840826,0.0,0.0,0.0,1.0,-1.0,-5.374129828650265e-09]]</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>[[-75.09755653690594,20.461694978841308,-1860.0,6.0,0.0,0.0,1.0],[20.461694978841308,27.34884824123752,-733.6843,8.0,0.0,0.0,1.0],[27.34884824123752,30.792424872435618,0.0,7.0,0.0,1.0,1.0],[30.792424872435618,43.70583723942849,1016.4999,9.0,0.0,0.0,1.0],[43.70583723942849,182.309796645152,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-75.09755653690594,20.461694978841308,-1860.0,6.0,0.0,0.0,1.0,0.21289156089093042],[20.461694978841308,27.34884824123752,-733.6843,8.0,0.0,0.0,1.0,0.14843373468611115],[27.34884824123752,30.792424872435618,0.0,7.0,0.0,1.0,1.0,0.1064457777584003],[30.792424872435618,43.70583723942849,1016.4999,9.0,0.0,0.0,1.0,0.041987952774253184],[43.70583723942849,182.309796645152,1678.65,0.0,0.0,0.0,-1.0,-5.374129821711371e-09]]</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>[[-69.70557502480818,22.25612471109514,-1860.0,6.0,0.0,0.0,1.0],[22.25612471109514,26.289532594248797,-733.6843,7.0,0.0,0.0,1.0],[26.289532594248797,29.516258900771717,0.0,6.0,0.0,1.0,1.0],[29.516258900771717,48.06993516327853,1016.4999,8.0,0.0,0.0,1.0],[48.06993516327853,171.49221638778036,1860.0,8.0,1.0,0.0,1.0]]</t>
+          <t>[[-69.70557502480818,22.25612471109514,-1860.0,6.0,0.0,0.0,1.0,0.3193373440234605],[22.25612471109514,26.289532594248797,-733.6843,7.0,0.0,0.0,1.0,0.25487951781864127],[26.289532594248797,29.516258900771717,0.0,6.0,0.0,1.0,1.0,0.2128915608909304],[29.516258900771717,48.06993516327853,1016.4999,8.0,0.0,0.0,1.0,0.14843373590678327],[48.06993516327853,171.49221638778036,1860.0,8.0,1.0,0.0,1.0,0.09494609481610476]]</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>[[-64.4738325697537,21.36243635530417,-1860.0,6.0,0.0,0.0,1.0],[21.36243635530417,27.548834115668697,-733.6843,5.0,0.0,0.0,1.0],[27.548834115668697,30.64203299585097,0.0,6.0,0.0,1.0,1.0],[30.64203299585097,49.20122627694455,1016.4999,7.0,0.0,0.0,1.0],[49.20122627694455,166.74278372387062,1860.0,7.0,1.0,0.0,1.0]]</t>
+          <t>[[-64.4738325697537,21.36243635530417,-1860.0,6.0,0.0,0.0,1.0,0.4257831271559906],[21.36243635530417,27.548834115668697,-733.6843,5.0,0.0,0.0,1.0,0.3613253009511713],[27.548834115668697,30.64203299585097,0.0,6.0,0.0,1.0,1.0,0.3193373440234605],[30.64203299585097,49.20122627694455,1016.4999,7.0,0.0,0.0,1.0,0.2548795190393134],[49.20122627694455,166.74278372387062,1860.0,7.0,1.0,0.0,1.0,0.20139187794863483]]</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>[[-67.3008446324787,20.120023706313034,-1860.0,4.0,0.0,0.0,1.0],[20.120023706313034,26.595643583260568,-733.6843,4.0,0.0,0.0,1.0],[26.595643583260568,29.024001037115895,0.0,4.0,0.0,1.0,1.0],[29.024001037115895,46.831955698721615,1016.4999,4.0,0.0,0.0,1.0],[46.831955698721615,174.72544826843543,1860.0,6.0,1.0,0.0,1.0]]</t>
+          <t>[[-67.3008446324787,20.120023706313034,-1860.0,4.0,0.0,0.0,1.0,0.5322289102885207],[20.120023706313034,26.595643583260568,-733.6843,4.0,0.0,0.0,1.0,0.46777108408370144],[26.595643583260568,29.024001037115895,0.0,4.0,0.0,1.0,1.0,0.4257831271559906],[29.024001037115895,46.831955698721615,1016.4999,4.0,0.0,0.0,1.0,0.36132530217184344],[46.831955698721615,174.72544826843543,1860.0,6.0,1.0,0.0,1.0,0.30783766108116495]]</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>[[-66.56325670229319,21.150599629583624,-1860.0,3.0,0.0,0.0,1.0],[21.150599629583624,27.58831385577642,-733.6843,3.0,0.0,0.0,1.0],[27.58831385577642,30.807170968872825,0.0,3.0,0.0,1.0,1.0],[30.807170968872825,45.29202797780661,1016.4999,4.0,0.0,0.0,1.0],[45.29202797780661,174.0463125016625,1860.0,4.0,1.0,0.0,1.0]]</t>
+          <t>[[-66.56325670229319,21.150599629583624,-1860.0,3.0,0.0,0.0,1.0,0.6386746934210508],[21.150599629583624,27.58831385577642,-733.6843,3.0,0.0,0.0,1.0,0.5742168672162316],[27.58831385577642,30.807170968872825,0.0,3.0,0.0,1.0,1.0,0.5322289102885207],[30.807170968872825,45.29202797780661,1016.4999,4.0,0.0,0.0,1.0,0.4677710853043736],[45.29202797780661,174.0463125016625,1860.0,4.0,1.0,0.0,1.0,0.41428344421369506]]</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>[[-60.51792790956439,20.422631980968077,-1860.0,2.0,0.0,0.0,1.0],[20.422631980968077,26.363223532566778,-733.6843,2.0,0.0,0.0,1.0],[26.363223532566778,29.333519308366135,0.0,2.0,0.0,1.0,1.0],[29.333519308366135,45.67014607526261,1016.4999,3.0,0.0,0.0,1.0],[45.67014607526261,161.51168133143747,1860.0,3.0,1.0,0.0,1.0]]</t>
+          <t>[[-60.51792790956439,20.422631980968077,-1860.0,2.0,0.0,0.0,1.0,0.7451204765535808],[20.422631980968077,26.363223532566778,-733.6843,2.0,0.0,0.0,1.0,0.6806626503487616],[26.363223532566778,29.333519308366135,0.0,2.0,0.0,1.0,1.0,0.6386746934210508],[29.333519308366135,45.67014607526261,1016.4999,3.0,0.0,0.0,1.0,0.5742168684369037],[45.67014607526261,161.51168133143747,1860.0,3.0,1.0,0.0,1.0,0.5207292273462252]]</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>[[-52.16614976780807,20.538012141937024,-1860.0,2.0,0.0,0.0,1.0],[20.538012141937024,26.769797448486592,-733.6843,2.0,0.0,0.0,1.0],[26.769797448486592,29.539479806953075,0.0,1.0,0.0,1.0,1.0],[29.539479806953075,44.77273277851871,1016.4999,2.0,0.0,0.0,1.0],[44.77273277851871,154.8676065275613,1860.0,2.0,1.0,0.0,1.0]]</t>
+          <t>[[-52.16614976780807,20.538012141937024,-1860.0,2.0,0.0,0.0,1.0,0.8515662596861109],[20.538012141937024,26.769797448486592,-733.6843,2.0,0.0,0.0,1.0,0.7871084334812917],[26.769797448486592,29.539479806953075,0.0,1.0,0.0,1.0,1.0,0.7451204765535808],[29.539479806953075,44.77273277851871,1016.4999,2.0,0.0,0.0,1.0,0.6806626515694337],[44.77273277851871,154.8676065275613,1860.0,2.0,1.0,0.0,1.0,0.6271750104787552]]</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>[[-60.55376458005992,21.01860909750002,-1860.0,1.0,0.0,0.0,1.0],[21.01860909750002,28.01052684129087,-733.6843,0.0,0.0,0.0,1.0],[28.01052684129087,30.341166089221147,0.0,1.0,0.0,1.0,1.0],[30.341166089221147,44.32500157680286,1016.4999,2.0,0.0,0.0,1.0],[44.32500157680286,171.7332804636584,1860.0,2.0,1.0,0.0,1.0]]</t>
+          <t>[[-60.55376458005992,21.01860909750002,-1860.0,1.0,0.0,0.0,1.0,0.9580120428186409],[21.01860909750002,28.01052684129087,-733.6843,0.0,0.0,0.0,1.0,0.8935542166138217],[28.01052684129087,30.341166089221147,0.0,1.0,0.0,1.0,1.0,0.8515662596861109],[30.341166089221147,44.32500157680286,1016.4999,2.0,0.0,0.0,1.0,0.7871084347019638],[44.32500157680286,171.7332804636584,1860.0,2.0,1.0,0.0,1.0,0.7336207936112853]]</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>[0,0,2.3306392479,13.9838354876,0]</t>
+          <t>[6.9919177438,0,2.3306392479,13.9838354876,0]</t>
         </is>
       </c>
     </row>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>[[-56.2385964592886,23.408804336929137,-733.6844,0.0,0.0,0.0,1.0],[23.408804336929137,25.684444359678224,-733.6843,0.0,0.0,0.0,1.0],[25.684444359678224,28.718631056676998,0.0,0.0,0.0,1.0,1.0],[28.718631056676998,45.40665789017024,1016.4999,1.0,0.0,0.0,1.0],[45.40665789017024,170.56685914136955,1860.0,1.0,1.0,0.0,1.0]]</t>
+          <t>[[-56.2385964592886,23.408804336929137,-733.6844,0.0,0.0,0.0,1.0,1.0000000054692433],[23.408804336929137,25.684444359678224,-733.6843,0.0,0.0,0.0,1.0,0.9999999997463518],[25.684444359678224,28.718631056676998,0.0,0.0,0.0,1.0,1.0,0.9580120428186409],[28.718631056676998,45.40665789017024,1016.4999,1.0,0.0,0.0,1.0,0.8935542178344938],[45.40665789017024,170.56685914136955,1860.0,1.0,1.0,0.0,1.0,0.8400665767438154]]</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>[0,0,0,16.6880268335,0]</t>
+          <t>[0,0,3.034186697,16.6880268335,0]</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>[[-51.41174234434813,46.63608271221847,0.0,0.0,0.0,1.0,1.0],[46.63608271221847,51.60952311363852,1678.65,1.0,0.0,0.0,1.0],[51.60952311363852,161.02521194487952,1860.0,1.0,10.0,1.0,-1.0]]</t>
+          <t>[[-51.41174234434813,46.63608271221847,0.0,0.0,0.0,1.0,1.0,1.000000005469243],[46.63608271221847,51.60952311363852,1678.65,1.0,0.0,0.0,1.0,0.8935542223367129],[51.60952311363852,161.02521194487952,1860.0,1.0,10.0,1.0,-1.0,0.8820545393944175]]</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>[[-55.608752947207634,53.39435877677569,0.0,0.0,0.0,1.0,1.0],[53.39435877677569,54.87739431043532,708.65,1.0,9.0,1.0,-1.0],[54.87739431043532,166.1050593349081,1860.0,1.0,10.0,0.0,-1.0]]</t>
+          <t>[[-55.608752947207634,53.39435877677569,0.0,0.0,0.0,1.0,1.0,1.000000005469243],[53.39435877677569,54.87739431043532,708.65,1.0,9.0,1.0,-1.0,0.9550634170101435],[54.87739431043532,166.1050593349081,1860.0,1.0,10.0,0.0,-1.0,0.8820545393944175]]</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>[[-53.23941266134108,49.47474983861322,0.0,0.0,0.0,1.0,1.0],[49.47474983861322,50.9113115518993,890.0,0.0,8.0,2.0,-1.0],[50.9113115518993,161.526563474927,1860.0,0.0,9.0,1.0,-1.0]]</t>
+          <t>[[-53.23941266134108,49.47474983861322,0.0,0.0,0.0,1.0,1.0,1.000000005469243],[49.47474983861322,50.9113115518993,890.0,0.0,8.0,2.0,-1.0,0.943563734067848],[50.9113115518993,161.526563474927,1860.0,0.0,9.0,1.0,-1.0,0.8820545393944175]]</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>[[-51.89642279356859,41.69038586790117,-1860.0,1.0,8.0,0.0,-1.0],[41.69038586790117,43.13018292423148,-1074.7921,0.0,8.0,1.0,-1.0],[43.13018292423148,48.16947262138754,0.0,0.0,7.0,2.0,-1.0],[48.16947262138754,51.04906673404814,890.0001,0.0,7.0,2.0,-1.0],[51.04906673404814,163.35323712781184,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[-51.89642279356859,41.69038586790117,-1860.0,1.0,8.0,0.0,-1.0,0.9885003225269478],[41.69038586790117,43.13018292423148,-1074.7921,0.0,8.0,1.0,-1.0,0.9435637258402008],[43.13018292423148,48.16947262138754,0.0,0.0,7.0,2.0,-1.0,0.8820545393944177],[48.16947262138754,51.04906673404814,890.0001,0.0,7.0,2.0,-1.0,0.8256182616518686],[51.04906673404814,163.35323712781184,1860.0,0.0,8.0,1.0,-1.0,0.7641090733195921]]</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>[[-53.032845015439705,40.42333136810589,-1860.0,1.0,7.0,0.0,-1.0],[40.42333136810589,44.770130269666154,-1074.7921,0.0,7.0,1.0,-1.0],[44.770130269666154,49.84139565481979,0.0,0.0,7.0,1.0,-1.0],[49.84139565481979,163.58263357897994,1860.0,1.0,7.0,0.0,-1.0]]</t>
+          <t>[[-53.032845015439705,40.42333136810589,-1860.0,1.0,7.0,0.0,-1.0,0.8705548564521222],[40.42333136810589,44.770130269666154,-1074.7921,0.0,7.0,1.0,-1.0,0.8256182597653752],[44.770130269666154,49.84139565481979,0.0,0.0,7.0,1.0,-1.0,0.7641090733195921],[49.84139565481979,163.58263357897994,1860.0,1.0,7.0,0.0,-1.0,0.6461636072447665]]</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>[[-52.26927344609204,41.93913906070384,-1860.0,1.0,6.0,0.0,-1.0],[41.93913906070384,44.08023934494919,-1074.7921,0.0,6.0,1.0,-1.0],[44.08023934494919,48.362439913439914,0.0,0.0,5.0,2.0,-1.0],[48.362439913439914,51.93094038718219,890.0001,0.0,5.0,2.0,-1.0],[51.93094038718219,161.12705488369562,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[-52.26927344609204,41.93913906070384,-1860.0,1.0,6.0,0.0,-1.0,0.7526093903772966],[41.93913906070384,44.08023934494919,-1074.7921,0.0,6.0,1.0,-1.0,0.7076727936905496],[44.08023934494919,48.362439913439914,0.0,0.0,5.0,2.0,-1.0,0.6461636072447665],[48.362439913439914,51.93094038718219,890.0001,0.0,5.0,2.0,-1.0,0.5897273295022174],[51.93094038718219,161.12705488369562,1860.0,0.0,6.0,1.0,-1.0,0.5282181411699409]]</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>[[-64.4631704594937,42.266143696148546,-1860.0,1.0,5.0,0.0,-1.0],[42.266143696148546,43.92086174507324,-1074.7921,0.0,5.0,1.0,-1.0],[43.92086174507324,48.88501589184729,0.0,0.0,4.0,2.0,-1.0],[48.88501589184729,51.36709296523432,890.0001,0.0,4.0,2.0,-1.0],[51.36709296523432,182.91717785474685,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[-64.4631704594937,42.266143696148546,-1860.0,1.0,5.0,0.0,-1.0,0.634663924302471],[42.266143696148546,43.92086174507324,-1074.7921,0.0,5.0,1.0,-1.0,0.589727327615724],[43.92086174507324,48.88501589184729,0.0,0.0,4.0,2.0,-1.0,0.5282181411699409],[48.88501589184729,51.36709296523432,890.0001,0.0,4.0,2.0,-1.0,0.47178186342739176],[51.36709296523432,182.91717785474685,1860.0,0.0,5.0,1.0,-1.0,0.4102726750951153]]</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>[[-55.33792760024792,40.51861498274825,-1860.0,1.0,4.0,0.0,-1.0],[40.51861498274825,42.765252699537214,-1074.7921,0.0,4.0,1.0,-1.0],[42.765252699537214,48.007407372044824,0.0,0.0,3.0,2.0,-1.0],[48.007407372044824,50.25404508883379,890.0001,0.0,3.0,2.0,-1.0],[50.25404508883379,168.5769648397197,1860.0,0.0,4.0,1.0,-1.0]]</t>
+          <t>[[-55.33792760024792,40.51861498274825,-1860.0,1.0,4.0,0.0,-1.0,0.5167184582276454],[40.51861498274825,42.765252699537214,-1074.7921,0.0,4.0,1.0,-1.0,0.4717818615408984],[42.765252699537214,48.007407372044824,0.0,0.0,3.0,2.0,-1.0,0.4102726750951153],[48.007407372044824,50.25404508883379,890.0001,0.0,3.0,2.0,-1.0,0.3538363973525661],[50.25404508883379,168.5769648397197,1860.0,0.0,4.0,1.0,-1.0,0.29232720902028964]]</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>[[-64.98163912123921,42.08320575697077,-1860.0,1.0,3.0,0.0,-1.0],[42.08320575697077,43.74312583260193,-1074.7921,0.0,3.0,1.0,-1.0],[43.74312583260193,48.72288605949542,0.0,0.0,2.0,2.0,-1.0],[48.72288605949542,50.382806135126586,890.0001,0.0,2.0,2.0,-1.0],[50.382806135126586,183.1764121856196,1860.0,0.0,2.0,2.0,-1.0]]</t>
+          <t>[[-64.98163912123921,42.08320575697077,-1860.0,1.0,3.0,0.0,-1.0,0.3987729921528197],[42.08320575697077,43.74312583260193,-1074.7921,0.0,3.0,1.0,-1.0,0.3538363954660727],[43.74312583260193,48.72288605949542,0.0,0.0,2.0,2.0,-1.0,0.2923272090202896],[48.72288605949542,50.382806135126586,890.0001,0.0,2.0,2.0,-1.0,0.23589093127774044],[50.382806135126586,183.1764121856196,1860.0,0.0,2.0,2.0,-1.0,0.17438174294546394]]</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>[[-62.60895391934817,42.10233373454764,-1860.0,10.0,2.0,1.0,1.0],[42.10233373454764,46.19261840852795,-1074.7921,0.0,2.0,1.0,-1.0],[46.19261840852795,51.10096001730432,0.0,0.0,2.0,1.0,-1.0],[51.10096001730432,54.37318775648856,708.6501,1.0,2.0,0.0,-1.0],[54.37318775648856,181.99006958467407,1860.0,1.0,2.0,0.0,-1.0]]</t>
+          <t>[[-62.60895391934817,42.10233373454764,-1860.0,10.0,2.0,1.0,1.0,0.2808275260779941],[42.10233373454764,46.19261840852795,-1074.7921,0.0,2.0,1.0,-1.0,0.23589092939124712],[46.19261840852795,51.10096001730432,0.0,0.0,2.0,1.0,-1.0,0.174381742945464],[51.10096001730432,54.37318775648856,708.6501,1.0,2.0,0.0,-1.0,0.12944514814521035],[54.37318775648856,181.99006958467407,1860.0,1.0,2.0,0.0,-1.0,0.05643627687063836]]</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>[[-59.56714904607172,38.836330120855706,-1860.0,10.0,2.0,0.0,1.0],[38.836330120855706,42.80421234532858,-1808.4764,9.0,2.0,1.0,1.0],[42.80421234532858,47.565671014696036,-1074.7921,0.0,2.0,0.0,-1.0],[47.565671014696036,53.120706128958076,0.0,0.0,1.0,1.0,-1.0],[53.120706128958076,57.08858835343095,890.0001,0.0,1.0,1.0,-1.0],[57.08858835343095,177.7122079774065,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[-59.56714904607172,38.836330120855706,-1860.0,10.0,2.0,0.0,1.0,0.2808275260779941],[38.836330120855706,42.80421234532858,-1808.4764,9.0,2.0,1.0,1.0,0.27787888631895796],[42.80421234532858,47.565671014696036,-1074.7921,0.0,2.0,0.0,-1.0,0.23589092939124712],[47.565671014696036,53.120706128958076,0.0,0.0,1.0,1.0,-1.0,0.174381742945464],[53.120706128958076,57.08858835343095,890.0001,0.0,1.0,1.0,-1.0,0.11794546520291485],[57.08858835343095,177.7122079774065,1860.0,0.0,1.0,1.0,-1.0,0.05643627687063836]]</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>[[-61.16341826478167,33.70077652650323,-1860.0,9.0,2.0,0.0,1.0],[33.70077652650323,40.99802227967899,-1808.4764,9.0,2.0,0.0,1.0],[40.99802227967899,45.05204769810997,0.0,9.0,1.0,1.0,1.0],[45.05204769810997,49.916878200227146,227.8501,9.0,1.0,1.0,1.0],[49.916878200227146,55.59251378603052,890.0001,0.0,1.0,0.0,-1.0],[55.59251378603052,181.26730175739084,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-61.16341826478167,33.70077652650323,-1860.0,9.0,2.0,0.0,1.0,0.2808275260779941],[33.70077652650323,40.99802227967899,-1808.4764,9.0,2.0,0.0,1.0,0.27787888631895796],[40.99802227967899,45.05204769810997,0.0,9.0,1.0,1.0,1.0,0.174381742945464],[45.05204769810997,49.916878200227146,227.8501,9.0,1.0,1.0,1.0,0.15993341701014377],[49.916878200227146,55.59251378603052,890.0001,0.0,1.0,0.0,-1.0,0.11794546520291485],[55.59251378603052,181.26730175739084,1860.0,0.0,1.0,0.0,-1.0,0.05643627687063836]]</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>[[-61.02849072065784,33.13452721531837,-1860.0,9.0,1.0,0.0,1.0],[33.13452721531837,39.573024168205635,-733.6842,9.0,1.0,0.0,1.0],[39.573024168205635,43.597084763760165,0.0,9.0,0.0,1.0,1.0],[43.597084763760165,48.425957478425616,1197.85,9.0,0.0,1.0,1.0],[48.425957478425616,179.6103328935036,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-61.02849072065784,33.13452721531837,-1860.0,9.0,1.0,0.0,1.0,0.22439124833544502],[33.13452721531837,39.573024168205635,-733.6842,9.0,1.0,0.0,1.0,0.15993341640773417],[39.573024168205635,43.597084763760165,0.0,9.0,0.0,1.0,1.0,0.1179454652029149],[43.597084763760165,48.425957478425616,1197.85,9.0,0.0,1.0,1.0,0.04198795093531821],[48.425957478425616,179.6103328935036,1860.0,0.0,1.0,0.0,-1.0,-8.719107241761392e-10]]</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>[[-62.496006772997745,32.33286922366315,-1860.0,9.0,0.0,0.0,1.0],[32.33286922366315,45.41271418871983,-733.6842,9.0,0.0,0.0,1.0],[45.41271418871983,181.93359601149888,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-62.496006772997745,32.33286922366315,-1860.0,9.0,0.0,0.0,1.0,0.10644578226061933],[32.33286922366315,45.41271418871983,-733.6842,9.0,0.0,0.0,1.0,0.041987950332908495],[45.41271418871983,181.93359601149888,0.0,0.0,0.0,1.0,-1.0,-8.719107796872905e-10]]</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>[[-60.42253137883692,45.182074743614535,-1860.0,9.0,0.0,0.0,1.0],[45.182074743614535,45.98210963848159,-873.8504,8.0,8.0,2.0,-1.0],[45.98210963848159,50.782319007683924,0.0,8.0,8.0,2.0,-1.0],[50.782319007683924,178.787902186413,662.1501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-60.42253137883692,45.182074743614535,-1860.0,9.0,0.0,0.0,1.0,0.14843373346543862],[45.182074743614535,45.98210963848159,-873.8504,8.0,8.0,2.0,-1.0,0.09199746117628199],[45.98210963848159,50.782319007683924,0.0,8.0,8.0,2.0,-1.0,0.0419879503329085],[50.782319007683924,178.787902186413,662.1501,0.0,0.0,0.0,-1.0,-7.815474496741803e-09]]</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>[[-64.9145333426362,43.76613032192236,-1860.0,8.0,0.0,0.0,1.0],[43.76613032192236,47.914247255684145,-873.8504,7.0,8.0,2.0,-1.0],[47.914247255684145,52.891987576198275,0.0,7.0,8.0,2.0,-1.0],[52.891987576198275,53.721610962950635,890.0,8.0,8.0,1.0,-1.0],[53.721610962950635,183.14285929631808,1860.0,8.0,9.0,0.0,-1.0]]</t>
+          <t>[[-64.9145333426362,43.76613032192236,-1860.0,8.0,0.0,0.0,1.0,0.2548795165979687],[43.76613032192236,47.914247255684145,-873.8504,7.0,8.0,2.0,-1.0,0.19844324430881208],[47.914247255684145,52.891987576198275,0.0,7.0,8.0,2.0,-1.0,0.1484337334654386],[52.891987576198275,53.721610962950635,890.0,8.0,8.0,1.0,-1.0,0.09199746206404354],[53.721610962950635,183.14285929631808,1860.0,8.0,9.0,0.0,-1.0,0.030488267390612958]]</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>[[-71.30865920306935,45.01557877189201,-1860.0,6.0,0.0,0.0,1.0],[45.01557877189201,50.11007094597791,0.0,6.0,0.0,1.0,1.0],[50.11007094597791,56.05364514907812,890.0,7.0,8.0,1.0,-1.0],[56.05364514907812,182.5668674722113,1860.0,7.0,9.0,0.0,-1.0]]</t>
+          <t>[[-71.30865920306935,45.01557877189201,-1860.0,6.0,0.0,0.0,1.0,0.3613252997304988],[45.01557877189201,50.11007094597791,0.0,6.0,0.0,1.0,1.0,0.2548795165979687],[50.11007094597791,56.05364514907812,890.0,7.0,8.0,1.0,-1.0,0.19844324519657364],[56.05364514907812,182.5668674722113,1860.0,7.0,9.0,0.0,-1.0,0.13693405052314306]]</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>[[-68.1521206730526,47.51842565505724,-1860.0,5.0,0.0,0.0,1.0],[47.51842565505724,52.54757984323594,0.0,4.0,8.0,2.0,-1.0],[52.54757984323594,56.73854166671818,890.0,4.0,8.0,1.0,-1.0],[56.73854166671818,182.46739637118537,1860.0,5.0,8.0,1.0,-1.0]]</t>
+          <t>[[-68.1521206730526,47.51842565505724,-1860.0,5.0,0.0,0.0,1.0,0.46777108286302893],[47.51842565505724,52.54757984323594,0.0,4.0,8.0,2.0,-1.0,0.3613252997304988],[52.54757984323594,56.73854166671818,890.0,4.0,8.0,1.0,-1.0,0.30488902832910375],[56.73854166671818,182.46739637118537,1860.0,5.0,8.0,1.0,-1.0,0.24337983365567317]]</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>[[-73.34212685512695,43.492779197149034,-1860.0,4.0,0.0,0.0,1.0],[43.492779197149034,46.980388333037865,-873.8504,3.0,8.0,2.0,-1.0],[46.980388333037865,51.339899752898916,0.0,3.0,8.0,2.0,-1.0],[51.339899752898916,53.95560660481554,890.0,4.0,8.0,1.0,-1.0],[53.95560660481554,187.35665605256347,1860.0,3.0,9.0,0.0,-1.0]]</t>
+          <t>[[-73.34212685512695,43.492779197149034,-1860.0,4.0,0.0,0.0,1.0,0.574216865995559],[43.492779197149034,46.980388333037865,-873.8504,3.0,8.0,2.0,-1.0,0.5177805937064024],[46.980388333037865,51.339899752898916,0.0,3.0,8.0,2.0,-1.0,0.4677710828630289],[51.339899752898916,53.95560660481554,890.0,4.0,8.0,1.0,-1.0,0.4113348114616338],[53.95560660481554,187.35665605256347,1860.0,3.0,9.0,0.0,-1.0,0.34982561678820323]]</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>[[-70.5486966220579,43.40240810681965,-1860.0,4.0,0.0,0.0,1.0],[43.40240810681965,45.953552242540795,-873.8504,2.0,8.0,2.0,-1.0],[45.953552242540795,51.05584051398307,0.0,2.0,8.0,2.0,-1.0],[51.05584051398307,53.6069846497042,890.0,4.0,8.0,1.0,-1.0],[53.6069846497042,183.71533557148234,1860.0,3.0,9.0,0.0,-1.0]]</t>
+          <t>[[-70.5486966220579,43.40240810681965,-1860.0,4.0,0.0,0.0,1.0,0.6806626491280892],[43.40240810681965,45.953552242540795,-873.8504,2.0,8.0,2.0,-1.0,0.6242263768389326],[45.953552242540795,51.05584051398307,0.0,2.0,8.0,2.0,-1.0,0.5742168659955591],[51.05584051398307,53.6069846497042,890.0,4.0,8.0,1.0,-1.0,0.517780594594164],[53.6069846497042,183.71533557148234,1860.0,3.0,9.0,0.0,-1.0,0.45627139992073346]]</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>[[-74.27431348799063,44.65565709850972,-1860.0,2.0,0.0,0.0,1.0],[44.65565709850972,47.27911233203547,-873.8504,2.0,8.0,2.0,-1.0],[47.27911233203547,52.526022799086945,0.0,2.0,8.0,2.0,-1.0],[52.526022799086945,55.14947803261269,890.0,2.0,8.0,1.0,-1.0],[55.14947803261269,187.19672478674175,1860.0,2.0,9.0,0.0,-1.0]]</t>
+          <t>[[-74.27431348799063,44.65565709850972,-1860.0,2.0,0.0,0.0,1.0,0.7871084322606192],[44.65565709850972,47.27911233203547,-873.8504,2.0,8.0,2.0,-1.0,0.7306721599714626],[47.27911233203547,52.526022799086945,0.0,2.0,8.0,2.0,-1.0,0.6806626491280892],[52.526022799086945,55.14947803261269,890.0,2.0,8.0,1.0,-1.0,0.6242263777266941],[55.14947803261269,187.19672478674175,1860.0,2.0,9.0,0.0,-1.0,0.5627171830532636]]</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>[[-73.33128533984443,43.496332603495816,-1860.0,2.0,0.0,0.0,1.0],[43.496332603495816,45.24002839369493,-873.8504,1.0,8.0,2.0,-1.0],[45.24002839369493,50.47111576429225,0.0,1.0,8.0,2.0,-1.0],[50.47111576429225,53.08665944959091,890.0,2.0,8.0,1.0,-1.0],[53.08665944959091,187.35123529492222,1860.0,1.0,9.0,0.0,-1.0]]</t>
+          <t>[[-73.33128533984443,43.496332603495816,-1860.0,2.0,0.0,0.0,1.0,0.8935542153931493],[43.496332603495816,45.24002839369493,-873.8504,1.0,8.0,2.0,-1.0,0.8371179431039927],[45.24002839369493,50.47111576429225,0.0,1.0,8.0,2.0,-1.0,0.7871084322606192],[50.47111576429225,53.08665944959091,890.0,2.0,8.0,1.0,-1.0,0.7306721608592242],[53.08665944959091,187.35123529492222,1860.0,1.0,9.0,0.0,-1.0,0.6691629661857936]]</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>[[-67.8277320956066,46.09737344435854,-1860.0,1.0,0.0,0.0,1.0],[46.09737344435854,47.74846193044499,-873.8504,0.0,8.0,2.0,-1.0],[47.74846193044499,52.70172738870434,0.0,0.0,8.0,2.0,-1.0],[52.70172738870434,56.82944860392048,890.0,0.0,8.0,1.0,-1.0],[56.82944860392048,179.0099965743179,1860.0,0.0,9.0,0.0,-1.0]]</t>
+          <t>[[-67.8277320956066,46.09737344435854,-1860.0,1.0,0.0,0.0,1.0,0.9999999985256793],[46.09737344435854,47.74846193044499,-873.8504,0.0,8.0,2.0,-1.0,0.9435637262365227],[47.74846193044499,52.70172738870434,0.0,0.0,8.0,2.0,-1.0,0.8935542153931493],[52.70172738870434,56.82944860392048,890.0,0.0,8.0,1.0,-1.0,0.8371179439917542],[56.82944860392048,179.0099965743179,1860.0,0.0,9.0,0.0,-1.0,0.7756087493183237]]</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>[[-73.92392189969307,50.30065842600803,0.0,0.0,0.0,1.0,1.0],[50.30065842600803,55.54958435526301,890.0,0.0,8.0,1.0,-1.0],[55.54958435526301,187.64755357484654,1860.0,0.0,9.0,0.0,-1.0]]</t>
+          <t>[[-73.92392189969307,50.30065842600803,0.0,0.0,0.0,1.0,1.0,0.9999999985256793],[50.30065842600803,55.54958435526301,890.0,0.0,8.0,1.0,-1.0,0.9435637271242843],[55.54958435526301,187.64755357484654,1860.0,0.0,9.0,0.0,-1.0,0.8820545324508537]]</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>[[-70.16087468141997,40.754335388867986,0.0,0.0,0.0,1.0,1.0],[40.754335388867986,63.61472219724796,890.0,0.0,8.0,0.0,-1.0],[63.61472219724796,182.99674219656552,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-70.16087468141997,40.754335388867986,0.0,0.0,0.0,1.0,1.0,0.9999999985256793],[40.754335388867986,63.61472219724796,890.0,0.0,8.0,0.0,-1.0,0.9435637271242843],[63.61472219724796,182.99674219656552,1860.0,0.0,8.0,0.0,-1.0,0.8820545324508537]]</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>[[-74.3308536195128,35.27695284130209,-986.1497,0.0,0.0,0.0,1.0],[35.27695284130209,44.04557735816728,0.0,0.0,8.0,1.0,-1.0],[44.04557735816728,187.85101943475638,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-74.3308536195128,35.27695284130209,-986.1497,0.0,0.0,0.0,1.0,1.0000000051363325],[35.27695284130209,44.04557735816728,0.0,0.0,8.0,1.0,-1.0,0.9435637271242843],[44.04557735816728,187.85101943475638,1860.0,0.0,8.0,0.0,-1.0,0.8256182610494587]]</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>[[-72.27076061565096,36.04518150327732,-1860.0,1.0,7.0,0.0,-1.0],[36.04518150327732,42.11087426193731,0.0,0.0,6.0,1.0,-1.0],[42.11087426193731,186.82097293282547,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-72.27076061565096,36.04518150327732,-1860.0,1.0,7.0,0.0,-1.0,0.9320640441819887],[36.04518150327732,42.11087426193731,0.0,0.0,6.0,1.0,-1.0,0.8256182610494587],[42.11087426193731,186.82097293282547,1860.0,0.0,7.0,0.0,-1.0,0.7076727949746331]]</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>[[-68.28236277642851,35.009094279128476,-1860.0,1.0,6.0,0.0,-1.0],[35.009094279128476,42.44607918712859,0.0,0.0,6.0,1.0,-1.0],[42.44607918712859,178.7908025004638,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[-68.28236277642851,35.009094279128476,-1860.0,1.0,6.0,0.0,-1.0,0.8141185781071631],[35.009094279128476,42.44607918712859,0.0,0.0,6.0,1.0,-1.0,0.7076727949746331],[42.44607918712859,178.7908025004638,1860.0,0.0,6.0,0.0,-1.0,0.5897273288998075]]</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>[[-70.29999513484253,34.9224184234527,-1860.0,1.0,5.0,1.0,-1.0],[34.9224184234527,41.6566528911836,0.0,0.0,5.0,1.0,-1.0],[41.6566528911836,181.39201809659966,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-70.29999513484253,34.9224184234527,-1860.0,1.0,5.0,1.0,-1.0,0.6961731120323376],[34.9224184234527,41.6566528911836,0.0,0.0,5.0,1.0,-1.0,0.5897273288998075],[41.6566528911836,181.39201809659966,1860.0,0.0,5.0,0.0,-1.0,0.47178186282498186]]</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>[[-73.30516281458453,36.53115973627325,-1860.0,1.0,4.0,0.0,-1.0],[36.53115973627325,41.76146081012362,0.0,0.0,4.0,1.0,-1.0],[41.76146081012362,187.33817403229227,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-73.30516281458453,36.53115973627325,-1860.0,1.0,4.0,0.0,-1.0,0.578227645957512],[36.53115973627325,41.76146081012362,0.0,0.0,4.0,1.0,-1.0,0.4717818628249819],[41.76146081012362,187.33817403229227,1860.0,0.0,4.0,0.0,-1.0,0.35383639675015627]]</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>[[-62.00120841207045,36.062508574454576,-1860.0,1.0,3.0,0.0,-1.0],[36.062508574454576,42.85153513506015,0.0,0.0,3.0,1.0,-1.0],[42.85153513506015,163.54534065693713,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-62.00120841207045,36.062508574454576,-1860.0,1.0,3.0,0.0,-1.0,0.4602821798826863],[36.062508574454576,42.85153513506015,0.0,0.0,3.0,1.0,-1.0,0.3538363967501562],[42.85153513506015,163.54534065693713,1860.0,0.0,3.0,0.0,-1.0,0.23589093067533057]]</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>[[-55.071464183907686,36.19444631252181,-1860.0,1.0,2.0,0.0,-1.0],[36.19444631252181,42.41712202818746,0.0,0.0,2.0,1.0,-1.0],[42.41712202818746,151.65965125876215,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-55.071464183907686,36.19444631252181,-1860.0,1.0,2.0,0.0,-1.0,0.3423367138078607],[36.19444631252181,42.41712202818746,0.0,0.0,2.0,1.0,-1.0,0.2358909306753306],[42.41712202818746,151.65965125876215,1860.0,0.0,2.0,0.0,-1.0,0.11794546460050497]]</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>[[-37.90986802591361,35.781242866742716,-1860.0,1.0,1.0,0.0,-1.0],[35.781242866742716,40.970757718338234,0.0,0.0,1.0,1.0,-1.0],[40.970757718338234,42.52761217381689,0.0,0.0,0.0,1.0,-1.0],[42.52761217381689,47.19817554025285,1860.0,0.0,0.0,0.0,-1.0],[47.19817554025285,117.2566260367923,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-37.90986802591361,35.781242866742716,-1860.0,1.0,1.0,0.0,-1.0,0.224391247733035],[35.781242866742716,40.970757718338234,0.0,0.0,1.0,1.0,-1.0,0.1179454646005049],[40.970757718338234,42.52761217381689,0.0,0.0,0.0,1.0,-1.0,0.1179454646005049],[42.52761217381689,47.19817554025285,1860.0,0.0,0.0,0.0,-1.0,-1.4743207349399157e-09],[47.19817554025285,117.2566260367923,1860.0,0.0,1.0,0.0,-1.0,-1.4743207349399157e-09]]</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>[0,0,5.1895148516,0,0]</t>
+          <t>[0,0,6.7463693071,0,0]</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>[[-35.51111917278135,35.576171109245024,-1860.0,1.0,0.0,0.0,-1.0],[35.576171109245024,112.09374051003729,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-35.51111917278135,35.576171109245024,-1860.0,1.0,0.0,0.0,-1.0,0.10644578165820942],[35.576171109245024,112.09374051003729,0.0,0.0,0.0,1.0,-1.0,-1.474320693306552e-09]]</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>[[-38.261590282984656,33.73431099839502,-1860.0,1.0,0.0,0.0,-1.0],[33.73431099839502,116.6072908906306,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-38.261590282984656,33.73431099839502,-1860.0,1.0,0.0,0.0,-1.0,0.10644578165820942],[33.73431099839502,116.6072908906306,0.0,0.0,0.0,1.0,-1.0,-1.474320693306552e-09]]</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>[[-36.414039058382414,34.11364336956133,-1860.0,1.0,0.0,0.0,-1.0],[34.11364336956133,115.29658717151098,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-36.414039058382414,34.11364336956133,-1860.0,1.0,0.0,0.0,-1.0,0.10644578165820942],[34.11364336956133,115.29658717151098,0.0,0.0,0.0,1.0,-1.0,-1.474320693306552e-09]]</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>[[-35.26962761303456,29.135946655655445,-1860.0,1.0,0.0,0.0,-1.0],[29.135946655655445,110.61875652589205,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-35.26962761303456,29.135946655655445,-1860.0,1.0,0.0,0.0,-1.0,0.10644578165820942],[29.135946655655445,110.61875652589205,0.0,0.0,0.0,1.0,-1.0,-1.474320693306552e-09]]</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>[[-36.29539611385319,27.11197401641879,-1860.0,9.0,0.0,0.0,1.0],[27.11197401641879,27.611244647365815,-733.6842,9.0,0.0,0.0,1.0],[27.611244647365815,112.98652253930683,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-36.29539611385319,27.11197401641879,-1860.0,9.0,0.0,0.0,1.0,0.10644578165820942],[27.11197401641879,27.611244647365815,-733.6842,9.0,0.0,0.0,1.0,0.04198794973049858],[27.611244647365815,112.98652253930683,0.0,0.0,0.0,1.0,-1.0,-1.474320693306552e-09]]</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>[[-34.4690359545955,28.212523379669925,-1860.0,9.0,0.0,0.0,1.0],[28.212523379669925,35.015173229900284,-733.6842,9.0,0.0,0.0,1.0],[35.015173229900284,110.81612870389566,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-34.4690359545955,28.212523379669925,-1860.0,9.0,0.0,0.0,1.0,0.10644578165820942],[28.212523379669925,35.015173229900284,-733.6842,9.0,0.0,0.0,1.0,0.04198794973049858],[35.015173229900284,110.81612870389566,0.0,0.0,0.0,1.0,-1.0,-1.474320693306552e-09]]</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>[[-32.90289514849633,29.176136846658288,-1860.0,7.0,0.0,0.0,1.0],[29.176136846658288,35.33665147213165,-733.6842,7.0,0.0,0.0,1.0],[35.33665147213165,39.60162313592089,0.0,7.0,8.0,3.0,-1.0],[39.60162313592089,40.07550887634193,227.85,7.0,8.0,1.0,-1.0],[40.07550887634193,108.78894123739094,1678.6501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-32.90289514849633,29.176136846658288,-1860.0,7.0,0.0,0.0,1.0,0.2128915647907395],[29.176136846658288,35.33665147213165,-733.6842,7.0,0.0,0.0,1.0,0.1484337328630287],[35.33665147213165,39.60162313592089,0.0,7.0,8.0,3.0,-1.0,0.1064457816582094],[39.60162313592089,40.07550887634193,227.85,7.0,8.0,1.0,-1.0,0.09199746206404327],[40.07550887634193,108.78894123739094,1678.6501,0.0,0.0,0.0,-1.0,-7.815474808992029e-09]]</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>[[-40.165362852779694,28.870181615617582,-1860.0,6.0,0.0,0.0,1.0],[28.870181615617582,33.61308161726319,-733.6842,7.0,0.0,0.0,1.0],[33.61308161726319,37.30200384076534,0.0,7.0,8.0,3.0,-1.0],[37.30200384076534,39.93694828612401,227.85,7.0,8.0,1.0,-1.0],[39.93694828612401,117.40431497966907,1860.0,7.0,9.0,0.0,-1.0]]</t>
+          <t>[[-40.165362852779694,28.870181615617582,-1860.0,6.0,0.0,0.0,1.0,0.3193373479232696],[28.870181615617582,33.61308161726319,-733.6842,7.0,0.0,0.0,1.0,0.2548795159955588],[33.61308161726319,37.30200384076534,0.0,7.0,8.0,3.0,-1.0,0.2128915647907395],[37.30200384076534,39.93694828612401,227.85,7.0,8.0,1.0,-1.0,0.19844324519657336],[39.93694828612401,117.40431497966907,1860.0,7.0,9.0,0.0,-1.0,0.09494609871591388]]</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>[[-40.520544861219804,27.474563740764808,-1860.0,6.0,0.0,0.0,1.0],[27.474563740764808,35.26026319900731,-733.6842,5.0,0.0,0.0,1.0],[35.26026319900731,39.41263624340333,0.0,5.0,8.0,2.0,-1.0],[39.41263624340333,114.67439767308097,1860.0,6.0,9.0,0.0,-1.0]]</t>
+          <t>[[-40.520544861219804,27.474563740764808,-1860.0,6.0,0.0,0.0,1.0,0.42578313105579974],[27.474563740764808,35.26026319900731,-733.6842,5.0,0.0,0.0,1.0,0.3613252991280889],[35.26026319900731,39.41263624340333,0.0,5.0,8.0,2.0,-1.0,0.3193373479232696],[39.41263624340333,114.67439767308097,1860.0,6.0,9.0,0.0,-1.0,0.20139188184844398]]</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>[[-45.69116193451907,28.777700018365536,-1860.0,4.0,0.0,0.0,1.0],[28.777700018365536,35.30052004343571,-733.6842,4.0,0.0,0.0,1.0],[35.30052004343571,39.105498391393326,0.0,4.0,8.0,2.0,-1.0],[39.105498391393326,41.27977173308338,227.85,4.0,8.0,1.0,-1.0],[41.27977173308338,116.83577035681301,1860.0,4.0,9.0,0.0,-1.0]]</t>
+          <t>[[-45.69116193451907,28.777700018365536,-1860.0,4.0,0.0,0.0,1.0,0.5322289141883298],[28.777700018365536,35.30052004343571,-733.6842,4.0,0.0,0.0,1.0,0.467771082260619],[35.30052004343571,39.105498391393326,0.0,4.0,8.0,2.0,-1.0,0.4257831310557997],[39.105498391393326,41.27977173308338,227.85,4.0,8.0,1.0,-1.0,0.41133481146163353],[41.27977173308338,116.83577035681301,1860.0,4.0,9.0,0.0,-1.0,0.30783766498097404]]</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>[[-47.40580798825006,28.996286888122228,-1860.0,4.0,0.0,0.0,1.0],[28.996286888122228,36.24612070850792,-733.6842,3.0,0.0,0.0,1.0],[36.24612070850792,40.14987738102329,0.0,3.0,0.0,1.0,1.0],[40.14987738102329,119.34036988062084,1860.0,4.0,9.0,0.0,-1.0]]</t>
+          <t>[[-47.40580798825006,28.996286888122228,-1860.0,4.0,0.0,0.0,1.0,0.6386746973208599],[28.996286888122228,36.24612070850792,-733.6842,3.0,0.0,0.0,1.0,0.5742168653931491],[36.24612070850792,40.14987738102329,0.0,3.0,0.0,1.0,1.0,0.5322289141883298],[40.14987738102329,119.34036988062084,1860.0,4.0,9.0,0.0,-1.0,0.4142834481135042]]</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>[[-48.19637509909735,29.32562809438474,-1860.0,2.0,0.0,0.0,1.0],[29.32562809438474,36.11587654928829,-733.6842,2.0,0.0,0.0,1.0],[36.11587654928829,40.076854814648684,0.0,3.0,8.0,2.0,-1.0],[40.076854814648684,40.642708852557305,227.85,2.0,8.0,1.0,-1.0],[40.642708852557305,120.99398223558256,1860.0,2.0,9.0,0.0,-1.0]]</t>
+          <t>[[-48.19637509909735,29.32562809438474,-1860.0,2.0,0.0,0.0,1.0,0.74512048045339],[29.32562809438474,36.11587654928829,-733.6842,2.0,0.0,0.0,1.0,0.6806626485256791],[36.11587654928829,40.076854814648684,0.0,3.0,8.0,2.0,-1.0,0.6386746973208599],[40.076854814648684,40.642708852557305,227.85,2.0,8.0,1.0,-1.0,0.6242263777266938],[40.642708852557305,120.99398223558256,1860.0,2.0,9.0,0.0,-1.0,0.5207292312460343]]</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>[[-44.91840199608115,28.53508218748535,-1860.0,2.0,0.0,0.0,1.0],[28.53508218748535,35.556371116796846,-733.6842,2.0,0.0,0.0,1.0],[35.556371116796846,39.337065155656894,0.0,2.0,0.0,1.0,1.0],[39.337065155656894,42.037560897699784,1016.5,2.0,0.0,0.0,1.0],[42.037560897699784,116.57124337808344,1860.0,2.0,9.0,0.0,-1.0]]</t>
+          <t>[[-44.91840199608115,28.53508218748535,-1860.0,2.0,0.0,0.0,1.0,0.85156626358592],[28.53508218748535,35.556371116796846,-733.6842,2.0,0.0,0.0,1.0,0.7871084316582092],[35.556371116796846,39.337065155656894,0.0,2.0,0.0,1.0,1.0,0.74512048045339],[39.337065155656894,42.037560897699784,1016.5,2.0,0.0,0.0,1.0,0.6806626491280887],[42.037560897699784,116.57124337808344,1860.0,2.0,9.0,0.0,-1.0,0.6271750143785644]]</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>[[-46.56886487284394,27.038638336179936,-1860.0,1.0,0.0,0.0,1.0],[27.038638336179936,36.44711618996494,-733.6842,1.0,0.0,0.0,1.0],[36.44711618996494,40.32119530622935,0.0,1.0,8.0,4.0,-1.0],[40.32119530622935,41.98151492748553,227.85,1.0,8.0,1.0,-1.0],[41.98151492748553,118.90965737902175,1860.0,1.0,9.0,0.0,-1.0]]</t>
+          <t>[[-46.56886487284394,27.038638336179936,-1860.0,1.0,0.0,0.0,1.0,0.9580120467184501],[27.038638336179936,36.44711618996494,-733.6842,1.0,0.0,0.0,1.0,0.8935542147907393],[36.44711618996494,40.32119530622935,0.0,1.0,8.0,4.0,-1.0,0.85156626358592],[40.32119530622935,41.98151492748553,227.85,1.0,8.0,1.0,-1.0,0.8371179439917539],[41.98151492748553,118.90965737902175,1860.0,1.0,9.0,0.0,-1.0,0.7336207975110944]]</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>[[-45.9979552411504,35.39751955892425,-1860.0,1.0,0.0,0.0,1.0],[35.39751955892425,37.014648197336335,0.0,0.0,0.0,1.0,1.0],[37.014648197336335,41.32699123310187,0.0,1.0,0.0,1.0,1.0],[41.32699123310187,44.02220563045534,890.0,1.0,8.0,0.0,-1.0],[44.02220563045534,115.17586572058683,1860.0,1.0,8.0,0.0,-1.0]]</t>
+          <t>[[-45.9979552411504,35.39751955892425,-1860.0,1.0,0.0,0.0,1.0,0.9999999979232694],[35.39751955892425,37.014648197336335,0.0,0.0,0.0,1.0,1.0,0.8935542147907393],[37.014648197336335,41.32699123310187,0.0,1.0,0.0,1.0,1.0,0.8935542147907393],[41.32699123310187,44.02220563045534,890.0,1.0,8.0,0.0,-1.0,0.8371179433893442],[44.02220563045534,115.17586572058683,1860.0,1.0,8.0,0.0,-1.0,0.7756087487159137]]</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="F234" s="4" t="inlineStr">
         <is>
-          <t>[0,0,4.3123430358,0,2.6952143974]</t>
+          <t>[0,0,5.9294716742,0,2.6952143974]</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>[[-46.73519968233807,40.05214980757233,0.0,0.0,0.0,1.0,1.0],[40.05214980757233,43.3688638008173,890.0,0.0,8.0,0.0,-1.0],[43.3688638008173,118.54771431437024,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-46.73519968233807,40.05214980757233,0.0,0.0,0.0,1.0,1.0,0.9999999979232694],[40.05214980757233,43.3688638008173,890.0,0.0,8.0,0.0,-1.0,0.9435637265218744],[43.3688638008173,118.54771431437024,1860.0,0.0,8.0,0.0,-1.0,0.8820545318484438]]</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>[[-45.787063530956715,39.01645170246444,0.0,0.0,0.0,1.0,1.0],[39.01645170246444,42.27812536528833,890.0,0.0,8.0,0.0,-1.0],[42.27812536528833,116.7530073331005,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-45.787063530956715,39.01645170246444,0.0,0.0,0.0,1.0,1.0,0.9999999979232694],[39.01645170246444,42.27812536528833,890.0,0.0,8.0,0.0,-1.0,0.9435637265218744],[42.27812536528833,116.7530073331005,1860.0,0.0,8.0,0.0,-1.0,0.8820545318484438]]</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>[[-48.805047236051934,35.71397014341068,-1860.0,1.0,8.0,0.0,-1.0],[35.71397014341068,39.71149123568256,0.0,0.0,7.0,2.0,-1.0],[39.71149123568256,41.99578900269506,890.0,0.0,7.0,0.0,-1.0],[41.99578900269506,121.94621084813267,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-48.805047236051934,35.71397014341068,-1860.0,1.0,8.0,0.0,-1.0,0.9885003149809739],[35.71397014341068,39.71149123568256,0.0,0.0,7.0,2.0,-1.0,0.8820545318484438],[39.71149123568256,41.99578900269506,890.0,0.0,7.0,0.0,-1.0,0.8256182604470488],[41.99578900269506,121.94621084813267,1860.0,0.0,7.0,0.0,-1.0,0.7641090657736183]]</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>[[-47.12138947645559,34.283548041773145,-1860.0,1.0,7.0,1.0,-1.0],[34.283548041773145,36.51382030254652,-1074.7923,0.0,7.0,2.0,-1.0],[36.51382030254652,40.41679675889996,0.0,0.0,6.0,3.0,-1.0],[40.41679675889996,42.64706901967335,890.0,0.0,6.0,0.0,-1.0],[42.64706901967335,119.59146201635531,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[-47.12138947645559,34.283548041773145,-1860.0,1.0,7.0,1.0,-1.0,0.8705548489061483],[34.283548041773145,36.51382030254652,-1074.7923,0.0,7.0,2.0,-1.0,0.8256182636651845],[36.51382030254652,40.41679675889996,0.0,0.0,6.0,3.0,-1.0,0.7641090657736183],[40.41679675889996,42.64706901967335,890.0,0.0,6.0,0.0,-1.0,0.7076727943722232],[42.64706901967335,119.59146201635531,1860.0,0.0,6.0,0.0,-1.0,0.6461635996987927]]</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>[[-46.25975501464441,35.2876917233215,-1860.0,1.0,6.0,0.0,-1.0],[35.2876917233215,39.11877982510512,0.0,0.0,5.0,2.0,-1.0],[39.11877982510512,39.66607812535993,890.0,0.0,5.0,1.0,-1.0],[39.66607812535993,117.38243676154222,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[-46.25975501464441,35.2876917233215,-1860.0,1.0,6.0,0.0,-1.0,0.7526093828313227],[35.2876917233215,39.11877982510512,0.0,0.0,5.0,2.0,-1.0,0.6461635996987927],[39.11877982510512,39.66607812535993,890.0,0.0,5.0,1.0,-1.0,0.5897273282973976],[39.66607812535993,117.38243676154222,1860.0,0.0,5.0,1.0,-1.0,0.5282181336239671]]</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>[[-47.68272460655692,34.21965403116536,-1860.0,1.0,5.0,0.0,-1.0],[34.21965403116536,35.34160442346294,-1074.7923,0.0,5.0,1.0,-1.0],[35.34160442346294,39.26843079650442,0.0,0.0,4.0,2.0,-1.0],[39.26843079650442,40.39038118880198,890.0,0.0,4.0,0.0,-1.0],[40.39038118880198,120.04885904192915,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-47.68272460655692,34.21965403116536,-1860.0,1.0,5.0,0.0,-1.0,0.6346639167564971],[34.21965403116536,35.34160442346294,-1074.7923,0.0,5.0,1.0,-1.0,0.5897273315155334],[35.34160442346294,39.26843079650442,0.0,0.0,4.0,2.0,-1.0,0.5282181336239671],[39.26843079650442,40.39038118880198,890.0,0.0,4.0,0.0,-1.0,0.471781862222572],[40.39038118880198,120.04885904192915,1860.0,0.0,4.0,0.0,-1.0,0.41027266754914143]]</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>[[-43.42665392824662,34.05303780289252,-1860.0,1.0,4.0,0.0,-1.0],[34.05303780289252,34.573035733973995,-1074.7923,0.0,4.0,0.0,-1.0],[34.573035733973995,38.73301918262575,0.0,0.0,3.0,1.0,-1.0],[38.73301918262575,40.29301297587017,890.0,0.0,3.0,0.0,-1.0],[40.29301297587017,112.05272746511312,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-43.42665392824662,34.05303780289252,-1860.0,1.0,4.0,0.0,-1.0,0.5167184506816715],[34.05303780289252,34.573035733973995,-1074.7923,0.0,4.0,0.0,-1.0,0.47178186544070766],[34.573035733973995,38.73301918262575,0.0,0.0,3.0,1.0,-1.0,0.4102726675491414],[38.73301918262575,40.29301297587017,890.0,0.0,3.0,0.0,-1.0,0.3538363961477463],[40.29301297587017,112.05272746511312,1860.0,0.0,3.0,0.0,-1.0,0.29232720147431573]]</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>[[-28.438364872686705,33.262176054666035,-1860.0,1.0,3.0,1.0,-1.0],[33.262176054666035,35.12062608259835,-1074.7923,0.0,3.0,1.0,-1.0],[35.12062608259835,38.83752613846298,0.0,0.0,2.0,2.0,-1.0],[38.83752613846298,39.209216144049435,890.0,0.0,2.0,0.0,-1.0],[39.209216144049435,82.69694679766553,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-28.438364872686705,33.262176054666035,-1860.0,1.0,3.0,1.0,-1.0,0.3987729846068459],[33.262176054666035,35.12062608259835,-1074.7923,0.0,3.0,1.0,-1.0,0.35383639936588207],[35.12062608259835,38.83752613846298,0.0,0.0,2.0,2.0,-1.0,0.2923272014743158],[38.83752613846298,39.209216144049435,890.0,0.0,2.0,0.0,-1.0,0.23589093007292072],[39.209216144049435,82.69694679766553,1860.0,0.0,2.0,0.0,-1.0,0.17438173539949015]]</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>[[-31.074123435346504,34.24494208211277,-1860.0,0.0,2.0,0.0,-1.0],[34.24494208211277,36.62018082820221,-1074.7923,0.0,2.0,1.0,-1.0],[36.62018082820221,40.578912071684584,0.0,0.0,1.0,2.0,-1.0],[40.578912071684584,87.29194074477667,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-31.074123435346504,34.24494208211277,-1860.0,0.0,2.0,0.0,-1.0,0.2808275185320202],[34.24494208211277,36.62018082820221,-1074.7923,0.0,2.0,1.0,-1.0,0.23589093329105637],[36.62018082820221,40.578912071684584,0.0,0.0,1.0,2.0,-1.0,0.1743817353994901],[40.578912071684584,87.29194074477667,1860.0,0.0,1.0,0.0,-1.0,0.05643626932466446]]</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>[[-28.16885745485601,34.88510791557208,-1860.0,1.0,1.0,1.0,-1.0],[34.88510791557208,35.97852928037719,-1074.7923,0.0,1.0,1.0,-1.0],[35.97852928037719,39.6232671630609,0.0,0.0,0.0,2.0,-1.0],[39.6232671630609,42.17458368093949,890.0,0.0,0.0,0.0,-1.0],[42.17458368093949,80.80880523738676,890.0001,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-28.16885745485601,34.88510791557208,-1860.0,1.0,1.0,1.0,-1.0,0.16288205245719461],[34.88510791557208,35.97852928037719,-1074.7923,0.0,1.0,1.0,-1.0,0.11794546721623078],[35.97852928037719,39.6232671630609,0.0,0.0,0.0,2.0,-1.0,0.05643626932466451],[39.6232671630609,42.17458368093949,890.0,0.0,0.0,0.0,-1.0,-2.076730544475769e-09],[42.17458368093949,80.80880523738676,890.0001,0.0,0.0,0.0,-1.0,-8.417884639344564e-09]]</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>[[-27.720435524112595,35.736042929461085,-1860.0,1.0,0.0,0.0,-1.0],[35.736042929461085,80.08346821235634,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-27.720435524112595,35.736042929461085,-1860.0,1.0,0.0,0.0,-1.0,0.10644578105579958],[35.736042929461085,80.08346821235634,0.0,0.0,0.0,1.0,-1.0,-2.076730537536875e-09]]</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>[[-28.92722290309662,33.33584921634973,-1860.0,1.0,0.0,0.0,-1.0],[33.33584921634973,82.54977448441511,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-28.92722290309662,33.33584921634973,-1860.0,1.0,0.0,0.0,-1.0,0.10644578105579958],[33.33584921634973,82.54977448441511,0.0,0.0,0.0,1.0,-1.0,-2.076730537536875e-09]]</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>[[-29.27200740596792,27.173986694446803,-1860.0,1.0,0.0,0.0,-1.0],[27.173986694446803,83.99881297003209,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-29.27200740596792,27.173986694446803,-1860.0,1.0,0.0,0.0,-1.0,0.10644578105579958],[27.173986694446803,83.99881297003209,0.0,0.0,0.0,1.0,-1.0,-2.076730537536875e-09]]</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>[[-28.737204425413648,23.50721188793168,-1860.0,9.0,0.0,0.0,1.0],[23.50721188793168,24.999909496884403,-733.6842,9.0,0.0,0.0,1.0],[24.999909496884403,82.84194184380243,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-28.737204425413648,23.50721188793168,-1860.0,9.0,0.0,0.0,1.0,0.10644578105579958],[23.50721188793168,24.999909496884403,-733.6842,9.0,0.0,0.0,1.0,0.04198794912808874],[24.999909496884403,82.84194184380243,0.0,0.0,0.0,1.0,-1.0,-2.076730537536875e-09]]</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>[[-30.15789664724482,24.100017907285626,-1860.0,9.0,0.0,0.0,1.0],[24.100017907285626,29.872136476916523,-733.6842,9.0,0.0,0.0,1.0],[29.872136476916523,84.89966684073107,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-30.15789664724482,24.100017907285626,-1860.0,9.0,0.0,0.0,1.0,0.10644578105579958],[24.100017907285626,29.872136476916523,-733.6842,9.0,0.0,0.0,1.0,0.04198794912808874],[29.872136476916523,84.89966684073107,0.0,0.0,0.0,1.0,-1.0,-2.076730537536875e-09]]</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>[[-29.733555115608347,24.66124925491406,-1860.0,7.0,0.0,0.0,1.0],[24.66124925491406,30.790241296663062,-733.6842,7.0,0.0,0.0,1.0],[30.790241296663062,33.85473731753756,0.0,7.0,0.0,1.0,1.0],[33.85473731753756,36.15310933319345,1016.5,8.0,0.0,0.0,1.0],[36.15310933319345,84.80198366457616,1678.6501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-29.733555115608347,24.66124925491406,-1860.0,7.0,0.0,0.0,1.0,0.21289156418832972],[24.66124925491406,30.790241296663062,-733.6842,7.0,0.0,0.0,1.0,0.14843373226061887],[30.790241296663062,33.85473731753756,0.0,7.0,0.0,1.0,1.0,0.1064457810557996],[33.85473731753756,36.15310933319345,1016.5,8.0,0.0,0.0,1.0,0.041987949730498395],[36.15310933319345,84.80198366457616,1678.6501,0.0,0.0,0.0,-1.0,-8.417884611588988e-09]]</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>[[-27.811266306337636,25.680932863751487,-1860.0,6.0,0.0,0.0,1.0],[25.680932863751487,30.047643000085287,-733.6842,7.0,0.0,0.0,1.0],[30.047643000085287,33.32267560233564,0.0,7.0,0.0,1.0,1.0],[33.32267560233564,35.8699231818637,1016.5,8.0,0.0,0.0,1.0],[35.8699231818637,80.99259459064635,1860.0,8.0,9.0,2.0,-1.0]]</t>
+          <t>[[-27.811266306337636,25.680932863751487,-1860.0,6.0,0.0,0.0,1.0,0.31933734732085983],[25.680932863751487,30.047643000085287,-733.6842,7.0,0.0,0.0,1.0,0.25487951539314896],[30.047643000085287,33.32267560233564,0.0,7.0,0.0,1.0,1.0,0.2128915641883297],[33.32267560233564,35.8699231818637,1016.5,8.0,0.0,0.0,1.0,0.14843373286302847],[35.8699231818637,80.99259459064635,1860.0,8.0,9.0,2.0,-1.0,0.09494609811350406]]</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>[[-28.602314767678976,25.252322255145984,-1860.0,5.0,0.0,0.0,1.0],[25.252322255145984,27.46552651635797,-733.6842,5.0,0.0,0.0,1.0],[27.46552651635797,30.785332908175945,0.0,5.0,0.0,1.0,1.0],[30.785332908175945,35.94947618433724,1016.5,6.0,0.0,0.0,1.0],[35.94947618433724,81.68903091605159,1860.0,6.0,9.0,0.0,-1.0]]</t>
+          <t>[[-28.602314767678976,25.252322255145984,-1860.0,5.0,0.0,0.0,1.0,0.4257831304533899],[25.252322255145984,27.46552651635797,-733.6842,5.0,0.0,0.0,1.0,0.3613252985256791],[27.46552651635797,30.785332908175945,0.0,5.0,0.0,1.0,1.0,0.3193373473208598],[30.785332908175945,35.94947618433724,1016.5,6.0,0.0,0.0,1.0,0.2548795159955586],[35.94947618433724,81.68903091605159,1860.0,6.0,9.0,0.0,-1.0,0.20139188124603413]]</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>[[-26.32250798943891,24.828735865638677,-1860.0,5.0,0.0,0.0,1.0],[24.828735865638677,27.631543748108676,-733.6842,4.0,0.0,0.0,1.0],[27.631543748108676,30.784702615887433,0.0,4.0,0.0,1.0,1.0],[30.784702615887433,36.390318380827445,1016.5,4.0,0.0,0.0,1.0],[36.390318380827445,78.4324366178775,1860.0,6.0,9.0,3.0,-1.0]]</t>
+          <t>[[-26.32250798943891,24.828735865638677,-1860.0,5.0,0.0,0.0,1.0,0.53222891358592],[24.828735865638677,27.631543748108676,-733.6842,4.0,0.0,0.0,1.0,0.4677710816582092],[27.631543748108676,30.784702615887433,0.0,4.0,0.0,1.0,1.0,0.4257831304533899],[30.784702615887433,36.390318380827445,1016.5,4.0,0.0,0.0,1.0,0.3613252991280887],[36.390318380827445,78.4324366178775,1860.0,6.0,9.0,3.0,-1.0,0.30783766437856425]]</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>[[-21.191703409019567,25.15042570853295,-1860.0,3.0,0.0,0.0,1.0],[25.15042570853295,29.58018805065194,-733.6842,3.0,0.0,0.0,1.0],[29.58018805065194,32.64694659519586,0.0,3.0,0.0,1.0,1.0],[32.64694659519586,36.735957987921076,1016.5,4.0,0.0,0.0,1.0],[36.735957987921076,80.69283045971721,1860.0,4.0,9.0,1.0,-1.0]]</t>
+          <t>[[-21.191703409019567,25.15042570853295,-1860.0,3.0,0.0,0.0,1.0,0.6386746967184502],[25.15042570853295,29.58018805065194,-733.6842,3.0,0.0,0.0,1.0,0.5742168647907393],[29.58018805065194,32.64694659519586,0.0,3.0,0.0,1.0,1.0,0.5322289135859201],[32.64694659519586,36.735957987921076,1016.5,4.0,0.0,0.0,1.0,0.46777108226061886],[36.735957987921076,80.69283045971721,1860.0,4.0,9.0,1.0,-1.0,0.4142834475110944]]</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>[[-14.290003549940293,24.908327940401612,-1860.0,2.0,0.0,0.0,1.0],[24.908327940401612,27.946958288490137,-733.6842,2.0,0.0,0.0,1.0],[27.946958288490137,30.985588636578655,0.0,2.0,0.0,1.0,1.0],[30.985588636578655,34.63194505428488,1016.5,4.0,0.0,0.0,1.0],[34.63194505428488,76.56504385790646,1860.0,3.0,9.0,4.0,-1.0]]</t>
+          <t>[[-14.290003549940293,24.908327940401612,-1860.0,2.0,0.0,0.0,1.0,0.7451204798509803],[24.908327940401612,27.946958288490137,-733.6842,2.0,0.0,0.0,1.0,0.6806626479232695],[27.946958288490137,30.985588636578655,0.0,2.0,0.0,1.0,1.0,0.6386746967184502],[30.985588636578655,34.63194505428488,1016.5,4.0,0.0,0.0,1.0,0.574216865393149],[34.63194505428488,76.56504385790646,1860.0,3.0,9.0,4.0,-1.0,0.5207292306436246]]</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>[[-13.253129198499321,25.340953231271016,-1860.0,2.0,0.0,0.0,1.0],[25.340953231271016,28.509124176998434,-733.6842,2.0,0.0,0.0,1.0],[28.509124176998434,31.389279582205177,0.0,1.0,0.0,1.0,1.0],[31.389279582205177,35.99752823053596,1016.5,2.0,0.0,0.0,1.0],[35.99752823053596,72.86351741718227,1860.0,3.0,9.0,2.0,-1.0]]</t>
+          <t>[[-13.253129198499321,25.340953231271016,-1860.0,2.0,0.0,0.0,1.0,0.8515662629835103],[25.340953231271016,28.509124176998434,-733.6842,2.0,0.0,0.0,1.0,0.7871084310557995],[28.509124176998434,31.389279582205177,0.0,1.0,0.0,1.0,1.0,0.7451204798509803],[31.389279582205177,35.99752823053596,1016.5,2.0,0.0,0.0,1.0,0.680662648525679],[35.99752823053596,72.86351741718227,1860.0,3.0,9.0,2.0,-1.0,0.6271750137761547]]</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>[[-13.087073539963981,25.429897407759782,-1860.0,1.0,0.0,0.0,1.0],[25.429897407759782,28.34784975228431,-733.6842,0.0,0.0,0.0,1.0],[28.34784975228431,31.55759733126129,0.0,1.0,0.0,1.0,1.0],[31.55759733126129,36.22632108250053,1016.5,2.0,0.0,0.0,1.0],[36.22632108250053,74.1597015613194,1860.0,1.0,9.0,2.0,-1.0]]</t>
+          <t>[[-13.087073539963981,25.429897407759782,-1860.0,1.0,0.0,0.0,1.0,0.9580120461160404],[25.429897407759782,28.34784975228431,-733.6842,0.0,0.0,0.0,1.0,0.8935542141883296],[28.34784975228431,31.55759733126129,0.0,1.0,0.0,1.0,1.0,0.8515662629835103],[31.55759733126129,36.22632108250053,1016.5,2.0,0.0,0.0,1.0,0.7871084316582091],[36.22632108250053,74.1597015613194,1860.0,1.0,9.0,2.0,-1.0,0.7336207969086848]]</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="F257" s="4" t="inlineStr">
         <is>
-          <t>[0,0,3.209747579,4.6687237512,0]</t>
+          <t>[2.9179523445,0,3.209747579,4.6687237512,0]</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>[[-14.757094423006306,26.004792820856927,-733.6844,0.0,0.0,0.0,1.0],[26.004792820856927,28.722251970447807,-733.6842,0.0,0.0,0.0,1.0],[28.722251970447807,31.74165102554879,0.0,0.0,0.0,1.0,1.0],[31.74165102554879,35.96880970269016,1016.5,1.0,0.0,0.0,1.0],[35.96880970269016,75.52293732451301,1860.0,1.0,9.0,2.0,-1.0]]</t>
+          <t>[[-14.757094423006306,26.004792820856927,-733.6844,0.0,0.0,0.0,1.0,1.0000000087666427],[26.004792820856927,28.722251970447807,-733.6842,0.0,0.0,0.0,1.0,0.9999999973208596],[28.722251970447807,31.74165102554879,0.0,0.0,0.0,1.0,1.0,0.9580120461160404],[31.74165102554879,35.96880970269016,1016.5,1.0,0.0,0.0,1.0,0.8935542147907392],[35.96880970269016,75.52293732451301,1860.0,1.0,9.0,2.0,-1.0,0.8400665800412148]]</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="F258" s="4" t="inlineStr">
         <is>
-          <t>[0,0,0,4.2271586771,0]</t>
+          <t>[0,0,3.0193990551,4.2271586771,0]</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7158,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>[[-12.675334027160716,36.92230027825415,0.0,0.0,0.0,1.0,1.0],[36.92230027825415,37.21065861723912,890.0,0.0,8.0,3.0,-1.0],[37.21065861723912,73.54380932934536,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[-12.675334027160716,36.92230027825415,0.0,0.0,0.0,1.0,1.0,1.000000008766643],[36.92230027825415,37.21065861723912,890.0,0.0,8.0,3.0,-1.0,0.9435637373652479],[37.21065861723912,73.54380932934536,1860.0,0.0,8.0,3.0,-1.0,0.8820545426918174]]</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>[[-12.154605100536116,35.39044776603929,0.0,0.0,0.0,1.0,1.0],[35.39044776603929,36.50915489231165,890.0,0.0,8.0,2.0,-1.0],[36.50915489231165,71.46875258832297,1860.0,0.0,9.0,1.0,-1.0]]</t>
+          <t>[[-12.154605100536116,35.39044776603929,0.0,0.0,0.0,1.0,1.0,1.000000008766643],[35.39044776603929,36.50915489231165,890.0,0.0,8.0,2.0,-1.0,0.9435637373652479],[36.50915489231165,71.46875258832297,1860.0,0.0,9.0,1.0,-1.0,0.8820545426918174]]</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>[[-13.728226864091235,31.676990468301753,-1860.0,1.0,8.0,2.0,-1.0],[31.676990468301753,32.262864240332625,-1074.7921,0.0,8.0,1.0,-1.0],[32.262864240332625,35.77810687251789,0.0,0.0,7.0,2.0,-1.0],[35.77810687251789,36.65691753056421,890.0001,0.0,7.0,0.0,-1.0],[36.65691753056421,73.8599020545249,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-13.728226864091235,31.676990468301753,-1860.0,1.0,8.0,2.0,-1.0,0.9885003258243472],[31.676990468301753,32.262864240332625,-1074.7921,0.0,8.0,1.0,-1.0,0.9435637291376002],[32.262864240332625,35.77810687251789,0.0,0.0,7.0,2.0,-1.0,0.8820545426918172],[35.77810687251789,36.65691753056421,890.0001,0.0,7.0,0.0,-1.0,0.825618264949268],[36.65691753056421,73.8599020545249,1860.0,0.0,7.0,0.0,-1.0,0.7641090766169916]]</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>[[-14.464450609947152,31.143150365294602,-1860.0,1.0,7.0,1.0,-1.0],[31.143150365294602,34.69698940232642,0.0,0.0,6.0,1.0,-1.0],[34.69698940232642,35.289295908498396,890.0001,0.0,6.0,0.0,-1.0],[35.289295908498396,74.08537206276247,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[-14.464450609947152,31.143150365294602,-1860.0,1.0,7.0,1.0,-1.0,0.8705548597495216],[31.143150365294602,34.69698940232642,0.0,0.0,6.0,1.0,-1.0,0.7641090766169916],[34.69698940232642,35.289295908498396,890.0001,0.0,6.0,0.0,-1.0,0.7076727988744425],[35.289295908498396,74.08537206276247,1860.0,0.0,6.0,0.0,-1.0,0.646163610542166]]</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>[[-12.145296669024917,30.509216985005388,-1860.0,1.0,6.0,0.0,-1.0],[30.509216985005388,31.903155339712256,-1074.7921,0.0,6.0,1.0,-1.0],[31.903155339712256,35.248607391008754,0.0,0.0,5.0,2.0,-1.0],[35.248607391008754,36.921333416657,890.0001,0.0,5.0,2.0,-1.0],[36.921333416657,71.21221694244606,1860.0,0.0,5.0,2.0,-1.0]]</t>
+          <t>[[-12.145296669024917,30.509216985005388,-1860.0,1.0,6.0,0.0,-1.0,0.752609393674696],[30.509216985005388,31.903155339712256,-1074.7921,0.0,6.0,1.0,-1.0,0.707672796987949],[31.903155339712256,35.248607391008754,0.0,0.0,5.0,2.0,-1.0,0.646163610542166],[35.248607391008754,36.921333416657,890.0001,0.0,5.0,2.0,-1.0,0.5897273327996169],[36.921333416657,71.21221694244606,1860.0,0.0,5.0,2.0,-1.0,0.5282181444673404]]</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>[[-14.750297275954274,31.066777093356563,-1860.0,1.0,5.0,0.0,-1.0],[31.066777093356563,31.66180403321774,-1074.7921,0.0,5.0,1.0,-1.0],[31.66180403321774,34.93445220245423,0.0,0.0,4.0,2.0,-1.0],[34.93445220245423,35.231965672384824,890.0001,0.0,4.0,0.0,-1.0],[35.231965672384824,74.2062302332921,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-14.750297275954274,31.066777093356563,-1860.0,1.0,5.0,0.0,-1.0,0.6346639275998704],[31.066777093356563,31.66180403321774,-1074.7921,0.0,5.0,1.0,-1.0,0.5897273309131235],[31.66180403321774,34.93445220245423,0.0,0.0,4.0,2.0,-1.0,0.5282181444673404],[34.93445220245423,35.231965672384824,890.0001,0.0,4.0,0.0,-1.0,0.4717818667247912],[35.231965672384824,74.2062302332921,1860.0,0.0,4.0,0.0,-1.0,0.41027267839251474]]</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>[[-8.51136331105541,31.9227097207391,-1860.0,1.0,4.0,0.0,-1.0],[31.9227097207391,32.16776470881058,-1074.7921,0.0,4.0,1.0,-1.0],[32.16776470881058,35.598534541811325,0.0,0.0,3.0,2.0,-1.0],[35.598534541811325,35.843589529882806,890.0001,0.0,3.0,1.0,-1.0],[35.843589529882806,64.76007812231768,1860.0,0.0,3.0,1.0,-1.0]]</t>
+          <t>[[-8.51136331105541,31.9227097207391,-1860.0,1.0,4.0,0.0,-1.0,0.5167184615250449],[31.9227097207391,32.16776470881058,-1074.7921,0.0,4.0,1.0,-1.0,0.4717818648382978],[32.16776470881058,35.598534541811325,0.0,0.0,3.0,2.0,-1.0,0.4102726783925147],[35.598534541811325,35.843589529882806,890.0001,0.0,3.0,1.0,-1.0,0.3538364006499655],[35.843589529882806,64.76007812231768,1860.0,0.0,3.0,1.0,-1.0,0.29232721231768904]]</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>[[-6.280352618710523,31.05378503511693,-1860.0,1.0,3.0,2.0,-1.0],[31.05378503511693,31.503593922512444,-1074.7921,0.0,3.0,1.0,-1.0],[31.503593922512444,34.87716057797878,0.0,0.0,2.0,2.0,-1.0],[34.87716057797878,35.32696946537429,890.0001,0.0,2.0,2.0,-1.0],[35.32696946537429,60.96607604691845,1860.0,0.0,2.0,2.0,-1.0]]</t>
+          <t>[[-6.280352618710523,31.05378503511693,-1860.0,1.0,3.0,2.0,-1.0,0.3987729954502192],[31.05378503511693,31.503593922512444,-1074.7921,0.0,3.0,1.0,-1.0,0.3538363987634722],[31.503593922512444,34.87716057797878,0.0,0.0,2.0,2.0,-1.0,0.2923272123176891],[34.87716057797878,35.32696946537429,890.0001,0.0,2.0,2.0,-1.0,0.23589093457513996],[35.32696946537429,60.96607604691845,1860.0,0.0,2.0,2.0,-1.0,0.17438174624286346]]</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>[[-6.575311714521524,32.04773232971075,-1860.0,1.0,2.0,2.0,-1.0],[32.04773232971075,32.71749609926391,-1074.7921,0.0,2.0,3.0,-1.0],[32.71749609926391,36.28956953688077,0.0,0.0,1.0,4.0,-1.0],[36.28956953688077,36.736078716582874,890.0001,0.0,1.0,2.0,-1.0],[36.736078716582874,60.17781065094351,1860.0,0.0,1.0,2.0,-1.0]]</t>
+          <t>[[-6.575311714521524,32.04773232971075,-1860.0,1.0,2.0,2.0,-1.0,0.2808275293753936],[32.04773232971075,32.71749609926391,-1074.7921,0.0,2.0,3.0,-1.0,0.23589093268864664],[32.71749609926391,36.28956953688077,0.0,0.0,1.0,4.0,-1.0,0.1743817462428635],[36.28956953688077,36.736078716582874,890.0001,0.0,1.0,2.0,-1.0,0.11794546850031437],[36.736078716582874,60.17781065094351,1860.0,0.0,1.0,2.0,-1.0,0.05643628016803788]]</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>[[-4.533634118996877,31.90714920131324,-1860.0,1.0,1.0,2.0,-1.0],[31.90714920131324,32.72604320851122,-1074.7921,0.0,1.0,1.0,-1.0],[32.72604320851122,36.20634273910264,0.0,0.0,0.0,2.0,-1.0],[36.20634273910264,38.66302476069658,890.0001,0.0,0.0,0.0,-1.0],[38.66302476069658,56.678692919052146,890.0002,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-4.533634118996877,31.90714920131324,-1860.0,1.0,1.0,2.0,-1.0,0.16288206330056795],[31.90714920131324,32.72604320851122,-1074.7921,0.0,1.0,1.0,-1.0,0.11794546661382095],[32.72604320851122,36.20634273910264,0.0,0.0,0.0,2.0,-1.0,0.05643628016803783],[36.20634273910264,38.66302476069658,890.0001,0.0,0.0,0.0,-1.0,2.425488684898447e-09],[38.66302476069658,56.678692919052146,890.0002,0.0,0.0,0.0,-1.0,-3.915665403031454e-09]]</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>[[-4.983689146231967,31.169142903577743,-1860.0,1.0,1.0,1.0,-1.0],[31.169142903577743,32.83134207828164,-1074.7921,0.0,1.0,0.0,-1.0],[32.83134207828164,36.36351532452741,0.0,0.0,0.0,1.0,-1.0],[36.36351532452741,40.31123836444916,890.0001,0.0,0.0,0.0,-1.0],[40.31123836444916,57.1410050083261,890.0002,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-4.983689146231967,31.169142903577743,-1860.0,1.0,1.0,1.0,-1.0,0.16288206330056795],[31.169142903577743,32.83134207828164,-1074.7921,0.0,1.0,0.0,-1.0,0.11794546661382095],[32.83134207828164,36.36351532452741,0.0,0.0,0.0,1.0,-1.0,0.05643628016803783],[36.36351532452741,40.31123836444916,890.0001,0.0,0.0,0.0,-1.0,2.425488684898447e-09],[40.31123836444916,57.1410050083261,890.0002,0.0,0.0,0.0,-1.0,-3.915665403031454e-09]]</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
-          <t>[0,1.6621991747,0,0,0]</t>
+          <t>[0,1.6621991747,3.5321732462,0,0]</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>[[-4.498076434263938,29.37401709693748,-1860.0,1.0,1.0,0.0,-1.0],[29.37401709693748,31.366493187008153,-1074.7921,0.0,1.0,1.0,-1.0],[31.366493187008153,34.753702540128295,0.0,0.0,0.0,2.0,-1.0],[34.753702540128295,36.14843580317776,890.0001,0.0,0.0,0.0,-1.0],[36.14843580317776,55.07695865884914,890.0002,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-4.498076434263938,29.37401709693748,-1860.0,1.0,1.0,0.0,-1.0,0.16288206330056795],[29.37401709693748,31.366493187008153,-1074.7921,0.0,1.0,1.0,-1.0,0.11794546661382095],[31.366493187008153,34.753702540128295,0.0,0.0,0.0,2.0,-1.0,0.05643628016803783],[34.753702540128295,36.14843580317776,890.0001,0.0,0.0,0.0,-1.0,2.425488684898447e-09],[36.14843580317776,55.07695865884914,890.0002,0.0,0.0,0.0,-1.0,-3.915665403031454e-09]]</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>[[-3.561510331216743,31.877279946615502,-1860.0,1.0,0.0,0.0,-1.0],[31.877279946615502,54.98102167470503,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-3.561510331216743,31.877279946615502,-1860.0,1.0,0.0,0.0,-1.0,0.10644577921686471],[31.877279946615502,54.98102167470503,0.0,0.0,0.0,1.0,-1.0,-3.915665409970348e-09]]</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>[[-3.2686085632233386,19.709831467096212,-1860.0,9.0,0.0,0.0,1.0],[19.709831467096212,21.254600544764752,-733.6842,9.0,0.0,0.0,1.0],[21.254600544764752,54.46713571463839,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-3.2686085632233386,19.709831467096212,-1860.0,9.0,0.0,0.0,1.0,0.10644577921686471],[19.709831467096212,21.254600544764752,-733.6842,9.0,0.0,0.0,1.0,0.041987947289153865],[21.254600544764752,54.46713571463839,0.0,0.0,0.0,1.0,-1.0,-3.915665409970348e-09]]</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>[[0.6204871315843832,21.98823177431731,-1860.0,9.0,8.0,3.0,-1.0],[21.98823177431731,22.1408585217654,-1607.5346,8.0,8.0,4.0,-1.0],[22.1408585217654,46.25588461856399,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[0.6204871315843832,21.98823177431731,-1860.0,9.0,8.0,3.0,-1.0,0.10644577921686471],[21.98823177431731,22.1408585217654,-1607.5346,8.0,8.0,4.0,-1.0,0.09199745813252735],[22.1408585217654,46.25588461856399,0.0,0.0,0.0,1.0,-1.0,-3.915665409970348e-09]]</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>[[-7.060638616535877,-0.14264439893268221,-1860.0,8.0,8.0,3.0,-1.0],[-0.14264439893268221,21.764337290144105,-1860.0,7.0,8.0,3.0,-1.0],[21.764337290144105,21.956503796188635,-1607.5347,7.0,8.0,1.0,-1.0],[21.956503796188635,24.454668374767564,0.0,7.0,7.0,2.0,-1.0],[24.454668374767564,50.39714669077955,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-7.060638616535877,-0.14264439893268221,-1860.0,8.0,8.0,3.0,-1.0,0.21289156234939483],[-0.14264439893268221,21.764337290144105,-1860.0,7.0,8.0,3.0,-1.0,0.21289156234939483],[21.764337290144105,21.956503796188635,-1607.5347,7.0,8.0,1.0,-1.0,0.19844324698794902],[21.956503796188635,24.454668374767564,0.0,7.0,7.0,2.0,-1.0,0.1064457792168647],[24.454668374767564,50.39714669077955,1678.65,0.0,0.0,0.0,-1.0,-3.91566543078703e-09]]</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>[[-11.084939538388552,22.070764525361263,-1860.0,7.0,8.0,3.0,-1.0],[22.070764525361263,22.29180255245293,-1607.5347,6.0,8.0,4.0,-1.0],[22.29180255245293,24.723220850461253,0.0,6.0,7.0,5.0,-1.0],[24.723220850461253,25.165296904644578,409.1999,6.0,7.0,4.0,-1.0],[25.165296904644578,55.00543056201941,1860.0,6.0,7.0,4.0,-1.0]]</t>
+          <t>[[-11.084939538388552,22.070764525361263,-1860.0,7.0,8.0,3.0,-1.0,0.31933734548192494],[22.070764525361263,22.29180255245293,-1607.5347,6.0,8.0,4.0,-1.0,0.30488903012047913],[22.29180255245293,24.723220850461253,0.0,6.0,7.0,5.0,-1.0,0.2128915623493948],[24.723220850461253,25.165296904644578,409.1999,6.0,7.0,4.0,-1.0,0.18694356615408725],[25.165296904644578,55.00543056201941,1860.0,6.0,7.0,4.0,-1.0,0.09494609627456917]]</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>[[-13.845500018062133,21.75706834918065,-1860.0,5.0,8.0,3.0,-1.0],[21.75706834918065,21.992846947639208,-1607.5347,4.0,8.0,4.0,-1.0],[21.992846947639208,24.350632932224826,0.0,4.0,7.0,5.0,-1.0],[24.350632932224826,24.82219012914195,409.1999,5.0,7.0,4.0,-1.0],[24.82219012914195,56.65230092104775,1860.0,5.0,8.0,3.0,-1.0]]</t>
+          <t>[[-13.845500018062133,21.75706834918065,-1860.0,5.0,8.0,3.0,-1.0,0.425783128614455],[21.75706834918065,21.992846947639208,-1607.5347,4.0,8.0,4.0,-1.0,0.41133481325300925],[21.992846947639208,24.350632932224826,0.0,4.0,7.0,5.0,-1.0,0.3193373454819249],[24.350632932224826,24.82219012914195,409.1999,5.0,7.0,4.0,-1.0,0.2933893492866173],[24.82219012914195,56.65230092104775,1860.0,5.0,8.0,3.0,-1.0,0.20139187940709924]]</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>[[-12.196808126607703,22.090446780605024,-1860.0,4.0,8.0,4.0,-1.0],[22.090446780605024,22.532862972956156,-1607.5347,3.0,8.0,4.0,-1.0],[22.532862972956156,24.966152030887383,0.0,3.0,8.0,4.0,-1.0],[24.966152030887383,25.408568223238515,227.8499,4.0,8.0,3.0,-1.0],[25.408568223238515,53.944412629886536,1860.0,3.0,8.0,3.0,-1.0]]</t>
+          <t>[[-12.196808126607703,22.090446780605024,-1860.0,4.0,8.0,4.0,-1.0,0.5322289117469852],[22.090446780605024,22.532862972956156,-1607.5347,3.0,8.0,4.0,-1.0,0.5177805963855394],[22.532862972956156,24.966152030887383,0.0,3.0,8.0,4.0,-1.0,0.4257831286144551],[24.966152030887383,25.408568223238515,227.8499,4.0,8.0,3.0,-1.0,0.41133481536144306],[25.408568223238515,53.944412629886536,1860.0,3.0,8.0,3.0,-1.0,0.30783766253962946]]</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>[[-15.181994501071365,21.89741718583057,-1860.0,4.0,8.0,3.0,-1.0],[21.89741718583057,22.126302443157122,-1607.5347,2.0,8.0,4.0,-1.0],[22.126302443157122,24.644040273749233,0.0,2.0,7.0,5.0,-1.0],[24.644040273749233,24.872925531075786,409.1999,2.0,7.0,5.0,-1.0],[24.872925531075786,53.25469743956862,1860.0,2.0,8.0,4.0,-1.0]]</t>
+          <t>[[-15.181994501071365,21.89741718583057,-1860.0,4.0,8.0,3.0,-1.0,0.6386746948795152],[21.89741718583057,22.126302443157122,-1607.5347,2.0,8.0,4.0,-1.0,0.6242263795180695],[22.126302443157122,24.644040273749233,0.0,2.0,7.0,5.0,-1.0,0.5322289117469852],[24.644040273749233,24.872925531075786,409.1999,2.0,7.0,5.0,-1.0,0.5062809155516776],[24.872925531075786,53.25469743956862,1860.0,2.0,8.0,4.0,-1.0,0.4142834456721595]]</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>[[-33.27172063947173,21.416135637271275,-1860.0,2.0,8.0,3.0,-1.0],[21.416135637271275,22.071080023819093,-1607.5347,2.0,8.0,4.0,-1.0],[22.071080023819093,24.363385376736467,0.0,2.0,7.0,5.0,-1.0],[24.363385376736467,25.673274149832103,409.1999,2.0,7.0,5.0,-1.0],[25.673274149832103,64.64246514942741,1860.0,2.0,7.0,5.0,-1.0]]</t>
+          <t>[[-33.27172063947173,21.416135637271275,-1860.0,2.0,8.0,3.0,-1.0,0.7451204780120453],[21.416135637271275,22.071080023819093,-1607.5347,2.0,8.0,4.0,-1.0,0.7306721626505995],[22.071080023819093,24.363385376736467,0.0,2.0,7.0,5.0,-1.0,0.6386746948795152],[24.363385376736467,25.673274149832103,409.1999,2.0,7.0,5.0,-1.0,0.6127266986842077],[25.673274149832103,64.64246514942741,1860.0,2.0,7.0,5.0,-1.0,0.5207292288046896]]</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>[[-36.83940544906829,22.008930273588398,-1860.0,2.0,8.0,3.0,-1.0],[22.008930273588398,22.35307258775598,-1607.5347,1.0,8.0,4.0,-1.0],[22.35307258775598,24.762068786929063,0.0,1.0,7.0,5.0,-1.0],[24.762068786929063,66.05914648703902,1860.0,1.0,7.0,5.0,-1.0]]</t>
+          <t>[[-36.83940544906829,22.008930273588398,-1860.0,2.0,8.0,3.0,-1.0,0.8515662611445753],[22.008930273588398,22.35307258775598,-1607.5347,1.0,8.0,4.0,-1.0,0.8371179457831296],[22.35307258775598,24.762068786929063,0.0,1.0,7.0,5.0,-1.0,0.7451204780120453],[24.762068786929063,66.05914648703902,1860.0,1.0,7.0,5.0,-1.0,0.6271750119372197]]</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>[[-47.29765077057202,21.56050411223343,-1860.0,1.0,8.0,3.0,-1.0],[21.56050411223343,23.921355136786772,0.0,0.0,7.0,5.0,-1.0],[23.921355136786772,24.70830547830454,409.1999,0.0,7.0,5.0,-1.0],[24.70830547830454,70.35142528633558,1860.0,0.0,7.0,5.0,-1.0]]</t>
+          <t>[[-47.29765077057202,21.56050411223343,-1860.0,1.0,8.0,3.0,-1.0,0.9580120442771054],[21.56050411223343,23.921355136786772,0.0,0.0,7.0,5.0,-1.0,0.8515662611445753],[23.921355136786772,24.70830547830454,409.1999,0.0,7.0,5.0,-1.0,0.8256182649492678],[24.70830547830454,70.35142528633558,1860.0,0.0,7.0,5.0,-1.0,0.7336207950697498]]</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>[[-48.63483302735374,22.1295555527175,-733.6844,0.0,0.0,0.0,1.0],[22.1295555527175,24.555763161177076,0.0,0.0,8.0,2.0,-1.0],[24.555763161177076,72.27117946088225,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-48.63483302735374,22.1295555527175,-733.6844,0.0,0.0,0.0,1.0,1.0000000069277077],[22.1295555527175,24.555763161177076,0.0,0.0,8.0,2.0,-1.0,0.9580120442771054],[24.555763161177076,72.27117946088225,1860.0,0.0,8.0,2.0,-1.0,0.8400665782022798]]</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>[[-50.52767615081027,21.154564768492087,-733.6844,0.0,0.0,0.0,1.0],[21.154564768492087,23.202628794757878,0.0,0.0,8.0,2.0,-1.0],[23.202628794757878,23.612241600011025,227.8499,0.0,8.0,1.0,-1.0],[23.612241600011025,71.94655261988346,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[-50.52767615081027,21.154564768492087,-733.6844,0.0,0.0,0.0,1.0,1.0000000069277077],[21.154564768492087,23.202628794757878,0.0,0.0,8.0,2.0,-1.0,0.9580120442771054],[23.202628794757878,23.612241600011025,227.8499,0.0,8.0,1.0,-1.0,0.9435637310240933],[23.612241600011025,71.94655261988346,1860.0,0.0,8.0,1.0,-1.0,0.8400665782022798]]</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>[[-51.09454229019595,21.282330403147775,-1860.0,1.0,8.0,0.0,-1.0],[21.282330403147775,23.807105031985337,0.0,0.0,7.0,2.0,-1.0],[23.807105031985337,24.6486965749312,227.8499,0.0,7.0,2.0,-1.0],[24.6486965749312,74.72339338020971,1860.0,0.0,7.0,2.0,-1.0]]</t>
+          <t>[[-51.09454229019595,21.282330403147775,-1860.0,1.0,8.0,0.0,-1.0,0.9465123613348099],[21.282330403147775,23.807105031985337,0.0,0.0,7.0,2.0,-1.0,0.8400665782022798],[23.807105031985337,24.6486965749312,227.8499,0.0,7.0,2.0,-1.0,0.8256182649492677],[24.6486965749312,74.72339338020971,1860.0,0.0,7.0,2.0,-1.0,0.7221211121274542]]</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>[[-45.76033967431601,20.968341742807347,-1860.0,1.0,7.0,0.0,-1.0],[20.968341742807347,21.713913602216543,-1808.4765,0.0,7.0,1.0,-1.0],[21.713913602216543,23.950629180444146,0.0,0.0,6.0,2.0,-1.0],[23.950629180444146,24.696201039853342,227.8499,0.0,6.0,1.0,-1.0],[24.696201039853342,65.7026533073593,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[-45.76033967431601,20.968341742807347,-1860.0,1.0,7.0,0.0,-1.0,0.8285668952599843],[20.968341742807347,21.713913602216543,-1808.4765,0.0,7.0,1.0,-1.0,0.8256182612238397],[21.713913602216543,23.950629180444146,0.0,0.0,6.0,2.0,-1.0,0.7221211121274542],[23.950629180444146,24.696201039853342,227.8499,0.0,6.0,1.0,-1.0,0.7076727988744421],[24.696201039853342,65.7026533073593,1860.0,0.0,6.0,1.0,-1.0,0.6041756460526286]]</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>[[-44.644838245912496,21.00400609644535,-1860.0,1.0,6.0,0.0,-1.0],[21.00400609644535,22.09210848886012,-1808.4765,0.0,6.0,1.0,-1.0],[22.09210848886012,24.268313273689657,0.0,0.0,5.0,2.0,-1.0],[24.268313273689657,24.993714868632836,227.8499,0.0,5.0,2.0,-1.0],[24.993714868632836,63.80270019809301,1860.0,0.0,5.0,2.0,-1.0]]</t>
+          <t>[[-44.644838245912496,21.00400609644535,-1860.0,1.0,6.0,0.0,-1.0,0.7106214291851587],[21.00400609644535,22.09210848886012,-1808.4765,0.0,6.0,1.0,-1.0,0.7076727951490142],[22.09210848886012,24.268313273689657,0.0,0.0,5.0,2.0,-1.0,0.6041756460526286],[24.268313273689657,24.993714868632836,227.8499,0.0,5.0,2.0,-1.0,0.5897273327996165],[24.993714868632836,63.80270019809301,1860.0,0.0,5.0,2.0,-1.0,0.486230179977803]]</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>[[-46.56516698128547,21.448955986646666,-1860.0,1.0,5.0,0.0,-1.0],[21.448955986646666,21.82892315406528,-1808.4765,0.0,5.0,1.0,-1.0],[21.82892315406528,24.10872615857697,0.0,0.0,4.0,2.0,-1.0],[24.10872615857697,24.488693325995584,227.8499,0.0,4.0,2.0,-1.0],[24.488693325995584,67.0450160768805,1860.0,0.0,4.0,2.0,-1.0]]</t>
+          <t>[[-46.56516698128547,21.448955986646666,-1860.0,1.0,5.0,0.0,-1.0,0.5926759631103331],[21.448955986646666,21.82892315406528,-1808.4765,0.0,5.0,1.0,-1.0,0.5897273290741886],[21.82892315406528,24.10872615857697,0.0,0.0,4.0,2.0,-1.0,0.486230179977803],[24.10872615857697,24.488693325995584,227.8499,0.0,4.0,2.0,-1.0,0.47178186672479094],[24.488693325995584,67.0450160768805,1860.0,0.0,4.0,2.0,-1.0,0.36828471390297735]]</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>[[-46.93764712088392,20.632485116318293,-1860.0,1.0,4.0,0.0,-1.0],[20.632485116318293,21.39598943538273,-1808.4765,0.0,4.0,1.0,-1.0],[21.39598943538273,23.686502392576017,0.0,0.0,3.0,2.0,-1.0],[23.686502392576017,24.068254552108243,227.8499,0.0,3.0,2.0,-1.0],[24.068254552108243,67.20624857924864,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[-46.93764712088392,20.632485116318293,-1860.0,1.0,4.0,0.0,-1.0,0.4747304970355074],[20.632485116318293,21.39598943538273,-1808.4765,0.0,4.0,1.0,-1.0,0.4717818629993628],[21.39598943538273,23.686502392576017,0.0,0.0,3.0,2.0,-1.0,0.3682847139029773],[23.686502392576017,24.068254552108243,227.8499,0.0,3.0,2.0,-1.0,0.35383640064996524],[24.068254552108243,67.20624857924864,1860.0,0.0,3.0,2.0,-1.0,0.25033924782815165]]</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>[[-49.10865194366217,21.286439174522556,-1860.0,1.0,3.0,0.0,-1.0],[21.286439174522556,21.69100866370752,-1808.4765,0.0,3.0,1.0,-1.0],[21.69100866370752,24.11842559881734,0.0,0.0,2.0,2.0,-1.0],[24.11842559881734,71.85762532264376,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[-49.10865194366217,21.286439174522556,-1860.0,1.0,3.0,0.0,-1.0,0.3567850309606818],[21.286439174522556,21.69100866370752,-1808.4765,0.0,3.0,1.0,-1.0,0.3538363969245372],[21.69100866370752,24.11842559881734,0.0,0.0,2.0,2.0,-1.0,0.2503392478281517],[24.11842559881734,71.85762532264376,1860.0,0.0,2.0,1.0,-1.0,0.13239378175332606]]</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>[[-50.157987535551484,21.6440438451545,-1860.0,1.0,2.0,0.0,-1.0],[21.6440438451545,24.148765870062846,0.0,0.0,1.0,2.0,-1.0],[24.148765870062846,24.56621954088091,227.8499,0.0,1.0,1.0,-1.0],[24.56621954088091,74.66066003904788,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[-50.157987535551484,21.6440438451545,-1860.0,1.0,2.0,0.0,-1.0,0.23883956488585623],[21.6440438451545,24.148765870062846,0.0,0.0,1.0,2.0,-1.0,0.1323937817533261],[24.148765870062846,24.56621954088091,227.8499,0.0,1.0,1.0,-1.0,0.11794546850031407],[24.56621954088091,74.66066003904788,1860.0,0.0,1.0,1.0,-1.0,0.014448315678500481]]</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>[[-53.01438170706225,21.125169845470275,-1860.0,1.0,1.0,0.0,-1.0],[21.125169845470275,24.698160281736897,0.0,0.0,1.0,2.0,-1.0],[24.698160281736897,80.52613584840297,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-53.01438170706225,21.125169845470275,-1860.0,1.0,1.0,0.0,-1.0,0.22439125163284412],[21.125169845470275,24.698160281736897,0.0,0.0,1.0,2.0,-1.0,0.117945468500314],[24.698160281736897,80.52613584840297,1860.0,0.0,1.0,0.0,-1.0,2.4254883657093274e-09]]</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>[[-52.61646903480439,20.48907235451302,-1860.0,1.0,1.0,0.0,-1.0],[20.48907235451302,24.84059267530572,0.0,0.0,1.0,1.0,-1.0],[24.84059267530572,77.49398855689742,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-52.61646903480439,20.48907235451302,-1860.0,1.0,1.0,0.0,-1.0,0.22439125163284412],[20.48907235451302,24.84059267530572,0.0,0.0,1.0,1.0,-1.0,0.117945468500314],[24.84059267530572,77.49398855689742,1860.0,0.0,1.0,0.0,-1.0,2.4254883657093274e-09]]</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>[[-53.140540949779,18.405725746480478,-1860.0,1.0,2.0,0.0,-1.0],[18.405725746480478,20.172300232807864,-200.9418,1.0,2.0,0.0,-1.0],[20.172300232807864,22.38051834071711,0.0,1.0,1.0,1.0,-1.0],[22.38051834071711,78.91090190319375,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-53.140540949779,18.405725746480478,-1860.0,1.0,2.0,0.0,-1.0,0.22439125163284412],[18.405725746480478,20.172300232807864,-200.9418,1.0,2.0,0.0,-1.0,0.1294451498256152],[20.172300232807864,22.38051834071711,0.0,1.0,1.0,1.0,-1.0,0.117945468500314],[22.38051834071711,78.91090190319375,1860.0,0.0,1.0,0.0,-1.0,2.4254883657093274e-09]]</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>[[-50.09061381993524,19.308178544347413,-1860.0,1.0,1.0,0.0,-1.0],[19.308178544347413,73.42271306649639,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-50.09061381993524,19.308178544347413,-1860.0,1.0,1.0,0.0,-1.0,0.1064457855580185],[19.308178544347413,73.42271306649639,0.0,0.0,0.0,1.0,-1.0,2.425488379587115e-09]]</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>[[-52.39748396732999,18.967402377196777,-1860.0,1.0,0.0,0.0,-1.0],[18.967402377196777,77.71288808763039,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-52.39748396732999,18.967402377196777,-1860.0,1.0,0.0,0.0,-1.0,0.1064457855580185],[18.967402377196777,77.71288808763039,0.0,0.0,0.0,1.0,-1.0,2.425488379587115e-09]]</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>[[-52.08057688456644,10.651632861255138,-1860.0,9.0,0.0,2.0,1.0],[10.651632861255138,78.17588640710474,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-52.08057688456644,10.651632861255138,-1860.0,9.0,0.0,2.0,1.0,0.1064457855580185],[10.651632861255138,78.17588640710474,0.0,0.0,0.0,1.0,-1.0,2.425488379587115e-09]]</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>[[-57.02582402510837,10.068398218264456,-1860.0,9.0,0.0,1.0,1.0],[10.068398218264456,10.551090464619655,-733.6842,9.0,0.0,1.0,1.0],[10.551090464619655,87.29915763509649,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-57.02582402510837,10.068398218264456,-1860.0,9.0,0.0,1.0,1.0,0.1064457855580185],[10.068398218264456,10.551090464619655,-733.6842,9.0,0.0,1.0,1.0,0.041987953630307655],[10.551090464619655,87.29915763509649,0.0,0.0,0.0,1.0,-1.0,2.425488379587115e-09]]</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -8172,7 +8172,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>[[-57.624756540724945,10.26844177317544,-1860.0,9.0,0.0,0.0,1.0],[10.26844177317544,18.08348618340858,-733.6842,9.0,0.0,0.0,1.0],[18.08348618340858,88.41888587550683,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-57.624756540724945,10.26844177317544,-1860.0,9.0,0.0,0.0,1.0,0.1064457855580185],[10.26844177317544,18.08348618340858,-733.6842,9.0,0.0,0.0,1.0,0.041987953630307655],[18.08348618340858,88.41888587550683,0.0,0.0,0.0,1.0,-1.0,2.425488379587115e-09]]</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>[[-56.12616672003434,16.97843038570941,-1860.0,9.0,0.0,0.0,1.0],[16.97843038570941,25.997828729924542,0.0,8.0,0.0,1.0,1.0],[25.997828729924542,85.81068090735126,662.1501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-56.12616672003434,16.97843038570941,-1860.0,9.0,0.0,0.0,1.0,0.14843373676283778],[16.97843038570941,25.997828729924542,0.0,8.0,0.0,1.0,1.0,0.04198795363030765],[25.997828729924542,85.81068090735126,662.1501,0.0,0.0,0.0,-1.0,-4.5180753513451855e-09]]</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>[[-56.89521856232649,17.524607776019806,-1860.0,7.0,0.0,0.0,1.0],[17.524607776019806,27.672765913067025,0.0,7.0,0.0,1.0,1.0],[27.672765913067025,28.156011538640698,890.0,7.0,8.0,4.0,-1.0],[28.156011538640698,87.59522348420302,1860.0,8.0,9.0,3.0,-1.0]]</t>
+          <t>[[-56.89521856232649,17.524607776019806,-1860.0,7.0,0.0,0.0,1.0,0.25487951989536795],[17.524607776019806,27.672765913067025,0.0,7.0,0.0,1.0,1.0,0.1484337367628378],[27.672765913067025,28.156011538640698,890.0,7.0,8.0,4.0,-1.0,0.09199746536144275],[28.156011538640698,87.59522348420302,1860.0,8.0,9.0,3.0,-1.0,0.030488270688012173]]</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>[[-58.103311420339,16.826861381451536,-1860.0,7.0,0.0,0.0,1.0],[16.826861381451536,27.67201797118439,0.0,6.0,0.0,1.0,1.0],[27.67201797118439,28.164979634354054,708.65,8.0,9.0,2.0,-1.0],[28.164979634354054,89.29222586739371,1860.0,8.0,10.0,1.0,-1.0]]</t>
+          <t>[[-58.103311420339,16.826861381451536,-1860.0,7.0,0.0,0.0,1.0,0.361325303027898],[16.826861381451536,27.67201797118439,0.0,6.0,0.0,1.0,1.0,0.2548795198953679],[27.67201797118439,28.164979634354054,708.65,8.0,9.0,2.0,-1.0,0.20994293143626833],[28.164979634354054,89.29222586739371,1860.0,8.0,10.0,1.0,-1.0,0.13693405382054225]]</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>[[-58.93018777869219,17.428542169693408,-1860.0,5.0,0.0,0.0,1.0],[17.428542169693408,27.642130251961554,0.0,6.0,0.0,1.0,1.0],[27.642130251961554,86.49185205931607,1860.0,6.0,8.0,4.0,-1.0]]</t>
+          <t>[[-58.93018777869219,17.428542169693408,-1860.0,5.0,0.0,0.0,1.0,0.4677710861604281],[17.428542169693408,27.642130251961554,0.0,6.0,0.0,1.0,1.0,0.361325303027898],[27.642130251961554,86.49185205931607,1860.0,6.0,8.0,4.0,-1.0,0.24337983695307236]]</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>[[-58.210474856597585,17.416613447059248,-1860.0,4.0,0.0,0.0,1.0],[17.416613447059248,27.17494742172464,0.0,4.0,0.0,1.0,1.0],[27.17494742172464,27.66286412045791,890.0,5.0,8.0,4.0,-1.0],[27.66286412045791,87.67661806465013,1860.0,5.0,9.0,3.0,-1.0]]</t>
+          <t>[[-58.210474856597585,17.416613447059248,-1860.0,4.0,0.0,0.0,1.0,0.5742168692929582],[17.416613447059248,27.17494742172464,0.0,4.0,0.0,1.0,1.0,0.4677710861604281],[27.17494742172464,27.66286412045791,890.0,5.0,8.0,4.0,-1.0,0.41133481475903305],[27.66286412045791,87.67661806465013,1860.0,5.0,9.0,3.0,-1.0,0.3498256200856025]]</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>[[-77.41639237982767,17.593594692385594,-1860.0,4.0,0.0,0.0,1.0],[17.593594692385594,28.15025992263152,0.0,4.0,0.0,1.0,1.0],[28.15025992263152,28.73674132431185,708.65,5.0,9.0,2.0,-1.0],[28.73674132431185,97.94154672259063,1860.0,5.0,9.0,2.0,-1.0]]</t>
+          <t>[[-77.41639237982767,17.593594692385594,-1860.0,4.0,0.0,0.0,1.0,0.6806626524254884],[17.593594692385594,28.15025992263152,0.0,4.0,0.0,1.0,1.0,0.5742168692929582],[28.15025992263152,28.73674132431185,708.65,5.0,9.0,2.0,-1.0,0.5292802808338587],[28.73674132431185,97.94154672259063,1860.0,5.0,9.0,2.0,-1.0,0.4562714032181326]]</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -8354,7 +8354,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>[[-78.89336161905823,16.863758431753467,-1860.0,3.0,0.0,0.0,1.0],[16.863758431753467,27.10194107869559,0.0,3.0,0.0,1.0,1.0],[27.10194107869559,27.704187116751015,890.0,3.0,8.0,4.0,-1.0],[27.704187116751015,101.1782037595122,1860.0,3.0,9.0,3.0,-1.0]]</t>
+          <t>[[-78.89336161905823,16.863758431753467,-1860.0,3.0,0.0,0.0,1.0,0.7871084355580185],[16.863758431753467,27.10194107869559,0.0,3.0,0.0,1.0,1.0,0.6806626524254884],[27.10194107869559,27.704187116751015,890.0,3.0,8.0,4.0,-1.0,0.6242263810240933],[27.704187116751015,101.1782037595122,1860.0,3.0,9.0,3.0,-1.0,0.5627171863506628]]</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>[[-78.55181954008546,17.05792651827396,-1860.0,2.0,0.0,0.0,1.0],[17.05792651827396,27.09104801822525,0.0,2.0,0.0,1.0,1.0],[27.09104801822525,28.271415253513638,890.0,2.0,8.0,4.0,-1.0],[28.271415253513638,97.91308213552851,1860.0,2.0,8.0,4.0,-1.0]]</t>
+          <t>[[-78.55181954008546,17.05792651827396,-1860.0,2.0,0.0,0.0,1.0,0.8935542186905485],[17.05792651827396,27.09104801822525,0.0,2.0,0.0,1.0,1.0,0.7871084355580185],[27.09104801822525,28.271415253513638,890.0,2.0,8.0,4.0,-1.0,0.7306721641566234],[28.271415253513638,97.91308213552851,1860.0,2.0,8.0,4.0,-1.0,0.6691629694831929]]</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>[[-78.17298230370383,-0.10757517648659132,-1860.0,1.0,0.0,0.0,1.0],[-0.10757517648659132,17.30701564420032,-1860.0,0.0,0.0,0.0,1.0],[17.30701564420032,28.116072015661175,0.0,0.0,0.0,1.0,1.0],[28.116072015661175,101.3774540888958,1860.0,2.0,9.0,2.0,-1.0]]</t>
+          <t>[[-78.17298230370383,-0.10757517648659132,-1860.0,1.0,0.0,0.0,1.0,1.0000000018230786],[-0.10757517648659132,17.30701564420032,-1860.0,0.0,0.0,0.0,1.0,1.0000000018230786],[17.30701564420032,28.116072015661175,0.0,0.0,0.0,1.0,1.0,0.8935542186905485],[28.116072015661175,101.3774540888958,1860.0,2.0,9.0,2.0,-1.0,0.7756087526157229]]</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="F307" s="4" t="inlineStr">
         <is>
-          <t>[0,0,0,0,0]</t>
+          <t>[0,0,10.8090563715,0,0]</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>[[-76.82123688797603,27.576057884790828,0.0,0.0,0.0,1.0,1.0],[27.576057884790828,28.162559540817597,1678.65,1.0,0.0,0.0,1.0],[28.162559540817597,98.5427582640312,1860.0,1.0,9.0,2.0,-1.0]]</t>
+          <t>[[-76.82123688797603,27.576057884790828,0.0,0.0,0.0,1.0,1.0,1.000000001823079],[27.576057884790828,28.162559540817597,1678.65,1.0,0.0,0.0,1.0,0.8935542186905489],[28.162559540817597,98.5427582640312,1860.0,1.0,9.0,2.0,-1.0,0.8820545357482534]]</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>[[-77.28309235745627,28.205004030662934,0.0,0.0,0.0,1.0,1.0],[28.205004030662934,28.79432300489823,890.0,0.0,8.0,3.0,-1.0],[28.79432300489823,98.92328093889927,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[-77.28309235745627,28.205004030662934,0.0,0.0,0.0,1.0,1.0,1.000000001823079],[28.205004030662934,28.79432300489823,890.0,0.0,8.0,3.0,-1.0,0.943563730421684],[28.79432300489823,98.92328093889927,1860.0,0.0,8.0,3.0,-1.0,0.8820545357482534]]</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>[[-78.75383820031401,26.311509402816753,0.0,0.0,0.0,1.0,1.0],[26.311509402816753,27.498688471778678,890.0,0.0,8.0,2.0,-1.0],[27.498688471778678,98.72943260949444,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-78.75383820031401,26.311509402816753,0.0,0.0,0.0,1.0,1.0,1.000000001823079],[26.311509402816753,27.498688471778678,890.0,0.0,8.0,2.0,-1.0,0.943563730421684],[27.498688471778678,98.72943260949444,1860.0,0.0,8.0,2.0,-1.0,0.8820545357482534]]</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>[[-78.49033405014359,22.240680343560555,-1860.0,1.0,8.0,0.0,-1.0],[22.240680343560555,24.62484636471332,-1074.7922,0.0,8.0,1.0,-1.0],[24.62484636471332,27.60505389115427,0.0,0.0,8.0,1.0,-1.0],[27.60505389115427,28.20109539644247,708.65,1.0,8.0,0.0,-1.0],[28.20109539644247,99.72607603102529,1860.0,1.0,8.0,0.0,-1.0]]</t>
+          <t>[[-78.49033405014359,22.240680343560555,-1860.0,1.0,8.0,0.0,-1.0,0.988500318880783],[22.240680343560555,24.62484636471332,-1074.7922,0.0,8.0,1.0,-1.0,0.9435637279169277],[24.62484636471332,27.60505389115427,0.0,0.0,8.0,1.0,-1.0,0.882054535748253],[27.60505389115427,28.20109539644247,708.65,1.0,8.0,0.0,-1.0,0.8371179472891535],[28.20109539644247,99.72607603102529,1860.0,1.0,8.0,0.0,-1.0,0.7641090696734274]]</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>[[-77.24075628550654,12.979504199324538,-1860.0,1.0,8.0,0.0,-1.0],[12.979504199324538,23.663482414633478,-1074.7922,0.0,8.0,0.0,-1.0],[23.663482414633478,26.631254141108172,0.0,0.0,7.0,1.0,-1.0],[26.631254141108172,27.22480848640312,890.0,0.0,7.0,1.0,-1.0],[27.22480848640312,100.23199295768087,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[-77.24075628550654,12.979504199324538,-1860.0,1.0,8.0,0.0,-1.0,0.988500318880783],[12.979504199324538,23.663482414633478,-1074.7922,0.0,8.0,0.0,-1.0,0.9435637279169277],[23.663482414633478,26.631254141108172,0.0,0.0,7.0,1.0,-1.0,0.882054535748253],[26.631254141108172,27.22480848640312,890.0,0.0,7.0,1.0,-1.0,0.8256182643468579],[27.22480848640312,100.23199295768087,1860.0,0.0,7.0,1.0,-1.0,0.7641090696734274]]</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>[[-79.36672443728148,12.962965173803298,-1860.0,1.0,7.0,0.0,-1.0],[12.962965173803298,23.089447260180336,-1074.7922,0.0,7.0,0.0,-1.0],[23.089447260180336,25.47214892756317,0.0,0.0,6.0,1.0,-1.0],[25.47214892756317,27.854850594946,890.0,0.0,6.0,1.0,-1.0],[27.854850594946,98.7402251995853,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-79.36672443728148,12.962965173803298,-1860.0,1.0,7.0,0.0,-1.0,0.8705548528059575],[12.962965173803298,23.089447260180336,-1074.7922,0.0,7.0,0.0,-1.0,0.8256182618421021],[23.089447260180336,25.47214892756317,0.0,0.0,6.0,1.0,-1.0,0.7641090696734274],[25.47214892756317,27.854850594946,890.0,0.0,6.0,1.0,-1.0,0.7076727982720323],[27.854850594946,98.7402251995853,1860.0,0.0,7.0,0.0,-1.0,0.6461636035986018]]</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>[[-76.30310316861275,13.049209030555218,-1860.0,1.0,6.0,0.0,-1.0],[13.049209030555218,22.849140045947834,-1074.7922,0.0,6.0,0.0,-1.0],[22.849140045947834,25.155006167216698,0.0,0.0,5.0,1.0,-1.0],[25.155006167216698,27.460872288485547,890.0,0.0,5.0,1.0,-1.0],[27.460872288485547,96.06038939623386,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[-76.30310316861275,13.049209030555218,-1860.0,1.0,6.0,0.0,-1.0,0.7526093867311319],[13.049209030555218,22.849140045947834,-1074.7922,0.0,6.0,0.0,-1.0,0.7076727957672765],[22.849140045947834,25.155006167216698,0.0,0.0,5.0,1.0,-1.0,0.6461636035986018],[25.155006167216698,27.460872288485547,890.0,0.0,5.0,1.0,-1.0,0.5897273321972067],[27.460872288485547,96.06038939623386,1860.0,0.0,5.0,1.0,-1.0,0.5282181375237762]]</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>[[-76.91211341013287,12.40546486328742,-1860.0,1.0,5.0,0.0,-1.0],[12.40546486328742,22.32964022700078,-1074.7922,0.0,5.0,0.0,-1.0],[22.32964022700078,24.664740312580406,0.0,0.0,4.0,1.0,-1.0],[24.664740312580406,27.583615419554917,890.0,0.0,4.0,1.0,-1.0],[27.583615419554917,97.63661798694339,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-76.91211341013287,12.40546486328742,-1860.0,1.0,5.0,0.0,-1.0,0.6346639206563063],[12.40546486328742,22.32964022700078,-1074.7922,0.0,5.0,0.0,-1.0,0.5897273296924509],[22.32964022700078,24.664740312580406,0.0,0.0,4.0,1.0,-1.0,0.5282181375237762],[24.664740312580406,27.583615419554917,890.0,0.0,4.0,1.0,-1.0,0.47178186612238115],[27.583615419554917,97.63661798694339,1860.0,0.0,5.0,0.0,-1.0,0.4102726714489506]]</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>[[-76.6849404411584,13.092704097159071,-1860.0,1.0,4.0,0.0,-1.0],[13.092704097159071,21.89443395385686,-1074.7922,0.0,4.0,0.0,-1.0],[21.89443395385686,24.241561915642947,0.0,0.0,3.0,1.0,-1.0],[24.241561915642947,27.175471867875544,890.0,0.0,3.0,1.0,-1.0],[27.175471867875544,98.76287470235093,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-76.6849404411584,13.092704097159071,-1860.0,1.0,4.0,0.0,-1.0,0.5167184545814807],[13.092704097159071,21.89443395385686,-1074.7922,0.0,4.0,0.0,-1.0,0.47178186361762525],[21.89443395385686,24.241561915642947,0.0,0.0,3.0,1.0,-1.0,0.4102726714489506],[24.241561915642947,27.175471867875544,890.0,0.0,3.0,1.0,-1.0,0.3538364000475555],[27.175471867875544,98.76287470235093,1860.0,0.0,4.0,0.0,-1.0,0.29232720537412493]]</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>[[-76.81938413515324,13.227126758793133,-1860.0,1.0,3.0,0.0,-1.0],[13.227126758793133,24.9979124965639,-1074.7922,0.0,3.0,0.0,-1.0],[24.9979124965639,27.35206964411806,0.0,0.0,2.0,1.0,-1.0],[27.35206964411806,30.29476607856074,890.0,0.0,2.0,1.0,-1.0],[30.29476607856074,99.15386264451976,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-76.81938413515324,13.227126758793133,-1860.0,1.0,3.0,0.0,-1.0,0.398772988506655],[13.227126758793133,24.9979124965639,-1074.7922,0.0,3.0,0.0,-1.0,0.35383639754279955],[24.9979124965639,27.35206964411806,0.0,0.0,2.0,1.0,-1.0,0.2923272053741249],[27.35206964411806,30.29476607856074,890.0,0.0,2.0,1.0,-1.0,0.2358909339727298],[30.29476607856074,99.15386264451976,1860.0,0.0,3.0,0.0,-1.0,0.17438173929929923]]</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -8692,7 +8692,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>[[-76.22674708860174,5.132350415475756,-1860.0,10.0,3.0,0.0,1.0],[5.132350415475756,5.709365291391194,-1808.4764,9.0,3.0,1.0,1.0],[5.709365291391194,13.21055867829196,-1074.7922,0.0,3.0,0.0,-1.0],[13.21055867829196,14.941603306038289,0.0,0.0,2.0,1.0,-1.0],[14.941603306038289,31.098019831670697,890.0,0.0,2.0,0.0,-1.0],[31.098019831670697,96.30070081011579,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-76.22674708860174,5.132350415475756,-1860.0,10.0,3.0,0.0,1.0,0.398772988506655],[5.132350415475756,5.709365291391194,-1808.4764,9.0,3.0,1.0,1.0,0.39582434874761885],[5.709365291391194,13.21055867829196,-1074.7922,0.0,3.0,0.0,-1.0,0.35383639754279955],[13.21055867829196,14.941603306038289,0.0,0.0,2.0,1.0,-1.0,0.2923272053741249],[14.941603306038289,31.098019831670697,890.0,0.0,2.0,0.0,-1.0,0.2358909339727298],[31.098019831670697,96.30070081011579,1860.0,0.0,2.0,0.0,-1.0,0.17438173929929923]]</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>[[-77.3758693032235,4.235039290689755,-1860.0,10.0,2.0,0.0,1.0],[4.235039290689755,4.822168129494898,-733.6842,9.0,2.0,1.0,1.0],[4.822168129494898,14.803358389182122,0.0,0.0,2.0,1.0,-1.0],[14.803358389182122,98.17565349951076,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-77.3758693032235,4.235039290689755,-1860.0,10.0,2.0,0.0,1.0,0.34233671710526004],[4.235039290689755,4.822168129494898,-733.6842,9.0,2.0,1.0,1.0,0.27787888517754916],[4.822168129494898,14.803358389182122,0.0,0.0,2.0,1.0,-1.0,0.2358909339727299],[14.803358389182122,98.17565349951076,1860.0,0.0,2.0,0.0,-1.0,0.11794546789790426]]</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>[[-76.15834053787013,5.166409497287617,-1860.0,10.0,1.0,0.0,1.0],[5.166409497287617,5.751479641425448,-733.6842,9.0,1.0,1.0,1.0],[5.751479641425448,14.527531803492835,0.0,0.0,1.0,1.0,-1.0],[14.527531803492835,98.77763255933972,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-76.15834053787013,5.166409497287617,-1860.0,10.0,1.0,0.0,1.0,0.2243912510304343],[5.166409497287617,5.751479641425448,-733.6842,9.0,1.0,1.0,1.0,0.15993341910272346],[5.751479641425448,14.527531803492835,0.0,0.0,1.0,1.0,-1.0,0.1179454678979042],[14.527531803492835,98.77763255933972,1860.0,0.0,1.0,0.0,-1.0,1.823078563112368e-09]]</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>[[-70.86689908854675,4.8735710469757265,-1860.0,10.0,0.0,0.0,1.0],[4.8735710469757265,5.399546534027962,-733.6842,9.0,0.0,1.0,1.0],[5.399546534027962,86.39977154007282,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-70.86689908854675,4.8735710469757265,-1860.0,10.0,0.0,0.0,1.0,0.10644578495560872],[4.8735710469757265,5.399546534027962,-733.6842,9.0,0.0,1.0,1.0,0.04198795302789788],[5.399546534027962,86.39977154007282,0.0,0.0,0.0,1.0,-1.0,1.823078604745731e-09]]</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>[[-74.04545270279169,1.3488134486434689,-1860.0,9.0,0.0,0.0,1.0],[1.3488134486434689,26.113353425392233,-733.6842,9.0,0.0,0.0,1.0],[26.113353425392233,90.50115736493905,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-74.04545270279169,1.3488134486434689,-1860.0,9.0,0.0,0.0,1.0,0.10644578495560872],[1.3488134486434689,26.113353425392233,-733.6842,9.0,0.0,0.0,1.0,0.04198795302789788],[26.113353425392233,90.50115736493905,0.0,0.0,0.0,1.0,-1.0,1.823078604745731e-09]]</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>[[-73.16739012069996,26.210182311470362,-1860.0,8.0,0.0,0.0,1.0],[26.210182311470362,28.955419118988885,0.0,8.0,7.0,1.0,-1.0],[28.955419118988885,90.99777096890739,662.1501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-73.16739012069996,26.210182311470362,-1860.0,8.0,0.0,0.0,1.0,0.148433736160428],[26.210182311470362,28.955419118988885,0.0,8.0,7.0,1.0,-1.0,0.04198795302789788],[28.955419118988885,90.99777096890739,662.1501,0.0,0.0,0.0,-1.0,-5.120485119247675e-09]]</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>[[-73.46734037194621,26.21708639766294,-1860.0,7.0,0.0,0.0,1.0],[26.21708639766294,27.860236289469682,-873.8504,7.0,8.0,0.0,-1.0],[27.860236289469682,31.14653607308317,0.0,7.0,7.0,1.0,-1.0],[31.14653607308317,90.29993217812597,1860.0,7.0,7.0,1.0,-1.0]]</t>
+          <t>[[-73.46734037194621,26.21708639766294,-1860.0,7.0,0.0,0.0,1.0,0.2548795192929581],[26.21708639766294,27.860236289469682,-873.8504,7.0,8.0,0.0,-1.0,0.19844324700380148],[27.860236289469682,31.14653607308317,0.0,7.0,7.0,1.0,-1.0,0.148433736160428],[31.14653607308317,90.29993217812597,1860.0,7.0,7.0,1.0,-1.0,0.030488270085602356]]</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>[[-73.16641720536043,25.028649252678335,-1860.0,6.0,0.0,0.0,1.0],[25.028649252678335,26.119705546656533,-1074.7922,7.0,9.0,1.0,-1.0],[26.119705546656533,28.847346281602057,0.0,7.0,8.0,2.0,-1.0],[28.847346281602057,29.39287442859117,890.0,7.0,8.0,1.0,-1.0],[29.39287442859117,89.94649874438173,1860.0,7.0,8.0,1.0,-1.0]]</t>
+          <t>[[-73.16641720536043,25.028649252678335,-1860.0,6.0,0.0,0.0,1.0,0.3613253024254882],[25.028649252678335,26.119705546656533,-1074.7922,7.0,9.0,1.0,-1.0,0.3163887114616328],[26.119705546656533,28.847346281602057,0.0,7.0,8.0,2.0,-1.0,0.2548795192929581],[28.847346281602057,29.39287442859117,890.0,7.0,8.0,1.0,-1.0,0.19844324789156303],[29.39287442859117,89.94649874438173,1860.0,7.0,8.0,1.0,-1.0,0.13693405321813246]]</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>[[-72.44436250767971,25.212408590236507,-1860.0,5.0,0.0,0.0,1.0],[25.212408590236507,25.754946207447148,-873.8504,5.0,8.0,0.0,-1.0],[25.754946207447148,29.010171910711023,0.0,5.0,7.0,1.0,-1.0],[29.010171910711023,30.63778476234296,1071.35,5.0,7.0,1.0,-1.0],[30.63778476234296,89.77438503830332,1860.0,5.0,7.0,1.0,-1.0]]</t>
+          <t>[[-72.44436250767971,25.212408590236507,-1860.0,5.0,0.0,0.0,1.0,0.46777108555801833],[25.212408590236507,25.754946207447148,-873.8504,5.0,8.0,0.0,-1.0,0.4113348132688617],[25.754946207447148,29.010171910711023,0.0,5.0,7.0,1.0,-1.0,0.3613253024254882],[29.010171910711023,30.63778476234296,1071.35,5.0,7.0,1.0,-1.0,0.2933893480817977],[30.63778476234296,89.77438503830332,1860.0,5.0,7.0,1.0,-1.0,0.24337983635066257]]</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>[[-72.5270402690748,25.66135004054381,-1860.0,4.0,0.0,0.0,1.0],[25.66135004054381,26.20382733507209,-873.8504,4.0,8.0,2.0,-1.0],[26.20382733507209,28.91621380771349,0.0,4.0,7.0,3.0,-1.0],[28.91621380771349,31.62860028035489,1071.35,4.0,7.0,1.0,-1.0],[31.62860028035489,89.6736707948808,1860.0,4.0,8.0,0.0,-1.0]]</t>
+          <t>[[-72.5270402690748,25.66135004054381,-1860.0,4.0,0.0,0.0,1.0,0.5742168686905484],[25.66135004054381,26.20382733507209,-873.8504,4.0,8.0,2.0,-1.0,0.5177805964013917],[26.20382733507209,28.91621380771349,0.0,4.0,7.0,3.0,-1.0,0.4677710855580183],[28.91621380771349,31.62860028035489,1071.35,4.0,7.0,1.0,-1.0,0.39983513121432773],[31.62860028035489,89.6736707948808,1860.0,4.0,8.0,0.0,-1.0,0.34982561948319263]]</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>[[-58.46120781971605,25.956452845326538,-1860.0,3.0,0.0,0.0,1.0],[25.956452845326538,28.786095102255345,0.0,3.0,7.0,1.0,-1.0],[28.786095102255345,30.672523273541202,1071.35,3.0,7.0,1.0,-1.0],[30.672523273541202,82.54929798390258,1860.0,3.0,7.0,1.0,-1.0]]</t>
+          <t>[[-58.46120781971605,25.956452845326538,-1860.0,3.0,0.0,0.0,1.0,0.6806626518230785],[25.956452845326538,28.786095102255345,0.0,3.0,7.0,1.0,-1.0,0.5742168686905484],[28.786095102255345,30.672523273541202,1071.35,3.0,7.0,1.0,-1.0,0.5062809143468578],[30.672523273541202,82.54929798390258,1860.0,3.0,7.0,1.0,-1.0,0.4562714026157228]]</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>[[-51.9868415710049,25.663683134040923,-1860.0,2.0,0.0,0.0,1.0],[25.663683134040923,26.097484948035586,-873.8504,2.0,8.0,2.0,-1.0],[26.097484948035586,28.700295832003604,0.0,2.0,7.0,3.0,-1.0],[28.700295832003604,29.567899459992944,1071.35,2.0,7.0,3.0,-1.0],[29.567899459992944,77.71990081340124,1860.0,2.0,7.0,3.0,-1.0]]</t>
+          <t>[[-51.9868415710049,25.663683134040923,-1860.0,2.0,0.0,0.0,1.0,0.7871084349556086],[25.663683134040923,26.097484948035586,-873.8504,2.0,8.0,2.0,-1.0,0.730672162666452],[26.097484948035586,28.700295832003604,0.0,2.0,7.0,3.0,-1.0,0.6806626518230785],[28.700295832003604,29.567899459992944,1071.35,2.0,7.0,3.0,-1.0,0.6127266974793879],[29.567899459992944,77.71990081340124,1860.0,2.0,7.0,3.0,-1.0,0.5627171857482529]]</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>[[-51.83092204715708,26.027184303636894,-1860.0,1.0,0.0,0.0,1.0],[26.027184303636894,27.75736444476565,-873.8504,0.0,8.0,0.0,-1.0],[27.75736444476565,30.78517969174097,0.0,1.0,7.0,1.0,-1.0],[30.78517969174097,77.50004350221737,1860.0,1.0,7.0,1.0,-1.0]]</t>
+          <t>[[-51.83092204715708,26.027184303636894,-1860.0,1.0,0.0,0.0,1.0,0.8935542180881386],[26.027184303636894,27.75736444476565,-873.8504,0.0,8.0,0.0,-1.0,0.837117945798982],[27.75736444476565,30.78517969174097,0.0,1.0,7.0,1.0,-1.0,0.7871084349556086],[30.78517969174097,77.50004350221737,1860.0,1.0,7.0,1.0,-1.0,0.669162968880783]]</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>[[-51.28193411127005,-0.4077283018936626,-1860.0,1.0,0.0,0.0,1.0],[-0.4077283018936626,26.098160439125962,-1860.0,0.0,0.0,0.0,1.0],[26.098160439125962,29.090760780853984,0.0,0.0,7.0,3.0,-1.0],[29.090760780853984,29.518275115386558,1071.35,0.0,7.0,1.0,-1.0],[29.518275115386558,76.54485191396977,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[-51.28193411127005,-0.4077283018936626,-1860.0,1.0,0.0,0.0,1.0,1.0000000012206687],[-0.4077283018936626,26.098160439125962,-1860.0,0.0,0.0,0.0,1.0,1.0000000012206687],[26.098160439125962,29.090760780853984,0.0,0.0,7.0,3.0,-1.0,0.8935542180881386],[29.090760780853984,29.518275115386558,1071.35,0.0,7.0,1.0,-1.0,0.825618263744448],[29.518275115386558,76.54485191396977,1860.0,0.0,7.0,1.0,-1.0,0.775608752013313]]</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>[[-52.72549261811467,27.491874941128486,0.0,0.0,0.0,1.0,1.0],[27.491874941128486,28.36856748275956,890.0,0.0,8.0,2.0,-1.0],[28.36856748275956,78.34004235573073,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-52.72549261811467,27.491874941128486,0.0,0.0,0.0,1.0,1.0,1.000000001220669],[27.491874941128486,28.36856748275956,890.0,0.0,8.0,2.0,-1.0,0.9435637298192738],[28.36856748275956,78.34004235573073,1860.0,0.0,8.0,2.0,-1.0,0.8820545351458433]]</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>[[-53.02861077817619,23.86127477172255,-1860.0,1.0,8.0,0.0,-1.0],[23.86127477172255,24.750175182704027,-1074.7922,0.0,8.0,0.0,-1.0],[24.750175182704027,27.86132662113924,0.0,0.0,7.0,1.0,-1.0],[27.86132662113924,28.750227032120733,890.0,0.0,7.0,1.0,-1.0],[28.750227032120733,79.8620006635563,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[-53.02861077817619,23.86127477172255,-1860.0,1.0,8.0,0.0,-1.0,0.9885003182783731],[23.86127477172255,24.750175182704027,-1074.7922,0.0,8.0,0.0,-1.0,0.9435637273145178],[24.750175182704027,27.86132662113924,0.0,0.0,7.0,1.0,-1.0,0.8820545351458431],[27.86132662113924,28.750227032120733,890.0,0.0,7.0,1.0,-1.0,0.825618263744448],[28.750227032120733,79.8620006635563,1860.0,0.0,7.0,1.0,-1.0,0.7641090690710175]]</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>[[-53.763008783892005,24.267762471335686,-1860.0,1.0,7.0,0.0,-1.0],[24.267762471335686,26.97403199463838,0.0,0.0,6.0,2.0,-1.0],[26.97403199463838,29.22925659739063,890.0,0.0,6.0,1.0,-1.0],[29.22925659739063,81.09942246069227,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[-53.763008783892005,24.267762471335686,-1860.0,1.0,7.0,0.0,-1.0,0.8705548522035476],[24.267762471335686,26.97403199463838,0.0,0.0,6.0,2.0,-1.0,0.7641090690710175],[26.97403199463838,29.22925659739063,890.0,0.0,6.0,1.0,-1.0,0.7076727976696224],[29.22925659739063,81.09942246069227,1860.0,0.0,6.0,1.0,-1.0,0.6461636029961919]]</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>[[-53.25147419588011,23.848205581550005,-1860.0,1.0,6.0,0.0,-1.0],[23.848205581550005,26.52218291487128,-1074.7922,0.0,6.0,1.0,-1.0],[26.52218291487128,29.196160248192555,0.0,0.0,6.0,1.0,-1.0],[29.196160248192555,80.00172958129681,1860.0,1.0,6.0,0.0,-1.0]]</t>
+          <t>[[-53.25147419588011,23.848205581550005,-1860.0,1.0,6.0,0.0,-1.0,0.752609386128722],[23.848205581550005,26.52218291487128,-1074.7922,0.0,6.0,1.0,-1.0,0.7076727951648666],[26.52218291487128,29.196160248192555,0.0,0.0,6.0,1.0,-1.0,0.6461636029961919],[29.196160248192555,80.00172958129681,1860.0,1.0,6.0,0.0,-1.0,0.5282181369213663]]</t>
         </is>
       </c>
       <c r="C335" t="n">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>[[-52.78838470680066,22.8872787367771,-1860.0,1.0,5.0,0.0,-1.0],[22.8872787367771,23.762141897974537,-1074.7922,0.0,5.0,1.0,-1.0],[23.762141897974537,26.386731381566825,0.0,0.0,4.0,2.0,-1.0],[26.386731381566825,28.13645770396169,890.0,0.0,4.0,1.0,-1.0],[28.13645770396169,78.00365789221523,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-52.78838470680066,22.8872787367771,-1860.0,1.0,5.0,0.0,-1.0,0.6346639200538964],[22.8872787367771,23.762141897974537,-1074.7922,0.0,5.0,1.0,-1.0,0.589727329090041],[23.762141897974537,26.386731381566825,0.0,0.0,4.0,2.0,-1.0,0.5282181369213663],[26.386731381566825,28.13645770396169,890.0,0.0,4.0,1.0,-1.0,0.47178186551997126],[28.13645770396169,78.00365789221523,1860.0,0.0,5.0,0.0,-1.0,0.4102726708465407]]</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>[[-51.94254860316724,24.827764393604028,-1860.0,1.0,4.0,0.0,-1.0],[24.827764393604028,25.690352180084602,-1074.7922,0.0,4.0,1.0,-1.0],[25.690352180084602,28.278115539526326,0.0,0.0,3.0,2.0,-1.0],[28.278115539526326,29.571997219247194,890.0,0.0,3.0,1.0,-1.0],[29.571997219247194,77.01432547567887,1860.0,0.0,3.0,1.0,-1.0]]</t>
+          <t>[[-51.94254860316724,24.827764393604028,-1860.0,1.0,4.0,0.0,-1.0,0.5167184539790708],[24.827764393604028,25.690352180084602,-1074.7922,0.0,4.0,1.0,-1.0,0.47178186301521535],[25.690352180084602,28.278115539526326,0.0,0.0,3.0,2.0,-1.0,0.4102726708465407],[28.278115539526326,29.571997219247194,890.0,0.0,3.0,1.0,-1.0,0.3538363994451456],[29.571997219247194,77.01432547567887,1860.0,0.0,3.0,1.0,-1.0,0.29232720477171503]]</t>
         </is>
       </c>
       <c r="C337" t="n">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>[[-53.61081927555152,24.995345218790504,-1860.0,1.0,3.0,0.0,-1.0],[24.995345218790504,27.659960964361417,0.0,0.0,2.0,2.0,-1.0],[27.659960964361417,29.436371461408697,890.0,0.0,2.0,1.0,-1.0],[29.436371461408697,79.17586537873245,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[-53.61081927555152,24.995345218790504,-1860.0,1.0,3.0,0.0,-1.0,0.3987729879042451],[24.995345218790504,27.659960964361417,0.0,0.0,2.0,2.0,-1.0,0.292327204771715],[27.659960964361417,29.436371461408697,890.0,0.0,2.0,1.0,-1.0,0.2358909333703199],[29.436371461408697,79.17586537873245,1860.0,0.0,2.0,1.0,-1.0,0.17438173869688933]]</t>
         </is>
       </c>
       <c r="C338" t="n">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>[[-52.25692344421887,24.072374850943987,-1860.0,1.0,2.0,0.0,-1.0],[24.072374850943987,25.380877107432497,-1074.7922,0.0,2.0,1.0,-1.0],[25.380877107432497,27.9978816204095,0.0,0.0,1.0,2.0,-1.0],[27.9978816204095,28.434049039239014,890.0,0.0,1.0,2.0,-1.0],[28.434049039239014,78.15713478580224,1860.0,0.0,1.0,2.0,-1.0]]</t>
+          <t>[[-52.25692344421887,24.072374850943987,-1860.0,1.0,2.0,0.0,-1.0,0.2808275218294195],[24.072374850943987,25.380877107432497,-1074.7922,0.0,2.0,1.0,-1.0,0.2358909308655641],[25.380877107432497,27.9978816204095,0.0,0.0,1.0,2.0,-1.0,0.1743817386968894],[27.9978816204095,28.434049039239014,890.0,0.0,1.0,2.0,-1.0,0.11794546729549434],[28.434049039239014,78.15713478580224,1860.0,0.0,1.0,2.0,-1.0,0.05643627262206376]]</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>[[-52.62343518832135,24.506548271152198,-1860.0,1.0,1.0,0.0,-1.0],[24.506548271152198,25.378073507982407,-1074.7922,0.0,1.0,0.0,-1.0],[25.378073507982407,27.992649218473034,0.0,0.0,0.0,1.0,-1.0],[27.992649218473034,31.042987547378758,890.0,0.0,0.0,0.0,-1.0],[31.042987547378758,77.669587717795,890.0001,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-52.62343518832135,24.506548271152198,-1860.0,1.0,1.0,0.0,-1.0,0.16288205575459386],[24.506548271152198,25.378073507982407,-1074.7922,0.0,1.0,0.0,-1.0,0.11794546479073845],[25.378073507982407,27.992649218473034,0.0,0.0,0.0,1.0,-1.0,0.05643627262206376],[27.992649218473034,31.042987547378758,890.0,0.0,0.0,0.0,-1.0,1.2206687050042575e-09],[31.042987547378758,77.669587717795,890.0001,0.0,0.0,0.0,-1.0,-5.1204853898645375e-09]]</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="F340" s="4" t="inlineStr">
         <is>
-          <t>[0,0.8715252368,0,0,0]</t>
+          <t>[0,0.8715252368,2.6145757105,0,0]</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>[[-51.28444037102793,20.403578379620157,-1860.0,1.0,1.0,0.0,-1.0],[20.403578379620157,25.493851900376242,-1074.7922,0.0,1.0,0.0,-1.0],[25.493851900376242,28.038988660754285,0.0,0.0,0.0,1.0,-1.0],[28.038988660754285,31.432504341258337,890.0,0.0,0.0,0.0,-1.0],[31.432504341258337,75.548208187811,890.0001,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-51.28444037102793,20.403578379620157,-1860.0,1.0,1.0,0.0,-1.0,0.16288205575459386],[20.403578379620157,25.493851900376242,-1074.7922,0.0,1.0,0.0,-1.0,0.11794546479073845],[25.493851900376242,28.038988660754285,0.0,0.0,0.0,1.0,-1.0,0.05643627262206376],[28.038988660754285,31.432504341258337,890.0,0.0,0.0,0.0,-1.0,1.2206687050042575e-09],[31.432504341258337,75.548208187811,890.0001,0.0,0.0,0.0,-1.0,-5.1204853898645375e-09]]</t>
         </is>
       </c>
       <c r="C341" t="n">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="F341" s="4" t="inlineStr">
         <is>
-          <t>[0,5.0902735208,0,0,0]</t>
+          <t>[0,5.0902735208,2.5451367604,0,0]</t>
         </is>
       </c>
     </row>
@@ -9316,7 +9316,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>[[-54.111548927125035,21.454922932296917,-1860.0,1.0,0.0,0.0,-1.0],[21.454922932296917,80.37877896553665,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-54.111548927125035,21.454922932296917,-1860.0,1.0,0.0,0.0,-1.0,0.10644578435319882],[21.454922932296917,80.37877896553665,0.0,0.0,0.0,1.0,-1.0,1.220668705004258e-09]]</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>[[-54.34885769927172,14.416985927648668,-1860.0,1.0,0.0,0.0,-1.0],[14.416985927648668,81.81662074078919,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-54.34885769927172,14.416985927648668,-1860.0,1.0,0.0,0.0,-1.0,0.10644578435319882],[14.416985927648668,81.81662074078919,0.0,0.0,0.0,1.0,-1.0,1.220668705004258e-09]]</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>[[-51.769675695793886,1.7519634513906297,-1860.0,1.0,0.0,0.0,-1.0],[1.7519634513906297,78.33577231240261,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-51.769675695793886,1.7519634513906297,-1860.0,1.0,0.0,0.0,-1.0,0.10644578435319882],[1.7519634513906297,78.33577231240261,0.0,0.0,0.0,1.0,-1.0,1.220668705004258e-09]]</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>[[-53.364024251043844,-3.49297891177482,-1860.0,9.0,0.0,0.0,1.0],[-3.49297891177482,0.9597929935170626,-733.6842,9.0,0.0,0.0,1.0],[0.9597929935170626,79.77385571718331,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-53.364024251043844,-3.49297891177482,-1860.0,9.0,0.0,0.0,1.0,0.10644578435319882],[-3.49297891177482,0.9597929935170626,-733.6842,9.0,0.0,0.0,1.0,0.04198795242548798],[0.9597929935170626,79.77385571718331,0.0,0.0,0.0,1.0,-1.0,1.220668705004258e-09]]</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>[[-50.62637249128569,0.8555271198121375,-1860.0,9.0,0.0,0.0,1.0],[0.8555271198121375,24.2944407638892,-733.6842,9.0,0.0,0.0,1.0],[24.2944407638892,74.52068428691146,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-50.62637249128569,0.8555271198121375,-1860.0,9.0,0.0,0.0,1.0,0.10644578435319882],[0.8555271198121375,24.2944407638892,-733.6842,9.0,0.0,0.0,1.0,0.04198795242548798],[24.2944407638892,74.52068428691146,0.0,0.0,0.0,1.0,-1.0,1.220668705004258e-09]]</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>[[-53.84943215711012,0.6402757873893492,-1860.0,8.0,0.0,0.0,1.0],[0.6402757873893492,23.607012193748623,-733.6842,8.0,0.0,0.0,1.0],[23.607012193748623,26.308981182732076,0.0,8.0,0.0,1.0,1.0],[26.308981182732076,27.659965677223802,1016.5,9.0,0.0,0.0,1.0],[27.659965677223802,80.79868912723154,1678.6501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-53.84943215711012,0.6402757873893492,-1860.0,8.0,0.0,0.0,1.0,0.2128915674857289],[0.6402757873893492,23.607012193748623,-733.6842,8.0,0.0,0.0,1.0,0.1484337355580181],[23.607012193748623,26.308981182732076,0.0,8.0,0.0,1.0,1.0,0.1064457843531988],[26.308981182732076,27.659965677223802,1016.5,9.0,0.0,0.0,1.0,0.041987953027897595],[27.659965677223802,80.79868912723154,1678.6501,0.0,0.0,0.0,-1.0,-5.120485410681219e-09]]</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>[[-52.22827420741968,0.8428918798104661,-1860.0,7.0,0.0,0.0,1.0],[0.8428918798104661,23.898398458689137,-733.6842,7.0,0.0,0.0,1.0],[23.898398458689137,26.07344624914939,0.0,7.0,9.0,3.0,-1.0],[26.07344624914939,27.378474923425536,46.5,8.0,9.0,2.0,-1.0],[27.378474923425536,27.813484481517584,1725.15,9.0,9.0,1.0,-1.0],[27.813484481517584,77.83958366210338,1860.0,9.0,9.0,1.0,-1.0]]</t>
+          <t>[[-52.22827420741968,0.8428918798104661,-1860.0,7.0,0.0,0.0,1.0,0.319337350618259],[0.8428918798104661,23.898398458689137,-733.6842,7.0,0.0,0.0,1.0,0.2548795186905482],[23.898398458689137,26.07344624914939,0.0,7.0,9.0,3.0,-1.0,0.2128915674857289],[26.07344624914939,27.378474923425536,46.5,8.0,9.0,2.0,-1.0,0.20994293083385826],[27.378474923425536,27.813484481517584,1725.15,9.0,9.0,1.0,-1.0,0.10349714770132815],[27.813484481517584,77.83958366210338,1860.0,9.0,9.0,1.0,-1.0,0.09494610141090327]]</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>[[-50.892780344396385,0.8524851969464464,-1860.0,6.0,0.0,0.0,1.0],[0.8524851969464464,23.569918849243308,-733.6842,6.0,0.0,0.0,1.0],[23.569918849243308,26.09407814394295,0.0,6.0,8.0,5.0,-1.0],[26.09407814394295,26.514771359726225,227.85,6.0,8.0,3.0,-1.0],[26.514771359726225,74.89449117480285,1860.0,6.0,9.0,2.0,-1.0]]</t>
+          <t>[[-50.892780344396385,0.8524851969464464,-1860.0,6.0,0.0,0.0,1.0,0.4257831337507892],[0.8524851969464464,23.569918849243308,-733.6842,6.0,0.0,0.0,1.0,0.36132530182307837],[23.569918849243308,26.09407814394295,0.0,6.0,8.0,5.0,-1.0,0.3193373506182591],[26.09407814394295,26.514771359726225,227.85,6.0,8.0,3.0,-1.0,0.3048890310240929],[26.514771359726225,74.89449117480285,1860.0,6.0,9.0,2.0,-1.0,0.20139188454343343]]</t>
         </is>
       </c>
       <c r="C349" t="n">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>[[-52.48481047428031,0.5876107189555526,-1860.0,5.0,0.0,0.0,1.0],[0.5876107189555526,23.643662548803917,-733.6842,5.0,0.0,0.0,1.0],[23.643662548803917,26.253781623881096,0.0,5.0,8.0,4.0,-1.0],[26.253781623881096,27.55884116141968,227.85,5.0,8.0,3.0,-1.0],[27.55884116141968,77.58612343373217,1860.0,5.0,9.0,2.0,-1.0]]</t>
+          <t>[[-52.48481047428031,0.5876107189555526,-1860.0,5.0,0.0,0.0,1.0,0.5322289168833193],[0.5876107189555526,23.643662548803917,-733.6842,5.0,0.0,0.0,1.0,0.4677710849556085],[23.643662548803917,26.253781623881096,0.0,5.0,8.0,4.0,-1.0,0.4257831337507892],[26.253781623881096,27.55884116141968,227.85,5.0,8.0,3.0,-1.0,0.41133481415662304],[27.55884116141968,77.58612343373217,1860.0,5.0,9.0,2.0,-1.0,0.30783766767596354]]</t>
         </is>
       </c>
       <c r="C350" t="n">
@@ -9550,7 +9550,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>[[-52.921615306892676,0.731066248110416,-1860.0,4.0,0.0,0.0,1.0],[0.731066248110416,24.47897447737408,-733.6842,4.0,0.0,0.0,1.0],[24.47897447737408,27.117630947292255,0.0,4.0,9.0,3.0,-1.0],[27.117630947292255,27.55740702561195,46.5,5.0,9.0,2.0,-1.0],[27.55740702561195,78.57143211069685,1860.0,5.0,9.0,2.0,-1.0]]</t>
+          <t>[[-52.921615306892676,0.731066248110416,-1860.0,4.0,0.0,0.0,1.0,0.6386747000158495],[0.731066248110416,24.47897447737408,-733.6842,4.0,0.0,0.0,1.0,0.5742168680881385],[24.47897447737408,27.117630947292255,0.0,4.0,9.0,3.0,-1.0,0.5322289168833193],[27.117630947292255,27.55740702561195,46.5,5.0,9.0,2.0,-1.0,0.5292802802314487],[27.55740702561195,78.57143211069685,1860.0,5.0,9.0,2.0,-1.0,0.41428345080849366]]</t>
         </is>
       </c>
       <c r="C351" t="n">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>[[-53.70585945289385,0.8340706073064155,-1860.0,3.0,0.0,0.0,1.0],[0.8340706073064155,23.633549566898324,-733.6842,3.0,0.0,0.0,1.0],[23.633549566898324,26.315841209203256,0.0,3.0,8.0,4.0,-1.0],[26.315841209203256,27.209938423304905,227.85,3.0,8.0,3.0,-1.0],[27.209938423304905,79.96167405530187,1860.0,3.0,9.0,2.0,-1.0]]</t>
+          <t>[[-53.70585945289385,0.8340706073064155,-1860.0,3.0,0.0,0.0,1.0,0.7451204831483795],[0.8340706073064155,23.633549566898324,-733.6842,3.0,0.0,0.0,1.0,0.6806626512206687],[23.633549566898324,26.315841209203256,0.0,3.0,8.0,4.0,-1.0,0.6386747000158495],[26.315841209203256,27.209938423304905,227.85,3.0,8.0,3.0,-1.0,0.6242263804216833],[27.209938423304905,79.96167405530187,1860.0,3.0,9.0,2.0,-1.0,0.5207292339410239]]</t>
         </is>
       </c>
       <c r="C352" t="n">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>[[-51.442497506295176,0.885661152353947,-1860.0,2.0,0.0,0.0,1.0],[0.885661152353947,23.85899910005356,-733.6842,2.0,0.0,0.0,1.0],[23.85899910005356,26.41159220535352,0.0,2.0,8.0,5.0,-1.0],[26.41159220535352,27.262456573786828,227.85,2.0,8.0,3.0,-1.0],[27.262456573786828,75.76172557448601,1860.0,2.0,9.0,2.0,-1.0]]</t>
+          <t>[[-51.442497506295176,0.885661152353947,-1860.0,2.0,0.0,0.0,1.0,0.8515662662809096],[0.885661152353947,23.85899910005356,-733.6842,2.0,0.0,0.0,1.0,0.7871084343531988],[23.85899910005356,26.41159220535352,0.0,2.0,8.0,5.0,-1.0,0.7451204831483795],[26.41159220535352,27.262456573786828,227.85,2.0,8.0,3.0,-1.0,0.7306721635542134],[27.262456573786828,75.76172557448601,1860.0,2.0,9.0,2.0,-1.0,0.6271750170735539]]</t>
         </is>
       </c>
       <c r="C353" t="n">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>[[-50.61850926697334,0.8924502784158221,-1860.0,1.0,0.0,0.0,1.0],[0.8924502784158221,24.30652279904725,-733.6842,1.0,0.0,0.0,1.0],[24.30652279904725,26.860785255843417,0.0,1.0,0.0,1.0,1.0],[26.860785255843417,76.66890316336847,1860.0,2.0,9.0,1.0,-1.0]]</t>
+          <t>[[-50.61850926697334,0.8924502784158221,-1860.0,1.0,0.0,0.0,1.0,0.9580120494134396],[0.8924502784158221,24.30652279904725,-733.6842,1.0,0.0,0.0,1.0,0.8935542174857288],[24.30652279904725,26.860785255843417,0.0,1.0,0.0,1.0,1.0,0.8515662662809096],[26.860785255843417,76.66890316336847,1860.0,2.0,9.0,1.0,-1.0,0.733620800206084]]</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>[[-35.899560866881444,22.513018335920655,-733.6843,0.0,0.0,0.0,1.0],[22.513018335920655,24.976199386641227,-733.6842,0.0,0.0,0.0,1.0],[24.976199386641227,27.439380437361798,0.0,0.0,8.0,4.0,-1.0],[27.439380437361798,27.791263444607594,227.85,0.0,8.0,4.0,-1.0],[27.791263444607594,69.3134582996115,1860.0,0.0,9.0,3.0,-1.0]]</t>
+          <t>[[-35.899560866881444,22.513018335920655,-733.6843,0.0,0.0,0.0,1.0,1.0000000063411505],[22.513018335920655,24.976199386641227,-733.6842,0.0,0.0,0.0,1.0,1.000000000618259],[24.976199386641227,27.439380437361798,0.0,0.0,8.0,4.0,-1.0,0.9580120494134396],[27.439380437361798,27.791263444607594,227.85,0.0,8.0,4.0,-1.0,0.9435637298192735],[27.791263444607594,69.3134582996115,1860.0,0.0,9.0,3.0,-1.0,0.8400665833386141]]</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -9680,7 +9680,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>[[-36.35540769670765,25.70999824884094,0.0,0.0,0.0,1.0,1.0],[25.70999824884094,27.136789190117916,890.0,0.0,8.0,2.0,-1.0],[27.136789190117916,70.29721516374654,1860.0,0.0,9.0,1.0,-1.0]]</t>
+          <t>[[-36.35540769670765,25.70999824884094,0.0,0.0,0.0,1.0,1.0,1.00000000634115],[25.70999824884094,27.136789190117916,890.0,0.0,8.0,2.0,-1.0,0.943563734939755],[27.136789190117916,70.29721516374654,1860.0,0.0,9.0,1.0,-1.0,0.8820545402663245]]</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>[[-35.37240980614478,25.66321239270355,0.0,0.0,0.0,1.0,1.0],[25.66321239270355,26.703592316547557,890.0,0.0,8.0,1.0,-1.0],[26.703592316547557,68.31878927030778,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[-35.37240980614478,25.66321239270355,0.0,0.0,0.0,1.0,1.0,1.00000000634115],[25.66321239270355,26.703592316547557,890.0,0.0,8.0,1.0,-1.0,0.943563734939755],[26.703592316547557,68.31878927030778,1860.0,0.0,8.0,1.0,-1.0,0.8820545402663245]]</t>
         </is>
       </c>
       <c r="C357" t="n">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>[[-38.33005939867277,22.635108349781014,-1860.0,1.0,8.0,1.0,-1.0],[22.635108349781014,23.76409293771534,-1074.7921,0.0,8.0,2.0,-1.0],[23.76409293771534,26.398390309562117,0.0,0.0,7.0,3.0,-1.0],[26.398390309562117,26.77471850554022,890.0001,0.0,7.0,3.0,-1.0],[26.77471850554022,74.19207119878206,1860.0,0.0,7.0,3.0,-1.0]]</t>
+          <t>[[-38.33005939867277,22.635108349781014,-1860.0,1.0,8.0,1.0,-1.0,0.988500323398855],[22.635108349781014,23.76409293771534,-1074.7921,0.0,8.0,2.0,-1.0,0.943563726712108],[23.76409293771534,26.398390309562117,0.0,0.0,7.0,3.0,-1.0,0.8820545402663249],[26.398390309562117,26.77471850554022,890.0001,0.0,7.0,3.0,-1.0,0.8256182625237758],[26.77471850554022,74.19207119878206,1860.0,0.0,7.0,3.0,-1.0,0.7641090741914993]]</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>[[-39.55687029096041,23.136019377474653,-1860.0,1.0,7.0,0.0,-1.0],[23.136019377474653,23.525416207713384,-1074.7921,0.0,7.0,1.0,-1.0],[23.525416207713384,26.251194019384478,0.0,0.0,6.0,2.0,-1.0],[26.251194019384478,76.87278195041901,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[-39.55687029096041,23.136019377474653,-1860.0,1.0,7.0,0.0,-1.0,0.8705548573240294],[23.136019377474653,23.525416207713384,-1074.7921,0.0,7.0,1.0,-1.0,0.8256182606372824],[23.525416207713384,26.251194019384478,0.0,0.0,6.0,2.0,-1.0,0.7641090741914993],[26.251194019384478,76.87278195041901,1860.0,0.0,6.0,1.0,-1.0,0.6461636081166737]]</t>
         </is>
       </c>
       <c r="C359" t="n">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>[[-37.26611296139012,23.070789861471688,-1860.0,1.0,6.0,1.0,-1.0],[23.070789861471688,23.80214625932456,-1074.7921,0.0,6.0,1.0,-1.0],[23.80214625932456,26.36189365180961,0.0,0.0,5.0,2.0,-1.0],[26.36189365180961,72.071668517614,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[-37.26611296139012,23.070789861471688,-1860.0,1.0,6.0,1.0,-1.0,0.7526093912492038],[23.070789861471688,23.80214625932456,-1074.7921,0.0,6.0,1.0,-1.0,0.7076727945624568],[23.80214625932456,26.36189365180961,0.0,0.0,5.0,2.0,-1.0,0.6461636081166737],[26.36189365180961,72.071668517614,1860.0,0.0,5.0,1.0,-1.0,0.5282181420418481]]</t>
         </is>
       </c>
       <c r="C360" t="n">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>[[-39.313787927702336,23.276053214456105,-1860.0,1.0,5.0,1.0,-1.0],[23.276053214456105,24.0487673026309,-1074.7921,0.0,5.0,2.0,-1.0],[24.0487673026309,26.36690956715529,0.0,0.0,4.0,3.0,-1.0],[26.36690956715529,26.753266611242694,890.0001,0.0,4.0,3.0,-1.0],[26.753266611242694,76.2069682544296,1860.0,0.0,4.0,3.0,-1.0]]</t>
+          <t>[[-39.313787927702336,23.276053214456105,-1860.0,1.0,5.0,1.0,-1.0,0.6346639251743782],[23.276053214456105,24.0487673026309,-1074.7921,0.0,5.0,2.0,-1.0,0.5897273284876312],[24.0487673026309,26.36690956715529,0.0,0.0,4.0,3.0,-1.0,0.5282181420418481],[26.36690956715529,26.753266611242694,890.0001,0.0,4.0,3.0,-1.0,0.47178186429929897],[26.753266611242694,76.2069682544296,1860.0,0.0,4.0,3.0,-1.0,0.4102726759670225]]</t>
         </is>
       </c>
       <c r="C361" t="n">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>[[-44.50115975465715,22.57868985920672,-1860.0,1.0,4.0,0.0,-1.0],[22.57868985920672,23.455550638472914,-1074.7921,0.0,4.0,0.0,-1.0],[23.455550638472914,26.0861329762715,0.0,0.0,3.0,1.0,-1.0],[26.0861329762715,86.58952674563892,1860.0,0.0,3.0,1.0,-1.0]]</t>
+          <t>[[-44.50115975465715,22.57868985920672,-1860.0,1.0,4.0,0.0,-1.0,0.5167184590995526],[22.57868985920672,23.455550638472914,-1074.7921,0.0,4.0,0.0,-1.0,0.4717818624128056],[23.455550638472914,26.0861329762715,0.0,0.0,3.0,1.0,-1.0,0.4102726759670225],[26.0861329762715,86.58952674563892,1860.0,0.0,3.0,1.0,-1.0,0.29232720989219685]]</t>
         </is>
       </c>
       <c r="C362" t="n">
@@ -9862,7 +9862,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>[[-46.71440595727711,23.33576313369703,-1860.0,1.0,3.0,1.0,-1.0],[23.33576313369703,23.79661950929554,-1074.7921,0.0,3.0,2.0,-1.0],[23.79661950929554,26.56175776288663,0.0,0.0,2.0,3.0,-1.0],[26.56175776288663,91.0816503466786,1860.0,0.0,2.0,3.0,-1.0]]</t>
+          <t>[[-46.71440595727711,23.33576313369703,-1860.0,1.0,3.0,1.0,-1.0,0.3987729930247269],[23.33576313369703,23.79661950929554,-1074.7921,0.0,3.0,2.0,-1.0,0.3538363963379799],[23.79661950929554,26.56175776288663,0.0,0.0,2.0,3.0,-1.0,0.2923272098921968],[26.56175776288663,91.0816503466786,1860.0,0.0,2.0,3.0,-1.0,0.17438174381737115]]</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>[[-43.936894580154444,23.64682219299344,-1860.0,1.0,2.0,1.0,-1.0],[23.64682219299344,26.24619591503759,0.0,0.0,1.0,2.0,-1.0],[26.24619591503759,28.845569637081738,890.0001,0.0,1.0,1.0,-1.0],[28.845569637081738,85.59856256837901,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-43.936894580154444,23.64682219299344,-1860.0,1.0,2.0,1.0,-1.0,0.2808275269499013],[23.64682219299344,26.24619591503759,0.0,0.0,1.0,2.0,-1.0,0.1743817438173712],[26.24619591503759,28.845569637081738,890.0001,0.0,1.0,1.0,-1.0,0.11794546607482206],[28.845569637081738,85.59856256837901,1860.0,0.0,2.0,0.0,-1.0,0.056436277742545574]]</t>
         </is>
       </c>
       <c r="C364" t="n">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>[[-42.06470214378976,23.791685275115242,-1860.0,1.0,2.0,0.0,-1.0],[23.791685275115242,24.205876390957414,-1074.7921,0.0,2.0,0.0,-1.0],[24.205876390957414,26.691023086010432,0.0,0.0,1.0,1.0,-1.0],[26.691023086010432,28.347787549379106,890.0001,0.0,1.0,0.0,-1.0],[28.347787549379106,81.77844149301902,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-42.06470214378976,23.791685275115242,-1860.0,1.0,2.0,0.0,-1.0,0.2808275269499013],[23.791685275115242,24.205876390957414,-1074.7921,0.0,2.0,0.0,-1.0,0.23589093026315433],[24.205876390957414,26.691023086010432,0.0,0.0,1.0,1.0,-1.0,0.1743817438173712],[26.691023086010432,28.347787549379106,890.0001,0.0,1.0,0.0,-1.0,0.11794546607482206],[28.347787549379106,81.77844149301902,1860.0,0.0,1.0,0.0,-1.0,0.056436277742545574]]</t>
         </is>
       </c>
       <c r="C365" t="n">
@@ -9940,7 +9940,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>[[-43.628766035987994,14.370722217997397,-1860.0,10.0,2.0,0.0,1.0],[14.370722217997397,15.659599734752625,-1808.4763,9.0,2.0,1.0,1.0],[15.659599734752625,23.392864835284016,-1074.7921,0.0,2.0,0.0,-1.0],[23.392864835284016,25.970619868794472,0.0,0.0,1.0,1.0,-1.0],[25.970619868794472,26.829871546631296,890.0001,0.0,1.0,1.0,-1.0],[26.829871546631296,84.82935980061669,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[-43.628766035987994,14.370722217997397,-1860.0,10.0,2.0,0.0,1.0,0.2808275269499013],[14.370722217997397,15.659599734752625,-1808.4763,9.0,2.0,1.0,1.0,0.2778788814679736],[15.659599734752625,23.392864835284016,-1074.7921,0.0,2.0,0.0,-1.0,0.23589093026315433],[23.392864835284016,25.970619868794472,0.0,0.0,1.0,1.0,-1.0,0.1743817438173712],[25.970619868794472,26.829871546631296,890.0001,0.0,1.0,1.0,-1.0,0.11794546607482206],[26.829871546631296,84.82935980061669,1860.0,0.0,1.0,1.0,-1.0,0.056436277742545574]]</t>
         </is>
       </c>
       <c r="C366" t="n">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>[[-43.95798917388249,14.484743220733584,-1860.0,10.0,1.0,0.0,1.0],[14.484743220733584,15.783470607280606,-1808.4763,9.0,1.0,1.0,1.0],[15.783470607280606,22.710016668864732,-1074.7921,0.0,1.0,0.0,-1.0],[22.710016668864732,25.30747144195879,0.0,0.0,0.0,1.0,-1.0],[25.30747144195879,27.904926215052832,890.0001,0.0,0.0,0.0,-1.0],[27.904926215052832,85.48184035197089,890.0002,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-43.95798917388249,14.484743220733584,-1860.0,10.0,1.0,0.0,1.0,0.16288206087507567],[14.484743220733584,15.783470607280606,-1808.4763,9.0,1.0,1.0,1.0,0.15993341539314798],[15.783470607280606,22.710016668864732,-1074.7921,0.0,1.0,0.0,-1.0,0.11794546418832869],[22.710016668864732,25.30747144195879,0.0,0.0,0.0,1.0,-1.0,0.05643627774254557],[25.30747144195879,27.904926215052832,890.0001,0.0,0.0,0.0,-1.0,-3.58046925441613e-15],[27.904926215052832,85.48184035197089,890.0002,0.0,0.0,0.0,-1.0,-6.3411576683991555e-09]]</t>
         </is>
       </c>
       <c r="C367" t="n">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="F367" s="4" t="inlineStr">
         <is>
-          <t>[1.2987273865,6.9265460616,0,0,0]</t>
+          <t>[1.2987273865,6.9265460616,2.5974547731,0,0]</t>
         </is>
       </c>
     </row>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>[[-44.977565684158776,14.893482520809393,-1860.0,10.0,0.0,0.0,1.0],[14.893482520809393,16.6674395046603,-733.6842,9.0,0.0,1.0,1.0],[16.6674395046603,87.62571885869666,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-44.977565684158776,14.893482520809393,-1860.0,10.0,0.0,0.0,1.0,0.10644578313252653],[14.893482520809393,16.6674395046603,-733.6842,9.0,0.0,1.0,1.0,0.0419879512048157],[16.6674395046603,87.62571885869666,0.0,0.0,0.0,1.0,-1.0,-3.573530360512223e-15]]</t>
         </is>
       </c>
       <c r="C368" t="n">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>[[-42.88606481539113,12.863781659998757,-1860.0,9.0,0.0,0.0,1.0],[12.863781659998757,17.93194952139784,-733.6842,9.0,0.0,0.0,1.0],[17.93194952139784,83.39578439780263,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-42.88606481539113,12.863781659998757,-1860.0,9.0,0.0,0.0,1.0,0.10644578313252653],[12.863781659998757,17.93194952139784,-733.6842,9.0,0.0,0.0,1.0,0.0419879512048157],[17.93194952139784,83.39578439780263,0.0,0.0,0.0,1.0,-1.0,-3.573530360512223e-15]]</t>
         </is>
       </c>
       <c r="C369" t="n">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>[[-43.43428050521803,18.17863324931909,-1860.0,7.0,0.0,0.0,1.0],[18.17863324931909,28.87531966503734,0.0,9.0,0.0,1.0,1.0],[28.87531966503734,84.49808902677223,662.1501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-43.43428050521803,18.17863324931909,-1860.0,7.0,0.0,0.0,1.0,0.1484337343373458],[18.17863324931909,28.87531966503734,0.0,9.0,0.0,1.0,1.0,0.0419879512048157],[28.87531966503734,84.49808902677223,662.1501,0.0,0.0,0.0,-1.0,-6.943567297523767e-09]]</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>[[-44.26762358060652,18.15259424276804,-1860.0,7.0,0.0,0.0,1.0],[18.15259424276804,29.501724756108864,0.0,8.0,0.0,1.0,1.0],[29.501724756108864,86.247377322813,1860.0,8.0,8.0,0.0,-1.0]]</t>
+          <t>[[-44.26762358060652,18.15259424276804,-1860.0,7.0,0.0,0.0,1.0,0.2548795174698759],[18.15259424276804,29.501724756108864,0.0,8.0,0.0,1.0,1.0,0.1484337343373458],[29.501724756108864,86.247377322813,1860.0,8.0,8.0,0.0,-1.0,0.03048826826252017]]</t>
         </is>
       </c>
       <c r="C371" t="n">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>[[-43.37304157686134,17.732484042105213,-1860.0,5.0,0.0,0.0,1.0],[17.732484042105213,30.12451371308444,0.0,7.0,0.0,1.0,1.0],[30.12451371308444,84.39305744461419,1860.0,7.0,8.0,1.0,-1.0]]</t>
+          <t>[[-43.37304157686134,17.732484042105213,-1860.0,5.0,0.0,0.0,1.0,0.36132530060240603],[17.732484042105213,30.12451371308444,0.0,7.0,0.0,1.0,1.0,0.2548795174698759],[30.12451371308444,84.39305744461419,1860.0,7.0,8.0,1.0,-1.0,0.13693405139505027]]</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>[[-43.85436521725654,17.510380652029177,-1860.0,4.0,0.0,0.0,1.0],[17.510380652029177,29.178325289146883,0.0,4.0,0.0,1.0,1.0],[29.178325289146883,30.474763582159966,890.0,4.0,8.0,1.0,-1.0],[30.474763582159966,85.35731798638028,1860.0,6.0,8.0,1.0,-1.0]]</t>
+          <t>[[-43.85436521725654,17.510380652029177,-1860.0,4.0,0.0,0.0,1.0,0.4677710837349361],[17.510380652029177,29.178325289146883,0.0,4.0,0.0,1.0,1.0,0.361325300602406],[29.178325289146883,30.474763582159966,890.0,4.0,8.0,1.0,-1.0,0.3048890292010109],[30.474763582159966,85.35731798638028,1860.0,6.0,8.0,1.0,-1.0,0.24337983452758033]]</t>
         </is>
       </c>
       <c r="C373" t="n">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>[[-43.67579502387214,17.403888582314437,-1860.0,3.0,0.0,0.0,1.0],[17.403888582314437,29.354261461785725,0.0,4.0,0.0,1.0,1.0],[29.354261461785725,31.124687073559244,890.0,4.0,8.0,0.0,-1.0],[31.124687073559244,88.6635194561988,1860.0,5.0,8.0,0.0,-1.0]]</t>
+          <t>[[-43.67579502387214,17.403888582314437,-1860.0,3.0,0.0,0.0,1.0,0.5742168668674662],[17.403888582314437,29.354261461785725,0.0,4.0,0.0,1.0,1.0,0.4677710837349361],[29.354261461785725,31.124687073559244,890.0,4.0,8.0,0.0,-1.0,0.411334812333541],[31.124687073559244,88.6635194561988,1860.0,5.0,8.0,0.0,-1.0,0.34982561766011044]]</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>[[-44.29522378114965,17.406137674052808,-1860.0,3.0,0.0,0.0,1.0],[17.406137674052808,28.26905342320817,0.0,3.0,0.0,1.0,1.0],[28.26905342320817,30.00711994307303,890.0,3.0,8.0,0.0,-1.0],[30.00711994307303,85.62524857874848,1860.0,3.0,8.0,0.0,-1.0]]</t>
+          <t>[[-44.29522378114965,17.406137674052808,-1860.0,3.0,0.0,0.0,1.0,0.6806626499999964],[17.406137674052808,28.26905342320817,0.0,3.0,0.0,1.0,1.0,0.5742168668674663],[28.26905342320817,30.00711994307303,890.0,3.0,8.0,0.0,-1.0,0.5177805954660712],[30.00711994307303,85.62524857874848,1860.0,3.0,8.0,0.0,-1.0,0.45627140079264067]]</t>
         </is>
       </c>
       <c r="C375" t="n">
@@ -10200,7 +10200,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>[[-48.440815679714234,17.774865169166546,-1860.0,3.0,0.0,0.0,1.0],[17.774865169166546,30.020230805603404,0.0,2.0,0.0,1.0,1.0],[30.020230805603404,30.92729492682095,890.0,2.0,8.0,1.0,-1.0],[30.92729492682095,87.16527044230872,1860.0,2.0,8.0,1.0,-1.0]]</t>
+          <t>[[-48.440815679714234,17.774865169166546,-1860.0,3.0,0.0,0.0,1.0,0.7871084331325264],[17.774865169166546,30.020230805603404,0.0,2.0,0.0,1.0,1.0,0.6806626499999964],[30.020230805603404,30.92729492682095,890.0,2.0,8.0,1.0,-1.0,0.6242263785986013],[30.92729492682095,87.16527044230872,1860.0,2.0,8.0,1.0,-1.0,0.5627171839251708]]</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>[[-50.02880273275703,17.926761280803504,-1860.0,1.0,0.0,0.0,1.0],[17.926761280803504,28.308861338430816,0.0,2.0,0.0,1.0,1.0],[28.308861338430816,29.252688616396924,890.0,2.0,8.0,0.0,-1.0],[29.252688616396924,91.0733753231777,1860.0,2.0,8.0,0.0,-1.0]]</t>
+          <t>[[-50.02880273275703,17.926761280803504,-1860.0,1.0,0.0,0.0,1.0,0.8935542162650565],[17.926761280803504,28.308861338430816,0.0,2.0,0.0,1.0,1.0,0.7871084331325264],[28.308861338430816,29.252688616396924,890.0,2.0,8.0,0.0,-1.0,0.7306721617311314],[29.252688616396924,91.0733753231777,1860.0,2.0,8.0,0.0,-1.0,0.6691629670577008]]</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>[[-49.08479838724948,18.04840042822886,-1860.0,1.0,0.0,0.0,1.0],[18.04840042822886,28.69711472309784,0.0,1.0,0.0,1.0,1.0],[28.69711472309784,29.623089879173392,890.0,1.0,8.0,1.0,-1.0],[29.623089879173392,89.34848744604723,1860.0,1.0,8.0,1.0,-1.0]]</t>
+          <t>[[-49.08479838724948,18.04840042822886,-1860.0,1.0,0.0,0.0,1.0,0.9999999993975865],[18.04840042822886,28.69711472309784,0.0,1.0,0.0,1.0,1.0,0.8935542162650565],[28.69711472309784,29.623089879173392,890.0,1.0,8.0,1.0,-1.0,0.8371179448636614],[29.623089879173392,89.34848744604723,1860.0,1.0,8.0,1.0,-1.0,0.7756087501902309]]</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>[[-48.461428716525944,29.445410866342286,0.0,0.0,0.0,1.0,1.0],[29.445410866342286,86.96964706997173,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[-48.461428716525944,29.445410866342286,0.0,0.0,0.0,1.0,1.0,0.9999999993975865],[29.445410866342286,86.96964706997173,1860.0,0.0,8.0,1.0,-1.0,0.882054533322761]]</t>
         </is>
       </c>
       <c r="C379" t="n">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>[[-47.616355059475936,27.887417503400272,0.0,0.0,0.0,1.0,1.0],[27.887417503400272,28.334185388387695,708.65,1.0,9.0,3.0,-1.0],[28.334185388387695,29.674489043349993,890.0,0.0,8.0,0.0,-1.0],[29.674489043349993,85.96724255176656,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-47.616355059475936,27.887417503400272,0.0,0.0,0.0,1.0,1.0,0.9999999993975865],[27.887417503400272,28.334185388387695,708.65,1.0,9.0,3.0,-1.0,0.955063410938487],[28.334185388387695,29.674489043349993,890.0,0.0,8.0,0.0,-1.0,0.9435637279961915],[29.674489043349993,85.96724255176656,1860.0,0.0,8.0,0.0,-1.0,0.882054533322761]]</t>
         </is>
       </c>
       <c r="C380" t="n">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>[[-49.97444593742551,23.81317338296065,-1860.0,2.0,10.0,0.0,-1.0],[23.81317338296065,24.753143055831806,-1476.6759,2.0,10.0,0.0,-1.0],[24.753143055831806,27.573052074445293,0.0,2.0,9.0,1.0,-1.0],[27.573052074445293,28.043036910880865,527.3,2.0,9.0,1.0,-1.0],[28.043036910880865,29.452991420187608,890.0,0.0,7.0,0.0,-1.0],[29.452991420187608,90.5510201568131,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-49.97444593742551,23.81317338296065,-1860.0,2.0,10.0,0.0,-1.0,0.988500316455291],[23.81317338296065,24.753143055831806,-1476.6759,2.0,10.0,0.0,-1.0,0.9665630938649297],[24.753143055831806,27.573052074445293,0.0,2.0,9.0,1.0,-1.0,0.882054533322761],[27.573052074445293,28.043036910880865,527.3,2.0,9.0,1.0,-1.0,0.848617627805957],[28.043036910880865,29.452991420187608,890.0,0.0,7.0,0.0,-1.0,0.8256182619213659],[29.452991420187608,90.5510201568131,1860.0,0.0,7.0,0.0,-1.0,0.7641090672479354]]</t>
         </is>
       </c>
       <c r="C381" t="n">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>[[-49.744856007796166,23.958590586287023,-1860.0,2.0,9.0,0.0,-1.0],[23.958590586287023,25.358023116554413,-1476.6759,2.0,9.0,0.0,-1.0],[25.358023116554413,28.156888177089222,0.0,2.0,8.0,1.0,-1.0],[28.156888177089222,28.623365687178357,890.0,0.0,6.0,0.0,-1.0],[28.623365687178357,89.73191950885493,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[-49.744856007796166,23.958590586287023,-1860.0,2.0,9.0,0.0,-1.0,0.8705548503804654],[23.958590586287023,25.358023116554413,-1476.6759,2.0,9.0,0.0,-1.0,0.8486176277901041],[25.358023116554413,28.156888177089222,0.0,2.0,8.0,1.0,-1.0,0.7641090672479354],[28.156888177089222,28.623365687178357,890.0,0.0,6.0,0.0,-1.0,0.7076727958465403],[28.623365687178357,89.73191950885493,1860.0,0.0,6.0,0.0,-1.0,0.6461636011731098]]</t>
         </is>
       </c>
       <c r="C382" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>[[-48.28957801826318,24.757605647598133,-1860.0,2.0,8.0,0.0,-1.0],[24.757605647598133,25.211314862914044,-1476.6759,2.0,8.0,0.0,-1.0],[25.211314862914044,27.933570154809495,0.0,2.0,7.0,1.0,-1.0],[27.933570154809495,29.748407016073138,890.0,0.0,5.0,0.0,-1.0],[29.748407016073138,87.36947736119356,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-48.28957801826318,24.757605647598133,-1860.0,2.0,8.0,0.0,-1.0,0.7526093843056398],[24.757605647598133,25.211314862914044,-1476.6759,2.0,8.0,0.0,-1.0,0.7306721617152785],[25.211314862914044,27.933570154809495,0.0,2.0,7.0,1.0,-1.0,0.6461636011731098],[27.933570154809495,29.748407016073138,890.0,0.0,5.0,0.0,-1.0,0.5897273297717147],[29.748407016073138,87.36947736119356,1860.0,0.0,5.0,0.0,-1.0,0.5282181350982842]]</t>
         </is>
       </c>
       <c r="C383" t="n">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>[[-47.92515782066425,23.92656721549932,-1860.0,2.0,7.0,0.0,-1.0],[23.92656721549932,24.375640496975336,-401.8837,2.0,7.0,0.0,-1.0],[24.375640496975336,27.070080185831472,0.0,2.0,6.0,1.0,-1.0],[27.070080185831472,28.866373311735558,1497.3,2.0,6.0,1.0,-1.0],[28.866373311735558,86.34775334066642,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-47.92515782066425,23.92656721549932,-1860.0,2.0,7.0,0.0,-1.0,0.6961731129042448],[23.92656721549932,24.375640496975336,-401.8837,2.0,7.0,0.0,-1.0,0.6127266981452086],[24.375640496975336,27.070080185831472,0.0,2.0,6.0,1.0,-1.0,0.5897273297717147],[27.070080185831472,28.866373311735558,1497.3,2.0,6.0,1.0,-1.0,0.4947812295814801],[28.866373311735558,86.34775334066642,1860.0,0.0,5.0,0.0,-1.0,0.47178186369688907]]</t>
         </is>
       </c>
       <c r="C384" t="n">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>[[-49.41637819090349,22.85504451806679,-1860.0,2.0,5.0,1.0,-1.0],[22.85504451806679,25.17143627155943,-200.9418,1.0,5.0,2.0,-1.0],[25.17143627155943,27.951106375750584,0.0,1.0,5.0,2.0,-1.0],[27.951106375750584,28.414384726449114,1497.3,2.0,5.0,1.0,-1.0],[28.414384726449114,89.10384866795621,1860.0,1.0,4.0,0.0,-1.0]]</t>
+          <t>[[-49.41637819090349,22.85504451806679,-1860.0,2.0,5.0,1.0,-1.0,0.5782276468294192],[22.85504451806679,25.17143627155943,-200.9418,1.0,5.0,2.0,-1.0,0.48328154502219034],[25.17143627155943,27.951106375750584,0.0,1.0,5.0,2.0,-1.0,0.4717818636968891],[27.951106375750584,28.414384726449114,1497.3,2.0,5.0,1.0,-1.0,0.3768357635066545],[28.414384726449114,89.10384866795621,1860.0,1.0,4.0,0.0,-1.0,0.3538363976220635]]</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>[[-49.914634163825305,24.247644570693062,-1860.0,2.0,5.0,0.0,-1.0],[24.247644570693062,24.717026081671015,-401.8837,2.0,5.0,0.0,-1.0],[24.717026081671015,27.06393363656084,0.0,2.0,4.0,1.0,-1.0],[27.06393363656084,28.002696658516776,1497.3,2.0,4.0,1.0,-1.0],[28.002696658516776,90.43043761858604,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-49.914634163825305,24.247644570693062,-1860.0,2.0,5.0,0.0,-1.0,0.46028218075459354],[24.247644570693062,24.717026081671015,-401.8837,2.0,5.0,0.0,-1.0,0.3768357659955574],[24.717026081671015,27.06393363656084,0.0,2.0,4.0,1.0,-1.0,0.3538363976220634],[27.06393363656084,28.002696658516776,1497.3,2.0,4.0,1.0,-1.0,0.2588902974318288],[28.002696658516776,90.43043761858604,1860.0,0.0,3.0,0.0,-1.0,0.23589093154723778]]</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>[[-45.795981233492824,24.480465352236735,-1860.0,2.0,4.0,0.0,-1.0],[24.480465352236735,27.051554861470734,0.0,2.0,3.0,1.0,-1.0],[27.051554861470734,82.32997931000189,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-45.795981233492824,24.480465352236735,-1860.0,2.0,4.0,0.0,-1.0,0.3423367146797679],[24.480465352236735,27.051554861470734,0.0,2.0,3.0,1.0,-1.0,0.2358909315472378],[27.051554861470734,82.32997931000189,1860.0,0.0,2.0,0.0,-1.0,0.11794546547241218]]</t>
         </is>
       </c>
       <c r="C387" t="n">
@@ -10512,7 +10512,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>[[-41.984310362120574,23.813084683045467,-1860.0,2.0,2.0,2.0,-1.0],[23.813084683045467,24.988038165994872,-200.9418,1.0,2.0,2.0,-1.0],[24.988038165994872,27.729596292876785,0.0,1.0,2.0,2.0,-1.0],[27.729596292876785,75.11938677183568,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-41.984310362120574,23.813084683045467,-1860.0,2.0,2.0,2.0,-1.0,0.2243912486049423],[23.813084683045467,24.988038165994872,-200.9418,1.0,2.0,2.0,-1.0,0.1294451467977134],[24.988038165994872,27.729596292876785,0.0,1.0,2.0,2.0,-1.0,0.1179454654724122],[27.729596292876785,75.11938677183568,1860.0,0.0,1.0,0.0,-1.0,-6.024134246995771e-10]]</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>[[-41.3949683533736,25.769622824552428,-1860.0,2.0,1.0,1.0,-1.0],[25.769622824552428,26.92101581617402,-200.9418,1.0,1.0,2.0,-1.0],[26.92101581617402,73.36053314491144,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-41.3949683533736,25.769622824552428,-1860.0,2.0,1.0,1.0,-1.0,0.10644578253011663],[25.769622824552428,26.92101581617402,-200.9418,1.0,1.0,2.0,-1.0,0.011499680722887725],[26.92101581617402,73.36053314491144,0.0,0.0,0.0,1.0,-1.0,-6.024134802107284e-10]]</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -10564,7 +10564,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>[[-41.37949541823291,22.771032583157385,-1860.0,1.0,2.0,0.0,-1.0],[22.771032583157385,24.691707074216986,-401.8837,1.0,2.0,0.0,-1.0],[24.691707074216986,27.38065136170041,0.0,1.0,1.0,1.0,-1.0],[27.38065136170041,30.453730547395743,1497.3,1.0,1.0,1.0,-1.0],[30.453730547395743,73.47683914713056,1678.6501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-41.37949541823291,22.771032583157385,-1860.0,1.0,2.0,0.0,-1.0,0.21289156566264672],[22.771032583157385,24.691707074216986,-401.8837,1.0,2.0,0.0,-1.0,0.12944515090361058],[24.691707074216986,27.38065136170041,0.0,1.0,1.0,1.0,-1.0,0.1064457825301166],[27.38065136170041,30.453730547395743,1497.3,1.0,1.0,1.0,-1.0,0.01149968233988198],[30.453730547395743,73.47683914713056,1678.6501,0.0,0.0,0.0,-1.0,-6.943567609773993e-09]]</t>
         </is>
       </c>
       <c r="C390" t="n">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>[[-42.77422500095992,22.85148058104614,-1860.0,2.0,1.0,0.0,-1.0],[22.85148058104614,32.79476930559252,0.0,1.0,1.0,1.0,-1.0],[32.79476930559252,36.3743532464292,0.0,1.0,0.0,1.0,-1.0],[36.3743532464292,76.1475081446147,181.35,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-42.77422500095992,22.85148058104614,-1860.0,2.0,1.0,0.0,-1.0,0.11794546547241212],[22.85148058104614,32.79476930559252,0.0,1.0,1.0,1.0,-1.0,0.01149968233988201],[32.79476930559252,36.3743532464292,0.0,1.0,0.0,1.0,-1.0,0.01149968233988201],[36.3743532464292,76.1475081446147,181.35,0.0,0.0,0.0,-1.0,-6.024134871496223e-10]]</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>[[-44.051359369577796,33.74226523045988,-1860.0,1.0,0.0,0.0,-1.0],[33.74226523045988,37.42722639572483,0.0,0.0,0.0,1.0,-1.0],[37.42722639572483,78.37123934311307,181.35,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-44.051359369577796,33.74226523045988,-1860.0,1.0,0.0,0.0,-1.0,0.11794546547241212],[33.74226523045988,37.42722639572483,0.0,0.0,0.0,1.0,-1.0,0.01149968233988201],[37.42722639572483,78.37123934311307,181.35,0.0,0.0,0.0,-1.0,-6.024134871496223e-10]]</t>
         </is>
       </c>
       <c r="C392" t="n">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="F392" s="4" t="inlineStr">
         <is>
-          <t>[0,0,0,0,0]</t>
+          <t>[0,0,3.6849611653,0,0]</t>
         </is>
       </c>
     </row>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>[[-42.19536113656463,10.731200725348465,-1860.0,9.0,1.0,0.0,1.0],[10.731200725348465,16.611929821116583,-733.6842,9.0,1.0,0.0,1.0],[16.611929821116583,23.27675612965379,0.0,0.0,1.0,1.0,-1.0],[23.27675612965379,25.62904776796104,0.0,0.0,0.0,1.0,-1.0],[25.62904776796104,28.373388012652825,1860.0,0.0,0.0,0.0,-1.0],[28.373388012652825,75.02717217241326,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-42.19536113656463,10.731200725348465,-1860.0,9.0,1.0,0.0,1.0,0.2243912486049422],[10.731200725348465,16.611929821116583,-733.6842,9.0,1.0,0.0,1.0,0.15993341667723138],[16.611929821116583,23.27675612965379,0.0,0.0,1.0,1.0,-1.0,0.1179454654724121],[23.27675612965379,25.62904776796104,0.0,0.0,0.0,1.0,-1.0,0.1179454654724121],[25.62904776796104,28.373388012652825,1860.0,0.0,0.0,0.0,-1.0,-6.024135357218796e-10],[28.373388012652825,75.02717217241326,1860.0,0.0,1.0,0.0,-1.0,-6.024135357218796e-10]]</t>
         </is>
       </c>
       <c r="C393" t="n">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="F393" s="4" t="inlineStr">
         <is>
-          <t>[5.8807290958,0,6.6648263085,0,0]</t>
+          <t>[5.8807290958,0,9.0171179468,0,0]</t>
         </is>
       </c>
     </row>
@@ -10668,7 +10668,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>[[-38.896672878861665,11.45648100486546,-1860.0,9.0,0.0,0.0,1.0],[11.45648100486546,16.979084979209723,-733.6842,9.0,0.0,0.0,1.0],[16.979084979209723,58.236185258134526,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-38.896672878861665,11.45648100486546,-1860.0,9.0,0.0,0.0,1.0,0.1064457825301166],[11.45648100486546,16.979084979209723,-733.6842,9.0,0.0,0.0,1.0,0.04198795060240577],[16.979084979209723,58.236185258134526,0.0,0.0,0.0,1.0,-1.0,-6.02413507966304e-10]]</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -10694,7 +10694,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>[[-60.85244892969504,16.727937912220938,-1860.0,9.0,8.0,3.0,-1.0],[16.727937912220938,73.23157225951235,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-60.85244892969504,16.727937912220938,-1860.0,9.0,8.0,3.0,-1.0,0.1064457825301166],[16.727937912220938,73.23157225951235,0.0,0.0,0.0,1.0,-1.0,-6.02413507966304e-10]]</t>
         </is>
       </c>
       <c r="C395" t="n">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>[[-72.12706908047414,16.804208607744172,-1860.0,8.0,9.0,2.0,-1.0],[16.804208607744172,17.295541633645925,-1808.4765,8.0,9.0,2.0,-1.0],[17.295541633645925,19.260873737252965,0.0,7.0,9.0,2.0,-1.0],[19.260873737252965,74.7815056641517,1678.6501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-72.12706908047414,16.804208607744172,-1860.0,8.0,9.0,2.0,-1.0,0.21289156566264672],[16.804208607744172,17.295541633645925,-1808.4765,8.0,9.0,2.0,-1.0,0.20994293162650213],[17.295541633645925,19.260873737252965,0.0,7.0,9.0,2.0,-1.0,0.1064457825301166],[19.260873737252965,74.7815056641517,1678.6501,0.0,0.0,0.0,-1.0,-6.943567609773993e-09]]</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>[[-76.740559208982,17.00812884225988,-1860.0,7.0,9.0,3.0,-1.0],[17.00812884225988,19.126743261496983,0.0,6.0,8.0,4.0,-1.0],[19.126743261496983,81.62586862899155,1860.0,7.0,9.0,2.0,-1.0]]</t>
+          <t>[[-76.740559208982,17.00812884225988,-1860.0,7.0,9.0,3.0,-1.0,0.31933734879517683],[17.00812884225988,19.126743261496983,0.0,6.0,8.0,4.0,-1.0,0.2128915656626467],[19.126743261496983,81.62586862899155,1860.0,7.0,9.0,2.0,-1.0,0.09494609958782106]]</t>
         </is>
       </c>
       <c r="C397" t="n">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>[[-84.30222317634846,15.845255007320986,-1860.0,6.0,0.0,0.0,1.0],[15.845255007320986,16.983294532135403,-733.6842,5.0,0.0,0.0,1.0],[16.983294532135403,19.25937358176425,0.0,5.0,8.0,3.0,-1.0],[19.25937358176425,19.828393344171474,227.85,5.0,8.0,3.0,-1.0],[19.828393344171474,85.83468578340813,1860.0,6.0,9.0,2.0,-1.0]]</t>
+          <t>[[-84.30222317634846,15.845255007320986,-1860.0,6.0,0.0,0.0,1.0,0.4257831319277069],[15.845255007320986,16.983294532135403,-733.6842,5.0,0.0,0.0,1.0,0.3613252999999961],[16.983294532135403,19.25937358176425,0.0,5.0,8.0,3.0,-1.0,0.3193373487951768],[19.25937358176425,19.828393344171474,227.85,5.0,8.0,3.0,-1.0,0.30488902920101063],[19.828393344171474,85.83468578340813,1860.0,6.0,9.0,2.0,-1.0,0.20139188272035113]]</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>[[-84.05531610496543,16.700478739052357,-1860.0,4.0,0.0,0.0,1.0],[16.700478739052357,18.379741986452643,0.0,4.0,8.0,3.0,-1.0],[18.379741986452643,19.499250818052843,227.85,4.0,8.0,3.0,-1.0],[19.499250818052843,83.31125421926413,1860.0,5.0,9.0,2.0,-1.0]]</t>
+          <t>[[-84.05531610496543,16.700478739052357,-1860.0,4.0,0.0,0.0,1.0,0.5322289150602371],[16.700478739052357,18.379741986452643,0.0,4.0,8.0,3.0,-1.0,0.4257831319277069],[18.379741986452643,19.499250818052843,227.85,4.0,8.0,3.0,-1.0,0.41133481233354074],[19.499250818052843,83.31125421926413,1860.0,5.0,9.0,2.0,-1.0,0.30783766585288125]]</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>[[-84.17136571412163,16.343638535462617,-1860.0,3.0,0.0,0.0,1.0],[16.343638535462617,17.460471916013546,-733.6842,3.0,0.0,0.0,1.0],[17.460471916013546,19.135721986839954,0.0,3.0,8.0,4.0,-1.0],[19.135721986839954,20.252555367390883,227.85,3.0,8.0,3.0,-1.0],[20.252555367390883,82.79522467824329,1860.0,3.0,9.0,2.0,-1.0]]</t>
+          <t>[[-84.17136571412163,16.343638535462617,-1860.0,3.0,0.0,0.0,1.0,0.6386746981927671],[16.343638535462617,17.460471916013546,-733.6842,3.0,0.0,0.0,1.0,0.5742168662650563],[17.460471916013546,19.135721986839954,0.0,3.0,8.0,4.0,-1.0,0.5322289150602371],[19.135721986839954,20.252555367390883,227.85,3.0,8.0,3.0,-1.0,0.5177805954660709],[20.252555367390883,82.79522467824329,1860.0,3.0,9.0,2.0,-1.0,0.4142834489854114]]</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -10850,7 +10850,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>[[-85.85315449925211,16.54861239406104,-1860.0,3.0,0.0,0.0,1.0],[16.54861239406104,18.849775695034367,0.0,2.0,9.0,2.0,-1.0],[18.849775695034367,86.15880224850424,1860.0,3.0,9.0,1.0,-1.0]]</t>
+          <t>[[-85.85315449925211,16.54861239406104,-1860.0,3.0,0.0,0.0,1.0,0.7451204813252972],[16.54861239406104,18.849775695034367,0.0,2.0,9.0,2.0,-1.0,0.6386746981927671],[18.849775695034367,86.15880224850424,1860.0,3.0,9.0,1.0,-1.0,0.5207292321179415]]</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -10876,7 +10876,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>[[-84.66456294678238,16.741165401921577,-1860.0,1.0,8.0,3.0,-1.0],[16.741165401921577,18.99462603189278,0.0,1.0,8.0,4.0,-1.0],[18.99462603189278,83.78161914356477,1860.0,2.0,8.0,3.0,-1.0]]</t>
+          <t>[[-84.66456294678238,16.741165401921577,-1860.0,1.0,8.0,3.0,-1.0,0.8515662644578272],[16.741165401921577,18.99462603189278,0.0,1.0,8.0,4.0,-1.0,0.7451204813252972],[18.99462603189278,83.78161914356477,1860.0,2.0,8.0,3.0,-1.0,0.6271750152504716]]</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>[[-83.39396338926025,16.716800010959616,-1860.0,1.0,0.0,0.0,1.0],[16.716800010959616,18.929192572290447,0.0,1.0,8.0,4.0,-1.0],[18.929192572290447,19.48229071262314,227.85,1.0,8.0,3.0,-1.0],[19.48229071262314,81.98238057021896,1860.0,1.0,9.0,2.0,-1.0]]</t>
+          <t>[[-83.39396338926025,16.716800010959616,-1860.0,1.0,0.0,0.0,1.0,0.9580120475903573],[16.716800010959616,18.929192572290447,0.0,1.0,8.0,4.0,-1.0,0.8515662644578272],[18.929192572290447,19.48229071262314,227.85,1.0,8.0,3.0,-1.0,0.8371179448636611],[19.48229071262314,81.98238057021896,1860.0,1.0,9.0,2.0,-1.0,0.7336207983830016]]</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>[[-85.88509706676096,16.8660304325132,-733.6843,0.0,0.0,0.0,1.0],[16.8660304325132,18.597791008343663,0.0,0.0,9.0,2.0,-1.0],[18.597791008343663,19.175044533620493,46.5,1.0,9.0,1.0,-1.0],[19.175044533620493,86.71370699100859,1860.0,1.0,9.0,1.0,-1.0]]</t>
+          <t>[[-85.88509706676096,16.8660304325132,-733.6843,0.0,0.0,0.0,1.0,1.0000000045180681],[16.8660304325132,18.597791008343663,0.0,0.0,9.0,2.0,-1.0,0.9580120475903573],[18.597791008343663,19.175044533620493,46.5,1.0,9.0,1.0,-1.0,0.9550634109384867],[19.175044533620493,86.71370699100859,1860.0,1.0,9.0,1.0,-1.0,0.8400665815155317]]</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -10954,7 +10954,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>[[-83.9856894235342,16.1939797193035,-733.6843,0.0,0.0,0.0,1.0],[16.1939797193035,17.863640871684126,0.0,0.0,8.0,2.0,-1.0],[17.863640871684126,18.420194589144344,227.85,0.0,8.0,2.0,-1.0],[18.420194589144344,82.42387209706841,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-83.9856894235342,16.1939797193035,-733.6843,0.0,0.0,0.0,1.0,1.0000000045180681],[16.1939797193035,17.863640871684126,0.0,0.0,8.0,2.0,-1.0,0.9580120475903573],[17.863640871684126,18.420194589144344,227.85,0.0,8.0,2.0,-1.0,0.9435637279961911],[18.420194589144344,82.42387209706841,1860.0,0.0,8.0,2.0,-1.0,0.8400665815155317]]</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>[[-86.93009382409059,16.249995175103237,-1860.0,1.0,8.0,1.0,-1.0],[16.249995175103237,16.83959568367007,-1808.4765,0.0,8.0,2.0,-1.0],[16.83959568367007,18.608397209370523,0.0,0.0,7.0,3.0,-1.0],[18.608397209370523,89.36045823738917,1860.0,0.0,7.0,3.0,-1.0]]</t>
+          <t>[[-86.93009382409059,16.249995175103237,-1860.0,1.0,8.0,1.0,-1.0,0.9465123646480618],[16.249995175103237,16.83959568367007,-1808.4765,0.0,8.0,2.0,-1.0,0.9435637306119172],[16.83959568367007,18.608397209370523,0.0,0.0,7.0,3.0,-1.0,0.8400665815155317],[18.608397209370523,89.36045823738917,1860.0,0.0,7.0,3.0,-1.0,0.7221211154407061]]</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>[[-86.52982971436238,15.916287012003309,-1860.0,1.0,7.0,1.0,-1.0],[15.916287012003309,16.49836722067583,-1808.4765,0.0,7.0,2.0,-1.0],[16.49836722067583,18.24460784669344,0.0,0.0,6.0,3.0,-1.0],[18.24460784669344,87.51215267872477,1860.0,0.0,6.0,3.0,-1.0]]</t>
+          <t>[[-86.52982971436238,15.916287012003309,-1860.0,1.0,7.0,1.0,-1.0,0.8285668985732362],[15.916287012003309,16.49836722067583,-1808.4765,0.0,7.0,2.0,-1.0,0.8256182645370916],[16.49836722067583,18.24460784669344,0.0,0.0,6.0,3.0,-1.0,0.7221211154407061],[18.24460784669344,87.51215267872477,1860.0,0.0,6.0,3.0,-1.0,0.6041756493658805]]</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>[[-87.15183381288854,16.01617654598614,-1860.0,1.0,6.0,0.0,-1.0],[16.01617654598614,17.794935345277082,0.0,0.0,5.0,2.0,-1.0],[17.794935345277082,18.38785494504073,227.85,0.0,5.0,2.0,-1.0],[18.38785494504073,90.13112651644212,1860.0,0.0,5.0,2.0,-1.0]]</t>
+          <t>[[-87.15183381288854,16.01617654598614,-1860.0,1.0,6.0,0.0,-1.0,0.7106214324984106],[16.01617654598614,17.794935345277082,0.0,0.0,5.0,2.0,-1.0,0.6041756493658805],[17.794935345277082,18.38785494504073,227.85,0.0,5.0,2.0,-1.0,0.5897273297717144],[18.38785494504073,90.13112651644212,1860.0,0.0,5.0,2.0,-1.0,0.4862301832910549]]</t>
         </is>
       </c>
       <c r="C408" t="n">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>[[-86.49003697269299,15.885810296811684,-1860.0,1.0,5.0,1.0,-1.0],[15.885810296811684,16.46749124720661,-1808.4765,0.0,5.0,2.0,-1.0],[16.46749124720661,18.212534098391345,0.0,0.0,4.0,3.0,-1.0],[18.212534098391345,18.794215048786256,227.85,0.0,4.0,3.0,-1.0],[18.794215048786256,87.432567195386,1860.0,0.0,5.0,2.0,-1.0]]</t>
+          <t>[[-86.49003697269299,15.885810296811684,-1860.0,1.0,5.0,1.0,-1.0,0.592675966423585],[15.885810296811684,16.46749124720661,-1808.4765,0.0,5.0,2.0,-1.0,0.5897273323874405],[16.46749124720661,18.212534098391345,0.0,0.0,4.0,3.0,-1.0,0.4862301832910549],[18.212534098391345,18.794215048786256,227.85,0.0,4.0,3.0,-1.0,0.47178186369688874],[18.794215048786256,87.432567195386,1860.0,0.0,5.0,2.0,-1.0,0.36828471721622924]]</t>
         </is>
       </c>
       <c r="C409" t="n">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>[[-87.59692805574056,16.140776118218625,-1860.0,1.0,4.0,1.0,-1.0],[16.140776118218625,17.91913676120079,0.0,0.0,3.0,2.0,-1.0],[17.91913676120079,18.511923642194844,227.85,0.0,3.0,2.0,-1.0],[18.511923642194844,89.64634936148113,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[-87.59692805574056,16.140776118218625,-1860.0,1.0,4.0,1.0,-1.0,0.4747305003487593],[16.140776118218625,17.91913676120079,0.0,0.0,3.0,2.0,-1.0,0.3682847172162292],[17.91913676120079,18.511923642194844,227.85,0.0,3.0,2.0,-1.0,0.35383639762206304],[18.511923642194844,89.64634936148113,1860.0,0.0,3.0,2.0,-1.0,0.25033925114140354]]</t>
         </is>
       </c>
       <c r="C410" t="n">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>[[-91.04324975298222,16.236226732067536,-1860.0,1.0,3.0,1.0,-1.0],[16.236226732067536,18.118322810752616,0.0,0.0,2.0,3.0,-1.0],[18.118322810752616,19.373053529876003,227.85,0.0,2.0,2.0,-1.0],[19.373053529876003,96.53899275596444,1860.0,0.0,3.0,1.0,-1.0]]</t>
+          <t>[[-91.04324975298222,16.236226732067536,-1860.0,1.0,3.0,1.0,-1.0,0.3567850342739337],[16.236226732067536,18.118322810752616,0.0,0.0,2.0,3.0,-1.0,0.2503392511414036],[18.118322810752616,19.373053529876003,227.85,0.0,2.0,2.0,-1.0,0.23589093154723745],[19.373053529876003,96.53899275596444,1860.0,0.0,3.0,1.0,-1.0,0.13239378506657795]]</t>
         </is>
       </c>
       <c r="C411" t="n">
@@ -11136,7 +11136,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>[[-87.73353588663284,16.486597092430117,-1860.0,1.0,2.0,0.0,-1.0],[16.486597092430117,20.655402411592632,0.0,0.0,2.0,2.0,-1.0],[20.655402411592632,21.846489645639068,1678.65,1.0,2.0,0.0,-1.0],[21.846489645639068,90.33400560330902,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-87.73353588663284,16.486597092430117,-1860.0,1.0,2.0,0.0,-1.0,0.3423367146797675],[16.486597092430117,20.655402411592632,0.0,0.0,2.0,2.0,-1.0,0.2358909315472374],[20.655402411592632,21.846489645639068,1678.65,1.0,2.0,0.0,-1.0,0.12944514841470728],[21.846489645639068,90.33400560330902,1860.0,0.0,2.0,0.0,-1.0,0.11794546547241176]]</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>[[-88.50924163988438,16.22841040533183,-1860.0,1.0,2.0,0.0,-1.0],[16.22841040533183,22.247815695286775,0.0,0.0,2.0,1.0,-1.0],[22.247815695286775,91.47097652976878,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-88.50924163988438,16.22841040533183,-1860.0,1.0,2.0,0.0,-1.0,0.3423367146797675],[16.22841040533183,22.247815695286775,0.0,0.0,2.0,1.0,-1.0,0.2358909315472374],[22.247815695286775,91.47097652976878,1860.0,0.0,2.0,0.0,-1.0,0.11794546547241176]]</t>
         </is>
       </c>
       <c r="C413" t="n">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>[[-87.96460406992695,-6.538896399691822,-1860.0,1.0,2.0,0.0,-1.0],[-6.538896399691822,18.607278027880795,0.0,0.0,2.0,1.0,-1.0],[18.607278027880795,91.05220911683999,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-87.96460406992695,-6.538896399691822,-1860.0,1.0,2.0,0.0,-1.0,0.3423367146797675],[-6.538896399691822,18.607278027880795,0.0,0.0,2.0,1.0,-1.0,0.2358909315472374],[18.607278027880795,91.05220911683999,1860.0,0.0,2.0,0.0,-1.0,0.11794546547241176]]</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>[[-87.03706814570316,-6.231485787405234,-1860.0,1.0,1.0,0.0,-1.0],[-6.231485787405234,16.18174143606427,0.0,0.0,1.0,1.0,-1.0],[16.18174143606427,17.95120674318028,0.0,0.0,0.0,1.0,-1.0],[17.95120674318028,20.310493819334965,1860.0,0.0,0.0,0.0,-1.0],[20.310493819334965,89.31964079685946,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-87.03706814570316,-6.231485787405234,-1860.0,1.0,1.0,0.0,-1.0,0.22439124860494192],[-6.231485787405234,16.18174143606427,0.0,0.0,1.0,1.0,-1.0,0.1179454654724118],[16.18174143606427,17.95120674318028,0.0,0.0,0.0,1.0,-1.0,0.1179454654724118],[17.95120674318028,20.310493819334965,1860.0,0.0,0.0,0.0,-1.0,-6.024138271554236e-10],[20.310493819334965,89.31964079685946,1860.0,0.0,1.0,0.0,-1.0,-6.024138271554236e-10]]</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="F415" s="4" t="inlineStr">
         <is>
-          <t>[0,0,22.4132272235,0,0]</t>
+          <t>[0,0,24.1826925306,0,0]</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>[[-89.806050772733,-6.787531870703347,-1860.0,1.0,0.0,0.0,-1.0],[-6.787531870703347,94.06459479546602,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-89.806050772733,-6.787531870703347,-1860.0,1.0,0.0,0.0,-1.0,0.1064457825301163],[-6.787531870703347,94.06459479546602,0.0,0.0,0.0,1.0,-1.0,-6.024138132776358e-10]]</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -11266,7 +11266,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>[[-89.30726743456471,-16.723517699147976,-1860.0,9.0,0.0,0.0,1.0],[-16.723517699147976,-8.184253024393072,-733.6842,9.0,0.0,0.0,1.0],[-8.184253024393072,93.06702811912943,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-89.30726743456471,-16.723517699147976,-1860.0,9.0,0.0,0.0,1.0,0.1064457825301163],[-16.723517699147976,-8.184253024393072,-733.6842,9.0,0.0,0.0,1.0,0.04198795060240546],[-8.184253024393072,93.06702811912943,0.0,0.0,0.0,1.0,-1.0,-6.024138132776358e-10]]</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>[[-88.62574959622957,-8.287515960138762,-1860.0,9.0,0.0,0.0,1.0],[-8.287515960138762,14.84015735934193,-733.6842,9.0,0.0,0.0,1.0],[14.84015735934193,93.35252204915793,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-88.62574959622957,-8.287515960138762,-1860.0,9.0,0.0,0.0,1.0,0.1064457825301163],[-8.287515960138762,14.84015735934193,-733.6842,9.0,0.0,0.0,1.0,0.04198795060240546],[14.84015735934193,93.35252204915793,0.0,0.0,0.0,1.0,-1.0,-6.024138132776358e-10]]</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>[[-87.78334823272513,-8.693924998252456,-1860.0,8.0,0.0,0.0,1.0],[-8.693924998252456,14.497710386292155,-733.6842,8.0,0.0,0.0,1.0],[14.497710386292155,16.281682338949437,0.0,8.0,0.0,1.0,1.0],[16.281682338949437,22.2282555144737,1016.5,9.0,0.0,0.0,1.0],[22.2282555144737,90.01918971545028,1678.6501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-87.78334823272513,-8.693924998252456,-1860.0,8.0,0.0,0.0,1.0,0.21289156566264641],[-8.693924998252456,14.497710386292155,-733.6842,8.0,0.0,0.0,1.0,0.14843373373493557],[14.497710386292155,16.281682338949437,0.0,8.0,0.0,1.0,1.0,0.1064457825301163],[16.281682338949437,22.2282555144737,1016.5,9.0,0.0,0.0,1.0,0.04198795120481509],[22.2282555144737,90.01918971545028,1678.6501,0.0,0.0,0.0,-1.0,-6.943567915085325e-09]]</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -11344,7 +11344,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>[[-87.61014065198471,-8.914611631872518,-1860.0,7.0,0.0,0.0,1.0],[-8.914611631872518,14.336340124069707,-733.6842,7.0,0.0,0.0,1.0],[14.336340124069707,16.12487487452681,0.0,7.0,0.0,1.0,1.0],[16.12487487452681,22.086657376050454,1016.5,8.0,0.0,0.0,1.0],[22.086657376050454,22.682835626202817,1543.8,10.0,10.0,0.0,-1.0],[22.682835626202817,90.64715614357245,1860.0,10.0,10.0,0.0,-1.0]]</t>
+          <t>[[-87.61014065198471,-8.914611631872518,-1860.0,7.0,0.0,0.0,1.0,0.3193373487951765],[-8.914611631872518,14.336340124069707,-733.6842,7.0,0.0,0.0,1.0,0.2548795168674657],[14.336340124069707,16.12487487452681,0.0,7.0,0.0,1.0,1.0,0.2128915656626464],[16.12487487452681,22.086657376050454,1016.5,8.0,0.0,0.0,1.0,0.1484337343373452],[22.086657376050454,22.682835626202817,1543.8,10.0,10.0,0.0,-1.0,0.11499682882054113],[22.682835626202817,90.64715614357245,1860.0,10.0,10.0,0.0,-1.0,0.09494609958782076]]</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>[[-87.25644445427977,-8.870146997732505,-1860.0,6.0,0.0,0.0,1.0],[-8.870146997732505,15.2940499625565,-733.6842,6.0,0.0,0.0,1.0],[15.2940499625565,16.47279127769255,0.0,6.0,0.0,1.0,1.0],[16.47279127769255,22.955868510940817,1016.5,7.0,0.0,0.0,1.0],[22.955868510940817,88.96538215855955,1860.0,8.0,10.0,1.0,-1.0]]</t>
+          <t>[[-87.25644445427977,-8.870146997732505,-1860.0,6.0,0.0,0.0,1.0,0.4257831319277066],[-8.870146997732505,15.2940499625565,-733.6842,6.0,0.0,0.0,1.0,0.3613252999999958],[15.2940499625565,16.47279127769255,0.0,6.0,0.0,1.0,1.0,0.3193373487951765],[16.47279127769255,22.955868510940817,1016.5,7.0,0.0,0.0,1.0,0.2548795174698753],[22.955868510940817,88.96538215855955,1860.0,8.0,10.0,1.0,-1.0,0.20139188272035086]]</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -11396,7 +11396,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>[[-87.28482705951345,-8.86065448762092,-1860.0,5.0,0.0,0.0,1.0],[-8.86065448762092,14.13590739436259,-733.6842,5.0,0.0,0.0,1.0],[14.13590739436259,15.31521826010534,0.0,5.0,0.0,1.0,1.0],[15.31521826010534,22.39108345456181,1016.5,6.0,0.0,0.0,1.0],[22.39108345456181,22.980738887433176,1725.15,7.0,9.0,2.0,-1.0],[22.980738887433176,89.0221473690269,1860.0,7.0,10.0,1.0,-1.0]]</t>
+          <t>[[-87.28482705951345,-8.86065448762092,-1860.0,5.0,0.0,0.0,1.0,0.5322289150602367],[-8.86065448762092,14.13590739436259,-733.6842,5.0,0.0,0.0,1.0,0.4677710831325259],[14.13590739436259,15.31521826010534,0.0,5.0,0.0,1.0,1.0,0.4257831319277066],[15.31521826010534,22.39108345456181,1016.5,6.0,0.0,0.0,1.0,0.3613253006024054],[22.39108345456181,22.980738887433176,1725.15,7.0,9.0,2.0,-1.0,0.3163887121433059],[22.980738887433176,89.0221473690269,1860.0,7.0,10.0,1.0,-1.0,0.30783766585288097]]</t>
         </is>
       </c>
       <c r="C422" t="n">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>[[-86.90928126716759,-8.923901169931284,-1860.0,4.0,0.0,0.0,1.0],[-8.923901169931284,14.708032192867591,-733.6842,4.0,0.0,0.0,1.0],[14.708032192867591,16.48042719507751,0.0,4.0,0.0,1.0,1.0],[16.48042719507751,22.388410535777226,1016.5,5.0,0.0,0.0,1.0],[22.388410535777226,22.9792088698472,1543.8,7.0,10.0,0.0,-1.0],[22.9792088698472,89.73942061975401,1860.0,7.0,10.0,0.0,-1.0]]</t>
+          <t>[[-86.90928126716759,-8.923901169931284,-1860.0,4.0,0.0,0.0,1.0,0.6386746981927669],[-8.923901169931284,14.708032192867591,-733.6842,4.0,0.0,0.0,1.0,0.574216866265056],[14.708032192867591,16.48042719507751,0.0,4.0,0.0,1.0,1.0,0.5322289150602367],[16.48042719507751,22.388410535777226,1016.5,5.0,0.0,0.0,1.0,0.46777108373493553],[22.388410535777226,22.9792088698472,1543.8,7.0,10.0,0.0,-1.0,0.4343341782181315],[22.9792088698472,89.73942061975401,1860.0,7.0,10.0,0.0,-1.0,0.4142834489854111]]</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>[[-84.74206287504296,-8.539057824034344,-1860.0,3.0,0.0,0.0,1.0],[-8.539057824034344,14.147332992678145,-733.6842,3.0,0.0,0.0,1.0],[14.147332992678145,15.310737649945452,0.0,3.0,0.0,1.0,1.0],[15.310737649945452,22.291165593549294,1016.5,4.0,0.0,0.0,1.0],[22.291165593549294,89.18693338641944,1860.0,6.0,10.0,0.0,-1.0]]</t>
+          <t>[[-84.74206287504296,-8.539057824034344,-1860.0,3.0,0.0,0.0,1.0,0.745120481325297],[-8.539057824034344,14.147332992678145,-733.6842,3.0,0.0,0.0,1.0,0.6806626493975861],[14.147332992678145,15.310737649945452,0.0,3.0,0.0,1.0,1.0,0.6386746981927669],[15.310737649945452,22.291165593549294,1016.5,4.0,0.0,0.0,1.0,0.5742168668674656],[22.291165593549294,89.18693338641944,1860.0,6.0,10.0,0.0,-1.0,0.5207292321179413]]</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -11474,7 +11474,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>[[-81.20673566403279,-8.85143691233246,-1860.0,2.0,0.0,0.0,1.0],[-8.85143691233246,14.706102216128116,-733.6842,2.0,0.0,0.0,1.0],[14.706102216128116,16.38878358244672,0.0,2.0,0.0,1.0,1.0],[16.38878358244672,21.997721470175435,1016.5,3.0,0.0,0.0,1.0],[21.997721470175435,23.119509047721166,1725.15,4.0,9.0,2.0,-1.0],[23.119509047721166,86.50050717905557,1860.0,4.0,10.0,1.0,-1.0]]</t>
+          <t>[[-81.20673566403279,-8.85143691233246,-1860.0,2.0,0.0,0.0,1.0,0.851566264457827],[-8.85143691233246,14.706102216128116,-733.6842,2.0,0.0,0.0,1.0,0.7871084325301162],[14.706102216128116,16.38878358244672,0.0,2.0,0.0,1.0,1.0,0.745120481325297],[16.38878358244672,21.997721470175435,1016.5,3.0,0.0,0.0,1.0,0.6806626499999957],[21.997721470175435,23.119509047721166,1725.15,4.0,9.0,2.0,-1.0,0.6357260615408962],[23.119509047721166,86.50050717905557,1860.0,4.0,10.0,1.0,-1.0,0.6271750152504714]]</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>[[-70.64100119605507,-8.709625243192797,-1860.0,1.0,0.0,0.0,1.0],[-8.709625243192797,15.030735538737744,-733.6842,1.0,0.0,0.0,1.0],[15.030735538737744,16.579019937559295,0.0,1.0,0.0,1.0,1.0],[16.579019937559295,22.772157532845526,1016.5,2.0,0.0,0.0,1.0],[22.772157532845526,83.67134388649342,1860.0,4.0,10.0,0.0,-1.0]]</t>
+          <t>[[-70.64100119605507,-8.709625243192797,-1860.0,1.0,0.0,0.0,1.0,0.9580120475903571],[-8.709625243192797,15.030735538737744,-733.6842,1.0,0.0,0.0,1.0,0.8935542156626463],[15.030735538737744,16.579019937559295,0.0,1.0,0.0,1.0,1.0,0.851566264457827],[16.579019937559295,22.772157532845526,1016.5,2.0,0.0,0.0,1.0,0.7871084331325258],[22.772157532845526,83.67134388649342,1860.0,4.0,10.0,0.0,-1.0,0.7336207983830014]]</t>
         </is>
       </c>
       <c r="C426" t="n">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>[[-55.58118859665393,13.213897700781501,-733.6843,0.0,0.0,0.0,1.0],[13.213897700781501,14.528453489904464,-733.6842,0.0,0.0,0.0,1.0],[14.528453489904464,16.28119454206842,0.0,0.0,0.0,1.0,1.0],[16.28119454206842,22.853973487683277,1016.5,1.0,0.0,0.0,1.0],[22.853973487683277,23.29215875072427,1543.8,3.0,10.0,0.0,-1.0],[23.29215875072427,75.43620505260209,1860.0,3.0,10.0,0.0,-1.0]]</t>
+          <t>[[-55.58118859665393,13.213897700781501,-733.6843,0.0,0.0,0.0,1.0,1.000000004518068],[13.213897700781501,14.528453489904464,-733.6842,0.0,0.0,0.0,1.0,0.9999999987951763],[14.528453489904464,16.28119454206842,0.0,0.0,0.0,1.0,1.0,0.9580120475903571],[16.28119454206842,22.853973487683277,1016.5,1.0,0.0,0.0,1.0,0.8935542162650558],[22.853973487683277,23.29215875072427,1543.8,3.0,10.0,0.0,-1.0,0.8601173107482518],[23.29215875072427,75.43620505260209,1860.0,3.0,10.0,0.0,-1.0,0.8400665815155315]]</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="F427" s="4" t="inlineStr">
         <is>
-          <t>[0,0,0,6.5727789456,0.438185263]</t>
+          <t>[0,0,1.7527410522,6.5727789456,0.438185263]</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>[[-57.447156425409915,21.561234780220246,0.0,0.0,0.0,1.0,1.0],[21.561234780220246,22.459057407556955,527.3,2.0,10.0,0.0,-1.0],[22.459057407556955,76.7773263614277,1860.0,2.0,10.0,0.0,-1.0]]</t>
+          <t>[[-57.447156425409915,21.561234780220246,0.0,0.0,0.0,1.0,1.0,1.000000004518068],[21.561234780220246,22.459057407556955,527.3,2.0,10.0,0.0,-1.0,0.9665630990012639],[22.459057407556955,76.7773263614277,1860.0,2.0,10.0,0.0,-1.0,0.8820545384432423]]</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -11578,7 +11578,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>[[-57.738570267030305,20.981902995192463,0.0,0.0,0.0,1.0,1.0],[20.981902995192463,22.331396822544853,708.65,1.0,9.0,1.0,-1.0],[22.331396822544853,76.7609811924246,1860.0,1.0,10.0,0.0,-1.0]]</t>
+          <t>[[-57.738570267030305,20.981902995192463,0.0,0.0,0.0,1.0,1.0,1.000000004518068],[20.981902995192463,22.331396822544853,708.65,1.0,9.0,1.0,-1.0,0.9550634160589684],[22.331396822544853,76.7609811924246,1860.0,1.0,10.0,0.0,-1.0,0.8820545384432423]]</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>[[-55.22522895798049,18.460871137315422,-1860.0,1.0,8.0,1.0,-1.0],[18.460871137315422,19.753609735478506,-1074.7922,0.0,8.0,2.0,-1.0],[19.753609735478506,21.908174065750316,0.0,0.0,8.0,2.0,-1.0],[21.908174065750316,22.769999797859043,708.6501,1.0,8.0,1.0,-1.0],[22.769999797859043,73.61771799227378,1860.0,1.0,9.0,0.0,-1.0]]</t>
+          <t>[[-55.22522895798049,18.460871137315422,-1860.0,1.0,8.0,1.0,-1.0,0.9885003215757724],[18.460871137315422,19.753609735478506,-1074.7922,0.0,8.0,2.0,-1.0,0.943563730611917],[19.753609735478506,21.908174065750316,0.0,0.0,8.0,2.0,-1.0,0.8820545384432423],[21.908174065750316,22.769999797859043,708.6501,1.0,8.0,1.0,-1.0,0.8371179436429886],[22.769999797859043,73.61771799227378,1860.0,1.0,9.0,0.0,-1.0,0.7641090723684167]]</t>
         </is>
       </c>
       <c r="C430" t="n">
@@ -11630,7 +11630,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>[[-59.86230346084341,17.808627484465347,-1860.0,1.0,7.0,1.0,-1.0],[17.808627484465347,19.229437196879545,-1074.7922,0.0,7.0,2.0,-1.0],[19.229437196879545,21.597453384236516,0.0,0.0,7.0,2.0,-1.0],[21.597453384236516,22.07105662170791,708.6501,1.0,7.0,1.0,-1.0],[22.07105662170791,81.74506454310367,1860.0,1.0,8.0,0.0,-1.0]]</t>
+          <t>[[-59.86230346084341,17.808627484465347,-1860.0,1.0,7.0,1.0,-1.0,0.8705548555009468],[17.808627484465347,19.229437196879545,-1074.7922,0.0,7.0,2.0,-1.0,0.8256182645370914],[19.229437196879545,21.597453384236516,0.0,0.0,7.0,2.0,-1.0,0.7641090723684167],[21.597453384236516,22.07105662170791,708.6501,1.0,7.0,1.0,-1.0,0.719172477568163],[22.07105662170791,81.74506454310367,1860.0,1.0,8.0,0.0,-1.0,0.6461636062935912]]</t>
         </is>
       </c>
       <c r="C431" t="n">
@@ -11656,7 +11656,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>[[-58.387726816210474,18.6248612397208,-1860.0,1.0,6.0,1.0,-1.0],[18.6248612397208,19.968104054649842,-1074.7922,0.0,6.0,2.0,-1.0],[19.968104054649842,22.206842079531555,0.0,0.0,6.0,2.0,-1.0],[22.206842079531555,22.65458968450791,708.6501,1.0,6.0,1.0,-1.0],[22.65458968450791,75.48880707171658,1860.0,1.0,7.0,0.0,-1.0]]</t>
+          <t>[[-58.387726816210474,18.6248612397208,-1860.0,1.0,6.0,1.0,-1.0,0.7526093894261212],[18.6248612397208,19.968104054649842,-1074.7922,0.0,6.0,2.0,-1.0,0.7076727984622658],[19.968104054649842,22.206842079531555,0.0,0.0,6.0,2.0,-1.0,0.6461636062935912],[22.206842079531555,22.65458968450791,708.6501,1.0,6.0,1.0,-1.0,0.6012270114933375],[22.65458968450791,75.48880707171658,1860.0,1.0,7.0,0.0,-1.0,0.5282181402187656]]</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>[[-65.59803390096648,18.275553614066766,-1860.0,1.0,5.0,1.0,-1.0],[18.275553614066766,20.38558097293553,-1074.7922,0.0,5.0,2.0,-1.0],[20.38558097293553,22.49560833180429,0.0,0.0,5.0,2.0,-1.0],[22.49560833180429,92.12651117447342,1860.0,1.0,6.0,0.0,-1.0]]</t>
+          <t>[[-65.59803390096648,18.275553614066766,-1860.0,1.0,5.0,1.0,-1.0,0.6346639233512956],[18.275553614066766,20.38558097293553,-1074.7922,0.0,5.0,2.0,-1.0,0.5897273323874402],[20.38558097293553,22.49560833180429,0.0,0.0,5.0,2.0,-1.0,0.5282181402187656],[22.49560833180429,92.12651117447342,1860.0,1.0,6.0,0.0,-1.0,0.4102726741439399]]</t>
         </is>
       </c>
       <c r="C433" t="n">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>[[-68.85511877284875,18.526786155867114,-1860.0,1.0,4.0,1.0,-1.0],[18.526786155867114,19.647066988286554,-1074.7922,0.0,4.0,2.0,-1.0],[19.647066988286554,21.3274882369157,0.0,0.0,4.0,2.0,-1.0],[21.3274882369157,23.007909485544857,708.6501,1.0,4.0,1.0,-1.0],[23.007909485544857,98.62686567385666,1860.0,1.0,4.0,1.0,-1.0]]</t>
+          <t>[[-68.85511877284875,18.526786155867114,-1860.0,1.0,4.0,1.0,-1.0,0.51671845727647],[18.526786155867114,19.647066988286554,-1074.7922,0.0,4.0,2.0,-1.0,0.4717818663126146],[19.647066988286554,21.3274882369157,0.0,0.0,4.0,2.0,-1.0,0.4102726741439399],[21.3274882369157,23.007909485544857,708.6501,1.0,4.0,1.0,-1.0,0.3653360793436863],[23.007909485544857,98.62686567385666,1860.0,1.0,4.0,1.0,-1.0,0.2923272080691143]]</t>
         </is>
       </c>
       <c r="C434" t="n">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>[[-68.34226158934614,18.224570253912745,-1860.0,1.0,3.0,1.0,-1.0],[18.224570253912745,19.33440143139042,-1074.7922,0.0,3.0,2.0,-1.0],[19.33440143139042,21.55406378634578,0.0,0.0,3.0,2.0,-1.0],[21.55406378634578,22.108979375084616,708.6501,1.0,3.0,1.0,-1.0],[22.108979375084616,97.5774994435667,1860.0,1.0,4.0,0.0,-1.0]]</t>
+          <t>[[-68.34226158934614,18.224570253912745,-1860.0,1.0,3.0,1.0,-1.0,0.3987729912016444],[18.224570253912745,19.33440143139042,-1074.7922,0.0,3.0,2.0,-1.0,0.35383640023778895],[19.33440143139042,21.55406378634578,0.0,0.0,3.0,2.0,-1.0,0.2923272080691143],[21.55406378634578,22.108979375084616,708.6501,1.0,3.0,1.0,-1.0,0.24739061326886064],[22.108979375084616,97.5774994435667,1860.0,1.0,4.0,0.0,-1.0,0.17438174199428863]]</t>
         </is>
       </c>
       <c r="C435" t="n">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>[[-71.39174568593896,20.869997737051747,-1860.0,1.0,3.0,0.0,-1.0],[20.869997737051747,23.235683465846392,0.0,1.0,2.0,1.0,-1.0],[23.235683465846392,23.82710489804505,708.6501,1.0,2.0,1.0,-1.0],[23.82710489804505,105.44326254145992,1860.0,1.0,2.0,1.0,-1.0]]</t>
+          <t>[[-71.39174568593896,20.869997737051747,-1860.0,1.0,3.0,0.0,-1.0,0.28082752512681874],[20.869997737051747,23.235683465846392,0.0,1.0,2.0,1.0,-1.0,0.1743817419942886],[23.235683465846392,23.82710489804505,708.6501,1.0,2.0,1.0,-1.0,0.12944514719403497],[23.82710489804505,105.44326254145992,1860.0,1.0,2.0,1.0,-1.0,0.05643627591946297]]</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>[[-73.20048621239661,6.649867072521928,-1860.0,1.0,3.0,0.0,-1.0],[6.649867072521928,18.057060398938873,-1275.734,0.0,3.0,0.0,-1.0],[18.057060398938873,19.858196187320488,0.0,0.0,2.0,1.0,-1.0],[19.858196187320488,22.259710571829316,708.6501,0.0,2.0,1.0,-1.0],[22.259710571829316,106.31271402963833,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-73.20048621239661,6.649867072521928,-1860.0,1.0,3.0,0.0,-1.0,0.3872733082593488],[6.649867072521928,18.057060398938873,-1275.734,0.0,3.0,0.0,-1.0,0.3538363986207946],[18.057060398938873,19.858196187320488,0.0,0.0,2.0,1.0,-1.0,0.2808275251268187],[19.858196187320488,22.259710571829316,708.6501,0.0,2.0,1.0,-1.0,0.23589093032656505],[22.259710571829316,106.31271402963833,1860.0,0.0,3.0,0.0,-1.0,0.16288205905199304]]</t>
         </is>
       </c>
       <c r="C437" t="n">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>[[-75.39030564304474,6.6274496673942025,-1860.0,1.0,2.0,0.0,-1.0],[6.6274496673942025,20.50737748916079,-1275.734,0.0,2.0,0.0,-1.0],[20.50737748916079,22.400094919401695,0.0,0.0,1.0,1.0,-1.0],[22.400094919401695,23.03100072948199,708.6501,0.0,1.0,1.0,-1.0],[23.03100072948199,113.25053157096482,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[-75.39030564304474,6.6274496673942025,-1860.0,1.0,2.0,0.0,-1.0,0.2693278421845232],[6.6274496673942025,20.50737748916079,-1275.734,0.0,2.0,0.0,-1.0,0.235890932545969],[20.50737748916079,22.400094919401695,0.0,0.0,1.0,1.0,-1.0,0.1628820590519931],[22.400094919401695,23.03100072948199,708.6501,0.0,1.0,1.0,-1.0,0.11794546425173946],[23.03100072948199,113.25053157096482,1860.0,0.0,1.0,1.0,-1.0,0.04493659297716747]]</t>
         </is>
       </c>
       <c r="C438" t="n">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>[[-75.73307982031147,4.232587673579744,-1860.0,10.0,2.0,0.0,1.0],[4.232587673579744,6.106783005467818,-1275.734,0.0,2.0,0.0,-1.0],[6.106783005467818,6.731514782763838,0.0,0.0,1.0,1.0,-1.0],[6.731514782763838,22.974540992460504,708.6501,0.0,1.0,0.0,-1.0],[22.974540992460504,111.06172159120005,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-75.73307982031147,4.232587673579744,-1860.0,10.0,2.0,0.0,1.0,0.2693278421845232],[4.232587673579744,6.106783005467818,-1275.734,0.0,2.0,0.0,-1.0,0.235890932545969],[6.106783005467818,6.731514782763838,0.0,0.0,1.0,1.0,-1.0,0.1628820590519931],[6.731514782763838,22.974540992460504,708.6501,0.0,1.0,0.0,-1.0,0.11794546425173946],[22.974540992460504,111.06172159120005,1860.0,0.0,1.0,0.0,-1.0,0.04493659297716747]]</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>[[-76.06077291540511,4.2468811797579775,-1860.0,10.0,1.0,0.0,1.0],[4.2468811797579775,6.143912378856328,-1275.734,0.0,1.0,0.0,-1.0],[6.143912378856328,6.776256111889097,0.0,0.0,0.0,1.0,-1.0],[6.776256111889097,7.408599844921881,708.6501,0.0,0.0,0.0,-1.0],[7.408599844921881,113.01000326139621,708.6502,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-76.06077291540511,4.2468811797579775,-1860.0,10.0,1.0,0.0,1.0,0.15138237610969757],[4.2468811797579775,6.143912378856328,-1275.734,0.0,1.0,0.0,-1.0,0.11794546647114336],[6.143912378856328,6.776256111889097,0.0,0.0,0.0,1.0,-1.0,0.04493659297716747],[6.776256111889097,7.408599844921881,708.6501,0.0,0.0,0.0,-1.0,-1.8230861750789806e-09],[7.408599844921881,113.01000326139621,708.6502,0.0,0.0,0.0,-1.0,-8.164240269947776e-09]]</t>
         </is>
       </c>
       <c r="C440" t="n">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="F440" s="4" t="inlineStr">
         <is>
-          <t>[0,1.8970311991,0,0,0]</t>
+          <t>[0,1.8970311991,0.632343733,0,0]</t>
         </is>
       </c>
     </row>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>[[-75.46128830423774,3.648298713919374,-1860.0,10.0,0.0,0.0,1.0],[3.648298713919374,4.276152579142845,-733.6842,9.0,0.0,1.0,1.0],[4.276152579142845,112.26701739757956,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-75.46128830423774,3.648298713919374,-1860.0,10.0,0.0,0.0,1.0,0.10644577496828984],[3.648298713919374,4.276152579142845,-733.6842,9.0,0.0,1.0,1.0,0.041987943040579005],[4.276152579142845,112.26701739757956,0.0,0.0,0.0,1.0,-1.0,-8.164240269947776e-09]]</t>
         </is>
       </c>
       <c r="C441" t="n">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>[[-79.0879603651538,0.8880012400037316,-1860.0,9.0,0.0,0.0,1.0],[0.8880012400037316,16.7510018889606,-733.6842,9.0,0.0,0.0,1.0],[16.7510018889606,118.53858938643381,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-79.0879603651538,0.8880012400037316,-1860.0,9.0,0.0,0.0,1.0,0.10644577496828984],[0.8880012400037316,16.7510018889606,-733.6842,9.0,0.0,0.0,1.0,0.041987943040579005],[16.7510018889606,118.53858938643381,0.0,0.0,0.0,1.0,-1.0,-8.164240269947776e-09]]</t>
         </is>
       </c>
       <c r="C442" t="n">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>[[-75.67917610678947,18.192484225757923,-1860.0,9.0,0.0,0.0,1.0],[18.192484225757923,32.05272937553002,0.0,9.0,0.0,1.0,1.0],[32.05272937553002,112.69415570147676,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-75.67917610678947,18.192484225757923,-1860.0,9.0,0.0,0.0,1.0,0.14843372617310913],[18.192484225757923,32.05272937553002,0.0,9.0,0.0,1.0,1.0,0.04198794304057901],[32.05272937553002,112.69415570147676,662.15,0.0,0.0,0.0,-1.0,-8.766649906011281e-09]]</t>
         </is>
       </c>
       <c r="C443" t="n">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>[[-76.51945508596222,18.15774896087585,-1860.0,8.0,0.0,0.0,1.0],[18.15774896087585,32.871098238425006,0.0,8.0,0.0,1.0,1.0],[32.871098238425006,33.51080907657932,1678.6499,9.0,0.0,2.0,1.0],[33.51080907657932,114.75408552217687,1860.0,9.0,1.0,1.0,1.0]]</t>
+          <t>[[-76.51945508596222,18.15774896087585,-1860.0,8.0,0.0,0.0,1.0,0.2548795093056392],[18.15774896087585,32.871098238425006,0.0,8.0,0.0,1.0,1.0,0.1484337261731091],[32.871098238425006,33.51080907657932,1678.6499,9.0,0.0,2.0,1.0,0.04198794938173306],[33.51080907657932,114.75408552217687,1860.0,9.0,1.0,1.0,1.0,0.030488260098283468]]</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>[[-76.52030236016499,17.55733797158554,-1860.0,7.0,0.0,0.0,1.0],[17.55733797158554,34.19692061529652,0.0,7.0,0.0,1.0,1.0],[34.19692061529652,114.83489804251124,1860.0,7.0,9.0,2.0,-1.0]]</t>
+          <t>[[-76.52030236016499,17.55733797158554,-1860.0,7.0,0.0,0.0,1.0,0.3613252924381693],[17.55733797158554,34.19692061529652,0.0,7.0,0.0,1.0,1.0,0.2548795093056392],[34.19692061529652,114.83489804251124,1860.0,7.0,9.0,2.0,-1.0,0.13693404323081354]]</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>[[-73.52803218553744,18.123858316098193,-1860.0,6.0,0.0,0.0,1.0],[18.123858316098193,32.177148193015654,0.0,6.0,0.0,1.0,1.0],[32.177148193015654,32.78816079635989,889.9999,6.0,8.0,3.0,-1.0],[32.78816079635989,109.1647362143896,1860.0,6.0,9.0,2.0,-1.0]]</t>
+          <t>[[-73.52803218553744,18.123858316098193,-1860.0,6.0,0.0,0.0,1.0,0.4677710755706995],[18.123858316098193,32.177148193015654,0.0,6.0,0.0,1.0,1.0,0.3613252924381694],[32.177148193015654,32.78816079635989,889.9999,6.0,8.0,3.0,-1.0,0.30488902737792845],[32.78816079635989,109.1647362143896,1860.0,6.0,9.0,2.0,-1.0,0.24337982636334377]]</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -12046,7 +12046,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>[[-75.44296645289369,17.38408870337058,-1860.0,5.0,0.0,0.0,1.0],[17.38408870337058,32.43712467465667,0.0,5.0,0.0,1.0,1.0],[32.43712467465667,34.31875417106744,1678.6499,6.0,0.0,0.0,1.0],[34.31875417106744,112.0927733560456,1860.0,6.0,1.0,0.0,1.0]]</t>
+          <t>[[-75.44296645289369,17.38408870337058,-1860.0,5.0,0.0,0.0,1.0,0.5742168587032297],[17.38408870337058,32.43712467465667,0.0,5.0,0.0,1.0,1.0,0.4677710755706995],[32.43712467465667,34.31875417106744,1678.6499,6.0,0.0,0.0,1.0,0.3613252987793235],[34.31875417106744,112.0927733560456,1860.0,6.0,1.0,0.0,1.0,0.3498256094958739]]</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -12072,7 +12072,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>[[-76.64405402299475,17.535702946708966,-1860.0,4.0,0.0,0.0,1.0],[17.535702946708966,33.552668417747014,0.0,4.0,0.0,1.0,1.0],[33.552668417747014,114.91885301062027,1860.0,4.0,9.0,2.0,-1.0]]</t>
+          <t>[[-76.64405402299475,17.535702946708966,-1860.0,4.0,0.0,0.0,1.0,0.6806626418357598],[17.535702946708966,33.552668417747014,0.0,4.0,0.0,1.0,1.0,0.5742168587032296],[33.552668417747014,114.91885301062027,1860.0,4.0,9.0,2.0,-1.0,0.45627139262840394]]</t>
         </is>
       </c>
       <c r="C448" t="n">
@@ -12098,7 +12098,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>[[-74.6482043869815,17.80592199171096,-1860.0,3.0,0.0,0.0,1.0],[17.80592199171096,33.4231730691928,0.0,3.0,0.0,1.0,1.0],[33.4231730691928,112.13411849970126,1860.0,3.0,9.0,2.0,-1.0]]</t>
+          <t>[[-74.6482043869815,17.80592199171096,-1860.0,3.0,0.0,0.0,1.0,0.7871084249682898],[17.80592199171096,33.4231730691928,0.0,3.0,0.0,1.0,1.0,0.6806626418357598],[33.4231730691928,112.13411849970126,1860.0,3.0,9.0,2.0,-1.0,0.5627171757609342]]</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>[[-73.3492649331987,17.741139404898334,-1860.0,2.0,0.0,0.0,1.0],[17.741139404898334,31.467090743515698,0.0,2.0,0.0,1.0,1.0],[31.467090743515698,33.96271825962795,889.9999,2.0,8.0,3.0,-1.0],[33.96271825962795,113.19889189619178,1860.0,2.0,9.0,2.0,-1.0]]</t>
+          <t>[[-73.3492649331987,17.741139404898334,-1860.0,2.0,0.0,0.0,1.0,0.8935542081008199],[17.741139404898334,31.467090743515698,0.0,2.0,0.0,1.0,1.0,0.7871084249682898],[31.467090743515698,33.96271825962795,889.9999,2.0,8.0,3.0,-1.0,0.7306721599080488],[33.96271825962795,113.19889189619178,1860.0,2.0,9.0,2.0,-1.0,0.6691629588934642]]</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -12150,7 +12150,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>[[-65.25296332283243,17.408820804777434,-1860.0,1.0,0.0,0.0,1.0],[17.408820804777434,28.39185505949483,0.0,1.0,0.0,1.0,1.0],[28.39185505949483,33.01629053516531,0.0,0.0,0.0,1.0,1.0],[33.01629053516531,33.59434496962412,889.9999,0.0,8.0,3.0,-1.0],[33.59434496962412,107.58531258035183,1860.0,0.0,9.0,2.0,-1.0]]</t>
+          <t>[[-65.25296332283243,17.408820804777434,-1860.0,1.0,0.0,0.0,1.0,0.9999999912333499],[17.408820804777434,28.39185505949483,0.0,1.0,0.0,1.0,1.0,0.8935542081008199],[28.39185505949483,33.01629053516531,0.0,0.0,0.0,1.0,1.0,0.8935542081008199],[33.01629053516531,33.59434496962412,889.9999,0.0,8.0,3.0,-1.0,0.8371179430405788],[33.59434496962412,107.58531258035183,1860.0,0.0,9.0,2.0,-1.0,0.7756087420259943]]</t>
         </is>
       </c>
       <c r="C451" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="F451" s="4" t="inlineStr">
         <is>
-          <t>[0,0,10.9830342547,0,0.5780544345]</t>
+          <t>[0,0,15.6074697304,0,0.5780544345]</t>
         </is>
       </c>
     </row>
@@ -12176,7 +12176,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>[[-64.05282772948772,33.56815955875055,0.0,0.0,0.0,1.0,1.0],[33.56815955875055,34.70328731791612,889.9999,0.0,8.0,3.0,-1.0],[34.70328731791612,105.64877226576371,1860.0,0.0,9.0,2.0,-1.0]]</t>
+          <t>[[-64.05282772948772,33.56815955875055,0.0,0.0,0.0,1.0,1.0,0.9999999912333499],[33.56815955875055,34.70328731791612,889.9999,0.0,8.0,3.0,-1.0,0.9435637261731089],[34.70328731791612,105.64877226576371,1860.0,0.0,9.0,2.0,-1.0,0.8820545251585243]]</t>
         </is>
       </c>
       <c r="C452" t="n">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>[[-65.59022917456494,33.26243311424453,0.0,0.0,0.0,1.0,1.0],[33.26243311424453,33.840518858623525,889.9999,0.0,8.0,2.0,-1.0],[33.840518858623525,107.25740839475687,1860.0,0.0,9.0,1.0,-1.0]]</t>
+          <t>[[-65.59022917456494,33.26243311424453,0.0,0.0,0.0,1.0,1.0,0.9999999912333499],[33.26243311424453,33.840518858623525,889.9999,0.0,8.0,2.0,-1.0,0.9435637261731089],[33.840518858623525,107.25740839475687,1860.0,0.0,9.0,1.0,-1.0,0.8820545251585243]]</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>[[-64.72564615698371,34.00324295510656,0.0,0.0,0.0,1.0,1.0],[34.00324295510656,34.57393017540767,1678.6499,0.0,0.0,0.0,1.0],[34.57393017540767,105.90983271304513,1860.0,0.0,9.0,0.0,-1.0]]</t>
+          <t>[[-64.72564615698371,34.00324295510656,0.0,0.0,0.0,1.0,1.0,0.9999999912333499],[34.00324295510656,34.57393017540767,1678.6499,0.0,0.0,0.0,1.0,0.8935542144419739],[34.57393017540767,105.90983271304513,1860.0,0.0,9.0,0.0,-1.0,0.8820545251585243]]</t>
         </is>
       </c>
       <c r="C454" t="n">
@@ -12244,7 +12244,7 @@
       </c>
       <c r="F454" s="4" t="inlineStr">
         <is>
-          <t>[0,0,0,0,0]</t>
+          <t>[0,0,0,0.5706872203,0]</t>
         </is>
       </c>
     </row>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>[[-64.58338730193968,33.09825608933434,0.0,0.0,0.0,1.0,1.0],[33.09825608933434,38.777421402780504,889.9999,0.0,8.0,0.0,-1.0],[38.777421402780504,105.22365557010065,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-64.58338730193968,33.09825608933434,0.0,0.0,0.0,1.0,1.0,0.9999999912333499],[33.09825608933434,38.777421402780504,889.9999,0.0,8.0,0.0,-1.0,0.9435637261731089],[38.777421402780504,105.22365557010065,1860.0,0.0,8.0,0.0,-1.0,0.8820545251585243]]</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>[[-62.720315895578096,9.44773605366926,0.0,0.0,0.0,1.0,1.0],[9.44773605366926,33.87384594418374,889.9999,0.0,8.0,0.0,-1.0],[33.87384594418374,103.26620358769084,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-62.720315895578096,9.44773605366926,0.0,0.0,0.0,1.0,1.0,0.9999999912333499],[9.44773605366926,33.87384594418374,889.9999,0.0,8.0,0.0,-1.0,0.9435637261731089],[33.87384594418374,103.26620358769084,1860.0,0.0,8.0,0.0,-1.0,0.8820545251585243]]</t>
         </is>
       </c>
       <c r="C456" t="n">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>[[-67.00519176049741,2.8457610456450197,-1860.0,1.0,8.0,0.0,-1.0],[2.8457610456450197,8.815927952152919,-1074.7924,0.0,8.0,0.0,-1.0],[8.815927952152919,10.009961333454498,0.0,0.0,7.0,1.0,-1.0],[10.009961333454498,33.293612268835304,889.9999,0.0,7.0,0.0,-1.0],[33.293612268835304,111.5027987440888,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-67.00519176049741,2.8457610456450197,-1860.0,1.0,8.0,0.0,-1.0,0.9885003082910544],[2.8457610456450197,8.815927952152919,-1074.7924,0.0,8.0,0.0,-1.0,0.9435637287729821],[8.815927952152919,10.009961333454498,0.0,0.0,7.0,1.0,-1.0,0.8820545251585243],[10.009961333454498,33.293612268835304,889.9999,0.0,7.0,0.0,-1.0,0.8256182600982833],[33.293612268835304,111.5027987440888,1860.0,0.0,7.0,0.0,-1.0,0.7641090590836987]]</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -12332,7 +12332,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>[[-69.97090497868466,2.9099973663842604,-1860.0,1.0,7.0,0.0,-1.0],[2.9099973663842604,9.139134318954262,-1074.7924,0.0,7.0,0.0,-1.0],[9.139134318954262,10.384961709468257,0.0,0.0,6.0,1.0,-1.0],[10.384961709468257,32.80985473872023,889.9999,0.0,6.0,0.0,-1.0],[32.80985473872023,116.28028990315818,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[-69.97090497868466,2.9099973663842604,-1860.0,1.0,7.0,0.0,-1.0,0.8705548422162288],[2.9099973663842604,9.139134318954262,-1074.7924,0.0,7.0,0.0,-1.0,0.8256182626981565],[9.139134318954262,10.384961709468257,0.0,0.0,6.0,1.0,-1.0,0.7641090590836987],[10.384961709468257,32.80985473872023,889.9999,0.0,6.0,0.0,-1.0,0.7076727940234577],[32.80985473872023,116.28028990315818,1860.0,0.0,6.0,0.0,-1.0,0.6461635930088732]]</t>
         </is>
       </c>
       <c r="C458" t="n">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>[[-70.27350632036618,2.980903240966441,-1860.0,9.0,14.0,0.0,0.0],[2.980903240966441,8.61585782260741,-1074.7924,0.0,6.0,0.0,-1.0],[8.61585782260741,9.86806995186096,0.0,0.0,5.0,1.0,-1.0],[9.86806995186096,34.28620647230517,889.9999,0.0,5.0,0.0,-1.0],[34.28620647230517,116.9322070030394,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-70.27350632036618,2.980903240966441,-1860.0,9.0,14.0,0.0,0.0,0.7526093761414032],[2.980903240966441,8.61585782260741,-1074.7924,0.0,6.0,0.0,-1.0,0.7076727966233309],[8.61585782260741,9.86806995186096,0.0,0.0,5.0,1.0,-1.0,0.6461635930088732],[9.86806995186096,34.28620647230517,889.9999,0.0,5.0,0.0,-1.0,0.5897273279486321],[34.28620647230517,116.9322070030394,1860.0,0.0,5.0,0.0,-1.0,0.5282181269340476]]</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>[[-68.63602725435922,3.07680889131575,-1860.0,9.0,5.0,0.0,1.0],[3.07680889131575,7.938696087632692,-1808.4766,9.0,5.0,0.0,1.0],[7.938696087632692,9.154167886711932,-1074.7924,0.0,5.0,0.0,-1.0],[9.154167886711932,10.36963968579117,0.0,0.0,4.0,1.0,-1.0],[10.36963968579117,34.07133976783628,889.9999,0.0,4.0,0.0,-1.0],[34.07133976783628,113.07700670798667,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-68.63602725435922,3.07680889131575,-1860.0,9.0,5.0,0.0,1.0,0.6346639100665776],[3.07680889131575,7.938696087632692,-1808.4766,9.0,5.0,0.0,1.0,0.6317152817533247],[7.938696087632692,9.154167886711932,-1074.7924,0.0,5.0,0.0,-1.0,0.5897273305485053],[9.154167886711932,10.36963968579117,0.0,0.0,4.0,1.0,-1.0,0.5282181269340476],[10.36963968579117,34.07133976783628,889.9999,0.0,4.0,0.0,-1.0,0.4717818618738066],[34.07133976783628,113.07700670798667,1860.0,0.0,4.0,0.0,-1.0,0.4102726608592219]]</t>
         </is>
       </c>
       <c r="C460" t="n">
@@ -12410,7 +12410,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>[[-65.66475429601871,2.6717539013956326,-1860.0,9.0,4.0,0.0,1.0],[2.6717539013956326,8.512481097755824,-1808.4766,9.0,4.0,0.0,1.0],[8.512481097755824,9.09655381739185,-1074.7924,0.0,4.0,0.0,-1.0],[9.09655381739185,10.264699256663889,0.0,0.0,3.0,1.0,-1.0],[10.264699256663889,34.795753481376735,889.9999,0.0,3.0,0.0,-1.0],[34.795753481376735,108.97298887515129,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-65.66475429601871,2.6717539013956326,-1860.0,9.0,4.0,0.0,1.0,0.516718443991752],[2.6717539013956326,8.512481097755824,-1808.4766,9.0,4.0,0.0,1.0,0.513769815678499],[8.512481097755824,9.09655381739185,-1074.7924,0.0,4.0,0.0,-1.0,0.47178186447367976],[9.09655381739185,10.264699256663889,0.0,0.0,3.0,1.0,-1.0,0.4102726608592219],[10.264699256663889,34.795753481376735,889.9999,0.0,3.0,0.0,-1.0,0.35383639579898096],[34.795753481376735,108.97298887515129,1860.0,0.0,3.0,0.0,-1.0,0.2923271947843963]]</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -12436,7 +12436,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>[[-67.90541271437728,2.8628022109253237,-1860.0,9.0,3.0,0.0,1.0],[2.8628022109253237,8.860108560527237,-1808.4766,9.0,3.0,0.0,1.0],[8.860108560527237,9.459839195487433,-1074.7924,0.0,3.0,0.0,-1.0],[9.459839195487433,10.65930046540781,0.0,0.0,2.0,1.0,-1.0],[10.65930046540781,33.44906459389509,889.9999,0.0,2.0,0.0,-1.0],[33.44906459389509,111.41404713871998,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-67.90541271437728,2.8628022109253237,-1860.0,9.0,3.0,0.0,1.0,0.3987729779169264],[2.8628022109253237,8.860108560527237,-1808.4766,9.0,3.0,0.0,1.0,0.3958243496036734],[8.860108560527237,9.459839195487433,-1074.7924,0.0,3.0,0.0,-1.0,0.3538363983988541],[9.459839195487433,10.65930046540781,0.0,0.0,2.0,1.0,-1.0,0.2923271947843963],[10.65930046540781,33.44906459389509,889.9999,0.0,2.0,0.0,-1.0,0.23589092972415532],[33.44906459389509,111.41404713871998,1860.0,0.0,2.0,0.0,-1.0,0.17438172870957064]]</t>
         </is>
       </c>
       <c r="C462" t="n">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>[[-71.79027741324822,3.3157473837580653,-1860.0,9.0,2.0,0.0,1.0],[3.3157473837580653,8.451202070732847,-1808.4766,9.0,2.0,0.0,1.0],[8.451202070732847,9.093133906604692,-1074.7924,0.0,2.0,0.0,-1.0],[9.093133906604692,9.73506574247655,0.0,0.0,1.0,1.0,-1.0],[9.73506574247655,33.48654366973494,889.9999,0.0,1.0,0.0,-1.0],[33.48654366973494,120.14734151243448,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-71.79027741324822,3.3157473837580653,-1860.0,9.0,2.0,0.0,1.0,0.28082751184210075],[3.3157473837580653,8.451202070732847,-1808.4766,9.0,2.0,0.0,1.0,0.2778788835288477],[8.451202070732847,9.093133906604692,-1074.7924,0.0,2.0,0.0,-1.0,0.23589093232402844],[9.093133906604692,9.73506574247655,0.0,0.0,1.0,1.0,-1.0,0.1743817287095706],[9.73506574247655,33.48654366973494,889.9999,0.0,1.0,0.0,-1.0,0.11794546364932965],[33.48654366973494,120.14734151243448,1860.0,0.0,1.0,0.0,-1.0,0.05643626263474498]]</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>[[-69.09615317010186,3.201514871311062,-1860.0,9.0,1.0,0.0,1.0],[3.201514871311062,8.762873951419735,-1808.4766,9.0,1.0,0.0,1.0],[8.762873951419735,9.380802738098481,-1074.7924,0.0,1.0,0.0,-1.0],[9.380802738098481,10.616660311455973,0.0,0.0,0.0,1.0,-1.0],[10.616660311455973,11.852517884813452,889.9999,0.0,0.0,0.0,-1.0],[11.852517884813452,115.66455404684226,890.0,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-69.09615317010186,3.201514871311062,-1860.0,9.0,1.0,0.0,1.0,0.1628820457672751],[3.201514871311062,8.762873951419735,-1808.4766,9.0,1.0,0.0,1.0,0.15993341745402212],[8.762873951419735,9.380802738098481,-1074.7924,0.0,1.0,0.0,-1.0,0.11794546624920284],[9.380802738098481,10.616660311455973,0.0,0.0,0.0,1.0,-1.0,0.05643626263474501],[10.616660311455973,11.852517884813452,889.9999,0.0,0.0,0.0,-1.0,-2.425495963798152e-09],[11.852517884813452,115.66455404684226,890.0,0.0,0.0,0.0,-1.0,-8.76665004478916e-09]]</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="F464" s="4" t="inlineStr">
         <is>
-          <t>[5.5613590801,0.6179287867,0,0,0]</t>
+          <t>[5.5613590801,0.6179287867,1.2358575734,0,0]</t>
         </is>
       </c>
     </row>
@@ -12514,7 +12514,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>[[-66.77925686089173,2.813710293499014,-1860.0,9.0,0.0,0.0,1.0],[2.813710293499014,9.301190282467644,-733.6842,9.0,0.0,0.0,1.0],[9.301190282467644,109.56224465743736,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-66.77925686089173,2.813710293499014,-1860.0,9.0,0.0,0.0,1.0,0.10644577436588007],[2.813710293499014,9.301190282467644,-733.6842,9.0,0.0,0.0,1.0,0.04198794243816923],[9.301190282467644,109.56224465743736,0.0,0.0,0.0,1.0,-1.0,-8.76665004478916e-09]]</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -12540,7 +12540,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>[[-67.70725064560375,8.978630625330297,-1860.0,9.0,0.0,0.0,1.0],[8.978630625330297,29.508709075816583,-733.6842,9.0,0.0,0.0,1.0],[29.508709075816583,112.8366745513197,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-67.70725064560375,8.978630625330297,-1860.0,9.0,0.0,0.0,1.0,0.10644577436588007],[8.978630625330297,29.508709075816583,-733.6842,9.0,0.0,0.0,1.0,0.04198794243816923],[29.508709075816583,112.8366745513197,0.0,0.0,0.0,1.0,-1.0,-8.76665004478916e-09]]</t>
         </is>
       </c>
       <c r="C466" t="n">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>[[-67.8849367059337,8.63833168981509,-1860.0,8.0,0.0,0.0,1.0],[8.63833168981509,29.72742140517893,-733.6844,8.0,0.0,0.0,1.0],[29.72742140517893,32.740148507373775,0.0,8.0,8.0,2.0,-1.0],[32.740148507373775,35.15033018912963,227.8499,8.0,8.0,1.0,-1.0],[35.15033018912963,112.27614400531739,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-67.8849367059337,8.63833168981509,-1860.0,8.0,0.0,0.0,1.0,0.2128915574984102],[8.63833168981509,29.72742140517893,-733.6844,8.0,0.0,0.0,1.0,0.1484337370164825],[29.72742140517893,32.740148507373775,0.0,8.0,8.0,2.0,-1.0,0.1064457743658801],[32.740148507373775,35.15033018912963,227.8499,8.0,8.0,1.0,-1.0,0.09199746111286805],[35.15033018912963,112.27614400531739,1678.65,0.0,0.0,0.0,-1.0,-8.766650030911372e-09]]</t>
         </is>
       </c>
       <c r="C467" t="n">
@@ -12592,7 +12592,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>[[-65.45478443348603,8.975870531251232,-1860.0,7.0,0.0,0.0,1.0],[8.975870531251232,29.17023428137375,-733.6844,7.0,0.0,0.0,1.0],[29.17023428137375,32.055143388534105,0.0,7.0,8.0,1.0,-1.0],[32.055143388534105,35.51703431712653,227.8499,7.0,8.0,1.0,-1.0],[35.51703431712653,107.0627801747034,1860.0,7.0,8.0,1.0,-1.0]]</t>
+          <t>[[-65.45478443348603,8.975870531251232,-1860.0,7.0,0.0,0.0,1.0,0.3193373406309403],[8.975870531251232,29.17023428137375,-733.6844,7.0,0.0,0.0,1.0,0.2548795201490126],[29.17023428137375,32.055143388534105,0.0,7.0,8.0,1.0,-1.0,0.2128915574984102],[32.055143388534105,35.51703431712653,227.8499,7.0,8.0,1.0,-1.0,0.19844324424539816],[35.51703431712653,107.0627801747034,1860.0,7.0,8.0,1.0,-1.0,0.09494609142358458]]</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -12618,7 +12618,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>[[-67.72107987391104,9.260212192776237,-1860.0,6.0,0.0,0.0,1.0],[9.260212192776237,30.30978424226103,-733.6844,6.0,0.0,0.0,1.0],[30.30978424226103,33.31686596361601,0.0,6.0,8.0,2.0,-1.0],[33.31686596361601,34.519698652158,227.8499,6.0,8.0,2.0,-1.0],[34.519698652158,112.10240706311626,1860.0,6.0,8.0,2.0,-1.0]]</t>
+          <t>[[-67.72107987391104,9.260212192776237,-1860.0,6.0,0.0,0.0,1.0,0.42578312376347044],[9.260212192776237,30.30978424226103,-733.6844,6.0,0.0,0.0,1.0,0.3613253032815427],[30.30978424226103,33.31686596361601,0.0,6.0,8.0,2.0,-1.0,0.3193373406309403],[33.31686596361601,34.519698652158,227.8499,6.0,8.0,2.0,-1.0,0.3048890273779283],[34.519698652158,112.10240706311626,1860.0,6.0,8.0,2.0,-1.0,0.20139187455611468]]</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>[[-67.78480320162409,8.678263326786237,-1860.0,5.0,0.0,0.0,1.0],[8.678263326786237,29.750761976348144,-733.6844,5.0,0.0,0.0,1.0],[29.750761976348144,33.363190316273034,0.0,5.0,8.0,3.0,-1.0],[33.363190316273034,34.56733309624801,227.8499,5.0,8.0,1.0,-1.0],[34.56733309624801,112.23454240463329,1860.0,5.0,8.0,1.0,-1.0]]</t>
+          <t>[[-67.78480320162409,8.678263326786237,-1860.0,5.0,0.0,0.0,1.0,0.5322289068960004],[8.678263326786237,29.750761976348144,-733.6844,5.0,0.0,0.0,1.0,0.4677710864140728],[29.750761976348144,33.363190316273034,0.0,5.0,8.0,3.0,-1.0,0.4257831237634704],[33.363190316273034,34.56733309624801,227.8499,5.0,8.0,1.0,-1.0,0.41133481051045834],[34.56733309624801,112.23454240463329,1860.0,5.0,8.0,1.0,-1.0,0.30783765768864474]]</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -12670,7 +12670,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>[[-70.47037761047007,8.764244205883031,-1860.0,4.0,0.0,0.0,1.0],[8.764244205883031,32.03155378687562,-733.6844,4.0,0.0,0.0,1.0],[32.03155378687562,35.17578481133407,0.0,4.0,8.0,2.0,-1.0],[35.17578481133407,35.804631016225756,227.8499,4.0,8.0,1.0,-1.0],[35.804631016225756,117.5546376521456,1860.0,4.0,9.0,0.0,-1.0]]</t>
+          <t>[[-70.47037761047007,8.764244205883031,-1860.0,4.0,0.0,0.0,1.0,0.6386746900285307],[8.764244205883031,32.03155378687562,-733.6844,4.0,0.0,0.0,1.0,0.574216869546603],[32.03155378687562,35.17578481133407,0.0,4.0,8.0,2.0,-1.0,0.5322289068960006],[35.17578481133407,35.804631016225756,227.8499,4.0,8.0,1.0,-1.0,0.5177805936429885],[35.804631016225756,117.5546376521456,1860.0,4.0,9.0,0.0,-1.0,0.4142834408211749]]</t>
         </is>
       </c>
       <c r="C471" t="n">
@@ -12696,7 +12696,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>[[-67.88219347520786,8.85975303197769,-1860.0,3.0,0.0,0.0,1.0],[8.85975303197769,31.642518401298403,-733.6844,3.0,0.0,0.0,1.0],[31.642518401298403,35.23979714382273,0.0,3.0,8.0,2.0,-1.0],[35.23979714382273,111.38219719392089,1860.0,3.0,8.0,1.0,-1.0]]</t>
+          <t>[[-67.88219347520786,8.85975303197769,-1860.0,3.0,0.0,0.0,1.0,0.7451204731610608],[8.85975303197769,31.642518401298403,-733.6844,3.0,0.0,0.0,1.0,0.6806626526791332],[31.642518401298403,35.23979714382273,0.0,3.0,8.0,2.0,-1.0,0.6386746900285307],[35.23979714382273,111.38219719392089,1860.0,3.0,8.0,1.0,-1.0,0.5207292239537051]]</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -12722,7 +12722,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>[[-55.84949744234979,8.630352692919402,-1860.0,1.0,0.0,0.0,1.0],[8.630352692919402,30.12363607134246,-733.6844,2.0,0.0,0.0,1.0],[30.12363607134246,33.347628578105926,0.0,2.0,8.0,2.0,-1.0],[33.347628578105926,34.42229274702707,227.8499,2.0,8.0,2.0,-1.0],[34.42229274702707,104.8127958113626,1860.0,1.0,8.0,2.0,-1.0]]</t>
+          <t>[[-55.84949744234979,8.630352692919402,-1860.0,1.0,0.0,0.0,1.0,0.8515662562935908],[8.630352692919402,30.12363607134246,-733.6844,2.0,0.0,0.0,1.0,0.7871084358116632],[30.12363607134246,33.347628578105926,0.0,2.0,8.0,2.0,-1.0,0.7451204731610608],[33.347628578105926,34.42229274702707,227.8499,2.0,8.0,2.0,-1.0,0.7306721599080487],[34.42229274702707,104.8127958113626,1860.0,1.0,8.0,2.0,-1.0,0.6271750070862352]]</t>
         </is>
       </c>
       <c r="C473" t="n">
@@ -12748,7 +12748,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>[[-48.471697308739955,8.819123619529854,-1860.0,1.0,0.0,0.0,1.0],[8.819123619529854,30.73908988773743,-733.6844,1.0,0.0,0.0,1.0],[30.73908988773743,33.72817619703846,0.0,1.0,8.0,2.0,-1.0],[33.72817619703846,36.219081454789325,227.8499,1.0,8.0,1.0,-1.0],[36.219081454789325,100.48443710476154,1860.0,1.0,9.0,0.0,-1.0]]</t>
+          <t>[[-48.471697308739955,8.819123619529854,-1860.0,1.0,0.0,0.0,1.0,0.9580120394261209],[8.819123619529854,30.73908988773743,-733.6844,1.0,0.0,0.0,1.0,0.8935542189441933],[30.73908988773743,33.72817619703846,0.0,1.0,8.0,2.0,-1.0,0.8515662562935908],[33.72817619703846,36.219081454789325,227.8499,1.0,8.0,1.0,-1.0,0.8371179430405787],[36.219081454789325,100.48443710476154,1860.0,1.0,9.0,0.0,-1.0,0.7336207902187653]]</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>[[-35.92269100631418,30.10913481698303,-733.6845,0.0,0.0,0.0,1.0],[30.10913481698303,33.70270356927131,0.0,0.0,8.0,1.0,-1.0],[33.70270356927131,98.3869411104604,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[-35.92269100631418,30.10913481698303,-733.6845,0.0,0.0,0.0,1.0,1.000000007799615],[30.10913481698303,33.70270356927131,0.0,0.0,8.0,1.0,-1.0,0.9580120394261209],[33.70270356927131,98.3869411104604,1860.0,0.0,8.0,1.0,-1.0,0.8400665733512953]]</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>[[-36.84668572579382,33.324379599668475,0.0,0.0,0.0,1.0,1.0],[33.324379599668475,34.229812700642185,890.0,0.0,8.0,0.0,-1.0],[34.229812700642185,98.51556286977541,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-36.84668572579382,33.324379599668475,0.0,0.0,0.0,1.0,1.0,1.000000007799615],[33.324379599668475,34.229812700642185,890.0,0.0,8.0,0.0,-1.0,0.9435637363982199],[34.229812700642185,98.51556286977541,1860.0,0.0,8.0,0.0,-1.0,0.8820545417247894]]</t>
         </is>
       </c>
       <c r="C476" t="n">
@@ -12826,7 +12826,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>[[-33.970965466574846,33.32968683262161,0.0,0.0,0.0,1.0,1.0],[33.32968683262161,94.2003405045063,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[-33.970965466574846,33.32968683262161,0.0,0.0,0.0,1.0,1.0,1.000000007799615],[33.32968683262161,94.2003405045063,1860.0,0.0,8.0,1.0,-1.0,0.8820545417247894]]</t>
         </is>
       </c>
       <c r="C477" t="n">
@@ -12852,7 +12852,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>[[-31.672012366347516,24.534584377274,-1860.0,1.0,8.0,0.0,-1.0],[24.534584377274,26.960768409372776,-1074.7921,0.0,8.0,0.0,-1.0],[26.960768409372776,29.79131644682134,0.0,0.0,7.0,1.0,-1.0],[29.79131644682134,33.834956500319294,890.0001,0.0,7.0,0.0,-1.0],[33.834956500319294,89.23282523324121,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-31.672012366347516,24.534584377274,-1860.0,1.0,8.0,0.0,-1.0,0.9885003248573194],[24.534584377274,26.960768409372776,-1074.7921,0.0,8.0,0.0,-1.0,0.9435637281705724],[26.960768409372776,29.79131644682134,0.0,0.0,7.0,1.0,-1.0,0.8820545417247894],[29.79131644682134,33.834956500319294,890.0001,0.0,7.0,0.0,-1.0,0.8256182639822403],[33.834956500319294,89.23282523324121,1860.0,0.0,7.0,0.0,-1.0,0.7641090756499638]]</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>[[-33.775752609823954,25.719008231301387,-1860.0,1.0,7.0,0.0,-1.0],[25.719008231301387,29.118708850794263,-1074.7921,0.0,7.0,0.0,-1.0],[29.118708850794263,32.51840947028714,0.0,0.0,6.0,1.0,-1.0],[32.51840947028714,33.36833462516036,890.0001,0.0,6.0,0.0,-1.0],[33.36833462516036,93.28805804372232,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[-33.775752609823954,25.719008231301387,-1860.0,1.0,7.0,0.0,-1.0,0.8705548587824938],[25.719008231301387,29.118708850794263,-1074.7921,0.0,7.0,0.0,-1.0,0.8256182620957468],[29.118708850794263,32.51840947028714,0.0,0.0,6.0,1.0,-1.0,0.7641090756499638],[32.51840947028714,33.36833462516036,890.0001,0.0,6.0,0.0,-1.0,0.7076727979074147],[33.36833462516036,93.28805804372232,1860.0,0.0,6.0,0.0,-1.0,0.6461636095751382]]</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>[[-34.39255287288686,24.68227779888568,-1860.0,1.0,6.0,1.0,-1.0],[24.68227779888568,27.700699804012743,-1074.7921,0.0,6.0,0.0,-1.0],[27.700699804012743,30.7191218091398,0.0,0.0,5.0,1.0,-1.0],[30.7191218091398,33.737543814266864,890.0001,0.0,5.0,0.0,-1.0],[33.737543814266864,94.53718706039774,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-34.39255287288686,24.68227779888568,-1860.0,1.0,6.0,1.0,-1.0,0.7526093927076682],[24.68227779888568,27.700699804012743,-1074.7921,0.0,6.0,0.0,-1.0,0.7076727960209213],[27.700699804012743,30.7191218091398,0.0,0.0,5.0,1.0,-1.0,0.6461636095751382],[30.7191218091398,33.737543814266864,890.0001,0.0,5.0,0.0,-1.0,0.5897273318325891],[33.737543814266864,94.53718706039774,1860.0,0.0,5.0,0.0,-1.0,0.5282181435003126]]</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -12930,7 +12930,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>[[-27.053391803393485,25.69902034864805,-1860.0,1.0,5.0,1.0,-1.0],[25.69902034864805,29.287619814773326,-1074.7921,0.0,5.0,0.0,-1.0],[29.287619814773326,32.158499387673544,0.0,0.0,4.0,1.0,-1.0],[32.158499387673544,33.95279912073619,890.0001,0.0,4.0,0.0,-1.0],[33.95279912073619,80.24573223375222,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-27.053391803393485,25.69902034864805,-1860.0,1.0,5.0,1.0,-1.0,0.6346639266328427],[25.69902034864805,29.287619814773326,-1074.7921,0.0,5.0,0.0,-1.0,0.5897273299460957],[29.287619814773326,32.158499387673544,0.0,0.0,4.0,1.0,-1.0,0.5282181435003126],[32.158499387673544,33.95279912073619,890.0001,0.0,4.0,0.0,-1.0,0.47178186575776343],[33.95279912073619,80.24573223375222,1860.0,0.0,4.0,0.0,-1.0,0.41027267742548695]]</t>
         </is>
       </c>
       <c r="C481" t="n">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>[[-28.1123048482271,24.886842948436442,-1860.0,1.0,4.0,1.0,-1.0],[24.886842948436442,28.222453648925754,-1074.7921,0.0,4.0,0.0,-1.0],[28.222453648925754,31.18744093824959,0.0,0.0,3.0,1.0,-1.0],[31.18744093824959,32.66993458291151,890.0001,0.0,3.0,0.0,-1.0],[32.66993458291151,82.70409509025122,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-28.1123048482271,24.886842948436442,-1860.0,1.0,4.0,1.0,-1.0,0.5167184605580171],[24.886842948436442,28.222453648925754,-1074.7921,0.0,4.0,0.0,-1.0,0.47178186387127014],[28.222453648925754,31.18744093824959,0.0,0.0,3.0,1.0,-1.0,0.410272677425487],[31.18744093824959,32.66993458291151,890.0001,0.0,3.0,0.0,-1.0,0.35383639968293784],[32.66993458291151,82.70409509025122,1860.0,0.0,3.0,0.0,-1.0,0.29232721135066136]]</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>[[-23.33014353398589,25.45817667541464,-1860.0,1.0,3.0,0.0,-1.0],[25.45817667541464,27.705007211373875,-1074.7921,0.0,3.0,0.0,-1.0],[27.705007211373875,30.914765119887065,0.0,0.0,2.0,1.0,-1.0],[30.914765119887065,33.80354723754894,890.0001,0.0,2.0,0.0,-1.0],[33.80354723754894,72.64161793055858,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-23.33014353398589,25.45817667541464,-1860.0,1.0,3.0,0.0,-1.0,0.3987729944831914],[25.45817667541464,27.705007211373875,-1074.7921,0.0,3.0,0.0,-1.0,0.35383639779644444],[27.705007211373875,30.914765119887065,0.0,0.0,2.0,1.0,-1.0,0.2923272113506613],[30.914765119887065,33.80354723754894,890.0001,0.0,2.0,0.0,-1.0,0.23589093360811217],[33.80354723754894,72.64161793055858,1860.0,0.0,2.0,0.0,-1.0,0.17438174527583566]]</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -13008,7 +13008,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>[[-22.04992675660945,24.614717383288983,-1860.0,1.0,2.0,1.0,-1.0],[24.614717383288983,29.52678518748882,-1074.7921,0.0,2.0,0.0,-1.0],[29.52678518748882,32.59682756511371,0.0,0.0,1.0,1.0,-1.0],[32.59682756511371,32.903831802876205,890.0001,0.0,1.0,0.0,-1.0],[32.903831802876205,69.74434033437497,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-22.04992675660945,24.614717383288983,-1860.0,1.0,2.0,1.0,-1.0,0.2808275284083658],[24.614717383288983,29.52678518748882,-1074.7921,0.0,2.0,0.0,-1.0,0.23589093172161882],[29.52678518748882,32.59682756511371,0.0,0.0,1.0,1.0,-1.0,0.1743817452758357],[32.59682756511371,32.903831802876205,890.0001,0.0,1.0,0.0,-1.0,0.11794546753328655],[32.903831802876205,69.74434033437497,1860.0,0.0,1.0,0.0,-1.0,0.05643627920101006]]</t>
         </is>
       </c>
       <c r="C484" t="n">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>[[-21.416828612183366,25.315679868627626,-1860.0,1.0,1.0,1.0,-1.0],[25.315679868627626,29.53668063463636,-1074.7921,0.0,1.0,0.0,-1.0],[29.53668063463636,32.85318123650037,0.0,0.0,0.0,1.0,-1.0],[32.85318123650037,36.47118189307929,890.0001,0.0,0.0,0.0,-1.0],[36.47118189307929,68.73168774757463,890.0002,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-21.416828612183366,25.315679868627626,-1860.0,1.0,1.0,1.0,-1.0,0.16288206233354013],[25.315679868627626,29.53668063463636,-1074.7921,0.0,1.0,0.0,-1.0,0.11794546564679315],[29.53668063463636,32.85318123650037,0.0,0.0,0.0,1.0,-1.0,0.05643627920101003],[32.85318123650037,36.47118189307929,890.0001,0.0,0.0,0.0,-1.0,1.4584608798440257e-09],[36.47118189307929,68.73168774757463,890.0002,0.0,0.0,0.0,-1.0,-4.882693208085875e-09]]</t>
         </is>
       </c>
       <c r="C485" t="n">
@@ -13050,7 +13050,7 @@
       </c>
       <c r="F485" s="4" t="inlineStr">
         <is>
-          <t>[0,4.221000766,0,0,0]</t>
+          <t>[0,4.221000766,3.3165006019,0,0]</t>
         </is>
       </c>
     </row>
@@ -13060,7 +13060,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>[[-23.096130627964016,24.949459163045695,-1860.0,1.0,0.0,0.0,-1.0],[24.949459163045695,72.04050081251216,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-23.096130627964016,24.949459163045695,-1860.0,1.0,0.0,0.0,-1.0,0.10644578459099101],[24.949459163045695,72.04050081251216,0.0,0.0,0.0,1.0,-1.0,1.45846088678292e-09]]</t>
         </is>
       </c>
       <c r="C486" t="n">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>[[-24.326399002130927,24.784867701718774,-1860.0,1.0,0.0,0.0,-1.0],[24.784867701718774,72.92041387502842,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-24.326399002130927,24.784867701718774,-1860.0,1.0,0.0,0.0,-1.0,0.10644578459099101],[24.784867701718774,72.92041387502842,0.0,0.0,0.0,1.0,-1.0,1.45846088678292e-09]]</t>
         </is>
       </c>
       <c r="C487" t="n">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>[[-20.71427560582122,15.465666775463745,-1860.0,8.0,0.0,1.0,1.0],[15.465666775463745,16.355337489757638,-733.6842,9.0,0.0,1.0,1.0],[16.355337489757638,67.9562389188034,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-20.71427560582122,15.465666775463745,-1860.0,8.0,0.0,1.0,1.0,0.10644578459099101],[15.465666775463745,16.355337489757638,-733.6842,9.0,0.0,1.0,1.0,0.04198795266328016],[16.355337489757638,67.9562389188034,0.0,0.0,0.0,1.0,-1.0,1.45846088678292e-09]]</t>
         </is>
       </c>
       <c r="C488" t="n">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>[[-19.139755032761002,15.207521508542733,-1860.0,8.0,0.0,0.0,1.0],[15.207521508542733,18.304407098332412,-733.6842,9.0,0.0,0.0,1.0],[18.304407098332412,65.03922599879488,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-19.139755032761002,15.207521508542733,-1860.0,8.0,0.0,0.0,1.0,0.10644578459099101],[15.207521508542733,18.304407098332412,-733.6842,9.0,0.0,0.0,1.0,0.04198795266328016],[18.304407098332412,65.03922599879488,0.0,0.0,0.0,1.0,-1.0,1.45846088678292e-09]]</t>
         </is>
       </c>
       <c r="C489" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>[[-20.864083348160932,16.027313694464233,-1860.0,8.0,0.0,0.0,1.0],[16.027313694464233,17.502969576169242,-733.6842,8.0,0.0,0.0,1.0],[17.502969576169242,19.568887810556248,0.0,8.0,0.0,1.0,1.0],[19.568887810556248,30.783872511514303,1016.5,9.0,0.0,0.0,1.0],[30.783872511514303,67.38013837779846,1678.6501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-20.864083348160932,16.027313694464233,-1860.0,8.0,0.0,0.0,1.0,0.2128915677235211],[16.027313694464233,17.502969576169242,-733.6842,8.0,0.0,0.0,1.0,0.14843373579581026],[17.502969576169242,19.568887810556248,0.0,8.0,0.0,1.0,1.0,0.106445784590991],[19.568887810556248,30.783872511514303,1016.5,9.0,0.0,0.0,1.0,0.041987953265689784],[30.783872511514303,67.38013837779846,1678.6501,0.0,0.0,0.0,-1.0,-4.882693221963663e-09]]</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -13190,7 +13190,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>[[-25.787079442132335,15.52642091000747,-1860.0,7.0,0.0,0.0,1.0],[15.52642091000747,18.454149281418953,-733.6842,7.0,0.0,0.0,1.0],[18.454149281418953,20.40596819569328,0.0,7.0,0.0,1.0,1.0],[20.40596819569328,29.189153309927722,1016.5,8.0,0.0,0.0,1.0],[29.189153309927722,71.4785631192047,1860.0,8.0,9.0,2.0,-1.0]]</t>
+          <t>[[-25.787079442132335,15.52642091000747,-1860.0,7.0,0.0,0.0,1.0,0.3193373508560512],[15.52642091000747,18.454149281418953,-733.6842,7.0,0.0,0.0,1.0,0.2548795189283404],[18.454149281418953,20.40596819569328,0.0,7.0,0.0,1.0,1.0,0.2128915677235211],[20.40596819569328,29.189153309927722,1016.5,8.0,0.0,0.0,1.0,0.14843373639821988],[29.189153309927722,71.4785631192047,1860.0,8.0,9.0,2.0,-1.0,0.09494610164869548]]</t>
         </is>
       </c>
       <c r="C491" t="n">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>[[-28.35829762481251,15.505948333682728,-1860.0,5.0,0.0,0.0,1.0],[15.505948333682728,17.514997766896254,-733.6842,5.0,0.0,0.0,1.0],[17.514997766896254,19.524047200109774,0.0,5.0,0.0,1.0,1.0],[19.524047200109774,29.234452793975134,1016.5,7.0,0.0,0.0,1.0],[29.234452793975134,71.75933246366137,1860.0,7.0,9.0,2.0,-1.0]]</t>
+          <t>[[-28.35829762481251,15.505948333682728,-1860.0,5.0,0.0,0.0,1.0,0.4257831339885813],[15.505948333682728,17.514997766896254,-733.6842,5.0,0.0,0.0,1.0,0.3613253020608705],[17.514997766896254,19.524047200109774,0.0,5.0,0.0,1.0,1.0,0.3193373508560512],[19.524047200109774,29.234452793975134,1016.5,7.0,0.0,0.0,1.0,0.25487951953075],[29.234452793975134,71.75933246366137,1860.0,7.0,9.0,2.0,-1.0,0.20139188478122555]]</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -13242,7 +13242,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>[[-30.326751199957208,15.850992285907992,-1860.0,5.0,0.0,0.0,1.0],[15.850992285907992,17.260999720590895,-733.6842,4.0,0.0,0.0,1.0],[17.260999720590895,19.023509013944526,0.0,4.0,0.0,1.0,1.0],[19.023509013944526,29.598564774066332,1016.5,5.0,0.0,0.0,1.0],[29.598564774066332,75.07130454259007,1860.0,6.0,9.0,2.0,-1.0]]</t>
+          <t>[[-30.326751199957208,15.850992285907992,-1860.0,5.0,0.0,0.0,1.0,0.5322289171211114],[15.850992285907992,17.260999720590895,-733.6842,4.0,0.0,0.0,1.0,0.4677710851934006],[17.260999720590895,19.023509013944526,0.0,4.0,0.0,1.0,1.0,0.4257831339885813],[19.023509013944526,29.598564774066332,1016.5,5.0,0.0,0.0,1.0,0.3613253026632801],[29.598564774066332,75.07130454259007,1860.0,6.0,9.0,2.0,-1.0,0.30783766791375566]]</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -13268,7 +13268,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>[[-28.74912447121622,15.790147306982966,-1860.0,4.0,0.0,0.0,1.0],[15.790147306982966,18.85009727647757,-733.6842,3.0,0.0,0.0,1.0],[18.85009727647757,20.8900639228073,0.0,3.0,0.0,1.0,1.0],[20.8900639228073,30.40990827234606,1016.5,4.0,0.0,0.0,1.0],[30.40990827234606,72.9092134042155,1860.0,4.0,9.0,1.0,-1.0]]</t>
+          <t>[[-28.74912447121622,15.790147306982966,-1860.0,4.0,0.0,0.0,1.0,0.6386747002536415],[15.790147306982966,18.85009727647757,-733.6842,3.0,0.0,0.0,1.0,0.5742168683259307],[18.85009727647757,20.8900639228073,0.0,3.0,0.0,1.0,1.0,0.5322289171211114],[20.8900639228073,30.40990827234606,1016.5,4.0,0.0,0.0,1.0,0.4677710857958102],[30.40990827234606,72.9092134042155,1860.0,4.0,9.0,1.0,-1.0,0.4142834510462858]]</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -13294,7 +13294,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>[[-27.982260036151196,14.842589378172718,-1860.0,3.0,0.0,0.0,1.0],[14.842589378172718,18.188280738666776,-733.6842,2.0,0.0,0.0,1.0],[18.188280738666776,19.861126418913805,0.0,2.0,0.0,1.0,1.0],[19.861126418913805,30.232769636445376,1016.5,3.0,0.0,0.0,1.0],[30.232769636445376,72.05391164262107,1860.0,3.0,9.0,1.0,-1.0]]</t>
+          <t>[[-27.982260036151196,14.842589378172718,-1860.0,3.0,0.0,0.0,1.0,0.7451204833861715],[14.842589378172718,18.188280738666776,-733.6842,2.0,0.0,0.0,1.0,0.6806626514584607],[18.188280738666776,19.861126418913805,0.0,2.0,0.0,1.0,1.0,0.6386747002536415],[19.861126418913805,30.232769636445376,1016.5,3.0,0.0,0.0,1.0,0.5742168689283402],[30.232769636445376,72.05391164262107,1860.0,3.0,9.0,1.0,-1.0,0.5207292341788159]]</t>
         </is>
       </c>
       <c r="C495" t="n">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>[[-31.58329688268858,18.179540046051592,-1860.0,1.0,0.0,0.0,1.0],[18.179540046051592,29.826161454905673,0.0,2.0,0.0,1.0,1.0],[29.826161454905673,30.179089376386102,890.0,2.0,8.0,3.0,-1.0],[30.179089376386102,73.94215163995902,1860.0,2.0,8.0,3.0,-1.0]]</t>
+          <t>[[-31.58329688268858,18.179540046051592,-1860.0,1.0,0.0,0.0,1.0,0.7871084345909909],[18.179540046051592,29.826161454905673,0.0,2.0,0.0,1.0,1.0,0.6806626514584607],[29.826161454905673,30.179089376386102,890.0,2.0,8.0,3.0,-1.0,0.6242263800570657],[30.179089376386102,73.94215163995902,1860.0,2.0,8.0,3.0,-1.0,0.5627171853836351]]</t>
         </is>
       </c>
       <c r="C496" t="n">
@@ -13346,7 +13346,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>[[-31.771665116489185,17.900059231648637,-1860.0,1.0,0.0,0.0,1.0],[17.900059231648637,27.05938428875206,0.0,2.0,0.0,1.0,1.0],[27.05938428875206,29.877638152476198,0.0,0.0,0.0,1.0,1.0],[29.877638152476198,30.934483351372744,890.0,1.0,8.0,1.0,-1.0],[30.934483351372744,73.56057304020024,1860.0,1.0,8.0,1.0,-1.0]]</t>
+          <t>[[-31.771665116489185,17.900059231648637,-1860.0,1.0,0.0,0.0,1.0,0.893554217723521],[17.900059231648637,27.05938428875206,0.0,2.0,0.0,1.0,1.0,0.7871084345909909],[27.05938428875206,29.877638152476198,0.0,0.0,0.0,1.0,1.0,0.7871084345909909],[29.877638152476198,30.934483351372744,890.0,1.0,8.0,1.0,-1.0,0.7306721631895958],[30.934483351372744,73.56057304020024,1860.0,1.0,8.0,1.0,-1.0,0.6691629685161653]]</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -13362,7 +13362,7 @@
       </c>
       <c r="F497" s="4" t="inlineStr">
         <is>
-          <t>[0,0,9.1593250571,0,1.0568451989]</t>
+          <t>[0,0,11.9775789208,0,1.0568451989]</t>
         </is>
       </c>
     </row>
@@ -13372,7 +13372,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>[[-31.433578002776393,-0.05832799770562147,-1860.0,1.0,0.0,0.0,1.0],[-0.05832799770562147,18.97834054469687,-1860.0,0.0,0.0,0.0,1.0],[18.97834054469687,29.554267512698253,0.0,0.0,0.0,1.0,1.0],[29.554267512698253,30.259329310565015,890.0,0.0,8.0,3.0,-1.0],[30.259329310565015,73.97316077830408,1860.0,1.0,8.0,3.0,-1.0]]</t>
+          <t>[[-31.433578002776393,-0.05832799770562147,-1860.0,1.0,0.0,0.0,1.0,1.000000000856051],[-0.05832799770562147,18.97834054469687,-1860.0,0.0,0.0,0.0,1.0,1.000000000856051],[18.97834054469687,29.554267512698253,0.0,0.0,0.0,1.0,1.0,0.893554217723521],[29.554267512698253,30.259329310565015,890.0,0.0,8.0,3.0,-1.0,0.8371179463221259],[30.259329310565015,73.97316077830408,1860.0,1.0,8.0,3.0,-1.0,0.7756087516486954]]</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="F498" s="4" t="inlineStr">
         <is>
-          <t>[0,0,0,0,0.7050617979]</t>
+          <t>[0,0,10.575926968,0,0.7050617979]</t>
         </is>
       </c>
     </row>
@@ -13398,7 +13398,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>[[-30.569961219741913,31.085741027845103,0.0,0.0,0.0,1.0,1.0],[31.085741027845103,71.8470108470832,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[-30.569961219741913,31.085741027845103,0.0,0.0,0.0,1.0,1.0,1.000000000856051],[31.085741027845103,71.8470108470832,1860.0,0.0,8.0,3.0,-1.0,0.8820545347812254]]</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>[[-31.10588079332176,29.27849134663594,0.0,0.0,0.0,1.0,1.0],[29.27849134663594,29.62552796812995,890.0,0.0,8.0,0.0,-1.0],[29.62552796812995,72.65806903338716,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-31.10588079332176,29.27849134663594,0.0,0.0,0.0,1.0,1.0,1.000000000856051],[29.27849134663594,29.62552796812995,890.0,0.0,8.0,0.0,-1.0,0.9435637294546559],[29.62552796812995,72.65806903338716,1860.0,0.0,8.0,0.0,-1.0,0.8820545347812254]]</t>
         </is>
       </c>
       <c r="C500" t="n">
@@ -13450,7 +13450,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>[[-28.91807686483798,25.499165353010085,-1860.0,1.0,8.0,0.0,-1.0],[25.499165353010085,26.48260948947722,-1074.7922,0.0,8.0,1.0,-1.0],[26.48260948947722,29.432941898878617,0.0,0.0,7.0,2.0,-1.0],[29.432941898878617,29.76075661103433,890.0,0.0,7.0,2.0,-1.0],[29.76075661103433,69.09852206971968,1860.0,0.0,7.0,2.0,-1.0]]</t>
+          <t>[[-28.91807686483798,25.499165353010085,-1860.0,1.0,8.0,0.0,-1.0,0.9885003179137555],[25.499165353010085,26.48260948947722,-1074.7922,0.0,8.0,1.0,-1.0,0.9435637269499001],[26.48260948947722,29.432941898878617,0.0,0.0,7.0,2.0,-1.0,0.8820545347812254],[29.432941898878617,29.76075661103433,890.0,0.0,7.0,2.0,-1.0,0.8256182633798304],[29.76075661103433,69.09852206971968,1860.0,0.0,7.0,2.0,-1.0,0.7641090687063998]]</t>
         </is>
       </c>
       <c r="C501" t="n">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>[[-28.66832059664743,26.356756277247857,-1860.0,1.0,7.0,0.0,-1.0],[26.356756277247857,29.269848582336433,0.0,0.0,6.0,2.0,-1.0],[29.269848582336433,29.917202427911672,890.0,0.0,6.0,0.0,-1.0],[29.917202427911672,68.11107931685075,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[-28.66832059664743,26.356756277247857,-1860.0,1.0,7.0,0.0,-1.0,0.8705548518389299],[26.356756277247857,29.269848582336433,0.0,0.0,6.0,2.0,-1.0,0.7641090687063998],[29.269848582336433,29.917202427911672,890.0,0.0,6.0,0.0,-1.0,0.7076727973050048],[29.917202427911672,68.11107931685075,1860.0,0.0,6.0,0.0,-1.0,0.6461636026315742]]</t>
         </is>
       </c>
       <c r="C502" t="n">
@@ -13502,7 +13502,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>[[-28.749647745304006,26.005830906359545,-1860.0,1.0,6.0,0.0,-1.0],[26.005830906359545,26.331756374524208,-1074.7922,0.0,6.0,0.0,-1.0],[26.331756374524208,29.265085588006183,0.0,0.0,5.0,1.0,-1.0],[29.265085588006183,29.591011056170853,890.0,0.0,5.0,1.0,-1.0],[29.591011056170853,68.70206723593053,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[-28.749647745304006,26.005830906359545,-1860.0,1.0,6.0,0.0,-1.0,0.7526093857641043],[26.005830906359545,26.331756374524208,-1074.7922,0.0,6.0,0.0,-1.0,0.7076727948002489],[26.331756374524208,29.265085588006183,0.0,0.0,5.0,1.0,-1.0,0.6461636026315742],[29.265085588006183,29.591011056170853,890.0,0.0,5.0,1.0,-1.0,0.5897273312301792],[29.591011056170853,68.70206723593053,1860.0,0.0,5.0,1.0,-1.0,0.5282181365567487]]</t>
         </is>
       </c>
       <c r="C503" t="n">
@@ -13528,7 +13528,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>[[-26.637875772114803,26.05540104289644,-1860.0,1.0,5.0,0.0,-1.0],[26.05540104289644,26.664571873127784,-1074.7922,0.0,5.0,1.0,-1.0],[26.664571873127784,29.405840609168834,0.0,0.0,4.0,2.0,-1.0],[29.405840609168834,30.31959685451585,890.0,0.0,4.0,0.0,-1.0],[30.31959685451585,64.43316334747112,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-26.637875772114803,26.05540104289644,-1860.0,1.0,5.0,0.0,-1.0,0.6346639196892787],[26.05540104289644,26.664571873127784,-1074.7922,0.0,5.0,1.0,-1.0,0.5897273287254233],[26.664571873127784,29.405840609168834,0.0,0.0,4.0,2.0,-1.0,0.5282181365567487],[29.405840609168834,30.31959685451585,890.0,0.0,4.0,0.0,-1.0,0.4717818651553536],[30.31959685451585,64.43316334747112,1860.0,0.0,4.0,0.0,-1.0,0.410272670481923]]</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -13554,7 +13554,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>[[-25.1868575292119,26.27372490143697,-1860.0,1.0,4.0,0.0,-1.0],[26.27372490143697,26.855200409127917,-1074.7922,0.0,4.0,1.0,-1.0],[26.855200409127917,29.762577947582656,0.0,0.0,3.0,2.0,-1.0],[29.762577947582656,61.743730870584784,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[-25.1868575292119,26.27372490143697,-1860.0,1.0,4.0,0.0,-1.0,0.5167184536144531],[26.27372490143697,26.855200409127917,-1074.7922,0.0,4.0,1.0,-1.0,0.4717818626505977],[26.855200409127917,29.762577947582656,0.0,0.0,3.0,2.0,-1.0,0.410272670481923],[29.762577947582656,61.743730870584784,1860.0,0.0,3.0,2.0,-1.0,0.29232720440709736]]</t>
         </is>
       </c>
       <c r="C505" t="n">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>[[-25.40482964349006,25.61284969984812,-1860.0,1.0,3.0,0.0,-1.0],[25.61284969984812,26.48743848859106,-1074.7922,0.0,3.0,0.0,-1.0],[26.48743848859106,29.402734451067523,0.0,0.0,2.0,1.0,-1.0],[29.402734451067523,29.985793643562822,890.0,0.0,2.0,0.0,-1.0],[29.985793643562822,61.76251963455632,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-25.40482964349006,25.61284969984812,-1860.0,1.0,3.0,0.0,-1.0,0.39877298753962753],[25.61284969984812,26.48743848859106,-1074.7922,0.0,3.0,0.0,-1.0,0.3538363965757721],[26.48743848859106,29.402734451067523,0.0,0.0,2.0,1.0,-1.0,0.2923272044070974],[29.402734451067523,29.985793643562822,890.0,0.0,2.0,0.0,-1.0,0.23589093300570235],[29.985793643562822,61.76251963455632,1860.0,0.0,2.0,0.0,-1.0,0.17438173833227177]]</t>
         </is>
       </c>
       <c r="C506" t="n">
@@ -13606,7 +13606,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>[[-30.82005360248547,26.45444004282518,-1860.0,1.0,2.0,0.0,-1.0],[26.45444004282518,29.559683674197448,0.0,0.0,1.0,2.0,-1.0],[29.559683674197448,72.3430403731042,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-30.82005360248547,26.45444004282518,-1860.0,1.0,2.0,0.0,-1.0,0.28082752146480183],[26.45444004282518,29.559683674197448,0.0,0.0,1.0,2.0,-1.0,0.1743817383322717],[29.559683674197448,72.3430403731042,1860.0,0.0,1.0,0.0,-1.0,0.05643627225744606]]</t>
         </is>
       </c>
       <c r="C507" t="n">
@@ -13632,7 +13632,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>[[-27.8291320847408,26.69405831477504,-1860.0,1.0,1.0,0.0,-1.0],[26.69405831477504,27.32438421534748,-1074.7922,0.0,1.0,1.0,-1.0],[27.32438421534748,30.476013718209664,0.0,0.0,0.0,2.0,-1.0],[30.476013718209664,32.99731732049941,890.0,0.0,0.0,0.0,-1.0],[32.99731732049941,66.4045900508386,890.0001,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-27.8291320847408,26.69405831477504,-1860.0,1.0,1.0,0.0,-1.0,0.1628820553899762],[26.69405831477504,27.32438421534748,-1074.7922,0.0,1.0,1.0,-1.0,0.11794546442612078],[27.32438421534748,30.476013718209664,0.0,0.0,0.0,2.0,-1.0,0.05643627225744609],[30.476013718209664,32.99731732049941,890.0,0.0,0.0,0.0,-1.0,8.56051035613703e-10],[32.99731732049941,66.4045900508386,890.0001,0.0,0.0,0.0,-1.0,-5.485103059255092e-09]]</t>
         </is>
       </c>
       <c r="C508" t="n">
@@ -13658,7 +13658,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>[[-28.74645912966488,25.322832441394073,-1860.0,1.0,1.0,0.0,-1.0],[25.322832441394073,26.94167350639584,-1074.7922,0.0,1.0,0.0,-1.0],[26.94167350639584,29.85558742339902,0.0,0.0,0.0,1.0,-1.0],[29.85558742339902,32.769501340402186,890.0,0.0,0.0,0.0,-1.0],[32.769501340402186,68.06023655744067,890.0001,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-28.74645912966488,25.322832441394073,-1860.0,1.0,1.0,0.0,-1.0,0.1628820553899762],[25.322832441394073,26.94167350639584,-1074.7922,0.0,1.0,0.0,-1.0,0.11794546442612078],[26.94167350639584,29.85558742339902,0.0,0.0,0.0,1.0,-1.0,0.05643627225744609],[29.85558742339902,32.769501340402186,890.0,0.0,0.0,0.0,-1.0,8.56051035613703e-10],[32.769501340402186,68.06023655744067,890.0001,0.0,0.0,0.0,-1.0,-5.485103059255092e-09]]</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -13674,7 +13674,7 @@
       </c>
       <c r="F509" s="4" t="inlineStr">
         <is>
-          <t>[0,1.618841065,0,0,0]</t>
+          <t>[0,1.618841065,2.913913917,0,0]</t>
         </is>
       </c>
     </row>
@@ -13684,7 +13684,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>[[-29.154198349967754,18.891778189286722,-1860.0,1.0,1.0,0.0,-1.0],[18.891778189286722,24.1934031867217,-1074.7922,0.0,1.0,0.0,-1.0],[24.1934031867217,26.844215685439185,0.0,0.0,0.0,1.0,-1.0],[26.844215685439185,29.82637974649636,890.0,0.0,0.0,0.0,-1.0],[29.82637974649636,69.91991878959837,890.0001,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-29.154198349967754,18.891778189286722,-1860.0,1.0,1.0,0.0,-1.0,0.1628820553899762],[18.891778189286722,24.1934031867217,-1074.7922,0.0,1.0,0.0,-1.0,0.11794546442612078],[24.1934031867217,26.844215685439185,0.0,0.0,0.0,1.0,-1.0,0.05643627225744609],[26.844215685439185,29.82637974649636,890.0,0.0,0.0,0.0,-1.0,8.56051035613703e-10],[29.82637974649636,69.91991878959837,890.0001,0.0,0.0,0.0,-1.0,-5.485103059255092e-09]]</t>
         </is>
       </c>
       <c r="C510" t="n">
@@ -13700,7 +13700,7 @@
       </c>
       <c r="F510" s="4" t="inlineStr">
         <is>
-          <t>[0,5.3016249974,0,0,0]</t>
+          <t>[0,5.3016249974,2.6508124987,0,0]</t>
         </is>
       </c>
     </row>
@@ -13710,7 +13710,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>[[-31.100509753778272,18.379041313644873,-1860.0,1.0,0.0,0.0,-1.0],[18.379041313644873,73.085305521993,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-31.100509753778272,18.379041313644873,-1860.0,1.0,0.0,0.0,-1.0,0.10644578398858115],[18.379041313644873,73.085305521993,0.0,0.0,0.0,1.0,-1.0,8.56051035613703e-10]]</t>
         </is>
       </c>
       <c r="C511" t="n">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>[[-28.850245855458876,16.1151221970074,-1860.0,9.0,0.0,1.0,1.0],[16.1151221970074,17.09263019814797,-733.6842,9.0,0.0,1.0,1.0],[17.09263019814797,68.57471825821804,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-28.850245855458876,16.1151221970074,-1860.0,9.0,0.0,1.0,1.0,0.10644578398858115],[16.1151221970074,17.09263019814797,-733.6842,9.0,0.0,1.0,1.0,0.04198795206087031],[17.09263019814797,68.57471825821804,0.0,0.0,0.0,1.0,-1.0,8.56051035613703e-10]]</t>
         </is>
       </c>
       <c r="C512" t="n">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>[[-29.42046271971215,17.14822321903124,-1860.0,9.0,0.0,0.0,1.0],[17.14822321903124,20.45096690263006,-733.6842,9.0,0.0,0.0,1.0],[20.45096690263006,69.33157341989264,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-29.42046271971215,17.14822321903124,-1860.0,9.0,0.0,0.0,1.0,0.10644578398858115],[17.14822321903124,20.45096690263006,-733.6842,9.0,0.0,0.0,1.0,0.04198795206087031],[20.45096690263006,69.33157341989264,0.0,0.0,0.0,1.0,-1.0,8.56051035613703e-10]]</t>
         </is>
       </c>
       <c r="C513" t="n">
@@ -13788,7 +13788,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>[[-26.75872381129966,18.06282879573594,-1860.0,8.0,0.0,0.0,1.0],[18.06282879573594,19.9048104097237,-733.6842,8.0,0.0,0.0,1.0],[19.9048104097237,22.053788959376092,0.0,8.0,0.0,1.0,1.0],[22.053788959376092,30.649703157985662,1016.5,9.0,0.0,0.0,1.0],[30.649703157985662,65.03335995242392,1678.6501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-26.75872381129966,18.06282879573594,-1860.0,8.0,0.0,0.0,1.0,0.2128915671211112],[18.06282879573594,19.9048104097237,-733.6842,8.0,0.0,0.0,1.0,0.14843373519340036],[19.9048104097237,22.053788959376092,0.0,8.0,0.0,1.0,1.0,0.1064457839885811],[22.053788959376092,30.649703157985662,1016.5,9.0,0.0,0.0,1.0,0.041987952663279884],[30.649703157985662,65.03335995242392,1678.6501,0.0,0.0,0.0,-1.0,-5.485103121705137e-09]]</t>
         </is>
       </c>
       <c r="C514" t="n">
@@ -13814,7 +13814,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>[[-26.95527576192014,17.86558261925981,-1860.0,7.0,0.0,0.0,1.0],[17.86558261925981,20.647566932574428,-733.6842,7.0,0.0,0.0,1.0],[20.647566932574428,22.81133250959691,0.0,7.0,0.0,1.0,1.0],[22.81133250959691,29.61173860881042,1016.5,8.0,0.0,0.0,1.0],[29.61173860881042,65.46842531375438,1860.0,8.0,9.0,2.0,-1.0]]</t>
+          <t>[[-26.95527576192014,17.86558261925981,-1860.0,7.0,0.0,0.0,1.0,0.3193373502536414],[17.86558261925981,20.647566932574428,-733.6842,7.0,0.0,0.0,1.0,0.2548795183259306],[20.647566932574428,22.81133250959691,0.0,7.0,0.0,1.0,1.0,0.2128915671211113],[22.81133250959691,29.61173860881042,1016.5,8.0,0.0,0.0,1.0,0.1484337357958101],[29.61173860881042,65.46842531375438,1860.0,8.0,9.0,2.0,-1.0,0.09494610104628566]]</t>
         </is>
       </c>
       <c r="C515" t="n">
@@ -13840,7 +13840,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>[[-27.264397509904832,17.207083681817224,-1860.0,6.0,0.0,0.0,1.0],[17.207083681817224,20.627966850411234,-733.6842,5.0,0.0,0.0,1.0],[20.627966850411234,22.80489250315287,0.0,6.0,0.0,1.0,1.0],[22.80489250315287,29.95764821930397,1016.5,7.0,0.0,0.0,1.0],[29.95764821930397,65.72142680005948,1860.0,7.0,9.0,2.0,-1.0]]</t>
+          <t>[[-27.264397509904832,17.207083681817224,-1860.0,6.0,0.0,0.0,1.0,0.4257831333861715],[17.207083681817224,20.627966850411234,-733.6842,5.0,0.0,0.0,1.0,0.3613253014584607],[20.627966850411234,22.80489250315287,0.0,6.0,0.0,1.0,1.0,0.3193373502536414],[22.80489250315287,29.95764821930397,1016.5,7.0,0.0,0.0,1.0,0.2548795189283402],[29.95764821930397,65.72142680005948,1860.0,7.0,9.0,2.0,-1.0,0.20139188417881576]]</t>
         </is>
       </c>
       <c r="C516" t="n">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>[[-27.021519333765497,17.721835156577136,-1860.0,4.0,0.0,0.0,1.0],[17.721835156577136,20.190434025009836,-733.6842,4.0,0.0,0.0,1.0],[20.190434025009836,22.35045803488844,0.0,4.0,0.0,1.0,1.0],[22.35045803488844,30.99055407440288,1016.5,4.0,0.0,0.0,1.0],[30.99055407440288,65.24236337390656,1860.0,5.0,9.0,0.0,-1.0]]</t>
+          <t>[[-27.021519333765497,17.721835156577136,-1860.0,4.0,0.0,0.0,1.0,0.5322289165187016],[17.721835156577136,20.190434025009836,-733.6842,4.0,0.0,0.0,1.0,0.4677710845909908],[20.190434025009836,22.35045803488844,0.0,4.0,0.0,1.0,1.0,0.4257831333861715],[22.35045803488844,30.99055407440288,1016.5,4.0,0.0,0.0,1.0,0.3613253020608703],[30.99055407440288,65.24236337390656,1860.0,5.0,9.0,0.0,-1.0,0.3078376673113459]]</t>
         </is>
       </c>
       <c r="C517" t="n">
@@ -13892,7 +13892,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>[[-31.96008707261515,16.849708318027506,-1860.0,3.0,0.0,0.0,1.0],[16.849708318027506,20.336122274501985,-733.6842,3.0,0.0,0.0,1.0],[20.336122274501985,22.427970648386673,0.0,3.0,0.0,1.0,1.0],[22.427970648386673,30.09808135263052,1016.5,4.0,0.0,0.0,1.0],[30.09808135263052,72.28369022597167,1860.0,4.0,9.0,2.0,-1.0]]</t>
+          <t>[[-31.96008707261515,16.849708318027506,-1860.0,3.0,0.0,0.0,1.0,0.6386746996512318],[16.849708318027506,20.336122274501985,-733.6842,3.0,0.0,0.0,1.0,0.5742168677235209],[20.336122274501985,22.427970648386673,0.0,3.0,0.0,1.0,1.0,0.5322289165187016],[22.427970648386673,30.09808135263052,1016.5,4.0,0.0,0.0,1.0,0.46777108519340044],[30.09808135263052,72.28369022597167,1860.0,4.0,9.0,2.0,-1.0,0.414283450443876]]</t>
         </is>
       </c>
       <c r="C518" t="n">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>[[-29.210232865094884,18.054919634398363,-1860.0,2.0,0.0,0.0,1.0],[18.054919634398363,20.321057083004202,-733.6842,2.0,0.0,0.0,1.0],[20.321057083004202,22.58719453161005,0.0,2.0,0.0,1.0,1.0],[22.58719453161005,30.033074719886375,1016.5,3.0,0.0,0.0,1.0],[30.033074719886375,30.356808641115787,1725.15,4.0,9.0,1.0,-1.0],[30.356808641115787,67.58620958249746,1860.0,4.0,9.0,1.0,-1.0]]</t>
+          <t>[[-29.210232865094884,18.054919634398363,-1860.0,2.0,0.0,0.0,1.0,0.7451204827837619],[18.054919634398363,20.321057083004202,-733.6842,2.0,0.0,0.0,1.0,0.680662650856051],[20.321057083004202,22.58719453161005,0.0,2.0,0.0,1.0,1.0,0.6386746996512318],[22.58719453161005,30.033074719886375,1016.5,3.0,0.0,0.0,1.0,0.5742168683259306],[30.033074719886375,30.356808641115787,1725.15,4.0,9.0,1.0,-1.0,0.529280279866831],[30.356808641115787,67.58620958249746,1860.0,4.0,9.0,1.0,-1.0,0.5207292335764062]]</t>
         </is>
       </c>
       <c r="C519" t="n">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>[[-29.18067801858622,17.387944840250036,-1860.0,2.0,0.0,0.0,1.0],[17.387944840250036,20.27841108666057,-733.6842,2.0,0.0,0.0,1.0],[20.27841108666057,22.20538858426758,0.0,1.0,0.0,1.0,1.0],[22.20538858426758,30.876787323499165,1016.5,2.0,0.0,0.0,1.0],[30.876787323499165,66.84703394549682,1860.0,2.0,9.0,0.0,-1.0]]</t>
+          <t>[[-29.18067801858622,17.387944840250036,-1860.0,2.0,0.0,0.0,1.0,0.8515662659162919],[17.387944840250036,20.27841108666057,-733.6842,2.0,0.0,0.0,1.0,0.7871084339885811],[20.27841108666057,22.20538858426758,0.0,1.0,0.0,1.0,1.0,0.7451204827837619],[22.20538858426758,30.876787323499165,1016.5,2.0,0.0,0.0,1.0,0.6806626514584606],[30.876787323499165,66.84703394549682,1860.0,2.0,9.0,0.0,-1.0,0.6271750167089363]]</t>
         </is>
       </c>
       <c r="C520" t="n">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>[[-29.47909945953337,15.306219117995798,-1860.0,1.0,0.0,0.0,1.0],[15.306219117995798,19.525125940516663,-733.6842,0.0,0.0,0.0,1.0],[19.525125940516663,21.47231370475706,0.0,1.0,0.0,1.0,1.0],[21.47231370475706,29.91012734979879,1016.5,2.0,0.0,0.0,1.0],[29.91012734979879,67.5557574584465,1860.0,2.0,9.0,2.0,-1.0]]</t>
+          <t>[[-29.47909945953337,15.306219117995798,-1860.0,1.0,0.0,0.0,1.0,0.958012049048822],[15.306219117995798,19.525125940516663,-733.6842,0.0,0.0,0.0,1.0,0.8935542171211112],[19.525125940516663,21.47231370475706,0.0,1.0,0.0,1.0,1.0,0.8515662659162919],[21.47231370475706,29.91012734979879,1016.5,2.0,0.0,0.0,1.0,0.7871084345909907],[29.91012734979879,67.5557574584465,1860.0,2.0,9.0,2.0,-1.0,0.7336207998414663]]</t>
         </is>
       </c>
       <c r="C521" t="n">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="F521" s="4" t="inlineStr">
         <is>
-          <t>[0,0,1.9471877642,8.437813645,0]</t>
+          <t>[4.2189068225,0,1.9471877642,8.437813645,0]</t>
         </is>
       </c>
     </row>
@@ -13996,7 +13996,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>[[-30.554885037809157,-0.13617972800503253,-1860.0,1.0,0.0,0.0,1.0],[-0.13617972800503253,20.25438097417136,-1860.0,0.0,0.0,0.0,1.0],[20.25438097417136,26.939810712589846,0.0,1.0,0.0,1.0,1.0],[26.939810712589846,29.948254094878166,0.0,0.0,0.0,1.0,1.0],[29.948254094878166,30.616797068720018,890.0,0.0,8.0,1.0,-1.0],[30.616797068720018,69.39228955154725,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[-30.554885037809157,-0.13617972800503253,-1860.0,1.0,0.0,0.0,1.0,1.0000000002536413],[-0.13617972800503253,20.25438097417136,-1860.0,0.0,0.0,0.0,1.0,1.0000000002536413],[20.25438097417136,26.939810712589846,0.0,1.0,0.0,1.0,1.0,0.8935542171211112],[26.939810712589846,29.948254094878166,0.0,0.0,0.0,1.0,1.0,0.8935542171211112],[29.948254094878166,30.616797068720018,890.0,0.0,8.0,1.0,-1.0,0.8371179457197161],[30.616797068720018,69.39228955154725,1860.0,0.0,8.0,1.0,-1.0,0.7756087510462856]]</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -14012,7 +14012,7 @@
       </c>
       <c r="F522" s="4" t="inlineStr">
         <is>
-          <t>[0,0,6.6854297384,0,0.6685429738]</t>
+          <t>[0,0,9.6938731207,0,0.6685429738]</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>[[-30.046692878191138,29.581067966836287,0.0,0.0,0.0,1.0,1.0],[29.581067966836287,30.898808537997112,890.0,0.0,8.0,1.0,-1.0],[30.898808537997112,68.45441481608069,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[-30.046692878191138,29.581067966836287,0.0,0.0,0.0,1.0,1.0,1.000000000253641],[29.581067966836287,30.898808537997112,890.0,0.0,8.0,1.0,-1.0,0.943563728852246],[30.898808537997112,68.45441481608069,1860.0,0.0,8.0,1.0,-1.0,0.8820545341788155]]</t>
         </is>
       </c>
       <c r="C523" t="n">
@@ -14048,7 +14048,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>[[-29.238327708623622,28.32054107134519,0.0,0.0,0.0,1.0,1.0],[28.32054107134519,30.24988862821565,890.0,0.0,8.0,0.0,-1.0],[30.24988862821565,66.90749220875446,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-29.238327708623622,28.32054107134519,0.0,0.0,0.0,1.0,1.0,1.000000000253641],[28.32054107134519,30.24988862821565,890.0,0.0,8.0,0.0,-1.0,0.943563728852246],[30.24988862821565,66.90749220875446,1860.0,0.0,8.0,0.0,-1.0,0.8820545341788155]]</t>
         </is>
       </c>
       <c r="C524" t="n">
@@ -14074,7 +14074,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>[[-30.066497600163746,25.523509519034423,-1860.0,1.0,8.0,0.0,-1.0],[25.523509519034423,26.181379425770498,-1074.7922,0.0,8.0,1.0,-1.0],[26.181379425770498,29.14179400608283,0.0,0.0,7.0,2.0,-1.0],[29.14179400608283,30.45753381955497,890.0,0.0,7.0,0.0,-1.0],[30.45753381955497,68.28505345687918,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-30.066497600163746,25.523509519034423,-1860.0,1.0,8.0,0.0,-1.0,0.9885003173113458],[25.523509519034423,26.181379425770498,-1074.7922,0.0,8.0,1.0,-1.0,0.9435637263474904],[26.181379425770498,29.14179400608283,0.0,0.0,7.0,2.0,-1.0,0.8820545341788157],[29.14179400608283,30.45753381955497,890.0,0.0,7.0,0.0,-1.0,0.8256182627774207],[30.45753381955497,68.28505345687918,1860.0,0.0,7.0,0.0,-1.0,0.7641090681039902]]</t>
         </is>
       </c>
       <c r="C525" t="n">
@@ -14100,7 +14100,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>[[-31.77415464138868,25.850980502795426,-1860.0,1.0,7.0,0.0,-1.0],[25.850980502795426,26.549466989391593,-1074.7922,0.0,7.0,0.0,-1.0],[26.549466989391593,29.343412935776282,0.0,0.0,6.0,1.0,-1.0],[29.343412935776282,30.391142665670532,890.0,0.0,6.0,0.0,-1.0],[30.391142665670532,72.64957510473889,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[-31.77415464138868,25.850980502795426,-1860.0,1.0,7.0,0.0,-1.0,0.8705548512365202],[25.850980502795426,26.549466989391593,-1074.7922,0.0,7.0,0.0,-1.0,0.8256182602726648],[26.549466989391593,29.343412935776282,0.0,0.0,6.0,1.0,-1.0,0.7641090681039902],[29.343412935776282,30.391142665670532,890.0,0.0,6.0,0.0,-1.0,0.7076727967025951],[30.391142665670532,72.64957510473889,1860.0,0.0,6.0,0.0,-1.0,0.6461636020291646]]</t>
         </is>
       </c>
       <c r="C526" t="n">
@@ -14126,7 +14126,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>[[-30.805696917922774,25.669064802562417,-1860.0,1.0,6.0,0.0,-1.0],[25.669064802562417,27.021753706047093,-1074.7922,0.0,6.0,1.0,-1.0],[27.021753706047093,30.065303738887607,0.0,0.0,5.0,2.0,-1.0],[30.065303738887607,32.09433709411462,890.0,0.0,5.0,0.0,-1.0],[32.09433709411462,70.3077986175567,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-30.805696917922774,25.669064802562417,-1860.0,1.0,6.0,0.0,-1.0,0.7526093851616946],[25.669064802562417,27.021753706047093,-1074.7922,0.0,6.0,1.0,-1.0,0.7076727941978392],[27.021753706047093,30.065303738887607,0.0,0.0,5.0,2.0,-1.0,0.6461636020291646],[30.065303738887607,32.09433709411462,890.0,0.0,5.0,0.0,-1.0,0.5897273306277695],[32.09433709411462,70.3077986175567,1860.0,0.0,5.0,0.0,-1.0,0.528218135954339]]</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>[[-33.64432648452241,25.50660240295447,-1860.0,1.0,5.0,1.0,-1.0],[25.50660240295447,30.28276436281285,0.0,0.0,5.0,2.0,-1.0],[30.28276436281285,31.01755851048337,1678.65,1.0,5.0,0.0,-1.0],[31.01755851048337,76.20739859222036,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-33.64432648452241,25.50660240295447,-1860.0,1.0,5.0,1.0,-1.0,0.6961731137602996],[25.50660240295447,30.28276436281285,0.0,0.0,5.0,2.0,-1.0,0.5897273306277695],[30.28276436281285,31.01755851048337,1678.65,1.0,5.0,0.0,-1.0,0.4832815474952394],[31.01755851048337,76.20739859222036,1860.0,0.0,5.0,0.0,-1.0,0.47178186455294385]]</t>
         </is>
       </c>
       <c r="C528" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>[[-37.08463457877714,26.23004672620882,-1860.0,1.0,4.0,0.0,-1.0],[26.23004672620882,29.43585337456254,0.0,0.0,4.0,2.0,-1.0],[29.43585337456254,82.73238890344312,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-37.08463457877714,26.23004672620882,-1860.0,1.0,4.0,0.0,-1.0,0.578227647685474],[26.23004672620882,29.43585337456254,0.0,0.0,4.0,2.0,-1.0,0.4717818645529439],[29.43585337456254,82.73238890344312,1860.0,0.0,4.0,0.0,-1.0,0.35383639847811826]]</t>
         </is>
       </c>
       <c r="C529" t="n">
@@ -14204,7 +14204,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>[[-35.93666378607449,25.78088294329543,-1860.0,1.0,3.0,1.0,-1.0],[25.78088294329543,29.66248965583442,0.0,0.0,3.0,2.0,-1.0],[29.66248965583442,80.12337691884127,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-35.93666378607449,25.78088294329543,-1860.0,1.0,3.0,1.0,-1.0,0.4602821816106483],[25.78088294329543,29.66248965583442,0.0,0.0,3.0,2.0,-1.0,0.3538363984781182],[29.66248965583442,80.12337691884127,1860.0,0.0,3.0,0.0,-1.0,0.23589093240329256]]</t>
         </is>
       </c>
       <c r="C530" t="n">
@@ -14230,7 +14230,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>[[-37.304636344656394,25.526487005592827,-1860.0,1.0,2.0,1.0,-1.0],[25.526487005592827,29.151359506568745,0.0,0.0,2.0,2.0,-1.0],[29.151359506568745,83.12168340998795,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-37.304636344656394,25.526487005592827,-1860.0,1.0,2.0,1.0,-1.0,0.3423367155358227],[25.526487005592827,29.151359506568745,0.0,0.0,2.0,2.0,-1.0,0.2358909324032926],[29.151359506568745,83.12168340998795,1860.0,0.0,2.0,0.0,-1.0,0.11794546632846696]]</t>
         </is>
       </c>
       <c r="C531" t="n">
@@ -14256,7 +14256,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>[[-41.18674610001178,25.64565471910702,-1860.0,1.0,1.0,1.0,-1.0],[25.64565471910702,28.743845485556243,0.0,0.0,1.0,2.0,-1.0],[28.743845485556243,91.15025949546188,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-41.18674610001178,25.64565471910702,-1860.0,1.0,1.0,1.0,-1.0,0.22439124946099703],[25.64565471910702,28.743845485556243,0.0,0.0,1.0,2.0,-1.0,0.1179454663284669],[28.743845485556243,91.15025949546188,1860.0,0.0,1.0,0.0,-1.0,2.536412746501071e-10]]</t>
         </is>
       </c>
       <c r="C532" t="n">
@@ -14282,7 +14282,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>[[-40.339051750766856,26.74346841667729,-1860.0,1.0,0.0,1.0,-1.0],[26.74346841667729,89.06529360449636,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-40.339051750766856,26.74346841667729,-1860.0,1.0,0.0,1.0,-1.0,0.10644578338617142],[26.74346841667729,89.06529360449636,0.0,0.0,0.0,1.0,-1.0,2.536413024056827e-10]]</t>
         </is>
       </c>
       <c r="C533" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>[[-40.7216637296497,25.392007728733738,-1860.0,1.0,0.0,0.0,-1.0],[25.392007728733738,90.19216253562611,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-40.7216637296497,25.392007728733738,-1860.0,1.0,0.0,0.0,-1.0,0.10644578338617142],[25.392007728733738,90.19216253562611,0.0,0.0,0.0,1.0,-1.0,2.536413024056827e-10]]</t>
         </is>
       </c>
       <c r="C534" t="n">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>[[-39.62587347273803,24.532880171733318,-1860.0,1.0,0.0,0.0,-1.0],[24.532880171733318,87.41695659148007,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-39.62587347273803,24.532880171733318,-1860.0,1.0,0.0,0.0,-1.0,0.10644578338617142],[24.532880171733318,87.41695659148007,0.0,0.0,0.0,1.0,-1.0,2.536413024056827e-10]]</t>
         </is>
       </c>
       <c r="C535" t="n">
@@ -14360,7 +14360,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>[[-39.95969167946674,12.429516559134271,-1860.0,10.0,0.0,0.0,1.0],[12.429516559134271,13.717775778116263,-733.6842,9.0,0.0,1.0,1.0],[13.717775778116263,88.4368104790718,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-39.95969167946674,12.429516559134271,-1860.0,10.0,0.0,0.0,1.0,0.10644578338617142],[12.429516559134271,13.717775778116263,-733.6842,9.0,0.0,1.0,1.0,0.04198795145846058],[13.717775778116263,88.4368104790718,0.0,0.0,0.0,1.0,-1.0,2.536413024056827e-10]]</t>
         </is>
       </c>
       <c r="C536" t="n">
@@ -14386,7 +14386,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>[[-39.08051891737976,8.25345706041805,-1860.0,9.0,0.0,0.0,1.0],[8.25345706041805,22.200074982447767,-733.6842,9.0,0.0,0.0,1.0],[22.200074982447767,87.28429195191977,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-39.08051891737976,8.25345706041805,-1860.0,9.0,0.0,0.0,1.0,0.10644578338617142],[8.25345706041805,22.200074982447767,-733.6842,9.0,0.0,0.0,1.0,0.04198795145846058],[22.200074982447767,87.28429195191977,0.0,0.0,0.0,1.0,-1.0,2.536413024056827e-10]]</t>
         </is>
       </c>
       <c r="C537" t="n">
@@ -14412,7 +14412,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>[[-39.48443584424238,21.755694313329286,-1860.0,9.0,0.0,0.0,1.0],[21.755694313329286,36.2151694894226,0.0,9.0,0.0,1.0,1.0],[36.2151694894226,87.67388996904877,662.1501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-39.48443584424238,21.755694313329286,-1860.0,9.0,0.0,0.0,1.0,0.14843373459099068],[21.755694313329286,36.2151694894226,0.0,9.0,0.0,1.0,1.0,0.04198795145846058],[36.2151694894226,87.67388996904877,662.1501,0.0,0.0,0.0,-1.0,-6.689922421587724e-09]]</t>
         </is>
       </c>
       <c r="C538" t="n">
@@ -14438,7 +14438,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>[[-48.553590946824976,21.34617211915843,-1860.0,8.0,0.0,0.0,1.0],[21.34617211915843,35.9873387073036,0.0,8.0,0.0,1.0,1.0],[35.9873387073036,36.45963440369538,890.0,8.0,8.0,4.0,-1.0],[36.45963440369538,92.66282227431716,1860.0,7.0,8.0,4.0,-1.0]]</t>
+          <t>[[-48.553590946824976,21.34617211915843,-1860.0,8.0,0.0,0.0,1.0,0.2548795177235208],[21.34617211915843,35.9873387073036,0.0,8.0,0.0,1.0,1.0,0.1484337345909907],[35.9873387073036,36.45963440369538,890.0,8.0,8.0,4.0,-1.0,0.09199746318959566],[36.45963440369538,92.66282227431716,1860.0,7.0,8.0,4.0,-1.0,0.030488268516165082]]</t>
         </is>
       </c>
       <c r="C539" t="n">
@@ -14464,7 +14464,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>[[-52.8692278731325,20.665110517307326,-1860.0,6.0,0.0,0.0,1.0],[20.665110517307326,35.67211835209096,0.0,7.0,0.0,1.0,1.0],[35.67211835209096,36.172351946583746,890.0,7.0,8.0,4.0,-1.0],[36.172351946583746,96.7006168802111,1860.0,5.0,8.0,4.0,-1.0]]</t>
+          <t>[[-52.8692278731325,20.665110517307326,-1860.0,6.0,0.0,0.0,1.0,0.3613253008560509],[20.665110517307326,35.67211835209096,0.0,7.0,0.0,1.0,1.0,0.2548795177235208],[35.67211835209096,36.172351946583746,890.0,7.0,8.0,4.0,-1.0,0.19844324632212573],[36.172351946583746,96.7006168802111,1860.0,5.0,8.0,4.0,-1.0,0.13693405164869515]]</t>
         </is>
       </c>
       <c r="C540" t="n">
@@ -14490,7 +14490,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>[[-59.650747615284374,20.728873413083022,-1860.0,5.0,0.0,0.0,1.0],[20.728873413083022,36.59327230026081,0.0,4.0,0.0,1.0,1.0],[36.59327230026081,37.12208559650006,890.0,4.0,8.0,4.0,-1.0],[37.12208559650006,98.46442796025414,1860.0,5.0,8.0,4.0,-1.0]]</t>
+          <t>[[-59.650747615284374,20.728873413083022,-1860.0,5.0,0.0,0.0,1.0,0.467771083988581],[20.728873413083022,36.59327230026081,0.0,4.0,0.0,1.0,1.0,0.3613253008560509],[36.59327230026081,37.12208559650006,890.0,4.0,8.0,4.0,-1.0,0.30488902945465585],[37.12208559650006,98.46442796025414,1860.0,5.0,8.0,4.0,-1.0,0.24337983478122527]]</t>
         </is>
       </c>
       <c r="C541" t="n">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>[[-67.90317206651065,21.105876755315506,-1860.0,4.0,0.0,0.0,1.0],[21.105876755315506,36.41316540620281,0.0,4.0,0.0,1.0,1.0],[36.41316540620281,36.980102022902344,890.0,4.0,8.0,3.0,-1.0],[36.980102022902344,101.61087632664874,1860.0,3.0,8.0,3.0,-1.0]]</t>
+          <t>[[-67.90317206651065,21.105876755315506,-1860.0,4.0,0.0,0.0,1.0,0.5742168671211112],[21.105876755315506,36.41316540620281,0.0,4.0,0.0,1.0,1.0,0.467771083988581],[36.41316540620281,36.980102022902344,890.0,4.0,8.0,3.0,-1.0,0.41133481258718596],[36.980102022902344,101.61087632664874,1860.0,3.0,8.0,3.0,-1.0,0.3498256179137554]]</t>
         </is>
       </c>
       <c r="C542" t="n">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>[[-73.23767892693259,21.389704502354306,-1860.0,3.0,0.0,0.0,1.0],[21.389704502354306,36.76665430961343,0.0,3.0,0.0,1.0,1.0],[36.76665430961343,37.35807545604648,890.0,4.0,8.0,4.0,-1.0],[37.35807545604648,103.5972438565473,1860.0,3.0,8.0,4.0,-1.0]]</t>
+          <t>[[-73.23767892693259,21.389704502354306,-1860.0,3.0,0.0,0.0,1.0,0.6806626502536413],[21.389704502354306,36.76665430961343,0.0,3.0,0.0,1.0,1.0,0.5742168671211112],[36.76665430961343,37.35807545604648,890.0,4.0,8.0,4.0,-1.0,0.5177805957197161],[37.35807545604648,103.5972438565473,1860.0,3.0,8.0,4.0,-1.0,0.45627140104628555]]</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -14568,7 +14568,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>[[-74.05587824124835,21.035465022263452,-1860.0,2.0,0.0,0.0,1.0],[21.035465022263452,36.487808302584114,0.0,2.0,0.0,1.0,1.0],[36.487808302584114,38.27077098877497,1678.65,3.0,0.0,0.0,1.0],[38.27077098877497,103.64606948243932,1860.0,3.0,9.0,2.0,-1.0]]</t>
+          <t>[[-74.05587824124835,21.035465022263452,-1860.0,2.0,0.0,0.0,1.0,0.7871084333861713],[21.035465022263452,36.487808302584114,0.0,2.0,0.0,1.0,1.0,0.6806626502536413],[36.487808302584114,38.27077098877497,1678.65,3.0,0.0,0.0,1.0,0.5742168671211111],[38.27077098877497,103.64606948243932,1860.0,3.0,9.0,2.0,-1.0,0.5627171841788157]]</t>
         </is>
       </c>
       <c r="C544" t="n">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>[[-78.69852255299874,22.275300769253064,-1860.0,2.0,0.0,0.0,1.0],[22.275300769253064,37.421374267590835,0.0,2.0,0.0,1.0,1.0],[37.421374267590835,109.99630978045934,1860.0,1.0,8.0,4.0,-1.0]]</t>
+          <t>[[-78.69852255299874,22.275300769253064,-1860.0,2.0,0.0,0.0,1.0,0.8935542165187014],[22.275300769253064,37.421374267590835,0.0,2.0,0.0,1.0,1.0,0.7871084333861713],[37.421374267590835,109.99630978045934,1860.0,1.0,8.0,4.0,-1.0,0.6691629673113457]]</t>
         </is>
       </c>
       <c r="C545" t="n">
@@ -14620,7 +14620,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>[[-76.43023570192025,20.741300443376446,-1860.0,1.0,0.0,0.0,1.0],[20.741300443376446,36.83340197062303,0.0,0.0,0.0,1.0,1.0],[36.83340197062303,37.45232895244021,890.0,0.0,8.0,2.0,-1.0],[37.45232895244021,108.62893186141551,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-76.43023570192025,20.741300443376446,-1860.0,1.0,0.0,0.0,1.0,0.9999999996512314],[20.741300443376446,36.83340197062303,0.0,0.0,0.0,1.0,1.0,0.8935542165187014],[36.83340197062303,37.45232895244021,890.0,0.0,8.0,2.0,-1.0,0.8371179451173063],[37.45232895244021,108.62893186141551,1860.0,0.0,8.0,2.0,-1.0,0.7756087504438758]]</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -14636,7 +14636,7 @@
       </c>
       <c r="F546" s="4" t="inlineStr">
         <is>
-          <t>[0,0,0,0,0.6189269818]</t>
+          <t>[0,0,16.0921015272,0,0.6189269818]</t>
         </is>
       </c>
     </row>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>[[-73.28476934164514,36.358474137173815,0.0,0.0,0.0,1.0,1.0],[36.358474137173815,37.53743374447295,890.0,0.0,8.0,4.0,-1.0],[37.53743374447295,102.96969194957461,1860.0,0.0,9.0,3.0,-1.0]]</t>
+          <t>[[-73.28476934164514,36.358474137173815,0.0,0.0,0.0,1.0,1.0,0.9999999996512314],[36.358474137173815,37.53743374447295,890.0,0.0,8.0,4.0,-1.0,0.9435637282498364],[37.53743374447295,102.96969194957461,1860.0,0.0,9.0,3.0,-1.0,0.8820545335764058]]</t>
         </is>
       </c>
       <c r="C547" t="n">
@@ -14672,7 +14672,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>[[-74.2780810225171,36.3951778476511,0.0,0.0,0.0,1.0,1.0],[36.3951778476511,36.99994975404546,890.0,0.0,8.0,2.0,-1.0],[36.99994975404546,106.54871898939706,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-74.2780810225171,36.3951778476511,0.0,0.0,0.0,1.0,1.0,0.9999999996512314],[36.3951778476511,36.99994975404546,890.0,0.0,8.0,2.0,-1.0,0.9435637282498364],[36.99994975404546,106.54871898939706,1860.0,0.0,8.0,2.0,-1.0,0.8820545335764058]]</t>
         </is>
       </c>
       <c r="C548" t="n">
@@ -14698,7 +14698,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>[[-74.27592531545434,36.82700344915273,0.0,0.0,0.0,1.0,1.0],[36.82700344915273,37.424331023156,890.0,0.0,8.0,2.0,-1.0],[37.424331023156,104.32501931152154,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-74.27592531545434,36.82700344915273,0.0,0.0,0.0,1.0,1.0,0.9999999996512314],[36.82700344915273,37.424331023156,890.0,0.0,8.0,2.0,-1.0,0.9435637282498364],[37.424331023156,104.32501931152154,1860.0,0.0,8.0,2.0,-1.0,0.8820545335764058]]</t>
         </is>
       </c>
       <c r="C549" t="n">
@@ -14724,7 +14724,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>[[-76.83217268697899,33.014432611729234,-986.1497,0.0,0.0,0.0,1.0],[33.014432611729234,37.35864864049171,0.0,0.0,7.0,1.0,-1.0],[37.35864864049171,108.7279119701609,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[-76.83217268697899,33.014432611729234,-986.1497,0.0,0.0,0.0,1.0,1.0000000062618846],[33.014432611729234,37.35864864049171,0.0,0.0,7.0,1.0,-1.0,0.9435637282498364],[37.35864864049171,108.7279119701609,1860.0,0.0,7.0,1.0,-1.0,0.8256182621750108]]</t>
         </is>
       </c>
       <c r="C550" t="n">
@@ -14750,7 +14750,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>[[-73.27601855608853,28.811206739619294,-986.1497,0.0,0.0,0.0,1.0],[28.811206739619294,36.52710167475999,0.0,0.0,8.0,1.0,-1.0],[36.52710167475999,104.18956495214772,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-73.27601855608853,28.811206739619294,-986.1497,0.0,0.0,0.0,1.0,1.0000000062618846],[28.811206739619294,36.52710167475999,0.0,0.0,8.0,1.0,-1.0,0.9435637282498364],[36.52710167475999,104.18956495214772,1860.0,0.0,7.0,0.0,-1.0,0.8256182621750108]]</t>
         </is>
       </c>
       <c r="C551" t="n">
@@ -14776,7 +14776,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>[[-73.34690903332539,26.88384603419749,-1860.0,1.0,7.0,0.0,-1.0],[26.88384603419749,36.966229680042986,0.0,0.0,7.0,1.0,-1.0],[36.966229680042986,103.98442685536891,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[-73.34690903332539,26.88384603419749,-1860.0,1.0,7.0,0.0,-1.0,0.9320640453075408],[26.88384603419749,36.966229680042986,0.0,0.0,7.0,1.0,-1.0,0.8256182621750108],[36.966229680042986,103.98442685536891,1860.0,0.0,6.0,1.0,-1.0,0.7076727961001852]]</t>
         </is>
       </c>
       <c r="C552" t="n">
@@ -14802,7 +14802,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>[[-77.92262329075888,26.958100531908315,-1860.0,1.0,6.0,0.0,-1.0],[26.958100531908315,35.171651192719594,0.0,0.0,6.0,1.0,-1.0],[35.171651192719594,110.98904190790068,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-77.92262329075888,26.958100531908315,-1860.0,1.0,6.0,0.0,-1.0,0.8141185792327152],[26.958100531908315,35.171651192719594,0.0,0.0,6.0,1.0,-1.0,0.7076727961001852],[35.171651192719594,110.98904190790068,1860.0,0.0,5.0,0.0,-1.0,0.5897273300253596]]</t>
         </is>
       </c>
       <c r="C553" t="n">
@@ -14828,7 +14828,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>[[-75.54305880081623,26.854190795108792,-1860.0,1.0,5.0,0.0,-1.0],[26.854190795108792,36.60630980424452,0.0,0.0,5.0,1.0,-1.0],[36.60630980424452,106.69966518240747,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-75.54305880081623,26.854190795108792,-1860.0,1.0,5.0,0.0,-1.0,0.6961731131578897],[26.854190795108792,36.60630980424452,0.0,0.0,5.0,1.0,-1.0,0.5897273300253596],[36.60630980424452,106.69966518240747,1860.0,0.0,4.0,0.0,-1.0,0.47178186395053395]]</t>
         </is>
       </c>
       <c r="C554" t="n">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>[[-74.12717105037504,26.485189090972426,-1860.0,1.0,4.0,0.0,-1.0],[26.485189090972426,36.72716587182816,0.0,0.0,4.0,1.0,-1.0],[36.72716587182816,106.01112644820515,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-74.12717105037504,26.485189090972426,-1860.0,1.0,4.0,0.0,-1.0,0.5782276470830641],[26.485189090972426,36.72716587182816,0.0,0.0,4.0,1.0,-1.0,0.471781863950534],[36.72716587182816,106.01112644820515,1860.0,0.0,3.0,0.0,-1.0,0.35383639787570836]]</t>
         </is>
       </c>
       <c r="C555" t="n">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>[[-67.97299051254734,26.80759493589086,-1860.0,1.0,3.0,0.0,-1.0],[26.80759493589086,35.96253784852409,0.0,0.0,3.0,1.0,-1.0],[35.96253784852409,93.04629953906073,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-67.97299051254734,26.80759493589086,-1860.0,1.0,3.0,0.0,-1.0,0.4602821810082384],[26.80759493589086,35.96253784852409,0.0,0.0,3.0,1.0,-1.0,0.3538363978757083],[35.96253784852409,93.04629953906073,1860.0,0.0,2.0,0.0,-1.0,0.23589093180088266]]</t>
         </is>
       </c>
       <c r="C556" t="n">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>[[-67.86640679103705,27.09686773682668,-1860.0,1.0,2.0,0.0,-1.0],[27.09686773682668,37.766898582654065,0.0,0.0,2.0,1.0,-1.0],[37.766898582654065,91.65055435408235,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[-67.86640679103705,27.09686773682668,-1860.0,1.0,2.0,0.0,-1.0,0.3423367149334128],[27.09686773682668,37.766898582654065,0.0,0.0,2.0,1.0,-1.0,0.2358909318008827],[37.766898582654065,91.65055435408235,1860.0,0.0,1.0,1.0,-1.0,0.11794546572605706]]</t>
         </is>
       </c>
       <c r="C557" t="n">
@@ -14932,7 +14932,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>[[-68.37180294061235,26.624527336778883,-1860.0,1.0,1.0,0.0,-1.0],[26.624527336778883,33.60165893907316,0.0,0.0,1.0,1.0,-1.0],[33.60165893907316,37.358575955693155,0.0,0.0,0.0,1.0,-1.0],[37.358575955693155,41.65219540325886,1860.0,0.0,0.0,0.0,-1.0],[41.65219540325886,92.10222391215589,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-68.37180294061235,26.624527336778883,-1860.0,1.0,1.0,0.0,-1.0,0.22439124885858713],[26.624527336778883,33.60165893907316,0.0,0.0,1.0,1.0,-1.0,0.117945465726057],[33.60165893907316,37.358575955693155,0.0,0.0,0.0,1.0,-1.0,0.117945465726057],[37.358575955693155,41.65219540325886,1860.0,0.0,0.0,0.0,-1.0,-3.4876862509136686e-10],[41.65219540325886,92.10222391215589,1860.0,0.0,1.0,0.0,-1.0,-3.4876862509136686e-10]]</t>
         </is>
       </c>
       <c r="C558" t="n">
@@ -14948,7 +14948,7 @@
       </c>
       <c r="F558" s="4" t="inlineStr">
         <is>
-          <t>[0,0,6.9771316023,0,0]</t>
+          <t>[0,0,10.7340486189,0,0]</t>
         </is>
       </c>
     </row>
@@ -14958,7 +14958,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>[[-66.5555944158746,26.62542323559144,-1860.0,1.0,0.0,0.0,-1.0],[26.62542323559144,89.09314456618318,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-66.5555944158746,26.62542323559144,-1860.0,1.0,0.0,0.0,-1.0,0.10644578278376152],[26.62542323559144,89.09314456618318,0.0,0.0,0.0,1.0,-1.0,-3.487685973357912e-10]]</t>
         </is>
       </c>
       <c r="C559" t="n">
@@ -14984,7 +14984,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>[[-65.69830267919284,5.48204558685336,-1860.0,1.0,0.0,0.0,-1.0],[5.48204558685336,88.52578523057392,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-65.69830267919284,5.48204558685336,-1860.0,1.0,0.0,0.0,-1.0,0.10644578278376152],[5.48204558685336,88.52578523057392,0.0,0.0,0.0,1.0,-1.0,-3.487685973357912e-10]]</t>
         </is>
       </c>
       <c r="C560" t="n">
@@ -15010,7 +15010,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>[[-66.16395896585394,-1.4998642971704754,-1860.0,9.0,0.0,0.0,1.0],[-1.4998642971704754,-0.4652387824715447,-733.6842,9.0,0.0,0.0,1.0],[-0.4652387824715447,88.5125554816369,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-66.16395896585394,-1.4998642971704754,-1860.0,9.0,0.0,0.0,1.0,0.10644578278376152],[-1.4998642971704754,-0.4652387824715447,-733.6842,9.0,0.0,0.0,1.0,0.04198795085605068],[-0.4652387824715447,88.5125554816369,0.0,0.0,0.0,1.0,-1.0,-3.487685973357912e-10]]</t>
         </is>
       </c>
       <c r="C561" t="n">
@@ -15036,7 +15036,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>[[-67.93200487811941,-0.22483386835314434,-1860.0,9.0,0.0,0.0,1.0],[-0.22483386835314434,23.918808507222423,-733.6842,9.0,0.0,0.0,1.0],[23.918808507222423,89.00167056312179,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-67.93200487811941,-0.22483386835314434,-1860.0,9.0,0.0,0.0,1.0,0.10644578278376152],[-0.22483386835314434,23.918808507222423,-733.6842,9.0,0.0,0.0,1.0,0.04198795085605068],[23.918808507222423,89.00167056312179,0.0,0.0,0.0,1.0,-1.0,-3.487685973357912e-10]]</t>
         </is>
       </c>
       <c r="C562" t="n">
@@ -15062,7 +15062,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>[[-65.9917347076625,-0.4171118828577818,-1860.0,8.0,0.0,0.0,1.0],[-0.4171118828577818,24.366997531241637,-733.6842,8.0,0.0,0.0,1.0],[24.366997531241637,26.948675595210332,0.0,9.0,9.0,2.0,-1.0],[26.948675595210332,27.98134682079781,46.5,9.0,9.0,2.0,-1.0],[27.98134682079781,88.39261351766513,1678.6501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-65.9917347076625,-0.4171118828577818,-1860.0,8.0,0.0,0.0,1.0,0.2128915659162916],[-0.4171118828577818,24.366997531241637,-733.6842,8.0,0.0,0.0,1.0,0.14843373398858078],[24.366997531241637,26.948675595210332,0.0,9.0,9.0,2.0,-1.0,0.1064457827837615],[26.948675595210332,27.98134682079781,46.5,9.0,9.0,2.0,-1.0,0.10349714613189086],[27.98134682079781,88.39261351766513,1678.6501,0.0,0.0,0.0,-1.0,-6.689922713021268e-09]]</t>
         </is>
       </c>
       <c r="C563" t="n">
@@ -15088,7 +15088,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>[[-65.27694204718907,-0.25265514240615516,-1860.0,7.0,0.0,0.0,1.0],[-0.25265514240615516,25.34745781223279,-733.6842,7.0,0.0,0.0,1.0],[25.34745781223279,27.907469107696684,0.0,7.0,8.0,4.0,-1.0],[27.907469107696684,87.81173342155182,1860.0,7.0,8.0,4.0,-1.0]]</t>
+          <t>[[-65.27694204718907,-0.25265514240615516,-1860.0,7.0,0.0,0.0,1.0,0.3193373490488217],[-0.25265514240615516,25.34745781223279,-733.6842,7.0,0.0,0.0,1.0,0.2548795171211109],[25.34745781223279,27.907469107696684,0.0,7.0,8.0,4.0,-1.0,0.2128915659162916],[27.907469107696684,87.81173342155182,1860.0,7.0,8.0,4.0,-1.0,0.09494609984146597]]</t>
         </is>
       </c>
       <c r="C564" t="n">
@@ -15114,7 +15114,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>[[-64.87895038959597,-0.32482930583701375,-1860.0,6.0,0.0,0.0,1.0],[-0.32482930583701375,23.882966100572602,-733.6842,6.0,0.0,0.0,1.0],[23.882966100572602,26.404611455406936,0.0,7.0,9.0,2.0,-1.0],[26.404611455406936,28.421927739274395,46.5,7.0,9.0,2.0,-1.0],[28.421927739274395,85.91544182949721,1860.0,8.0,9.0,1.0,-1.0]]</t>
+          <t>[[-64.87895038959597,-0.32482930583701375,-1860.0,6.0,0.0,0.0,1.0,0.42578313218135183],[-0.32482930583701375,23.882966100572602,-733.6842,6.0,0.0,0.0,1.0,0.361325300253641],[23.882966100572602,26.404611455406936,0.0,7.0,9.0,2.0,-1.0,0.3193373490488217],[26.404611455406936,28.421927739274395,46.5,7.0,9.0,2.0,-1.0,0.3163887123969511],[28.421927739274395,85.91544182949721,1860.0,8.0,9.0,1.0,-1.0,0.20139188297399607]]</t>
         </is>
       </c>
       <c r="C565" t="n">
@@ -15140,7 +15140,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>[[-72.52488892802708,-0.1044417671686233,-1860.0,5.0,0.0,0.0,1.0],[-0.1044417671686233,24.772811074347644,-733.6842,5.0,0.0,0.0,1.0],[24.772811074347644,27.53695027896056,0.0,5.0,8.0,4.0,-1.0],[27.53695027896056,28.089778119883135,227.85,5.0,8.0,4.0,-1.0],[28.089778119883135,92.77063550782543,1860.0,5.0,9.0,3.0,-1.0]]</t>
+          <t>[[-72.52488892802708,-0.1044417671686233,-1860.0,5.0,0.0,0.0,1.0,0.532228915313882],[-0.1044417671686233,24.772811074347644,-733.6842,5.0,0.0,0.0,1.0,0.46777108338617107],[24.772811074347644,27.53695027896056,0.0,5.0,8.0,4.0,-1.0,0.4257831321813518],[27.53695027896056,28.089778119883135,227.85,5.0,8.0,4.0,-1.0,0.4113348125871856],[28.089778119883135,92.77063550782543,1860.0,5.0,9.0,3.0,-1.0,0.30783766610652613]]</t>
         </is>
       </c>
       <c r="C566" t="n">
@@ -15166,7 +15166,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>[[-70.89828970235627,0.006589625489567652,-1860.0,4.0,0.0,0.0,1.0],[0.006589625489567652,24.17870757816428,-733.6842,4.0,0.0,0.0,1.0],[24.17870757816428,26.86449846179481,0.0,4.0,8.0,4.0,-1.0],[26.86449846179481,89.71200513874905,1860.0,4.0,9.0,3.0,-1.0]]</t>
+          <t>[[-70.89828970235627,0.006589625489567652,-1860.0,4.0,0.0,0.0,1.0,0.638674698446412],[0.006589625489567652,24.17870757816428,-733.6842,4.0,0.0,0.0,1.0,0.5742168665187012],[24.17870757816428,26.86449846179481,0.0,4.0,8.0,4.0,-1.0,0.532228915313882],[26.86449846179481,89.71200513874905,1860.0,4.0,9.0,3.0,-1.0,0.4142834492390563]]</t>
         </is>
       </c>
       <c r="C567" t="n">
@@ -15192,7 +15192,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>[[-74.06198672847708,0.014874576337817302,-1860.0,3.0,0.0,0.0,1.0],[0.014874576337817302,24.707161677942793,-733.6842,3.0,0.0,0.0,1.0],[24.707161677942793,26.95191505081597,0.0,3.0,8.0,4.0,-1.0],[26.95191505081597,27.51310339403426,227.85,3.0,8.0,4.0,-1.0],[27.51310339403426,93.73332789379303,1860.0,3.0,9.0,3.0,-1.0]]</t>
+          <t>[[-74.06198672847708,0.014874576337817302,-1860.0,3.0,0.0,0.0,1.0,0.7451204815789421],[0.014874576337817302,24.707161677942793,-733.6842,3.0,0.0,0.0,1.0,0.6806626496512312],[24.707161677942793,26.95191505081597,0.0,3.0,8.0,4.0,-1.0,0.638674698446412],[26.95191505081597,27.51310339403426,227.85,3.0,8.0,4.0,-1.0,0.6242263788522459],[27.51310339403426,93.73332789379303,1860.0,3.0,9.0,3.0,-1.0,0.5207292323715864]]</t>
         </is>
       </c>
       <c r="C568" t="n">
@@ -15218,7 +15218,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>[[-71.58208046552647,-0.31027930225015155,-1860.0,2.0,0.0,0.0,1.0],[-0.31027930225015155,23.628340935796842,-733.6842,2.0,0.0,0.0,1.0],[23.628340935796842,26.348638690120367,0.0,2.0,9.0,3.0,-1.0],[26.348638690120367,26.892698240985084,46.5,3.0,9.0,2.0,-1.0],[26.892698240985084,27.980817342714488,1725.15,4.0,9.0,1.0,-1.0],[27.980817342714488,91.09172524302022,1860.0,4.0,9.0,1.0,-1.0]]</t>
+          <t>[[-71.58208046552647,-0.31027930225015155,-1860.0,2.0,0.0,0.0,1.0,0.8515662647114721],[-0.31027930225015155,23.628340935796842,-733.6842,2.0,0.0,0.0,1.0,0.7871084327837613],[23.628340935796842,26.348638690120367,0.0,2.0,9.0,3.0,-1.0,0.7451204815789421],[26.348638690120367,26.892698240985084,46.5,3.0,9.0,2.0,-1.0,0.7421718449270714],[26.892698240985084,27.980817342714488,1725.15,4.0,9.0,1.0,-1.0,0.6357260617945413],[27.980817342714488,91.09172524302022,1860.0,4.0,9.0,1.0,-1.0,0.6271750155041165]]</t>
         </is>
       </c>
       <c r="C569" t="n">
@@ -15244,7 +15244,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>[[-73.04705470456781,-0.4359794191675519,-1860.0,1.0,0.0,0.0,1.0],[-0.4359794191675519,23.21762843895526,-733.6842,0.0,0.0,0.0,1.0],[23.21762843895526,25.968047957341625,0.0,1.0,8.0,4.0,-1.0],[25.968047957341625,26.5181318610189,227.85,1.0,8.0,4.0,-1.0],[26.5181318610189,91.42803249493733,1860.0,1.0,9.0,3.0,-1.0]]</t>
+          <t>[[-73.04705470456781,-0.4359794191675519,-1860.0,1.0,0.0,0.0,1.0,0.9580120478440022],[-0.4359794191675519,23.21762843895526,-733.6842,0.0,0.0,0.0,1.0,0.8935542159162914],[23.21762843895526,25.968047957341625,0.0,1.0,8.0,4.0,-1.0,0.8515662647114721],[25.968047957341625,26.5181318610189,227.85,1.0,8.0,4.0,-1.0,0.837117945117306],[26.5181318610189,91.42803249493733,1860.0,1.0,9.0,3.0,-1.0,0.7336207986366465]]</t>
         </is>
       </c>
       <c r="C570" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="F570" s="4" t="inlineStr">
         <is>
-          <t>[0,0,2.7504195184,0,0.5500839037]</t>
+          <t>[23.6536078581,0,2.7504195184,0,0.5500839037]</t>
         </is>
       </c>
     </row>
@@ -15270,7 +15270,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>[[-73.21880030914004,24.402323987114897,-733.6843,0.0,0.0,0.0,1.0],[24.402323987114897,27.191498967007902,0.0,0.0,9.0,3.0,-1.0],[27.191498967007902,27.749333962986498,1725.15,2.0,9.0,1.0,-1.0],[27.749333962986498,93.57386348846126,1860.0,2.0,9.0,1.0,-1.0]]</t>
+          <t>[[-73.21880030914004,24.402323987114897,-733.6843,0.0,0.0,0.0,1.0,1.000000004771713],[24.402323987114897,27.191498967007902,0.0,0.0,9.0,3.0,-1.0,0.9580120478440022],[27.191498967007902,27.749333962986498,1725.15,2.0,9.0,1.0,-1.0,0.8486176280596014],[27.749333962986498,93.57386348846126,1860.0,2.0,9.0,1.0,-1.0,0.8400665817691766]]</t>
         </is>
       </c>
       <c r="C571" t="n">
@@ -15296,7 +15296,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>[[-73.10202975953513,26.523021707807473,0.0,0.0,0.0,1.0,1.0],[26.523021707807473,27.079586241144582,890.0,0.0,8.0,3.0,-1.0],[27.079586241144582,93.31076570826062,1860.0,0.0,9.0,2.0,-1.0]]</t>
+          <t>[[-73.10202975953513,26.523021707807473,0.0,0.0,0.0,1.0,1.0,1.000000004771713],[26.523021707807473,27.079586241144582,890.0,0.0,8.0,3.0,-1.0,0.943563733370318],[27.079586241144582,93.31076570826062,1860.0,0.0,9.0,2.0,-1.0,0.8820545386968874]]</t>
         </is>
       </c>
       <c r="C572" t="n">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>[[-73.84162679569825,22.200817841121378,-1860.0,1.0,8.0,1.0,-1.0],[22.200817841121378,23.84725974918115,-1074.7922,0.0,8.0,2.0,-1.0],[23.84725974918115,26.591329595947414,0.0,0.0,7.0,3.0,-1.0],[26.591329595947414,90.25375004092498,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-73.84162679569825,22.200817841121378,-1860.0,1.0,8.0,1.0,-1.0,0.9885003218294175],[22.200817841121378,23.84725974918115,-1074.7922,0.0,8.0,2.0,-1.0,0.9435637308655621],[23.84725974918115,26.591329595947414,0.0,0.0,7.0,3.0,-1.0,0.8820545386968874],[26.591329595947414,90.25375004092498,1860.0,0.0,8.0,2.0,-1.0,0.7641090726220618]]</t>
         </is>
       </c>
       <c r="C573" t="n">
@@ -15348,7 +15348,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>[[-70.23068965357729,22.89514781831255,-1860.0,1.0,7.0,1.0,-1.0],[22.89514781831255,24.500765705758923,-1074.7922,0.0,7.0,2.0,-1.0],[24.500765705758923,27.176795518169556,0.0,0.0,6.0,3.0,-1.0],[27.176795518169556,89.79589312857823,1860.0,0.0,7.0,2.0,-1.0]]</t>
+          <t>[[-70.23068965357729,22.89514781831255,-1860.0,1.0,7.0,1.0,-1.0,0.8705548557545919],[22.89514781831255,24.500765705758923,-1074.7922,0.0,7.0,2.0,-1.0,0.8256182647907365],[24.500765705758923,27.176795518169556,0.0,0.0,6.0,3.0,-1.0,0.7641090726220618],[27.176795518169556,89.79589312857823,1860.0,0.0,7.0,2.0,-1.0,0.6461636065472363]]</t>
         </is>
       </c>
       <c r="C574" t="n">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>[[-71.70920061542468,22.719347992490967,-1860.0,1.0,6.0,1.0,-1.0],[22.719347992490967,23.804733608673914,-1074.7922,0.0,6.0,2.0,-1.0],[23.804733608673914,25.975504841039793,0.0,0.0,5.0,3.0,-1.0],[25.975504841039793,26.518197649131253,890.0001,0.0,5.0,3.0,-1.0],[26.518197649131253,90.55594900392461,1860.0,0.0,6.0,2.0,-1.0]]</t>
+          <t>[[-71.70920061542468,22.719347992490967,-1860.0,1.0,6.0,1.0,-1.0,0.7526093896797663],[22.719347992490967,23.804733608673914,-1074.7922,0.0,6.0,2.0,-1.0,0.7076727987159109],[23.804733608673914,25.975504841039793,0.0,0.0,5.0,3.0,-1.0,0.6461636065472363],[25.975504841039793,26.518197649131253,890.0001,0.0,5.0,3.0,-1.0,0.5897273288046871],[26.518197649131253,90.55594900392461,1860.0,0.0,6.0,2.0,-1.0,0.5282181404724107]]</t>
         </is>
       </c>
       <c r="C575" t="n">
@@ -15400,7 +15400,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>[[-72.34832234637152,22.846239655238875,-1860.0,1.0,5.0,1.0,-1.0],[22.846239655238875,23.390208580962366,-1074.7922,0.0,5.0,2.0,-1.0],[23.390208580962366,26.110053209579803,0.0,0.0,4.0,3.0,-1.0],[26.110053209579803,90.2983864449514,1860.0,0.0,4.0,3.0,-1.0]]</t>
+          <t>[[-72.34832234637152,22.846239655238875,-1860.0,1.0,5.0,1.0,-1.0,0.6346639236049407],[22.846239655238875,23.390208580962366,-1074.7922,0.0,5.0,2.0,-1.0,0.5897273326410853],[23.390208580962366,26.110053209579803,0.0,0.0,4.0,3.0,-1.0,0.5282181404724107],[26.110053209579803,90.2983864449514,1860.0,0.0,4.0,3.0,-1.0,0.410272674397585]]</t>
         </is>
       </c>
       <c r="C576" t="n">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>[[-71.00409205681312,22.36595753970859,-1860.0,1.0,4.0,1.0,-1.0],[22.36595753970859,23.98509134774075,-1074.7922,0.0,4.0,2.0,-1.0],[23.98509134774075,26.68364769446103,0.0,0.0,3.0,3.0,-1.0],[26.68364769446103,27.223358963805097,890.0001,0.0,3.0,3.0,-1.0],[27.223358963805097,90.36957747705966,1860.0,0.0,3.0,3.0,-1.0]]</t>
+          <t>[[-71.00409205681312,22.36595753970859,-1860.0,1.0,4.0,1.0,-1.0,0.5167184575301151],[22.36595753970859,23.98509134774075,-1074.7922,0.0,4.0,2.0,-1.0,0.4717818665662597],[23.98509134774075,26.68364769446103,0.0,0.0,3.0,3.0,-1.0,0.410272674397585],[26.68364769446103,27.223358963805097,890.0001,0.0,3.0,3.0,-1.0,0.35383639665503586],[27.223358963805097,90.36957747705966,1860.0,0.0,3.0,3.0,-1.0,0.2923272083227594]]</t>
         </is>
       </c>
       <c r="C577" t="n">
@@ -15452,7 +15452,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>[[-67.11912606720267,23.216165016479124,-1860.0,1.0,3.0,1.0,-1.0],[23.216165016479124,23.709800486881747,-1074.7922,0.0,3.0,2.0,-1.0],[23.709800486881747,26.17797783889492,0.0,0.0,2.0,3.0,-1.0],[26.17797783889492,28.15251972050544,890.0001,0.0,2.0,3.0,-1.0],[28.15251972050544,80.47787958318453,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[-67.11912606720267,23.216165016479124,-1860.0,1.0,3.0,1.0,-1.0,0.3987729914552895],[23.216165016479124,23.709800486881747,-1074.7922,0.0,3.0,2.0,-1.0,0.35383640049143406],[23.709800486881747,26.17797783889492,0.0,0.0,2.0,3.0,-1.0,0.2923272083227594],[26.17797783889492,28.15251972050544,890.0001,0.0,2.0,3.0,-1.0,0.23589093058021024],[28.15251972050544,80.47787958318453,1860.0,0.0,3.0,2.0,-1.0,0.17438174224793374]]</t>
         </is>
       </c>
       <c r="C578" t="n">
@@ -15478,7 +15478,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>[[-67.86662808025613,23.35845969044007,-1860.0,1.0,2.0,1.0,-1.0],[23.35845969044007,28.316344895369213,0.0,0.0,2.0,3.0,-1.0],[28.316344895369213,28.81213341586212,1678.65,1.0,2.0,1.0,-1.0],[28.81213341586212,80.37413954712518,1860.0,1.0,3.0,0.0,-1.0]]</t>
+          <t>[[-67.86662808025613,23.35845969044007,-1860.0,1.0,2.0,1.0,-1.0,0.3423367137127403],[23.35845969044007,28.316344895369213,0.0,0.0,2.0,3.0,-1.0,0.2358909305802102],[28.316344895369213,28.81213341586212,1678.65,1.0,2.0,1.0,-1.0,0.1294451474476801],[28.81213341586212,80.37413954712518,1860.0,1.0,3.0,0.0,-1.0,0.11794546450538458]]</t>
         </is>
       </c>
       <c r="C579" t="n">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>[[-67.86924670332263,24.072597554449032,-1860.0,1.0,2.0,0.0,-1.0],[24.072597554449032,29.539409915721933,0.0,0.0,2.0,2.0,-1.0],[29.539409915721933,80.72865293491373,1860.0,1.0,2.0,0.0,-1.0]]</t>
+          <t>[[-67.86924670332263,24.072597554449032,-1860.0,1.0,2.0,0.0,-1.0,0.3423367137127403],[24.072597554449032,29.539409915721933,0.0,0.0,2.0,2.0,-1.0,0.2358909305802102],[29.539409915721933,80.72865293491373,1860.0,1.0,2.0,0.0,-1.0,0.11794546450538458]]</t>
         </is>
       </c>
       <c r="C580" t="n">
@@ -15530,7 +15530,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>[[-64.91878341317573,21.036204944232082,-1860.0,1.0,2.0,0.0,-1.0],[21.036204944232082,29.631703779972867,0.0,0.0,2.0,1.0,-1.0],[29.631703779972867,77.86200280274059,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-64.91878341317573,21.036204944232082,-1860.0,1.0,2.0,0.0,-1.0,0.3423367137127403],[21.036204944232082,29.631703779972867,0.0,0.0,2.0,1.0,-1.0,0.2358909305802102],[29.631703779972867,77.86200280274059,1860.0,0.0,1.0,0.0,-1.0,0.11794546450538458]]</t>
         </is>
       </c>
       <c r="C581" t="n">
@@ -15556,7 +15556,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>[[-66.9817029985548,-4.128977742443318,-1860.0,1.0,2.0,0.0,-1.0],[-4.128977742443318,24.080513120535855,0.0,0.0,2.0,1.0,-1.0],[24.080513120535855,80.99439819496753,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-66.9817029985548,-4.128977742443318,-1860.0,1.0,2.0,0.0,-1.0,0.3423367137127403],[-4.128977742443318,24.080513120535855,0.0,0.0,2.0,1.0,-1.0,0.2358909305802102],[24.080513120535855,80.99439819496753,1860.0,0.0,2.0,0.0,-1.0,0.11794546450538458]]</t>
         </is>
       </c>
       <c r="C582" t="n">
@@ -15582,7 +15582,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>[[-66.35930603878737,-4.403292060948843,-1860.0,10.0,1.0,0.0,1.0],[-4.403292060948843,22.012062735804022,0.0,0.0,1.0,1.0,-1.0],[22.012062735804022,24.41345862641792,0.0,0.0,0.0,1.0,-1.0],[24.41345862641792,26.814854517031804,1860.0,0.0,0.0,0.0,-1.0],[26.814854517031804,77.24416821992364,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-66.35930603878737,-4.403292060948843,-1860.0,10.0,1.0,0.0,1.0,0.2243912476379147],[-4.403292060948843,22.012062735804022,0.0,0.0,1.0,1.0,-1.0,0.1179454645053846],[22.012062735804022,24.41345862641792,0.0,0.0,0.0,1.0,-1.0,0.1179454645053846],[24.41345862641792,26.814854517031804,1860.0,0.0,0.0,0.0,-1.0,-1.569441035464969e-09],[26.814854517031804,77.24416821992364,1860.0,0.0,1.0,0.0,-1.0,-1.569441035464969e-09]]</t>
         </is>
       </c>
       <c r="C583" t="n">
@@ -15598,7 +15598,7 @@
       </c>
       <c r="F583" s="4" t="inlineStr">
         <is>
-          <t>[0,0,26.4153547968,0,0]</t>
+          <t>[0,0,28.8167506874,0,0]</t>
         </is>
       </c>
     </row>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>[[-61.74931111486082,-3.797435212398618,-1860.0,1.0,0.0,0.0,-1.0],[-3.797435212398618,69.52046839147403,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-61.74931111486082,-3.797435212398618,-1860.0,1.0,0.0,0.0,-1.0,0.10644578156308909],[-3.797435212398618,69.52046839147403,0.0,0.0,0.0,1.0,-1.0,-1.569441021587181e-09]]</t>
         </is>
       </c>
       <c r="C584" t="n">
@@ -15634,7 +15634,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>[[-63.02918942205004,-10.167424852820616,-1860.0,9.0,0.0,0.0,1.0],[-10.167424852820616,-4.243261582131119,-733.6842,9.0,0.0,0.0,1.0],[-4.243261582131119,73.22656580380857,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-63.02918942205004,-10.167424852820616,-1860.0,9.0,0.0,0.0,1.0,0.10644578156308909],[-10.167424852820616,-4.243261582131119,-733.6842,9.0,0.0,0.0,1.0,0.041987949635378254],[-4.243261582131119,73.22656580380857,0.0,0.0,0.0,1.0,-1.0,-1.569441021587181e-09]]</t>
         </is>
       </c>
       <c r="C585" t="n">
@@ -15660,7 +15660,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>[[-60.326378557156744,-4.44826753367461,-1860.0,9.0,0.0,0.0,1.0],[-4.44826753367461,15.477260428187236,-733.6842,9.0,0.0,0.0,1.0],[15.477260428187236,69.18955319494525,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-60.326378557156744,-4.44826753367461,-1860.0,9.0,0.0,0.0,1.0,0.10644578156308909],[-4.44826753367461,15.477260428187236,-733.6842,9.0,0.0,0.0,1.0,0.041987949635378254],[15.477260428187236,69.18955319494525,0.0,0.0,0.0,1.0,-1.0,-1.569441021587181e-09]]</t>
         </is>
       </c>
       <c r="C586" t="n">
@@ -15686,7 +15686,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>[[-61.06655967764078,-3.8576436859492205,-1860.0,8.0,0.0,0.0,1.0],[-3.8576436859492205,15.794274021120401,-733.6842,8.0,0.0,0.0,1.0],[15.794274021120401,17.54111115063769,0.0,8.0,8.0,3.0,-1.0],[17.54111115063769,18.851238997775667,227.85,8.0,8.0,1.0,-1.0],[18.851238997775667,69.50951575377735,1678.6501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-61.06655967764078,-3.8576436859492205,-1860.0,8.0,0.0,0.0,1.0,0.2128915646956192],[-3.8576436859492205,15.794274021120401,-733.6842,8.0,0.0,0.0,1.0,0.1484337327679084],[15.794274021120401,17.54111115063769,0.0,8.0,8.0,3.0,-1.0,0.1064457815630891],[17.54111115063769,18.851238997775667,227.85,8.0,8.0,1.0,-1.0,0.09199746196892297],[18.851238997775667,69.50951575377735,1678.6501,0.0,0.0,0.0,-1.0,-7.910595109517082e-09]]</t>
         </is>
       </c>
       <c r="C587" t="n">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>[[-61.66799279458303,-4.194562170793866,-1860.0,7.0,0.0,0.0,1.0],[-4.194562170793866,15.854308977039565,-733.6842,7.0,0.0,0.0,1.0],[15.854308977039565,17.63643085684697,0.0,7.0,9.0,2.0,-1.0],[17.63643085684697,18.52749179675068,46.5,8.0,9.0,1.0,-1.0],[18.52749179675068,18.973022266702543,227.85,7.0,8.0,1.0,-1.0],[18.973022266702543,71.54561772102132,1860.0,7.0,9.0,0.0,-1.0]]</t>
+          <t>[[-61.66799279458303,-4.194562170793866,-1860.0,7.0,0.0,0.0,1.0,0.3193373478281493],[-4.194562170793866,15.854308977039565,-733.6842,7.0,0.0,0.0,1.0,0.2548795159004385],[15.854308977039565,17.63643085684697,0.0,7.0,9.0,2.0,-1.0,0.2128915646956192],[17.63643085684697,18.52749179675068,46.5,8.0,9.0,1.0,-1.0,0.20994292804374856],[18.52749179675068,18.973022266702543,227.85,7.0,8.0,1.0,-1.0,0.19844324510145306],[18.973022266702543,71.54561772102132,1860.0,7.0,9.0,0.0,-1.0,0.09494609862079358]]</t>
         </is>
       </c>
       <c r="C588" t="n">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>[[-61.15893472842964,-4.147685863810359,-1860.0,6.0,0.0,0.0,1.0],[-4.147685863810359,15.586977204711701,-733.6842,6.0,0.0,0.0,1.0],[15.586977204711701,17.341169477469208,0.0,7.0,9.0,1.0,-1.0],[17.341169477469208,19.09536175022673,46.5,7.0,9.0,1.0,-1.0],[19.09536175022673,19.972457886605483,1725.15,8.0,9.0,0.0,-1.0],[19.972457886605483,69.9669376601947,1860.0,8.0,9.0,0.0,-1.0]]</t>
+          <t>[[-61.15893472842964,-4.147685863810359,-1860.0,6.0,0.0,0.0,1.0,0.42578313096067943],[-4.147685863810359,15.586977204711701,-733.6842,6.0,0.0,0.0,1.0,0.3613252990329686],[15.586977204711701,17.341169477469208,0.0,7.0,9.0,1.0,-1.0,0.3193373478281493],[17.341169477469208,19.09536175022673,46.5,7.0,9.0,1.0,-1.0,0.3163887111762787],[19.09536175022673,19.972457886605483,1725.15,8.0,9.0,0.0,-1.0,0.20994292804374856],[19.972457886605483,69.9669376601947,1860.0,8.0,9.0,0.0,-1.0,0.20139188175332368]]</t>
         </is>
       </c>
       <c r="C589" t="n">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>[[-59.34169778937822,-4.233449462244032,-1860.0,5.0,0.0,0.0,1.0],[-4.233449462244032,15.266392253511135,-733.6842,5.0,0.0,0.0,1.0],[15.266392253511135,16.962030663576805,0.0,6.0,9.0,1.0,-1.0],[16.962030663576805,18.657669073642474,46.5,6.0,9.0,1.0,-1.0],[18.657669073642474,19.08157867615889,227.85,5.0,8.0,1.0,-1.0],[19.08157867615889,67.40727336303041,1860.0,5.0,9.0,0.0,-1.0]]</t>
+          <t>[[-59.34169778937822,-4.233449462244032,-1860.0,5.0,0.0,0.0,1.0,0.5322289140932095],[-4.233449462244032,15.266392253511135,-733.6842,5.0,0.0,0.0,1.0,0.4677710821654987],[15.266392253511135,16.962030663576805,0.0,6.0,9.0,1.0,-1.0,0.4257831309606794],[16.962030663576805,18.657669073642474,46.5,6.0,9.0,1.0,-1.0,0.42283449430880876],[18.657669073642474,19.08157867615889,227.85,5.0,8.0,1.0,-1.0,0.41133481136651323],[19.08157867615889,67.40727336303041,1860.0,5.0,9.0,0.0,-1.0,0.30783766488585373]]</t>
         </is>
       </c>
       <c r="C590" t="n">
@@ -15790,7 +15790,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>[[-61.119593128447576,-4.123368487131742,-1860.0,4.0,0.0,0.0,1.0],[-4.123368487131742,15.606093888708344,-733.6842,4.0,0.0,0.0,1.0],[15.606093888708344,17.359823877671914,0.0,5.0,9.0,1.0,-1.0],[17.359823877671914,18.236688872153692,46.5,5.0,9.0,1.0,-1.0],[18.236688872153692,19.113553866635485,227.85,4.0,8.0,1.0,-1.0],[19.113553866635485,69.97172354657881,1860.0,4.0,9.0,0.0,-1.0]]</t>
+          <t>[[-61.119593128447576,-4.123368487131742,-1860.0,4.0,0.0,0.0,1.0,0.6386746972257396],[-4.123368487131742,15.606093888708344,-733.6842,4.0,0.0,0.0,1.0,0.5742168652980287],[15.606093888708344,17.359823877671914,0.0,5.0,9.0,1.0,-1.0,0.5322289140932095],[17.359823877671914,18.236688872153692,46.5,5.0,9.0,1.0,-1.0,0.5292802774413389],[18.236688872153692,19.113553866635485,227.85,4.0,8.0,1.0,-1.0,0.5177805944990433],[19.113553866635485,69.97172354657881,1860.0,4.0,9.0,0.0,-1.0,0.41428344801838385]]</t>
         </is>
       </c>
       <c r="C591" t="n">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>[[-61.75664350184151,-4.153588495592551,-1860.0,3.0,0.0,0.0,1.0],[-4.153588495592551,15.63372047601969,-733.6842,3.0,0.0,0.0,1.0],[15.63372047601969,17.39259238460744,0.0,3.0,8.0,3.0,-1.0],[17.39259238460744,18.711746316048263,227.85,3.0,8.0,1.0,-1.0],[18.711746316048263,69.71903166509314,1860.0,3.0,9.0,0.0,-1.0]]</t>
+          <t>[[-61.75664350184151,-4.153588495592551,-1860.0,3.0,0.0,0.0,1.0,0.7451204803582696],[-4.153588495592551,15.63372047601969,-733.6842,3.0,0.0,0.0,1.0,0.6806626484305588],[15.63372047601969,17.39259238460744,0.0,3.0,8.0,3.0,-1.0,0.6386746972257396],[17.39259238460744,18.711746316048263,227.85,3.0,8.0,1.0,-1.0,0.6242263776315734],[18.711746316048263,69.71903166509314,1860.0,3.0,9.0,0.0,-1.0,0.520729231150914]]</t>
         </is>
       </c>
       <c r="C592" t="n">
@@ -15842,7 +15842,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>[[-56.08557154369497,-4.024559246389764,-1860.0,2.0,0.0,0.0,1.0],[-4.024559246389764,15.498320365099687,-733.6842,2.0,0.0,0.0,1.0],[15.498320365099687,17.53195365796317,0.0,3.0,9.0,1.0,-1.0],[17.53195365796317,17.938680316535866,46.5,3.0,9.0,1.0,-1.0],[17.938680316535866,19.158860292253962,227.85,2.0,8.0,1.0,-1.0],[19.158860292253962,65.5256993695414,1860.0,2.0,9.0,0.0,-1.0]]</t>
+          <t>[[-56.08557154369497,-4.024559246389764,-1860.0,2.0,0.0,0.0,1.0,0.8515662634907997],[-4.024559246389764,15.498320365099687,-733.6842,2.0,0.0,0.0,1.0,0.7871084315630889],[15.498320365099687,17.53195365796317,0.0,3.0,9.0,1.0,-1.0,0.7451204803582696],[17.53195365796317,17.938680316535866,46.5,3.0,9.0,1.0,-1.0,0.742171843706399],[17.938680316535866,19.158860292253962,227.85,2.0,8.0,1.0,-1.0,0.7306721607641035],[19.158860292253962,65.5256993695414,1860.0,2.0,9.0,0.0,-1.0,0.627175014283444]]</t>
         </is>
       </c>
       <c r="C593" t="n">
@@ -15868,7 +15868,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>[[-53.5951423978797,-4.0015687357938035,-1860.0,1.0,0.0,0.0,1.0],[-4.0015687357938035,15.755220771866433,-733.6842,1.0,0.0,0.0,1.0],[15.755220771866433,17.36801991534891,0.0,2.0,9.0,1.0,-1.0],[17.36801991534891,18.57761927296076,46.5,2.0,9.0,1.0,-1.0],[18.57761927296076,19.384018844701984,227.85,1.0,8.0,1.0,-1.0],[19.384018844701984,66.9615935774348,1860.0,1.0,9.0,0.0,-1.0]]</t>
+          <t>[[-53.5951423978797,-4.0015687357938035,-1860.0,1.0,0.0,0.0,1.0,0.9580120466233297],[-4.0015687357938035,15.755220771866433,-733.6842,1.0,0.0,0.0,1.0,0.8935542146956189],[15.755220771866433,17.36801991534891,0.0,2.0,9.0,1.0,-1.0,0.8515662634907997],[17.36801991534891,18.57761927296076,46.5,2.0,9.0,1.0,-1.0,0.848617626838929],[18.57761927296076,19.384018844701984,227.85,1.0,8.0,1.0,-1.0,0.8371179438966335],[19.384018844701984,66.9615935774348,1860.0,1.0,9.0,0.0,-1.0,0.7336207974159741]]</t>
         </is>
       </c>
       <c r="C594" t="n">
@@ -15894,7 +15894,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>[[-55.29238463564716,15.734383592991897,-733.6843,0.0,0.0,0.0,1.0],[15.734383592991897,17.775382680021757,0.0,1.0,9.0,1.0,-1.0],[17.775382680021757,18.18358249742773,46.5,1.0,9.0,1.0,-1.0],[18.18358249742773,19.408181949645645,227.85,0.0,8.0,1.0,-1.0],[19.408181949645645,66.75936076873836,1860.0,0.0,9.0,0.0,-1.0]]</t>
+          <t>[[-55.29238463564716,15.734383592991897,-733.6843,0.0,0.0,0.0,1.0,1.0000000035510406],[15.734383592991897,17.775382680021757,0.0,1.0,9.0,1.0,-1.0,0.9580120466233297],[17.775382680021757,18.18358249742773,46.5,1.0,9.0,1.0,-1.0,0.9550634099714591],[18.18358249742773,19.408181949645645,227.85,0.0,8.0,1.0,-1.0,0.9435637270291636],[19.408181949645645,66.75936076873836,1860.0,0.0,9.0,0.0,-1.0,0.8400665805485041]]</t>
         </is>
       </c>
       <c r="C595" t="n">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>[[-52.606184947931744,16.38323175230277,0.0,0.0,0.0,1.0,1.0],[16.38323175230277,18.762177155759126,708.65,1.0,9.0,0.0,-1.0],[18.762177155759126,20.348140758063373,890.0,0.0,8.0,0.0,-1.0],[20.348140758063373,65.94459432431032,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-52.606184947931744,16.38323175230277,0.0,0.0,0.0,1.0,1.0,1.000000003551041],[16.38323175230277,18.762177155759126,708.65,1.0,9.0,0.0,-1.0,0.9550634150919415],[18.762177155759126,20.348140758063373,890.0,0.0,8.0,0.0,-1.0,0.943563732149646],[20.348140758063373,65.94459432431032,1860.0,0.0,8.0,0.0,-1.0,0.8820545374762154]]</t>
         </is>
       </c>
       <c r="C596" t="n">
@@ -15946,7 +15946,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>[[-53.341423857788556,13.277782341966855,-785.2078,0.0,0.0,0.0,1.0],[13.277782341966855,14.873451951541838,0.0,0.0,8.0,1.0,-1.0],[14.873451951541838,16.469121561116808,181.3501,0.0,8.0,1.0,-1.0],[16.469121561116808,65.93487945794118,1860.0,0.0,9.0,0.0,-1.0]]</t>
+          <t>[[-53.341423857788556,13.277782341966855,-785.2078,0.0,0.0,0.0,1.0,1.0000000060557965],[13.277782341966855,14.873451951541838,0.0,0.0,8.0,1.0,-1.0,0.955063415091941],[14.873451951541838,16.469121561116808,181.3501,0.0,8.0,1.0,-1.0,0.9435637258084915],[16.469121561116808,65.93487945794118,1860.0,0.0,9.0,0.0,-1.0,0.8371179490171154]]</t>
         </is>
       </c>
       <c r="C597" t="n">
@@ -15972,7 +15972,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>[[-56.575043771127724,-3.687302901063454,-1860.0,1.0,8.0,0.0,-1.0],[-3.687302901063454,13.373258669925022,-1859.9999,0.0,8.0,0.0,-1.0],[13.373258669925022,14.652800787749158,0.0,0.0,7.0,1.0,-1.0],[14.652800787749158,16.358856944848,181.3501,0.0,7.0,1.0,-1.0],[16.358856944848,70.95265397201112,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-56.575043771127724,-3.687302901063454,-1860.0,1.0,8.0,0.0,-1.0,0.9435637321496455],[-3.687302901063454,13.373258669925022,-1859.9999,0.0,8.0,0.0,-1.0,0.943563726426754],[13.373258669925022,14.652800787749158,0.0,0.0,7.0,1.0,-1.0,0.8371179490171154],[14.652800787749158,16.358856944848,181.3501,0.0,7.0,1.0,-1.0,0.8256182597336659],[16.358856944848,70.95265397201112,1860.0,0.0,8.0,0.0,-1.0,0.7191724829422899]]</t>
         </is>
       </c>
       <c r="C598" t="n">
@@ -15998,7 +15998,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>[[-60.937715578558844,-3.5146334426300783,-1860.0,1.0,7.0,0.0,-1.0],[-3.5146334426300783,13.09534899338238,-1859.9999,0.0,7.0,0.0,-1.0],[13.09534899338238,14.519061773612016,0.0,0.0,6.0,1.0,-1.0],[14.519061773612016,15.942774553841652,181.3501,0.0,6.0,1.0,-1.0],[15.942774553841652,80.95899151766181,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-60.937715578558844,-3.5146334426300783,-1860.0,1.0,7.0,0.0,-1.0,0.8256182660748199],[-3.5146334426300783,13.09534899338238,-1859.9999,0.0,7.0,0.0,-1.0,0.8256182603519284],[13.09534899338238,14.519061773612016,0.0,0.0,6.0,1.0,-1.0,0.7191724829422899],[14.519061773612016,15.942774553841652,181.3501,0.0,6.0,1.0,-1.0,0.7076727936588403],[15.942774553841652,80.95899151766181,1860.0,0.0,7.0,0.0,-1.0,0.6012270168674643]]</t>
         </is>
       </c>
       <c r="C599" t="n">
@@ -16024,7 +16024,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>[[-62.83697201651942,-3.478265428907612,-1860.0,1.0,6.0,0.0,-1.0],[-3.478265428907612,13.691608377426384,-1859.9999,0.0,6.0,0.0,-1.0],[13.691608377426384,15.163311846540715,0.0,0.0,5.0,1.0,-1.0],[15.163311846540715,16.63501531565506,181.3501,0.0,5.0,1.0,-1.0],[16.63501531565506,83.8428070718767,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[-62.83697201651942,-3.478265428907612,-1860.0,1.0,6.0,0.0,-1.0,0.7076727999999943],[-3.478265428907612,13.691608377426384,-1859.9999,0.0,6.0,0.0,-1.0,0.7076727942771028],[13.691608377426384,15.163311846540715,0.0,0.0,5.0,1.0,-1.0,0.6012270168674643],[15.163311846540715,16.63501531565506,181.3501,0.0,5.0,1.0,-1.0,0.5897273275840147],[16.63501531565506,83.8428070718767,1860.0,0.0,6.0,0.0,-1.0,0.4832815507926386]]</t>
         </is>
       </c>
       <c r="C600" t="n">
@@ -16050,7 +16050,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>[[-61.09897627080342,-3.7391080067222617,-1860.0,1.0,5.0,0.0,-1.0],[-3.7391080067222617,13.468852472502093,-1859.9999,0.0,5.0,0.0,-1.0],[13.468852472502093,14.90284917910411,0.0,0.0,4.0,1.0,-1.0],[14.90284917910411,16.33684588570614,181.3501,0.0,4.0,1.0,-1.0],[16.33684588570614,81.8226954871988,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-61.09897627080342,-3.7391080067222617,-1860.0,1.0,5.0,0.0,-1.0,0.5897273339251687],[-3.7391080067222617,13.468852472502093,-1859.9999,0.0,5.0,0.0,-1.0,0.5897273282022771],[13.468852472502093,14.90284917910411,0.0,0.0,4.0,1.0,-1.0,0.4832815507926386],[14.90284917910411,16.33684588570614,181.3501,0.0,4.0,1.0,-1.0,0.47178186150918905],[16.33684588570614,81.8226954871988,1860.0,0.0,5.0,0.0,-1.0,0.365336084717813]]</t>
         </is>
       </c>
       <c r="C601" t="n">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>[[-58.93685726436499,-3.3853564560232385,-1860.0,1.0,4.0,0.0,-1.0],[-3.3853564560232385,13.601466105205233,-1859.9999,0.0,4.0,0.0,-1.0],[13.601466105205233,14.978776042602135,0.0,0.0,3.0,1.0,-1.0],[14.978776042602135,16.815189292464666,181.3501,0.0,3.0,1.0,-1.0],[16.815189292464666,78.33503316285967,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-58.93685726436499,-3.3853564560232385,-1860.0,1.0,4.0,0.0,-1.0,0.4717818678503431],[-3.3853564560232385,13.601466105205233,-1859.9999,0.0,4.0,0.0,-1.0,0.47178186212745155],[13.601466105205233,14.978776042602135,0.0,0.0,3.0,1.0,-1.0,0.365336084717813],[14.978776042602135,16.815189292464666,181.3501,0.0,3.0,1.0,-1.0,0.3538363954343634],[16.815189292464666,78.33503316285967,1860.0,0.0,4.0,0.0,-1.0,0.24739061864298734]]</t>
         </is>
       </c>
       <c r="C602" t="n">
@@ -16102,7 +16102,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>[[-60.40256446941761,-3.450281297970406,-1860.0,1.0,3.0,0.0,-1.0],[-3.450281297970406,13.49419964560066,-1859.9999,0.0,3.0,0.0,-1.0],[13.49419964560066,14.906239724231582,0.0,0.0,2.0,1.0,-1.0],[14.906239724231582,16.318279802862506,181.3501,0.0,2.0,1.0,-1.0],[16.318279802862506,80.3307633674643,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-60.40256446941761,-3.450281297970406,-1860.0,1.0,3.0,0.0,-1.0,0.35383640177551745],[-3.450281297970406,13.49419964560066,-1859.9999,0.0,3.0,0.0,-1.0,0.35383639605262585],[13.49419964560066,14.906239724231582,0.0,0.0,2.0,1.0,-1.0,0.2473906186429873],[14.906239724231582,16.318279802862506,181.3501,0.0,2.0,1.0,-1.0,0.23589092935953773],[16.318279802862506,80.3307633674643,1860.0,0.0,3.0,0.0,-1.0,0.1294451525681617]]</t>
         </is>
       </c>
       <c r="C603" t="n">
@@ -16128,7 +16128,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>[[-61.449530049013056,-3.598949030749303,-1860.0,1.0,2.0,0.0,-1.0],[-3.598949030749303,13.612794082122555,-1859.9999,0.0,2.0,0.0,-1.0],[13.612794082122555,15.047106008195207,0.0,0.0,1.0,1.0,-1.0],[15.047106008195207,16.959521909625416,181.3501,0.0,1.0,1.0,-1.0],[16.959521909625416,81.5035585828949,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-61.449530049013056,-3.598949030749303,-1860.0,1.0,2.0,0.0,-1.0,0.2358909357006918],[-3.598949030749303,13.612794082122555,-1859.9999,0.0,2.0,0.0,-1.0,0.23589092997780026],[13.612794082122555,15.047106008195207,0.0,0.0,1.0,1.0,-1.0,0.1294451525681617],[15.047106008195207,16.959521909625416,181.3501,0.0,1.0,1.0,-1.0,0.1179454632847121],[16.959521909625416,81.5035585828949,1860.0,0.0,2.0,0.0,-1.0,0.011499686493336062]]</t>
         </is>
       </c>
       <c r="C604" t="n">
@@ -16154,7 +16154,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>[[-60.57858166422504,-3.880126614406535,-1860.0,1.0,1.0,0.0,-1.0],[-3.880126614406535,16.607550420401836,-1859.9999,0.0,1.0,0.0,-1.0],[16.607550420401836,18.03692323678382,0.0,0.0,0.0,1.0,-1.0],[18.03692323678382,20.41921126408711,181.3501,0.0,0.0,0.0,-1.0],[20.41921126408711,81.88224236851221,181.3502,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-60.57858166422504,-3.880126614406535,-1860.0,1.0,1.0,0.0,-1.0,0.11794546962586618],[-3.880126614406535,16.607550420401836,-1859.9999,0.0,1.0,0.0,-1.0,0.11794546390297461],[16.607550420401836,18.03692323678382,0.0,0.0,0.0,1.0,-1.0,0.01149968649333606],[18.03692323678382,20.41921126408711,181.3501,0.0,0.0,0.0,-1.0,-2.790113529105298e-09],[20.41921126408711,81.88224236851221,181.3502,0.0,0.0,0.0,-1.0,-9.131267618769923e-09]]</t>
         </is>
       </c>
       <c r="C605" t="n">
@@ -16170,7 +16170,7 @@
       </c>
       <c r="F605" s="4" t="inlineStr">
         <is>
-          <t>[0,20.4876770348,0,0,0]</t>
+          <t>[0,20.4876770348,1.4293728164,0,0]</t>
         </is>
       </c>
     </row>
@@ -16180,7 +16180,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>[[-60.935328120962026,12.090086756429287,-1860.0,1.0,1.0,0.0,-1.0],[12.090086756429287,13.038468767823971,0.0,0.0,1.0,1.0,-1.0],[13.038468767823971,14.46104178491602,0.0,0.0,0.0,1.0,-1.0],[14.46104178491602,80.84778258254448,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-60.935328120962026,12.090086756429287,-1860.0,1.0,1.0,0.0,-1.0,0.22439124703550473],[12.090086756429287,13.038468767823971,0.0,0.0,1.0,1.0,-1.0,0.1179454639029746],[13.038468767823971,14.46104178491602,0.0,0.0,0.0,1.0,-1.0,0.1179454639029746],[14.46104178491602,80.84778258254448,1860.0,0.0,1.0,0.0,-1.0,-2.1718510323509577e-09]]</t>
         </is>
       </c>
       <c r="C606" t="n">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="F606" s="4" t="inlineStr">
         <is>
-          <t>[0,0,0.9483820114,0,0]</t>
+          <t>[0,0,2.3709550285,0,0]</t>
         </is>
       </c>
     </row>
@@ -16206,7 +16206,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>[[-60.96753749295767,12.010243793325039,-1860.0,1.0,0.0,0.0,-1.0],[12.010243793325039,81.64917234101965,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-60.96753749295767,12.010243793325039,-1860.0,1.0,0.0,0.0,-1.0,0.1064457809606791],[12.010243793325039,81.64917234101965,0.0,0.0,0.0,1.0,-1.0,-2.17185101847317e-09]]</t>
         </is>
       </c>
       <c r="C607" t="n">
@@ -16232,7 +16232,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>[[-60.61226158181542,-3.114785636291323,-1860.0,10.0,0.0,0.0,1.0],[-3.114785636291323,81.46827815133918,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-60.61226158181542,-3.114785636291323,-1860.0,10.0,0.0,0.0,1.0,0.1064457809606791],[-3.114785636291323,81.46827815133918,0.0,0.0,0.0,1.0,-1.0,-2.17185101847317e-09]]</t>
         </is>
       </c>
       <c r="C608" t="n">
@@ -16258,7 +16258,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>[[-61.054942406552776,-3.7740749035792476,-1860.0,9.0,0.0,0.0,1.0],[-3.7740749035792476,6.7274174719659,-733.6842,9.0,0.0,0.0,1.0],[6.7274174719659,81.66988578835625,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-61.054942406552776,-3.7740749035792476,-1860.0,9.0,0.0,0.0,1.0,0.1064457809606791],[-3.7740749035792476,6.7274174719659,-733.6842,9.0,0.0,0.0,1.0,0.04198794903296826],[6.7274174719659,81.66988578835625,0.0,0.0,0.0,1.0,-1.0,-2.17185101847317e-09]]</t>
         </is>
       </c>
       <c r="C609" t="n">
@@ -16284,7 +16284,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>[[-62.23350227029674,7.361259121091308,-1860.0,9.0,0.0,0.0,1.0],[7.361259121091308,24.14297463390828,0.0,9.0,0.0,1.0,1.0],[24.14297463390828,85.34687826888783,662.1501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-62.23350227029674,7.361259121091308,-1860.0,9.0,0.0,0.0,1.0,0.14843373216549838],[7.361259121091308,24.14297463390828,0.0,9.0,0.0,1.0,1.0,0.04198794903296826],[24.14297463390828,85.34687826888783,662.1501,0.0,0.0,0.0,-1.0,-9.115414742466577e-09]]</t>
         </is>
       </c>
       <c r="C610" t="n">
@@ -16310,7 +16310,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>[[-61.159274141658855,6.319463860506204,-1860.0,8.0,0.0,0.0,1.0],[6.319463860506204,25.32755907238368,0.0,8.0,0.0,1.0,1.0],[25.32755907238368,30.55478525564999,1678.65,9.0,0.0,0.0,1.0],[30.55478525564999,80.9262375671253,1860.0,9.0,9.0,1.0,-1.0]]</t>
+          <t>[[-61.159274141658855,6.319463860506204,-1860.0,8.0,0.0,0.0,1.0,0.25487951529802855],[6.319463860506204,25.32755907238368,0.0,8.0,0.0,1.0,1.0,0.1484337321654984],[25.32755907238368,30.55478525564999,1678.65,9.0,0.0,0.0,1.0,0.04198794903296828],[30.55478525564999,80.9262375671253,1860.0,9.0,9.0,1.0,-1.0,0.030488266090672775]]</t>
         </is>
       </c>
       <c r="C611" t="n">
@@ -16336,7 +16336,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>[[-60.60112169891692,6.538003763237022,-1860.0,7.0,0.0,0.0,1.0],[6.538003763237022,25.45043347088602,0.0,7.0,0.0,1.0,1.0],[25.45043347088602,29.232919412415818,1678.65,8.0,0.0,0.0,1.0],[29.232919412415818,80.76929036575933,1860.0,8.0,9.0,1.0,-1.0]]</t>
+          <t>[[-60.60112169891692,6.538003763237022,-1860.0,7.0,0.0,0.0,1.0,0.3613252984305586],[6.538003763237022,25.45043347088602,0.0,7.0,0.0,1.0,1.0,0.2548795152980285],[25.45043347088602,29.232919412415818,1678.65,8.0,0.0,0.0,1.0,0.14843373216549838],[29.232919412415818,80.76929036575933,1860.0,8.0,9.0,1.0,-1.0,0.13693404922320285]]</t>
         </is>
       </c>
       <c r="C612" t="n">
@@ -16362,7 +16362,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>[[-61.08785672492348,6.994811828398539,-1860.0,6.0,0.0,0.0,1.0],[6.994811828398539,23.658402033757085,0.0,6.0,0.0,1.0,1.0],[23.658402033757085,29.84773553860454,1678.65,7.0,0.0,0.0,1.0],[29.84773553860454,81.26681388656803,1860.0,7.0,9.0,1.0,-1.0]]</t>
+          <t>[[-61.08785672492348,6.994811828398539,-1860.0,6.0,0.0,0.0,1.0,0.4677710815630887],[6.994811828398539,23.658402033757085,0.0,6.0,0.0,1.0,1.0,0.3613252984305586],[23.658402033757085,29.84773553860454,1678.65,7.0,0.0,0.0,1.0,0.2548795152980285],[29.84773553860454,81.26681388656803,1860.0,7.0,9.0,1.0,-1.0,0.24337983235573296]]</t>
         </is>
       </c>
       <c r="C613" t="n">
@@ -16388,7 +16388,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>[[-58.41958878581747,6.751103476234107,-1860.0,5.0,0.0,0.0,1.0],[6.751103476234107,24.19114788438874,0.0,5.0,0.0,1.0,1.0],[24.19114788438874,29.698530329069158,1678.65,6.0,0.0,0.0,1.0],[29.698530329069158,78.8060237941362,1860.0,6.0,9.0,1.0,-1.0]]</t>
+          <t>[[-58.41958878581747,6.751103476234107,-1860.0,5.0,0.0,0.0,1.0,0.5742168646956188],[6.751103476234107,24.19114788438874,0.0,5.0,0.0,1.0,1.0,0.4677710815630887],[24.19114788438874,29.698530329069158,1678.65,6.0,0.0,0.0,1.0,0.3613252984305586],[29.698530329069158,78.8060237941362,1860.0,6.0,9.0,1.0,-1.0,0.3498256154882631]]</t>
         </is>
       </c>
       <c r="C614" t="n">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>[[-60.981417490623286,6.657233140838315,-1860.0,4.0,0.0,0.0,1.0],[6.657233140838315,23.926675855254032,0.0,4.0,0.0,1.0,1.0],[23.926675855254032,30.162863502126385,1678.65,5.0,0.0,0.0,1.0],[30.162863502126385,82.45089838744067,1860.0,4.0,9.0,1.0,-1.0]]</t>
+          <t>[[-60.981417490623286,6.657233140838315,-1860.0,4.0,0.0,0.0,1.0,0.680662647828149],[6.657233140838315,23.926675855254032,0.0,4.0,0.0,1.0,1.0,0.5742168646956188],[23.926675855254032,30.162863502126385,1678.65,5.0,0.0,0.0,1.0,0.4677710815630887],[30.162863502126385,82.45089838744067,1860.0,4.0,9.0,1.0,-1.0,0.4562713986207932]]</t>
         </is>
       </c>
       <c r="C615" t="n">
@@ -16440,7 +16440,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>[[-55.365048795604366,6.771389241809331,-1860.0,3.0,0.0,0.0,1.0],[6.771389241809331,24.331686948034942,0.0,3.0,0.0,1.0,1.0],[24.331686948034942,29.734855473027437,1678.65,4.0,0.0,0.0,1.0],[29.734855473027437,79.26390028545865,1860.0,4.0,9.0,1.0,-1.0]]</t>
+          <t>[[-55.365048795604366,6.771389241809331,-1860.0,3.0,0.0,0.0,1.0,0.7871084309606791],[6.771389241809331,24.331686948034942,0.0,3.0,0.0,1.0,1.0,0.680662647828149],[24.331686948034942,29.734855473027437,1678.65,4.0,0.0,0.0,1.0,0.5742168646956188],[29.734855473027437,79.26390028545865,1860.0,4.0,9.0,1.0,-1.0,0.5627171817533234]]</t>
         </is>
       </c>
       <c r="C616" t="n">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>[[-43.70322964273586,6.5553034319586345,-1860.0,2.0,0.0,0.0,1.0],[6.5553034319586345,23.697748821776912,0.0,2.0,0.0,1.0,1.0],[23.697748821776912,30.710567390338937,1678.65,3.0,0.0,0.0,1.0],[30.710567390338937,72.78747880171107,1860.0,2.0,9.0,1.0,-1.0]]</t>
+          <t>[[-43.70322964273586,6.5553034319586345,-1860.0,2.0,0.0,0.0,1.0,0.8935542140932091],[6.5553034319586345,23.697748821776912,0.0,2.0,0.0,1.0,1.0,0.7871084309606791],[23.697748821776912,30.710567390338937,1678.65,3.0,0.0,0.0,1.0,0.6806626478281489],[30.710567390338937,72.78747880171107,1860.0,2.0,9.0,1.0,-1.0,0.6691629648858535]]</t>
         </is>
       </c>
       <c r="C617" t="n">
@@ -16492,7 +16492,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>[[-43.595422870099426,6.900930037322219,-1860.0,1.0,0.0,0.0,1.0],[6.900930037322219,19.719235006129253,0.0,1.0,0.0,1.0,1.0],[19.719235006129253,23.99200332906493,0.0,0.0,0.0,1.0,1.0],[23.99200332906493,29.818505587613586,1678.65,1.0,0.0,0.0,1.0],[29.818505587613586,72.54618881697036,1860.0,0.0,9.0,1.0,-1.0]]</t>
+          <t>[[-43.595422870099426,6.900930037322219,-1860.0,1.0,0.0,0.0,1.0,0.9999999972257392],[6.900930037322219,19.719235006129253,0.0,1.0,0.0,1.0,1.0,0.8935542140932091],[19.719235006129253,23.99200332906493,0.0,0.0,0.0,1.0,1.0,0.8935542140932091],[23.99200332906493,29.818505587613586,1678.65,1.0,0.0,0.0,1.0,0.787108430960679],[29.818505587613586,72.54618881697036,1860.0,0.0,9.0,1.0,-1.0,0.7756087480183835]]</t>
         </is>
       </c>
       <c r="C618" t="n">
@@ -16508,7 +16508,7 @@
       </c>
       <c r="F618" s="4" t="inlineStr">
         <is>
-          <t>[0,0,12.8183049688,5.8265022585,0]</t>
+          <t>[0,0,17.0910732917,5.8265022585,0]</t>
         </is>
       </c>
     </row>
@@ -16518,7 +16518,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>[[-24.92658722200752,23.740002761262332,0.0,0.0,0.0,1.0,1.0],[23.740002761262332,30.00993153211305,1678.65,0.0,0.0,0.0,1.0],[30.00993153211305,64.34525575343842,1860.0,0.0,9.0,1.0,-1.0]]</t>
+          <t>[[-24.92658722200752,23.740002761262332,0.0,0.0,0.0,1.0,1.0,0.9999999972257392],[23.740002761262332,30.00993153211305,1678.65,0.0,0.0,0.0,1.0,0.893554214093209],[30.00993153211305,64.34525575343842,1860.0,0.0,9.0,1.0,-1.0,0.8820545311509136]]</t>
         </is>
       </c>
       <c r="C619" t="n">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="F619" s="4" t="inlineStr">
         <is>
-          <t>[0,0,0,0,0]</t>
+          <t>[0,0,0,6.2699287709,0]</t>
         </is>
       </c>
     </row>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>[[-24.20982912354691,31.294223033493104,0.0,0.0,0.0,1.0,1.0],[31.294223033493104,31.584820165205358,890.0,0.0,8.0,2.0,-1.0],[31.584820165205358,62.67871325841625,1860.0,0.0,9.0,1.0,-1.0]]</t>
+          <t>[[-24.20982912354691,31.294223033493104,0.0,0.0,0.0,1.0,1.0,0.9999999972257392],[31.294223033493104,31.584820165205358,890.0,0.0,8.0,2.0,-1.0,0.9435637258243441],[31.584820165205358,62.67871325841625,1860.0,0.0,9.0,1.0,-1.0,0.8820545311509136]]</t>
         </is>
       </c>
       <c r="C620" t="n">
@@ -16570,7 +16570,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>[[-23.30070892631298,29.38981411370122,0.0,0.0,0.0,1.0,1.0],[29.38981411370122,30.806226023379025,890.0,0.0,8.0,1.0,-1.0],[30.806226023379025,61.40072327241952,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[-23.30070892631298,29.38981411370122,0.0,0.0,0.0,1.0,1.0,0.9999999972257392],[29.38981411370122,30.806226023379025,890.0,0.0,8.0,1.0,-1.0,0.9435637258243441],[30.806226023379025,61.40072327241952,1860.0,0.0,8.0,1.0,-1.0,0.8820545311509136]]</t>
         </is>
       </c>
       <c r="C621" t="n">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>[[-38.425278835732435,24.26973360442014,-1860.0,1.0,8.0,1.0,-1.0],[24.26973360442014,28.18817188192967,-1074.7923,0.0,8.0,0.0,-1.0],[28.18817188192967,30.800464066936037,0.0,0.0,7.0,1.0,-1.0],[30.800464066936037,31.235846097770427,890.0,0.0,7.0,1.0,-1.0],[31.235846097770427,91.75394838375104,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[-38.425278835732435,24.26973360442014,-1860.0,1.0,8.0,1.0,-1.0,0.9885003142834436],[24.26973360442014,28.18817188192967,-1074.7923,0.0,8.0,0.0,-1.0,0.9435637290424799],[28.18817188192967,30.800464066936037,0.0,0.0,7.0,1.0,-1.0,0.8820545311509136],[30.800464066936037,31.235846097770427,890.0,0.0,7.0,1.0,-1.0,0.8256182597495185],[31.235846097770427,91.75394838375104,1860.0,0.0,7.0,1.0,-1.0,0.764109065076088]]</t>
         </is>
       </c>
       <c r="C622" t="n">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>[[-43.46712622078352,24.521592024628227,-1860.0,1.0,8.0,0.0,-1.0],[24.521592024628227,26.93253948013929,-1074.7923,0.0,8.0,0.0,-1.0],[26.93253948013929,29.825676426752544,0.0,0.0,7.0,1.0,-1.0],[29.825676426752544,100.70753161877757,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-43.46712622078352,24.521592024628227,-1860.0,1.0,8.0,0.0,-1.0,0.9885003142834436],[24.521592024628227,26.93253948013929,-1074.7923,0.0,8.0,0.0,-1.0,0.9435637290424799],[26.93253948013929,29.825676426752544,0.0,0.0,7.0,1.0,-1.0,0.8820545311509136],[29.825676426752544,100.70753161877757,1860.0,0.0,7.0,0.0,-1.0,0.764109065076088]]</t>
         </is>
       </c>
       <c r="C623" t="n">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>[[-45.61643870141037,24.27829555348719,-1860.0,1.0,7.0,0.0,-1.0],[24.27829555348719,24.784779135044424,-1074.7923,0.0,7.0,1.0,-1.0],[24.784779135044424,27.823680624387798,0.0,0.0,6.0,2.0,-1.0],[27.823680624387798,30.356098532173938,890.0,0.0,6.0,0.0,-1.0],[30.356098532173938,105.82215218420102,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[-45.61643870141037,24.27829555348719,-1860.0,1.0,7.0,0.0,-1.0,0.8705548482086181],[24.27829555348719,24.784779135044424,-1074.7923,0.0,7.0,1.0,-1.0,0.8256182629676543],[24.784779135044424,27.823680624387798,0.0,0.0,6.0,2.0,-1.0,0.764109065076088],[27.823680624387798,30.356098532173938,890.0,0.0,6.0,0.0,-1.0,0.7076727936746929],[30.356098532173938,105.82215218420102,1860.0,0.0,6.0,0.0,-1.0,0.6461635990012624]]</t>
         </is>
       </c>
       <c r="C624" t="n">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>[[-46.49059259185445,24.416184131451544,-1860.0,1.0,6.0,0.0,-1.0],[24.416184131451544,24.93375184476035,-1074.7923,0.0,6.0,1.0,-1.0],[24.93375184476035,27.52159041130436,0.0,0.0,5.0,2.0,-1.0],[27.52159041130436,31.14456440446598,890.0,0.0,5.0,0.0,-1.0],[31.14456440446598,108.26215368747762,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-46.49059259185445,24.416184131451544,-1860.0,1.0,6.0,0.0,-1.0,0.7526093821337925],[24.416184131451544,24.93375184476035,-1074.7923,0.0,6.0,1.0,-1.0,0.7076727968928287],[24.93375184476035,27.52159041130436,0.0,0.0,5.0,2.0,-1.0,0.6461635990012624],[27.52159041130436,31.14456440446598,890.0,0.0,5.0,0.0,-1.0,0.5897273275998673],[31.14456440446598,108.26215368747762,1860.0,0.0,5.0,0.0,-1.0,0.5282181329264368]]</t>
         </is>
       </c>
       <c r="C625" t="n">
@@ -16700,7 +16700,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>[[-47.11834961385731,24.05050208101752,-1860.0,1.0,5.0,0.0,-1.0],[24.05050208101752,24.573802461126895,-1074.7923,0.0,5.0,0.0,-1.0],[24.573802461126895,27.19030436167376,0.0,0.0,4.0,1.0,-1.0],[27.19030436167376,30.33010664233,890.0,0.0,4.0,0.0,-1.0],[30.33010664233,109.34846403884544,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-47.11834961385731,24.05050208101752,-1860.0,1.0,5.0,0.0,-1.0,0.6346639160589669],[24.05050208101752,24.573802461126895,-1074.7923,0.0,5.0,0.0,-1.0,0.5897273308180031],[24.573802461126895,27.19030436167376,0.0,0.0,4.0,1.0,-1.0,0.5282181329264368],[27.19030436167376,30.33010664233,890.0,0.0,4.0,0.0,-1.0,0.47178186152504176],[30.33010664233,109.34846403884544,1860.0,0.0,4.0,0.0,-1.0,0.4102726668516112]]</t>
         </is>
       </c>
       <c r="C626" t="n">
@@ -16726,7 +16726,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>[[-48.82962137476409,24.34453944000353,-1860.0,1.0,4.0,0.0,-1.0],[24.34453944000353,27.054693544254192,0.0,0.0,3.0,2.0,-1.0],[27.054693544254192,31.39094011105523,890.0,0.0,3.0,0.0,-1.0],[31.39094011105523,113.23759405942494,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-48.82962137476409,24.34453944000353,-1860.0,1.0,4.0,0.0,-1.0,0.5167184499841413],[24.34453944000353,27.054693544254192,0.0,0.0,3.0,2.0,-1.0,0.4102726668516112],[27.054693544254192,31.39094011105523,890.0,0.0,3.0,0.0,-1.0,0.3538363954502161],[31.39094011105523,113.23759405942494,1860.0,0.0,3.0,0.0,-1.0,0.29232720077678553]]</t>
         </is>
       </c>
       <c r="C627" t="n">
@@ -16752,7 +16752,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>[[-46.08850076487653,24.663642824034184,-1860.0,1.0,3.0,0.0,-1.0],[24.663642824034184,27.739822980073782,0.0,0.0,2.0,1.0,-1.0],[27.739822980073782,107.20781034443,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-46.08850076487653,24.663642824034184,-1860.0,1.0,3.0,0.0,-1.0,0.4602821785827462],[24.663642824034184,27.739822980073782,0.0,0.0,2.0,1.0,-1.0,0.3538363954502161],[27.739822980073782,107.20781034443,1860.0,0.0,3.0,0.0,-1.0,0.23589092937539047]]</t>
         </is>
       </c>
       <c r="C628" t="n">
@@ -16778,7 +16778,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>[[-45.96773642926471,24.406251769212297,-1860.0,1.0,2.0,0.0,-1.0],[24.406251769212297,27.975946822758225,0.0,0.0,1.0,2.0,-1.0],[27.975946822758225,106.5092380007688,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-45.96773642926471,24.406251769212297,-1860.0,1.0,2.0,0.0,-1.0,0.34233671250792064],[24.406251769212297,27.975946822758225,0.0,0.0,1.0,2.0,-1.0,0.2358909293753905],[27.975946822758225,106.5092380007688,1860.0,0.0,2.0,0.0,-1.0,0.11794546330056487]]</t>
         </is>
       </c>
       <c r="C629" t="n">
@@ -16804,7 +16804,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>[[-44.858589897304945,25.189095929197187,-1860.0,1.0,1.0,0.0,-1.0],[25.189095929197187,25.689436542243634,0.0,0.0,1.0,1.0,-1.0],[25.689436542243634,28.191139607475854,0.0,0.0,0.0,1.0,-1.0],[28.191139607475854,30.692842672708075,1860.0,0.0,0.0,0.0,-1.0],[30.692842672708075,104.74325340358178,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-44.858589897304945,25.189095929197187,-1860.0,1.0,1.0,0.0,-1.0,0.2243912464330949],[25.189095929197187,25.689436542243634,0.0,0.0,1.0,1.0,-1.0,0.1179454633005648],[25.689436542243634,28.191139607475854,0.0,0.0,0.0,1.0,-1.0,0.1179454633005648],[28.191139607475854,30.692842672708075,1860.0,0.0,0.0,0.0,-1.0,-2.774260834947917e-09],[30.692842672708075,104.74325340358178,1860.0,0.0,1.0,0.0,-1.0,-2.774260834947917e-09]]</t>
         </is>
       </c>
       <c r="C630" t="n">
@@ -16820,7 +16820,7 @@
       </c>
       <c r="F630" s="4" t="inlineStr">
         <is>
-          <t>[0,0,0.500340613,0,0]</t>
+          <t>[0,0,3.0020436783,0,0]</t>
         </is>
       </c>
     </row>
@@ -16830,7 +16830,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>[[-43.781580489130874,25.47982190182354,-1860.0,1.0,0.0,0.0,-1.0],[25.47982190182354,103.09188982927598,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-43.781580489130874,25.47982190182354,-1860.0,1.0,0.0,0.0,-1.0,0.10644578035826932],[25.47982190182354,103.09188982927598,0.0,0.0,0.0,1.0,-1.0,-2.774260793314554e-09]]</t>
         </is>
       </c>
       <c r="C631" t="n">
@@ -16856,7 +16856,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>[[-47.79826232885244,12.025942142748931,-1860.0,9.0,0.0,0.0,1.0],[12.025942142748931,15.731866313556097,-733.6842,9.0,0.0,0.0,1.0],[15.731866313556097,110.49764153848216,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-47.79826232885244,12.025942142748931,-1860.0,9.0,0.0,0.0,1.0,0.10644578035826932],[12.025942142748931,15.731866313556097,-733.6842,9.0,0.0,0.0,1.0,0.04198794843055848],[15.731866313556097,110.49764153848216,0.0,0.0,0.0,1.0,-1.0,-2.774260793314554e-09]]</t>
         </is>
       </c>
       <c r="C632" t="n">
@@ -16882,7 +16882,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>[[-44.810813810846334,16.148770254390065,-1860.0,9.0,0.0,0.0,1.0],[16.148770254390065,21.145457472852065,-733.6842,9.0,0.0,0.0,1.0],[21.145457472852065,104.59013402116747,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-44.810813810846334,16.148770254390065,-1860.0,9.0,0.0,0.0,1.0,0.10644578035826932],[16.148770254390065,21.145457472852065,-733.6842,9.0,0.0,0.0,1.0,0.04198794843055848],[21.145457472852065,104.59013402116747,0.0,0.0,0.0,1.0,-1.0,-2.774260793314554e-09]]</t>
         </is>
       </c>
       <c r="C633" t="n">
@@ -16908,7 +16908,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>[[-44.02322992219492,15.615612893223712,-1860.0,7.0,0.0,0.0,1.0],[15.615612893223712,22.02309187339265,-733.6843,8.0,0.0,0.0,1.0],[22.02309187339265,24.48750686576532,0.0,7.0,0.0,1.0,1.0],[24.48750686576532,33.35940083830695,1016.5,9.0,0.0,0.0,1.0],[33.35940083830695,103.34878662169078,1678.6501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-44.02322992219492,15.615612893223712,-1860.0,7.0,0.0,0.0,1.0,0.2128915634907994],[15.615612893223712,22.02309187339265,-733.6843,8.0,0.0,0.0,1.0,0.14843373728598014],[22.02309187339265,24.48750686576532,0.0,7.0,0.0,1.0,1.0,0.1064457803582693],[24.48750686576532,33.35940083830695,1016.5,9.0,0.0,0.0,1.0,0.0419879490329681],[33.35940083830695,103.34878662169078,1678.6501,0.0,0.0,0.0,-1.0,-9.11541490900003e-09]]</t>
         </is>
       </c>
       <c r="C634" t="n">
@@ -16934,7 +16934,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>[[-47.07798238373145,16.13849942163636,-1860.0,6.0,0.0,0.0,1.0],[16.13849942163636,22.407902575887718,-733.6843,6.0,0.0,0.0,1.0],[22.407902575887718,25.020153890159108,0.0,6.0,0.0,1.0,1.0],[25.020153890159108,34.42425862153614,1016.5,7.0,0.0,0.0,1.0],[34.42425862153614,109.13464620969808,1860.0,7.0,1.0,0.0,1.0]]</t>
+          <t>[[-47.07798238373145,16.13849942163636,-1860.0,6.0,0.0,0.0,1.0,0.3193373466233295],[16.13849942163636,22.407902575887718,-733.6843,6.0,0.0,0.0,1.0,0.25487952041851025],[22.407902575887718,25.020153890159108,0.0,6.0,0.0,1.0,1.0,0.2128915634907994],[25.020153890159108,34.42425862153614,1016.5,7.0,0.0,0.0,1.0,0.1484337321654982],[34.42425862153614,109.13464620969808,1860.0,7.0,1.0,0.0,1.0,0.09494609741597378]]</t>
         </is>
       </c>
       <c r="C635" t="n">
@@ -16960,7 +16960,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>[[-45.935251723209284,15.421408237700312,-1860.0,5.0,0.0,0.0,1.0],[15.421408237700312,21.045768734117026,-733.6843,5.0,0.0,0.0,1.0],[21.045768734117026,23.602296232488264,0.0,5.0,0.0,1.0,1.0],[23.602296232488264,33.82840622597319,1016.5,6.0,0.0,0.0,1.0],[33.82840622597319,106.94509267939047,1860.0,6.0,1.0,0.0,1.0]]</t>
+          <t>[[-45.935251723209284,15.421408237700312,-1860.0,5.0,0.0,0.0,1.0,0.4257831297558597],[15.421408237700312,21.045768734117026,-733.6843,5.0,0.0,0.0,1.0,0.3613253035510404],[21.045768734117026,23.602296232488264,0.0,5.0,0.0,1.0,1.0,0.3193373466233296],[23.602296232488264,33.82840622597319,1016.5,6.0,0.0,0.0,1.0,0.2548795152980284],[33.82840622597319,106.94509267939047,1860.0,6.0,1.0,0.0,1.0,0.20139188054850393]]</t>
         </is>
       </c>
       <c r="C636" t="n">
@@ -16986,7 +16986,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>[[-46.83786553926141,15.145067380842335,-1860.0,4.0,0.0,0.0,1.0],[15.145067380842335,21.91631215362677,-733.6843,4.0,0.0,0.0,1.0],[21.91631215362677,24.520637066236183,0.0,4.0,0.0,1.0,1.0],[24.520637066236183,32.33361180406438,1016.5,4.0,0.0,0.0,1.0],[32.33361180406438,108.90076423478078,1860.0,6.0,1.0,0.0,1.0]]</t>
+          <t>[[-46.83786553926141,15.145067380842335,-1860.0,4.0,0.0,0.0,1.0,0.5322289128883898],[15.145067380842335,21.91631215362677,-733.6843,4.0,0.0,0.0,1.0,0.46777108668357054],[21.91631215362677,24.520637066236183,0.0,4.0,0.0,1.0,1.0,0.4257831297558597],[24.520637066236183,32.33361180406438,1016.5,4.0,0.0,0.0,1.0,0.3613252984305585],[32.33361180406438,108.90076423478078,1860.0,6.0,1.0,0.0,1.0,0.30783766368103405]]</t>
         </is>
       </c>
       <c r="C637" t="n">
@@ -17012,7 +17012,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>[[-45.61710698118845,15.89395785311224,-1860.0,3.0,0.0,0.0,1.0],[15.89395785311224,21.48587283804867,-733.6843,3.0,0.0,0.0,1.0],[21.48587283804867,23.519296468934634,0.0,3.0,0.0,1.0,1.0],[23.519296468934634,33.17805871564301,1016.5,4.0,0.0,0.0,1.0],[33.17805871564301,106.38130942753807,1860.0,4.0,1.0,0.0,1.0]]</t>
+          <t>[[-45.61710698118845,15.89395785311224,-1860.0,3.0,0.0,0.0,1.0,0.63867469602092],[15.89395785311224,21.48587283804867,-733.6843,3.0,0.0,0.0,1.0,0.5742168698161007],[21.48587283804867,23.519296468934634,0.0,3.0,0.0,1.0,1.0,0.5322289128883898],[23.519296468934634,33.17805871564301,1016.5,4.0,0.0,0.0,1.0,0.4677710815630886],[33.17805871564301,106.38130942753807,1860.0,4.0,1.0,0.0,1.0,0.41428344681356416]]</t>
         </is>
       </c>
       <c r="C638" t="n">
@@ -17038,7 +17038,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>[[-44.076507629046716,16.0735990601732,-1860.0,3.0,0.0,0.0,1.0],[16.0735990601732,21.496969335430734,-733.6843,2.0,0.0,0.0,1.0],[21.496969335430734,23.962137642365974,0.0,2.0,0.0,1.0,1.0],[23.962137642365974,32.83674354733286,1016.5,3.0,0.0,0.0,1.0],[32.83674354733286,103.3405571256808,1860.0,3.0,1.0,0.0,1.0]]</t>
+          <t>[[-44.076507629046716,16.0735990601732,-1860.0,3.0,0.0,0.0,1.0,0.74512047915345],[16.0735990601732,21.496969335430734,-733.6843,2.0,0.0,0.0,1.0,0.6806626529486308],[21.496969335430734,23.962137642365974,0.0,2.0,0.0,1.0,1.0,0.63867469602092],[23.962137642365974,32.83674354733286,1016.5,3.0,0.0,0.0,1.0,0.5742168646956187],[32.83674354733286,103.3405571256808,1860.0,3.0,1.0,0.0,1.0,0.5207292299460944]]</t>
         </is>
       </c>
       <c r="C639" t="n">
@@ -17064,7 +17064,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>[[-46.39088533017101,15.66397552707712,-1860.0,1.0,0.0,0.0,1.0],[15.66397552707712,20.835213931847797,-733.6843,2.0,0.0,0.0,1.0],[20.835213931847797,22.90370929375606,0.0,2.0,0.0,1.0,1.0],[22.90370929375606,34.79755762472862,1016.5,2.0,0.0,0.0,1.0],[34.79755762472862,108.22914297247223,1860.0,3.0,1.0,0.0,1.0]]</t>
+          <t>[[-46.39088533017101,15.66397552707712,-1860.0,1.0,0.0,0.0,1.0,0.8515662622859801],[15.66397552707712,20.835213931847797,-733.6843,2.0,0.0,0.0,1.0,0.7871084360811609],[20.835213931847797,22.90370929375606,0.0,2.0,0.0,1.0,1.0,0.74512047915345],[22.90370929375606,34.79755762472862,1016.5,2.0,0.0,0.0,1.0,0.6806626478281488],[34.79755762472862,108.22914297247223,1860.0,3.0,1.0,0.0,1.0,0.6271750130786244]]</t>
         </is>
       </c>
       <c r="C640" t="n">
@@ -17090,7 +17090,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>[[-31.348909435901195,16.11593040905449,-1860.0,1.0,0.0,0.0,1.0],[16.11593040905449,21.38980150293845,-733.6843,1.0,0.0,0.0,1.0],[21.38980150293845,24.026737049880435,0.0,1.0,0.0,1.0,1.0],[24.026737049880435,33.25601146417738,1016.5,2.0,0.0,0.0,1.0],[33.25601146417738,100.05837865337426,1860.0,2.0,1.0,0.0,1.0]]</t>
+          <t>[[-31.348909435901195,16.11593040905449,-1860.0,1.0,0.0,0.0,1.0,0.9580120454185101],[16.11593040905449,21.38980150293845,-733.6843,1.0,0.0,0.0,1.0,0.8935542192136909],[21.38980150293845,24.026737049880435,0.0,1.0,0.0,1.0,1.0,0.8515662622859801],[24.026737049880435,33.25601146417738,1016.5,2.0,0.0,0.0,1.0,0.7871084309606788],[33.25601146417738,100.05837865337426,1860.0,2.0,1.0,0.0,1.0,0.7336207962111545]]</t>
         </is>
       </c>
       <c r="C641" t="n">
@@ -17116,7 +17116,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>[[-27.87964338101098,19.586101598882927,-733.6844,0.0,0.0,0.0,1.0],[19.586101598882927,21.705108071199618,-733.6843,0.0,0.0,0.0,1.0],[21.705108071199618,24.247915837979647,0.0,0.0,0.0,1.0,1.0],[24.247915837979647,29.757332666003045,1016.5,0.0,0.0,0.0,1.0],[29.757332666003045,33.14774302170975,1016.5,1.0,0.0,0.0,1.0],[33.14774302170975,98.83694366352721,1860.0,1.0,1.0,0.0,1.0]]</t>
+          <t>[[-27.87964338101098,19.586101598882927,-733.6844,0.0,0.0,0.0,1.0,1.0000000080691125],[19.586101598882927,21.705108071199618,-733.6843,0.0,0.0,0.0,1.0,1.000000002346221],[21.705108071199618,24.247915837979647,0.0,0.0,0.0,1.0,1.0,0.9580120454185101],[24.247915837979647,29.757332666003045,1016.5,0.0,0.0,0.0,1.0,0.8935542140932089],[29.757332666003045,33.14774302170975,1016.5,1.0,0.0,0.0,1.0,0.8935542140932089],[33.14774302170975,98.83694366352721,1860.0,1.0,1.0,0.0,1.0,0.8400665793436846]]</t>
         </is>
       </c>
       <c r="C642" t="n">
@@ -17132,7 +17132,7 @@
       </c>
       <c r="F642" s="4" t="inlineStr">
         <is>
-          <t>[0,0,0,3.3904103557,0]</t>
+          <t>[0,0,2.5428077668,8.8998271837,0]</t>
         </is>
       </c>
     </row>
@@ -17142,7 +17142,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>[[-24.260474306777862,34.33672810498781,0.0,0.0,0.0,1.0,1.0],[34.33672810498781,39.91741404896548,1678.65,1.0,0.0,0.0,1.0],[39.91741404896548,94.92703263960264,1860.0,1.0,9.0,1.0,-1.0]]</t>
+          <t>[[-24.260474306777862,34.33672810498781,0.0,0.0,0.0,1.0,1.0,1.000000008069112],[34.33672810498781,39.91741404896548,1678.65,1.0,0.0,0.0,1.0,0.8935542249365819],[39.91741404896548,94.92703263960264,1860.0,1.0,9.0,1.0,-1.0,0.8820545419942865]]</t>
         </is>
       </c>
       <c r="C643" t="n">
@@ -17168,7 +17168,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>[[-25.531644736369287,39.82047842760424,0.0,0.0,0.0,1.0,1.0],[39.82047842760424,40.23149807014495,890.0,0.0,8.0,2.0,-1.0],[40.23149807014495,97.36322838330419,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-25.531644736369287,39.82047842760424,0.0,0.0,0.0,1.0,1.0,1.000000008069112],[39.82047842760424,40.23149807014495,890.0,0.0,8.0,2.0,-1.0,0.943563736667717],[40.23149807014495,97.36322838330419,1860.0,0.0,8.0,2.0,-1.0,0.8820545419942865]]</t>
         </is>
       </c>
       <c r="C644" t="n">
@@ -17194,7 +17194,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>[[-25.25798785161762,39.56863507474504,0.0,0.0,0.0,1.0,1.0],[39.56863507474504,39.976349684344804,890.0,0.0,8.0,1.0,-1.0],[39.976349684344804,96.64868041871216,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[-25.25798785161762,39.56863507474504,0.0,0.0,0.0,1.0,1.0,1.000000008069112],[39.56863507474504,39.976349684344804,890.0,0.0,8.0,1.0,-1.0,0.943563736667717],[39.976349684344804,96.64868041871216,1860.0,0.0,8.0,1.0,-1.0,0.8820545419942865]]</t>
         </is>
       </c>
       <c r="C645" t="n">
@@ -17220,7 +17220,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>[[-26.795740186926828,34.865565589567716,-1860.0,1.0,8.0,0.0,-1.0],[34.865565589567716,35.70449491986016,-1074.7921,0.0,8.0,0.0,-1.0],[35.70449491986016,39.479676906176145,0.0,0.0,7.0,1.0,-1.0],[39.479676906176145,40.31860623646859,890.0001,0.0,7.0,1.0,-1.0],[40.31860623646859,98.62419469179338,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[-26.795740186926828,34.865565589567716,-1860.0,1.0,8.0,0.0,-1.0,0.988500325126817],[34.865565589567716,35.70449491986016,-1074.7921,0.0,8.0,0.0,-1.0,0.94356372844007],[35.70449491986016,39.479676906176145,0.0,0.0,7.0,1.0,-1.0,0.8820545419942869],[39.479676906176145,40.31860623646859,890.0001,0.0,7.0,1.0,-1.0,0.8256182642517378],[40.31860623646859,98.62419469179338,1860.0,0.0,7.0,1.0,-1.0,0.7641090759194613]]</t>
         </is>
       </c>
       <c r="C646" t="n">
@@ -17246,7 +17246,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>[[-22.913115009354108,33.32223336738307,-1860.0,1.0,7.0,0.0,-1.0],[33.32223336738307,34.87355332260341,-1074.7921,0.0,7.0,0.0,-1.0],[34.87355332260341,38.751853210654254,0.0,0.0,6.0,1.0,-1.0],[38.751853210654254,93.04805164336602,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[-22.913115009354108,33.32223336738307,-1860.0,1.0,7.0,0.0,-1.0,0.8705548590519914],[33.32223336738307,34.87355332260341,-1074.7921,0.0,7.0,0.0,-1.0,0.8256182623652444],[34.87355332260341,38.751853210654254,0.0,0.0,6.0,1.0,-1.0,0.7641090759194613],[38.751853210654254,93.04805164336602,1860.0,0.0,6.0,1.0,-1.0,0.6461636098446357]]</t>
         </is>
       </c>
       <c r="C647" t="n">
@@ -17272,7 +17272,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>[[-26.042025271166146,34.905421245205375,-1860.0,1.0,6.0,0.0,-1.0],[34.905421245205375,35.31722831626194,-1074.7921,0.0,6.0,0.0,-1.0],[35.31722831626194,39.435299026827586,0.0,0.0,5.0,1.0,-1.0],[39.435299026827586,97.08828897474659,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[-26.042025271166146,34.905421245205375,-1860.0,1.0,6.0,0.0,-1.0,0.7526093929771658],[34.905421245205375,35.31722831626194,-1074.7921,0.0,6.0,0.0,-1.0,0.7076727962904188],[35.31722831626194,39.435299026827586,0.0,0.0,5.0,1.0,-1.0,0.6461636098446357],[39.435299026827586,97.08828897474659,1860.0,0.0,5.0,1.0,-1.0,0.5282181437698101]]</t>
         </is>
       </c>
       <c r="C648" t="n">
@@ -17298,7 +17298,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>[[-24.936045976362898,32.89972778427733,-1860.0,1.0,5.0,0.0,-1.0],[32.89972778427733,35.30955169097068,-1074.7921,0.0,5.0,0.0,-1.0],[35.30955169097068,38.92428755101069,0.0,0.0,4.0,1.0,-1.0],[38.92428755101069,39.727562186575135,890.0001,0.0,4.0,0.0,-1.0],[39.727562186575135,95.15351204052203,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-24.936045976362898,32.89972778427733,-1860.0,1.0,5.0,0.0,-1.0,0.6346639269023402],[32.89972778427733,35.30955169097068,-1074.7921,0.0,5.0,0.0,-1.0,0.5897273302155932],[35.30955169097068,38.92428755101069,0.0,0.0,4.0,1.0,-1.0,0.5282181437698101],[38.92428755101069,39.727562186575135,890.0001,0.0,4.0,0.0,-1.0,0.47178186602726097],[39.727562186575135,95.15351204052203,1860.0,0.0,4.0,0.0,-1.0,0.4102726776949845]]</t>
         </is>
       </c>
       <c r="C649" t="n">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>[[-20.534790345201245,34.140145642212254,-1860.0,1.0,4.0,0.0,-1.0],[34.140145642212254,35.569555733386466,-1074.7921,0.0,4.0,0.0,-1.0],[35.569555733386466,39.50043348411554,0.0,0.0,3.0,1.0,-1.0],[39.50043348411554,86.31361397007089,1860.0,0.0,3.0,1.0,-1.0]]</t>
+          <t>[[-20.534790345201245,34.140145642212254,-1860.0,1.0,4.0,0.0,-1.0,0.5167184608275146],[34.140145642212254,35.569555733386466,-1074.7921,0.0,4.0,0.0,-1.0,0.4717818641407676],[35.569555733386466,39.50043348411554,0.0,0.0,3.0,1.0,-1.0,0.4102726776949845],[39.50043348411554,86.31361397007089,1860.0,0.0,3.0,1.0,-1.0,0.29232721162015884]]</t>
         </is>
       </c>
       <c r="C650" t="n">
@@ -17350,7 +17350,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>[[-18.143955755197105,33.38086613364957,-1860.0,1.0,3.0,0.0,-1.0],[33.38086613364957,35.36259005245136,-1074.7921,0.0,3.0,0.0,-1.0],[35.36259005245136,39.326037890054955,0.0,0.0,2.0,1.0,-1.0],[39.326037890054955,39.98661252965555,890.0001,0.0,2.0,1.0,-1.0],[39.98661252965555,80.61195286509235,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[-18.143955755197105,33.38086613364957,-1860.0,1.0,3.0,0.0,-1.0,0.3987729947526889],[33.38086613364957,35.36259005245136,-1074.7921,0.0,3.0,0.0,-1.0,0.3538363980659419],[35.36259005245136,39.326037890054955,0.0,0.0,2.0,1.0,-1.0,0.2923272116201588],[39.326037890054955,39.98661252965555,890.0001,0.0,2.0,1.0,-1.0,0.23589093387760965],[39.98661252965555,80.61195286509235,1860.0,0.0,2.0,1.0,-1.0,0.17438174554533314]]</t>
         </is>
       </c>
       <c r="C651" t="n">
@@ -17376,7 +17376,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>[[-17.428000799813802,34.50495605573933,-1860.0,1.0,2.0,0.0,-1.0],[34.50495605573933,39.8314131691294,0.0,0.0,2.0,1.0,-1.0],[39.8314131691294,82.11016650666303,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[-17.428000799813802,34.50495605573933,-1860.0,1.0,2.0,0.0,-1.0,0.3423367170101398],[34.50495605573933,39.8314131691294,0.0,0.0,2.0,1.0,-1.0,0.2358909338776097],[39.8314131691294,82.11016650666303,1860.0,0.0,2.0,1.0,-1.0,0.11794546780278407]]</t>
         </is>
       </c>
       <c r="C652" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>[[-15.951514392902089,30.99468029643696,-1860.0,1.0,2.0,0.0,-1.0],[30.99468029643696,36.74319393186623,0.0,0.0,2.0,1.0,-1.0],[36.74319393186623,79.53768432895082,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-15.951514392902089,30.99468029643696,-1860.0,1.0,2.0,0.0,-1.0,0.3423367170101398],[30.99468029643696,36.74319393186623,0.0,0.0,2.0,1.0,-1.0,0.2358909338776097],[36.74319393186623,79.53768432895082,1860.0,0.0,2.0,0.0,-1.0,0.11794546780278407]]</t>
         </is>
       </c>
       <c r="C653" t="n">
@@ -17428,7 +17428,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>[[-17.20785096525953,30.558256144596477,-1860.0,1.0,1.0,0.0,-1.0],[30.558256144596477,37.05704622757008,0.0,0.0,1.0,1.0,-1.0],[37.05704622757008,79.9490607751959,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-17.20785096525953,30.558256144596477,-1860.0,1.0,1.0,0.0,-1.0,0.2243912509353142],[30.558256144596477,37.05704622757008,0.0,0.0,1.0,1.0,-1.0,0.1179454678027841],[37.05704622757008,79.9490607751959,1860.0,0.0,1.0,0.0,-1.0,1.7279584707541318e-09]]</t>
         </is>
       </c>
       <c r="C654" t="n">
@@ -17454,7 +17454,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>[[-14.822341019644306,29.38434550872062,-1860.0,1.0,0.0,0.0,-1.0],[29.38434550872062,76.96793170244675,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-14.822341019644306,29.38434550872062,-1860.0,1.0,0.0,0.0,-1.0,0.10644578486048856],[29.38434550872062,76.96793170244675,0.0,0.0,0.0,1.0,-1.0,1.727958442998556e-09]]</t>
         </is>
       </c>
       <c r="C655" t="n">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>[[-14.979587138758449,23.090559252505194,-1860.0,8.0,0.0,1.0,1.0],[23.090559252505194,23.69484729046176,-733.6842,9.0,0.0,1.0,1.0],[23.69484729046176,75.36147453574813,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-14.979587138758449,23.090559252505194,-1860.0,8.0,0.0,1.0,1.0,0.10644578486048856],[23.090559252505194,23.69484729046176,-733.6842,9.0,0.0,1.0,1.0,0.04198795293277772],[23.69484729046176,75.36147453574813,0.0,0.0,0.0,1.0,-1.0,1.727958442998556e-09]]</t>
         </is>
       </c>
       <c r="C656" t="n">
@@ -17506,7 +17506,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>[[-19.273007882388143,23.451746046050722,-1860.0,9.0,0.0,0.0,1.0],[23.451746046050722,25.486258137881144,-733.6842,9.0,0.0,0.0,1.0],[25.486258137881144,82.11351136049456,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-19.273007882388143,23.451746046050722,-1860.0,9.0,0.0,0.0,1.0,0.10644578486048856],[23.451746046050722,25.486258137881144,-733.6842,9.0,0.0,0.0,1.0,0.04198795293277772],[25.486258137881144,82.11351136049456,0.0,0.0,0.0,1.0,-1.0,1.727958442998556e-09]]</t>
         </is>
       </c>
       <c r="C657" t="n">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>[[-14.920825882559948,24.267784604729172,-1860.0,7.0,0.0,0.0,1.0],[24.267784604729172,28.24787785734447,-733.6842,8.0,0.0,0.0,1.0],[28.24787785734447,31.309488051663934,0.0,7.0,0.0,1.0,1.0],[31.309488051663934,34.98342028484729,1016.5,9.0,0.0,0.0,1.0],[34.98342028484729,76.62131892759197,1678.6501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-14.920825882559948,24.267784604729172,-1860.0,7.0,0.0,0.0,1.0,0.21289156799301873],[24.267784604729172,28.24787785734447,-733.6842,8.0,0.0,0.0,1.0,0.14843373606530788],[28.24787785734447,31.309488051663934,0.0,7.0,0.0,1.0,1.0,0.1064457848604886],[31.309488051663934,34.98342028484729,1016.5,9.0,0.0,0.0,1.0,0.04198795353518739],[34.98342028484729,76.62131892759197,1678.6501,0.0,0.0,0.0,-1.0,-4.613195617175769e-09]]</t>
         </is>
       </c>
       <c r="C658" t="n">
@@ -17558,7 +17558,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>[[-14.470272758630614,23.4403634906472,-1860.0,6.0,0.0,0.0,1.0],[23.4403634906472,29.202780200537433,-733.6842,6.0,0.0,0.0,1.0],[29.202780200537433,32.538916190473884,0.0,6.0,0.0,1.0,1.0],[32.538916190473884,34.66191182043344,1016.5,8.0,0.0,0.0,1.0],[34.66191182043344,35.26848200042188,1725.15,8.0,9.0,2.0,-1.0],[35.26848200042188,76.21196914964193,1860.0,9.0,9.0,2.0,-1.0]]</t>
+          <t>[[-14.470272758630614,23.4403634906472,-1860.0,6.0,0.0,0.0,1.0,0.31933735112554884],[23.4403634906472,29.202780200537433,-733.6842,6.0,0.0,0.0,1.0,0.25487951919783797],[29.202780200537433,32.538916190473884,0.0,6.0,0.0,1.0,1.0,0.2128915679930187],[32.538916190473884,34.66191182043344,1016.5,8.0,0.0,0.0,1.0,0.14843373666771748],[34.66191182043344,35.26848200042188,1725.15,8.0,9.0,2.0,-1.0,0.10349714820861794],[35.26848200042188,76.21196914964193,1860.0,9.0,9.0,2.0,-1.0,0.09494610191819307]]</t>
         </is>
       </c>
       <c r="C659" t="n">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>[[-17.156468120339788,23.364018233220165,-1860.0,6.0,0.0,0.0,1.0],[23.364018233220165,28.91924620104693,-733.6842,5.0,0.0,0.0,1.0],[28.91924620104693,32.18702735859209,0.0,5.0,0.0,1.0,1.0],[32.18702735859209,34.474474168873705,1016.5,7.0,0.0,0.0,1.0],[34.474474168873705,34.80125228462822,1725.15,8.0,9.0,2.0,-1.0],[34.80125228462822,80.55018849026044,1860.0,8.0,9.0,2.0,-1.0]]</t>
+          <t>[[-17.156468120339788,23.364018233220165,-1860.0,6.0,0.0,0.0,1.0,0.4257831342580789],[23.364018233220165,28.91924620104693,-733.6842,5.0,0.0,0.0,1.0,0.3613253023303681],[28.91924620104693,32.18702735859209,0.0,5.0,0.0,1.0,1.0,0.3193373511255488],[32.18702735859209,34.474474168873705,1016.5,7.0,0.0,0.0,1.0,0.2548795198002476],[34.474474168873705,34.80125228462822,1725.15,8.0,9.0,2.0,-1.0,0.20994293134114803],[34.80125228462822,80.55018849026044,1860.0,8.0,9.0,2.0,-1.0,0.20139188505072314]]</t>
         </is>
       </c>
       <c r="C660" t="n">
@@ -17610,7 +17610,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>[[-18.72906095877353,22.803512456543366,-1860.0,5.0,0.0,0.0,1.0],[22.803512456543366,28.6386673991912,-733.6842,4.0,0.0,0.0,1.0],[28.6386673991912,31.727867074710637,0.0,5.0,0.0,1.0,1.0],[31.727867074710637,34.130577933447974,1016.5,4.0,0.0,0.0,1.0],[34.130577933447974,34.817066750230076,1725.15,7.0,9.0,2.0,-1.0],[34.817066750230076,83.90101715015004,1860.0,6.0,9.0,2.0,-1.0]]</t>
+          <t>[[-18.72906095877353,22.803512456543366,-1860.0,5.0,0.0,0.0,1.0,0.532228917390609],[22.803512456543366,28.6386673991912,-733.6842,4.0,0.0,0.0,1.0,0.4677710854628982],[28.6386673991912,31.727867074710637,0.0,5.0,0.0,1.0,1.0,0.4257831342580789],[31.727867074710637,34.130577933447974,1016.5,4.0,0.0,0.0,1.0,0.3613253029327777],[34.130577933447974,34.817066750230076,1725.15,7.0,9.0,2.0,-1.0,0.3163887144736781],[34.817066750230076,83.90101715015004,1860.0,6.0,9.0,2.0,-1.0,0.30783766818325325]]</t>
         </is>
       </c>
       <c r="C661" t="n">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>[[-18.775124489763733,18.834267251161123,-1860.0,3.0,0.0,0.0,1.0],[18.834267251161123,28.407566967032906,-733.6842,4.0,0.0,0.0,1.0],[28.407566967032906,31.484699018563127,0.0,3.0,0.0,1.0,1.0],[31.484699018563127,34.219927508812205,1016.5,4.0,0.0,0.0,1.0],[34.219927508812205,34.56183107009334,1725.15,5.0,9.0,2.0,-1.0],[34.56183107009334,83.45404033329565,1860.0,5.0,9.0,2.0,-1.0]]</t>
+          <t>[[-18.775124489763733,18.834267251161123,-1860.0,3.0,0.0,0.0,1.0,0.638674700523139],[18.834267251161123,28.407566967032906,-733.6842,4.0,0.0,0.0,1.0,0.5742168685954282],[28.407566967032906,31.484699018563127,0.0,3.0,0.0,1.0,1.0,0.532228917390609],[31.484699018563127,34.219927508812205,1016.5,4.0,0.0,0.0,1.0,0.46777108606530776],[34.219927508812205,34.56183107009334,1725.15,5.0,9.0,2.0,-1.0,0.42283449760620817],[34.56183107009334,83.45404033329565,1860.0,5.0,9.0,2.0,-1.0,0.4142834513157833]]</t>
         </is>
       </c>
       <c r="C662" t="n">
@@ -17662,7 +17662,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>[[-15.237972275380889,27.992036157586455,-1860.0,3.0,0.0,0.0,1.0],[27.992036157586455,35.043739660836444,0.0,3.0,0.0,1.0,1.0],[35.043739660836444,76.43417326686901,1860.0,4.0,9.0,2.0,-1.0]]</t>
+          <t>[[-15.237972275380889,27.992036157586455,-1860.0,3.0,0.0,0.0,1.0,0.6806626517279584],[27.992036157586455,35.043739660836444,0.0,3.0,0.0,1.0,1.0,0.5742168685954282],[35.043739660836444,76.43417326686901,1860.0,4.0,9.0,2.0,-1.0,0.45627140252060255]]</t>
         </is>
       </c>
       <c r="C663" t="n">
@@ -17688,7 +17688,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>[[-14.095513124237838,28.003582025490793,-1860.0,1.0,0.0,0.0,1.0],[28.003582025490793,34.61915412044815,0.0,2.0,0.0,1.0,1.0],[34.61915412044815,35.220569765444274,890.0,2.0,8.0,4.0,-1.0],[35.220569765444274,75.81612580268259,1860.0,2.0,8.0,4.0,-1.0]]</t>
+          <t>[[-14.095513124237838,28.003582025490793,-1860.0,1.0,0.0,0.0,1.0,0.7871084348604884],[28.003582025490793,34.61915412044815,0.0,2.0,0.0,1.0,1.0,0.6806626517279584],[34.61915412044815,35.220569765444274,890.0,2.0,8.0,4.0,-1.0,0.6242263803265633],[35.220569765444274,75.81612580268259,1860.0,2.0,8.0,4.0,-1.0,0.5627171856531328]]</t>
         </is>
       </c>
       <c r="C664" t="n">
@@ -17714,7 +17714,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>[[-30.74893406160225,27.824404386088254,-1860.0,1.0,0.0,0.0,1.0],[27.824404386088254,32.035559437883,0.0,1.0,0.0,1.0,1.0],[32.035559437883,32.80122399275477,0.0,0.0,0.0,1.0,1.0],[32.80122399275477,35.863882212241855,0.0,2.0,0.0,1.0,1.0],[35.863882212241855,36.246714489677736,890.0,1.0,8.0,0.0,-1.0],[36.246714489677736,83.71791689172755,1860.0,1.0,8.0,0.0,-1.0]]</t>
+          <t>[[-30.74893406160225,27.824404386088254,-1860.0,1.0,0.0,0.0,1.0,0.8935542179930185],[27.824404386088254,32.035559437883,0.0,1.0,0.0,1.0,1.0,0.7871084348604884],[32.035559437883,32.80122399275477,0.0,0.0,0.0,1.0,1.0,0.7871084348604884],[32.80122399275477,35.863882212241855,0.0,2.0,0.0,1.0,1.0,0.7871084348604884],[35.863882212241855,36.246714489677736,890.0,1.0,8.0,0.0,-1.0,0.7306721634590934],[36.246714489677736,83.71791689172755,1860.0,1.0,8.0,0.0,-1.0,0.6691629687856628]]</t>
         </is>
       </c>
       <c r="C665" t="n">
@@ -17730,7 +17730,7 @@
       </c>
       <c r="F665" s="4" t="inlineStr">
         <is>
-          <t>[0,0,7.2738132713,0,0.3828322774]</t>
+          <t>[0,0,8.0394778262,0,0.3828322774]</t>
         </is>
       </c>
     </row>
@@ -17740,7 +17740,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>[[-31.354974386492554,-0.29324361899402973,-1860.0,1.0,0.0,0.0,1.0],[-0.29324361899402973,28.050585706348375,-1860.0,0.0,0.0,0.0,1.0],[28.050585706348375,35.03947512903554,0.0,0.0,0.0,1.0,1.0],[35.03947512903554,84.73824435703317,1860.0,2.0,9.0,2.0,-1.0]]</t>
+          <t>[[-31.354974386492554,-0.29324361899402973,-1860.0,1.0,0.0,0.0,1.0,1.0000000011255485],[-0.29324361899402973,28.050585706348375,-1860.0,0.0,0.0,0.0,1.0,1.0000000011255485],[28.050585706348375,35.03947512903554,0.0,0.0,0.0,1.0,1.0,0.8935542179930185],[35.03947512903554,84.73824435703317,1860.0,2.0,9.0,2.0,-1.0,0.7756087519181929]]</t>
         </is>
       </c>
       <c r="C666" t="n">
@@ -17756,7 +17756,7 @@
       </c>
       <c r="F666" s="4" t="inlineStr">
         <is>
-          <t>[0,0,0,0,0]</t>
+          <t>[0,0,6.9888894227,0,0]</t>
         </is>
       </c>
     </row>
@@ -17766,7 +17766,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>[[-31.828332235715447,35.09535051955285,0.0,0.0,0.0,1.0,1.0],[35.09535051955285,35.87353287717225,708.65,1.0,9.0,2.0,-1.0],[35.87353287717225,84.50993022838469,1860.0,1.0,9.0,2.0,-1.0]]</t>
+          <t>[[-31.828332235715447,35.09535051955285,0.0,0.0,0.0,1.0,1.0,1.000000001125549],[35.09535051955285,35.87353287717225,708.65,1.0,9.0,2.0,-1.0,0.9550634126664495],[35.87353287717225,84.50993022838469,1860.0,1.0,9.0,2.0,-1.0,0.8820545350507234]]</t>
         </is>
       </c>
       <c r="C667" t="n">
@@ -17792,7 +17792,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>[[-33.90698597714727,34.09493626394419,0.0,0.0,0.0,1.0,1.0],[34.09493626394419,35.33133485014585,890.0,0.0,8.0,3.0,-1.0],[35.33133485014585,89.32073978095181,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[-33.90698597714727,34.09493626394419,0.0,0.0,0.0,1.0,1.0,1.000000001125549],[34.09493626394419,35.33133485014585,890.0,0.0,8.0,3.0,-1.0,0.9435637297241539],[35.33133485014585,89.32073978095181,1860.0,0.0,8.0,3.0,-1.0,0.8820545350507234]]</t>
         </is>
       </c>
       <c r="C668" t="n">
@@ -17818,7 +17818,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>[[-33.185101756658604,29.614912640058996,-1860.0,1.0,8.0,2.0,-1.0],[29.614912640058996,30.01747683490975,-1074.7922,0.0,8.0,2.0,-1.0],[30.01747683490975,33.23799039371578,0.0,0.0,7.0,3.0,-1.0],[33.23799039371578,34.8482471731188,890.0,0.0,7.0,3.0,-1.0],[34.8482471731188,87.18159250371679,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-33.185101756658604,29.614912640058996,-1860.0,1.0,8.0,2.0,-1.0,0.988500318183253],[29.614912640058996,30.01747683490975,-1074.7922,0.0,8.0,2.0,-1.0,0.9435637272193976],[30.01747683490975,33.23799039371578,0.0,0.0,7.0,3.0,-1.0,0.882054535050723],[33.23799039371578,34.8482471731188,890.0,0.0,7.0,3.0,-1.0,0.8256182636493279],[34.8482471731188,87.18159250371679,1860.0,0.0,8.0,2.0,-1.0,0.7641090689758974]]</t>
         </is>
       </c>
       <c r="C669" t="n">
@@ -17844,7 +17844,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>[[-26.22554618816401,29.470728900250407,-1860.0,1.0,7.0,1.0,-1.0],[29.470728900250407,30.820941629666514,-1074.7922,0.0,7.0,2.0,-1.0],[30.820941629666514,34.19647345320678,0.0,0.0,6.0,3.0,-1.0],[34.19647345320678,34.53402663556081,890.0,0.0,6.0,3.0,-1.0],[34.53402663556081,74.70285533569,1860.0,0.0,7.0,2.0,-1.0]]</t>
+          <t>[[-26.22554618816401,29.470728900250407,-1860.0,1.0,7.0,1.0,-1.0,0.8705548521084274],[29.470728900250407,30.820941629666514,-1074.7922,0.0,7.0,2.0,-1.0,0.825618261144572],[30.820941629666514,34.19647345320678,0.0,0.0,6.0,3.0,-1.0,0.7641090689758974],[34.19647345320678,34.53402663556081,890.0,0.0,6.0,3.0,-1.0,0.7076727975745023],[34.53402663556081,74.70285533569,1860.0,0.0,7.0,2.0,-1.0,0.6461636029010718]]</t>
         </is>
       </c>
       <c r="C670" t="n">
@@ -17870,7 +17870,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>[[-24.27570248893813,29.777813305321807,-1860.0,1.0,6.0,1.0,-1.0],[29.777813305321807,30.726120599957945,-1074.7922,0.0,6.0,2.0,-1.0],[30.726120599957945,33.887144915411746,0.0,0.0,6.0,2.0,-1.0],[33.887144915411746,35.151554641593265,708.65,1.0,6.0,1.0,-1.0],[35.151554641593265,70.23892454313042,1860.0,1.0,6.0,1.0,-1.0]]</t>
+          <t>[[-24.27570248893813,29.777813305321807,-1860.0,1.0,6.0,1.0,-1.0,0.7526093860336018],[29.777813305321807,30.726120599957945,-1074.7922,0.0,6.0,2.0,-1.0,0.7076727950697465],[30.726120599957945,33.887144915411746,0.0,0.0,6.0,2.0,-1.0,0.6461636029010718],[33.887144915411746,35.151554641593265,708.65,1.0,6.0,1.0,-1.0,0.6012270144419722],[35.151554641593265,70.23892454313042,1860.0,1.0,6.0,1.0,-1.0,0.5282181368262462]]</t>
         </is>
       </c>
       <c r="C671" t="n">
@@ -17896,7 +17896,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>[[-27.099707609929105,29.142142677825028,-1860.0,1.0,5.0,1.0,-1.0],[29.142142677825028,31.1997713468892,-1074.7922,0.0,5.0,2.0,-1.0],[31.1997713468892,34.286214350485466,0.0,0.0,5.0,2.0,-1.0],[34.286214350485466,35.31502868501755,708.65,1.0,5.0,1.0,-1.0],[35.31502868501755,75.43878773176898,1860.0,1.0,5.0,1.0,-1.0]]</t>
+          <t>[[-27.099707609929105,29.142142677825028,-1860.0,1.0,5.0,1.0,-1.0,0.6346639199587762],[29.142142677825028,31.1997713468892,-1074.7922,0.0,5.0,2.0,-1.0,0.5897273289949209],[31.1997713468892,34.286214350485466,0.0,0.0,5.0,2.0,-1.0,0.5282181368262462],[34.286214350485466,35.31502868501755,708.65,1.0,5.0,1.0,-1.0,0.48328154836714665],[35.31502868501755,75.43878773176898,1860.0,1.0,5.0,1.0,-1.0,0.41027267075142054]]</t>
         </is>
       </c>
       <c r="C672" t="n">
@@ -17922,7 +17922,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>[[-31.020071838401307,29.428000559887252,-1860.0,1.0,4.0,2.0,-1.0],[29.428000559887252,30.56853022777949,-1074.7922,0.0,4.0,2.0,-1.0],[30.56853022777949,33.990119231456205,0.0,0.0,3.0,3.0,-1.0],[33.990119231456205,35.510825455312514,890.0,0.0,3.0,3.0,-1.0],[35.510825455312514,82.65271839485831,1860.0,0.0,3.0,3.0,-1.0]]</t>
+          <t>[[-31.020071838401307,29.428000559887252,-1860.0,1.0,4.0,2.0,-1.0,0.5167184538839507],[29.428000559887252,30.56853022777949,-1074.7922,0.0,4.0,2.0,-1.0,0.47178186292009516],[30.56853022777949,33.990119231456205,0.0,0.0,3.0,3.0,-1.0,0.4102726707514205],[33.990119231456205,35.510825455312514,890.0,0.0,3.0,3.0,-1.0,0.3538363993500254],[35.510825455312514,82.65271839485831,1860.0,0.0,3.0,3.0,-1.0,0.29232720467659484]]</t>
         </is>
       </c>
       <c r="C673" t="n">
@@ -17948,7 +17948,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>[[-30.93098828347613,28.592837133693326,-1860.0,1.0,3.0,1.0,-1.0],[28.592837133693326,30.109367717570255,-1074.7922,0.0,3.0,2.0,-1.0],[30.109367717570255,33.521561531293344,0.0,0.0,2.0,3.0,-1.0],[33.521561531293344,35.03809211517027,890.0,0.0,2.0,3.0,-1.0],[35.03809211517027,82.42967286132429,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[-30.93098828347613,28.592837133693326,-1860.0,1.0,3.0,1.0,-1.0,0.398772987809125],[28.592837133693326,30.109367717570255,-1074.7922,0.0,3.0,2.0,-1.0,0.3538363968452696],[30.109367717570255,33.521561531293344,0.0,0.0,2.0,3.0,-1.0,0.2923272046765949],[33.521561531293344,35.03809211517027,890.0,0.0,2.0,3.0,-1.0,0.23589093327519983],[35.03809211517027,82.42967286132429,1860.0,0.0,3.0,2.0,-1.0,0.17438173860176925]]</t>
         </is>
       </c>
       <c r="C674" t="n">
@@ -17974,7 +17974,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>[[-30.599016386269405,29.20463288517808,-1860.0,1.0,2.0,2.0,-1.0],[29.20463288517808,31.804791549154054,-1074.7922,0.0,2.0,2.0,-1.0],[31.804791549154054,35.147852688551744,0.0,0.0,2.0,2.0,-1.0],[35.147852688551744,80.46490368927593,1860.0,1.0,2.0,1.0,-1.0]]</t>
+          <t>[[-30.599016386269405,29.20463288517808,-1860.0,1.0,2.0,2.0,-1.0,0.2808275217342994],[29.20463288517808,31.804791549154054,-1074.7922,0.0,2.0,2.0,-1.0,0.235890930770444],[31.804791549154054,35.147852688551744,0.0,0.0,2.0,2.0,-1.0,0.1743817386017693],[35.147852688551744,80.46490368927593,1860.0,1.0,2.0,1.0,-1.0,0.05643627252694368]]</t>
         </is>
       </c>
       <c r="C675" t="n">
@@ -18000,7 +18000,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>[[-28.171330417118213,32.29362240124345,-1860.0,1.0,1.0,1.0,-1.0],[32.29362240124345,32.6472186165555,-1074.7922,0.0,1.0,2.0,-1.0],[32.6472186165555,36.18318076967607,0.0,0.0,1.0,2.0,-1.0],[36.18318076967607,36.890373200300175,708.65,1.0,1.0,1.0,-1.0],[36.890373200300175,39.36554670748457,890.0,0.0,0.0,0.0,-1.0],[39.36554670748457,77.55393796118668,890.0001,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-28.171330417118213,32.29362240124345,-1860.0,1.0,1.0,1.0,-1.0,0.16288205565947372],[32.29362240124345,32.6472186165555,-1074.7922,0.0,1.0,2.0,-1.0,0.11794546469561831],[32.6472186165555,36.18318076967607,0.0,0.0,1.0,2.0,-1.0,0.05643627252694362],[36.18318076967607,36.890373200300175,708.65,1.0,1.0,1.0,-1.0,0.011499684067844067],[36.890373200300175,39.36554670748457,890.0,0.0,0.0,0.0,-1.0,1.1255485710126578e-09],[39.36554670748457,77.55393796118668,890.0001,0.0,0.0,0.0,-1.0,-5.215605523856137e-09]]</t>
         </is>
       </c>
       <c r="C676" t="n">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>[[-29.273599285248203,29.50962019304434,-1860.0,1.0,2.0,0.0,-1.0],[29.50962019304434,30.60495968642867,-1275.7341,0.0,2.0,1.0,-1.0],[30.60495968642867,33.890978166581675,0.0,0.0,1.0,2.0,-1.0],[33.890978166581675,36.08165715335034,708.65,0.0,1.0,1.0,-1.0],[36.08165715335034,79.89523688872367,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-29.273599285248203,29.50962019304434,-1860.0,1.0,2.0,0.0,-1.0,0.26932783879200384],[29.50962019304434,30.60495968642867,-1275.7341,0.0,2.0,1.0,-1.0,0.23589093487634116],[30.60495968642867,33.890978166581675,0.0,0.0,1.0,2.0,-1.0,0.1628820556594737],[33.890978166581675,36.08165715335034,708.65,0.0,1.0,1.0,-1.0,0.11794546720037413],[36.08165715335034,79.89523688872367,1860.0,0.0,2.0,0.0,-1.0,0.044936589584648065]]</t>
         </is>
       </c>
       <c r="C677" t="n">
@@ -18052,7 +18052,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>[[-28.81166850675564,29.812480848511253,-1860.0,1.0,1.0,0.0,-1.0],[29.812480848511253,38.0341603312621,0.0,0.0,1.0,1.0,-1.0],[38.0341603312621,78.07016476900534,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-28.81166850675564,29.812480848511253,-1860.0,1.0,1.0,0.0,-1.0,0.2243912503329043],[29.812480848511253,38.0341603312621,0.0,0.0,1.0,1.0,-1.0,0.1179454672003742],[38.0341603312621,78.07016476900534,1860.0,0.0,1.0,0.0,-1.0,1.1255485710126578e-09]]</t>
         </is>
       </c>
       <c r="C678" t="n">
@@ -18078,7 +18078,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>[[-31.104303731529257,24.42502849584755,-1860.0,9.0,1.0,1.0,1.0],[24.42502849584755,24.802779055217464,-733.6842,9.0,1.0,1.0,1.0],[24.802779055217464,32.73554080198558,0.0,0.0,1.0,1.0,-1.0],[32.73554080198558,81.84311352007391,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-31.104303731529257,24.42502849584755,-1860.0,9.0,1.0,1.0,1.0,0.2243912503329043],[24.42502849584755,24.802779055217464,-733.6842,9.0,1.0,1.0,1.0,0.15993341840519348],[24.802779055217464,32.73554080198558,0.0,0.0,1.0,1.0,-1.0,0.1179454672003742],[32.73554080198558,81.84311352007391,1860.0,0.0,1.0,0.0,-1.0,1.1255485710126578e-09]]</t>
         </is>
       </c>
       <c r="C679" t="n">
@@ -18104,7 +18104,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>[[-31.56079275673752,24.287556886543868,-1860.0,9.0,1.0,0.0,1.0],[24.287556886543868,24.672717918566498,-934.626,9.0,1.0,0.0,1.0],[24.672717918566498,83.60235581802891,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-31.56079275673752,24.287556886543868,-1860.0,9.0,1.0,0.0,1.0,0.10644578425807864],[24.287556886543868,24.672717918566498,-934.626,9.0,1.0,0.0,1.0,0.053487633655669005],[24.672717918566498,83.60235581802891,0.0,0.0,0.0,1.0,-1.0,1.125548529379294e-09]]</t>
         </is>
       </c>
       <c r="C680" t="n">
@@ -18130,7 +18130,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>[[-27.650756889219956,24.51577912634574,-1860.0,8.0,0.0,1.0,1.0],[24.51577912634574,26.254663660197934,-733.6842,9.0,0.0,1.0,1.0],[26.254663660197934,76.334538235141,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-27.650756889219956,24.51577912634574,-1860.0,8.0,0.0,1.0,1.0,0.10644578425807864],[24.51577912634574,26.254663660197934,-733.6842,9.0,0.0,1.0,1.0,0.041987952330367805],[26.254663660197934,76.334538235141,0.0,0.0,0.0,1.0,-1.0,1.125548529379294e-09]]</t>
         </is>
       </c>
       <c r="C681" t="n">
@@ -18156,7 +18156,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>[[-29.230527204547855,26.001225636262163,-1860.0,8.0,0.0,1.0,1.0],[26.001225636262163,36.60864836727865,0.0,8.0,0.0,1.0,1.0],[36.60864836727865,80.1356588842084,662.1501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-29.230527204547855,26.001225636262163,-1860.0,8.0,0.0,1.0,1.0,0.1484337354628979],[26.001225636262163,36.60864836727865,0.0,8.0,0.0,1.0,1.0,0.0419879523303678],[36.60864836727865,80.1356588842084,662.1501,0.0,0.0,0.0,-1.0,-5.818015201553006e-09]]</t>
         </is>
       </c>
       <c r="C682" t="n">
@@ -18182,7 +18182,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>[[-28.61852342963555,26.344652389034138,-1860.0,7.0,0.0,1.0,1.0],[26.344652389034138,34.96632702725683,0.0,7.0,0.0,1.0,1.0],[34.96632702725683,35.684799913775386,890.0,7.0,8.0,4.0,-1.0],[35.684799913775386,78.79317310488887,1860.0,7.0,9.0,3.0,-1.0]]</t>
+          <t>[[-28.61852342963555,26.344652389034138,-1860.0,7.0,0.0,1.0,1.0,0.254879518595428],[26.344652389034138,34.96632702725683,0.0,7.0,0.0,1.0,1.0,0.1484337354628979],[34.96632702725683,35.684799913775386,890.0,7.0,8.0,4.0,-1.0,0.09199746406150285],[35.684799913775386,78.79317310488887,1860.0,7.0,9.0,3.0,-1.0,0.030488269388072267]]</t>
         </is>
       </c>
       <c r="C683" t="n">
@@ -18208,7 +18208,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>[[-28.79265679427514,26.699409428314077,-1860.0,6.0,0.0,1.0,1.0],[26.699409428314077,36.42853792188492,0.0,6.0,0.0,1.0,1.0],[36.42853792188492,36.7888760142394,890.0,7.0,8.0,3.0,-1.0],[36.7888760142394,78.94843281971302,1860.0,6.0,9.0,2.0,-1.0]]</t>
+          <t>[[-28.79265679427514,26.699409428314077,-1860.0,6.0,0.0,1.0,1.0,0.3613253017279581],[26.699409428314077,36.42853792188492,0.0,6.0,0.0,1.0,1.0,0.254879518595428],[36.42853792188492,36.7888760142394,890.0,7.0,8.0,3.0,-1.0,0.19844324719403295],[36.7888760142394,78.94843281971302,1860.0,6.0,9.0,2.0,-1.0,0.13693405252060237]]</t>
         </is>
       </c>
       <c r="C684" t="n">
@@ -18234,7 +18234,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>[[-30.771271789398448,26.104666428876143,-1860.0,5.0,0.0,1.0,1.0],[26.104666428876143,36.342335308165566,0.0,4.0,0.0,1.0,1.0],[36.342335308165566,37.47985407253106,890.0,4.0,8.0,4.0,-1.0],[37.47985407253106,82.60143172569559,1860.0,6.0,8.0,4.0,-1.0]]</t>
+          <t>[[-30.771271789398448,26.104666428876143,-1860.0,5.0,0.0,1.0,1.0,0.46777108486048824],[26.104666428876143,36.342335308165566,0.0,4.0,0.0,1.0,1.0,0.3613253017279581],[36.342335308165566,37.47985407253106,890.0,4.0,8.0,4.0,-1.0,0.30488903032656306],[37.47985407253106,82.60143172569559,1860.0,6.0,8.0,4.0,-1.0,0.24337983565313248]]</t>
         </is>
       </c>
       <c r="C685" t="n">
@@ -18260,7 +18260,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>[[-30.404471253732922,24.166964204055162,-1860.0,3.0,0.0,0.0,1.0],[24.166964204055162,36.536489574487135,0.0,4.0,0.0,1.0,1.0],[36.536489574487135,78.37459009212466,1860.0,4.0,9.0,3.0,-1.0]]</t>
+          <t>[[-30.404471253732922,24.166964204055162,-1860.0,3.0,0.0,0.0,1.0,0.5742168679930183],[24.166964204055162,36.536489574487135,0.0,4.0,0.0,1.0,1.0,0.4677710848604882],[36.536489574487135,78.37459009212466,1860.0,4.0,9.0,3.0,-1.0,0.34982561878566254]]</t>
         </is>
       </c>
       <c r="C686" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>[[-32.417326714932386,32.7659977033137,-1860.0,3.0,0.0,0.0,1.0],[32.7659977033137,37.36717354460167,0.0,4.0,0.0,1.0,1.0],[37.36717354460167,82.22863799715927,1860.0,4.0,8.0,3.0,-1.0]]</t>
+          <t>[[-32.417326714932386,32.7659977033137,-1860.0,3.0,0.0,0.0,1.0,0.5742168679930183],[32.7659977033137,37.36717354460167,0.0,4.0,0.0,1.0,1.0,0.4677710848604882],[37.36717354460167,82.22863799715927,1860.0,4.0,8.0,3.0,-1.0,0.34982561878566254]]</t>
         </is>
       </c>
       <c r="C687" t="n">
@@ -18312,7 +18312,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>[[-33.1293164050997,33.7844365518729,-1860.0,2.0,0.0,0.0,1.0],[33.7844365518729,34.17122125104615,-873.8504,2.0,8.0,3.0,-1.0],[34.17122125104615,37.65228354360542,0.0,2.0,7.0,4.0,-1.0],[37.65228354360542,82.51930864770266,1860.0,2.0,8.0,3.0,-1.0]]</t>
+          <t>[[-33.1293164050997,33.7844365518729,-1860.0,2.0,0.0,0.0,1.0,0.6806626511255485],[33.7844365518729,34.17122125104615,-873.8504,2.0,8.0,3.0,-1.0,0.6242263788363919],[34.17122125104615,37.65228354360542,0.0,2.0,7.0,4.0,-1.0,0.5742168679930184],[37.65228354360542,82.51930864770266,1860.0,2.0,8.0,3.0,-1.0,0.45627140191819276]]</t>
         </is>
       </c>
       <c r="C688" t="n">
@@ -18338,7 +18338,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>[[-31.71919514495139,32.94477883491197,-1860.0,2.0,0.0,0.0,1.0],[32.94477883491197,36.704312205834256,0.0,1.0,7.0,4.0,-1.0],[36.704312205834256,37.83217221711095,1071.35,2.0,7.0,4.0,-1.0],[37.83217221711095,80.69085264562503,1860.0,2.0,7.0,4.0,-1.0]]</t>
+          <t>[[-31.71919514495139,32.94477883491197,-1860.0,2.0,0.0,0.0,1.0,0.7871084342580785],[32.94477883491197,36.704312205834256,0.0,1.0,7.0,4.0,-1.0,0.6806626511255485],[36.704312205834256,37.83217221711095,1071.35,2.0,7.0,4.0,-1.0,0.6127266967818579],[37.83217221711095,80.69085264562503,1860.0,2.0,7.0,4.0,-1.0,0.5627171850507229]]</t>
         </is>
       </c>
       <c r="C689" t="n">
@@ -18364,7 +18364,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>[[-32.69866998057273,32.084518720121764,-1860.0,1.0,0.0,0.0,1.0],[32.084518720121764,32.47244200575467,-1860.0,0.0,0.0,0.0,1.0],[32.47244200575467,35.963751576450775,0.0,1.0,7.0,4.0,-1.0],[35.963751576450775,37.90336800461529,1071.35,0.0,7.0,1.0,-1.0],[37.90336800461529,83.29039242366473,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-32.69866998057273,32.084518720121764,-1860.0,1.0,0.0,0.0,1.0,0.8935542173906086],[32.084518720121764,32.47244200575467,-1860.0,0.0,0.0,0.0,1.0,0.8935542173906086],[32.47244200575467,35.963751576450775,0.0,1.0,7.0,4.0,-1.0,0.7871084342580785],[35.963751576450775,37.90336800461529,1071.35,0.0,7.0,1.0,-1.0,0.7191724799143879],[37.90336800461529,83.29039242366473,1860.0,0.0,8.0,0.0,-1.0,0.6691629681832529]]</t>
         </is>
       </c>
       <c r="C690" t="n">
@@ -18390,7 +18390,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>[[-32.81701824396253,-0.31010899154613725,-1860.0,1.0,0.0,0.0,1.0],[-0.31010899154613725,32.583787275779976,-1860.0,0.0,0.0,0.0,1.0],[32.583787275779976,36.06667040996745,0.0,0.0,7.0,5.0,-1.0],[36.06667040996745,37.22763145469661,1071.35,0.0,7.0,5.0,-1.0],[37.22763145469661,82.89209921404344,1860.0,0.0,7.0,5.0,-1.0]]</t>
+          <t>[[-32.81701824396253,-0.31010899154613725,-1860.0,1.0,0.0,0.0,1.0,1.0000000005231386],[-0.31010899154613725,32.583787275779976,-1860.0,0.0,0.0,0.0,1.0,1.0000000005231386],[32.583787275779976,36.06667040996745,0.0,0.0,7.0,5.0,-1.0,0.8935542173906086],[36.06667040996745,37.22763145469661,1071.35,0.0,7.0,5.0,-1.0,0.825618263046918],[37.22763145469661,82.89209921404344,1860.0,0.0,7.0,5.0,-1.0,0.775608751315783]]</t>
         </is>
       </c>
       <c r="C691" t="n">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>[[-30.184209392918717,37.34446037139034,0.0,0.0,0.0,1.0,1.0],[37.34446037139034,37.70948020795417,890.0,0.0,8.0,2.0,-1.0],[37.70948020795417,78.95672173966727,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-30.184209392918717,37.34446037139034,0.0,0.0,0.0,1.0,1.0,1.000000000523139],[37.34446037139034,37.70948020795417,890.0,0.0,8.0,2.0,-1.0,0.943563729121744],[37.70948020795417,78.95672173966727,1860.0,0.0,8.0,2.0,-1.0,0.8820545344483135]]</t>
         </is>
       </c>
       <c r="C692" t="n">
@@ -18442,7 +18442,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>[[-41.752715310779145,35.50317683559792,0.0,0.0,0.0,1.0,1.0],[35.50317683559792,35.9800650587237,890.0,0.0,8.0,0.0,-1.0],[35.9800650587237,100.83686340383039,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-41.752715310779145,35.50317683559792,0.0,0.0,0.0,1.0,1.0,1.000000000523139],[35.50317683559792,35.9800650587237,890.0,0.0,8.0,0.0,-1.0,0.943563729121744],[35.9800650587237,100.83686340383039,1860.0,0.0,8.0,0.0,-1.0,0.8820545344483135]]</t>
         </is>
       </c>
       <c r="C693" t="n">
@@ -18468,7 +18468,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>[[-53.279831199170204,30.627517510166143,-1860.0,1.0,8.0,0.0,-1.0],[30.627517510166143,33.582001619649816,-1074.7922,0.0,8.0,1.0,-1.0],[33.582001619649816,37.12738255103024,0.0,0.0,7.0,2.0,-1.0],[37.12738255103024,123.39831854795352,1860.0,0.0,7.0,2.0,-1.0]]</t>
+          <t>[[-53.279831199170204,30.627517510166143,-1860.0,1.0,8.0,0.0,-1.0,0.9885003175808431],[30.627517510166143,33.582001619649816,-1074.7922,0.0,8.0,1.0,-1.0,0.9435637266169877],[33.582001619649816,37.12738255103024,0.0,0.0,7.0,2.0,-1.0,0.882054534448313],[37.12738255103024,123.39831854795352,1860.0,0.0,7.0,2.0,-1.0,0.7641090683734875]]</t>
         </is>
       </c>
       <c r="C694" t="n">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>[[-56.62233414937768,31.26180929274551,-1860.0,1.0,7.0,0.0,-1.0],[31.26180929274551,31.88955317447497,-1074.7922,0.0,7.0,1.0,-1.0],[31.88955317447497,35.02827258312223,0.0,0.0,6.0,2.0,-1.0],[35.02827258312223,36.28376034658113,890.0,0.0,6.0,2.0,-1.0],[36.28376034658113,131.0730864877283,1860.0,0.0,6.0,2.0,-1.0]]</t>
+          <t>[[-56.62233414937768,31.26180929274551,-1860.0,1.0,7.0,0.0,-1.0,0.8705548515060175],[31.26180929274551,31.88955317447497,-1074.7922,0.0,7.0,1.0,-1.0,0.8256182605421621],[31.88955317447497,35.02827258312223,0.0,0.0,6.0,2.0,-1.0,0.7641090683734875],[35.02827258312223,36.28376034658113,890.0,0.0,6.0,2.0,-1.0,0.7076727969720924],[36.28376034658113,131.0730864877283,1860.0,0.0,6.0,2.0,-1.0,0.6461636022986619]]</t>
         </is>
       </c>
       <c r="C695" t="n">
@@ -18520,7 +18520,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>[[-51.164869456986665,30.914812336440463,-1860.0,1.0,6.0,0.0,-1.0],[30.914812336440463,32.05480791690472,-1074.7922,0.0,6.0,1.0,-1.0],[32.05480791690472,35.474794658297526,0.0,0.0,5.0,2.0,-1.0],[35.474794658297526,37.18478802899392,890.0,0.0,5.0,2.0,-1.0],[37.18478802899392,119.26446982242103,1860.0,0.0,5.0,2.0,-1.0]]</t>
+          <t>[[-51.164869456986665,30.914812336440463,-1860.0,1.0,6.0,0.0,-1.0,0.7526093854311919],[30.914812336440463,32.05480791690472,-1074.7922,0.0,6.0,1.0,-1.0,0.7076727944673366],[32.05480791690472,35.474794658297526,0.0,0.0,5.0,2.0,-1.0,0.6461636022986619],[35.474794658297526,37.18478802899392,890.0,0.0,5.0,2.0,-1.0,0.5897273308972668],[37.18478802899392,119.26446982242103,1860.0,0.0,5.0,2.0,-1.0,0.5282181362238363]]</t>
         </is>
       </c>
       <c r="C696" t="n">
@@ -18546,7 +18546,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>[[-56.39901469332861,30.81843071001454,-1860.0,1.0,5.0,0.0,-1.0],[30.81843071001454,32.06439421577659,-1074.7922,0.0,5.0,1.0,-1.0],[32.06439421577659,35.80228473306272,0.0,0.0,4.0,2.0,-1.0],[35.80228473306272,129.87252941809712,1860.0,0.0,4.0,1.0,-1.0]]</t>
+          <t>[[-56.39901469332861,30.81843071001454,-1860.0,1.0,5.0,0.0,-1.0,0.6346639193563663],[30.81843071001454,32.06439421577659,-1074.7922,0.0,5.0,1.0,-1.0,0.589727328392511],[32.06439421577659,35.80228473306272,0.0,0.0,4.0,2.0,-1.0,0.5282181362238363],[35.80228473306272,129.87252941809712,1860.0,0.0,4.0,1.0,-1.0,0.41027267014901064]]</t>
         </is>
       </c>
       <c r="C697" t="n">
@@ -18572,7 +18572,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>[[-55.221949823032176,31.514669514507816,-1860.0,1.0,4.0,0.0,-1.0],[31.514669514507816,32.73631204038867,-1074.7922,0.0,4.0,1.0,-1.0],[32.73631204038867,36.4012396180312,0.0,0.0,3.0,2.0,-1.0],[36.4012396180312,37.01206088097162,890.0,0.0,3.0,2.0,-1.0],[37.01206088097162,127.41360779615414,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[-55.221949823032176,31.514669514507816,-1860.0,1.0,4.0,0.0,-1.0,0.5167184532815408],[31.514669514507816,32.73631204038867,-1074.7922,0.0,4.0,1.0,-1.0,0.47178186231768526],[32.73631204038867,36.4012396180312,0.0,0.0,3.0,2.0,-1.0,0.4102726701490106],[36.4012396180312,37.01206088097162,890.0,0.0,3.0,2.0,-1.0,0.3538363987476155],[37.01206088097162,127.41360779615414,1860.0,0.0,3.0,2.0,-1.0,0.29232720407418494]]</t>
         </is>
       </c>
       <c r="C698" t="n">
@@ -18598,7 +18598,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>[[-54.72951406538033,31.72223537142459,-1860.0,10.0,11.0,2.0,0.0],[31.72223537142459,34.76631105581913,0.0,9.0,11.0,3.0,0.0],[34.76631105581913,35.37512619269803,890.0,0.0,2.0,1.0,-1.0],[35.37512619269803,127.30621186141312,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[-54.72951406538033,31.72223537142459,-1860.0,10.0,11.0,2.0,0.0,0.3987729872067151],[31.72223537142459,34.76631105581913,0.0,9.0,11.0,3.0,0.0,0.292327204074185],[34.76631105581913,35.37512619269803,890.0,0.0,2.0,1.0,-1.0,0.23589093267278993],[35.37512619269803,127.30621186141312,1860.0,0.0,2.0,1.0,-1.0,0.17438173799935935]]</t>
         </is>
       </c>
       <c r="C699" t="n">
@@ -18624,7 +18624,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>[[-53.894626048225064,31.92805761423942,-1860.0,9.0,1.0,2.0,1.0],[31.92805761423942,32.528216241249666,-1607.5346,8.0,1.0,3.0,1.0],[32.528216241249666,33.1283748682599,-822.3269,9.0,10.0,4.0,0.0],[33.1283748682599,36.72932663032135,0.0,9.0,10.0,4.0,0.0],[36.72932663032135,37.92964388434183,890.0,0.0,1.0,1.0,-1.0],[37.92964388434183,125.55280342783703,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[-53.894626048225064,31.92805761423942,-1860.0,9.0,1.0,2.0,1.0,0.2808275211318895],[31.92805761423942,32.528216241249666,-1607.5346,8.0,1.0,3.0,1.0,0.26637920004755217],[32.528216241249666,33.1283748682599,-822.3269,9.0,10.0,4.0,0.0,0.22144261480658833],[33.1283748682599,36.72932663032135,0.0,9.0,10.0,4.0,0.0,0.1743817379993594],[36.72932663032135,37.92964388434183,890.0,0.0,1.0,1.0,-1.0,0.11794546659796436],[37.92964388434183,125.55280342783703,1860.0,0.0,1.0,1.0,-1.0,0.05643627192453378]]</t>
         </is>
       </c>
       <c r="C700" t="n">
@@ -18650,7 +18650,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>[[-53.2551816766877,32.34419224654151,-1860.0,9.0,2.0,0.0,1.0],[32.34419224654151,35.88623530543376,0.0,9.0,1.0,1.0,1.0],[35.88623530543376,36.476575815249134,227.85,9.0,1.0,1.0,1.0],[36.476575815249134,37.65725683487989,890.0,0.0,1.0,0.0,-1.0],[37.65725683487989,123.25663075810913,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-53.2551816766877,32.34419224654151,-1860.0,9.0,2.0,0.0,1.0,0.2808275211318895],[32.34419224654151,35.88623530543376,0.0,9.0,1.0,1.0,1.0,0.1743817379993594],[35.88623530543376,36.476575815249134,227.85,9.0,1.0,1.0,1.0,0.15993341840519326],[36.476575815249134,37.65725683487989,890.0,0.0,1.0,0.0,-1.0,0.11794546659796436],[37.65725683487989,123.25663075810913,1860.0,0.0,1.0,0.0,-1.0,0.05643627192453378]]</t>
         </is>
       </c>
       <c r="C701" t="n">
@@ -18676,7 +18676,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>[[-50.97033535992235,32.312253649405214,-1860.0,9.0,1.0,1.0,1.0],[32.312253649405214,36.30525449231818,0.0,8.0,1.0,1.0,1.0],[36.30525449231818,119.58784350164575,1860.0,9.0,1.0,1.0,1.0]]</t>
+          <t>[[-50.97033535992235,32.312253649405214,-1860.0,9.0,1.0,1.0,1.0,0.2663792015377233],[32.312253649405214,36.30525449231818,0.0,8.0,1.0,1.0,1.0,0.1599334184051932],[36.30525449231818,119.58784350164575,1860.0,9.0,1.0,1.0,1.0,0.041987952330367576]]</t>
         </is>
       </c>
       <c r="C702" t="n">
@@ -18702,7 +18702,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>[[-52.059301324887315,32.380397891143005,-1860.0,9.0,0.0,1.0,1.0],[32.380397891143005,38.78616817649703,0.0,8.0,0.0,1.0,1.0],[38.78616817649703,122.06118188609936,662.1501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-52.059301324887315,32.380397891143005,-1860.0,9.0,0.0,1.0,1.0,0.1484337354628977],[32.380397891143005,38.78616817649703,0.0,8.0,0.0,1.0,1.0,0.04198795233036758],[38.78616817649703,122.06118188609936,662.1501,0.0,0.0,0.0,-1.0,-5.818015416658717e-09]]</t>
         </is>
       </c>
       <c r="C703" t="n">
@@ -18728,7 +18728,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>[[-54.53051563387305,34.6883912357676,-1860.0,8.0,0.0,0.0,1.0],[34.6883912357676,38.90820439852088,0.0,8.0,0.0,3.0,1.0],[38.90820439852088,125.71578946087396,662.1501,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-54.53051563387305,34.6883912357676,-1860.0,8.0,0.0,0.0,1.0,0.1484337354628977],[34.6883912357676,38.90820439852088,0.0,8.0,0.0,3.0,1.0,0.04198795233036758],[38.90820439852088,125.71578946087396,662.1501,0.0,0.0,0.0,-1.0,-5.818015416658717e-09]]</t>
         </is>
       </c>
       <c r="C704" t="n">
@@ -18754,7 +18754,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>[[-53.05658329962533,33.33859178583401,-1860.0,7.0,0.0,0.0,1.0],[33.33859178583401,39.80353686025613,0.0,7.0,0.0,3.0,1.0],[39.80353686025613,40.978981419241975,890.0,7.0,8.0,2.0,-1.0],[40.978981419241975,122.67237826875794,1860.0,6.0,9.0,1.0,-1.0]]</t>
+          <t>[[-53.05658329962533,33.33859178583401,-1860.0,7.0,0.0,0.0,1.0,0.2548795185954278],[33.33859178583401,39.80353686025613,0.0,7.0,0.0,3.0,1.0,0.1484337354628977],[39.80353686025613,40.978981419241975,890.0,7.0,8.0,2.0,-1.0,0.09199746406150265],[40.978981419241975,122.67237826875794,1860.0,6.0,9.0,1.0,-1.0,0.030488269388072073]]</t>
         </is>
       </c>
       <c r="C705" t="n">
@@ -18780,7 +18780,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>[[-52.18292626015968,34.02845649462032,-1860.0,5.0,0.0,0.0,1.0],[34.02845649462032,38.688531238121946,0.0,7.0,0.0,3.0,1.0],[38.688531238121946,121.98736727821341,1860.0,5.0,8.0,2.0,-1.0]]</t>
+          <t>[[-52.18292626015968,34.02845649462032,-1860.0,5.0,0.0,0.0,1.0,0.3613253017279579],[34.02845649462032,38.688531238121946,0.0,7.0,0.0,3.0,1.0,0.2548795185954278],[38.688531238121946,121.98736727821341,1860.0,5.0,8.0,2.0,-1.0,0.13693405252060215]]</t>
         </is>
       </c>
       <c r="C706" t="n">
@@ -18806,7 +18806,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>[[-52.825652769352274,33.628194414107995,-1860.0,5.0,0.0,0.0,1.0],[33.628194414107995,39.50940850822093,0.0,4.0,0.0,3.0,1.0],[39.50940850822093,40.09752991763223,890.0,4.0,8.0,3.0,-1.0],[40.09752991763223,123.02264864462472,1860.0,5.0,8.0,3.0,-1.0]]</t>
+          <t>[[-52.825652769352274,33.628194414107995,-1860.0,5.0,0.0,0.0,1.0,0.467771084860488],[33.628194414107995,39.50940850822093,0.0,4.0,0.0,3.0,1.0,0.3613253017279579],[39.50940850822093,40.09752991763223,890.0,4.0,8.0,3.0,-1.0,0.30488903032656284],[40.09752991763223,123.02264864462472,1860.0,5.0,8.0,3.0,-1.0,0.24337983565313226]]</t>
         </is>
       </c>
       <c r="C707" t="n">
@@ -18832,7 +18832,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>[[-55.59379515015006,34.22057374367917,-1860.0,3.0,0.0,0.0,1.0],[34.22057374367917,34.835740653910875,-1074.7922,4.0,9.0,3.0,-1.0],[34.835740653910875,38.52674211530112,0.0,5.0,8.0,4.0,-1.0],[38.52674211530112,39.75707593576453,890.0,4.0,8.0,4.0,-1.0],[39.75707593576453,128.34111100913032,1860.0,4.0,8.0,4.0,-1.0]]</t>
+          <t>[[-55.59379515015006,34.22057374367917,-1860.0,3.0,0.0,0.0,1.0,0.5742168679930182],[34.22057374367917,34.835740653910875,-1074.7922,4.0,9.0,3.0,-1.0,0.5292802770291627],[34.835740653910875,38.52674211530112,0.0,5.0,8.0,4.0,-1.0,0.467771084860488],[38.52674211530112,39.75707593576453,890.0,4.0,8.0,4.0,-1.0,0.41133481345909295],[39.75707593576453,128.34111100913032,1860.0,4.0,8.0,4.0,-1.0,0.3498256187856624]]</t>
         </is>
       </c>
       <c r="C708" t="n">
@@ -18858,7 +18858,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>[[-54.549407150899896,33.56131932061149,-1860.0,3.0,0.0,0.0,1.0],[33.56131932061149,34.164817447128684,-1074.7922,4.0,9.0,3.0,-1.0],[34.164817447128684,37.7858062062319,0.0,3.0,8.0,4.0,-1.0],[37.7858062062319,38.38930433274909,890.0,4.0,8.0,1.0,-1.0],[38.38930433274909,125.89653267774327,1860.0,3.0,8.0,1.0,-1.0]]</t>
+          <t>[[-54.549407150899896,33.56131932061149,-1860.0,3.0,0.0,0.0,1.0,0.6806626511255482],[33.56131932061149,34.164817447128684,-1074.7922,4.0,9.0,3.0,-1.0,0.6357260601616929],[34.164817447128684,37.7858062062319,0.0,3.0,8.0,4.0,-1.0,0.5742168679930182],[37.7858062062319,38.38930433274909,890.0,4.0,8.0,1.0,-1.0,0.5177805965916231],[38.38930433274909,125.89653267774327,1860.0,3.0,8.0,1.0,-1.0,0.45627140191819254]]</t>
         </is>
       </c>
       <c r="C709" t="n">
@@ -18884,7 +18884,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>[[-43.24000177629236,34.95161254995996,-1860.0,2.0,0.0,0.0,1.0],[34.95161254995996,39.265632650718715,0.0,1.0,0.0,3.0,1.0],[39.265632650718715,117.99649948956588,1860.0,2.0,8.0,4.0,-1.0]]</t>
+          <t>[[-43.24000177629236,34.95161254995996,-1860.0,2.0,0.0,0.0,1.0,0.7871084342580783],[34.95161254995996,39.265632650718715,0.0,1.0,0.0,3.0,1.0,0.6806626511255482],[39.265632650718715,117.99649948956588,1860.0,2.0,8.0,4.0,-1.0,0.5627171850507227]]</t>
         </is>
       </c>
       <c r="C710" t="n">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>[[-30.46844293043983,34.352888460668424,-1860.0,1.0,0.0,0.0,1.0],[34.352888460668424,39.11916282766167,0.0,1.0,0.0,3.0,1.0],[39.11916282766167,40.07241770106032,890.0,2.0,8.0,2.0,-1.0],[40.07241770106032,112.04316064265846,1860.0,2.0,8.0,2.0,-1.0]]</t>
+          <t>[[-30.46844293043983,34.352888460668424,-1860.0,1.0,0.0,0.0,1.0,0.8935542173906084],[34.352888460668424,39.11916282766167,0.0,1.0,0.0,3.0,1.0,0.7871084342580783],[39.11916282766167,40.07241770106032,890.0,2.0,8.0,2.0,-1.0,0.7306721628566832],[40.07241770106032,112.04316064265846,1860.0,2.0,8.0,2.0,-1.0,0.6691629681832527]]</t>
         </is>
       </c>
       <c r="C711" t="n">
@@ -18936,7 +18936,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>[[-29.708943869863496,-0.19950202422281293,-1860.0,1.0,0.0,0.0,1.0],[-0.19950202422281293,34.38187513863736,-1860.0,0.0,0.0,0.0,1.0],[34.38187513863736,35.30404519631363,0.0,1.0,0.0,3.0,1.0],[35.30404519631363,38.99272542701872,0.0,0.0,0.0,3.0,1.0],[38.99272542701872,40.37598051353313,890.0,1.0,8.0,3.0,-1.0],[40.37598051353313,108.15547975273907,1860.0,1.0,8.0,3.0,-1.0]]</t>
+          <t>[[-29.708943869863496,-0.19950202422281293,-1860.0,1.0,0.0,0.0,1.0,1.0000000005231384],[-0.19950202422281293,34.38187513863736,-1860.0,0.0,0.0,0.0,1.0,1.0000000005231384],[34.38187513863736,35.30404519631363,0.0,1.0,0.0,3.0,1.0,0.8935542173906084],[35.30404519631363,38.99272542701872,0.0,0.0,0.0,3.0,1.0,0.8935542173906084],[38.99272542701872,40.37598051353313,890.0,1.0,8.0,3.0,-1.0,0.8371179459892133],[40.37598051353313,108.15547975273907,1860.0,1.0,8.0,3.0,-1.0,0.7756087513157828]]</t>
         </is>
       </c>
       <c r="C712" t="n">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>[[-35.729377033057155,38.17732213159969,0.0,0.0,0.0,1.0,1.0],[38.17732213159969,40.148167442657204,1678.65,1.0,0.0,1.0,1.0],[40.148167442657204,111.59130996849217,1860.0,1.0,9.0,2.0,-1.0]]</t>
+          <t>[[-35.729377033057155,38.17732213159969,0.0,0.0,0.0,1.0,1.0,1.000000000523138],[38.17732213159969,40.148167442657204,1678.65,1.0,0.0,1.0,1.0,0.8935542173906078],[40.148167442657204,111.59130996849217,1860.0,1.0,9.0,2.0,-1.0,0.8820545344483124]]</t>
         </is>
       </c>
       <c r="C713" t="n">
@@ -18988,7 +18988,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>[[-44.31633785002805,-0.09161757305785301,-1860.0,1.0,0.0,0.0,1.0],[-0.09161757305785301,29.93751347920586,-1860.0,0.0,0.0,0.0,1.0],[29.93751347920586,35.39735548870836,0.0,1.0,0.0,1.0,1.0],[35.39735548870836,38.127276493459604,0.0,0.0,0.0,1.0,1.0],[38.127276493459604,39.219244895360106,0.0,1.0,0.0,1.0,1.0],[39.219244895360106,118.9329382340965,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-44.31633785002805,-0.09161757305785301,-1860.0,1.0,0.0,0.0,1.0,1.0000000005231384],[-0.09161757305785301,29.93751347920586,-1860.0,0.0,0.0,0.0,1.0,1.0000000005231384],[29.93751347920586,35.39735548870836,0.0,1.0,0.0,1.0,1.0,0.8935542173906083],[35.39735548870836,38.127276493459604,0.0,0.0,0.0,1.0,1.0,0.8935542173906083],[38.127276493459604,39.219244895360106,0.0,1.0,0.0,1.0,1.0,0.8935542173906083],[39.219244895360106,118.9329382340965,1860.0,0.0,8.0,0.0,-1.0,0.7756087513157827]]</t>
         </is>
       </c>
       <c r="C714" t="n">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="F714" s="4" t="inlineStr">
         <is>
-          <t>[0,0,6.5518104114,0,0]</t>
+          <t>[0,0,9.2817314162,0,0]</t>
         </is>
       </c>
     </row>
@@ -19014,7 +19014,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>[[-51.7791342196587,-0.14977784049241905,-1860.0,1.0,0.0,0.0,1.0],[-0.14977784049241905,35.236634958711434,-1860.0,0.0,0.0,0.0,1.0],[35.236634958711434,36.39684521442304,-873.8504,0.0,8.0,0.0,-1.0],[36.39684521442304,40.45758110941365,0.0,0.0,7.0,1.0,-1.0],[40.45758110941365,41.61779136512524,1071.35,0.0,7.0,0.0,-1.0],[41.61779136512524,121.67229900922578,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-51.7791342196587,-0.14977784049241905,-1860.0,1.0,0.0,0.0,1.0,1.0000000005231384],[-0.14977784049241905,35.236634958711434,-1860.0,0.0,0.0,0.0,1.0,1.0000000005231384],[35.236634958711434,36.39684521442304,-873.8504,0.0,8.0,0.0,-1.0,0.9435637282339817],[36.39684521442304,40.45758110941365,0.0,0.0,7.0,1.0,-1.0,0.8935542173906083],[40.45758110941365,41.61779136512524,1071.35,0.0,7.0,0.0,-1.0,0.8256182630469177],[41.61779136512524,121.67229900922578,1860.0,0.0,7.0,0.0,-1.0,0.7756087513157827]]</t>
         </is>
       </c>
       <c r="C715" t="n">
@@ -19040,7 +19040,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>[[-51.610287345826784,37.27241010005192,0.0,0.0,0.0,1.0,1.0],[37.27241010005192,39.58105159215267,890.0,0.0,8.0,1.0,-1.0],[39.58105159215267,120.96066418870396,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[-51.610287345826784,37.27241010005192,0.0,0.0,0.0,1.0,1.0,1.000000000523138],[37.27241010005192,39.58105159215267,890.0,0.0,8.0,1.0,-1.0,0.9435637291217429],[39.58105159215267,120.96066418870396,1860.0,0.0,8.0,1.0,-1.0,0.8820545344483124]]</t>
         </is>
       </c>
       <c r="C716" t="n">
@@ -19066,7 +19066,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>[[-53.60351622394437,31.728141412287144,-1860.0,1.0,8.0,2.0,-1.0],[31.728141412287144,33.51831604801228,-1074.7922,0.0,8.0,0.0,-1.0],[33.51831604801228,37.098665319462555,0.0,0.0,7.0,1.0,-1.0],[37.098665319462555,39.48556483376274,890.0,0.0,7.0,1.0,-1.0],[39.48556483376274,124.81722246999423,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[-53.60351622394437,31.728141412287144,-1860.0,1.0,8.0,2.0,-1.0,0.9885003175808429],[31.728141412287144,33.51831604801228,-1074.7922,0.0,8.0,0.0,-1.0,0.9435637266169875],[33.51831604801228,37.098665319462555,0.0,0.0,7.0,1.0,-1.0,0.8820545344483128],[37.098665319462555,39.48556483376274,890.0,0.0,7.0,1.0,-1.0,0.8256182630469178],[39.48556483376274,124.81722246999423,1860.0,0.0,7.0,1.0,-1.0,0.7641090683734872]]</t>
         </is>
       </c>
       <c r="C717" t="n">
@@ -19092,7 +19092,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>[[-39.202862162310026,31.869556187806978,-1860.0,1.0,7.0,0.0,-1.0],[31.869556187806978,35.01833421597672,-1074.7922,0.0,7.0,0.0,-1.0],[35.01833421597672,39.06676310933781,0.0,0.0,6.0,1.0,-1.0],[39.06676310933781,39.51658854193349,890.0,0.0,6.0,1.0,-1.0],[39.51658854193349,95.29494218379749,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[-39.202862162310026,31.869556187806978,-1860.0,1.0,7.0,0.0,-1.0,0.8705548515060173],[31.869556187806978,35.01833421597672,-1074.7922,0.0,7.0,0.0,-1.0,0.8256182605421619],[35.01833421597672,39.06676310933781,0.0,0.0,6.0,1.0,-1.0,0.7641090683734872],[39.06676310933781,39.51658854193349,890.0,0.0,6.0,1.0,-1.0,0.7076727969720922],[39.51658854193349,95.29494218379749,1860.0,0.0,6.0,1.0,-1.0,0.6461636022986617]]</t>
         </is>
       </c>
       <c r="C718" t="n">
@@ -19118,7 +19118,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>[[-34.43128099819712,32.509721522506474,-1860.0,1.0,6.0,0.0,-1.0],[32.509721522506474,35.34964284156663,-1074.7922,0.0,6.0,0.0,-1.0],[35.34964284156663,39.00097025178682,0.0,0.0,5.0,1.0,-1.0],[39.00097025178682,41.02948547968693,890.0,0.0,5.0,1.0,-1.0],[41.02948547968693,86.87392963022938,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[-34.43128099819712,32.509721522506474,-1860.0,1.0,6.0,0.0,-1.0,0.7526093854311917],[32.509721522506474,35.34964284156663,-1074.7922,0.0,6.0,0.0,-1.0,0.7076727944673363],[35.34964284156663,39.00097025178682,0.0,0.0,5.0,1.0,-1.0,0.6461636022986617],[39.00097025178682,41.02948547968693,890.0,0.0,5.0,1.0,-1.0,0.5897273308972666],[41.02948547968693,86.87392963022938,1860.0,0.0,5.0,1.0,-1.0,0.5282181362238361]]</t>
         </is>
       </c>
       <c r="C719" t="n">
@@ -19144,7 +19144,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>[[-33.03137420629556,33.143871937576456,-1860.0,1.0,5.0,1.0,-1.0],[33.143871937576456,33.53086168110787,-1074.7922,0.0,5.0,0.0,-1.0],[33.53086168110787,37.013769372890614,0.0,0.0,4.0,1.0,-1.0],[37.013769372890614,39.72269757761051,890.0,0.0,4.0,1.0,-1.0],[39.72269757761051,82.67855910959761,1860.0,0.0,4.0,1.0,-1.0]]</t>
+          <t>[[-33.03137420629556,33.143871937576456,-1860.0,1.0,5.0,1.0,-1.0,0.6346639193563661],[33.143871937576456,33.53086168110787,-1074.7922,0.0,5.0,0.0,-1.0,0.5897273283925107],[33.53086168110787,37.013769372890614,0.0,0.0,4.0,1.0,-1.0,0.5282181362238361],[37.013769372890614,39.72269757761051,890.0,0.0,4.0,1.0,-1.0,0.471781864822441],[39.72269757761051,82.67855910959761,1860.0,0.0,4.0,1.0,-1.0,0.4102726701490104]]</t>
         </is>
       </c>
       <c r="C720" t="n">
@@ -19170,7 +19170,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>[[-30.89081250446817,32.53339319379579,-1860.0,0.0,4.0,0.0,-1.0],[32.53339319379579,34.75880392005067,-1074.7922,0.0,4.0,0.0,-1.0],[34.75880392005067,38.46782179714212,0.0,0.0,3.0,1.0,-1.0],[38.46782179714212,38.838723584851266,890.0,0.0,3.0,0.0,-1.0],[38.838723584851266,80.00882202056647,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-30.89081250446817,32.53339319379579,-1860.0,0.0,4.0,0.0,-1.0,0.5167184532815405],[32.53339319379579,34.75880392005067,-1074.7922,0.0,4.0,0.0,-1.0,0.4717818623176851],[34.75880392005067,38.46782179714212,0.0,0.0,3.0,1.0,-1.0,0.4102726701490104],[38.46782179714212,38.838723584851266,890.0,0.0,3.0,0.0,-1.0,0.35383639874761535],[38.838723584851266,80.00882202056647,1860.0,0.0,3.0,0.0,-1.0,0.2923272040741848]]</t>
         </is>
       </c>
       <c r="C721" t="n">
@@ -19196,7 +19196,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>[[-28.768782865052465,32.14414761567465,-1860.0,1.0,3.0,0.0,-1.0],[32.14414761567465,34.25673479997732,-1074.7922,0.0,3.0,0.0,-1.0],[34.25673479997732,38.12981130453223,0.0,0.0,2.0,1.0,-1.0],[38.12981130453223,38.83400703263312,890.0,0.0,2.0,0.0,-1.0],[38.83400703263312,76.50847848603081,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-28.768782865052465,32.14414761567465,-1860.0,1.0,3.0,0.0,-1.0,0.3987729872067149],[32.14414761567465,34.25673479997732,-1074.7922,0.0,3.0,0.0,-1.0,0.35383639624285945],[34.25673479997732,38.12981130453223,0.0,0.0,2.0,1.0,-1.0,0.2923272040741848],[38.12981130453223,38.83400703263312,890.0,0.0,2.0,0.0,-1.0,0.2358909326727897],[38.83400703263312,76.50847848603081,1860.0,0.0,2.0,0.0,-1.0,0.17438173799935913]]</t>
         </is>
       </c>
       <c r="C722" t="n">
@@ -19222,7 +19222,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>[[-34.19594199225515,32.771232137024036,-1860.0,1.0,2.0,1.0,-1.0],[32.771232137024036,34.76430279563353,-1074.7922,0.0,2.0,0.0,-1.0],[34.76430279563353,38.75044411285253,0.0,0.0,1.0,1.0,-1.0],[38.75044411285253,39.14905824457443,890.0,0.0,1.0,0.0,-1.0],[39.14905824457443,84.98968339259292,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-34.19594199225515,32.771232137024036,-1860.0,1.0,2.0,1.0,-1.0,0.28082752113188925],[32.771232137024036,34.76430279563353,-1074.7922,0.0,2.0,0.0,-1.0,0.2358909301680338],[34.76430279563353,38.75044411285253,0.0,0.0,1.0,1.0,-1.0,0.1743817379993591],[38.75044411285253,39.14905824457443,890.0,0.0,1.0,0.0,-1.0,0.11794546659796405],[39.14905824457443,84.98968339259292,1860.0,0.0,1.0,0.0,-1.0,0.056436271924533474]]</t>
         </is>
       </c>
       <c r="C723" t="n">
@@ -19248,7 +19248,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>[[-30.966837435697183,31.758947849117977,-1860.0,1.0,1.0,0.0,-1.0],[31.758947849117977,36.924600754926274,-1074.7922,0.0,1.0,0.0,-1.0],[36.924600754926274,40.98332803806137,0.0,0.0,0.0,1.0,-1.0],[40.98332803806137,45.41103052875421,890.0,0.0,0.0,0.0,-1.0],[45.41103052875421,79.35674962406594,890.0001,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-30.966837435697183,31.758947849117977,-1860.0,1.0,1.0,0.0,-1.0,0.1628820550570636],[31.758947849117977,36.924600754926274,-1074.7922,0.0,1.0,0.0,-1.0,0.11794546409320819],[36.924600754926274,40.98332803806137,0.0,0.0,0.0,1.0,-1.0,0.0564362719245335],[40.98332803806137,45.41103052875421,890.0,0.0,0.0,0.0,-1.0,5.231384492265789e-10],[45.41103052875421,79.35674962406594,890.0001,0.0,0.0,0.0,-1.0,-5.818015645642216e-09]]</t>
         </is>
       </c>
       <c r="C724" t="n">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="F724" s="4" t="inlineStr">
         <is>
-          <t>[0,5.1656529058,0,0,0]</t>
+          <t>[0,5.1656529058,4.0587272831,0,0]</t>
         </is>
       </c>
     </row>
@@ -19274,7 +19274,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>[[-32.55042779959685,31.4305174132816,-1860.0,1.0,1.0,0.0,-1.0],[31.4305174132816,32.972226936483494,-1074.7922,0.0,1.0,1.0,-1.0],[32.972226936483494,36.441073363687735,0.0,0.0,0.0,2.0,-1.0],[36.441073363687735,38.75363764849058,890.0,0.0,0.0,0.0,-1.0],[38.75363764849058,82.69235905974445,890.0001,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-32.55042779959685,31.4305174132816,-1860.0,1.0,1.0,0.0,-1.0,0.1628820550570636],[31.4305174132816,32.972226936483494,-1074.7922,0.0,1.0,1.0,-1.0,0.11794546409320819],[32.972226936483494,36.441073363687735,0.0,0.0,0.0,2.0,-1.0,0.0564362719245335],[36.441073363687735,38.75363764849058,890.0,0.0,0.0,0.0,-1.0,5.231384492265789e-10],[38.75363764849058,82.69235905974445,890.0001,0.0,0.0,0.0,-1.0,-5.818015645642216e-09]]</t>
         </is>
       </c>
       <c r="C725" t="n">
@@ -19300,7 +19300,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>[[-29.368462303648357,31.785697373569768,-1860.0,1.0,0.0,1.0,-1.0],[31.785697373569768,77.5619104652886,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-29.368462303648357,31.785697373569768,-1860.0,1.0,0.0,1.0,-1.0,0.10644577731451446],[31.785697373569768,77.5619104652886,0.0,0.0,0.0,1.0,-1.0,-5.818015645642216e-09]]</t>
         </is>
       </c>
       <c r="C726" t="n">
@@ -19326,7 +19326,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>[[-30.131967271497746,31.383679290121737,-1860.0,1.0,0.0,0.0,-1.0],[31.383679290121737,77.43047905554451,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-30.131967271497746,31.383679290121737,-1860.0,1.0,0.0,0.0,-1.0,0.10644577731451446],[31.383679290121737,77.43047905554451,0.0,0.0,0.0,1.0,-1.0,-5.818015645642216e-09]]</t>
         </is>
       </c>
       <c r="C727" t="n">
@@ -19352,7 +19352,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>[[-35.7758807308387,24.256513894983648,-1860.0,10.0,0.0,0.0,1.0],[24.256513894983648,27.17475530040557,-733.6842,9.0,0.0,1.0,1.0],[27.17475530040557,88.87471644361187,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-35.7758807308387,24.256513894983648,-1860.0,10.0,0.0,0.0,1.0,0.10644577731451446],[24.256513894983648,27.17475530040557,-733.6842,9.0,0.0,1.0,1.0,0.04198794538680363],[27.17475530040557,88.87471644361187,0.0,0.0,0.0,1.0,-1.0,-5.818015645642216e-09]]</t>
         </is>
       </c>
       <c r="C728" t="n">
@@ -19378,7 +19378,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>[[-32.50548000638426,22.943010270492124,-1860.0,9.0,0.0,0.0,1.0],[22.943010270492124,28.67906098878968,-733.6842,9.0,0.0,0.0,1.0],[28.67906098878968,81.83313097834704,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-32.50548000638426,22.943010270492124,-1860.0,9.0,0.0,0.0,1.0,0.10644577731451446],[22.943010270492124,28.67906098878968,-733.6842,9.0,0.0,0.0,1.0,0.04198794538680363],[28.67906098878968,81.83313097834704,0.0,0.0,0.0,1.0,-1.0,-5.818015645642216e-09]]</t>
         </is>
       </c>
       <c r="C729" t="n">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>[[-31.078974934820035,28.588273765570985,-1860.0,8.0,0.0,0.0,1.0],[28.588273765570985,28.96119406994843,-1074.7924,8.0,9.0,2.0,-1.0],[28.96119406994843,32.31747680934542,0.0,8.0,8.0,3.0,-1.0],[32.31747680934542,80.42419607403569,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-31.078974934820035,28.588273765570985,-1860.0,8.0,0.0,0.0,1.0,0.14843372851933373],[28.588273765570985,28.96119406994843,-1074.7924,8.0,9.0,2.0,-1.0,0.10349714900126146],[28.96119406994843,32.31747680934542,0.0,8.0,8.0,3.0,-1.0,0.04198794538680363],[32.31747680934542,80.42419607403569,662.15,0.0,0.0,0.0,-1.0,-6.420425288644616e-09]]</t>
         </is>
       </c>
       <c r="C730" t="n">
@@ -19430,7 +19430,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>[[-32.485242608611614,29.834443079613628,-1860.0,8.0,0.0,0.0,1.0],[29.834443079613628,30.221521872708195,-873.8505,7.0,8.0,1.0,-1.0],[30.221521872708195,33.7052310105593,0.0,7.0,8.0,1.0,-1.0],[33.7052310105593,83.25131652666384,1860.0,8.0,8.0,0.0,-1.0]]</t>
+          <t>[[-32.485242608611614,29.834443079613628,-1860.0,8.0,0.0,0.0,1.0,0.25487951165186384],[29.834443079613628,30.221521872708195,-873.8505,7.0,8.0,1.0,-1.0,0.19844324508559877],[30.221521872708195,33.7052310105593,0.0,7.0,8.0,1.0,-1.0,0.1484337285193337],[33.7052310105593,83.25131652666384,1860.0,8.0,8.0,0.0,-1.0,0.03048826244450807]]</t>
         </is>
       </c>
       <c r="C731" t="n">
@@ -19456,7 +19456,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>[[-31.61580257078431,29.42855830180786,-1860.0,6.0,0.0,0.0,1.0],[29.42855830180786,30.182192386654677,-873.8505,5.0,8.0,4.0,-1.0],[30.182192386654677,33.19672872604194,0.0,6.0,7.0,5.0,-1.0],[33.19672872604194,33.95036281088876,1071.3499,6.0,7.0,5.0,-1.0],[33.95036281088876,81.05249311381482,1860.0,6.0,7.0,5.0,-1.0]]</t>
+          <t>[[-31.61580257078431,29.42855830180786,-1860.0,6.0,0.0,0.0,1.0,0.3613252947843939],[29.42855830180786,30.182192386654677,-873.8505,5.0,8.0,4.0,-1.0,0.30488902821812885],[30.182192386654677,33.19672872604194,0.0,6.0,7.0,5.0,-1.0,0.2548795116518638],[33.19672872604194,33.95036281088876,1071.3499,6.0,7.0,5.0,-1.0,0.18694356364932732],[33.95036281088876,81.05249311381482,1860.0,6.0,7.0,5.0,-1.0,0.13693404557703814]]</t>
         </is>
       </c>
       <c r="C732" t="n">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>[[-31.769087416979048,29.661683433528907,-1860.0,5.0,0.0,0.0,1.0],[29.661683433528907,30.038559328317298,-1074.7924,5.0,9.0,2.0,-1.0],[30.038559328317298,33.43044238141283,0.0,4.0,8.0,3.0,-1.0],[33.43044238141283,80.91680512475027,1860.0,6.0,8.0,3.0,-1.0]]</t>
+          <t>[[-31.769087416979048,29.661683433528907,-1860.0,5.0,0.0,0.0,1.0,0.4677710779169241],[29.661683433528907,30.038559328317298,-1074.7924,5.0,9.0,2.0,-1.0,0.42283449839885184],[30.038559328317298,33.43044238141283,0.0,4.0,8.0,3.0,-1.0,0.361325294784394],[33.43044238141283,80.91680512475027,1860.0,6.0,8.0,3.0,-1.0,0.24337982870956837]]</t>
         </is>
       </c>
       <c r="C733" t="n">
@@ -19508,7 +19508,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>[[-32.2778656719903,29.427625793212563,-1860.0,4.0,0.0,0.0,1.0],[29.427625793212563,32.877001092509616,0.0,3.0,7.0,4.0,-1.0],[32.877001092509616,82.31804704910073,1860.0,4.0,8.0,3.0,-1.0]]</t>
+          <t>[[-32.2778656719903,29.427625793212563,-1860.0,4.0,0.0,0.0,1.0,0.5742168610494542],[29.427625793212563,32.877001092509616,0.0,3.0,7.0,4.0,-1.0,0.4677710779169241],[32.877001092509616,82.31804704910073,1860.0,4.0,8.0,3.0,-1.0,0.3498256118420985]]</t>
         </is>
       </c>
       <c r="C734" t="n">
@@ -19534,7 +19534,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>[[-30.993354997041923,28.697334156139195,-1860.0,3.0,0.0,0.0,1.0],[28.697334156139195,29.065795200294634,-1074.7924,3.0,9.0,2.0,-1.0],[29.065795200294634,32.38194459769359,0.0,3.0,8.0,3.0,-1.0],[32.38194459769359,32.75040564184903,889.9999,3.0,8.0,3.0,-1.0],[32.75040564184903,79.17649720543434,1860.0,3.0,9.0,2.0,-1.0]]</t>
+          <t>[[-30.993354997041923,28.697334156139195,-1860.0,3.0,0.0,0.0,1.0,0.6806626441819843],[28.697334156139195,29.065795200294634,-1074.7924,3.0,9.0,2.0,-1.0,0.635726064663912],[29.065795200294634,32.38194459769359,0.0,3.0,8.0,3.0,-1.0,0.5742168610494542],[32.38194459769359,32.75040564184903,889.9999,3.0,8.0,3.0,-1.0,0.5177805959892132],[32.75040564184903,79.17649720543434,1860.0,3.0,9.0,2.0,-1.0,0.4562713949746286]]</t>
         </is>
       </c>
       <c r="C735" t="n">
@@ -19560,7 +19560,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>[[-30.943796990996304,29.151698280208457,-1860.0,3.0,0.0,0.0,1.0],[29.151698280208457,29.522658127561577,-873.8505,2.0,8.0,3.0,-1.0],[29.522658127561577,32.861296753739616,0.0,1.0,7.0,4.0,-1.0],[32.861296753739616,33.23225660109273,1071.3499,2.0,7.0,2.0,-1.0],[33.23225660109273,79.97319736758533,1860.0,1.0,8.0,1.0,-1.0]]</t>
+          <t>[[-30.943796990996304,29.151698280208457,-1860.0,3.0,0.0,0.0,1.0,0.7871084273145144],[29.151698280208457,29.522658127561577,-873.8505,2.0,8.0,3.0,-1.0,0.7306721607482494],[29.522658127561577,32.861296753739616,0.0,1.0,7.0,4.0,-1.0,0.6806626441819843],[32.861296753739616,33.23225660109273,1071.3499,2.0,7.0,2.0,-1.0,0.6127266961794479],[33.23225660109273,79.97319736758533,1860.0,1.0,8.0,1.0,-1.0,0.5627171781071587]]</t>
         </is>
       </c>
       <c r="C736" t="n">
@@ -19586,7 +19586,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>[[-32.65701041984325,28.86103775854218,-1860.0,1.0,0.0,0.0,1.0],[28.86103775854218,30.40866161208647,-873.8505,0.0,8.0,3.0,-1.0],[30.40866161208647,33.503909319175044,0.0,1.0,7.0,4.0,-1.0],[33.503909319175044,33.890815282561114,1071.3499,1.0,7.0,4.0,-1.0],[33.890815282561114,83.02787263259225,1860.0,1.0,7.0,4.0,-1.0]]</t>
+          <t>[[-32.65701041984325,28.86103775854218,-1860.0,1.0,0.0,0.0,1.0,0.8935542104470444],[28.86103775854218,30.40866161208647,-873.8505,0.0,8.0,3.0,-1.0,0.8371179438807794],[30.40866161208647,33.503909319175044,0.0,1.0,7.0,4.0,-1.0,0.7871084273145144],[33.503909319175044,33.890815282561114,1071.3499,1.0,7.0,4.0,-1.0,0.7191724793119779],[33.890815282561114,83.02787263259225,1860.0,1.0,7.0,4.0,-1.0,0.6691629612396888]]</t>
         </is>
       </c>
       <c r="C737" t="n">
@@ -19612,7 +19612,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>[[-32.51466806125558,29.434510847703038,-1860.0,1.0,0.0,0.0,1.0],[29.434510847703038,29.81928835645433,-873.8505,0.0,8.0,4.0,-1.0],[29.81928835645433,32.8975084264647,0.0,0.0,7.0,5.0,-1.0],[32.8975084264647,33.282285935215995,1071.3499,0.0,7.0,2.0,-1.0],[33.282285935215995,82.53380705538186,1860.0,0.0,7.0,2.0,-1.0]]</t>
+          <t>[[-32.51466806125558,29.434510847703038,-1860.0,1.0,0.0,0.0,1.0,0.9999999935795745],[29.434510847703038,29.81928835645433,-873.8505,0.0,8.0,4.0,-1.0,0.9435637270133095],[29.81928835645433,32.8975084264647,0.0,0.0,7.0,5.0,-1.0,0.8935542104470444],[32.8975084264647,33.282285935215995,1071.3499,0.0,7.0,2.0,-1.0,0.825618262444508],[33.282285935215995,82.53380705538186,1860.0,0.0,7.0,2.0,-1.0,0.7756087443722188]]</t>
         </is>
       </c>
       <c r="C738" t="n">
@@ -19638,7 +19638,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>[[-13.131316306579096,31.671417569136253,0.0,0.0,0.0,1.0,1.0],[31.671417569136253,31.949695419295978,889.9999,0.0,8.0,2.0,-1.0],[31.949695419295978,70.07376089117798,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-13.131316306579096,31.671417569136253,0.0,0.0,0.0,1.0,1.0,0.9999999935795745],[31.671417569136253,31.949695419295978,889.9999,0.0,8.0,2.0,-1.0,0.9435637285193335],[31.949695419295978,70.07376089117798,1860.0,0.0,8.0,2.0,-1.0,0.8820545275047489]]</t>
         </is>
       </c>
       <c r="C739" t="n">
@@ -19664,7 +19664,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>[[-15.634361583389646,26.93733307354377,-1860.0,1.0,8.0,3.0,-1.0],[26.93733307354377,28.736137073132504,-1074.7924,0.0,8.0,2.0,-1.0],[28.736137073132504,31.734143739113733,0.0,0.0,8.0,2.0,-1.0],[31.734143739113733,32.33374507230998,708.6499,1.0,8.0,1.0,-1.0],[32.33374507230998,74.00603772944902,1860.0,1.0,8.0,1.0,-1.0]]</t>
+          <t>[[-15.634361583389646,26.93733307354377,-1860.0,1.0,8.0,3.0,-1.0,0.988500310637279],[26.93733307354377,28.736137073132504,-1074.7924,0.0,8.0,2.0,-1.0,0.9435637311192067],[28.736137073132504,31.734143739113733,0.0,0.0,8.0,2.0,-1.0,0.8820545275047489],[31.734143739113733,32.33374507230998,708.6499,1.0,8.0,1.0,-1.0,0.8371179453868034],[32.33374507230998,74.00603772944902,1860.0,1.0,8.0,1.0,-1.0,0.7641090614299233]]</t>
         </is>
       </c>
       <c r="C740" t="n">
@@ -19690,7 +19690,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>[[-13.347120595703004,28.568804033086494,-1860.0,1.0,7.0,2.0,-1.0],[28.568804033086494,31.87795597746461,0.0,0.0,7.0,2.0,-1.0],[31.87795597746461,69.10591535171844,1860.0,1.0,7.0,1.0,-1.0]]</t>
+          <t>[[-13.347120595703004,28.568804033086494,-1860.0,1.0,7.0,2.0,-1.0,0.8705548445624534],[28.568804033086494,31.87795597746461,0.0,0.0,7.0,2.0,-1.0,0.7641090614299233],[31.87795597746461,69.10591535171844,1860.0,1.0,7.0,1.0,-1.0,0.6461635953550977]]</t>
         </is>
       </c>
       <c r="C741" t="n">
@@ -19716,7 +19716,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>[[-16.26337656287661,28.438059445631964,-1860.0,1.0,6.0,3.0,-1.0],[28.438059445631964,28.73806908327296,-1074.7924,0.0,6.0,2.0,-1.0],[28.73806908327296,32.03817509732393,0.0,0.0,5.0,3.0,-1.0],[32.03817509732393,73.43950509178154,1860.0,0.0,5.0,2.0,-1.0]]</t>
+          <t>[[-16.26337656287661,28.438059445631964,-1860.0,1.0,6.0,3.0,-1.0,0.7526093784876278],[28.438059445631964,28.73806908327296,-1074.7924,0.0,6.0,2.0,-1.0,0.7076727989695555],[28.73806908327296,32.03817509732393,0.0,0.0,5.0,3.0,-1.0,0.6461635953550977],[32.03817509732393,73.43950509178154,1860.0,0.0,5.0,2.0,-1.0,0.5282181292802721]]</t>
         </is>
       </c>
       <c r="C742" t="n">
@@ -19742,7 +19742,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>[[-11.07847102430893,27.028891454445095,-1860.0,1.0,5.0,1.0,-1.0],[27.028891454445095,28.342938436471094,-1074.7924,0.0,5.0,2.0,-1.0],[28.342938436471094,31.4966511933335,0.0,0.0,5.0,2.0,-1.0],[31.4966511933335,31.759460589738694,708.6499,1.0,5.0,1.0,-1.0],[31.759460589738694,67.50153850084592,1860.0,1.0,5.0,1.0,-1.0]]</t>
+          <t>[[-11.07847102430893,27.028891454445095,-1860.0,1.0,5.0,1.0,-1.0,0.6346639124128022],[27.028891454445095,28.342938436471094,-1074.7924,0.0,5.0,2.0,-1.0,0.5897273328947299],[28.342938436471094,31.4966511933335,0.0,0.0,5.0,2.0,-1.0,0.5282181292802721],[31.4966511933335,31.759460589738694,708.6499,1.0,5.0,1.0,-1.0,0.48328154716232663],[31.759460589738694,67.50153850084592,1860.0,1.0,5.0,1.0,-1.0,0.4102726632054465]]</t>
         </is>
       </c>
       <c r="C743" t="n">
@@ -19768,7 +19768,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>[[-13.027495675023388,27.2594268380329,-1860.0,1.0,4.0,2.0,-1.0],[27.2594268380329,29.437098325225136,-1074.7924,0.0,4.0,2.0,-1.0],[29.437098325225136,32.431396620114455,0.0,0.0,4.0,2.0,-1.0],[32.431396620114455,33.24802342781154,708.6499,1.0,4.0,1.0,-1.0],[33.24802342781154,68.36297615878628,1860.0,1.0,5.0,0.0,-1.0]]</t>
+          <t>[[-13.027495675023388,27.2594268380329,-1860.0,1.0,4.0,2.0,-1.0,0.5167184463379766],[27.2594268380329,29.437098325225136,-1074.7924,0.0,4.0,2.0,-1.0,0.4717818668199043],[29.437098325225136,32.431396620114455,0.0,0.0,4.0,2.0,-1.0,0.4102726632054465],[32.431396620114455,33.24802342781154,708.6499,1.0,4.0,1.0,-1.0,0.365336081087501],[33.24802342781154,68.36297615878628,1860.0,1.0,5.0,0.0,-1.0,0.29232719713062083]]</t>
         </is>
       </c>
       <c r="C744" t="n">
@@ -19794,7 +19794,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>[[-14.608046835750933,29.378461153398014,-1860.0,1.0,3.0,1.0,-1.0],[29.378461153398014,29.67367261641244,-1074.7924,0.0,3.0,2.0,-1.0],[29.67367261641244,32.92099870957109,0.0,0.0,2.0,3.0,-1.0],[32.92099870957109,73.66018060556138,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[-14.608046835750933,29.378461153398014,-1860.0,1.0,3.0,1.0,-1.0,0.3987729802631509],[29.378461153398014,29.67367261641244,-1074.7924,0.0,3.0,2.0,-1.0,0.3538364007450786],[29.67367261641244,32.92099870957109,0.0,0.0,2.0,3.0,-1.0,0.2923271971306208],[32.92099870957109,73.66018060556138,1860.0,0.0,3.0,2.0,-1.0,0.17438173105579513]]</t>
         </is>
       </c>
       <c r="C745" t="n">

--- a/Figure_Plot/figure_plot_4_c/input/dsfunction_May2025_exact_V5_k20_classified.xlsx
+++ b/Figure_Plot/figure_plot_4_c/input/dsfunction_May2025_exact_V5_k20_classified.xlsx
@@ -15988,7 +15988,7 @@
       </c>
       <c r="F598" s="4" t="inlineStr">
         <is>
-          <t>[0,16.6315309082,1.750687464,0,1.313015598]</t>
+          <t>[0,0,1.750687464,0,1.313015598]</t>
         </is>
       </c>
     </row>
@@ -16014,7 +16014,7 @@
       </c>
       <c r="F599" s="4" t="inlineStr">
         <is>
-          <t>[0,16.7827991083,1.3607674953,0,1.8143566604]</t>
+          <t>[0,0,1.3607674953,0,1.8143566604]</t>
         </is>
       </c>
     </row>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="F600" s="4" t="inlineStr">
         <is>
-          <t>[0,17.8011135412,1.3693164262,0,1.825755235]</t>
+          <t>[0,0,1.3693164262,0,1.825755235]</t>
         </is>
       </c>
     </row>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="F601" s="4" t="inlineStr">
         <is>
-          <t>[0,16.8011129209,1.4400953932,0,1.4400953932]</t>
+          <t>[0,0,1.4400953932,0,1.4400953932]</t>
         </is>
       </c>
     </row>
@@ -16092,7 +16092,7 @@
       </c>
       <c r="F602" s="4" t="inlineStr">
         <is>
-          <t>[0,17.0457152914,1.4204762743,0,1.8939683657]</t>
+          <t>[0,0,1.4204762743,0,1.8939683657]</t>
         </is>
       </c>
     </row>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="F603" s="4" t="inlineStr">
         <is>
-          <t>[0,16.8625319601,1.4453598823,0,1.4453598823]</t>
+          <t>[0,0,1.4453598823,0,1.4453598823]</t>
         </is>
       </c>
     </row>
@@ -16144,7 +16144,7 @@
       </c>
       <c r="F604" s="4" t="inlineStr">
         <is>
-          <t>[0,16.9755098227,1.4146258186,0,1.4146258186]</t>
+          <t>[0,0,1.4146258186,0,1.4146258186]</t>
         </is>
       </c>
     </row>
@@ -16162,7 +16162,7 @@
       </c>
       <c r="D605" s="4" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>MC</t>
         </is>
       </c>
       <c r="E605" t="n">
@@ -16170,7 +16170,7 @@
       </c>
       <c r="F605" s="4" t="inlineStr">
         <is>
-          <t>[0,20.4297334611,1.9456889011,0,0]</t>
+          <t>[0,0,1.9456889011,0,0]</t>
         </is>
       </c>
     </row>
